--- a/data/NVDA_data.xlsx
+++ b/data/NVDA_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:H252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -433,22 +433,22 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Close</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Open</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -469,17 +469,25 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45911</v>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+        <v>45915</v>
+      </c>
+      <c r="B2" t="n">
+        <v>175.2501493971494</v>
+      </c>
+      <c r="C2" t="n">
+        <v>178.4225571584428</v>
+      </c>
+      <c r="D2" t="n">
+        <v>174.0929181271268</v>
+      </c>
+      <c r="E2" t="n">
+        <v>177.3251800537109</v>
+      </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>147061600</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -487,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45912</v>
+        <v>45916</v>
       </c>
       <c r="B3" t="n">
-        <v>177.3949890136719</v>
+        <v>176.5769643945311</v>
       </c>
       <c r="C3" t="n">
-        <v>178.1731234709029</v>
+        <v>177.0757693786965</v>
       </c>
       <c r="D3" t="n">
-        <v>176.0282531820179</v>
+        <v>173.9632311486472</v>
       </c>
       <c r="E3" t="n">
-        <v>177.34510547722</v>
+        <v>174.4620361328125</v>
       </c>
       <c r="F3" t="n">
-        <v>124911000</v>
+        <v>140737800</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -513,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45915</v>
+        <v>45917</v>
       </c>
       <c r="B4" t="n">
-        <v>177.3251647949219</v>
+        <v>172.2273696616015</v>
       </c>
       <c r="C4" t="n">
-        <v>178.4225418052247</v>
+        <v>172.7860287607356</v>
       </c>
       <c r="D4" t="n">
-        <v>174.0929031464731</v>
+        <v>168.007484117061</v>
       </c>
       <c r="E4" t="n">
-        <v>175.2501343169162</v>
+        <v>169.8829803466797</v>
       </c>
       <c r="F4" t="n">
-        <v>147061600</v>
+        <v>211843800</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -539,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45916</v>
+        <v>45918</v>
       </c>
       <c r="B5" t="n">
-        <v>174.4620208740234</v>
+        <v>173.5641783462465</v>
       </c>
       <c r="C5" t="n">
-        <v>177.0757538913052</v>
+        <v>176.6767318043244</v>
       </c>
       <c r="D5" t="n">
-        <v>173.9632159334845</v>
+        <v>172.5466271367534</v>
       </c>
       <c r="E5" t="n">
-        <v>176.5769489507663</v>
+        <v>175.8187866210938</v>
       </c>
       <c r="F5" t="n">
-        <v>140737800</v>
+        <v>191763300</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -565,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45917</v>
+        <v>45919</v>
       </c>
       <c r="B6" t="n">
-        <v>169.8829956054688</v>
+        <v>175.349898865447</v>
       </c>
       <c r="C6" t="n">
-        <v>172.7860442802747</v>
+        <v>177.6543753314711</v>
       </c>
       <c r="D6" t="n">
-        <v>168.0074992073941</v>
+        <v>174.7612974471592</v>
       </c>
       <c r="E6" t="n">
-        <v>172.2273851309623</v>
+        <v>176.2477416992188</v>
       </c>
       <c r="F6" t="n">
-        <v>211843800</v>
+        <v>237182100</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -591,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45918</v>
+        <v>45922</v>
       </c>
       <c r="B7" t="n">
-        <v>175.8187866210938</v>
+        <v>174.8810218455756</v>
       </c>
       <c r="C7" t="n">
-        <v>176.6767318043244</v>
+        <v>184.1089135963474</v>
       </c>
       <c r="D7" t="n">
-        <v>172.5466271367534</v>
+        <v>174.2924356467209</v>
       </c>
       <c r="E7" t="n">
-        <v>173.5641783462465</v>
+        <v>183.1711578369141</v>
       </c>
       <c r="F7" t="n">
-        <v>191763300</v>
+        <v>269637000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -617,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45919</v>
+        <v>45923</v>
       </c>
       <c r="B8" t="n">
-        <v>176.2477416992188</v>
+        <v>181.5350878652714</v>
       </c>
       <c r="C8" t="n">
-        <v>177.6543753314711</v>
+        <v>181.9840093083128</v>
       </c>
       <c r="D8" t="n">
-        <v>174.7612974471592</v>
+        <v>175.7888599052367</v>
       </c>
       <c r="E8" t="n">
-        <v>175.349898865447</v>
+        <v>178.0035400390625</v>
       </c>
       <c r="F8" t="n">
-        <v>237182100</v>
+        <v>192559600</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -643,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45922</v>
+        <v>45924</v>
       </c>
       <c r="B9" t="n">
-        <v>183.1711578369141</v>
+        <v>179.3403383898065</v>
       </c>
       <c r="C9" t="n">
-        <v>184.1089135963474</v>
+        <v>179.3503090089054</v>
       </c>
       <c r="D9" t="n">
-        <v>174.2924356467209</v>
+        <v>174.9807727171775</v>
       </c>
       <c r="E9" t="n">
-        <v>174.8810218455756</v>
+        <v>176.5470275878906</v>
       </c>
       <c r="F9" t="n">
-        <v>269637000</v>
+        <v>143564100</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -669,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45923</v>
+        <v>45925</v>
       </c>
       <c r="B10" t="n">
-        <v>178.0035400390625</v>
+        <v>174.0629701066951</v>
       </c>
       <c r="C10" t="n">
-        <v>181.9840093083128</v>
+        <v>179.8291540783439</v>
       </c>
       <c r="D10" t="n">
-        <v>175.7888599052367</v>
+        <v>172.7162058826927</v>
       </c>
       <c r="E10" t="n">
-        <v>181.5350878652714</v>
+        <v>177.2653045654297</v>
       </c>
       <c r="F10" t="n">
-        <v>192559600</v>
+        <v>191586700</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -695,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45924</v>
+        <v>45926</v>
       </c>
       <c r="B11" t="n">
-        <v>176.5470275878906</v>
+        <v>177.7441426621237</v>
       </c>
       <c r="C11" t="n">
-        <v>179.3503090089054</v>
+        <v>179.3403244887289</v>
       </c>
       <c r="D11" t="n">
-        <v>174.9807727171775</v>
+        <v>174.5118813132914</v>
       </c>
       <c r="E11" t="n">
-        <v>179.3403383898065</v>
+        <v>177.7640991210938</v>
       </c>
       <c r="F11" t="n">
-        <v>143564100</v>
+        <v>148573700</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -721,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45925</v>
+        <v>45929</v>
       </c>
       <c r="B12" t="n">
-        <v>177.2653045654297</v>
+        <v>179.9987400973632</v>
       </c>
       <c r="C12" t="n">
-        <v>179.8291540783439</v>
+        <v>183.5602146114836</v>
       </c>
       <c r="D12" t="n">
-        <v>172.7162058826927</v>
+        <v>179.8890176259668</v>
       </c>
       <c r="E12" t="n">
-        <v>174.0629701066951</v>
+        <v>181.4153594970703</v>
       </c>
       <c r="F12" t="n">
-        <v>191586700</v>
+        <v>193063500</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -747,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45926</v>
+        <v>45930</v>
       </c>
       <c r="B13" t="n">
-        <v>177.7641143798828</v>
+        <v>181.6448190078555</v>
       </c>
       <c r="C13" t="n">
-        <v>179.3403398828169</v>
+        <v>186.9022276338177</v>
       </c>
       <c r="D13" t="n">
-        <v>174.5118962929188</v>
+        <v>181.0462469572146</v>
       </c>
       <c r="E13" t="n">
-        <v>177.7441579191998</v>
+        <v>186.1340637207031</v>
       </c>
       <c r="F13" t="n">
-        <v>148573700</v>
+        <v>236981000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -773,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45929</v>
+        <v>45931</v>
       </c>
       <c r="B14" t="n">
-        <v>181.4153747558594</v>
+        <v>184.7972606974542</v>
       </c>
       <c r="C14" t="n">
-        <v>183.5602300506758</v>
+        <v>187.6903232769056</v>
       </c>
       <c r="D14" t="n">
-        <v>179.8890327563757</v>
+        <v>183.4604518817237</v>
       </c>
       <c r="E14" t="n">
-        <v>179.9987552370008</v>
+        <v>186.79248046875</v>
       </c>
       <c r="F14" t="n">
-        <v>193063500</v>
+        <v>173844900</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -799,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45930</v>
+        <v>45932</v>
       </c>
       <c r="B15" t="n">
-        <v>186.1340637207031</v>
+        <v>189.146847340247</v>
       </c>
       <c r="C15" t="n">
-        <v>186.9022276338177</v>
+        <v>190.59337868299</v>
       </c>
       <c r="D15" t="n">
-        <v>181.0462469572146</v>
+        <v>187.6105195355423</v>
       </c>
       <c r="E15" t="n">
-        <v>181.6448190078555</v>
+        <v>188.4385375976562</v>
       </c>
       <c r="F15" t="n">
-        <v>236981000</v>
+        <v>136805800</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -825,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="B16" t="n">
-        <v>186.79248046875</v>
+        <v>188.7378401044004</v>
       </c>
       <c r="C16" t="n">
-        <v>187.6903232769056</v>
+        <v>189.9050419886609</v>
       </c>
       <c r="D16" t="n">
-        <v>183.4604518817237</v>
+        <v>184.9369484043502</v>
       </c>
       <c r="E16" t="n">
-        <v>184.7972606974542</v>
+        <v>187.1715850830078</v>
       </c>
       <c r="F16" t="n">
-        <v>173844900</v>
+        <v>137596900</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -851,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45932</v>
+        <v>45936</v>
       </c>
       <c r="B17" t="n">
-        <v>188.4385528564453</v>
+        <v>185.0566446584491</v>
       </c>
       <c r="C17" t="n">
-        <v>190.593394116267</v>
+        <v>186.7825055997528</v>
       </c>
       <c r="D17" t="n">
-        <v>187.6105347272827</v>
+        <v>182.8918329061041</v>
       </c>
       <c r="E17" t="n">
-        <v>189.1468626563914</v>
+        <v>185.0965423583984</v>
       </c>
       <c r="F17" t="n">
-        <v>136805800</v>
+        <v>157678100</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -877,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45933</v>
+        <v>45937</v>
       </c>
       <c r="B18" t="n">
-        <v>187.1715545654297</v>
+        <v>185.7848907820332</v>
       </c>
       <c r="C18" t="n">
-        <v>189.9050110254035</v>
+        <v>188.6081286768816</v>
       </c>
       <c r="D18" t="n">
-        <v>184.9369182511207</v>
+        <v>183.5602249269612</v>
       </c>
       <c r="E18" t="n">
-        <v>188.7378093314507</v>
+        <v>184.5977325439453</v>
       </c>
       <c r="F18" t="n">
-        <v>137596900</v>
+        <v>140088000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -903,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45936</v>
+        <v>45938</v>
       </c>
       <c r="B19" t="n">
-        <v>185.0965423583984</v>
+        <v>186.1240823667868</v>
       </c>
       <c r="C19" t="n">
-        <v>186.7825055997528</v>
+        <v>189.1468390813163</v>
       </c>
       <c r="D19" t="n">
-        <v>182.8918329061041</v>
+        <v>186.094140065894</v>
       </c>
       <c r="E19" t="n">
-        <v>185.0566446584491</v>
+        <v>188.6580047607422</v>
       </c>
       <c r="F19" t="n">
-        <v>157678100</v>
+        <v>130168900</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -929,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45937</v>
+        <v>45939</v>
       </c>
       <c r="B20" t="n">
-        <v>184.5977325439453</v>
+        <v>191.7705422839889</v>
       </c>
       <c r="C20" t="n">
-        <v>188.6081286768816</v>
+        <v>194.8332119113436</v>
       </c>
       <c r="D20" t="n">
-        <v>183.5602249269612</v>
+        <v>190.6033405552435</v>
       </c>
       <c r="E20" t="n">
-        <v>185.7848907820332</v>
+        <v>192.1097412109375</v>
       </c>
       <c r="F20" t="n">
-        <v>140088000</v>
+        <v>182997200</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -955,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45938</v>
+        <v>45940</v>
       </c>
       <c r="B21" t="n">
-        <v>188.6580047607422</v>
+        <v>193.0474821132437</v>
       </c>
       <c r="C21" t="n">
-        <v>189.1468390813163</v>
+        <v>195.1524395658232</v>
       </c>
       <c r="D21" t="n">
-        <v>186.094140065894</v>
+        <v>181.6148814298513</v>
       </c>
       <c r="E21" t="n">
-        <v>186.1240823667868</v>
+        <v>182.7222290039062</v>
       </c>
       <c r="F21" t="n">
-        <v>130168900</v>
+        <v>268774400</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -981,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45939</v>
+        <v>45943</v>
       </c>
       <c r="B22" t="n">
-        <v>192.1097412109375</v>
+        <v>187.5207340107304</v>
       </c>
       <c r="C22" t="n">
-        <v>194.8332119113436</v>
+        <v>189.6556185865847</v>
       </c>
       <c r="D22" t="n">
-        <v>190.6033405552435</v>
+        <v>185.5155435929421</v>
       </c>
       <c r="E22" t="n">
-        <v>191.7705422839889</v>
+        <v>187.8699035644531</v>
       </c>
       <c r="F22" t="n">
-        <v>182997200</v>
+        <v>153482800</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1007,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45940</v>
+        <v>45944</v>
       </c>
       <c r="B23" t="n">
-        <v>182.7222290039062</v>
+        <v>184.3283927796865</v>
       </c>
       <c r="C23" t="n">
-        <v>195.1524395658232</v>
+        <v>184.3583198600852</v>
       </c>
       <c r="D23" t="n">
-        <v>181.6148814298513</v>
+        <v>179.2705030798172</v>
       </c>
       <c r="E23" t="n">
-        <v>193.0474821132437</v>
+        <v>179.5997161865234</v>
       </c>
       <c r="F23" t="n">
-        <v>268774400</v>
+        <v>205641400</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1033,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45943</v>
+        <v>45945</v>
       </c>
       <c r="B24" t="n">
-        <v>187.8699035644531</v>
+        <v>184.3582990595379</v>
       </c>
       <c r="C24" t="n">
-        <v>189.6556185865847</v>
+        <v>184.4281238318171</v>
       </c>
       <c r="D24" t="n">
-        <v>185.5155435929421</v>
+        <v>176.8662395170747</v>
       </c>
       <c r="E24" t="n">
-        <v>187.5207340107304</v>
+        <v>179.4001770019531</v>
       </c>
       <c r="F24" t="n">
-        <v>153482800</v>
+        <v>214450500</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1059,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45944</v>
+        <v>45946</v>
       </c>
       <c r="B25" t="n">
-        <v>179.5997161865234</v>
+        <v>181.7944368108431</v>
       </c>
       <c r="C25" t="n">
-        <v>184.3583198600852</v>
+        <v>182.8419301869027</v>
       </c>
       <c r="D25" t="n">
-        <v>179.2705030798172</v>
+        <v>179.3403251298876</v>
       </c>
       <c r="E25" t="n">
-        <v>184.3283927796865</v>
+        <v>181.3754425048828</v>
       </c>
       <c r="F25" t="n">
-        <v>205641400</v>
+        <v>179723300</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1085,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45945</v>
+        <v>45947</v>
       </c>
       <c r="B26" t="n">
-        <v>179.4001922607422</v>
+        <v>179.7493465774322</v>
       </c>
       <c r="C26" t="n">
-        <v>184.4281395182556</v>
+        <v>183.6599908268075</v>
       </c>
       <c r="D26" t="n">
-        <v>176.866254560341</v>
+        <v>179.3203816221287</v>
       </c>
       <c r="E26" t="n">
-        <v>184.3583147400375</v>
+        <v>182.7820892333984</v>
       </c>
       <c r="F26" t="n">
-        <v>214450500</v>
+        <v>173135200</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1111,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45946</v>
+        <v>45950</v>
       </c>
       <c r="B27" t="n">
-        <v>181.3754577636719</v>
+        <v>182.6922949953283</v>
       </c>
       <c r="C27" t="n">
-        <v>182.8419455690647</v>
+        <v>184.7573394499357</v>
       </c>
       <c r="D27" t="n">
-        <v>179.3403402174659</v>
+        <v>181.2956320849819</v>
       </c>
       <c r="E27" t="n">
-        <v>181.7944521048813</v>
+        <v>182.2034606933594</v>
       </c>
       <c r="F27" t="n">
-        <v>179723300</v>
+        <v>128544700</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1137,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45947</v>
+        <v>45951</v>
       </c>
       <c r="B28" t="n">
-        <v>182.7821044921875</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="C28" t="n">
-        <v>183.6600061588844</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="D28" t="n">
-        <v>179.3203965919317</v>
+        <v>179.3702701372806</v>
       </c>
       <c r="E28" t="n">
-        <v>179.7493615830456</v>
+        <v>180.7270202636719</v>
       </c>
       <c r="F28" t="n">
-        <v>173135200</v>
+        <v>124240200</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1163,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45950</v>
+        <v>45952</v>
       </c>
       <c r="B29" t="n">
-        <v>182.2034759521484</v>
+        <v>180.7070662621498</v>
       </c>
       <c r="C29" t="n">
-        <v>184.7573549226016</v>
+        <v>183.0015721983185</v>
       </c>
       <c r="D29" t="n">
-        <v>181.2956472677441</v>
+        <v>176.3375297972393</v>
       </c>
       <c r="E29" t="n">
-        <v>182.6923102950553</v>
+        <v>179.84912109375</v>
       </c>
       <c r="F29" t="n">
-        <v>128544700</v>
+        <v>162249600</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1189,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="B30" t="n">
-        <v>180.7270202636719</v>
+        <v>179.988793025541</v>
       </c>
       <c r="C30" t="n">
-        <v>182.3531141136141</v>
+        <v>182.5925557149365</v>
       </c>
       <c r="D30" t="n">
-        <v>179.3702701372806</v>
+        <v>179.3602938591047</v>
       </c>
       <c r="E30" t="n">
-        <v>182.3531141136141</v>
+        <v>181.7246398925781</v>
       </c>
       <c r="F30" t="n">
-        <v>124240200</v>
+        <v>111363700</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1215,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45952</v>
+        <v>45954</v>
       </c>
       <c r="B31" t="n">
-        <v>179.8491058349609</v>
+        <v>183.400590081168</v>
       </c>
       <c r="C31" t="n">
-        <v>183.0015566720687</v>
+        <v>187.0219186862977</v>
       </c>
       <c r="D31" t="n">
-        <v>176.3375148363812</v>
+        <v>183.0614063875393</v>
       </c>
       <c r="E31" t="n">
-        <v>180.7070509305708</v>
+        <v>185.8148040771484</v>
       </c>
       <c r="F31" t="n">
-        <v>162249600</v>
+        <v>131296700</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1241,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45953</v>
+        <v>45957</v>
       </c>
       <c r="B32" t="n">
-        <v>181.7246398925781</v>
+        <v>189.5359184602369</v>
       </c>
       <c r="C32" t="n">
-        <v>182.5925557149365</v>
+        <v>191.5411089646758</v>
       </c>
       <c r="D32" t="n">
-        <v>179.3602938591047</v>
+        <v>187.9796341631504</v>
       </c>
       <c r="E32" t="n">
-        <v>179.988793025541</v>
+        <v>191.0323333740234</v>
       </c>
       <c r="F32" t="n">
-        <v>111363700</v>
+        <v>153452700</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1267,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="B33" t="n">
-        <v>185.8148040771484</v>
+        <v>192.588592118433</v>
       </c>
       <c r="C33" t="n">
-        <v>187.0219186862977</v>
+        <v>202.6644428640734</v>
       </c>
       <c r="D33" t="n">
-        <v>183.0614063875393</v>
+        <v>191.4513174538508</v>
       </c>
       <c r="E33" t="n">
-        <v>183.400590081168</v>
+        <v>200.5495147705078</v>
       </c>
       <c r="F33" t="n">
-        <v>131296700</v>
+        <v>297986200</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1293,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45957</v>
+        <v>45959</v>
       </c>
       <c r="B34" t="n">
-        <v>191.0323333740234</v>
+        <v>207.482906515472</v>
       </c>
       <c r="C34" t="n">
-        <v>191.5411089646758</v>
+        <v>211.6828509687219</v>
       </c>
       <c r="D34" t="n">
-        <v>187.9796341631504</v>
+        <v>204.2905578218423</v>
       </c>
       <c r="E34" t="n">
-        <v>189.5359184602369</v>
+        <v>206.5451507568359</v>
       </c>
       <c r="F34" t="n">
-        <v>153452700</v>
+        <v>308829600</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1319,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45958</v>
+        <v>45960</v>
       </c>
       <c r="B35" t="n">
-        <v>200.5495300292969</v>
+        <v>204.6596525726598</v>
       </c>
       <c r="C35" t="n">
-        <v>202.6644582837766</v>
+        <v>205.6672482532724</v>
       </c>
       <c r="D35" t="n">
-        <v>191.4513320204045</v>
+        <v>200.9286015136062</v>
       </c>
       <c r="E35" t="n">
-        <v>192.5886067715161</v>
+        <v>202.4050598144531</v>
       </c>
       <c r="F35" t="n">
-        <v>297986200</v>
+        <v>178864400</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1345,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45959</v>
+        <v>45961</v>
       </c>
       <c r="B36" t="n">
-        <v>206.545166015625</v>
+        <v>205.9565693232556</v>
       </c>
       <c r="C36" t="n">
-        <v>211.6828666070652</v>
+        <v>207.4729406961805</v>
       </c>
       <c r="D36" t="n">
-        <v>204.2905729140704</v>
+        <v>201.5870481318289</v>
       </c>
       <c r="E36" t="n">
-        <v>207.482921843539</v>
+        <v>202.0060424804688</v>
       </c>
       <c r="F36" t="n">
-        <v>308829600</v>
+        <v>179802200</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1371,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45960</v>
+        <v>45964</v>
       </c>
       <c r="B37" t="n">
-        <v>202.4050750732422</v>
+        <v>207.5826726752522</v>
       </c>
       <c r="C37" t="n">
-        <v>205.6672637579894</v>
+        <v>210.8348755139714</v>
       </c>
       <c r="D37" t="n">
-        <v>200.9286166610889</v>
+        <v>205.0686914304077</v>
       </c>
       <c r="E37" t="n">
-        <v>204.6596680014167</v>
+        <v>206.3855438232422</v>
       </c>
       <c r="F37" t="n">
-        <v>178864400</v>
+        <v>180267300</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1397,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45961</v>
+        <v>45965</v>
       </c>
       <c r="B38" t="n">
-        <v>202.0060272216797</v>
+        <v>202.5148147488263</v>
       </c>
       <c r="C38" t="n">
-        <v>207.4729250244422</v>
+        <v>203.4824975937368</v>
       </c>
       <c r="D38" t="n">
-        <v>201.5870329046891</v>
+        <v>197.4569251230167</v>
       </c>
       <c r="E38" t="n">
-        <v>205.9565537660584</v>
+        <v>198.2151184082031</v>
       </c>
       <c r="F38" t="n">
-        <v>179802200</v>
+        <v>188919300</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1423,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="B39" t="n">
-        <v>206.3855438232422</v>
+        <v>198.2949275919373</v>
       </c>
       <c r="C39" t="n">
-        <v>210.8348755139714</v>
+        <v>202.4350026612236</v>
       </c>
       <c r="D39" t="n">
-        <v>205.0686914304077</v>
+        <v>194.1847643800754</v>
       </c>
       <c r="E39" t="n">
-        <v>207.5826726752522</v>
+        <v>194.7434387207031</v>
       </c>
       <c r="F39" t="n">
-        <v>180267300</v>
+        <v>171350300</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1449,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="B40" t="n">
-        <v>198.2151184082031</v>
+        <v>195.9505410878136</v>
       </c>
       <c r="C40" t="n">
-        <v>203.4824975937368</v>
+        <v>197.1476699621838</v>
       </c>
       <c r="D40" t="n">
-        <v>197.4569251230167</v>
+        <v>185.9345440647224</v>
       </c>
       <c r="E40" t="n">
-        <v>202.5148147488263</v>
+        <v>187.6304779052734</v>
       </c>
       <c r="F40" t="n">
-        <v>188919300</v>
+        <v>223029800</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1475,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45966</v>
+        <v>45968</v>
       </c>
       <c r="B41" t="n">
-        <v>194.7434387207031</v>
+        <v>184.4580698535366</v>
       </c>
       <c r="C41" t="n">
-        <v>202.4350026612236</v>
+        <v>187.8699092076593</v>
       </c>
       <c r="D41" t="n">
-        <v>194.1847643800754</v>
+        <v>178.4823961188316</v>
       </c>
       <c r="E41" t="n">
-        <v>198.2949275919373</v>
+        <v>187.7003021240234</v>
       </c>
       <c r="F41" t="n">
-        <v>171350300</v>
+        <v>264942300</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1501,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45967</v>
+        <v>45971</v>
       </c>
       <c r="B42" t="n">
-        <v>187.6304779052734</v>
+        <v>194.6436639125443</v>
       </c>
       <c r="C42" t="n">
-        <v>197.1476699621838</v>
+        <v>199.4621214501376</v>
       </c>
       <c r="D42" t="n">
-        <v>185.9345440647224</v>
+        <v>193.3268115668235</v>
       </c>
       <c r="E42" t="n">
-        <v>195.9505410878136</v>
+        <v>198.5742492675781</v>
       </c>
       <c r="F42" t="n">
-        <v>223029800</v>
+        <v>198897100</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1527,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45968</v>
+        <v>45972</v>
       </c>
       <c r="B43" t="n">
-        <v>187.7003021240234</v>
+        <v>194.6935689756818</v>
       </c>
       <c r="C43" t="n">
-        <v>187.8699092076593</v>
+        <v>194.9529420926121</v>
       </c>
       <c r="D43" t="n">
-        <v>178.4823961188316</v>
+        <v>190.8427938118383</v>
       </c>
       <c r="E43" t="n">
-        <v>184.4580698535366</v>
+        <v>192.6983489990234</v>
       </c>
       <c r="F43" t="n">
-        <v>264942300</v>
+        <v>176483300</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1553,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
       <c r="B44" t="n">
-        <v>198.5742645263672</v>
+        <v>195.2522318976041</v>
       </c>
       <c r="C44" t="n">
-        <v>199.4621367771523</v>
+        <v>195.4218237722109</v>
       </c>
       <c r="D44" t="n">
-        <v>193.3268264223904</v>
+        <v>190.6732056162565</v>
       </c>
       <c r="E44" t="n">
-        <v>194.6436788693004</v>
+        <v>193.3368225097656</v>
       </c>
       <c r="F44" t="n">
-        <v>198897100</v>
+        <v>154935300</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1579,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45972</v>
+        <v>45974</v>
       </c>
       <c r="B45" t="n">
-        <v>192.6983337402344</v>
+        <v>190.5933791327836</v>
       </c>
       <c r="C45" t="n">
-        <v>194.9529266552934</v>
+        <v>190.9824463944715</v>
       </c>
       <c r="D45" t="n">
-        <v>190.8427786999811</v>
+        <v>183.4105907203728</v>
       </c>
       <c r="E45" t="n">
-        <v>194.6935535589016</v>
+        <v>186.4133911132812</v>
       </c>
       <c r="F45" t="n">
-        <v>176483300</v>
+        <v>207423100</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1605,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45973</v>
+        <v>45975</v>
       </c>
       <c r="B46" t="n">
-        <v>193.3368072509766</v>
+        <v>182.4229435613052</v>
       </c>
       <c r="C46" t="n">
-        <v>195.4218083488666</v>
+        <v>190.553458007553</v>
       </c>
       <c r="D46" t="n">
-        <v>190.673190567689</v>
+        <v>180.1483942490048</v>
       </c>
       <c r="E46" t="n">
-        <v>195.2522164876445</v>
+        <v>189.7154693603516</v>
       </c>
       <c r="F46" t="n">
-        <v>154935300</v>
+        <v>186591900</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1631,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="B47" t="n">
-        <v>186.4133758544922</v>
+        <v>185.525507871713</v>
       </c>
       <c r="C47" t="n">
-        <v>190.9824307616844</v>
+        <v>188.5482645458532</v>
       </c>
       <c r="D47" t="n">
-        <v>183.4105757073767</v>
+        <v>183.8794576828592</v>
       </c>
       <c r="E47" t="n">
-        <v>190.5933635318434</v>
+        <v>186.1540069580078</v>
       </c>
       <c r="F47" t="n">
-        <v>207423100</v>
+        <v>173628900</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1657,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45975</v>
+        <v>45979</v>
       </c>
       <c r="B48" t="n">
-        <v>189.7154693603516</v>
+        <v>182.9417205846578</v>
       </c>
       <c r="C48" t="n">
-        <v>190.553458007553</v>
+        <v>184.3583249108488</v>
       </c>
       <c r="D48" t="n">
-        <v>180.1483942490048</v>
+        <v>179.2206244483882</v>
       </c>
       <c r="E48" t="n">
-        <v>182.4229435613052</v>
+        <v>180.9265441894531</v>
       </c>
       <c r="F48" t="n">
-        <v>186591900</v>
+        <v>213598900</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1683,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="B49" t="n">
-        <v>186.1540069580078</v>
+        <v>184.3483273978252</v>
       </c>
       <c r="C49" t="n">
-        <v>188.5482645458532</v>
+        <v>187.4109971087465</v>
       </c>
       <c r="D49" t="n">
-        <v>183.8794576828592</v>
+        <v>182.3930205111681</v>
       </c>
       <c r="E49" t="n">
-        <v>185.525507871713</v>
+        <v>186.0742034912109</v>
       </c>
       <c r="F49" t="n">
-        <v>173628900</v>
+        <v>247246400</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1709,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45979</v>
+        <v>45981</v>
       </c>
       <c r="B50" t="n">
-        <v>180.926513671875</v>
+        <v>195.4816571057099</v>
       </c>
       <c r="C50" t="n">
-        <v>184.358293814419</v>
+        <v>195.5315406452363</v>
       </c>
       <c r="D50" t="n">
-        <v>179.2205942185541</v>
+        <v>179.4201468289569</v>
       </c>
       <c r="E50" t="n">
-        <v>182.9416897271721</v>
+        <v>180.208251953125</v>
       </c>
       <c r="F50" t="n">
-        <v>213598900</v>
+        <v>343504800</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1735,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45980</v>
+        <v>45982</v>
       </c>
       <c r="B51" t="n">
-        <v>186.0741882324219</v>
+        <v>180.8068443722038</v>
       </c>
       <c r="C51" t="n">
-        <v>187.4109817403353</v>
+        <v>184.1189017022491</v>
       </c>
       <c r="D51" t="n">
-        <v>182.39300555425</v>
+        <v>172.5166923711864</v>
       </c>
       <c r="E51" t="n">
-        <v>184.3483122805645</v>
+        <v>178.4524841308594</v>
       </c>
       <c r="F51" t="n">
-        <v>247246400</v>
+        <v>346926200</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1761,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45981</v>
+        <v>45985</v>
       </c>
       <c r="B52" t="n">
-        <v>180.208251953125</v>
+        <v>179.0610243324759</v>
       </c>
       <c r="C52" t="n">
-        <v>195.5315406452363</v>
+        <v>183.0614349513779</v>
       </c>
       <c r="D52" t="n">
-        <v>179.4201468289569</v>
+        <v>176.0582084909882</v>
       </c>
       <c r="E52" t="n">
-        <v>195.4816571057099</v>
+        <v>182.1137084960938</v>
       </c>
       <c r="F52" t="n">
-        <v>343504800</v>
+        <v>256618300</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1787,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="B53" t="n">
-        <v>178.4524536132812</v>
+        <v>174.4919407266003</v>
       </c>
       <c r="C53" t="n">
-        <v>184.1188702156436</v>
+        <v>177.7341727058355</v>
       </c>
       <c r="D53" t="n">
-        <v>172.5166628687019</v>
+        <v>169.1447513765687</v>
       </c>
       <c r="E53" t="n">
-        <v>180.806813452001</v>
+        <v>177.3949890136719</v>
       </c>
       <c r="F53" t="n">
-        <v>346926200</v>
+        <v>320600300</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1813,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45985</v>
+        <v>45987</v>
       </c>
       <c r="B54" t="n">
-        <v>182.1136932373047</v>
+        <v>181.1959139436215</v>
       </c>
       <c r="C54" t="n">
-        <v>183.0614196131816</v>
+        <v>182.4728535594688</v>
       </c>
       <c r="D54" t="n">
-        <v>176.0581937395723</v>
+        <v>177.8140165634392</v>
       </c>
       <c r="E54" t="n">
-        <v>179.0610093294625</v>
+        <v>179.8291778564453</v>
       </c>
       <c r="F54" t="n">
-        <v>256618300</v>
+        <v>183852000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1839,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="B55" t="n">
-        <v>177.3949890136719</v>
+        <v>178.5821404669205</v>
       </c>
       <c r="C55" t="n">
-        <v>177.7341727058355</v>
+        <v>178.8614700176124</v>
       </c>
       <c r="D55" t="n">
-        <v>169.1447513765687</v>
+        <v>176.0781451295325</v>
       </c>
       <c r="E55" t="n">
-        <v>174.4919407266003</v>
+        <v>176.5769500732422</v>
       </c>
       <c r="F55" t="n">
-        <v>320600300</v>
+        <v>121332800</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1865,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45987</v>
+        <v>45992</v>
       </c>
       <c r="B56" t="n">
-        <v>179.8291473388672</v>
+        <v>174.3423041351479</v>
       </c>
       <c r="C56" t="n">
-        <v>182.4728225932506</v>
+        <v>179.8690716163194</v>
       </c>
       <c r="D56" t="n">
-        <v>177.8139863878403</v>
+        <v>173.2648835948944</v>
       </c>
       <c r="E56" t="n">
-        <v>181.1958831941039</v>
+        <v>179.4899749755859</v>
       </c>
       <c r="F56" t="n">
-        <v>183852000</v>
+        <v>188131000</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1891,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45989</v>
+        <v>45993</v>
       </c>
       <c r="B57" t="n">
-        <v>176.5769500732422</v>
+        <v>181.3255769560617</v>
       </c>
       <c r="C57" t="n">
-        <v>178.8614700176124</v>
+        <v>185.2162648499111</v>
       </c>
       <c r="D57" t="n">
-        <v>176.0781451295325</v>
+        <v>179.569788944198</v>
       </c>
       <c r="E57" t="n">
-        <v>178.5821404669205</v>
+        <v>181.0263061523438</v>
       </c>
       <c r="F57" t="n">
-        <v>121332800</v>
+        <v>182632200</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1917,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45992</v>
+        <v>45994</v>
       </c>
       <c r="B58" t="n">
-        <v>179.489990234375</v>
+        <v>180.6472109015755</v>
       </c>
       <c r="C58" t="n">
-        <v>179.8690869073362</v>
+        <v>182.0139316568558</v>
       </c>
       <c r="D58" t="n">
-        <v>173.2648983244765</v>
+        <v>178.681918089591</v>
       </c>
       <c r="E58" t="n">
-        <v>174.3423189563235</v>
+        <v>179.1607666015625</v>
       </c>
       <c r="F58" t="n">
-        <v>188131000</v>
+        <v>165138000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1943,25 +1951,25 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="B59" t="n">
-        <v>181.0263061523438</v>
+        <v>181.1960032737075</v>
       </c>
       <c r="C59" t="n">
-        <v>185.2162648499111</v>
+        <v>184.0892423581687</v>
       </c>
       <c r="D59" t="n">
-        <v>179.569788944198</v>
+        <v>179.5398901129937</v>
       </c>
       <c r="E59" t="n">
-        <v>181.3255769560617</v>
+        <v>182.951904296875</v>
       </c>
       <c r="F59" t="n">
-        <v>182632200</v>
+        <v>167364900</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -1969,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45994</v>
+        <v>45996</v>
       </c>
       <c r="B60" t="n">
-        <v>179.1607666015625</v>
+        <v>183.4607020047171</v>
       </c>
       <c r="C60" t="n">
-        <v>182.0139316568558</v>
+        <v>184.2289086763207</v>
       </c>
       <c r="D60" t="n">
-        <v>178.681918089591</v>
+        <v>180.4876631773748</v>
       </c>
       <c r="E60" t="n">
-        <v>180.6472109015755</v>
+        <v>181.9841613769531</v>
       </c>
       <c r="F60" t="n">
-        <v>165138000</v>
+        <v>143971100</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -1995,25 +2003,25 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45995</v>
+        <v>45999</v>
       </c>
       <c r="B61" t="n">
-        <v>182.9518890380859</v>
+        <v>182.2136112701494</v>
       </c>
       <c r="C61" t="n">
-        <v>184.089227004522</v>
+        <v>187.5610985176648</v>
       </c>
       <c r="D61" t="n">
-        <v>179.5398751387779</v>
+        <v>181.9741660895743</v>
       </c>
       <c r="E61" t="n">
-        <v>181.1959881613664</v>
+        <v>185.1168212890625</v>
       </c>
       <c r="F61" t="n">
-        <v>167364900</v>
+        <v>204378100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2021,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="B62" t="n">
-        <v>181.9841613769531</v>
+        <v>185.1268117532098</v>
       </c>
       <c r="C62" t="n">
-        <v>184.2289086763207</v>
+        <v>185.2864418902268</v>
       </c>
       <c r="D62" t="n">
-        <v>180.4876631773748</v>
+        <v>182.8920507276432</v>
       </c>
       <c r="E62" t="n">
-        <v>183.4607020047171</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="F62" t="n">
-        <v>143971100</v>
+        <v>144719700</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2047,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="B63" t="n">
-        <v>185.1168212890625</v>
+        <v>184.538176449994</v>
       </c>
       <c r="C63" t="n">
-        <v>187.5610985176648</v>
+        <v>185.0469803407326</v>
       </c>
       <c r="D63" t="n">
-        <v>181.9741660895743</v>
+        <v>181.6150088138297</v>
       </c>
       <c r="E63" t="n">
-        <v>182.2136112701494</v>
+        <v>183.3509521484375</v>
       </c>
       <c r="F63" t="n">
-        <v>204378100</v>
+        <v>162785400</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2073,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="B64" t="n">
-        <v>184.5381927490234</v>
+        <v>179.8591224369562</v>
       </c>
       <c r="C64" t="n">
-        <v>185.2864418902268</v>
+        <v>180.8967030087509</v>
       </c>
       <c r="D64" t="n">
-        <v>182.8920507276432</v>
+        <v>176.2076633109278</v>
       </c>
       <c r="E64" t="n">
-        <v>185.1268117532098</v>
+        <v>180.5075988769531</v>
       </c>
       <c r="F64" t="n">
-        <v>144719700</v>
+        <v>182136600</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2099,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="B65" t="n">
-        <v>183.3509521484375</v>
+        <v>180.6871831157045</v>
       </c>
       <c r="C65" t="n">
-        <v>185.0469803407326</v>
+        <v>182.3931976659576</v>
       </c>
       <c r="D65" t="n">
-        <v>181.6150088138297</v>
+        <v>174.2123291208211</v>
       </c>
       <c r="E65" t="n">
-        <v>184.538176449994</v>
+        <v>174.6114044189453</v>
       </c>
       <c r="F65" t="n">
-        <v>162785400</v>
+        <v>204274900</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2125,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="B66" t="n">
-        <v>180.5075988769531</v>
+        <v>177.5245903328353</v>
       </c>
       <c r="C66" t="n">
-        <v>180.8967030087509</v>
+        <v>178.0034654802094</v>
       </c>
       <c r="D66" t="n">
-        <v>176.2076633109278</v>
+        <v>174.6213802569945</v>
       </c>
       <c r="E66" t="n">
-        <v>179.8591224369562</v>
+        <v>175.8784332275391</v>
       </c>
       <c r="F66" t="n">
-        <v>182136600</v>
+        <v>164775600</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2151,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46003</v>
+        <v>46007</v>
       </c>
       <c r="B67" t="n">
-        <v>174.6114196777344</v>
+        <v>175.8485164107673</v>
       </c>
       <c r="C67" t="n">
-        <v>182.3932136047752</v>
+        <v>178.0733214473424</v>
       </c>
       <c r="D67" t="n">
-        <v>174.2123443447362</v>
+        <v>174.4916907151964</v>
       </c>
       <c r="E67" t="n">
-        <v>180.6871989054384</v>
+        <v>177.3051147460938</v>
       </c>
       <c r="F67" t="n">
-        <v>204274900</v>
+        <v>148588100</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2177,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="B68" t="n">
-        <v>175.8784332275391</v>
+        <v>175.6888968536916</v>
       </c>
       <c r="C68" t="n">
-        <v>178.0034654802094</v>
+        <v>175.7188256001934</v>
       </c>
       <c r="D68" t="n">
-        <v>174.6213802569945</v>
+        <v>169.9124052081842</v>
       </c>
       <c r="E68" t="n">
-        <v>177.5245903328353</v>
+        <v>170.5409393310547</v>
       </c>
       <c r="F68" t="n">
-        <v>164775600</v>
+        <v>222775500</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2203,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="B69" t="n">
-        <v>177.3050994873047</v>
+        <v>174.1225483861358</v>
       </c>
       <c r="C69" t="n">
-        <v>178.0733061224419</v>
+        <v>175.7387615308714</v>
       </c>
       <c r="D69" t="n">
-        <v>174.4916756985292</v>
+        <v>171.4188835631069</v>
       </c>
       <c r="E69" t="n">
-        <v>175.8485012773324</v>
+        <v>173.7334594726562</v>
       </c>
       <c r="F69" t="n">
-        <v>148588100</v>
+        <v>176096000</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2229,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="B70" t="n">
-        <v>170.5409393310547</v>
+        <v>176.2575523358494</v>
       </c>
       <c r="C70" t="n">
-        <v>175.7188256001934</v>
+        <v>181.0263919449467</v>
       </c>
       <c r="D70" t="n">
-        <v>169.9124052081842</v>
+        <v>175.9283209122297</v>
       </c>
       <c r="E70" t="n">
-        <v>175.6888968536916</v>
+        <v>180.5674743652344</v>
       </c>
       <c r="F70" t="n">
-        <v>222775500</v>
+        <v>324925900</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2255,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="B71" t="n">
-        <v>173.7334594726562</v>
+        <v>183.4906129473229</v>
       </c>
       <c r="C71" t="n">
-        <v>175.7387615308714</v>
+        <v>183.730058116363</v>
       </c>
       <c r="D71" t="n">
-        <v>171.4188835631069</v>
+        <v>181.9242862331203</v>
       </c>
       <c r="E71" t="n">
-        <v>174.1225483861358</v>
+        <v>183.2611541748047</v>
       </c>
       <c r="F71" t="n">
-        <v>176096000</v>
+        <v>129064400</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2281,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="B72" t="n">
-        <v>180.5674743652344</v>
+        <v>182.5428571096804</v>
       </c>
       <c r="C72" t="n">
-        <v>181.0263919449467</v>
+        <v>188.8880102762506</v>
       </c>
       <c r="D72" t="n">
-        <v>175.9283209122297</v>
+        <v>182.4730132178061</v>
       </c>
       <c r="E72" t="n">
-        <v>176.2575523358494</v>
+        <v>188.7682952880859</v>
       </c>
       <c r="F72" t="n">
-        <v>324925900</v>
+        <v>174873600</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2307,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="B73" t="n">
-        <v>183.2611694335938</v>
+        <v>187.5012437217294</v>
       </c>
       <c r="C73" t="n">
-        <v>183.7300734141942</v>
+        <v>188.4689804086018</v>
       </c>
       <c r="D73" t="n">
-        <v>181.9243013805983</v>
+        <v>186.154389299292</v>
       </c>
       <c r="E73" t="n">
-        <v>183.4906282252173</v>
+        <v>188.169677734375</v>
       </c>
       <c r="F73" t="n">
-        <v>129064400</v>
+        <v>65528500</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2333,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="B74" t="n">
-        <v>188.7682952880859</v>
+        <v>189.4766133088049</v>
       </c>
       <c r="C74" t="n">
-        <v>188.8880102762506</v>
+        <v>192.2401507638228</v>
       </c>
       <c r="D74" t="n">
-        <v>182.4730132178061</v>
+        <v>187.5610975436497</v>
       </c>
       <c r="E74" t="n">
-        <v>182.5428571096804</v>
+        <v>190.0851898193359</v>
       </c>
       <c r="F74" t="n">
-        <v>174873600</v>
+        <v>139740300</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2359,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="B75" t="n">
-        <v>188.169677734375</v>
+        <v>187.2717899684254</v>
       </c>
       <c r="C75" t="n">
-        <v>188.4689804086018</v>
+        <v>188.3193265216257</v>
       </c>
       <c r="D75" t="n">
-        <v>186.154389299292</v>
+        <v>185.4759890979627</v>
       </c>
       <c r="E75" t="n">
-        <v>187.5012437217294</v>
+        <v>187.7805938720703</v>
       </c>
       <c r="F75" t="n">
-        <v>65528500</v>
+        <v>120006100</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2385,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="B76" t="n">
-        <v>190.085205078125</v>
+        <v>187.8005508490403</v>
       </c>
       <c r="C76" t="n">
-        <v>192.240166195598</v>
+        <v>188.5487999407664</v>
       </c>
       <c r="D76" t="n">
-        <v>187.5611125998212</v>
+        <v>186.4935963146986</v>
       </c>
       <c r="E76" t="n">
-        <v>189.4766285187414</v>
+        <v>187.1021728515625</v>
       </c>
       <c r="F76" t="n">
-        <v>139740300</v>
+        <v>97687300</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2411,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46020</v>
+        <v>46022</v>
       </c>
       <c r="B77" t="n">
-        <v>187.7805938720703</v>
+        <v>189.127461449755</v>
       </c>
       <c r="C77" t="n">
-        <v>188.3193265216257</v>
+        <v>190.1151405796458</v>
       </c>
       <c r="D77" t="n">
-        <v>185.4759890979627</v>
+        <v>186.0546497967401</v>
       </c>
       <c r="E77" t="n">
-        <v>187.2717899684254</v>
+        <v>186.0646209716797</v>
       </c>
       <c r="F77" t="n">
-        <v>120006100</v>
+        <v>120100500</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2437,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46021</v>
+        <v>46024</v>
       </c>
       <c r="B78" t="n">
-        <v>187.1021881103516</v>
+        <v>189.3967976648124</v>
       </c>
       <c r="C78" t="n">
-        <v>188.5488153175326</v>
+        <v>192.479580126264</v>
       </c>
       <c r="D78" t="n">
-        <v>186.4936115238563</v>
+        <v>187.8204844911982</v>
       </c>
       <c r="E78" t="n">
-        <v>187.8005661647843</v>
+        <v>188.4091186523438</v>
       </c>
       <c r="F78" t="n">
-        <v>97687300</v>
+        <v>148240500</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2463,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46022</v>
+        <v>46027</v>
       </c>
       <c r="B79" t="n">
-        <v>186.0646057128906</v>
+        <v>191.3123337767646</v>
       </c>
       <c r="C79" t="n">
-        <v>190.1151249886817</v>
+        <v>193.1779786425506</v>
       </c>
       <c r="D79" t="n">
-        <v>186.0546345387688</v>
+        <v>185.7154296257417</v>
       </c>
       <c r="E79" t="n">
-        <v>189.1274459397885</v>
+        <v>187.6808319091797</v>
       </c>
       <c r="F79" t="n">
-        <v>120100500</v>
+        <v>183529700</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2489,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="B80" t="n">
-        <v>188.4091339111328</v>
+        <v>190.0752284670132</v>
       </c>
       <c r="C80" t="n">
-        <v>192.4795957147097</v>
+        <v>191.7213703933745</v>
       </c>
       <c r="D80" t="n">
-        <v>187.8204997023152</v>
+        <v>186.3838692947835</v>
       </c>
       <c r="E80" t="n">
-        <v>189.3968130035911</v>
+        <v>186.8028869628906</v>
       </c>
       <c r="F80" t="n">
-        <v>148240500</v>
+        <v>176862600</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2515,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="B81" t="n">
-        <v>187.6808319091797</v>
+        <v>188.1297701943655</v>
       </c>
       <c r="C81" t="n">
-        <v>193.1779786425506</v>
+        <v>190.9232211122124</v>
       </c>
       <c r="D81" t="n">
-        <v>185.7154296257417</v>
+        <v>186.1244530144955</v>
       </c>
       <c r="E81" t="n">
-        <v>191.3123337767646</v>
+        <v>188.6685028076172</v>
       </c>
       <c r="F81" t="n">
-        <v>183529700</v>
+        <v>153543200</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2541,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="B82" t="n">
-        <v>186.8029022216797</v>
+        <v>188.6685228499072</v>
       </c>
       <c r="C82" t="n">
-        <v>191.7213860539245</v>
+        <v>189.1074981045344</v>
       </c>
       <c r="D82" t="n">
-        <v>186.3838845193456</v>
+        <v>183.2811352524241</v>
       </c>
       <c r="E82" t="n">
-        <v>190.0752439930999</v>
+        <v>184.6080169677734</v>
       </c>
       <c r="F82" t="n">
-        <v>176862600</v>
+        <v>172457000</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2567,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B83" t="n">
-        <v>188.6685180664062</v>
+        <v>184.6479238968445</v>
       </c>
       <c r="C83" t="n">
-        <v>190.9232365533545</v>
+        <v>185.9049768874807</v>
       </c>
       <c r="D83" t="n">
-        <v>186.1244680675316</v>
+        <v>183.2412119543349</v>
       </c>
       <c r="E83" t="n">
-        <v>188.1297854095839</v>
+        <v>184.4284362792969</v>
       </c>
       <c r="F83" t="n">
-        <v>153543200</v>
+        <v>131327500</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2593,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="B84" t="n">
-        <v>184.6080017089844</v>
+        <v>182.7922691735387</v>
       </c>
       <c r="C84" t="n">
-        <v>189.1074824738404</v>
+        <v>186.6831584288149</v>
       </c>
       <c r="D84" t="n">
-        <v>183.2811201033086</v>
+        <v>182.5927391235801</v>
       </c>
       <c r="E84" t="n">
-        <v>188.6685072554968</v>
+        <v>184.5082550048828</v>
       </c>
       <c r="F84" t="n">
-        <v>172457000</v>
+        <v>137968500</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2619,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="B85" t="n">
-        <v>184.4284362792969</v>
+        <v>184.5681140987238</v>
       </c>
       <c r="C85" t="n">
-        <v>185.9049768874807</v>
+        <v>187.6708543554723</v>
       </c>
       <c r="D85" t="n">
-        <v>183.2412119543349</v>
+        <v>182.9718432388734</v>
       </c>
       <c r="E85" t="n">
-        <v>184.6479238968445</v>
+        <v>185.376220703125</v>
       </c>
       <c r="F85" t="n">
-        <v>131327500</v>
+        <v>160128900</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2645,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="B86" t="n">
-        <v>184.5082550048828</v>
+        <v>183.8897012556695</v>
       </c>
       <c r="C86" t="n">
-        <v>186.6831584288149</v>
+        <v>184.0293738083791</v>
       </c>
       <c r="D86" t="n">
-        <v>182.5927391235801</v>
+        <v>180.3779146434709</v>
       </c>
       <c r="E86" t="n">
-        <v>182.7922691735387</v>
+        <v>182.7124481201172</v>
       </c>
       <c r="F86" t="n">
-        <v>137968500</v>
+        <v>159586100</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2671,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="B87" t="n">
-        <v>185.376220703125</v>
+        <v>186.0646079796491</v>
       </c>
       <c r="C87" t="n">
-        <v>187.6708543554723</v>
+        <v>189.2571344016907</v>
       </c>
       <c r="D87" t="n">
-        <v>182.9718432388734</v>
+        <v>185.895006678512</v>
       </c>
       <c r="E87" t="n">
-        <v>184.5681140987238</v>
+        <v>186.6133270263672</v>
       </c>
       <c r="F87" t="n">
-        <v>160128900</v>
+        <v>206188600</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2697,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="B88" t="n">
-        <v>182.7124481201172</v>
+        <v>188.6385795892923</v>
       </c>
       <c r="C88" t="n">
-        <v>184.0293738083791</v>
+        <v>189.99540517049</v>
       </c>
       <c r="D88" t="n">
-        <v>180.3779146434709</v>
+        <v>185.6455833269296</v>
       </c>
       <c r="E88" t="n">
-        <v>183.8897012556695</v>
+        <v>185.7952270507812</v>
       </c>
       <c r="F88" t="n">
-        <v>159586100</v>
+        <v>187967200</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2723,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46037</v>
+        <v>46042</v>
       </c>
       <c r="B89" t="n">
-        <v>186.6133270263672</v>
+        <v>181.4753266272146</v>
       </c>
       <c r="C89" t="n">
-        <v>189.2571344016907</v>
+        <v>181.9542169705431</v>
       </c>
       <c r="D89" t="n">
-        <v>185.895006678512</v>
+        <v>177.1953488429791</v>
       </c>
       <c r="E89" t="n">
-        <v>186.0646079796491</v>
+        <v>177.6542816162109</v>
       </c>
       <c r="F89" t="n">
-        <v>206188600</v>
+        <v>223345300</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2749,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46038</v>
+        <v>46043</v>
       </c>
       <c r="B90" t="n">
-        <v>185.7952423095703</v>
+        <v>178.6320081827799</v>
       </c>
       <c r="C90" t="n">
-        <v>189.9954207742267</v>
+        <v>184.9472325313386</v>
       </c>
       <c r="D90" t="n">
-        <v>185.6455985734289</v>
+        <v>177.9835164834521</v>
       </c>
       <c r="E90" t="n">
-        <v>188.6385950815971</v>
+        <v>182.8920440673828</v>
       </c>
       <c r="F90" t="n">
-        <v>187967200</v>
+        <v>200381000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2775,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="B91" t="n">
-        <v>177.6542816162109</v>
+        <v>184.3186915464293</v>
       </c>
       <c r="C91" t="n">
-        <v>181.9542169705431</v>
+        <v>185.7353746560278</v>
       </c>
       <c r="D91" t="n">
-        <v>177.1953488429791</v>
+        <v>183.5005985718231</v>
       </c>
       <c r="E91" t="n">
-        <v>181.4753266272146</v>
+        <v>184.4084777832031</v>
       </c>
       <c r="F91" t="n">
-        <v>223345300</v>
+        <v>139636600</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2801,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="B92" t="n">
-        <v>182.8920440673828</v>
+        <v>187.0622712594319</v>
       </c>
       <c r="C92" t="n">
-        <v>184.9472325313386</v>
+        <v>189.1573747868041</v>
       </c>
       <c r="D92" t="n">
-        <v>177.9835164834521</v>
+        <v>186.3838660627843</v>
       </c>
       <c r="E92" t="n">
-        <v>178.6320081827799</v>
+        <v>187.2318725585938</v>
       </c>
       <c r="F92" t="n">
-        <v>200381000</v>
+        <v>142748100</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2827,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="B93" t="n">
-        <v>184.4084777832031</v>
+        <v>186.7230748442759</v>
       </c>
       <c r="C93" t="n">
-        <v>185.7353746560278</v>
+        <v>188.6784906596197</v>
       </c>
       <c r="D93" t="n">
-        <v>183.5005985718231</v>
+        <v>185.555808059744</v>
       </c>
       <c r="E93" t="n">
-        <v>184.3186915464293</v>
+        <v>186.0346832275391</v>
       </c>
       <c r="F93" t="n">
-        <v>139636600</v>
+        <v>124799600</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2853,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="B94" t="n">
-        <v>187.2318725585938</v>
+        <v>186.8028844605491</v>
       </c>
       <c r="C94" t="n">
-        <v>189.1573747868041</v>
+        <v>189.5564356240106</v>
       </c>
       <c r="D94" t="n">
-        <v>186.3838660627843</v>
+        <v>185.2664711415707</v>
       </c>
       <c r="E94" t="n">
-        <v>187.0622712594319</v>
+        <v>188.0798950195312</v>
       </c>
       <c r="F94" t="n">
-        <v>142748100</v>
+        <v>143711600</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2879,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="B95" t="n">
-        <v>186.03466796875</v>
+        <v>190.8234748728661</v>
       </c>
       <c r="C95" t="n">
-        <v>188.6784751839824</v>
+        <v>191.9009553855833</v>
       </c>
       <c r="D95" t="n">
-        <v>185.5557928402329</v>
+        <v>189.3968053634026</v>
       </c>
       <c r="E95" t="n">
-        <v>186.7230595290241</v>
+        <v>191.0728912353516</v>
       </c>
       <c r="F95" t="n">
-        <v>124799600</v>
+        <v>148552700</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2905,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="B96" t="n">
-        <v>188.0798950195312</v>
+        <v>190.8932954336949</v>
       </c>
       <c r="C96" t="n">
-        <v>189.5564356240106</v>
+        <v>193.0282987969995</v>
       </c>
       <c r="D96" t="n">
-        <v>185.2664711415707</v>
+        <v>185.625623299501</v>
       </c>
       <c r="E96" t="n">
-        <v>186.8028844605491</v>
+        <v>192.0605621337891</v>
       </c>
       <c r="F96" t="n">
-        <v>143711600</v>
+        <v>171764400</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2931,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="B97" t="n">
-        <v>191.0728759765625</v>
+        <v>190.7636071727618</v>
       </c>
       <c r="C97" t="n">
-        <v>191.9009400606663</v>
+        <v>194.0359484555967</v>
       </c>
       <c r="D97" t="n">
-        <v>189.3967902384632</v>
+        <v>189.0276639024229</v>
       </c>
       <c r="E97" t="n">
-        <v>190.823459633995</v>
+        <v>190.6837921142578</v>
       </c>
       <c r="F97" t="n">
-        <v>148552700</v>
+        <v>179489500</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2957,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="B98" t="n">
-        <v>192.0605773925781</v>
+        <v>186.7629812920276</v>
       </c>
       <c r="C98" t="n">
-        <v>193.0283141326731</v>
+        <v>189.8557504766133</v>
       </c>
       <c r="D98" t="n">
-        <v>185.6256380470483</v>
+        <v>184.4484052141589</v>
       </c>
       <c r="E98" t="n">
-        <v>190.8933105997472</v>
+        <v>185.1766967773438</v>
       </c>
       <c r="F98" t="n">
-        <v>171764400</v>
+        <v>165794100</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2983,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="B99" t="n">
-        <v>190.6838073730469</v>
+        <v>185.8052108647954</v>
       </c>
       <c r="C99" t="n">
-        <v>194.0359639826301</v>
+        <v>185.8351396091497</v>
       </c>
       <c r="D99" t="n">
-        <v>189.0276790286862</v>
+        <v>175.8185703987175</v>
       </c>
       <c r="E99" t="n">
-        <v>190.7636224379378</v>
+        <v>179.9189758300781</v>
       </c>
       <c r="F99" t="n">
-        <v>179489500</v>
+        <v>204019600</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3009,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B100" t="n">
-        <v>185.1766815185547</v>
+        <v>179.0410414348666</v>
       </c>
       <c r="C100" t="n">
-        <v>189.8557348322644</v>
+        <v>179.160756412826</v>
       </c>
       <c r="D100" t="n">
-        <v>184.4483900153819</v>
+        <v>171.5086645338761</v>
       </c>
       <c r="E100" t="n">
-        <v>186.7629659025267</v>
+        <v>173.7833404541016</v>
       </c>
       <c r="F100" t="n">
-        <v>165794100</v>
+        <v>207014100</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3035,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="B101" t="n">
-        <v>179.9189758300781</v>
+        <v>174.5215964583249</v>
       </c>
       <c r="C101" t="n">
-        <v>185.8351396091497</v>
+        <v>176.4071986282528</v>
       </c>
       <c r="D101" t="n">
-        <v>175.8185703987175</v>
+        <v>170.6307075914073</v>
       </c>
       <c r="E101" t="n">
-        <v>185.8052108647954</v>
+        <v>171.4787292480469</v>
       </c>
       <c r="F101" t="n">
-        <v>204019600</v>
+        <v>206312900</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3061,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46057</v>
+        <v>46059</v>
       </c>
       <c r="B102" t="n">
-        <v>173.7833557128906</v>
+        <v>176.277498975506</v>
       </c>
       <c r="C102" t="n">
-        <v>179.1607721437711</v>
+        <v>186.5634266395524</v>
       </c>
       <c r="D102" t="n">
-        <v>171.5086795929406</v>
+        <v>174.1923819783884</v>
       </c>
       <c r="E102" t="n">
-        <v>179.0410571553003</v>
+        <v>184.9771423339844</v>
       </c>
       <c r="F102" t="n">
-        <v>207014100</v>
+        <v>231346200</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3087,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="B103" t="n">
-        <v>171.4787445068359</v>
+        <v>183.8298238555102</v>
       </c>
       <c r="C103" t="n">
-        <v>176.4072143255947</v>
+        <v>193.2078878887748</v>
       </c>
       <c r="D103" t="n">
-        <v>170.6307227747363</v>
+        <v>183.5205500126207</v>
       </c>
       <c r="E103" t="n">
-        <v>174.5216119878791</v>
+        <v>189.5963287353516</v>
       </c>
       <c r="F103" t="n">
-        <v>206312900</v>
+        <v>196387400</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3113,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="B104" t="n">
-        <v>184.9771575927734</v>
+        <v>190.933219719687</v>
       </c>
       <c r="C104" t="n">
-        <v>186.5634420291942</v>
+        <v>192.0306425866914</v>
       </c>
       <c r="D104" t="n">
-        <v>174.1923963475411</v>
+        <v>187.6808205923615</v>
       </c>
       <c r="E104" t="n">
-        <v>176.2775135166603</v>
+        <v>188.0998382568359</v>
       </c>
       <c r="F104" t="n">
-        <v>231346200</v>
+        <v>136764800</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3139,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46062</v>
+        <v>46064</v>
       </c>
       <c r="B105" t="n">
-        <v>189.5963439941406</v>
+        <v>192.0007297023972</v>
       </c>
       <c r="C105" t="n">
-        <v>193.2079034382237</v>
+        <v>192.8088363522974</v>
       </c>
       <c r="D105" t="n">
-        <v>183.5205647824287</v>
+        <v>188.3293278304631</v>
       </c>
       <c r="E105" t="n">
-        <v>183.8298386502086</v>
+        <v>189.6063385009766</v>
       </c>
       <c r="F105" t="n">
-        <v>196387400</v>
+        <v>144192700</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3165,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B106" t="n">
-        <v>188.0998382568359</v>
+        <v>192.5793648877844</v>
       </c>
       <c r="C106" t="n">
-        <v>192.0306425866914</v>
+        <v>193.1580126884611</v>
       </c>
       <c r="D106" t="n">
-        <v>187.6808205923615</v>
+        <v>186.0745817463215</v>
       </c>
       <c r="E106" t="n">
-        <v>190.933219719687</v>
+        <v>186.5035858154297</v>
       </c>
       <c r="F106" t="n">
-        <v>136764800</v>
+        <v>189932500</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3191,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="B107" t="n">
-        <v>189.6063385009766</v>
+        <v>187.042320465516</v>
       </c>
       <c r="C107" t="n">
-        <v>192.8088363522974</v>
+        <v>187.0622780376601</v>
       </c>
       <c r="D107" t="n">
-        <v>188.3293278304631</v>
+        <v>181.1660713803529</v>
       </c>
       <c r="E107" t="n">
-        <v>192.0007297023972</v>
+        <v>182.3832244873047</v>
       </c>
       <c r="F107" t="n">
-        <v>144192700</v>
+        <v>161888000</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3217,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46065</v>
+        <v>46070</v>
       </c>
       <c r="B108" t="n">
-        <v>186.5036010742188</v>
+        <v>181.3257085516038</v>
       </c>
       <c r="C108" t="n">
-        <v>193.158028491682</v>
+        <v>186.7130962790006</v>
       </c>
       <c r="D108" t="n">
-        <v>186.0745969700116</v>
+        <v>178.7617008539599</v>
       </c>
       <c r="E108" t="n">
-        <v>192.5793806436633</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="F108" t="n">
-        <v>189932500</v>
+        <v>162276900</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3243,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46066</v>
+        <v>46071</v>
       </c>
       <c r="B109" t="n">
-        <v>182.3832092285156</v>
+        <v>188.3093443160685</v>
       </c>
       <c r="C109" t="n">
-        <v>187.0622623874058</v>
+        <v>189.9255573932224</v>
       </c>
       <c r="D109" t="n">
-        <v>181.1660562233949</v>
+        <v>186.3239846890322</v>
       </c>
       <c r="E109" t="n">
-        <v>187.0423048169314</v>
+        <v>187.5411376953125</v>
       </c>
       <c r="F109" t="n">
-        <v>161888000</v>
+        <v>164749100</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3269,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="B110" t="n">
-        <v>184.5381927490234</v>
+        <v>186.62329889396</v>
       </c>
       <c r="C110" t="n">
-        <v>186.7130962790006</v>
+        <v>187.9900957055448</v>
       </c>
       <c r="D110" t="n">
-        <v>178.7617008539599</v>
+        <v>185.2265733363672</v>
       </c>
       <c r="E110" t="n">
-        <v>181.3257085516038</v>
+        <v>187.4613342285156</v>
       </c>
       <c r="F110" t="n">
-        <v>162276900</v>
+        <v>126554500</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3295,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B111" t="n">
-        <v>187.5411376953125</v>
+        <v>186.1344488846578</v>
       </c>
       <c r="C111" t="n">
-        <v>189.9255573932224</v>
+        <v>189.8856654675195</v>
       </c>
       <c r="D111" t="n">
-        <v>186.3239846890322</v>
+        <v>185.5059147845697</v>
       </c>
       <c r="E111" t="n">
-        <v>188.3093443160685</v>
+        <v>189.3768615722656</v>
       </c>
       <c r="F111" t="n">
-        <v>164749100</v>
+        <v>178422300</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3321,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46072</v>
+        <v>46076</v>
       </c>
       <c r="B112" t="n">
-        <v>187.4613189697266</v>
+        <v>190.9531700210539</v>
       </c>
       <c r="C112" t="n">
-        <v>187.9900804037161</v>
+        <v>193.4972200828311</v>
       </c>
       <c r="D112" t="n">
-        <v>185.226558259481</v>
+        <v>189.1374267327081</v>
       </c>
       <c r="E112" t="n">
-        <v>186.6232837033845</v>
+        <v>191.1028289794922</v>
       </c>
       <c r="F112" t="n">
-        <v>126554500</v>
+        <v>171584800</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3347,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="B113" t="n">
-        <v>189.3768615722656</v>
+        <v>191.0429698590405</v>
       </c>
       <c r="C113" t="n">
-        <v>189.8856654675195</v>
+        <v>193.3176459547985</v>
       </c>
       <c r="D113" t="n">
-        <v>185.5059147845697</v>
+        <v>186.9625064417709</v>
       </c>
       <c r="E113" t="n">
-        <v>186.1344488846578</v>
+        <v>192.3997955322266</v>
       </c>
       <c r="F113" t="n">
-        <v>178422300</v>
+        <v>175123600</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3373,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="B114" t="n">
-        <v>191.1028137207031</v>
+        <v>193.9960453222018</v>
       </c>
       <c r="C114" t="n">
-        <v>193.4972046328596</v>
+        <v>197.1686293956491</v>
       </c>
       <c r="D114" t="n">
-        <v>189.1374116308485</v>
+        <v>193.3375824661624</v>
       </c>
       <c r="E114" t="n">
-        <v>190.9531547742145</v>
+        <v>195.1034545898438</v>
       </c>
       <c r="F114" t="n">
-        <v>171584800</v>
+        <v>250637100</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3399,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B115" t="n">
-        <v>192.3997955322266</v>
+        <v>193.8164813019665</v>
       </c>
       <c r="C115" t="n">
-        <v>193.3176459547985</v>
+        <v>193.8364236513225</v>
       </c>
       <c r="D115" t="n">
-        <v>186.9625064417709</v>
+        <v>183.8897126034445</v>
       </c>
       <c r="E115" t="n">
-        <v>191.0429698590405</v>
+        <v>184.4583740234375</v>
       </c>
       <c r="F115" t="n">
-        <v>175123600</v>
+        <v>360807900</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3425,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="B116" t="n">
-        <v>195.1034545898438</v>
+        <v>180.8268714126474</v>
       </c>
       <c r="C116" t="n">
-        <v>197.1686293956491</v>
+        <v>182.1637395256691</v>
       </c>
       <c r="D116" t="n">
-        <v>193.3375824661624</v>
+        <v>175.9682453114839</v>
       </c>
       <c r="E116" t="n">
-        <v>193.9960453222018</v>
+        <v>176.7763519287109</v>
       </c>
       <c r="F116" t="n">
-        <v>250637100</v>
+        <v>311636500</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3451,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="B117" t="n">
-        <v>184.4583740234375</v>
+        <v>174.6014235260267</v>
       </c>
       <c r="C117" t="n">
-        <v>193.8364236513225</v>
+        <v>183.0317086895539</v>
       </c>
       <c r="D117" t="n">
-        <v>183.8897126034445</v>
+        <v>174.2322921838959</v>
       </c>
       <c r="E117" t="n">
-        <v>193.8164813019665</v>
+        <v>182.0539855957031</v>
       </c>
       <c r="F117" t="n">
-        <v>360807900</v>
+        <v>209095300</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3477,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46080</v>
+        <v>46084</v>
       </c>
       <c r="B118" t="n">
-        <v>176.7763366699219</v>
+        <v>178.0733135069376</v>
       </c>
       <c r="C118" t="n">
-        <v>182.1637238018573</v>
+        <v>180.4776756968921</v>
       </c>
       <c r="D118" t="n">
-        <v>175.9682301224481</v>
+        <v>176.5069714269912</v>
       </c>
       <c r="E118" t="n">
-        <v>180.82685580423</v>
+        <v>179.6296691894531</v>
       </c>
       <c r="F118" t="n">
-        <v>311636500</v>
+        <v>178099400</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3503,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="B119" t="n">
-        <v>182.0539703369141</v>
+        <v>180.0187649948852</v>
       </c>
       <c r="C119" t="n">
-        <v>183.0316933488174</v>
+        <v>184.2688145383873</v>
       </c>
       <c r="D119" t="n">
-        <v>174.2322775806792</v>
+        <v>179.6396472340209</v>
       </c>
       <c r="E119" t="n">
-        <v>174.6014088918714</v>
+        <v>182.6126861572266</v>
       </c>
       <c r="F119" t="n">
-        <v>209095300</v>
+        <v>177731200</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3529,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="B120" t="n">
-        <v>179.6296691894531</v>
+        <v>180.7470550179114</v>
       </c>
       <c r="C120" t="n">
-        <v>180.4776756968921</v>
+        <v>183.6303076754259</v>
       </c>
       <c r="D120" t="n">
-        <v>176.5069714269912</v>
+        <v>177.4647422536165</v>
       </c>
       <c r="E120" t="n">
-        <v>178.0733135069376</v>
+        <v>182.9119873046875</v>
       </c>
       <c r="F120" t="n">
-        <v>178099400</v>
+        <v>198779700</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3555,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="B121" t="n">
-        <v>182.6126861572266</v>
+        <v>179.420134514761</v>
       </c>
       <c r="C121" t="n">
-        <v>184.2688145383873</v>
+        <v>182.3333155363547</v>
       </c>
       <c r="D121" t="n">
-        <v>179.6396472340209</v>
+        <v>176.4071960911633</v>
       </c>
       <c r="E121" t="n">
-        <v>180.0187649948852</v>
+        <v>177.4048614501953</v>
       </c>
       <c r="F121" t="n">
-        <v>177731200</v>
+        <v>189021900</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3581,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="B122" t="n">
-        <v>182.9119720458984</v>
+        <v>176.4171820751478</v>
       </c>
       <c r="C122" t="n">
-        <v>183.6302923567135</v>
+        <v>182.4829897940845</v>
       </c>
       <c r="D122" t="n">
-        <v>177.4647274492447</v>
+        <v>175.1501427003192</v>
       </c>
       <c r="E122" t="n">
-        <v>180.7470399397241</v>
+        <v>182.2235870361328</v>
       </c>
       <c r="F122" t="n">
-        <v>198779700</v>
+        <v>177213600</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3607,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="B123" t="n">
-        <v>177.4048767089844</v>
+        <v>181.9741760435397</v>
       </c>
       <c r="C123" t="n">
-        <v>182.3333312190456</v>
+        <v>186.0047530762794</v>
       </c>
       <c r="D123" t="n">
-        <v>176.407211264142</v>
+        <v>181.5850871183009</v>
       </c>
       <c r="E123" t="n">
-        <v>179.420149946886</v>
+        <v>184.3386535644531</v>
       </c>
       <c r="F123" t="n">
-        <v>189021900</v>
+        <v>179118500</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3633,25 +3641,25 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="B124" t="n">
-        <v>182.2235870361328</v>
+        <v>185.4860219488843</v>
       </c>
       <c r="C124" t="n">
-        <v>182.4829897940845</v>
+        <v>187.1921136401388</v>
       </c>
       <c r="D124" t="n">
-        <v>175.1501427003192</v>
+        <v>184.0293448898806</v>
       </c>
       <c r="E124" t="n">
-        <v>176.4171820751478</v>
+        <v>185.6057434082031</v>
       </c>
       <c r="F124" t="n">
-        <v>177213600</v>
+        <v>145280400</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3659,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="B125" t="n">
-        <v>184.3386535644531</v>
+        <v>183.6302641505579</v>
       </c>
       <c r="C125" t="n">
-        <v>186.0047530762794</v>
+        <v>184.5182338343672</v>
       </c>
       <c r="D125" t="n">
-        <v>181.5850871183009</v>
+        <v>181.3355064165816</v>
       </c>
       <c r="E125" t="n">
-        <v>181.9741760435397</v>
+        <v>182.7223358154297</v>
       </c>
       <c r="F125" t="n">
-        <v>179118500</v>
+        <v>155762700</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3685,25 +3693,25 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="B126" t="n">
-        <v>185.6057434082031</v>
+        <v>184.4982918130038</v>
       </c>
       <c r="C126" t="n">
-        <v>187.1921136401388</v>
+        <v>185.6656218245341</v>
       </c>
       <c r="D126" t="n">
-        <v>184.0293448898806</v>
+        <v>179.5296528660815</v>
       </c>
       <c r="E126" t="n">
-        <v>185.4860219488843</v>
+        <v>179.8389434814453</v>
       </c>
       <c r="F126" t="n">
-        <v>145280400</v>
+        <v>160988400</v>
       </c>
       <c r="G126" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -3711,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="B127" t="n">
-        <v>182.7223358154297</v>
+        <v>182.5527246843909</v>
       </c>
       <c r="C127" t="n">
-        <v>184.5182338343672</v>
+        <v>188.4492501487561</v>
       </c>
       <c r="D127" t="n">
-        <v>181.3355064165816</v>
+        <v>180.9962848148914</v>
       </c>
       <c r="E127" t="n">
-        <v>183.6302641505579</v>
+        <v>182.8021545410156</v>
       </c>
       <c r="F127" t="n">
-        <v>155762700</v>
+        <v>217307400</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3737,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="B128" t="n">
-        <v>179.8389434814453</v>
+        <v>184.6379731916982</v>
       </c>
       <c r="C128" t="n">
-        <v>185.6656218245341</v>
+        <v>184.9771941770484</v>
       </c>
       <c r="D128" t="n">
-        <v>179.5296528660815</v>
+        <v>181.2656763194747</v>
       </c>
       <c r="E128" t="n">
-        <v>184.4982918130038</v>
+        <v>181.5151062011719</v>
       </c>
       <c r="F128" t="n">
-        <v>160988400</v>
+        <v>182497800</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3763,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="B129" t="n">
-        <v>182.8021545410156</v>
+        <v>182.0638447517288</v>
       </c>
       <c r="C129" t="n">
-        <v>188.4492501487561</v>
+        <v>182.9618014097589</v>
       </c>
       <c r="D129" t="n">
-        <v>180.9962848148914</v>
+        <v>179.9187539793071</v>
       </c>
       <c r="E129" t="n">
-        <v>182.5527246843909</v>
+        <v>179.9885864257812</v>
       </c>
       <c r="F129" t="n">
-        <v>217307400</v>
+        <v>156683100</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3789,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="B130" t="n">
-        <v>181.5151062011719</v>
+        <v>177.6040222894031</v>
       </c>
       <c r="C130" t="n">
-        <v>184.9771941770484</v>
+        <v>179.5695306962835</v>
       </c>
       <c r="D130" t="n">
-        <v>181.2656763194747</v>
+        <v>175.3890840362079</v>
       </c>
       <c r="E130" t="n">
-        <v>184.6379731916982</v>
+        <v>178.1527709960938</v>
       </c>
       <c r="F130" t="n">
-        <v>182497800</v>
+        <v>170968500</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3815,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="B131" t="n">
-        <v>179.9885864257812</v>
+        <v>177.5940686691464</v>
       </c>
       <c r="C131" t="n">
-        <v>182.9618014097589</v>
+        <v>177.853470255105</v>
       </c>
       <c r="D131" t="n">
-        <v>179.9187539793071</v>
+        <v>171.3283915093003</v>
       </c>
       <c r="E131" t="n">
-        <v>182.0638447517288</v>
+        <v>172.30615234375</v>
       </c>
       <c r="F131" t="n">
-        <v>156683100</v>
+        <v>241323500</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3841,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="B132" t="n">
-        <v>178.1527709960938</v>
+        <v>176.8557415306554</v>
       </c>
       <c r="C132" t="n">
-        <v>179.5695306962835</v>
+        <v>177.9632107122345</v>
       </c>
       <c r="D132" t="n">
-        <v>175.3890840362079</v>
+        <v>174.3614429436745</v>
       </c>
       <c r="E132" t="n">
-        <v>177.6040222894031</v>
+        <v>175.2394409179688</v>
       </c>
       <c r="F132" t="n">
-        <v>170968500</v>
+        <v>182836300</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3867,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="B133" t="n">
-        <v>172.30615234375</v>
+        <v>174.4312942297872</v>
       </c>
       <c r="C133" t="n">
-        <v>177.853470255105</v>
+        <v>175.8181236639554</v>
       </c>
       <c r="D133" t="n">
-        <v>171.3283915093003</v>
+        <v>173.5832266030264</v>
       </c>
       <c r="E133" t="n">
-        <v>177.5940686691464</v>
+        <v>174.8004455566406</v>
       </c>
       <c r="F133" t="n">
-        <v>241323500</v>
+        <v>147667800</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3893,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="B134" t="n">
-        <v>175.2394409179688</v>
+        <v>176.6961233561449</v>
       </c>
       <c r="C134" t="n">
-        <v>177.9632107122345</v>
+        <v>180.8067226806179</v>
       </c>
       <c r="D134" t="n">
-        <v>174.3614429436745</v>
+        <v>176.4466934898736</v>
       </c>
       <c r="E134" t="n">
-        <v>176.8557415306554</v>
+        <v>178.2725067138672</v>
       </c>
       <c r="F134" t="n">
-        <v>182836300</v>
+        <v>162602100</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3919,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B135" t="n">
-        <v>174.8004455566406</v>
+        <v>175.6684741654964</v>
       </c>
       <c r="C135" t="n">
-        <v>175.8181236639554</v>
+        <v>176.1074579435819</v>
       </c>
       <c r="D135" t="n">
-        <v>173.5832266030264</v>
+        <v>170.7497092682189</v>
       </c>
       <c r="E135" t="n">
-        <v>174.4312942297872</v>
+        <v>170.8494873046875</v>
       </c>
       <c r="F135" t="n">
-        <v>147667800</v>
+        <v>186152200</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3945,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="B136" t="n">
-        <v>178.2725067138672</v>
+        <v>169.6123099949711</v>
       </c>
       <c r="C136" t="n">
-        <v>180.8067226806179</v>
+        <v>170.5800990993323</v>
       </c>
       <c r="D136" t="n">
-        <v>176.4466934898736</v>
+        <v>166.629123297364</v>
       </c>
       <c r="E136" t="n">
-        <v>176.6961233561449</v>
+        <v>167.1379699707031</v>
       </c>
       <c r="F136" t="n">
-        <v>162602100</v>
+        <v>196212700</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3971,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="B137" t="n">
-        <v>170.8494873046875</v>
+        <v>168.3950875250076</v>
       </c>
       <c r="C137" t="n">
-        <v>176.1074579435819</v>
+        <v>169.0635577295173</v>
       </c>
       <c r="D137" t="n">
-        <v>170.7497092682189</v>
+        <v>163.8953782868944</v>
       </c>
       <c r="E137" t="n">
-        <v>175.6684741654964</v>
+        <v>164.7933197021484</v>
       </c>
       <c r="F137" t="n">
-        <v>186152200</v>
+        <v>185627000</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -3997,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="B138" t="n">
-        <v>167.1379699707031</v>
+        <v>166.589210422399</v>
       </c>
       <c r="C138" t="n">
-        <v>170.5800990993323</v>
+        <v>174.2217577880002</v>
       </c>
       <c r="D138" t="n">
-        <v>166.629123297364</v>
+        <v>166.5792387089764</v>
       </c>
       <c r="E138" t="n">
-        <v>169.6123099949711</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="F138" t="n">
-        <v>196212700</v>
+        <v>226181300</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4023,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="B139" t="n">
-        <v>164.7933197021484</v>
+        <v>175.5986119754623</v>
       </c>
       <c r="C139" t="n">
-        <v>169.0635577295173</v>
+        <v>176.9654826629128</v>
       </c>
       <c r="D139" t="n">
-        <v>163.8953782868944</v>
+        <v>174.351462742682</v>
       </c>
       <c r="E139" t="n">
-        <v>168.3950875250076</v>
+        <v>175.3491821289062</v>
       </c>
       <c r="F139" t="n">
-        <v>185627000</v>
+        <v>168132000</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4049,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="B140" t="n">
-        <v>174.0022583007812</v>
+        <v>171.787333172162</v>
       </c>
       <c r="C140" t="n">
-        <v>174.2217577880002</v>
+        <v>177.0852364118599</v>
       </c>
       <c r="D140" t="n">
-        <v>166.5792387089764</v>
+        <v>170.9791828272563</v>
       </c>
       <c r="E140" t="n">
-        <v>166.589210422399</v>
+        <v>176.9854583740234</v>
       </c>
       <c r="F140" t="n">
-        <v>226181300</v>
+        <v>143143200</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4075,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B141" t="n">
-        <v>175.3491821289062</v>
+        <v>176.7559774774269</v>
       </c>
       <c r="C141" t="n">
-        <v>176.9654826629128</v>
+        <v>177.3845303646084</v>
       </c>
       <c r="D141" t="n">
-        <v>174.351462742682</v>
+        <v>175.3591611441553</v>
       </c>
       <c r="E141" t="n">
-        <v>175.5986119754623</v>
+        <v>177.2348785400391</v>
       </c>
       <c r="F141" t="n">
-        <v>168132000</v>
+        <v>107564300</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4101,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B142" t="n">
-        <v>176.9854583740234</v>
+        <v>175.3292270516068</v>
       </c>
       <c r="C142" t="n">
-        <v>177.0852364118599</v>
+        <v>177.8235255680002</v>
       </c>
       <c r="D142" t="n">
-        <v>170.9791828272563</v>
+        <v>173.2639557965079</v>
       </c>
       <c r="E142" t="n">
-        <v>171.787333172162</v>
+        <v>177.6938323974609</v>
       </c>
       <c r="F142" t="n">
-        <v>143143200</v>
+        <v>132534900</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4127,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="B143" t="n">
-        <v>177.2348785400391</v>
+        <v>184.079243714486</v>
       </c>
       <c r="C143" t="n">
-        <v>177.3845303646084</v>
+        <v>184.837505037226</v>
       </c>
       <c r="D143" t="n">
-        <v>175.3591611441553</v>
+        <v>179.8888249511496</v>
       </c>
       <c r="E143" t="n">
-        <v>176.7559774774269</v>
+        <v>181.6647644042969</v>
       </c>
       <c r="F143" t="n">
-        <v>107564300</v>
+        <v>147732700</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4153,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="B144" t="n">
-        <v>177.6938323974609</v>
+        <v>181.4253138719204</v>
       </c>
       <c r="C144" t="n">
-        <v>177.8235255680002</v>
+        <v>183.6602110774668</v>
       </c>
       <c r="D144" t="n">
-        <v>173.2639557965079</v>
+        <v>180.2080948395415</v>
       </c>
       <c r="E144" t="n">
-        <v>175.3292270516068</v>
+        <v>183.4906005859375</v>
       </c>
       <c r="F144" t="n">
-        <v>132534900</v>
+        <v>116428500</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4179,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="B145" t="n">
-        <v>181.6647644042969</v>
+        <v>183.8896736698189</v>
       </c>
       <c r="C145" t="n">
-        <v>184.837505037226</v>
+        <v>189.5666999081706</v>
       </c>
       <c r="D145" t="n">
-        <v>179.8888249511496</v>
+        <v>183.8797019557237</v>
       </c>
       <c r="E145" t="n">
-        <v>184.079243714486</v>
+        <v>188.1998291015625</v>
       </c>
       <c r="F145" t="n">
-        <v>147732700</v>
+        <v>160459500</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4205,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="B146" t="n">
-        <v>183.4906005859375</v>
+        <v>185.605746824658</v>
       </c>
       <c r="C146" t="n">
-        <v>183.6602110774668</v>
+        <v>189.2274732756209</v>
       </c>
       <c r="D146" t="n">
-        <v>180.2080948395415</v>
+        <v>185.3164148846483</v>
       </c>
       <c r="E146" t="n">
-        <v>181.4253138719204</v>
+        <v>188.8782653808594</v>
       </c>
       <c r="F146" t="n">
-        <v>116428500</v>
+        <v>133648200</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4231,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="B147" t="n">
-        <v>188.1998291015625</v>
+        <v>190.4047764107204</v>
       </c>
       <c r="C147" t="n">
-        <v>189.5666999081706</v>
+        <v>196.0618438720703</v>
       </c>
       <c r="D147" t="n">
-        <v>183.8797019557237</v>
+        <v>190.3349439656124</v>
       </c>
       <c r="E147" t="n">
-        <v>183.8896736698189</v>
+        <v>196.0618438720703</v>
       </c>
       <c r="F147" t="n">
-        <v>160459500</v>
+        <v>161307000</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4257,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="B148" t="n">
-        <v>188.8782653808594</v>
+        <v>196.0917851116163</v>
       </c>
       <c r="C148" t="n">
-        <v>189.2274732756209</v>
+        <v>199.9429830157183</v>
       </c>
       <c r="D148" t="n">
-        <v>185.3164148846483</v>
+        <v>195.2936216855987</v>
       </c>
       <c r="E148" t="n">
-        <v>185.605746824658</v>
+        <v>198.4164733886719</v>
       </c>
       <c r="F148" t="n">
-        <v>133648200</v>
+        <v>185338400</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4283,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="B149" t="n">
-        <v>196.0618438720703</v>
+        <v>196.9797440092329</v>
       </c>
       <c r="C149" t="n">
-        <v>196.0618438720703</v>
+        <v>199.3942384790618</v>
       </c>
       <c r="D149" t="n">
-        <v>190.3349439656124</v>
+        <v>195.3634433694217</v>
       </c>
       <c r="E149" t="n">
-        <v>190.4047764107204</v>
+        <v>197.8976593017578</v>
       </c>
       <c r="F149" t="n">
-        <v>161307000</v>
+        <v>134012900</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4309,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46127</v>
+        <v>46129</v>
       </c>
       <c r="B150" t="n">
-        <v>198.4164733886719</v>
+        <v>199.444107632571</v>
       </c>
       <c r="C150" t="n">
-        <v>199.9429830157183</v>
+        <v>201.2400056483541</v>
       </c>
       <c r="D150" t="n">
-        <v>195.2936216855987</v>
+        <v>198.8155547450397</v>
       </c>
       <c r="E150" t="n">
-        <v>196.0917851116163</v>
+        <v>201.2200469970703</v>
       </c>
       <c r="F150" t="n">
-        <v>185338400</v>
+        <v>160324400</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4335,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="B151" t="n">
-        <v>197.8976593017578</v>
+        <v>199.5239239232554</v>
       </c>
       <c r="C151" t="n">
-        <v>199.3942384790618</v>
+        <v>201.7089318732817</v>
       </c>
       <c r="D151" t="n">
-        <v>195.3634433694217</v>
+        <v>197.3888049886708</v>
       </c>
       <c r="E151" t="n">
-        <v>196.9797440092329</v>
+        <v>201.5991821289062</v>
       </c>
       <c r="F151" t="n">
-        <v>134012900</v>
+        <v>119381400</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4361,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="B152" t="n">
-        <v>201.2200469970703</v>
+        <v>201.6690479582887</v>
       </c>
       <c r="C152" t="n">
-        <v>201.2400056483541</v>
+        <v>202.2876291783034</v>
       </c>
       <c r="D152" t="n">
-        <v>198.8155547450397</v>
+        <v>198.5461810430697</v>
       </c>
       <c r="E152" t="n">
-        <v>199.444107632571</v>
+        <v>199.4241790771484</v>
       </c>
       <c r="F152" t="n">
-        <v>160324400</v>
+        <v>107945300</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4387,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B153" t="n">
-        <v>201.5991821289062</v>
+        <v>200.5316418294082</v>
       </c>
       <c r="C153" t="n">
-        <v>201.7089318732817</v>
+        <v>202.0381927490234</v>
       </c>
       <c r="D153" t="n">
-        <v>197.3888049886708</v>
+        <v>198.546174602744</v>
       </c>
       <c r="E153" t="n">
-        <v>199.5239239232554</v>
+        <v>202.0381927490234</v>
       </c>
       <c r="F153" t="n">
-        <v>119381400</v>
+        <v>107501000</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4413,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B154" t="n">
-        <v>199.4241790771484</v>
+        <v>201.9982837593082</v>
       </c>
       <c r="C154" t="n">
-        <v>202.2876291783034</v>
+        <v>203.3651545152774</v>
       </c>
       <c r="D154" t="n">
-        <v>198.5461810430697</v>
+        <v>196.7702284327844</v>
       </c>
       <c r="E154" t="n">
-        <v>201.6690479582887</v>
+        <v>199.1847076416016</v>
       </c>
       <c r="F154" t="n">
-        <v>107945300</v>
+        <v>113561800</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4439,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="B155" t="n">
-        <v>202.0381927490234</v>
+        <v>199.5039827094276</v>
       </c>
       <c r="C155" t="n">
-        <v>202.0381927490234</v>
+        <v>210.468909435165</v>
       </c>
       <c r="D155" t="n">
-        <v>198.546174602744</v>
+        <v>199.3543156614425</v>
       </c>
       <c r="E155" t="n">
-        <v>200.5316418294082</v>
+        <v>207.7950286865234</v>
       </c>
       <c r="F155" t="n">
-        <v>107501000</v>
+        <v>214134400</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4465,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="B156" t="n">
-        <v>199.1847076416016</v>
+        <v>209.1718784416434</v>
       </c>
       <c r="C156" t="n">
-        <v>203.3651545152774</v>
+        <v>216.335512072091</v>
       </c>
       <c r="D156" t="n">
-        <v>196.7702284327844</v>
+        <v>206.9070662315077</v>
       </c>
       <c r="E156" t="n">
-        <v>201.9982837593082</v>
+        <v>216.1160125732422</v>
       </c>
       <c r="F156" t="n">
-        <v>113561800</v>
+        <v>187172400</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4491,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="B157" t="n">
-        <v>207.7950286865234</v>
+        <v>209.0122528840405</v>
       </c>
       <c r="C157" t="n">
-        <v>210.468909435165</v>
+        <v>214.2402930542568</v>
       </c>
       <c r="D157" t="n">
-        <v>199.3543156614425</v>
+        <v>207.7251862691963</v>
       </c>
       <c r="E157" t="n">
-        <v>199.5039827094276</v>
+        <v>212.6838531494141</v>
       </c>
       <c r="F157" t="n">
-        <v>214134400</v>
+        <v>180275400</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4517,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="B158" t="n">
-        <v>216.1160125732422</v>
+        <v>212.2149257168926</v>
       </c>
       <c r="C158" t="n">
-        <v>216.335512072091</v>
+        <v>212.2348843687743</v>
       </c>
       <c r="D158" t="n">
-        <v>206.9070662315077</v>
+        <v>207.1066069625242</v>
       </c>
       <c r="E158" t="n">
-        <v>209.1718784416434</v>
+        <v>208.7727966308594</v>
       </c>
       <c r="F158" t="n">
-        <v>187172400</v>
+        <v>123711800</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4543,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B159" t="n">
-        <v>212.6838531494141</v>
+        <v>209.4512265433391</v>
       </c>
       <c r="C159" t="n">
-        <v>214.2402930542568</v>
+        <v>209.8203930740204</v>
       </c>
       <c r="D159" t="n">
-        <v>207.7251862691963</v>
+        <v>198.2468419328838</v>
       </c>
       <c r="E159" t="n">
-        <v>209.0122528840405</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="F159" t="n">
-        <v>180275400</v>
+        <v>225239200</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4569,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B160" t="n">
-        <v>208.7727966308594</v>
+        <v>200.8209846036705</v>
       </c>
       <c r="C160" t="n">
-        <v>212.2348843687743</v>
+        <v>202.5370634031337</v>
       </c>
       <c r="D160" t="n">
-        <v>207.1066069625242</v>
+        <v>196.6704677294345</v>
       </c>
       <c r="E160" t="n">
-        <v>212.2149257168926</v>
+        <v>197.9974365234375</v>
       </c>
       <c r="F160" t="n">
-        <v>123711800</v>
+        <v>128647000</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4595,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="B161" t="n">
-        <v>199.1148681640625</v>
+        <v>199.0450218084295</v>
       </c>
       <c r="C161" t="n">
-        <v>209.8203930740204</v>
+        <v>201.2699318245734</v>
       </c>
       <c r="D161" t="n">
-        <v>198.2468419328838</v>
+        <v>194.2958829090753</v>
       </c>
       <c r="E161" t="n">
-        <v>209.4512265433391</v>
+        <v>198.02734375</v>
       </c>
       <c r="F161" t="n">
-        <v>225239200</v>
+        <v>125368100</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4621,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="B162" t="n">
-        <v>197.9974365234375</v>
+        <v>198.8454820247872</v>
       </c>
       <c r="C162" t="n">
-        <v>202.5370634031337</v>
+        <v>199.7833407086998</v>
       </c>
       <c r="D162" t="n">
-        <v>196.6704677294345</v>
+        <v>195.5829352820671</v>
       </c>
       <c r="E162" t="n">
-        <v>200.8209846036705</v>
+        <v>196.0518646240234</v>
       </c>
       <c r="F162" t="n">
-        <v>128647000</v>
+        <v>113406600</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4647,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B163" t="n">
-        <v>198.02734375</v>
+        <v>199.4341385249406</v>
       </c>
       <c r="C163" t="n">
-        <v>201.2699318245734</v>
+        <v>207.7950323152332</v>
       </c>
       <c r="D163" t="n">
-        <v>194.2958829090753</v>
+        <v>198.1570588579161</v>
       </c>
       <c r="E163" t="n">
-        <v>199.0450218084295</v>
+        <v>207.3560333251953</v>
       </c>
       <c r="F163" t="n">
-        <v>125368100</v>
+        <v>188362800</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4673,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B164" t="n">
-        <v>196.0518646240234</v>
+        <v>207.8648724722903</v>
       </c>
       <c r="C164" t="n">
-        <v>199.7833407086998</v>
+        <v>213.7115092245668</v>
       </c>
       <c r="D164" t="n">
-        <v>195.5829352820671</v>
+        <v>206.0290722858257</v>
       </c>
       <c r="E164" t="n">
-        <v>198.8454820247872</v>
+        <v>211.0176696777344</v>
       </c>
       <c r="F164" t="n">
-        <v>113406600</v>
+        <v>168307900</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4699,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B165" t="n">
-        <v>207.3560333251953</v>
+        <v>212.5441790763045</v>
       </c>
       <c r="C165" t="n">
-        <v>207.7950323152332</v>
+        <v>217.3033052467507</v>
       </c>
       <c r="D165" t="n">
-        <v>198.1570588579161</v>
+        <v>212.4044989584125</v>
       </c>
       <c r="E165" t="n">
-        <v>199.4341385249406</v>
+        <v>214.709228515625</v>
       </c>
       <c r="F165" t="n">
-        <v>188362800</v>
+        <v>136421400</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4725,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B166" t="n">
-        <v>211.0176696777344</v>
+        <v>213.5518657378577</v>
       </c>
       <c r="C166" t="n">
-        <v>213.7115092245668</v>
+        <v>221.7930381906342</v>
       </c>
       <c r="D166" t="n">
-        <v>206.0290722858257</v>
+        <v>213.402213909002</v>
       </c>
       <c r="E166" t="n">
-        <v>207.8648724722903</v>
+        <v>218.9395599365234</v>
       </c>
       <c r="F166" t="n">
-        <v>168307900</v>
+        <v>160685800</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4751,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B167" t="n">
-        <v>214.709228515625</v>
+        <v>218.0515943496244</v>
       </c>
       <c r="C167" t="n">
-        <v>217.3033052467507</v>
+        <v>223.239732575863</v>
       </c>
       <c r="D167" t="n">
-        <v>212.4044989584125</v>
+        <v>214.4298677829735</v>
       </c>
       <c r="E167" t="n">
-        <v>212.5441790763045</v>
+        <v>220.2765045166016</v>
       </c>
       <c r="F167" t="n">
-        <v>136421400</v>
+        <v>159176600</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4777,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B168" t="n">
-        <v>218.9395599365234</v>
+        <v>224.4170305354026</v>
       </c>
       <c r="C168" t="n">
-        <v>221.7930381906342</v>
+        <v>227.3203978139454</v>
       </c>
       <c r="D168" t="n">
-        <v>213.402213909002</v>
+        <v>221.0647077692387</v>
       </c>
       <c r="E168" t="n">
-        <v>213.5518657378577</v>
+        <v>225.3149871826172</v>
       </c>
       <c r="F168" t="n">
-        <v>160685800</v>
+        <v>150405400</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4803,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B169" t="n">
-        <v>220.2765045166016</v>
+        <v>229.3258255277811</v>
       </c>
       <c r="C169" t="n">
-        <v>223.239732575863</v>
+        <v>236.0005559723521</v>
       </c>
       <c r="D169" t="n">
-        <v>214.4298677829735</v>
+        <v>228.7770767762568</v>
       </c>
       <c r="E169" t="n">
-        <v>218.0515943496244</v>
+        <v>235.202392578125</v>
       </c>
       <c r="F169" t="n">
-        <v>159176600</v>
+        <v>180782900</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4829,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B170" t="n">
-        <v>225.3149871826172</v>
+        <v>229.2360138852663</v>
       </c>
       <c r="C170" t="n">
-        <v>227.3203978139454</v>
+        <v>230.9720511978</v>
       </c>
       <c r="D170" t="n">
-        <v>221.0647077692387</v>
+        <v>223.7286135177626</v>
       </c>
       <c r="E170" t="n">
-        <v>224.4170305354026</v>
+        <v>224.80615234375</v>
       </c>
       <c r="F170" t="n">
-        <v>150405400</v>
+        <v>180977600</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4855,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="B171" t="n">
-        <v>235.202392578125</v>
+        <v>229.345773483712</v>
       </c>
       <c r="C171" t="n">
-        <v>236.0005559723521</v>
+        <v>229.4754818886306</v>
       </c>
       <c r="D171" t="n">
-        <v>228.7770767762568</v>
+        <v>217.8719993892805</v>
       </c>
       <c r="E171" t="n">
-        <v>229.3258255277811</v>
+        <v>221.8130035400391</v>
       </c>
       <c r="F171" t="n">
-        <v>180782900</v>
+        <v>146280900</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4881,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B172" t="n">
-        <v>224.80615234375</v>
+        <v>219.1191400841904</v>
       </c>
       <c r="C172" t="n">
-        <v>230.9720511978</v>
+        <v>223.9680572056967</v>
       </c>
       <c r="D172" t="n">
-        <v>223.7286135177626</v>
+        <v>217.4130483552105</v>
       </c>
       <c r="E172" t="n">
-        <v>229.2360138852663</v>
+        <v>220.1068878173828</v>
       </c>
       <c r="F172" t="n">
-        <v>180977600</v>
+        <v>140948200</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4907,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B173" t="n">
-        <v>221.8130035400391</v>
+        <v>222.6710257508039</v>
       </c>
       <c r="C173" t="n">
-        <v>229.4754818886306</v>
+        <v>225.6143103895453</v>
       </c>
       <c r="D173" t="n">
-        <v>217.8719993892805</v>
+        <v>219.9971448577806</v>
       </c>
       <c r="E173" t="n">
-        <v>229.345773483712</v>
+        <v>222.9603729248047</v>
       </c>
       <c r="F173" t="n">
-        <v>146280900</v>
+        <v>184201600</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4933,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="B174" t="n">
-        <v>220.1068878173828</v>
+        <v>221.7830583738447</v>
       </c>
       <c r="C174" t="n">
-        <v>223.9680572056967</v>
+        <v>226.8814055684356</v>
       </c>
       <c r="D174" t="n">
-        <v>217.4130483552105</v>
+        <v>217.4330007955402</v>
       </c>
       <c r="E174" t="n">
-        <v>219.1191400841904</v>
+        <v>219.0093994140625</v>
       </c>
       <c r="F174" t="n">
-        <v>140948200</v>
+        <v>203381800</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4959,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B175" t="n">
-        <v>222.9603729248047</v>
+        <v>220.3962175709585</v>
       </c>
       <c r="C175" t="n">
-        <v>225.6143103895453</v>
+        <v>220.5059673180016</v>
       </c>
       <c r="D175" t="n">
-        <v>219.9971448577806</v>
+        <v>214.3101381389001</v>
       </c>
       <c r="E175" t="n">
-        <v>222.6710257508039</v>
+        <v>214.8389282226562</v>
       </c>
       <c r="F175" t="n">
-        <v>184201600</v>
+        <v>169275700</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4985,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="B176" t="n">
-        <v>219.0093994140625</v>
+        <v>216.0461718127993</v>
       </c>
       <c r="C176" t="n">
-        <v>226.8814055684356</v>
+        <v>217.6824311685512</v>
       </c>
       <c r="D176" t="n">
-        <v>217.4330007955402</v>
+        <v>211.5165320236786</v>
       </c>
       <c r="E176" t="n">
-        <v>221.7830583738447</v>
+        <v>214.3700103759766</v>
       </c>
       <c r="F176" t="n">
-        <v>203381800</v>
+        <v>187202600</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5011,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="B177" t="n">
-        <v>214.8389282226562</v>
+        <v>213.6316806617713</v>
       </c>
       <c r="C177" t="n">
-        <v>220.5059673180016</v>
+        <v>213.6616110269177</v>
       </c>
       <c r="D177" t="n">
-        <v>214.3101381389001</v>
+        <v>208.3038625298546</v>
       </c>
       <c r="E177" t="n">
-        <v>220.3962175709585</v>
+        <v>212.1151580810547</v>
       </c>
       <c r="F177" t="n">
-        <v>169275700</v>
+        <v>167601200</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5037,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="B178" t="n">
-        <v>214.3700103759766</v>
+        <v>210.7981702457166</v>
       </c>
       <c r="C178" t="n">
-        <v>217.6824311685512</v>
+        <v>215.0285063161196</v>
       </c>
       <c r="D178" t="n">
-        <v>211.5165320236786</v>
+        <v>210.738309512832</v>
       </c>
       <c r="E178" t="n">
-        <v>216.0461718127993</v>
+        <v>213.7613983154297</v>
       </c>
       <c r="F178" t="n">
-        <v>187202600</v>
+        <v>143996000</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5063,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B179" t="n">
-        <v>212.1151580810547</v>
+        <v>214.0906505321041</v>
       </c>
       <c r="C179" t="n">
-        <v>213.6616110269177</v>
+        <v>217.3631692496548</v>
       </c>
       <c r="D179" t="n">
-        <v>208.3038625298546</v>
+        <v>210.6485213277038</v>
       </c>
       <c r="E179" t="n">
-        <v>213.6316806617713</v>
+        <v>210.6584930419922</v>
       </c>
       <c r="F179" t="n">
-        <v>167601200</v>
+        <v>289410600</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5089,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="B180" t="n">
-        <v>213.7613983154297</v>
+        <v>215.2380189209027</v>
       </c>
       <c r="C180" t="n">
-        <v>215.0285063161196</v>
+        <v>224.3571743491113</v>
       </c>
       <c r="D180" t="n">
-        <v>210.738309512832</v>
+        <v>215.2080885544549</v>
       </c>
       <c r="E180" t="n">
-        <v>210.7981702457166</v>
+        <v>223.8483428955078</v>
       </c>
       <c r="F180" t="n">
-        <v>143996000</v>
+        <v>212850700</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5115,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="B181" t="n">
-        <v>210.6584930419922</v>
+        <v>226.6618858382332</v>
       </c>
       <c r="C181" t="n">
-        <v>217.3631692496548</v>
+        <v>231.7502608645459</v>
       </c>
       <c r="D181" t="n">
-        <v>210.6485213277038</v>
+        <v>220.8451951370975</v>
       </c>
       <c r="E181" t="n">
-        <v>214.0906505321041</v>
+        <v>222.3118438720703</v>
       </c>
       <c r="F181" t="n">
-        <v>289410600</v>
+        <v>193362900</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5141,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B182" t="n">
-        <v>223.8483428955078</v>
+        <v>221.2143597561905</v>
       </c>
       <c r="C182" t="n">
-        <v>224.3571743491113</v>
+        <v>222.3118572511273</v>
       </c>
       <c r="D182" t="n">
-        <v>215.2080885544549</v>
+        <v>214.0207957553572</v>
       </c>
       <c r="E182" t="n">
-        <v>215.2380189209027</v>
+        <v>214.26025390625</v>
       </c>
       <c r="F182" t="n">
-        <v>212850700</v>
+        <v>160907000</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5167,25 +5175,25 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B183" t="n">
-        <v>222.3118438720703</v>
+        <v>213.6709127939037</v>
       </c>
       <c r="C183" t="n">
-        <v>231.7502608645459</v>
+        <v>221.3523199881091</v>
       </c>
       <c r="D183" t="n">
-        <v>220.8451951370975</v>
+        <v>210.73419644349</v>
       </c>
       <c r="E183" t="n">
-        <v>226.6618858382332</v>
+        <v>218.4156036376953</v>
       </c>
       <c r="F183" t="n">
-        <v>193362900</v>
+        <v>169022200</v>
       </c>
       <c r="G183" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5193,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B184" t="n">
-        <v>214.26025390625</v>
+        <v>214.2902104723603</v>
       </c>
       <c r="C184" t="n">
-        <v>222.3118572511273</v>
+        <v>214.6298267834636</v>
       </c>
       <c r="D184" t="n">
-        <v>214.0207957553572</v>
+        <v>204.101614447126</v>
       </c>
       <c r="E184" t="n">
-        <v>221.2143597561905</v>
+        <v>204.8707580566406</v>
       </c>
       <c r="F184" t="n">
-        <v>160907000</v>
+        <v>219655500</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5219,25 +5227,25 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B185" t="n">
-        <v>218.4156036376953</v>
+        <v>209.9450713288228</v>
       </c>
       <c r="C185" t="n">
-        <v>221.3523199881091</v>
+        <v>210.2347557268212</v>
       </c>
       <c r="D185" t="n">
-        <v>210.73419644349</v>
+        <v>205.7697506938822</v>
       </c>
       <c r="E185" t="n">
-        <v>213.6709127939037</v>
+        <v>208.4067993164062</v>
       </c>
       <c r="F185" t="n">
-        <v>169022200</v>
+        <v>138372800</v>
       </c>
       <c r="G185" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -5245,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B186" t="n">
-        <v>204.8707580566406</v>
+        <v>210.3845825512031</v>
       </c>
       <c r="C186" t="n">
-        <v>214.6298267834636</v>
+        <v>211.1637095162451</v>
       </c>
       <c r="D186" t="n">
-        <v>204.101614447126</v>
+        <v>199.1171915656509</v>
       </c>
       <c r="E186" t="n">
-        <v>214.2902104723603</v>
+        <v>207.9573059082031</v>
       </c>
       <c r="F186" t="n">
-        <v>219655500</v>
+        <v>180962500</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5271,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B187" t="n">
-        <v>208.4067993164062</v>
+        <v>204.2014963256503</v>
       </c>
       <c r="C187" t="n">
-        <v>210.2347557268212</v>
+        <v>206.9883864105018</v>
       </c>
       <c r="D187" t="n">
-        <v>205.7697506938822</v>
+        <v>199.696542748819</v>
       </c>
       <c r="E187" t="n">
-        <v>209.9450713288228</v>
+        <v>200.1959838867188</v>
       </c>
       <c r="F187" t="n">
-        <v>138372800</v>
+        <v>161746600</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5297,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B188" t="n">
-        <v>207.9573059082031</v>
+        <v>201.2647947500858</v>
       </c>
       <c r="C188" t="n">
-        <v>211.1637095162451</v>
+        <v>205.4301320010667</v>
       </c>
       <c r="D188" t="n">
-        <v>199.1171915656509</v>
+        <v>199.3169621236104</v>
       </c>
       <c r="E188" t="n">
-        <v>210.3845825512031</v>
+        <v>204.6410064697266</v>
       </c>
       <c r="F188" t="n">
-        <v>180962500</v>
+        <v>158643200</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5323,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B189" t="n">
-        <v>200.1959838867188</v>
+        <v>204.6310298517525</v>
       </c>
       <c r="C189" t="n">
-        <v>206.9883864105018</v>
+        <v>206.8385664547524</v>
       </c>
       <c r="D189" t="n">
-        <v>199.696542748819</v>
+        <v>203.2126188059985</v>
       </c>
       <c r="E189" t="n">
-        <v>204.2014963256503</v>
+        <v>204.9606628417969</v>
       </c>
       <c r="F189" t="n">
-        <v>161746600</v>
+        <v>112001800</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5349,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="B190" t="n">
-        <v>204.6410064697266</v>
+        <v>208.6864864049894</v>
       </c>
       <c r="C190" t="n">
-        <v>205.4301320010667</v>
+        <v>212.4722588232193</v>
       </c>
       <c r="D190" t="n">
-        <v>199.3169621236104</v>
+        <v>208.1071328472061</v>
       </c>
       <c r="E190" t="n">
-        <v>201.2647947500858</v>
+        <v>212.2125396728516</v>
       </c>
       <c r="F190" t="n">
-        <v>158643200</v>
+        <v>149936700</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5375,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="B191" t="n">
-        <v>204.9606628417969</v>
+        <v>210.9439520928381</v>
       </c>
       <c r="C191" t="n">
-        <v>206.8385664547524</v>
+        <v>211.2536184019877</v>
       </c>
       <c r="D191" t="n">
-        <v>203.2126188059985</v>
+        <v>207.0583006421773</v>
       </c>
       <c r="E191" t="n">
-        <v>204.6310298517525</v>
+        <v>207.1781768798828</v>
       </c>
       <c r="F191" t="n">
-        <v>112001800</v>
+        <v>125694100</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5401,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B192" t="n">
-        <v>212.2125396728516</v>
+        <v>208.2969174543329</v>
       </c>
       <c r="C192" t="n">
-        <v>212.4722588232193</v>
+        <v>208.9761653200819</v>
       </c>
       <c r="D192" t="n">
-        <v>208.1071328472061</v>
+        <v>202.8530121596522</v>
       </c>
       <c r="E192" t="n">
-        <v>208.6864864049894</v>
+        <v>204.4212493896484</v>
       </c>
       <c r="F192" t="n">
-        <v>149936700</v>
+        <v>128363500</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5427,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B193" t="n">
-        <v>207.1781768798828</v>
+        <v>207.0982684229139</v>
       </c>
       <c r="C193" t="n">
-        <v>211.2536184019877</v>
+        <v>211.1537281092123</v>
       </c>
       <c r="D193" t="n">
-        <v>207.0583006421773</v>
+        <v>206.2691942875683</v>
       </c>
       <c r="E193" t="n">
-        <v>210.9439520928381</v>
+        <v>210.4545135498047</v>
       </c>
       <c r="F193" t="n">
-        <v>125694100</v>
+        <v>241272000</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5453,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="B194" t="n">
-        <v>204.4212493896484</v>
+        <v>211.2036686200953</v>
       </c>
       <c r="C194" t="n">
-        <v>208.9761653200819</v>
+        <v>213.7508214450341</v>
       </c>
       <c r="D194" t="n">
-        <v>202.8530121596522</v>
+        <v>207.4878253737282</v>
       </c>
       <c r="E194" t="n">
-        <v>208.2969174543329</v>
+        <v>208.4167785644531</v>
       </c>
       <c r="F194" t="n">
-        <v>128363500</v>
+        <v>122041400</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5479,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46191</v>
+        <v>46196</v>
       </c>
       <c r="B195" t="n">
-        <v>210.4545135498047</v>
+        <v>201.9440304014853</v>
       </c>
       <c r="C195" t="n">
-        <v>211.1537281092123</v>
+        <v>203.5422481594977</v>
       </c>
       <c r="D195" t="n">
-        <v>206.2691942875683</v>
+        <v>199.77645766483</v>
       </c>
       <c r="E195" t="n">
-        <v>207.0982684229139</v>
+        <v>199.81640625</v>
       </c>
       <c r="F195" t="n">
-        <v>241272000</v>
+        <v>153496200</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5505,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B196" t="n">
-        <v>208.4167785644531</v>
+        <v>199.8963159019567</v>
       </c>
       <c r="C196" t="n">
-        <v>213.7508214450341</v>
+        <v>201.4445864758279</v>
       </c>
       <c r="D196" t="n">
-        <v>207.4878253737282</v>
+        <v>196.360279356477</v>
       </c>
       <c r="E196" t="n">
-        <v>211.2036686200953</v>
+        <v>198.7775726318359</v>
       </c>
       <c r="F196" t="n">
-        <v>122041400</v>
+        <v>151810700</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5531,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B197" t="n">
-        <v>199.81640625</v>
+        <v>199.8563704571445</v>
       </c>
       <c r="C197" t="n">
-        <v>203.5422481594977</v>
+        <v>200.5755669254449</v>
       </c>
       <c r="D197" t="n">
-        <v>199.77645766483</v>
+        <v>191.9152592982058</v>
       </c>
       <c r="E197" t="n">
-        <v>201.9440304014853</v>
+        <v>195.5212249755859</v>
       </c>
       <c r="F197" t="n">
-        <v>153496200</v>
+        <v>149550000</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5557,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="B198" t="n">
-        <v>198.7775726318359</v>
+        <v>192.9041409641119</v>
       </c>
       <c r="C198" t="n">
-        <v>201.4445864758279</v>
+        <v>195.331432829306</v>
       </c>
       <c r="D198" t="n">
-        <v>196.360279356477</v>
+        <v>191.0062707295152</v>
       </c>
       <c r="E198" t="n">
-        <v>199.8963159019567</v>
+        <v>192.3148040771484</v>
       </c>
       <c r="F198" t="n">
-        <v>151810700</v>
+        <v>179304100</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5583,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="B199" t="n">
-        <v>195.5212249755859</v>
+        <v>193.6333319429392</v>
       </c>
       <c r="C199" t="n">
-        <v>200.5755669254449</v>
+        <v>195.9607141929515</v>
       </c>
       <c r="D199" t="n">
-        <v>191.9152592982058</v>
+        <v>189.5878557469149</v>
       </c>
       <c r="E199" t="n">
-        <v>199.8563704571445</v>
+        <v>194.7520751953125</v>
       </c>
       <c r="F199" t="n">
-        <v>149550000</v>
+        <v>148835700</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5609,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="B200" t="n">
-        <v>192.3148040771484</v>
+        <v>197.0195429632178</v>
       </c>
       <c r="C200" t="n">
-        <v>195.331432829306</v>
+        <v>200.4057532237791</v>
       </c>
       <c r="D200" t="n">
-        <v>191.0062707295152</v>
+        <v>194.8919188665145</v>
       </c>
       <c r="E200" t="n">
-        <v>192.9041409641119</v>
+        <v>199.8663482666016</v>
       </c>
       <c r="F200" t="n">
-        <v>179304100</v>
+        <v>166476700</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5635,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="B201" t="n">
-        <v>194.7520751953125</v>
+        <v>195.9806989625188</v>
       </c>
       <c r="C201" t="n">
-        <v>195.9607141929515</v>
+        <v>199.626628404907</v>
       </c>
       <c r="D201" t="n">
-        <v>189.5878557469149</v>
+        <v>193.2337727110923</v>
       </c>
       <c r="E201" t="n">
-        <v>193.6333319429392</v>
+        <v>197.3591613769531</v>
       </c>
       <c r="F201" t="n">
-        <v>148835700</v>
+        <v>146147600</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5661,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="B202" t="n">
-        <v>199.8663482666016</v>
+        <v>196.9196593659626</v>
       </c>
       <c r="C202" t="n">
-        <v>200.4057532237791</v>
+        <v>199.8363939026278</v>
       </c>
       <c r="D202" t="n">
-        <v>194.8919188665145</v>
+        <v>192.1350197738411</v>
       </c>
       <c r="E202" t="n">
-        <v>197.0195429632178</v>
+        <v>194.6122436523438</v>
       </c>
       <c r="F202" t="n">
-        <v>166476700</v>
+        <v>142068700</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5687,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B203" t="n">
-        <v>197.3591613769531</v>
+        <v>194.202694284663</v>
       </c>
       <c r="C203" t="n">
-        <v>199.626628404907</v>
+        <v>197.3292007505161</v>
       </c>
       <c r="D203" t="n">
-        <v>193.2337727110923</v>
+        <v>193.7731822131383</v>
       </c>
       <c r="E203" t="n">
-        <v>195.9806989625188</v>
+        <v>195.3314361572266</v>
       </c>
       <c r="F203" t="n">
-        <v>146147600</v>
+        <v>108999000</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5713,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B204" t="n">
-        <v>194.6122436523438</v>
+        <v>192.1549837798622</v>
       </c>
       <c r="C204" t="n">
-        <v>199.8363939026278</v>
+        <v>198.1882414262674</v>
       </c>
       <c r="D204" t="n">
-        <v>192.1350197738411</v>
+        <v>190.9263628146717</v>
       </c>
       <c r="E204" t="n">
-        <v>196.9196593659626</v>
+        <v>196.7098846435547</v>
       </c>
       <c r="F204" t="n">
-        <v>142068700</v>
+        <v>124154600</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5739,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B205" t="n">
-        <v>195.3314361572266</v>
+        <v>194.9618356993413</v>
       </c>
       <c r="C205" t="n">
-        <v>197.3292007505161</v>
+        <v>204.9306918075912</v>
       </c>
       <c r="D205" t="n">
-        <v>193.7731822131383</v>
+        <v>194.841974703339</v>
       </c>
       <c r="E205" t="n">
-        <v>194.202694284663</v>
+        <v>203.891845703125</v>
       </c>
       <c r="F205" t="n">
-        <v>108999000</v>
+        <v>147419100</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5765,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B206" t="n">
-        <v>196.7098846435547</v>
+        <v>204.2314748595287</v>
       </c>
       <c r="C206" t="n">
-        <v>198.1882414262674</v>
+        <v>204.3613191897594</v>
       </c>
       <c r="D206" t="n">
-        <v>190.9263628146717</v>
+        <v>198.7376223952696</v>
       </c>
       <c r="E206" t="n">
-        <v>192.1549837798622</v>
+        <v>202.5533447265625</v>
       </c>
       <c r="F206" t="n">
-        <v>124154600</v>
+        <v>132037400</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5791,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B207" t="n">
-        <v>203.891845703125</v>
+        <v>201.7742207048944</v>
       </c>
       <c r="C207" t="n">
-        <v>204.9306918075912</v>
+        <v>210.7641612313501</v>
       </c>
       <c r="D207" t="n">
-        <v>194.841974703339</v>
+        <v>201.6943082934289</v>
       </c>
       <c r="E207" t="n">
-        <v>194.9618356993413</v>
+        <v>210.7242126464844</v>
       </c>
       <c r="F207" t="n">
-        <v>147419100</v>
+        <v>148421000</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5817,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B208" t="n">
-        <v>202.5533447265625</v>
+        <v>208.3069001369788</v>
       </c>
       <c r="C208" t="n">
-        <v>204.3613191897594</v>
+        <v>210.3346451505122</v>
       </c>
       <c r="D208" t="n">
-        <v>198.7376223952696</v>
+        <v>202.7730991138312</v>
       </c>
       <c r="E208" t="n">
-        <v>204.2314748595287</v>
+        <v>203.3025054931641</v>
       </c>
       <c r="F208" t="n">
-        <v>132037400</v>
+        <v>121411000</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5843,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B209" t="n">
-        <v>210.7242126464844</v>
+        <v>207.9672957533915</v>
       </c>
       <c r="C209" t="n">
-        <v>210.7641612313501</v>
+        <v>212.3124399374416</v>
       </c>
       <c r="D209" t="n">
-        <v>201.6943082934289</v>
+        <v>203.5722196467825</v>
       </c>
       <c r="E209" t="n">
-        <v>201.7742207048944</v>
+        <v>211.5632781982422</v>
       </c>
       <c r="F209" t="n">
-        <v>148421000</v>
+        <v>124379600</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5869,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B210" t="n">
-        <v>203.3025054931641</v>
+        <v>211.7230919717581</v>
       </c>
       <c r="C210" t="n">
-        <v>210.3346451505122</v>
+        <v>213.5710150202495</v>
       </c>
       <c r="D210" t="n">
-        <v>202.7730991138312</v>
+        <v>205.8096955397309</v>
       </c>
       <c r="E210" t="n">
-        <v>208.3069001369788</v>
+        <v>212.2624816894531</v>
       </c>
       <c r="F210" t="n">
-        <v>121411000</v>
+        <v>124797200</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5895,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B211" t="n">
-        <v>211.5632781982422</v>
+        <v>209.9350906043833</v>
       </c>
       <c r="C211" t="n">
-        <v>212.3124399374416</v>
+        <v>210.8440771529852</v>
       </c>
       <c r="D211" t="n">
-        <v>203.5722196467825</v>
+        <v>205.6199270055466</v>
       </c>
       <c r="E211" t="n">
-        <v>207.9672957533915</v>
+        <v>207.1681823730469</v>
       </c>
       <c r="F211" t="n">
-        <v>124379600</v>
+        <v>122986100</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5921,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B212" t="n">
-        <v>212.2624816894531</v>
+        <v>202.4135048295048</v>
       </c>
       <c r="C212" t="n">
-        <v>213.5710150202495</v>
+        <v>206.4190172896336</v>
       </c>
       <c r="D212" t="n">
-        <v>205.8096955397309</v>
+        <v>197.7487264058434</v>
       </c>
       <c r="E212" t="n">
-        <v>211.7230919717581</v>
+        <v>202.5833129882812</v>
       </c>
       <c r="F212" t="n">
-        <v>124797200</v>
+        <v>144281900</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5947,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B213" t="n">
-        <v>207.1681823730469</v>
+        <v>205.639896943356</v>
       </c>
       <c r="C213" t="n">
-        <v>210.8440771529852</v>
+        <v>207.5078172334397</v>
       </c>
       <c r="D213" t="n">
-        <v>205.6199270055466</v>
+        <v>202.0539130969454</v>
       </c>
       <c r="E213" t="n">
-        <v>209.9350906043833</v>
+        <v>203.0527954101562</v>
       </c>
       <c r="F213" t="n">
-        <v>122986100</v>
+        <v>88701500</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5973,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B214" t="n">
-        <v>202.5833129882812</v>
+        <v>207.308024406286</v>
       </c>
       <c r="C214" t="n">
-        <v>206.4190172896336</v>
+        <v>208.4167843613107</v>
       </c>
       <c r="D214" t="n">
-        <v>197.7487264058434</v>
+        <v>203.7819711309363</v>
       </c>
       <c r="E214" t="n">
-        <v>202.4135048295048</v>
+        <v>207.0583038330078</v>
       </c>
       <c r="F214" t="n">
-        <v>144281900</v>
+        <v>108685600</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -5999,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B215" t="n">
-        <v>203.0527954101562</v>
+        <v>205.579968274895</v>
       </c>
       <c r="C215" t="n">
-        <v>207.5078172334397</v>
+        <v>214.1503804276117</v>
       </c>
       <c r="D215" t="n">
-        <v>202.0539130969454</v>
+        <v>204.7209288682105</v>
       </c>
       <c r="E215" t="n">
-        <v>205.639896943356</v>
+        <v>211.8229827880859</v>
       </c>
       <c r="F215" t="n">
-        <v>88701500</v>
+        <v>137645600</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6025,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B216" t="n">
-        <v>207.0583038330078</v>
+        <v>209.2258868865651</v>
       </c>
       <c r="C216" t="n">
-        <v>208.4167843613107</v>
+        <v>210.6342993029147</v>
       </c>
       <c r="D216" t="n">
-        <v>203.7819711309363</v>
+        <v>205.7297989431358</v>
       </c>
       <c r="E216" t="n">
-        <v>207.308024406286</v>
+        <v>208.5266571044922</v>
       </c>
       <c r="F216" t="n">
-        <v>108685600</v>
+        <v>110505300</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6051,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B217" t="n">
-        <v>211.8229827880859</v>
+        <v>207.2181292349697</v>
       </c>
       <c r="C217" t="n">
-        <v>214.1503804276117</v>
+        <v>211.6731509810223</v>
       </c>
       <c r="D217" t="n">
-        <v>204.7209288682105</v>
+        <v>204.5810805834776</v>
       </c>
       <c r="E217" t="n">
-        <v>205.579968274895</v>
+        <v>206.6088104248047</v>
       </c>
       <c r="F217" t="n">
-        <v>137645600</v>
+        <v>114836800</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6077,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B218" t="n">
-        <v>208.5266571044922</v>
+        <v>207.9672962732577</v>
       </c>
       <c r="C218" t="n">
-        <v>210.6342993029147</v>
+        <v>208.5166845983908</v>
       </c>
       <c r="D218" t="n">
-        <v>205.7297989431358</v>
+        <v>195.2215633388429</v>
       </c>
       <c r="E218" t="n">
-        <v>209.2258868865651</v>
+        <v>196.2903594970703</v>
       </c>
       <c r="F218" t="n">
-        <v>110505300</v>
+        <v>154353700</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6103,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="B219" t="n">
-        <v>206.6088104248047</v>
+        <v>194.782047001347</v>
       </c>
       <c r="C219" t="n">
-        <v>211.6731509810223</v>
+        <v>198.4779084345641</v>
       </c>
       <c r="D219" t="n">
-        <v>204.5810805834776</v>
+        <v>192.5245785077403</v>
       </c>
       <c r="E219" t="n">
-        <v>207.2181292349697</v>
+        <v>196.789794921875</v>
       </c>
       <c r="F219" t="n">
-        <v>114836800</v>
+        <v>134111500</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6129,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B220" t="n">
-        <v>196.2903594970703</v>
+        <v>195.6311069684468</v>
       </c>
       <c r="C220" t="n">
-        <v>208.5166845983908</v>
+        <v>196.8497446088402</v>
       </c>
       <c r="D220" t="n">
-        <v>195.2215633388429</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="E220" t="n">
-        <v>207.9672962732577</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="F220" t="n">
-        <v>154353700</v>
+        <v>147680800</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6155,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B221" t="n">
-        <v>196.789794921875</v>
+        <v>193.2337718176948</v>
       </c>
       <c r="C221" t="n">
-        <v>198.4779084345641</v>
+        <v>197.0295274868271</v>
       </c>
       <c r="D221" t="n">
-        <v>192.5245785077403</v>
+        <v>191.3059363552755</v>
       </c>
       <c r="E221" t="n">
-        <v>194.782047001347</v>
+        <v>194.8219909667969</v>
       </c>
       <c r="F221" t="n">
-        <v>134111500</v>
+        <v>129010200</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6181,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B222" t="n">
-        <v>189.7976226806641</v>
+        <v>198.2182038580375</v>
       </c>
       <c r="C222" t="n">
-        <v>196.8497446088402</v>
+        <v>201.7742223680242</v>
       </c>
       <c r="D222" t="n">
-        <v>189.7976226806641</v>
+        <v>194.7320991825756</v>
       </c>
       <c r="E222" t="n">
-        <v>195.6311069684468</v>
+        <v>200.5256195068359</v>
       </c>
       <c r="F222" t="n">
-        <v>147680800</v>
+        <v>139961200</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6207,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B223" t="n">
-        <v>194.8219909667969</v>
+        <v>197.4690486270115</v>
       </c>
       <c r="C223" t="n">
-        <v>197.0295274868271</v>
+        <v>208.506701330784</v>
       </c>
       <c r="D223" t="n">
-        <v>191.3059363552755</v>
+        <v>196.6299911347511</v>
       </c>
       <c r="E223" t="n">
-        <v>193.2337718176948</v>
+        <v>206.4090423583984</v>
       </c>
       <c r="F223" t="n">
-        <v>129010200</v>
+        <v>128406900</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6233,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B224" t="n">
-        <v>200.5256195068359</v>
+        <v>211.0638257011038</v>
       </c>
       <c r="C224" t="n">
-        <v>201.7742223680242</v>
+        <v>212.8218530009649</v>
       </c>
       <c r="D224" t="n">
-        <v>194.7320991825756</v>
+        <v>208.8163406042335</v>
       </c>
       <c r="E224" t="n">
-        <v>198.2182038580375</v>
+        <v>211.7031097412109</v>
       </c>
       <c r="F224" t="n">
-        <v>139961200</v>
+        <v>134922000</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6259,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B225" t="n">
-        <v>206.4090423583984</v>
+        <v>216.6176127852948</v>
       </c>
       <c r="C225" t="n">
-        <v>208.506701330784</v>
+        <v>221.9716224388697</v>
       </c>
       <c r="D225" t="n">
-        <v>196.6299911347511</v>
+        <v>216.1581202281489</v>
       </c>
       <c r="E225" t="n">
-        <v>197.4690486270115</v>
+        <v>218.9749755859375</v>
       </c>
       <c r="F225" t="n">
-        <v>128406900</v>
+        <v>158187400</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6285,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B226" t="n">
-        <v>211.7031097412109</v>
+        <v>221.2823935806188</v>
       </c>
       <c r="C226" t="n">
-        <v>212.8218530009649</v>
+        <v>223.3800524967045</v>
       </c>
       <c r="D226" t="n">
-        <v>208.8163406042335</v>
+        <v>216.7574580038405</v>
       </c>
       <c r="E226" t="n">
-        <v>211.0638257011038</v>
+        <v>218.7452392578125</v>
       </c>
       <c r="F226" t="n">
-        <v>134922000</v>
+        <v>113940600</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6311,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B227" t="n">
-        <v>218.9749755859375</v>
+        <v>221.2923777041913</v>
       </c>
       <c r="C227" t="n">
-        <v>221.9716224388697</v>
+        <v>224.5087799247126</v>
       </c>
       <c r="D227" t="n">
-        <v>216.1581202281489</v>
+        <v>220.4133716458871</v>
       </c>
       <c r="E227" t="n">
-        <v>216.6176127852948</v>
+        <v>223.7096862792969</v>
       </c>
       <c r="F227" t="n">
-        <v>158187400</v>
+        <v>105669400</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6337,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B228" t="n">
-        <v>218.7452392578125</v>
+        <v>223.1502910726907</v>
       </c>
       <c r="C228" t="n">
-        <v>223.3800524967045</v>
+        <v>223.8894694330602</v>
       </c>
       <c r="D228" t="n">
-        <v>216.7574580038405</v>
+        <v>216.5277120448001</v>
       </c>
       <c r="E228" t="n">
-        <v>221.2823935806188</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="F228" t="n">
-        <v>113940600</v>
+        <v>115846600</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6363,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B229" t="n">
-        <v>223.7096862792969</v>
+        <v>221.9216754142795</v>
       </c>
       <c r="C229" t="n">
-        <v>224.5087799247126</v>
+        <v>221.9516406634887</v>
       </c>
       <c r="D229" t="n">
-        <v>220.4133716458871</v>
+        <v>215.9583469538982</v>
       </c>
       <c r="E229" t="n">
-        <v>221.2923777041913</v>
+        <v>217.2568969726562</v>
       </c>
       <c r="F229" t="n">
-        <v>105669400</v>
+        <v>101273100</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6389,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B230" t="n">
-        <v>217.3068389892578</v>
+        <v>220.7929293559802</v>
       </c>
       <c r="C230" t="n">
-        <v>223.8894694330602</v>
+        <v>224.848404158734</v>
       </c>
       <c r="D230" t="n">
-        <v>216.5277120448001</v>
+        <v>219.9538719106106</v>
       </c>
       <c r="E230" t="n">
-        <v>223.1502910726907</v>
+        <v>223.8395233154297</v>
       </c>
       <c r="F230" t="n">
-        <v>115846600</v>
+        <v>108783600</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6415,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B231" t="n">
-        <v>217.2568969726562</v>
+        <v>224.8084500146858</v>
       </c>
       <c r="C231" t="n">
-        <v>221.9516406634887</v>
+        <v>226.9760227961096</v>
       </c>
       <c r="D231" t="n">
-        <v>215.9583469538982</v>
+        <v>223.4599680426375</v>
       </c>
       <c r="E231" t="n">
-        <v>221.9216754142795</v>
+        <v>225.0481872558594</v>
       </c>
       <c r="F231" t="n">
-        <v>101273100</v>
+        <v>98867200</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6441,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B232" t="n">
-        <v>223.8395233154297</v>
+        <v>226.5165415533859</v>
       </c>
       <c r="C232" t="n">
-        <v>224.848404158734</v>
+        <v>227.2357380227387</v>
       </c>
       <c r="D232" t="n">
-        <v>219.9538719106106</v>
+        <v>224.2490744835724</v>
       </c>
       <c r="E232" t="n">
-        <v>220.7929293559802</v>
+        <v>224.9083404541016</v>
       </c>
       <c r="F232" t="n">
-        <v>108783600</v>
+        <v>75680900</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6467,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B233" t="n">
-        <v>225.0481872558594</v>
+        <v>225.7274161885591</v>
       </c>
       <c r="C233" t="n">
-        <v>226.9760227961096</v>
+        <v>227.6652502746616</v>
       </c>
       <c r="D233" t="n">
-        <v>223.4599680426375</v>
+        <v>224.6086728983284</v>
       </c>
       <c r="E233" t="n">
-        <v>224.8084500146858</v>
+        <v>224.7584991455078</v>
       </c>
       <c r="F233" t="n">
-        <v>98867200</v>
+        <v>93678700</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6493,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B234" t="n">
-        <v>224.9083404541016</v>
+        <v>220.203597915372</v>
       </c>
       <c r="C234" t="n">
-        <v>227.2357380227387</v>
+        <v>221.3922702798686</v>
       </c>
       <c r="D234" t="n">
-        <v>224.2490744835724</v>
+        <v>218.4455705709327</v>
       </c>
       <c r="E234" t="n">
-        <v>226.5165415533859</v>
+        <v>219.4944000244141</v>
       </c>
       <c r="F234" t="n">
-        <v>75680900</v>
+        <v>103128200</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6519,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B235" t="n">
-        <v>224.7584991455078</v>
+        <v>221.4222404106533</v>
       </c>
       <c r="C235" t="n">
-        <v>227.6652502746616</v>
+        <v>222.6208961374568</v>
       </c>
       <c r="D235" t="n">
-        <v>224.6086728983284</v>
+        <v>216.5177245976465</v>
       </c>
       <c r="E235" t="n">
-        <v>225.7274161885591</v>
+        <v>217.3168334960938</v>
       </c>
       <c r="F235" t="n">
-        <v>93678700</v>
+        <v>96797300</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6545,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B236" t="n">
-        <v>219.4944000244141</v>
+        <v>218.1159423024499</v>
       </c>
       <c r="C236" t="n">
-        <v>221.3922702798686</v>
+        <v>219.6142657707553</v>
       </c>
       <c r="D236" t="n">
-        <v>218.4455705709327</v>
+        <v>215.418963107847</v>
       </c>
       <c r="E236" t="n">
-        <v>220.203597915372</v>
+        <v>216.6076354980469</v>
       </c>
       <c r="F236" t="n">
-        <v>103128200</v>
+        <v>92457000</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6571,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B237" t="n">
-        <v>217.3168334960938</v>
+        <v>218.1758724878036</v>
       </c>
       <c r="C237" t="n">
-        <v>222.6208961374568</v>
+        <v>218.4955221432803</v>
       </c>
       <c r="D237" t="n">
-        <v>216.5177245976465</v>
+        <v>214.2602556586216</v>
       </c>
       <c r="E237" t="n">
-        <v>221.4222404106533</v>
+        <v>214.4800109863281</v>
       </c>
       <c r="F237" t="n">
-        <v>96797300</v>
+        <v>98869300</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6597,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B238" t="n">
-        <v>216.6076354980469</v>
+        <v>215.2891020611033</v>
       </c>
       <c r="C238" t="n">
-        <v>219.6142657707553</v>
+        <v>215.3490325607492</v>
       </c>
       <c r="D238" t="n">
-        <v>215.418963107847</v>
+        <v>207.0183577918231</v>
       </c>
       <c r="E238" t="n">
-        <v>218.1159423024499</v>
+        <v>208.2469787597656</v>
       </c>
       <c r="F238" t="n">
-        <v>92457000</v>
+        <v>135187300</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6623,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B239" t="n">
-        <v>214.4800109863281</v>
+        <v>210.7941279013131</v>
       </c>
       <c r="C239" t="n">
-        <v>218.4955221432803</v>
+        <v>214.4899893165327</v>
       </c>
       <c r="D239" t="n">
-        <v>214.2602556586216</v>
+        <v>209.8751580258669</v>
       </c>
       <c r="E239" t="n">
-        <v>218.1758724878036</v>
+        <v>212.8118743896484</v>
       </c>
       <c r="F239" t="n">
-        <v>98869300</v>
+        <v>122309000</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6649,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B240" t="n">
-        <v>208.2469787597656</v>
+        <v>212.4023240594531</v>
       </c>
       <c r="C240" t="n">
-        <v>215.3490325607492</v>
+        <v>213.3612577394914</v>
       </c>
       <c r="D240" t="n">
-        <v>207.0183577918231</v>
+        <v>208.9961318803605</v>
       </c>
       <c r="E240" t="n">
-        <v>215.2891020611033</v>
+        <v>209.4256591796875</v>
       </c>
       <c r="F240" t="n">
-        <v>135187300</v>
+        <v>179900000</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6675,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B241" t="n">
-        <v>212.8118743896484</v>
+        <v>222.6109016432552</v>
       </c>
       <c r="C241" t="n">
-        <v>214.4899893165327</v>
+        <v>230.2123962709879</v>
       </c>
       <c r="D241" t="n">
-        <v>209.8751580258669</v>
+        <v>220.6530857022795</v>
       </c>
       <c r="E241" t="n">
-        <v>210.7941279013131</v>
+        <v>227.7251739501953</v>
       </c>
       <c r="F241" t="n">
-        <v>122309000</v>
+        <v>298909800</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6701,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B242" t="n">
-        <v>209.4256591796875</v>
+        <v>227.1058715337123</v>
       </c>
       <c r="C242" t="n">
-        <v>213.3612577394914</v>
+        <v>229.003741733446</v>
       </c>
       <c r="D242" t="n">
-        <v>208.9961318803605</v>
+        <v>216.5676606288883</v>
       </c>
       <c r="E242" t="n">
-        <v>212.4023240594531</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="F242" t="n">
-        <v>179900000</v>
+        <v>195116400</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6727,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B243" t="n">
-        <v>227.7251739501953</v>
+        <v>218.6253647857836</v>
       </c>
       <c r="C243" t="n">
-        <v>230.2123962709879</v>
+        <v>221.0526567078369</v>
       </c>
       <c r="D243" t="n">
-        <v>220.6530857022795</v>
+        <v>215.9683494434545</v>
       </c>
       <c r="E243" t="n">
-        <v>222.6109016432552</v>
+        <v>220.5332336425781</v>
       </c>
       <c r="F243" t="n">
-        <v>298909800</v>
+        <v>124702700</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6753,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B244" t="n">
-        <v>217.3068389892578</v>
+        <v>216.5077444634259</v>
       </c>
       <c r="C244" t="n">
-        <v>229.003741733446</v>
+        <v>220.1636574397174</v>
       </c>
       <c r="D244" t="n">
-        <v>216.5676606288883</v>
+        <v>214.8595947199138</v>
       </c>
       <c r="E244" t="n">
-        <v>227.1058715337123</v>
+        <v>217.1969757080078</v>
       </c>
       <c r="F244" t="n">
-        <v>195116400</v>
+        <v>109756200</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6779,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B245" t="n">
-        <v>220.5332336425781</v>
+        <v>218.5454508199983</v>
       </c>
       <c r="C245" t="n">
-        <v>221.0526567078369</v>
+        <v>227.6952163087265</v>
       </c>
       <c r="D245" t="n">
-        <v>215.9683494434545</v>
+        <v>218.2357997469377</v>
       </c>
       <c r="E245" t="n">
-        <v>218.6253647857836</v>
+        <v>224.1591796875</v>
       </c>
       <c r="F245" t="n">
-        <v>124702700</v>
+        <v>157104700</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6805,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B246" t="n">
-        <v>217.1969757080078</v>
+        <v>225.7673797205316</v>
       </c>
       <c r="C246" t="n">
-        <v>220.1636574397174</v>
+        <v>230.1424737915274</v>
       </c>
       <c r="D246" t="n">
-        <v>214.8595947199138</v>
+        <v>224.4987949430455</v>
       </c>
       <c r="E246" t="n">
-        <v>216.5077444634259</v>
+        <v>228.1946563720703</v>
       </c>
       <c r="F246" t="n">
-        <v>109756200</v>
+        <v>134681600</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6831,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B247" t="n">
-        <v>224.1591796875</v>
+        <v>230.8317036041433</v>
       </c>
       <c r="C247" t="n">
-        <v>227.6952163087265</v>
+        <v>234.4975997614268</v>
       </c>
       <c r="D247" t="n">
-        <v>218.2357997469377</v>
+        <v>229.3733440032785</v>
       </c>
       <c r="E247" t="n">
-        <v>218.5454508199983</v>
+        <v>230.1025238037109</v>
       </c>
       <c r="F247" t="n">
-        <v>157104700</v>
+        <v>135352400</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6857,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B248" t="n">
-        <v>228.1946563720703</v>
+        <v>232.8494477166676</v>
       </c>
       <c r="C248" t="n">
-        <v>230.1424737915274</v>
+        <v>233.4487831783142</v>
       </c>
       <c r="D248" t="n">
-        <v>224.4987949430455</v>
+        <v>224.5986856128386</v>
       </c>
       <c r="E248" t="n">
-        <v>225.7673797205316</v>
+        <v>225.4776916503906</v>
       </c>
       <c r="F248" t="n">
-        <v>134681600</v>
+        <v>122965600</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6883,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="B249" t="n">
-        <v>230.1025238037109</v>
+        <v>225.0281992525124</v>
       </c>
       <c r="C249" t="n">
-        <v>234.4975997614268</v>
+        <v>225.9271872095504</v>
       </c>
       <c r="D249" t="n">
-        <v>229.3733440032785</v>
+        <v>223.2102414251123</v>
       </c>
       <c r="E249" t="n">
-        <v>230.8317036041433</v>
+        <v>223.4199981689453</v>
       </c>
       <c r="F249" t="n">
-        <v>135352400</v>
+        <v>82955500</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6909,25 +6917,25 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B250" t="n">
-        <v>225.4776916503906</v>
+        <v>220.5299987792969</v>
       </c>
       <c r="C250" t="n">
-        <v>233.4487831783142</v>
+        <v>220.9900054931641</v>
       </c>
       <c r="D250" t="n">
-        <v>224.5986856128386</v>
+        <v>217.1999969482422</v>
       </c>
       <c r="E250" t="n">
-        <v>232.8494477166676</v>
+        <v>218.3600006103516</v>
       </c>
       <c r="F250" t="n">
-        <v>122965600</v>
+        <v>105768000</v>
       </c>
       <c r="G250" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -6935,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B251" t="n">
-        <v>223.4199981689453</v>
+        <v>221.2400054931641</v>
       </c>
       <c r="C251" t="n">
-        <v>225.9271872095504</v>
+        <v>222</v>
       </c>
       <c r="D251" t="n">
-        <v>223.2102414251123</v>
+        <v>218.1499938964844</v>
       </c>
       <c r="E251" t="n">
-        <v>225.0281992525124</v>
+        <v>218.2899932861328</v>
       </c>
       <c r="F251" t="n">
-        <v>82955500</v>
+        <v>89060100</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6961,53 +6969,27 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B252" t="n">
-        <v>218.3600006103516</v>
+        <v>211.2400054931641</v>
       </c>
       <c r="C252" t="n">
-        <v>220.9900054931641</v>
+        <v>212.7700042724609</v>
       </c>
       <c r="D252" t="n">
-        <v>217.1999969482422</v>
+        <v>208.9299926757812</v>
       </c>
       <c r="E252" t="n">
-        <v>220.5299987792969</v>
+        <v>210.9600067138672</v>
       </c>
       <c r="F252" t="n">
-        <v>105768000</v>
+        <v>131942300</v>
       </c>
       <c r="G252" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H252" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="1" t="n">
-        <v>46276</v>
-      </c>
-      <c r="B253" t="n">
-        <v>218.2899932861328</v>
-      </c>
-      <c r="C253" t="n">
-        <v>222</v>
-      </c>
-      <c r="D253" t="n">
-        <v>218.1499938964844</v>
-      </c>
-      <c r="E253" t="n">
-        <v>221.2400054931641</v>
-      </c>
-      <c r="F253" t="n">
-        <v>88804100</v>
-      </c>
-      <c r="G253" t="n">
-        <v>0</v>
-      </c>
-      <c r="H253" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10902,34 +10884,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>210.96</v>
+      </c>
+      <c r="D2" t="n">
         <v>218.29</v>
       </c>
-      <c r="D2" t="n">
-        <v>218.36</v>
-      </c>
       <c r="E2" t="n">
-        <v>221.25</v>
+        <v>211.08</v>
       </c>
       <c r="F2" t="n">
-        <v>222</v>
+        <v>212.77</v>
       </c>
       <c r="G2" t="n">
-        <v>218.15</v>
+        <v>208.93</v>
       </c>
       <c r="H2" t="n">
-        <v>86818741</v>
+        <v>131608711</v>
       </c>
       <c r="I2" t="n">
-        <v>132087064</v>
+        <v>131798644</v>
       </c>
       <c r="J2" t="n">
-        <v>5271048421376</v>
+        <v>5094050889728</v>
       </c>
       <c r="K2" t="n">
-        <v>27.631645</v>
+        <v>26.703798</v>
       </c>
       <c r="L2" t="n">
-        <v>14.022135</v>
+        <v>13.510182</v>
       </c>
       <c r="M2" t="n">
         <v>7.9</v>
@@ -10968,7 +10950,7 @@
         <v>9.483000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>23.019087</v>
+        <v>22.246126</v>
       </c>
       <c r="Z2" t="n">
         <v>1.278</v>
@@ -10980,7 +10962,7 @@
         <v>302970011648</v>
       </c>
       <c r="AC2" t="n">
-        <v>5237179940864</v>
+        <v>5060526866432</v>
       </c>
       <c r="AD2" t="n">
         <v>201266003968</v>
@@ -11007,7 +10989,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-12 21:47:03</t>
+          <t>2026-09-15 14:14:09</t>
         </is>
       </c>
     </row>

--- a/data/NVDA_data.xlsx
+++ b/data/NVDA_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45915</v>
+        <v>45917</v>
       </c>
       <c r="B2" t="n">
-        <v>175.2501493971494</v>
+        <v>172.2273696616015</v>
       </c>
       <c r="C2" t="n">
-        <v>178.4225571584428</v>
+        <v>172.7860287607356</v>
       </c>
       <c r="D2" t="n">
-        <v>174.0929181271268</v>
+        <v>168.007484117061</v>
       </c>
       <c r="E2" t="n">
-        <v>177.3251800537109</v>
+        <v>169.8829803466797</v>
       </c>
       <c r="F2" t="n">
-        <v>147061600</v>
+        <v>211843800</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45916</v>
+        <v>45918</v>
       </c>
       <c r="B3" t="n">
-        <v>176.5769643945311</v>
+        <v>173.5641632831282</v>
       </c>
       <c r="C3" t="n">
-        <v>177.0757693786965</v>
+        <v>176.6767164710769</v>
       </c>
       <c r="D3" t="n">
-        <v>173.9632311486472</v>
+        <v>172.5466121619453</v>
       </c>
       <c r="E3" t="n">
-        <v>174.4620361328125</v>
+        <v>175.8187713623047</v>
       </c>
       <c r="F3" t="n">
-        <v>140737800</v>
+        <v>191763300</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45917</v>
+        <v>45919</v>
       </c>
       <c r="B4" t="n">
-        <v>172.2273696616015</v>
+        <v>175.349898865447</v>
       </c>
       <c r="C4" t="n">
-        <v>172.7860287607356</v>
+        <v>177.6543753314711</v>
       </c>
       <c r="D4" t="n">
-        <v>168.007484117061</v>
+        <v>174.7612974471592</v>
       </c>
       <c r="E4" t="n">
-        <v>169.8829803466797</v>
+        <v>176.2477416992188</v>
       </c>
       <c r="F4" t="n">
-        <v>211843800</v>
+        <v>237182100</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45918</v>
+        <v>45922</v>
       </c>
       <c r="B5" t="n">
-        <v>173.5641783462465</v>
+        <v>174.8810364137678</v>
       </c>
       <c r="C5" t="n">
-        <v>176.6767318043244</v>
+        <v>184.1089289332547</v>
       </c>
       <c r="D5" t="n">
-        <v>172.5466271367534</v>
+        <v>174.2924501658818</v>
       </c>
       <c r="E5" t="n">
-        <v>175.8187866210938</v>
+        <v>183.1711730957031</v>
       </c>
       <c r="F5" t="n">
-        <v>191763300</v>
+        <v>269637000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45919</v>
+        <v>45923</v>
       </c>
       <c r="B6" t="n">
-        <v>175.349898865447</v>
+        <v>181.5350878652714</v>
       </c>
       <c r="C6" t="n">
-        <v>177.6543753314711</v>
+        <v>181.9840093083128</v>
       </c>
       <c r="D6" t="n">
-        <v>174.7612974471592</v>
+        <v>175.7888599052367</v>
       </c>
       <c r="E6" t="n">
-        <v>176.2477416992188</v>
+        <v>178.0035400390625</v>
       </c>
       <c r="F6" t="n">
-        <v>237182100</v>
+        <v>192559600</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45922</v>
+        <v>45924</v>
       </c>
       <c r="B7" t="n">
-        <v>174.8810218455756</v>
+        <v>179.3403538900187</v>
       </c>
       <c r="C7" t="n">
-        <v>184.1089135963474</v>
+        <v>179.3503245099793</v>
       </c>
       <c r="D7" t="n">
-        <v>174.2924356467209</v>
+        <v>174.9807878405966</v>
       </c>
       <c r="E7" t="n">
-        <v>183.1711578369141</v>
+        <v>176.5470428466797</v>
       </c>
       <c r="F7" t="n">
-        <v>269637000</v>
+        <v>143564100</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45923</v>
+        <v>45925</v>
       </c>
       <c r="B8" t="n">
-        <v>181.5350878652714</v>
+        <v>174.0629701066951</v>
       </c>
       <c r="C8" t="n">
-        <v>181.9840093083128</v>
+        <v>179.8291540783439</v>
       </c>
       <c r="D8" t="n">
-        <v>175.7888599052367</v>
+        <v>172.7162058826927</v>
       </c>
       <c r="E8" t="n">
-        <v>178.0035400390625</v>
+        <v>177.2653045654297</v>
       </c>
       <c r="F8" t="n">
-        <v>192559600</v>
+        <v>191586700</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45924</v>
+        <v>45926</v>
       </c>
       <c r="B9" t="n">
-        <v>179.3403383898065</v>
+        <v>177.7441579191998</v>
       </c>
       <c r="C9" t="n">
-        <v>179.3503090089054</v>
+        <v>179.3403398828169</v>
       </c>
       <c r="D9" t="n">
-        <v>174.9807727171775</v>
+        <v>174.5118962929188</v>
       </c>
       <c r="E9" t="n">
-        <v>176.5470275878906</v>
+        <v>177.7641143798828</v>
       </c>
       <c r="F9" t="n">
-        <v>143564100</v>
+        <v>148573700</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45925</v>
+        <v>45929</v>
       </c>
       <c r="B10" t="n">
-        <v>174.0629701066951</v>
+        <v>179.9987400973632</v>
       </c>
       <c r="C10" t="n">
-        <v>179.8291540783439</v>
+        <v>183.5602146114836</v>
       </c>
       <c r="D10" t="n">
-        <v>172.7162058826927</v>
+        <v>179.8890176259668</v>
       </c>
       <c r="E10" t="n">
-        <v>177.2653045654297</v>
+        <v>181.4153594970703</v>
       </c>
       <c r="F10" t="n">
-        <v>191586700</v>
+        <v>193063500</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45926</v>
+        <v>45930</v>
       </c>
       <c r="B11" t="n">
-        <v>177.7441426621237</v>
+        <v>181.6448190078555</v>
       </c>
       <c r="C11" t="n">
-        <v>179.3403244887289</v>
+        <v>186.9022276338177</v>
       </c>
       <c r="D11" t="n">
-        <v>174.5118813132914</v>
+        <v>181.0462469572146</v>
       </c>
       <c r="E11" t="n">
-        <v>177.7640991210938</v>
+        <v>186.1340637207031</v>
       </c>
       <c r="F11" t="n">
-        <v>148573700</v>
+        <v>236981000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45929</v>
+        <v>45931</v>
       </c>
       <c r="B12" t="n">
-        <v>179.9987400973632</v>
+        <v>184.7972606974542</v>
       </c>
       <c r="C12" t="n">
-        <v>183.5602146114836</v>
+        <v>187.6903232769056</v>
       </c>
       <c r="D12" t="n">
-        <v>179.8890176259668</v>
+        <v>183.4604518817237</v>
       </c>
       <c r="E12" t="n">
-        <v>181.4153594970703</v>
+        <v>186.79248046875</v>
       </c>
       <c r="F12" t="n">
-        <v>193063500</v>
+        <v>173844900</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45930</v>
+        <v>45932</v>
       </c>
       <c r="B13" t="n">
-        <v>181.6448190078555</v>
+        <v>189.146847340247</v>
       </c>
       <c r="C13" t="n">
-        <v>186.9022276338177</v>
+        <v>190.59337868299</v>
       </c>
       <c r="D13" t="n">
-        <v>181.0462469572146</v>
+        <v>187.6105195355423</v>
       </c>
       <c r="E13" t="n">
-        <v>186.1340637207031</v>
+        <v>188.4385375976562</v>
       </c>
       <c r="F13" t="n">
-        <v>236981000</v>
+        <v>136805800</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="B14" t="n">
-        <v>184.7972606974542</v>
+        <v>188.7378247179256</v>
       </c>
       <c r="C14" t="n">
-        <v>187.6903232769056</v>
+        <v>189.9050265070322</v>
       </c>
       <c r="D14" t="n">
-        <v>183.4604518817237</v>
+        <v>184.9369333277354</v>
       </c>
       <c r="E14" t="n">
-        <v>186.79248046875</v>
+        <v>187.1715698242188</v>
       </c>
       <c r="F14" t="n">
-        <v>173844900</v>
+        <v>137596900</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45932</v>
+        <v>45936</v>
       </c>
       <c r="B15" t="n">
-        <v>189.146847340247</v>
+        <v>185.0566294029491</v>
       </c>
       <c r="C15" t="n">
-        <v>190.59337868299</v>
+        <v>186.7824902019781</v>
       </c>
       <c r="D15" t="n">
-        <v>187.6105195355423</v>
+        <v>182.8918178290645</v>
       </c>
       <c r="E15" t="n">
-        <v>188.4385375976562</v>
+        <v>185.0965270996094</v>
       </c>
       <c r="F15" t="n">
-        <v>136805800</v>
+        <v>157678100</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45933</v>
+        <v>45937</v>
       </c>
       <c r="B16" t="n">
-        <v>188.7378401044004</v>
+        <v>185.7848907820332</v>
       </c>
       <c r="C16" t="n">
-        <v>189.9050419886609</v>
+        <v>188.6081286768816</v>
       </c>
       <c r="D16" t="n">
-        <v>184.9369484043502</v>
+        <v>183.5602249269612</v>
       </c>
       <c r="E16" t="n">
-        <v>187.1715850830078</v>
+        <v>184.5977325439453</v>
       </c>
       <c r="F16" t="n">
-        <v>137596900</v>
+        <v>140088000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45936</v>
+        <v>45938</v>
       </c>
       <c r="B17" t="n">
-        <v>185.0566446584491</v>
+        <v>186.1240974206304</v>
       </c>
       <c r="C17" t="n">
-        <v>186.7825055997528</v>
+        <v>189.1468543796426</v>
       </c>
       <c r="D17" t="n">
-        <v>182.8918329061041</v>
+        <v>186.0941551173159</v>
       </c>
       <c r="E17" t="n">
-        <v>185.0965423583984</v>
+        <v>188.6580200195312</v>
       </c>
       <c r="F17" t="n">
-        <v>157678100</v>
+        <v>130168900</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45937</v>
+        <v>45939</v>
       </c>
       <c r="B18" t="n">
-        <v>185.7848907820332</v>
+        <v>191.7705575158363</v>
       </c>
       <c r="C18" t="n">
-        <v>188.6081286768816</v>
+        <v>194.833227386451</v>
       </c>
       <c r="D18" t="n">
-        <v>183.5602249269612</v>
+        <v>190.6033556943829</v>
       </c>
       <c r="E18" t="n">
-        <v>184.5977325439453</v>
+        <v>192.1097564697266</v>
       </c>
       <c r="F18" t="n">
-        <v>140088000</v>
+        <v>182997200</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45938</v>
+        <v>45940</v>
       </c>
       <c r="B19" t="n">
-        <v>186.1240823667868</v>
+        <v>193.0474982342752</v>
       </c>
       <c r="C19" t="n">
-        <v>189.1468390813163</v>
+        <v>195.1524558626357</v>
       </c>
       <c r="D19" t="n">
-        <v>186.094140065894</v>
+        <v>181.6148965961679</v>
       </c>
       <c r="E19" t="n">
-        <v>188.6580047607422</v>
+        <v>182.7222442626953</v>
       </c>
       <c r="F19" t="n">
-        <v>130168900</v>
+        <v>268774400</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45939</v>
+        <v>45943</v>
       </c>
       <c r="B20" t="n">
-        <v>191.7705422839889</v>
+        <v>187.5207644715895</v>
       </c>
       <c r="C20" t="n">
-        <v>194.8332119113436</v>
+        <v>189.6556493942343</v>
       </c>
       <c r="D20" t="n">
-        <v>190.6033405552435</v>
+        <v>185.5155737280782</v>
       </c>
       <c r="E20" t="n">
-        <v>192.1097412109375</v>
+        <v>187.8699340820312</v>
       </c>
       <c r="F20" t="n">
-        <v>182997200</v>
+        <v>153482800</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45940</v>
+        <v>45944</v>
       </c>
       <c r="B21" t="n">
-        <v>193.0474821132437</v>
+        <v>184.3283927796865</v>
       </c>
       <c r="C21" t="n">
-        <v>195.1524395658232</v>
+        <v>184.3583198600852</v>
       </c>
       <c r="D21" t="n">
-        <v>181.6148814298513</v>
+        <v>179.2705030798172</v>
       </c>
       <c r="E21" t="n">
-        <v>182.7222290039062</v>
+        <v>179.5997161865234</v>
       </c>
       <c r="F21" t="n">
-        <v>268774400</v>
+        <v>205641400</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45943</v>
+        <v>45945</v>
       </c>
       <c r="B22" t="n">
-        <v>187.5207340107304</v>
+        <v>184.3583147400375</v>
       </c>
       <c r="C22" t="n">
-        <v>189.6556185865847</v>
+        <v>184.4281395182556</v>
       </c>
       <c r="D22" t="n">
-        <v>185.5155435929421</v>
+        <v>176.866254560341</v>
       </c>
       <c r="E22" t="n">
-        <v>187.8699035644531</v>
+        <v>179.4001922607422</v>
       </c>
       <c r="F22" t="n">
-        <v>153482800</v>
+        <v>214450500</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45944</v>
+        <v>45946</v>
       </c>
       <c r="B23" t="n">
-        <v>184.3283927796865</v>
+        <v>181.7944521048813</v>
       </c>
       <c r="C23" t="n">
-        <v>184.3583198600852</v>
+        <v>182.8419455690647</v>
       </c>
       <c r="D23" t="n">
-        <v>179.2705030798172</v>
+        <v>179.3403402174659</v>
       </c>
       <c r="E23" t="n">
-        <v>179.5997161865234</v>
+        <v>181.3754577636719</v>
       </c>
       <c r="F23" t="n">
-        <v>205641400</v>
+        <v>179723300</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45945</v>
+        <v>45947</v>
       </c>
       <c r="B24" t="n">
-        <v>184.3582990595379</v>
+        <v>179.7493465774322</v>
       </c>
       <c r="C24" t="n">
-        <v>184.4281238318171</v>
+        <v>183.6599908268075</v>
       </c>
       <c r="D24" t="n">
-        <v>176.8662395170747</v>
+        <v>179.3203816221287</v>
       </c>
       <c r="E24" t="n">
-        <v>179.4001770019531</v>
+        <v>182.7820892333984</v>
       </c>
       <c r="F24" t="n">
-        <v>214450500</v>
+        <v>173135200</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45946</v>
+        <v>45950</v>
       </c>
       <c r="B25" t="n">
-        <v>181.7944368108431</v>
+        <v>182.6923102950553</v>
       </c>
       <c r="C25" t="n">
-        <v>182.8419301869027</v>
+        <v>184.7573549226016</v>
       </c>
       <c r="D25" t="n">
-        <v>179.3403251298876</v>
+        <v>181.2956472677441</v>
       </c>
       <c r="E25" t="n">
-        <v>181.3754425048828</v>
+        <v>182.2034759521484</v>
       </c>
       <c r="F25" t="n">
-        <v>179723300</v>
+        <v>128544700</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45947</v>
+        <v>45951</v>
       </c>
       <c r="B26" t="n">
-        <v>179.7493465774322</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="C26" t="n">
-        <v>183.6599908268075</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="D26" t="n">
-        <v>179.3203816221287</v>
+        <v>179.3702701372806</v>
       </c>
       <c r="E26" t="n">
-        <v>182.7820892333984</v>
+        <v>180.7270202636719</v>
       </c>
       <c r="F26" t="n">
-        <v>173135200</v>
+        <v>124240200</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45950</v>
+        <v>45952</v>
       </c>
       <c r="B27" t="n">
-        <v>182.6922949953283</v>
+        <v>180.7070509305708</v>
       </c>
       <c r="C27" t="n">
-        <v>184.7573394499357</v>
+        <v>183.0015566720687</v>
       </c>
       <c r="D27" t="n">
-        <v>181.2956320849819</v>
+        <v>176.3375148363812</v>
       </c>
       <c r="E27" t="n">
-        <v>182.2034606933594</v>
+        <v>179.8491058349609</v>
       </c>
       <c r="F27" t="n">
-        <v>128544700</v>
+        <v>162249600</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="B28" t="n">
-        <v>182.3531141136141</v>
+        <v>179.988777912505</v>
       </c>
       <c r="C28" t="n">
-        <v>182.3531141136141</v>
+        <v>182.5925403832715</v>
       </c>
       <c r="D28" t="n">
-        <v>179.3702701372806</v>
+        <v>179.3602787988416</v>
       </c>
       <c r="E28" t="n">
-        <v>180.7270202636719</v>
+        <v>181.7246246337891</v>
       </c>
       <c r="F28" t="n">
-        <v>124240200</v>
+        <v>111363700</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45952</v>
+        <v>45954</v>
       </c>
       <c r="B29" t="n">
-        <v>180.7070662621498</v>
+        <v>183.4006051417061</v>
       </c>
       <c r="C29" t="n">
-        <v>183.0015721983185</v>
+        <v>187.0219340442129</v>
       </c>
       <c r="D29" t="n">
-        <v>176.3375297972393</v>
+        <v>183.0614214202242</v>
       </c>
       <c r="E29" t="n">
-        <v>179.84912109375</v>
+        <v>185.8148193359375</v>
       </c>
       <c r="F29" t="n">
-        <v>162249600</v>
+        <v>131296700</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45953</v>
+        <v>45957</v>
       </c>
       <c r="B30" t="n">
-        <v>179.988793025541</v>
+        <v>189.5359033209746</v>
       </c>
       <c r="C30" t="n">
-        <v>182.5925557149365</v>
+        <v>191.541093665248</v>
       </c>
       <c r="D30" t="n">
-        <v>179.3602938591047</v>
+        <v>187.979619148197</v>
       </c>
       <c r="E30" t="n">
-        <v>181.7246398925781</v>
+        <v>191.0323181152344</v>
       </c>
       <c r="F30" t="n">
-        <v>111363700</v>
+        <v>153452700</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="B31" t="n">
-        <v>183.400590081168</v>
+        <v>192.5886067715161</v>
       </c>
       <c r="C31" t="n">
-        <v>187.0219186862977</v>
+        <v>202.6644582837766</v>
       </c>
       <c r="D31" t="n">
-        <v>183.0614063875393</v>
+        <v>191.4513320204045</v>
       </c>
       <c r="E31" t="n">
-        <v>185.8148040771484</v>
+        <v>200.5495300292969</v>
       </c>
       <c r="F31" t="n">
-        <v>131296700</v>
+        <v>297986200</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45957</v>
+        <v>45959</v>
       </c>
       <c r="B32" t="n">
-        <v>189.5359184602369</v>
+        <v>207.482891187405</v>
       </c>
       <c r="C32" t="n">
-        <v>191.5411089646758</v>
+        <v>211.6828353303786</v>
       </c>
       <c r="D32" t="n">
-        <v>187.9796341631504</v>
+        <v>204.2905427296142</v>
       </c>
       <c r="E32" t="n">
-        <v>191.0323333740234</v>
+        <v>206.5451354980469</v>
       </c>
       <c r="F32" t="n">
-        <v>153452700</v>
+        <v>308829600</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45958</v>
+        <v>45960</v>
       </c>
       <c r="B33" t="n">
-        <v>192.588592118433</v>
+        <v>204.6596525726598</v>
       </c>
       <c r="C33" t="n">
-        <v>202.6644428640734</v>
+        <v>205.6672482532724</v>
       </c>
       <c r="D33" t="n">
-        <v>191.4513174538508</v>
+        <v>200.9286015136062</v>
       </c>
       <c r="E33" t="n">
-        <v>200.5495147705078</v>
+        <v>202.4050598144531</v>
       </c>
       <c r="F33" t="n">
-        <v>297986200</v>
+        <v>178864400</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45959</v>
+        <v>45961</v>
       </c>
       <c r="B34" t="n">
-        <v>207.482906515472</v>
+        <v>205.9565693232556</v>
       </c>
       <c r="C34" t="n">
-        <v>211.6828509687219</v>
+        <v>207.4729406961805</v>
       </c>
       <c r="D34" t="n">
-        <v>204.2905578218423</v>
+        <v>201.5870481318289</v>
       </c>
       <c r="E34" t="n">
-        <v>206.5451507568359</v>
+        <v>202.0060424804688</v>
       </c>
       <c r="F34" t="n">
-        <v>308829600</v>
+        <v>179802200</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45960</v>
+        <v>45964</v>
       </c>
       <c r="B35" t="n">
-        <v>204.6596525726598</v>
+        <v>207.5826726752522</v>
       </c>
       <c r="C35" t="n">
-        <v>205.6672482532724</v>
+        <v>210.8348755139714</v>
       </c>
       <c r="D35" t="n">
-        <v>200.9286015136062</v>
+        <v>205.0686914304077</v>
       </c>
       <c r="E35" t="n">
-        <v>202.4050598144531</v>
+        <v>206.3855438232422</v>
       </c>
       <c r="F35" t="n">
-        <v>178864400</v>
+        <v>180267300</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45961</v>
+        <v>45965</v>
       </c>
       <c r="B36" t="n">
-        <v>205.9565693232556</v>
+        <v>202.5148147488263</v>
       </c>
       <c r="C36" t="n">
-        <v>207.4729406961805</v>
+        <v>203.4824975937368</v>
       </c>
       <c r="D36" t="n">
-        <v>201.5870481318289</v>
+        <v>197.4569251230167</v>
       </c>
       <c r="E36" t="n">
-        <v>202.0060424804688</v>
+        <v>198.2151184082031</v>
       </c>
       <c r="F36" t="n">
-        <v>179802200</v>
+        <v>188919300</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="B37" t="n">
-        <v>207.5826726752522</v>
+        <v>198.2949120548774</v>
       </c>
       <c r="C37" t="n">
-        <v>210.8348755139714</v>
+        <v>202.4349867997753</v>
       </c>
       <c r="D37" t="n">
-        <v>205.0686914304077</v>
+        <v>194.1847491650603</v>
       </c>
       <c r="E37" t="n">
-        <v>206.3855438232422</v>
+        <v>194.7434234619141</v>
       </c>
       <c r="F37" t="n">
-        <v>180267300</v>
+        <v>171350300</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="B38" t="n">
-        <v>202.5148147488263</v>
+        <v>195.9505251524069</v>
       </c>
       <c r="C38" t="n">
-        <v>203.4824975937368</v>
+        <v>197.1476539294223</v>
       </c>
       <c r="D38" t="n">
-        <v>197.4569251230167</v>
+        <v>185.9345289438528</v>
       </c>
       <c r="E38" t="n">
-        <v>198.2151184082031</v>
+        <v>187.6304626464844</v>
       </c>
       <c r="F38" t="n">
-        <v>188919300</v>
+        <v>223029800</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45966</v>
+        <v>45968</v>
       </c>
       <c r="B39" t="n">
-        <v>198.2949275919373</v>
+        <v>184.4580698535366</v>
       </c>
       <c r="C39" t="n">
-        <v>202.4350026612236</v>
+        <v>187.8699092076593</v>
       </c>
       <c r="D39" t="n">
-        <v>194.1847643800754</v>
+        <v>178.4823961188316</v>
       </c>
       <c r="E39" t="n">
-        <v>194.7434387207031</v>
+        <v>187.7003021240234</v>
       </c>
       <c r="F39" t="n">
-        <v>171350300</v>
+        <v>264942300</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45967</v>
+        <v>45971</v>
       </c>
       <c r="B40" t="n">
-        <v>195.9505410878136</v>
+        <v>194.6436788693004</v>
       </c>
       <c r="C40" t="n">
-        <v>197.1476699621838</v>
+        <v>199.4621367771523</v>
       </c>
       <c r="D40" t="n">
-        <v>185.9345440647224</v>
+        <v>193.3268264223904</v>
       </c>
       <c r="E40" t="n">
-        <v>187.6304779052734</v>
+        <v>198.5742645263672</v>
       </c>
       <c r="F40" t="n">
-        <v>223029800</v>
+        <v>198897100</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45968</v>
+        <v>45972</v>
       </c>
       <c r="B41" t="n">
-        <v>184.4580698535366</v>
+        <v>194.6935535589016</v>
       </c>
       <c r="C41" t="n">
-        <v>187.8699092076593</v>
+        <v>194.9529266552934</v>
       </c>
       <c r="D41" t="n">
-        <v>178.4823961188316</v>
+        <v>190.8427786999811</v>
       </c>
       <c r="E41" t="n">
-        <v>187.7003021240234</v>
+        <v>192.6983337402344</v>
       </c>
       <c r="F41" t="n">
-        <v>264942300</v>
+        <v>176483300</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
       <c r="B42" t="n">
-        <v>194.6436639125443</v>
+        <v>195.2522164876445</v>
       </c>
       <c r="C42" t="n">
-        <v>199.4621214501376</v>
+        <v>195.4218083488666</v>
       </c>
       <c r="D42" t="n">
-        <v>193.3268115668235</v>
+        <v>190.673190567689</v>
       </c>
       <c r="E42" t="n">
-        <v>198.5742492675781</v>
+        <v>193.3368072509766</v>
       </c>
       <c r="F42" t="n">
-        <v>198897100</v>
+        <v>154935300</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45972</v>
+        <v>45974</v>
       </c>
       <c r="B43" t="n">
-        <v>194.6935689756818</v>
+        <v>190.5933947337238</v>
       </c>
       <c r="C43" t="n">
-        <v>194.9529420926121</v>
+        <v>190.9824620272586</v>
       </c>
       <c r="D43" t="n">
-        <v>190.8427938118383</v>
+        <v>183.4106057333689</v>
       </c>
       <c r="E43" t="n">
-        <v>192.6983489990234</v>
+        <v>186.4134063720703</v>
       </c>
       <c r="F43" t="n">
-        <v>176483300</v>
+        <v>207423100</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45973</v>
+        <v>45975</v>
       </c>
       <c r="B44" t="n">
-        <v>195.2522318976041</v>
+        <v>182.4229582335574</v>
       </c>
       <c r="C44" t="n">
-        <v>195.4218237722109</v>
+        <v>190.5534733337414</v>
       </c>
       <c r="D44" t="n">
-        <v>190.6732056162565</v>
+        <v>180.1484087383153</v>
       </c>
       <c r="E44" t="n">
-        <v>193.3368225097656</v>
+        <v>189.7154846191406</v>
       </c>
       <c r="F44" t="n">
-        <v>154935300</v>
+        <v>186591900</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="B45" t="n">
-        <v>190.5933791327836</v>
+        <v>185.5255382862568</v>
       </c>
       <c r="C45" t="n">
-        <v>190.9824463944715</v>
+        <v>188.5482954559393</v>
       </c>
       <c r="D45" t="n">
-        <v>183.4105907203728</v>
+        <v>183.879487827554</v>
       </c>
       <c r="E45" t="n">
-        <v>186.4133911132812</v>
+        <v>186.1540374755859</v>
       </c>
       <c r="F45" t="n">
-        <v>207423100</v>
+        <v>173628900</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45975</v>
+        <v>45979</v>
       </c>
       <c r="B46" t="n">
-        <v>182.4229435613052</v>
+        <v>182.941705155915</v>
       </c>
       <c r="C46" t="n">
-        <v>190.553458007553</v>
+        <v>184.3583093626339</v>
       </c>
       <c r="D46" t="n">
-        <v>180.1483942490048</v>
+        <v>179.2206093334711</v>
       </c>
       <c r="E46" t="n">
-        <v>189.7154693603516</v>
+        <v>180.9265289306641</v>
       </c>
       <c r="F46" t="n">
-        <v>186591900</v>
+        <v>213598900</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="B47" t="n">
-        <v>185.525507871713</v>
+        <v>184.3483273978252</v>
       </c>
       <c r="C47" t="n">
-        <v>188.5482645458532</v>
+        <v>187.4109971087465</v>
       </c>
       <c r="D47" t="n">
-        <v>183.8794576828592</v>
+        <v>182.3930205111681</v>
       </c>
       <c r="E47" t="n">
-        <v>186.1540069580078</v>
+        <v>186.0742034912109</v>
       </c>
       <c r="F47" t="n">
-        <v>173628900</v>
+        <v>247246400</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45979</v>
+        <v>45981</v>
       </c>
       <c r="B48" t="n">
-        <v>182.9417205846578</v>
+        <v>195.4816571057099</v>
       </c>
       <c r="C48" t="n">
-        <v>184.3583249108488</v>
+        <v>195.5315406452363</v>
       </c>
       <c r="D48" t="n">
-        <v>179.2206244483882</v>
+        <v>179.4201468289569</v>
       </c>
       <c r="E48" t="n">
-        <v>180.9265441894531</v>
+        <v>180.208251953125</v>
       </c>
       <c r="F48" t="n">
-        <v>213598900</v>
+        <v>343504800</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45980</v>
+        <v>45982</v>
       </c>
       <c r="B49" t="n">
-        <v>184.3483273978252</v>
+        <v>180.8068289121023</v>
       </c>
       <c r="C49" t="n">
-        <v>187.4109971087465</v>
+        <v>184.1188859589464</v>
       </c>
       <c r="D49" t="n">
-        <v>182.3930205111681</v>
+        <v>172.5166776199441</v>
       </c>
       <c r="E49" t="n">
-        <v>186.0742034912109</v>
+        <v>178.4524688720703</v>
       </c>
       <c r="F49" t="n">
-        <v>247246400</v>
+        <v>346926200</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45981</v>
+        <v>45985</v>
       </c>
       <c r="B50" t="n">
-        <v>195.4816571057099</v>
+        <v>179.0610093294625</v>
       </c>
       <c r="C50" t="n">
-        <v>195.5315406452363</v>
+        <v>183.0614196131816</v>
       </c>
       <c r="D50" t="n">
-        <v>179.4201468289569</v>
+        <v>176.0581937395723</v>
       </c>
       <c r="E50" t="n">
-        <v>180.208251953125</v>
+        <v>182.1136932373047</v>
       </c>
       <c r="F50" t="n">
-        <v>343504800</v>
+        <v>256618300</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="B51" t="n">
-        <v>180.8068443722038</v>
+        <v>174.4919707447618</v>
       </c>
       <c r="C51" t="n">
-        <v>184.1189017022491</v>
+        <v>177.734203281764</v>
       </c>
       <c r="D51" t="n">
-        <v>172.5166923711864</v>
+        <v>169.1447804748437</v>
       </c>
       <c r="E51" t="n">
-        <v>178.4524841308594</v>
+        <v>177.39501953125</v>
       </c>
       <c r="F51" t="n">
-        <v>346926200</v>
+        <v>320600300</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45985</v>
+        <v>45987</v>
       </c>
       <c r="B52" t="n">
-        <v>179.0610243324759</v>
+        <v>181.1958985688627</v>
       </c>
       <c r="C52" t="n">
-        <v>183.0614349513779</v>
+        <v>182.4728380763597</v>
       </c>
       <c r="D52" t="n">
-        <v>176.0582084909882</v>
+        <v>177.8140014756398</v>
       </c>
       <c r="E52" t="n">
-        <v>182.1137084960938</v>
+        <v>179.8291625976562</v>
       </c>
       <c r="F52" t="n">
-        <v>256618300</v>
+        <v>183852000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="B53" t="n">
-        <v>174.4919407266003</v>
+        <v>178.5821558989869</v>
       </c>
       <c r="C53" t="n">
-        <v>177.7341727058355</v>
+        <v>178.8614854738169</v>
       </c>
       <c r="D53" t="n">
-        <v>169.1447513765687</v>
+        <v>176.0781603452176</v>
       </c>
       <c r="E53" t="n">
-        <v>177.3949890136719</v>
+        <v>176.5769653320312</v>
       </c>
       <c r="F53" t="n">
-        <v>320600300</v>
+        <v>121332800</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45987</v>
+        <v>45992</v>
       </c>
       <c r="B54" t="n">
-        <v>181.1959139436215</v>
+        <v>174.3423041351479</v>
       </c>
       <c r="C54" t="n">
-        <v>182.4728535594688</v>
+        <v>179.8690716163194</v>
       </c>
       <c r="D54" t="n">
-        <v>177.8140165634392</v>
+        <v>173.2648835948944</v>
       </c>
       <c r="E54" t="n">
-        <v>179.8291778564453</v>
+        <v>179.4899749755859</v>
       </c>
       <c r="F54" t="n">
-        <v>183852000</v>
+        <v>188131000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45989</v>
+        <v>45993</v>
       </c>
       <c r="B55" t="n">
-        <v>178.5821404669205</v>
+        <v>181.3255769560617</v>
       </c>
       <c r="C55" t="n">
-        <v>178.8614700176124</v>
+        <v>185.2162648499111</v>
       </c>
       <c r="D55" t="n">
-        <v>176.0781451295325</v>
+        <v>179.569788944198</v>
       </c>
       <c r="E55" t="n">
-        <v>176.5769500732422</v>
+        <v>181.0263061523438</v>
       </c>
       <c r="F55" t="n">
-        <v>121332800</v>
+        <v>182632200</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45992</v>
+        <v>45994</v>
       </c>
       <c r="B56" t="n">
-        <v>174.3423041351479</v>
+        <v>180.6471955161887</v>
       </c>
       <c r="C56" t="n">
-        <v>179.8690716163194</v>
+        <v>182.013916155068</v>
       </c>
       <c r="D56" t="n">
-        <v>173.2648835948944</v>
+        <v>178.6819028715845</v>
       </c>
       <c r="E56" t="n">
-        <v>179.4899749755859</v>
+        <v>179.1607513427734</v>
       </c>
       <c r="F56" t="n">
-        <v>188131000</v>
+        <v>165138000</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,25 +1899,25 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="B57" t="n">
-        <v>181.3255769560617</v>
+        <v>181.1959881613664</v>
       </c>
       <c r="C57" t="n">
-        <v>185.2162648499111</v>
+        <v>184.089227004522</v>
       </c>
       <c r="D57" t="n">
-        <v>179.569788944198</v>
+        <v>179.5398751387779</v>
       </c>
       <c r="E57" t="n">
-        <v>181.0263061523438</v>
+        <v>182.9518890380859</v>
       </c>
       <c r="F57" t="n">
-        <v>182632200</v>
+        <v>167364900</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45994</v>
+        <v>45996</v>
       </c>
       <c r="B58" t="n">
-        <v>180.6472109015755</v>
+        <v>183.4606866221248</v>
       </c>
       <c r="C58" t="n">
-        <v>182.0139316568558</v>
+        <v>184.2288932293168</v>
       </c>
       <c r="D58" t="n">
-        <v>178.681918089591</v>
+        <v>180.4876480440623</v>
       </c>
       <c r="E58" t="n">
-        <v>179.1607666015625</v>
+        <v>181.9841461181641</v>
       </c>
       <c r="F58" t="n">
-        <v>165138000</v>
+        <v>143971100</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,25 +1951,25 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45995</v>
+        <v>45999</v>
       </c>
       <c r="B59" t="n">
-        <v>181.1960032737075</v>
+        <v>182.2136112701494</v>
       </c>
       <c r="C59" t="n">
-        <v>184.0892423581687</v>
+        <v>187.5610985176648</v>
       </c>
       <c r="D59" t="n">
-        <v>179.5398901129937</v>
+        <v>181.9741660895743</v>
       </c>
       <c r="E59" t="n">
-        <v>182.951904296875</v>
+        <v>185.1168212890625</v>
       </c>
       <c r="F59" t="n">
-        <v>167364900</v>
+        <v>204378100</v>
       </c>
       <c r="G59" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="B60" t="n">
-        <v>183.4607020047171</v>
+        <v>185.12679644575</v>
       </c>
       <c r="C60" t="n">
-        <v>184.2289086763207</v>
+        <v>185.2864265695677</v>
       </c>
       <c r="D60" t="n">
-        <v>180.4876631773748</v>
+        <v>182.8920356049676</v>
       </c>
       <c r="E60" t="n">
-        <v>181.9841613769531</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="F60" t="n">
-        <v>143971100</v>
+        <v>144719700</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="B61" t="n">
-        <v>182.2136112701494</v>
+        <v>184.5381918075859</v>
       </c>
       <c r="C61" t="n">
-        <v>187.5610985176648</v>
+        <v>185.0469957406681</v>
       </c>
       <c r="D61" t="n">
-        <v>181.9741660895743</v>
+        <v>181.6150239281505</v>
       </c>
       <c r="E61" t="n">
-        <v>185.1168212890625</v>
+        <v>183.3509674072266</v>
       </c>
       <c r="F61" t="n">
-        <v>204378100</v>
+        <v>162785400</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="B62" t="n">
-        <v>185.1268117532098</v>
+        <v>179.8591376409278</v>
       </c>
       <c r="C62" t="n">
-        <v>185.2864418902268</v>
+        <v>180.896718300432</v>
       </c>
       <c r="D62" t="n">
-        <v>182.8920507276432</v>
+        <v>176.2076782062319</v>
       </c>
       <c r="E62" t="n">
-        <v>184.5381927490234</v>
+        <v>180.5076141357422</v>
       </c>
       <c r="F62" t="n">
-        <v>144719700</v>
+        <v>182136600</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="B63" t="n">
-        <v>184.538176449994</v>
+        <v>180.6871989054384</v>
       </c>
       <c r="C63" t="n">
-        <v>185.0469803407326</v>
+        <v>182.3932136047752</v>
       </c>
       <c r="D63" t="n">
-        <v>181.6150088138297</v>
+        <v>174.2123443447362</v>
       </c>
       <c r="E63" t="n">
-        <v>183.3509521484375</v>
+        <v>174.6114196777344</v>
       </c>
       <c r="F63" t="n">
-        <v>162785400</v>
+        <v>204274900</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="B64" t="n">
-        <v>179.8591224369562</v>
+        <v>177.5245903328353</v>
       </c>
       <c r="C64" t="n">
-        <v>180.8967030087509</v>
+        <v>178.0034654802094</v>
       </c>
       <c r="D64" t="n">
-        <v>176.2076633109278</v>
+        <v>174.6213802569945</v>
       </c>
       <c r="E64" t="n">
-        <v>180.5075988769531</v>
+        <v>175.8784332275391</v>
       </c>
       <c r="F64" t="n">
-        <v>182136600</v>
+        <v>164775600</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46003</v>
+        <v>46007</v>
       </c>
       <c r="B65" t="n">
-        <v>180.6871831157045</v>
+        <v>175.8485012773324</v>
       </c>
       <c r="C65" t="n">
-        <v>182.3931976659576</v>
+        <v>178.0733061224419</v>
       </c>
       <c r="D65" t="n">
-        <v>174.2123291208211</v>
+        <v>174.4916756985292</v>
       </c>
       <c r="E65" t="n">
-        <v>174.6114044189453</v>
+        <v>177.3050994873047</v>
       </c>
       <c r="F65" t="n">
-        <v>204274900</v>
+        <v>148588100</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="B66" t="n">
-        <v>177.5245903328353</v>
+        <v>175.6888968536916</v>
       </c>
       <c r="C66" t="n">
-        <v>178.0034654802094</v>
+        <v>175.7188256001934</v>
       </c>
       <c r="D66" t="n">
-        <v>174.6213802569945</v>
+        <v>169.9124052081842</v>
       </c>
       <c r="E66" t="n">
-        <v>175.8784332275391</v>
+        <v>170.5409393310547</v>
       </c>
       <c r="F66" t="n">
-        <v>164775600</v>
+        <v>222775500</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="B67" t="n">
-        <v>175.8485164107673</v>
+        <v>174.1225483861358</v>
       </c>
       <c r="C67" t="n">
-        <v>178.0733214473424</v>
+        <v>175.7387615308714</v>
       </c>
       <c r="D67" t="n">
-        <v>174.4916907151964</v>
+        <v>171.4188835631069</v>
       </c>
       <c r="E67" t="n">
-        <v>177.3051147460938</v>
+        <v>173.7334594726562</v>
       </c>
       <c r="F67" t="n">
-        <v>148588100</v>
+        <v>176096000</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="B68" t="n">
-        <v>175.6888968536916</v>
+        <v>176.2575523358494</v>
       </c>
       <c r="C68" t="n">
-        <v>175.7188256001934</v>
+        <v>181.0263919449467</v>
       </c>
       <c r="D68" t="n">
-        <v>169.9124052081842</v>
+        <v>175.9283209122297</v>
       </c>
       <c r="E68" t="n">
-        <v>170.5409393310547</v>
+        <v>180.5674743652344</v>
       </c>
       <c r="F68" t="n">
-        <v>222775500</v>
+        <v>324925900</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="B69" t="n">
-        <v>174.1225483861358</v>
+        <v>183.4906282252173</v>
       </c>
       <c r="C69" t="n">
-        <v>175.7387615308714</v>
+        <v>183.7300734141942</v>
       </c>
       <c r="D69" t="n">
-        <v>171.4188835631069</v>
+        <v>181.9243013805983</v>
       </c>
       <c r="E69" t="n">
-        <v>173.7334594726562</v>
+        <v>183.2611694335938</v>
       </c>
       <c r="F69" t="n">
-        <v>176096000</v>
+        <v>129064400</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="B70" t="n">
-        <v>176.2575523358494</v>
+        <v>182.5428423541149</v>
       </c>
       <c r="C70" t="n">
-        <v>181.0263919449467</v>
+        <v>188.8879950077845</v>
       </c>
       <c r="D70" t="n">
-        <v>175.9283209122297</v>
+        <v>182.4729984678863</v>
       </c>
       <c r="E70" t="n">
-        <v>180.5674743652344</v>
+        <v>188.7682800292969</v>
       </c>
       <c r="F70" t="n">
-        <v>324925900</v>
+        <v>174873600</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="B71" t="n">
-        <v>183.4906129473229</v>
+        <v>187.5012437217294</v>
       </c>
       <c r="C71" t="n">
-        <v>183.730058116363</v>
+        <v>188.4689804086018</v>
       </c>
       <c r="D71" t="n">
-        <v>181.9242862331203</v>
+        <v>186.154389299292</v>
       </c>
       <c r="E71" t="n">
-        <v>183.2611541748047</v>
+        <v>188.169677734375</v>
       </c>
       <c r="F71" t="n">
-        <v>129064400</v>
+        <v>65528500</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="B72" t="n">
-        <v>182.5428571096804</v>
+        <v>189.4766285187414</v>
       </c>
       <c r="C72" t="n">
-        <v>188.8880102762506</v>
+        <v>192.240166195598</v>
       </c>
       <c r="D72" t="n">
-        <v>182.4730132178061</v>
+        <v>187.5611125998212</v>
       </c>
       <c r="E72" t="n">
-        <v>188.7682952880859</v>
+        <v>190.085205078125</v>
       </c>
       <c r="F72" t="n">
-        <v>174873600</v>
+        <v>139740300</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="B73" t="n">
-        <v>187.5012437217294</v>
+        <v>187.2717899684254</v>
       </c>
       <c r="C73" t="n">
-        <v>188.4689804086018</v>
+        <v>188.3193265216257</v>
       </c>
       <c r="D73" t="n">
-        <v>186.154389299292</v>
+        <v>185.4759890979627</v>
       </c>
       <c r="E73" t="n">
-        <v>188.169677734375</v>
+        <v>187.7805938720703</v>
       </c>
       <c r="F73" t="n">
-        <v>65528500</v>
+        <v>120006100</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="B74" t="n">
-        <v>189.4766133088049</v>
+        <v>187.8005508490403</v>
       </c>
       <c r="C74" t="n">
-        <v>192.2401507638228</v>
+        <v>188.5487999407664</v>
       </c>
       <c r="D74" t="n">
-        <v>187.5610975436497</v>
+        <v>186.4935963146986</v>
       </c>
       <c r="E74" t="n">
-        <v>190.0851898193359</v>
+        <v>187.1021728515625</v>
       </c>
       <c r="F74" t="n">
-        <v>139740300</v>
+        <v>97687300</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46020</v>
+        <v>46022</v>
       </c>
       <c r="B75" t="n">
-        <v>187.2717899684254</v>
+        <v>189.1274459397885</v>
       </c>
       <c r="C75" t="n">
-        <v>188.3193265216257</v>
+        <v>190.1151249886817</v>
       </c>
       <c r="D75" t="n">
-        <v>185.4759890979627</v>
+        <v>186.0546345387688</v>
       </c>
       <c r="E75" t="n">
-        <v>187.7805938720703</v>
+        <v>186.0646057128906</v>
       </c>
       <c r="F75" t="n">
-        <v>120006100</v>
+        <v>120100500</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46021</v>
+        <v>46024</v>
       </c>
       <c r="B76" t="n">
-        <v>187.8005508490403</v>
+        <v>189.3968130035911</v>
       </c>
       <c r="C76" t="n">
-        <v>188.5487999407664</v>
+        <v>192.4795957147097</v>
       </c>
       <c r="D76" t="n">
-        <v>186.4935963146986</v>
+        <v>187.8204997023152</v>
       </c>
       <c r="E76" t="n">
-        <v>187.1021728515625</v>
+        <v>188.4091339111328</v>
       </c>
       <c r="F76" t="n">
-        <v>97687300</v>
+        <v>148240500</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46022</v>
+        <v>46027</v>
       </c>
       <c r="B77" t="n">
-        <v>189.127461449755</v>
+        <v>191.3123182227279</v>
       </c>
       <c r="C77" t="n">
-        <v>190.1151405796458</v>
+        <v>193.1779629368336</v>
       </c>
       <c r="D77" t="n">
-        <v>186.0546497967401</v>
+        <v>185.7154145267434</v>
       </c>
       <c r="E77" t="n">
-        <v>186.0646209716797</v>
+        <v>187.6808166503906</v>
       </c>
       <c r="F77" t="n">
-        <v>120100500</v>
+        <v>183529700</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="B78" t="n">
-        <v>189.3967976648124</v>
+        <v>190.0752284670132</v>
       </c>
       <c r="C78" t="n">
-        <v>192.479580126264</v>
+        <v>191.7213703933745</v>
       </c>
       <c r="D78" t="n">
-        <v>187.8204844911982</v>
+        <v>186.3838692947835</v>
       </c>
       <c r="E78" t="n">
-        <v>188.4091186523438</v>
+        <v>186.8028869628906</v>
       </c>
       <c r="F78" t="n">
-        <v>148240500</v>
+        <v>176862600</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="B79" t="n">
-        <v>191.3123337767646</v>
+        <v>188.1297854095839</v>
       </c>
       <c r="C79" t="n">
-        <v>193.1779786425506</v>
+        <v>190.9232365533545</v>
       </c>
       <c r="D79" t="n">
-        <v>185.7154296257417</v>
+        <v>186.1244680675316</v>
       </c>
       <c r="E79" t="n">
-        <v>187.6808319091797</v>
+        <v>188.6685180664062</v>
       </c>
       <c r="F79" t="n">
-        <v>183529700</v>
+        <v>153543200</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="B80" t="n">
-        <v>190.0752284670132</v>
+        <v>188.6685228499072</v>
       </c>
       <c r="C80" t="n">
-        <v>191.7213703933745</v>
+        <v>189.1074981045344</v>
       </c>
       <c r="D80" t="n">
-        <v>186.3838692947835</v>
+        <v>183.2811352524241</v>
       </c>
       <c r="E80" t="n">
-        <v>186.8028869628906</v>
+        <v>184.6080169677734</v>
       </c>
       <c r="F80" t="n">
-        <v>176862600</v>
+        <v>172457000</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B81" t="n">
-        <v>188.1297701943655</v>
+        <v>184.6479238968445</v>
       </c>
       <c r="C81" t="n">
-        <v>190.9232211122124</v>
+        <v>185.9049768874807</v>
       </c>
       <c r="D81" t="n">
-        <v>186.1244530144955</v>
+        <v>183.2412119543349</v>
       </c>
       <c r="E81" t="n">
-        <v>188.6685028076172</v>
+        <v>184.4284362792969</v>
       </c>
       <c r="F81" t="n">
-        <v>153543200</v>
+        <v>131327500</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="B82" t="n">
-        <v>188.6685228499072</v>
+        <v>182.7922691735387</v>
       </c>
       <c r="C82" t="n">
-        <v>189.1074981045344</v>
+        <v>186.6831584288149</v>
       </c>
       <c r="D82" t="n">
-        <v>183.2811352524241</v>
+        <v>182.5927391235801</v>
       </c>
       <c r="E82" t="n">
-        <v>184.6080169677734</v>
+        <v>184.5082550048828</v>
       </c>
       <c r="F82" t="n">
-        <v>172457000</v>
+        <v>137968500</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="B83" t="n">
-        <v>184.6479238968445</v>
+        <v>184.5680989064521</v>
       </c>
       <c r="C83" t="n">
-        <v>185.9049768874807</v>
+        <v>187.6708389078061</v>
       </c>
       <c r="D83" t="n">
-        <v>183.2412119543349</v>
+        <v>182.9718281779948</v>
       </c>
       <c r="E83" t="n">
-        <v>184.4284362792969</v>
+        <v>185.3762054443359</v>
       </c>
       <c r="F83" t="n">
-        <v>131327500</v>
+        <v>160128900</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="B84" t="n">
-        <v>182.7922691735387</v>
+        <v>183.8897012556695</v>
       </c>
       <c r="C84" t="n">
-        <v>186.6831584288149</v>
+        <v>184.0293738083791</v>
       </c>
       <c r="D84" t="n">
-        <v>182.5927391235801</v>
+        <v>180.3779146434709</v>
       </c>
       <c r="E84" t="n">
-        <v>184.5082550048828</v>
+        <v>182.7124481201172</v>
       </c>
       <c r="F84" t="n">
-        <v>137968500</v>
+        <v>159586100</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="B85" t="n">
-        <v>184.5681140987238</v>
+        <v>186.0646079796491</v>
       </c>
       <c r="C85" t="n">
-        <v>187.6708543554723</v>
+        <v>189.2571344016907</v>
       </c>
       <c r="D85" t="n">
-        <v>182.9718432388734</v>
+        <v>185.895006678512</v>
       </c>
       <c r="E85" t="n">
-        <v>185.376220703125</v>
+        <v>186.6133270263672</v>
       </c>
       <c r="F85" t="n">
-        <v>160128900</v>
+        <v>206188600</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="B86" t="n">
-        <v>183.8897012556695</v>
+        <v>188.6385950815971</v>
       </c>
       <c r="C86" t="n">
-        <v>184.0293738083791</v>
+        <v>189.9954207742267</v>
       </c>
       <c r="D86" t="n">
-        <v>180.3779146434709</v>
+        <v>185.6455985734289</v>
       </c>
       <c r="E86" t="n">
-        <v>182.7124481201172</v>
+        <v>185.7952423095703</v>
       </c>
       <c r="F86" t="n">
-        <v>159586100</v>
+        <v>187967200</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46037</v>
+        <v>46042</v>
       </c>
       <c r="B87" t="n">
-        <v>186.0646079796491</v>
+        <v>181.4753422141945</v>
       </c>
       <c r="C87" t="n">
-        <v>189.2571344016907</v>
+        <v>181.9542325986551</v>
       </c>
       <c r="D87" t="n">
-        <v>185.895006678512</v>
+        <v>177.1953640623503</v>
       </c>
       <c r="E87" t="n">
-        <v>186.6133270263672</v>
+        <v>177.654296875</v>
       </c>
       <c r="F87" t="n">
-        <v>206188600</v>
+        <v>223345300</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46038</v>
+        <v>46043</v>
       </c>
       <c r="B88" t="n">
-        <v>188.6385795892923</v>
+        <v>178.6320081827799</v>
       </c>
       <c r="C88" t="n">
-        <v>189.99540517049</v>
+        <v>184.9472325313386</v>
       </c>
       <c r="D88" t="n">
-        <v>185.6455833269296</v>
+        <v>177.9835164834521</v>
       </c>
       <c r="E88" t="n">
-        <v>185.7952270507812</v>
+        <v>182.8920440673828</v>
       </c>
       <c r="F88" t="n">
-        <v>187967200</v>
+        <v>200381000</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="B89" t="n">
-        <v>181.4753266272146</v>
+        <v>184.3186915464293</v>
       </c>
       <c r="C89" t="n">
-        <v>181.9542169705431</v>
+        <v>185.7353746560278</v>
       </c>
       <c r="D89" t="n">
-        <v>177.1953488429791</v>
+        <v>183.5005985718231</v>
       </c>
       <c r="E89" t="n">
-        <v>177.6542816162109</v>
+        <v>184.4084777832031</v>
       </c>
       <c r="F89" t="n">
-        <v>223345300</v>
+        <v>139636600</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="B90" t="n">
-        <v>178.6320081827799</v>
+        <v>187.0622712594319</v>
       </c>
       <c r="C90" t="n">
-        <v>184.9472325313386</v>
+        <v>189.1573747868041</v>
       </c>
       <c r="D90" t="n">
-        <v>177.9835164834521</v>
+        <v>186.3838660627843</v>
       </c>
       <c r="E90" t="n">
-        <v>182.8920440673828</v>
+        <v>187.2318725585938</v>
       </c>
       <c r="F90" t="n">
-        <v>200381000</v>
+        <v>142748100</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="B91" t="n">
-        <v>184.3186915464293</v>
+        <v>186.7230748442759</v>
       </c>
       <c r="C91" t="n">
-        <v>185.7353746560278</v>
+        <v>188.6784906596197</v>
       </c>
       <c r="D91" t="n">
-        <v>183.5005985718231</v>
+        <v>185.555808059744</v>
       </c>
       <c r="E91" t="n">
-        <v>184.4084777832031</v>
+        <v>186.0346832275391</v>
       </c>
       <c r="F91" t="n">
-        <v>139636600</v>
+        <v>124799600</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="B92" t="n">
-        <v>187.0622712594319</v>
+        <v>186.8028844605491</v>
       </c>
       <c r="C92" t="n">
-        <v>189.1573747868041</v>
+        <v>189.5564356240106</v>
       </c>
       <c r="D92" t="n">
-        <v>186.3838660627843</v>
+        <v>185.2664711415707</v>
       </c>
       <c r="E92" t="n">
-        <v>187.2318725585938</v>
+        <v>188.0798950195312</v>
       </c>
       <c r="F92" t="n">
-        <v>142748100</v>
+        <v>143711600</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="B93" t="n">
-        <v>186.7230748442759</v>
+        <v>190.8234748728661</v>
       </c>
       <c r="C93" t="n">
-        <v>188.6784906596197</v>
+        <v>191.9009553855833</v>
       </c>
       <c r="D93" t="n">
-        <v>185.555808059744</v>
+        <v>189.3968053634026</v>
       </c>
       <c r="E93" t="n">
-        <v>186.0346832275391</v>
+        <v>191.0728912353516</v>
       </c>
       <c r="F93" t="n">
-        <v>124799600</v>
+        <v>148552700</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="B94" t="n">
-        <v>186.8028844605491</v>
+        <v>190.8933105997472</v>
       </c>
       <c r="C94" t="n">
-        <v>189.5564356240106</v>
+        <v>193.0283141326731</v>
       </c>
       <c r="D94" t="n">
-        <v>185.2664711415707</v>
+        <v>185.6256380470483</v>
       </c>
       <c r="E94" t="n">
-        <v>188.0798950195312</v>
+        <v>192.0605773925781</v>
       </c>
       <c r="F94" t="n">
-        <v>143711600</v>
+        <v>171764400</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="B95" t="n">
-        <v>190.8234748728661</v>
+        <v>190.7636224379378</v>
       </c>
       <c r="C95" t="n">
-        <v>191.9009553855833</v>
+        <v>194.0359639826301</v>
       </c>
       <c r="D95" t="n">
-        <v>189.3968053634026</v>
+        <v>189.0276790286862</v>
       </c>
       <c r="E95" t="n">
-        <v>191.0728912353516</v>
+        <v>190.6838073730469</v>
       </c>
       <c r="F95" t="n">
-        <v>148552700</v>
+        <v>179489500</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="B96" t="n">
-        <v>190.8932954336949</v>
+        <v>186.7629659025267</v>
       </c>
       <c r="C96" t="n">
-        <v>193.0282987969995</v>
+        <v>189.8557348322644</v>
       </c>
       <c r="D96" t="n">
-        <v>185.625623299501</v>
+        <v>184.4483900153819</v>
       </c>
       <c r="E96" t="n">
-        <v>192.0605621337891</v>
+        <v>185.1766815185547</v>
       </c>
       <c r="F96" t="n">
-        <v>171764400</v>
+        <v>165794100</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="B97" t="n">
-        <v>190.7636071727618</v>
+        <v>185.8052266227915</v>
       </c>
       <c r="C97" t="n">
-        <v>194.0359484555967</v>
+        <v>185.835155369684</v>
       </c>
       <c r="D97" t="n">
-        <v>189.0276639024229</v>
+        <v>175.8185853097543</v>
       </c>
       <c r="E97" t="n">
-        <v>190.6837921142578</v>
+        <v>179.9189910888672</v>
       </c>
       <c r="F97" t="n">
-        <v>179489500</v>
+        <v>204019600</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B98" t="n">
-        <v>186.7629812920276</v>
+        <v>179.0410571553003</v>
       </c>
       <c r="C98" t="n">
-        <v>189.8557504766133</v>
+        <v>179.1607721437711</v>
       </c>
       <c r="D98" t="n">
-        <v>184.4484052141589</v>
+        <v>171.5086795929406</v>
       </c>
       <c r="E98" t="n">
-        <v>185.1766967773438</v>
+        <v>173.7833557128906</v>
       </c>
       <c r="F98" t="n">
-        <v>165794100</v>
+        <v>207014100</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="B99" t="n">
-        <v>185.8052108647954</v>
+        <v>174.5216119878791</v>
       </c>
       <c r="C99" t="n">
-        <v>185.8351396091497</v>
+        <v>176.4072143255947</v>
       </c>
       <c r="D99" t="n">
-        <v>175.8185703987175</v>
+        <v>170.6307227747363</v>
       </c>
       <c r="E99" t="n">
-        <v>179.9189758300781</v>
+        <v>171.4787445068359</v>
       </c>
       <c r="F99" t="n">
-        <v>204019600</v>
+        <v>206312900</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46057</v>
+        <v>46059</v>
       </c>
       <c r="B100" t="n">
-        <v>179.0410414348666</v>
+        <v>176.2775135166603</v>
       </c>
       <c r="C100" t="n">
-        <v>179.160756412826</v>
+        <v>186.5634420291942</v>
       </c>
       <c r="D100" t="n">
-        <v>171.5086645338761</v>
+        <v>174.1923963475411</v>
       </c>
       <c r="E100" t="n">
-        <v>173.7833404541016</v>
+        <v>184.9771575927734</v>
       </c>
       <c r="F100" t="n">
-        <v>207014100</v>
+        <v>231346200</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="B101" t="n">
-        <v>174.5215964583249</v>
+        <v>183.8298238555102</v>
       </c>
       <c r="C101" t="n">
-        <v>176.4071986282528</v>
+        <v>193.2078878887748</v>
       </c>
       <c r="D101" t="n">
-        <v>170.6307075914073</v>
+        <v>183.5205500126207</v>
       </c>
       <c r="E101" t="n">
-        <v>171.4787292480469</v>
+        <v>189.5963287353516</v>
       </c>
       <c r="F101" t="n">
-        <v>206312900</v>
+        <v>196387400</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="B102" t="n">
-        <v>176.277498975506</v>
+        <v>190.933219719687</v>
       </c>
       <c r="C102" t="n">
-        <v>186.5634266395524</v>
+        <v>192.0306425866914</v>
       </c>
       <c r="D102" t="n">
-        <v>174.1923819783884</v>
+        <v>187.6808205923615</v>
       </c>
       <c r="E102" t="n">
-        <v>184.9771423339844</v>
+        <v>188.0998382568359</v>
       </c>
       <c r="F102" t="n">
-        <v>231346200</v>
+        <v>136764800</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46062</v>
+        <v>46064</v>
       </c>
       <c r="B103" t="n">
-        <v>183.8298238555102</v>
+        <v>192.0007142509167</v>
       </c>
       <c r="C103" t="n">
-        <v>193.2078878887748</v>
+        <v>192.8088208357837</v>
       </c>
       <c r="D103" t="n">
-        <v>183.5205500126207</v>
+        <v>188.329312674443</v>
       </c>
       <c r="E103" t="n">
-        <v>189.5963287353516</v>
+        <v>189.6063232421875</v>
       </c>
       <c r="F103" t="n">
-        <v>196387400</v>
+        <v>144192700</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B104" t="n">
-        <v>190.933219719687</v>
+        <v>192.5793648877844</v>
       </c>
       <c r="C104" t="n">
-        <v>192.0306425866914</v>
+        <v>193.1580126884611</v>
       </c>
       <c r="D104" t="n">
-        <v>187.6808205923615</v>
+        <v>186.0745817463215</v>
       </c>
       <c r="E104" t="n">
-        <v>188.0998382568359</v>
+        <v>186.5035858154297</v>
       </c>
       <c r="F104" t="n">
-        <v>136764800</v>
+        <v>189932500</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="B105" t="n">
-        <v>192.0007297023972</v>
+        <v>187.0423048169314</v>
       </c>
       <c r="C105" t="n">
-        <v>192.8088363522974</v>
+        <v>187.0622623874058</v>
       </c>
       <c r="D105" t="n">
-        <v>188.3293278304631</v>
+        <v>181.1660562233949</v>
       </c>
       <c r="E105" t="n">
-        <v>189.6063385009766</v>
+        <v>182.3832092285156</v>
       </c>
       <c r="F105" t="n">
-        <v>144192700</v>
+        <v>161888000</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46065</v>
+        <v>46070</v>
       </c>
       <c r="B106" t="n">
-        <v>192.5793648877844</v>
+        <v>181.3256935584433</v>
       </c>
       <c r="C106" t="n">
-        <v>193.1580126884611</v>
+        <v>186.7130808403767</v>
       </c>
       <c r="D106" t="n">
-        <v>186.0745817463215</v>
+        <v>178.7616860728079</v>
       </c>
       <c r="E106" t="n">
-        <v>186.5035858154297</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="F106" t="n">
-        <v>189932500</v>
+        <v>162276900</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46066</v>
+        <v>46071</v>
       </c>
       <c r="B107" t="n">
-        <v>187.042320465516</v>
+        <v>188.3093443160685</v>
       </c>
       <c r="C107" t="n">
-        <v>187.0622780376601</v>
+        <v>189.9255573932224</v>
       </c>
       <c r="D107" t="n">
-        <v>181.1660713803529</v>
+        <v>186.3239846890322</v>
       </c>
       <c r="E107" t="n">
-        <v>182.3832244873047</v>
+        <v>187.5411376953125</v>
       </c>
       <c r="F107" t="n">
-        <v>161888000</v>
+        <v>164749100</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="B108" t="n">
-        <v>181.3257085516038</v>
+        <v>186.62329889396</v>
       </c>
       <c r="C108" t="n">
-        <v>186.7130962790006</v>
+        <v>187.9900957055448</v>
       </c>
       <c r="D108" t="n">
-        <v>178.7617008539599</v>
+        <v>185.2265733363672</v>
       </c>
       <c r="E108" t="n">
-        <v>184.5381927490234</v>
+        <v>187.4613342285156</v>
       </c>
       <c r="F108" t="n">
-        <v>162276900</v>
+        <v>126554500</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B109" t="n">
-        <v>188.3093443160685</v>
+        <v>186.1344488846578</v>
       </c>
       <c r="C109" t="n">
-        <v>189.9255573932224</v>
+        <v>189.8856654675195</v>
       </c>
       <c r="D109" t="n">
-        <v>186.3239846890322</v>
+        <v>185.5059147845697</v>
       </c>
       <c r="E109" t="n">
-        <v>187.5411376953125</v>
+        <v>189.3768615722656</v>
       </c>
       <c r="F109" t="n">
-        <v>164749100</v>
+        <v>178422300</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46072</v>
+        <v>46076</v>
       </c>
       <c r="B110" t="n">
-        <v>186.62329889396</v>
+        <v>190.9531547742145</v>
       </c>
       <c r="C110" t="n">
-        <v>187.9900957055448</v>
+        <v>193.4972046328596</v>
       </c>
       <c r="D110" t="n">
-        <v>185.2265733363672</v>
+        <v>189.1374116308485</v>
       </c>
       <c r="E110" t="n">
-        <v>187.4613342285156</v>
+        <v>191.1028137207031</v>
       </c>
       <c r="F110" t="n">
-        <v>126554500</v>
+        <v>171584800</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="B111" t="n">
-        <v>186.1344488846578</v>
+        <v>191.0429698590405</v>
       </c>
       <c r="C111" t="n">
-        <v>189.8856654675195</v>
+        <v>193.3176459547985</v>
       </c>
       <c r="D111" t="n">
-        <v>185.5059147845697</v>
+        <v>186.9625064417709</v>
       </c>
       <c r="E111" t="n">
-        <v>189.3768615722656</v>
+        <v>192.3997955322266</v>
       </c>
       <c r="F111" t="n">
-        <v>178422300</v>
+        <v>175123600</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="B112" t="n">
-        <v>190.9531700210539</v>
+        <v>193.9960453222018</v>
       </c>
       <c r="C112" t="n">
-        <v>193.4972200828311</v>
+        <v>197.1686293956491</v>
       </c>
       <c r="D112" t="n">
-        <v>189.1374267327081</v>
+        <v>193.3375824661624</v>
       </c>
       <c r="E112" t="n">
-        <v>191.1028289794922</v>
+        <v>195.1034545898438</v>
       </c>
       <c r="F112" t="n">
-        <v>171584800</v>
+        <v>250637100</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B113" t="n">
-        <v>191.0429698590405</v>
+        <v>193.8164813019665</v>
       </c>
       <c r="C113" t="n">
-        <v>193.3176459547985</v>
+        <v>193.8364236513225</v>
       </c>
       <c r="D113" t="n">
-        <v>186.9625064417709</v>
+        <v>183.8897126034445</v>
       </c>
       <c r="E113" t="n">
-        <v>192.3997955322266</v>
+        <v>184.4583740234375</v>
       </c>
       <c r="F113" t="n">
-        <v>175123600</v>
+        <v>360807900</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="B114" t="n">
-        <v>193.9960453222018</v>
+        <v>180.8268714126474</v>
       </c>
       <c r="C114" t="n">
-        <v>197.1686293956491</v>
+        <v>182.1637395256691</v>
       </c>
       <c r="D114" t="n">
-        <v>193.3375824661624</v>
+        <v>175.9682453114839</v>
       </c>
       <c r="E114" t="n">
-        <v>195.1034545898438</v>
+        <v>176.7763519287109</v>
       </c>
       <c r="F114" t="n">
-        <v>250637100</v>
+        <v>311636500</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="B115" t="n">
-        <v>193.8164813019665</v>
+        <v>174.6014235260267</v>
       </c>
       <c r="C115" t="n">
-        <v>193.8364236513225</v>
+        <v>183.0317086895539</v>
       </c>
       <c r="D115" t="n">
-        <v>183.8897126034445</v>
+        <v>174.2322921838959</v>
       </c>
       <c r="E115" t="n">
-        <v>184.4583740234375</v>
+        <v>182.0539855957031</v>
       </c>
       <c r="F115" t="n">
-        <v>360807900</v>
+        <v>209095300</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46080</v>
+        <v>46084</v>
       </c>
       <c r="B116" t="n">
-        <v>180.8268714126474</v>
+        <v>178.0733135069376</v>
       </c>
       <c r="C116" t="n">
-        <v>182.1637395256691</v>
+        <v>180.4776756968921</v>
       </c>
       <c r="D116" t="n">
-        <v>175.9682453114839</v>
+        <v>176.5069714269912</v>
       </c>
       <c r="E116" t="n">
-        <v>176.7763519287109</v>
+        <v>179.6296691894531</v>
       </c>
       <c r="F116" t="n">
-        <v>311636500</v>
+        <v>178099400</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="B117" t="n">
-        <v>174.6014235260267</v>
+        <v>180.0187499528396</v>
       </c>
       <c r="C117" t="n">
-        <v>183.0317086895539</v>
+        <v>184.2687991412151</v>
       </c>
       <c r="D117" t="n">
-        <v>174.2322921838959</v>
+        <v>179.6396322236537</v>
       </c>
       <c r="E117" t="n">
-        <v>182.0539855957031</v>
+        <v>182.6126708984375</v>
       </c>
       <c r="F117" t="n">
-        <v>209095300</v>
+        <v>177731200</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="B118" t="n">
-        <v>178.0733135069376</v>
+        <v>180.7470399397241</v>
       </c>
       <c r="C118" t="n">
-        <v>180.4776756968921</v>
+        <v>183.6302923567135</v>
       </c>
       <c r="D118" t="n">
-        <v>176.5069714269912</v>
+        <v>177.4647274492447</v>
       </c>
       <c r="E118" t="n">
-        <v>179.6296691894531</v>
+        <v>182.9119720458984</v>
       </c>
       <c r="F118" t="n">
-        <v>178099400</v>
+        <v>198779700</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="B119" t="n">
-        <v>180.0187649948852</v>
+        <v>179.4201653790109</v>
       </c>
       <c r="C119" t="n">
-        <v>184.2688145383873</v>
+        <v>182.3333469017365</v>
       </c>
       <c r="D119" t="n">
-        <v>179.6396472340209</v>
+        <v>176.4072264371208</v>
       </c>
       <c r="E119" t="n">
-        <v>182.6126861572266</v>
+        <v>177.4048919677734</v>
       </c>
       <c r="F119" t="n">
-        <v>177731200</v>
+        <v>189021900</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="B120" t="n">
-        <v>180.7470550179114</v>
+        <v>176.4171968477281</v>
       </c>
       <c r="C120" t="n">
-        <v>183.6303076754259</v>
+        <v>182.4830050745951</v>
       </c>
       <c r="D120" t="n">
-        <v>177.4647422536165</v>
+        <v>175.1501573668019</v>
       </c>
       <c r="E120" t="n">
-        <v>182.9119873046875</v>
+        <v>182.2236022949219</v>
       </c>
       <c r="F120" t="n">
-        <v>198779700</v>
+        <v>177213600</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="B121" t="n">
-        <v>179.420134514761</v>
+        <v>181.9741760435397</v>
       </c>
       <c r="C121" t="n">
-        <v>182.3333155363547</v>
+        <v>186.0047530762794</v>
       </c>
       <c r="D121" t="n">
-        <v>176.4071960911633</v>
+        <v>181.5850871183009</v>
       </c>
       <c r="E121" t="n">
-        <v>177.4048614501953</v>
+        <v>184.3386535644531</v>
       </c>
       <c r="F121" t="n">
-        <v>189021900</v>
+        <v>179118500</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,25 +3589,25 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="B122" t="n">
-        <v>176.4171820751478</v>
+        <v>185.4860219488843</v>
       </c>
       <c r="C122" t="n">
-        <v>182.4829897940845</v>
+        <v>187.1921136401388</v>
       </c>
       <c r="D122" t="n">
-        <v>175.1501427003192</v>
+        <v>184.0293448898806</v>
       </c>
       <c r="E122" t="n">
-        <v>182.2235870361328</v>
+        <v>185.6057434082031</v>
       </c>
       <c r="F122" t="n">
-        <v>177213600</v>
+        <v>145280400</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="B123" t="n">
-        <v>181.9741760435397</v>
+        <v>183.6302641505579</v>
       </c>
       <c r="C123" t="n">
-        <v>186.0047530762794</v>
+        <v>184.5182338343672</v>
       </c>
       <c r="D123" t="n">
-        <v>181.5850871183009</v>
+        <v>181.3355064165816</v>
       </c>
       <c r="E123" t="n">
-        <v>184.3386535644531</v>
+        <v>182.7223358154297</v>
       </c>
       <c r="F123" t="n">
-        <v>179118500</v>
+        <v>155762700</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,25 +3641,25 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="B124" t="n">
-        <v>185.4860219488843</v>
+        <v>184.4982918130038</v>
       </c>
       <c r="C124" t="n">
-        <v>187.1921136401388</v>
+        <v>185.6656218245341</v>
       </c>
       <c r="D124" t="n">
-        <v>184.0293448898806</v>
+        <v>179.5296528660815</v>
       </c>
       <c r="E124" t="n">
-        <v>185.6057434082031</v>
+        <v>179.8389434814453</v>
       </c>
       <c r="F124" t="n">
-        <v>145280400</v>
+        <v>160988400</v>
       </c>
       <c r="G124" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="B125" t="n">
-        <v>183.6302641505579</v>
+        <v>182.5527246843909</v>
       </c>
       <c r="C125" t="n">
-        <v>184.5182338343672</v>
+        <v>188.4492501487561</v>
       </c>
       <c r="D125" t="n">
-        <v>181.3355064165816</v>
+        <v>180.9962848148914</v>
       </c>
       <c r="E125" t="n">
-        <v>182.7223358154297</v>
+        <v>182.8021545410156</v>
       </c>
       <c r="F125" t="n">
-        <v>155762700</v>
+        <v>217307400</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="B126" t="n">
-        <v>184.4982918130038</v>
+        <v>184.6379731916982</v>
       </c>
       <c r="C126" t="n">
-        <v>185.6656218245341</v>
+        <v>184.9771941770484</v>
       </c>
       <c r="D126" t="n">
-        <v>179.5296528660815</v>
+        <v>181.2656763194747</v>
       </c>
       <c r="E126" t="n">
-        <v>179.8389434814453</v>
+        <v>181.5151062011719</v>
       </c>
       <c r="F126" t="n">
-        <v>160988400</v>
+        <v>182497800</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="B127" t="n">
-        <v>182.5527246843909</v>
+        <v>182.0638447517288</v>
       </c>
       <c r="C127" t="n">
-        <v>188.4492501487561</v>
+        <v>182.9618014097589</v>
       </c>
       <c r="D127" t="n">
-        <v>180.9962848148914</v>
+        <v>179.9187539793071</v>
       </c>
       <c r="E127" t="n">
-        <v>182.8021545410156</v>
+        <v>179.9885864257812</v>
       </c>
       <c r="F127" t="n">
-        <v>217307400</v>
+        <v>156683100</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="B128" t="n">
-        <v>184.6379731916982</v>
+        <v>177.6040222894031</v>
       </c>
       <c r="C128" t="n">
-        <v>184.9771941770484</v>
+        <v>179.5695306962835</v>
       </c>
       <c r="D128" t="n">
-        <v>181.2656763194747</v>
+        <v>175.3890840362079</v>
       </c>
       <c r="E128" t="n">
-        <v>181.5151062011719</v>
+        <v>178.1527709960938</v>
       </c>
       <c r="F128" t="n">
-        <v>182497800</v>
+        <v>170968500</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="B129" t="n">
-        <v>182.0638447517288</v>
+        <v>177.5940686691464</v>
       </c>
       <c r="C129" t="n">
-        <v>182.9618014097589</v>
+        <v>177.853470255105</v>
       </c>
       <c r="D129" t="n">
-        <v>179.9187539793071</v>
+        <v>171.3283915093003</v>
       </c>
       <c r="E129" t="n">
-        <v>179.9885864257812</v>
+        <v>172.30615234375</v>
       </c>
       <c r="F129" t="n">
-        <v>156683100</v>
+        <v>241323500</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="B130" t="n">
-        <v>177.6040222894031</v>
+        <v>176.8557415306554</v>
       </c>
       <c r="C130" t="n">
-        <v>179.5695306962835</v>
+        <v>177.9632107122345</v>
       </c>
       <c r="D130" t="n">
-        <v>175.3890840362079</v>
+        <v>174.3614429436745</v>
       </c>
       <c r="E130" t="n">
-        <v>178.1527709960938</v>
+        <v>175.2394409179688</v>
       </c>
       <c r="F130" t="n">
-        <v>170968500</v>
+        <v>182836300</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="B131" t="n">
-        <v>177.5940686691464</v>
+        <v>174.4312942297872</v>
       </c>
       <c r="C131" t="n">
-        <v>177.853470255105</v>
+        <v>175.8181236639554</v>
       </c>
       <c r="D131" t="n">
-        <v>171.3283915093003</v>
+        <v>173.5832266030264</v>
       </c>
       <c r="E131" t="n">
-        <v>172.30615234375</v>
+        <v>174.8004455566406</v>
       </c>
       <c r="F131" t="n">
-        <v>241323500</v>
+        <v>147667800</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="B132" t="n">
-        <v>176.8557415306554</v>
+        <v>176.6961233561449</v>
       </c>
       <c r="C132" t="n">
-        <v>177.9632107122345</v>
+        <v>180.8067226806179</v>
       </c>
       <c r="D132" t="n">
-        <v>174.3614429436745</v>
+        <v>176.4466934898736</v>
       </c>
       <c r="E132" t="n">
-        <v>175.2394409179688</v>
+        <v>178.2725067138672</v>
       </c>
       <c r="F132" t="n">
-        <v>182836300</v>
+        <v>162602100</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B133" t="n">
-        <v>174.4312942297872</v>
+        <v>175.6684741654964</v>
       </c>
       <c r="C133" t="n">
-        <v>175.8181236639554</v>
+        <v>176.1074579435819</v>
       </c>
       <c r="D133" t="n">
-        <v>173.5832266030264</v>
+        <v>170.7497092682189</v>
       </c>
       <c r="E133" t="n">
-        <v>174.8004455566406</v>
+        <v>170.8494873046875</v>
       </c>
       <c r="F133" t="n">
-        <v>147667800</v>
+        <v>186152200</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="B134" t="n">
-        <v>176.6961233561449</v>
+        <v>169.6123099949711</v>
       </c>
       <c r="C134" t="n">
-        <v>180.8067226806179</v>
+        <v>170.5800990993323</v>
       </c>
       <c r="D134" t="n">
-        <v>176.4466934898736</v>
+        <v>166.629123297364</v>
       </c>
       <c r="E134" t="n">
-        <v>178.2725067138672</v>
+        <v>167.1379699707031</v>
       </c>
       <c r="F134" t="n">
-        <v>162602100</v>
+        <v>196212700</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="B135" t="n">
-        <v>175.6684741654964</v>
+        <v>168.3950875250076</v>
       </c>
       <c r="C135" t="n">
-        <v>176.1074579435819</v>
+        <v>169.0635577295173</v>
       </c>
       <c r="D135" t="n">
-        <v>170.7497092682189</v>
+        <v>163.8953782868944</v>
       </c>
       <c r="E135" t="n">
-        <v>170.8494873046875</v>
+        <v>164.7933197021484</v>
       </c>
       <c r="F135" t="n">
-        <v>186152200</v>
+        <v>185627000</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="B136" t="n">
-        <v>169.6123099949711</v>
+        <v>166.589210422399</v>
       </c>
       <c r="C136" t="n">
-        <v>170.5800990993323</v>
+        <v>174.2217577880002</v>
       </c>
       <c r="D136" t="n">
-        <v>166.629123297364</v>
+        <v>166.5792387089764</v>
       </c>
       <c r="E136" t="n">
-        <v>167.1379699707031</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="F136" t="n">
-        <v>196212700</v>
+        <v>226181300</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="B137" t="n">
-        <v>168.3950875250076</v>
+        <v>175.5986119754623</v>
       </c>
       <c r="C137" t="n">
-        <v>169.0635577295173</v>
+        <v>176.9654826629128</v>
       </c>
       <c r="D137" t="n">
-        <v>163.8953782868944</v>
+        <v>174.351462742682</v>
       </c>
       <c r="E137" t="n">
-        <v>164.7933197021484</v>
+        <v>175.3491821289062</v>
       </c>
       <c r="F137" t="n">
-        <v>185627000</v>
+        <v>168132000</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="B138" t="n">
-        <v>166.589210422399</v>
+        <v>171.787333172162</v>
       </c>
       <c r="C138" t="n">
-        <v>174.2217577880002</v>
+        <v>177.0852364118599</v>
       </c>
       <c r="D138" t="n">
-        <v>166.5792387089764</v>
+        <v>170.9791828272563</v>
       </c>
       <c r="E138" t="n">
-        <v>174.0022583007812</v>
+        <v>176.9854583740234</v>
       </c>
       <c r="F138" t="n">
-        <v>226181300</v>
+        <v>143143200</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B139" t="n">
-        <v>175.5986119754623</v>
+        <v>176.7559774774269</v>
       </c>
       <c r="C139" t="n">
-        <v>176.9654826629128</v>
+        <v>177.3845303646084</v>
       </c>
       <c r="D139" t="n">
-        <v>174.351462742682</v>
+        <v>175.3591611441553</v>
       </c>
       <c r="E139" t="n">
-        <v>175.3491821289062</v>
+        <v>177.2348785400391</v>
       </c>
       <c r="F139" t="n">
-        <v>168132000</v>
+        <v>107564300</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B140" t="n">
-        <v>171.787333172162</v>
+        <v>175.3292270516068</v>
       </c>
       <c r="C140" t="n">
-        <v>177.0852364118599</v>
+        <v>177.8235255680002</v>
       </c>
       <c r="D140" t="n">
-        <v>170.9791828272563</v>
+        <v>173.2639557965079</v>
       </c>
       <c r="E140" t="n">
-        <v>176.9854583740234</v>
+        <v>177.6938323974609</v>
       </c>
       <c r="F140" t="n">
-        <v>143143200</v>
+        <v>132534900</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="B141" t="n">
-        <v>176.7559774774269</v>
+        <v>184.079243714486</v>
       </c>
       <c r="C141" t="n">
-        <v>177.3845303646084</v>
+        <v>184.837505037226</v>
       </c>
       <c r="D141" t="n">
-        <v>175.3591611441553</v>
+        <v>179.8888249511496</v>
       </c>
       <c r="E141" t="n">
-        <v>177.2348785400391</v>
+        <v>181.6647644042969</v>
       </c>
       <c r="F141" t="n">
-        <v>107564300</v>
+        <v>147732700</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="B142" t="n">
-        <v>175.3292270516068</v>
+        <v>181.4253138719204</v>
       </c>
       <c r="C142" t="n">
-        <v>177.8235255680002</v>
+        <v>183.6602110774668</v>
       </c>
       <c r="D142" t="n">
-        <v>173.2639557965079</v>
+        <v>180.2080948395415</v>
       </c>
       <c r="E142" t="n">
-        <v>177.6938323974609</v>
+        <v>183.4906005859375</v>
       </c>
       <c r="F142" t="n">
-        <v>132534900</v>
+        <v>116428500</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="B143" t="n">
-        <v>184.079243714486</v>
+        <v>183.8896736698189</v>
       </c>
       <c r="C143" t="n">
-        <v>184.837505037226</v>
+        <v>189.5666999081706</v>
       </c>
       <c r="D143" t="n">
-        <v>179.8888249511496</v>
+        <v>183.8797019557237</v>
       </c>
       <c r="E143" t="n">
-        <v>181.6647644042969</v>
+        <v>188.1998291015625</v>
       </c>
       <c r="F143" t="n">
-        <v>147732700</v>
+        <v>160459500</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="B144" t="n">
-        <v>181.4253138719204</v>
+        <v>185.605746824658</v>
       </c>
       <c r="C144" t="n">
-        <v>183.6602110774668</v>
+        <v>189.2274732756209</v>
       </c>
       <c r="D144" t="n">
-        <v>180.2080948395415</v>
+        <v>185.3164148846483</v>
       </c>
       <c r="E144" t="n">
-        <v>183.4906005859375</v>
+        <v>188.8782653808594</v>
       </c>
       <c r="F144" t="n">
-        <v>116428500</v>
+        <v>133648200</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="B145" t="n">
-        <v>183.8896736698189</v>
+        <v>190.4047764107204</v>
       </c>
       <c r="C145" t="n">
-        <v>189.5666999081706</v>
+        <v>196.0618438720703</v>
       </c>
       <c r="D145" t="n">
-        <v>183.8797019557237</v>
+        <v>190.3349439656124</v>
       </c>
       <c r="E145" t="n">
-        <v>188.1998291015625</v>
+        <v>196.0618438720703</v>
       </c>
       <c r="F145" t="n">
-        <v>160459500</v>
+        <v>161307000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="B146" t="n">
-        <v>185.605746824658</v>
+        <v>196.0917851116163</v>
       </c>
       <c r="C146" t="n">
-        <v>189.2274732756209</v>
+        <v>199.9429830157183</v>
       </c>
       <c r="D146" t="n">
-        <v>185.3164148846483</v>
+        <v>195.2936216855987</v>
       </c>
       <c r="E146" t="n">
-        <v>188.8782653808594</v>
+        <v>198.4164733886719</v>
       </c>
       <c r="F146" t="n">
-        <v>133648200</v>
+        <v>185338400</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="B147" t="n">
-        <v>190.4047764107204</v>
+        <v>196.9797440092329</v>
       </c>
       <c r="C147" t="n">
-        <v>196.0618438720703</v>
+        <v>199.3942384790618</v>
       </c>
       <c r="D147" t="n">
-        <v>190.3349439656124</v>
+        <v>195.3634433694217</v>
       </c>
       <c r="E147" t="n">
-        <v>196.0618438720703</v>
+        <v>197.8976593017578</v>
       </c>
       <c r="F147" t="n">
-        <v>161307000</v>
+        <v>134012900</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46127</v>
+        <v>46129</v>
       </c>
       <c r="B148" t="n">
-        <v>196.0917851116163</v>
+        <v>199.444107632571</v>
       </c>
       <c r="C148" t="n">
-        <v>199.9429830157183</v>
+        <v>201.2400056483541</v>
       </c>
       <c r="D148" t="n">
-        <v>195.2936216855987</v>
+        <v>198.8155547450397</v>
       </c>
       <c r="E148" t="n">
-        <v>198.4164733886719</v>
+        <v>201.2200469970703</v>
       </c>
       <c r="F148" t="n">
-        <v>185338400</v>
+        <v>160324400</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="B149" t="n">
-        <v>196.9797440092329</v>
+        <v>199.5239239232554</v>
       </c>
       <c r="C149" t="n">
-        <v>199.3942384790618</v>
+        <v>201.7089318732817</v>
       </c>
       <c r="D149" t="n">
-        <v>195.3634433694217</v>
+        <v>197.3888049886708</v>
       </c>
       <c r="E149" t="n">
-        <v>197.8976593017578</v>
+        <v>201.5991821289062</v>
       </c>
       <c r="F149" t="n">
-        <v>134012900</v>
+        <v>119381400</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="B150" t="n">
-        <v>199.444107632571</v>
+        <v>201.6690479582887</v>
       </c>
       <c r="C150" t="n">
-        <v>201.2400056483541</v>
+        <v>202.2876291783034</v>
       </c>
       <c r="D150" t="n">
-        <v>198.8155547450397</v>
+        <v>198.5461810430697</v>
       </c>
       <c r="E150" t="n">
-        <v>201.2200469970703</v>
+        <v>199.4241790771484</v>
       </c>
       <c r="F150" t="n">
-        <v>160324400</v>
+        <v>107945300</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B151" t="n">
-        <v>199.5239239232554</v>
+        <v>200.5316418294082</v>
       </c>
       <c r="C151" t="n">
-        <v>201.7089318732817</v>
+        <v>202.0381927490234</v>
       </c>
       <c r="D151" t="n">
-        <v>197.3888049886708</v>
+        <v>198.546174602744</v>
       </c>
       <c r="E151" t="n">
-        <v>201.5991821289062</v>
+        <v>202.0381927490234</v>
       </c>
       <c r="F151" t="n">
-        <v>119381400</v>
+        <v>107501000</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B152" t="n">
-        <v>201.6690479582887</v>
+        <v>201.9982837593082</v>
       </c>
       <c r="C152" t="n">
-        <v>202.2876291783034</v>
+        <v>203.3651545152774</v>
       </c>
       <c r="D152" t="n">
-        <v>198.5461810430697</v>
+        <v>196.7702284327844</v>
       </c>
       <c r="E152" t="n">
-        <v>199.4241790771484</v>
+        <v>199.1847076416016</v>
       </c>
       <c r="F152" t="n">
-        <v>107945300</v>
+        <v>113561800</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="B153" t="n">
-        <v>200.5316418294082</v>
+        <v>199.5039827094276</v>
       </c>
       <c r="C153" t="n">
-        <v>202.0381927490234</v>
+        <v>210.468909435165</v>
       </c>
       <c r="D153" t="n">
-        <v>198.546174602744</v>
+        <v>199.3543156614425</v>
       </c>
       <c r="E153" t="n">
-        <v>202.0381927490234</v>
+        <v>207.7950286865234</v>
       </c>
       <c r="F153" t="n">
-        <v>107501000</v>
+        <v>214134400</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="B154" t="n">
-        <v>201.9982837593082</v>
+        <v>209.1718784416434</v>
       </c>
       <c r="C154" t="n">
-        <v>203.3651545152774</v>
+        <v>216.335512072091</v>
       </c>
       <c r="D154" t="n">
-        <v>196.7702284327844</v>
+        <v>206.9070662315077</v>
       </c>
       <c r="E154" t="n">
-        <v>199.1847076416016</v>
+        <v>216.1160125732422</v>
       </c>
       <c r="F154" t="n">
-        <v>113561800</v>
+        <v>187172400</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="B155" t="n">
-        <v>199.5039827094276</v>
+        <v>209.0122528840405</v>
       </c>
       <c r="C155" t="n">
-        <v>210.468909435165</v>
+        <v>214.2402930542568</v>
       </c>
       <c r="D155" t="n">
-        <v>199.3543156614425</v>
+        <v>207.7251862691963</v>
       </c>
       <c r="E155" t="n">
-        <v>207.7950286865234</v>
+        <v>212.6838531494141</v>
       </c>
       <c r="F155" t="n">
-        <v>214134400</v>
+        <v>180275400</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="B156" t="n">
-        <v>209.1718784416434</v>
+        <v>212.2149257168926</v>
       </c>
       <c r="C156" t="n">
-        <v>216.335512072091</v>
+        <v>212.2348843687743</v>
       </c>
       <c r="D156" t="n">
-        <v>206.9070662315077</v>
+        <v>207.1066069625242</v>
       </c>
       <c r="E156" t="n">
-        <v>216.1160125732422</v>
+        <v>208.7727966308594</v>
       </c>
       <c r="F156" t="n">
-        <v>187172400</v>
+        <v>123711800</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B157" t="n">
-        <v>209.0122528840405</v>
+        <v>209.4512265433391</v>
       </c>
       <c r="C157" t="n">
-        <v>214.2402930542568</v>
+        <v>209.8203930740204</v>
       </c>
       <c r="D157" t="n">
-        <v>207.7251862691963</v>
+        <v>198.2468419328838</v>
       </c>
       <c r="E157" t="n">
-        <v>212.6838531494141</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="F157" t="n">
-        <v>180275400</v>
+        <v>225239200</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B158" t="n">
-        <v>212.2149257168926</v>
+        <v>200.8209846036705</v>
       </c>
       <c r="C158" t="n">
-        <v>212.2348843687743</v>
+        <v>202.5370634031337</v>
       </c>
       <c r="D158" t="n">
-        <v>207.1066069625242</v>
+        <v>196.6704677294345</v>
       </c>
       <c r="E158" t="n">
-        <v>208.7727966308594</v>
+        <v>197.9974365234375</v>
       </c>
       <c r="F158" t="n">
-        <v>123711800</v>
+        <v>128647000</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="B159" t="n">
-        <v>209.4512265433391</v>
+        <v>199.0450218084295</v>
       </c>
       <c r="C159" t="n">
-        <v>209.8203930740204</v>
+        <v>201.2699318245734</v>
       </c>
       <c r="D159" t="n">
-        <v>198.2468419328838</v>
+        <v>194.2958829090753</v>
       </c>
       <c r="E159" t="n">
-        <v>199.1148681640625</v>
+        <v>198.02734375</v>
       </c>
       <c r="F159" t="n">
-        <v>225239200</v>
+        <v>125368100</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="B160" t="n">
-        <v>200.8209846036705</v>
+        <v>198.8454820247872</v>
       </c>
       <c r="C160" t="n">
-        <v>202.5370634031337</v>
+        <v>199.7833407086998</v>
       </c>
       <c r="D160" t="n">
-        <v>196.6704677294345</v>
+        <v>195.5829352820671</v>
       </c>
       <c r="E160" t="n">
-        <v>197.9974365234375</v>
+        <v>196.0518646240234</v>
       </c>
       <c r="F160" t="n">
-        <v>128647000</v>
+        <v>113406600</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B161" t="n">
-        <v>199.0450218084295</v>
+        <v>199.4341385249406</v>
       </c>
       <c r="C161" t="n">
-        <v>201.2699318245734</v>
+        <v>207.7950323152332</v>
       </c>
       <c r="D161" t="n">
-        <v>194.2958829090753</v>
+        <v>198.1570588579161</v>
       </c>
       <c r="E161" t="n">
-        <v>198.02734375</v>
+        <v>207.3560333251953</v>
       </c>
       <c r="F161" t="n">
-        <v>125368100</v>
+        <v>188362800</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B162" t="n">
-        <v>198.8454820247872</v>
+        <v>207.8648724722903</v>
       </c>
       <c r="C162" t="n">
-        <v>199.7833407086998</v>
+        <v>213.7115092245668</v>
       </c>
       <c r="D162" t="n">
-        <v>195.5829352820671</v>
+        <v>206.0290722858257</v>
       </c>
       <c r="E162" t="n">
-        <v>196.0518646240234</v>
+        <v>211.0176696777344</v>
       </c>
       <c r="F162" t="n">
-        <v>113406600</v>
+        <v>168307900</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B163" t="n">
-        <v>199.4341385249406</v>
+        <v>212.5441790763045</v>
       </c>
       <c r="C163" t="n">
-        <v>207.7950323152332</v>
+        <v>217.3033052467507</v>
       </c>
       <c r="D163" t="n">
-        <v>198.1570588579161</v>
+        <v>212.4044989584125</v>
       </c>
       <c r="E163" t="n">
-        <v>207.3560333251953</v>
+        <v>214.709228515625</v>
       </c>
       <c r="F163" t="n">
-        <v>188362800</v>
+        <v>136421400</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B164" t="n">
-        <v>207.8648724722903</v>
+        <v>213.5518657378577</v>
       </c>
       <c r="C164" t="n">
-        <v>213.7115092245668</v>
+        <v>221.7930381906342</v>
       </c>
       <c r="D164" t="n">
-        <v>206.0290722858257</v>
+        <v>213.402213909002</v>
       </c>
       <c r="E164" t="n">
-        <v>211.0176696777344</v>
+        <v>218.9395599365234</v>
       </c>
       <c r="F164" t="n">
-        <v>168307900</v>
+        <v>160685800</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B165" t="n">
-        <v>212.5441790763045</v>
+        <v>218.0515943496244</v>
       </c>
       <c r="C165" t="n">
-        <v>217.3033052467507</v>
+        <v>223.239732575863</v>
       </c>
       <c r="D165" t="n">
-        <v>212.4044989584125</v>
+        <v>214.4298677829735</v>
       </c>
       <c r="E165" t="n">
-        <v>214.709228515625</v>
+        <v>220.2765045166016</v>
       </c>
       <c r="F165" t="n">
-        <v>136421400</v>
+        <v>159176600</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B166" t="n">
-        <v>213.5518657378577</v>
+        <v>224.4170305354026</v>
       </c>
       <c r="C166" t="n">
-        <v>221.7930381906342</v>
+        <v>227.3203978139454</v>
       </c>
       <c r="D166" t="n">
-        <v>213.402213909002</v>
+        <v>221.0647077692387</v>
       </c>
       <c r="E166" t="n">
-        <v>218.9395599365234</v>
+        <v>225.3149871826172</v>
       </c>
       <c r="F166" t="n">
-        <v>160685800</v>
+        <v>150405400</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B167" t="n">
-        <v>218.0515943496244</v>
+        <v>229.3258255277811</v>
       </c>
       <c r="C167" t="n">
-        <v>223.239732575863</v>
+        <v>236.0005559723521</v>
       </c>
       <c r="D167" t="n">
-        <v>214.4298677829735</v>
+        <v>228.7770767762568</v>
       </c>
       <c r="E167" t="n">
-        <v>220.2765045166016</v>
+        <v>235.202392578125</v>
       </c>
       <c r="F167" t="n">
-        <v>159176600</v>
+        <v>180782900</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B168" t="n">
-        <v>224.4170305354026</v>
+        <v>229.2360138852663</v>
       </c>
       <c r="C168" t="n">
-        <v>227.3203978139454</v>
+        <v>230.9720511978</v>
       </c>
       <c r="D168" t="n">
-        <v>221.0647077692387</v>
+        <v>223.7286135177626</v>
       </c>
       <c r="E168" t="n">
-        <v>225.3149871826172</v>
+        <v>224.80615234375</v>
       </c>
       <c r="F168" t="n">
-        <v>150405400</v>
+        <v>180977600</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="B169" t="n">
-        <v>229.3258255277811</v>
+        <v>229.345773483712</v>
       </c>
       <c r="C169" t="n">
-        <v>236.0005559723521</v>
+        <v>229.4754818886306</v>
       </c>
       <c r="D169" t="n">
-        <v>228.7770767762568</v>
+        <v>217.8719993892805</v>
       </c>
       <c r="E169" t="n">
-        <v>235.202392578125</v>
+        <v>221.8130035400391</v>
       </c>
       <c r="F169" t="n">
-        <v>180782900</v>
+        <v>146280900</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B170" t="n">
-        <v>229.2360138852663</v>
+        <v>219.1191400841904</v>
       </c>
       <c r="C170" t="n">
-        <v>230.9720511978</v>
+        <v>223.9680572056967</v>
       </c>
       <c r="D170" t="n">
-        <v>223.7286135177626</v>
+        <v>217.4130483552105</v>
       </c>
       <c r="E170" t="n">
-        <v>224.80615234375</v>
+        <v>220.1068878173828</v>
       </c>
       <c r="F170" t="n">
-        <v>180977600</v>
+        <v>140948200</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B171" t="n">
-        <v>229.345773483712</v>
+        <v>222.6710257508039</v>
       </c>
       <c r="C171" t="n">
-        <v>229.4754818886306</v>
+        <v>225.6143103895453</v>
       </c>
       <c r="D171" t="n">
-        <v>217.8719993892805</v>
+        <v>219.9971448577806</v>
       </c>
       <c r="E171" t="n">
-        <v>221.8130035400391</v>
+        <v>222.9603729248047</v>
       </c>
       <c r="F171" t="n">
-        <v>146280900</v>
+        <v>184201600</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="B172" t="n">
-        <v>219.1191400841904</v>
+        <v>221.7830583738447</v>
       </c>
       <c r="C172" t="n">
-        <v>223.9680572056967</v>
+        <v>226.8814055684356</v>
       </c>
       <c r="D172" t="n">
-        <v>217.4130483552105</v>
+        <v>217.4330007955402</v>
       </c>
       <c r="E172" t="n">
-        <v>220.1068878173828</v>
+        <v>219.0093994140625</v>
       </c>
       <c r="F172" t="n">
-        <v>140948200</v>
+        <v>203381800</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B173" t="n">
-        <v>222.6710257508039</v>
+        <v>220.3962175709585</v>
       </c>
       <c r="C173" t="n">
-        <v>225.6143103895453</v>
+        <v>220.5059673180016</v>
       </c>
       <c r="D173" t="n">
-        <v>219.9971448577806</v>
+        <v>214.3101381389001</v>
       </c>
       <c r="E173" t="n">
-        <v>222.9603729248047</v>
+        <v>214.8389282226562</v>
       </c>
       <c r="F173" t="n">
-        <v>184201600</v>
+        <v>169275700</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="B174" t="n">
-        <v>221.7830583738447</v>
+        <v>216.0461718127993</v>
       </c>
       <c r="C174" t="n">
-        <v>226.8814055684356</v>
+        <v>217.6824311685512</v>
       </c>
       <c r="D174" t="n">
-        <v>217.4330007955402</v>
+        <v>211.5165320236786</v>
       </c>
       <c r="E174" t="n">
-        <v>219.0093994140625</v>
+        <v>214.3700103759766</v>
       </c>
       <c r="F174" t="n">
-        <v>203381800</v>
+        <v>187202600</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="B175" t="n">
-        <v>220.3962175709585</v>
+        <v>213.6316806617713</v>
       </c>
       <c r="C175" t="n">
-        <v>220.5059673180016</v>
+        <v>213.6616110269177</v>
       </c>
       <c r="D175" t="n">
-        <v>214.3101381389001</v>
+        <v>208.3038625298546</v>
       </c>
       <c r="E175" t="n">
-        <v>214.8389282226562</v>
+        <v>212.1151580810547</v>
       </c>
       <c r="F175" t="n">
-        <v>169275700</v>
+        <v>167601200</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="B176" t="n">
-        <v>216.0461718127993</v>
+        <v>210.7981702457166</v>
       </c>
       <c r="C176" t="n">
-        <v>217.6824311685512</v>
+        <v>215.0285063161196</v>
       </c>
       <c r="D176" t="n">
-        <v>211.5165320236786</v>
+        <v>210.738309512832</v>
       </c>
       <c r="E176" t="n">
-        <v>214.3700103759766</v>
+        <v>213.7613983154297</v>
       </c>
       <c r="F176" t="n">
-        <v>187202600</v>
+        <v>143996000</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B177" t="n">
-        <v>213.6316806617713</v>
+        <v>214.0906505321041</v>
       </c>
       <c r="C177" t="n">
-        <v>213.6616110269177</v>
+        <v>217.3631692496548</v>
       </c>
       <c r="D177" t="n">
-        <v>208.3038625298546</v>
+        <v>210.6485213277038</v>
       </c>
       <c r="E177" t="n">
-        <v>212.1151580810547</v>
+        <v>210.6584930419922</v>
       </c>
       <c r="F177" t="n">
-        <v>167601200</v>
+        <v>289410600</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="B178" t="n">
-        <v>210.7981702457166</v>
+        <v>215.2380189209027</v>
       </c>
       <c r="C178" t="n">
-        <v>215.0285063161196</v>
+        <v>224.3571743491113</v>
       </c>
       <c r="D178" t="n">
-        <v>210.738309512832</v>
+        <v>215.2080885544549</v>
       </c>
       <c r="E178" t="n">
-        <v>213.7613983154297</v>
+        <v>223.8483428955078</v>
       </c>
       <c r="F178" t="n">
-        <v>143996000</v>
+        <v>212850700</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="B179" t="n">
-        <v>214.0906505321041</v>
+        <v>226.6618858382332</v>
       </c>
       <c r="C179" t="n">
-        <v>217.3631692496548</v>
+        <v>231.7502608645459</v>
       </c>
       <c r="D179" t="n">
-        <v>210.6485213277038</v>
+        <v>220.8451951370975</v>
       </c>
       <c r="E179" t="n">
-        <v>210.6584930419922</v>
+        <v>222.3118438720703</v>
       </c>
       <c r="F179" t="n">
-        <v>289410600</v>
+        <v>193362900</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B180" t="n">
-        <v>215.2380189209027</v>
+        <v>221.2143597561905</v>
       </c>
       <c r="C180" t="n">
-        <v>224.3571743491113</v>
+        <v>222.3118572511273</v>
       </c>
       <c r="D180" t="n">
-        <v>215.2080885544549</v>
+        <v>214.0207957553572</v>
       </c>
       <c r="E180" t="n">
-        <v>223.8483428955078</v>
+        <v>214.26025390625</v>
       </c>
       <c r="F180" t="n">
-        <v>212850700</v>
+        <v>160907000</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,25 +5123,25 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B181" t="n">
-        <v>226.6618858382332</v>
+        <v>213.6709127939037</v>
       </c>
       <c r="C181" t="n">
-        <v>231.7502608645459</v>
+        <v>221.3523199881091</v>
       </c>
       <c r="D181" t="n">
-        <v>220.8451951370975</v>
+        <v>210.73419644349</v>
       </c>
       <c r="E181" t="n">
-        <v>222.3118438720703</v>
+        <v>218.4156036376953</v>
       </c>
       <c r="F181" t="n">
-        <v>193362900</v>
+        <v>169022200</v>
       </c>
       <c r="G181" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B182" t="n">
-        <v>221.2143597561905</v>
+        <v>214.2902104723603</v>
       </c>
       <c r="C182" t="n">
-        <v>222.3118572511273</v>
+        <v>214.6298267834636</v>
       </c>
       <c r="D182" t="n">
-        <v>214.0207957553572</v>
+        <v>204.101614447126</v>
       </c>
       <c r="E182" t="n">
-        <v>214.26025390625</v>
+        <v>204.8707580566406</v>
       </c>
       <c r="F182" t="n">
-        <v>160907000</v>
+        <v>219655500</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,25 +5175,25 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B183" t="n">
-        <v>213.6709127939037</v>
+        <v>209.9450713288228</v>
       </c>
       <c r="C183" t="n">
-        <v>221.3523199881091</v>
+        <v>210.2347557268212</v>
       </c>
       <c r="D183" t="n">
-        <v>210.73419644349</v>
+        <v>205.7697506938822</v>
       </c>
       <c r="E183" t="n">
-        <v>218.4156036376953</v>
+        <v>208.4067993164062</v>
       </c>
       <c r="F183" t="n">
-        <v>169022200</v>
+        <v>138372800</v>
       </c>
       <c r="G183" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B184" t="n">
-        <v>214.2902104723603</v>
+        <v>210.3845825512031</v>
       </c>
       <c r="C184" t="n">
-        <v>214.6298267834636</v>
+        <v>211.1637095162451</v>
       </c>
       <c r="D184" t="n">
-        <v>204.101614447126</v>
+        <v>199.1171915656509</v>
       </c>
       <c r="E184" t="n">
-        <v>204.8707580566406</v>
+        <v>207.9573059082031</v>
       </c>
       <c r="F184" t="n">
-        <v>219655500</v>
+        <v>180962500</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B185" t="n">
-        <v>209.9450713288228</v>
+        <v>204.2014963256503</v>
       </c>
       <c r="C185" t="n">
-        <v>210.2347557268212</v>
+        <v>206.9883864105018</v>
       </c>
       <c r="D185" t="n">
-        <v>205.7697506938822</v>
+        <v>199.696542748819</v>
       </c>
       <c r="E185" t="n">
-        <v>208.4067993164062</v>
+        <v>200.1959838867188</v>
       </c>
       <c r="F185" t="n">
-        <v>138372800</v>
+        <v>161746600</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B186" t="n">
-        <v>210.3845825512031</v>
+        <v>201.2647947500858</v>
       </c>
       <c r="C186" t="n">
-        <v>211.1637095162451</v>
+        <v>205.4301320010667</v>
       </c>
       <c r="D186" t="n">
-        <v>199.1171915656509</v>
+        <v>199.3169621236104</v>
       </c>
       <c r="E186" t="n">
-        <v>207.9573059082031</v>
+        <v>204.6410064697266</v>
       </c>
       <c r="F186" t="n">
-        <v>180962500</v>
+        <v>158643200</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B187" t="n">
-        <v>204.2014963256503</v>
+        <v>204.6310298517525</v>
       </c>
       <c r="C187" t="n">
-        <v>206.9883864105018</v>
+        <v>206.8385664547524</v>
       </c>
       <c r="D187" t="n">
-        <v>199.696542748819</v>
+        <v>203.2126188059985</v>
       </c>
       <c r="E187" t="n">
-        <v>200.1959838867188</v>
+        <v>204.9606628417969</v>
       </c>
       <c r="F187" t="n">
-        <v>161746600</v>
+        <v>112001800</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="B188" t="n">
-        <v>201.2647947500858</v>
+        <v>208.6864864049894</v>
       </c>
       <c r="C188" t="n">
-        <v>205.4301320010667</v>
+        <v>212.4722588232193</v>
       </c>
       <c r="D188" t="n">
-        <v>199.3169621236104</v>
+        <v>208.1071328472061</v>
       </c>
       <c r="E188" t="n">
-        <v>204.6410064697266</v>
+        <v>212.2125396728516</v>
       </c>
       <c r="F188" t="n">
-        <v>158643200</v>
+        <v>149936700</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="B189" t="n">
-        <v>204.6310298517525</v>
+        <v>210.9439520928381</v>
       </c>
       <c r="C189" t="n">
-        <v>206.8385664547524</v>
+        <v>211.2536184019877</v>
       </c>
       <c r="D189" t="n">
-        <v>203.2126188059985</v>
+        <v>207.0583006421773</v>
       </c>
       <c r="E189" t="n">
-        <v>204.9606628417969</v>
+        <v>207.1781768798828</v>
       </c>
       <c r="F189" t="n">
-        <v>112001800</v>
+        <v>125694100</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B190" t="n">
-        <v>208.6864864049894</v>
+        <v>208.2969174543329</v>
       </c>
       <c r="C190" t="n">
-        <v>212.4722588232193</v>
+        <v>208.9761653200819</v>
       </c>
       <c r="D190" t="n">
-        <v>208.1071328472061</v>
+        <v>202.8530121596522</v>
       </c>
       <c r="E190" t="n">
-        <v>212.2125396728516</v>
+        <v>204.4212493896484</v>
       </c>
       <c r="F190" t="n">
-        <v>149936700</v>
+        <v>128363500</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B191" t="n">
-        <v>210.9439520928381</v>
+        <v>207.0982684229139</v>
       </c>
       <c r="C191" t="n">
-        <v>211.2536184019877</v>
+        <v>211.1537281092123</v>
       </c>
       <c r="D191" t="n">
-        <v>207.0583006421773</v>
+        <v>206.2691942875683</v>
       </c>
       <c r="E191" t="n">
-        <v>207.1781768798828</v>
+        <v>210.4545135498047</v>
       </c>
       <c r="F191" t="n">
-        <v>125694100</v>
+        <v>241272000</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="B192" t="n">
-        <v>208.2969174543329</v>
+        <v>211.2036686200953</v>
       </c>
       <c r="C192" t="n">
-        <v>208.9761653200819</v>
+        <v>213.7508214450341</v>
       </c>
       <c r="D192" t="n">
-        <v>202.8530121596522</v>
+        <v>207.4878253737282</v>
       </c>
       <c r="E192" t="n">
-        <v>204.4212493896484</v>
+        <v>208.4167785644531</v>
       </c>
       <c r="F192" t="n">
-        <v>128363500</v>
+        <v>122041400</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46191</v>
+        <v>46196</v>
       </c>
       <c r="B193" t="n">
-        <v>207.0982684229139</v>
+        <v>201.9440304014853</v>
       </c>
       <c r="C193" t="n">
-        <v>211.1537281092123</v>
+        <v>203.5422481594977</v>
       </c>
       <c r="D193" t="n">
-        <v>206.2691942875683</v>
+        <v>199.77645766483</v>
       </c>
       <c r="E193" t="n">
-        <v>210.4545135498047</v>
+        <v>199.81640625</v>
       </c>
       <c r="F193" t="n">
-        <v>241272000</v>
+        <v>153496200</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B194" t="n">
-        <v>211.2036686200953</v>
+        <v>199.8963159019567</v>
       </c>
       <c r="C194" t="n">
-        <v>213.7508214450341</v>
+        <v>201.4445864758279</v>
       </c>
       <c r="D194" t="n">
-        <v>207.4878253737282</v>
+        <v>196.360279356477</v>
       </c>
       <c r="E194" t="n">
-        <v>208.4167785644531</v>
+        <v>198.7775726318359</v>
       </c>
       <c r="F194" t="n">
-        <v>122041400</v>
+        <v>151810700</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B195" t="n">
-        <v>201.9440304014853</v>
+        <v>199.8563704571445</v>
       </c>
       <c r="C195" t="n">
-        <v>203.5422481594977</v>
+        <v>200.5755669254449</v>
       </c>
       <c r="D195" t="n">
-        <v>199.77645766483</v>
+        <v>191.9152592982058</v>
       </c>
       <c r="E195" t="n">
-        <v>199.81640625</v>
+        <v>195.5212249755859</v>
       </c>
       <c r="F195" t="n">
-        <v>153496200</v>
+        <v>149550000</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="B196" t="n">
-        <v>199.8963159019567</v>
+        <v>192.9041409641119</v>
       </c>
       <c r="C196" t="n">
-        <v>201.4445864758279</v>
+        <v>195.331432829306</v>
       </c>
       <c r="D196" t="n">
-        <v>196.360279356477</v>
+        <v>191.0062707295152</v>
       </c>
       <c r="E196" t="n">
-        <v>198.7775726318359</v>
+        <v>192.3148040771484</v>
       </c>
       <c r="F196" t="n">
-        <v>151810700</v>
+        <v>179304100</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="B197" t="n">
-        <v>199.8563704571445</v>
+        <v>193.6333319429392</v>
       </c>
       <c r="C197" t="n">
-        <v>200.5755669254449</v>
+        <v>195.9607141929515</v>
       </c>
       <c r="D197" t="n">
-        <v>191.9152592982058</v>
+        <v>189.5878557469149</v>
       </c>
       <c r="E197" t="n">
-        <v>195.5212249755859</v>
+        <v>194.7520751953125</v>
       </c>
       <c r="F197" t="n">
-        <v>149550000</v>
+        <v>148835700</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="B198" t="n">
-        <v>192.9041409641119</v>
+        <v>197.0195429632178</v>
       </c>
       <c r="C198" t="n">
-        <v>195.331432829306</v>
+        <v>200.4057532237791</v>
       </c>
       <c r="D198" t="n">
-        <v>191.0062707295152</v>
+        <v>194.8919188665145</v>
       </c>
       <c r="E198" t="n">
-        <v>192.3148040771484</v>
+        <v>199.8663482666016</v>
       </c>
       <c r="F198" t="n">
-        <v>179304100</v>
+        <v>166476700</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="B199" t="n">
-        <v>193.6333319429392</v>
+        <v>195.9806989625188</v>
       </c>
       <c r="C199" t="n">
-        <v>195.9607141929515</v>
+        <v>199.626628404907</v>
       </c>
       <c r="D199" t="n">
-        <v>189.5878557469149</v>
+        <v>193.2337727110923</v>
       </c>
       <c r="E199" t="n">
-        <v>194.7520751953125</v>
+        <v>197.3591613769531</v>
       </c>
       <c r="F199" t="n">
-        <v>148835700</v>
+        <v>146147600</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="B200" t="n">
-        <v>197.0195429632178</v>
+        <v>196.9196593659626</v>
       </c>
       <c r="C200" t="n">
-        <v>200.4057532237791</v>
+        <v>199.8363939026278</v>
       </c>
       <c r="D200" t="n">
-        <v>194.8919188665145</v>
+        <v>192.1350197738411</v>
       </c>
       <c r="E200" t="n">
-        <v>199.8663482666016</v>
+        <v>194.6122436523438</v>
       </c>
       <c r="F200" t="n">
-        <v>166476700</v>
+        <v>142068700</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B201" t="n">
-        <v>195.9806989625188</v>
+        <v>194.202694284663</v>
       </c>
       <c r="C201" t="n">
-        <v>199.626628404907</v>
+        <v>197.3292007505161</v>
       </c>
       <c r="D201" t="n">
-        <v>193.2337727110923</v>
+        <v>193.7731822131383</v>
       </c>
       <c r="E201" t="n">
-        <v>197.3591613769531</v>
+        <v>195.3314361572266</v>
       </c>
       <c r="F201" t="n">
-        <v>146147600</v>
+        <v>108999000</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B202" t="n">
-        <v>196.9196593659626</v>
+        <v>192.1549837798622</v>
       </c>
       <c r="C202" t="n">
-        <v>199.8363939026278</v>
+        <v>198.1882414262674</v>
       </c>
       <c r="D202" t="n">
-        <v>192.1350197738411</v>
+        <v>190.9263628146717</v>
       </c>
       <c r="E202" t="n">
-        <v>194.6122436523438</v>
+        <v>196.7098846435547</v>
       </c>
       <c r="F202" t="n">
-        <v>142068700</v>
+        <v>124154600</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B203" t="n">
-        <v>194.202694284663</v>
+        <v>194.9618356993413</v>
       </c>
       <c r="C203" t="n">
-        <v>197.3292007505161</v>
+        <v>204.9306918075912</v>
       </c>
       <c r="D203" t="n">
-        <v>193.7731822131383</v>
+        <v>194.841974703339</v>
       </c>
       <c r="E203" t="n">
-        <v>195.3314361572266</v>
+        <v>203.891845703125</v>
       </c>
       <c r="F203" t="n">
-        <v>108999000</v>
+        <v>147419100</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B204" t="n">
-        <v>192.1549837798622</v>
+        <v>204.2314748595287</v>
       </c>
       <c r="C204" t="n">
-        <v>198.1882414262674</v>
+        <v>204.3613191897594</v>
       </c>
       <c r="D204" t="n">
-        <v>190.9263628146717</v>
+        <v>198.7376223952696</v>
       </c>
       <c r="E204" t="n">
-        <v>196.7098846435547</v>
+        <v>202.5533447265625</v>
       </c>
       <c r="F204" t="n">
-        <v>124154600</v>
+        <v>132037400</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B205" t="n">
-        <v>194.9618356993413</v>
+        <v>201.7742207048944</v>
       </c>
       <c r="C205" t="n">
-        <v>204.9306918075912</v>
+        <v>210.7641612313501</v>
       </c>
       <c r="D205" t="n">
-        <v>194.841974703339</v>
+        <v>201.6943082934289</v>
       </c>
       <c r="E205" t="n">
-        <v>203.891845703125</v>
+        <v>210.7242126464844</v>
       </c>
       <c r="F205" t="n">
-        <v>147419100</v>
+        <v>148421000</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B206" t="n">
-        <v>204.2314748595287</v>
+        <v>208.3069001369788</v>
       </c>
       <c r="C206" t="n">
-        <v>204.3613191897594</v>
+        <v>210.3346451505122</v>
       </c>
       <c r="D206" t="n">
-        <v>198.7376223952696</v>
+        <v>202.7730991138312</v>
       </c>
       <c r="E206" t="n">
-        <v>202.5533447265625</v>
+        <v>203.3025054931641</v>
       </c>
       <c r="F206" t="n">
-        <v>132037400</v>
+        <v>121411000</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B207" t="n">
-        <v>201.7742207048944</v>
+        <v>207.9672957533915</v>
       </c>
       <c r="C207" t="n">
-        <v>210.7641612313501</v>
+        <v>212.3124399374416</v>
       </c>
       <c r="D207" t="n">
-        <v>201.6943082934289</v>
+        <v>203.5722196467825</v>
       </c>
       <c r="E207" t="n">
-        <v>210.7242126464844</v>
+        <v>211.5632781982422</v>
       </c>
       <c r="F207" t="n">
-        <v>148421000</v>
+        <v>124379600</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B208" t="n">
-        <v>208.3069001369788</v>
+        <v>211.7230919717581</v>
       </c>
       <c r="C208" t="n">
-        <v>210.3346451505122</v>
+        <v>213.5710150202495</v>
       </c>
       <c r="D208" t="n">
-        <v>202.7730991138312</v>
+        <v>205.8096955397309</v>
       </c>
       <c r="E208" t="n">
-        <v>203.3025054931641</v>
+        <v>212.2624816894531</v>
       </c>
       <c r="F208" t="n">
-        <v>121411000</v>
+        <v>124797200</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B209" t="n">
-        <v>207.9672957533915</v>
+        <v>209.9350906043833</v>
       </c>
       <c r="C209" t="n">
-        <v>212.3124399374416</v>
+        <v>210.8440771529852</v>
       </c>
       <c r="D209" t="n">
-        <v>203.5722196467825</v>
+        <v>205.6199270055466</v>
       </c>
       <c r="E209" t="n">
-        <v>211.5632781982422</v>
+        <v>207.1681823730469</v>
       </c>
       <c r="F209" t="n">
-        <v>124379600</v>
+        <v>122986100</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B210" t="n">
-        <v>211.7230919717581</v>
+        <v>202.4135048295048</v>
       </c>
       <c r="C210" t="n">
-        <v>213.5710150202495</v>
+        <v>206.4190172896336</v>
       </c>
       <c r="D210" t="n">
-        <v>205.8096955397309</v>
+        <v>197.7487264058434</v>
       </c>
       <c r="E210" t="n">
-        <v>212.2624816894531</v>
+        <v>202.5833129882812</v>
       </c>
       <c r="F210" t="n">
-        <v>124797200</v>
+        <v>144281900</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B211" t="n">
-        <v>209.9350906043833</v>
+        <v>205.639896943356</v>
       </c>
       <c r="C211" t="n">
-        <v>210.8440771529852</v>
+        <v>207.5078172334397</v>
       </c>
       <c r="D211" t="n">
-        <v>205.6199270055466</v>
+        <v>202.0539130969454</v>
       </c>
       <c r="E211" t="n">
-        <v>207.1681823730469</v>
+        <v>203.0527954101562</v>
       </c>
       <c r="F211" t="n">
-        <v>122986100</v>
+        <v>88701500</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B212" t="n">
-        <v>202.4135048295048</v>
+        <v>207.308024406286</v>
       </c>
       <c r="C212" t="n">
-        <v>206.4190172896336</v>
+        <v>208.4167843613107</v>
       </c>
       <c r="D212" t="n">
-        <v>197.7487264058434</v>
+        <v>203.7819711309363</v>
       </c>
       <c r="E212" t="n">
-        <v>202.5833129882812</v>
+        <v>207.0583038330078</v>
       </c>
       <c r="F212" t="n">
-        <v>144281900</v>
+        <v>108685600</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B213" t="n">
-        <v>205.639896943356</v>
+        <v>205.579968274895</v>
       </c>
       <c r="C213" t="n">
-        <v>207.5078172334397</v>
+        <v>214.1503804276117</v>
       </c>
       <c r="D213" t="n">
-        <v>202.0539130969454</v>
+        <v>204.7209288682105</v>
       </c>
       <c r="E213" t="n">
-        <v>203.0527954101562</v>
+        <v>211.8229827880859</v>
       </c>
       <c r="F213" t="n">
-        <v>88701500</v>
+        <v>137645600</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B214" t="n">
-        <v>207.308024406286</v>
+        <v>209.2258868865651</v>
       </c>
       <c r="C214" t="n">
-        <v>208.4167843613107</v>
+        <v>210.6342993029147</v>
       </c>
       <c r="D214" t="n">
-        <v>203.7819711309363</v>
+        <v>205.7297989431358</v>
       </c>
       <c r="E214" t="n">
-        <v>207.0583038330078</v>
+        <v>208.5266571044922</v>
       </c>
       <c r="F214" t="n">
-        <v>108685600</v>
+        <v>110505300</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B215" t="n">
-        <v>205.579968274895</v>
+        <v>207.2181292349697</v>
       </c>
       <c r="C215" t="n">
-        <v>214.1503804276117</v>
+        <v>211.6731509810223</v>
       </c>
       <c r="D215" t="n">
-        <v>204.7209288682105</v>
+        <v>204.5810805834776</v>
       </c>
       <c r="E215" t="n">
-        <v>211.8229827880859</v>
+        <v>206.6088104248047</v>
       </c>
       <c r="F215" t="n">
-        <v>137645600</v>
+        <v>114836800</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B216" t="n">
-        <v>209.2258868865651</v>
+        <v>207.9672962732577</v>
       </c>
       <c r="C216" t="n">
-        <v>210.6342993029147</v>
+        <v>208.5166845983908</v>
       </c>
       <c r="D216" t="n">
-        <v>205.7297989431358</v>
+        <v>195.2215633388429</v>
       </c>
       <c r="E216" t="n">
-        <v>208.5266571044922</v>
+        <v>196.2903594970703</v>
       </c>
       <c r="F216" t="n">
-        <v>110505300</v>
+        <v>154353700</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="B217" t="n">
-        <v>207.2181292349697</v>
+        <v>194.782047001347</v>
       </c>
       <c r="C217" t="n">
-        <v>211.6731509810223</v>
+        <v>198.4779084345641</v>
       </c>
       <c r="D217" t="n">
-        <v>204.5810805834776</v>
+        <v>192.5245785077403</v>
       </c>
       <c r="E217" t="n">
-        <v>206.6088104248047</v>
+        <v>196.789794921875</v>
       </c>
       <c r="F217" t="n">
-        <v>114836800</v>
+        <v>134111500</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B218" t="n">
-        <v>207.9672962732577</v>
+        <v>195.6311069684468</v>
       </c>
       <c r="C218" t="n">
-        <v>208.5166845983908</v>
+        <v>196.8497446088402</v>
       </c>
       <c r="D218" t="n">
-        <v>195.2215633388429</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="E218" t="n">
-        <v>196.2903594970703</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="F218" t="n">
-        <v>154353700</v>
+        <v>147680800</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B219" t="n">
-        <v>194.782047001347</v>
+        <v>193.2337718176948</v>
       </c>
       <c r="C219" t="n">
-        <v>198.4779084345641</v>
+        <v>197.0295274868271</v>
       </c>
       <c r="D219" t="n">
-        <v>192.5245785077403</v>
+        <v>191.3059363552755</v>
       </c>
       <c r="E219" t="n">
-        <v>196.789794921875</v>
+        <v>194.8219909667969</v>
       </c>
       <c r="F219" t="n">
-        <v>134111500</v>
+        <v>129010200</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B220" t="n">
-        <v>195.6311069684468</v>
+        <v>198.2182038580375</v>
       </c>
       <c r="C220" t="n">
-        <v>196.8497446088402</v>
+        <v>201.7742223680242</v>
       </c>
       <c r="D220" t="n">
-        <v>189.7976226806641</v>
+        <v>194.7320991825756</v>
       </c>
       <c r="E220" t="n">
-        <v>189.7976226806641</v>
+        <v>200.5256195068359</v>
       </c>
       <c r="F220" t="n">
-        <v>147680800</v>
+        <v>139961200</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B221" t="n">
-        <v>193.2337718176948</v>
+        <v>197.4690486270115</v>
       </c>
       <c r="C221" t="n">
-        <v>197.0295274868271</v>
+        <v>208.506701330784</v>
       </c>
       <c r="D221" t="n">
-        <v>191.3059363552755</v>
+        <v>196.6299911347511</v>
       </c>
       <c r="E221" t="n">
-        <v>194.8219909667969</v>
+        <v>206.4090423583984</v>
       </c>
       <c r="F221" t="n">
-        <v>129010200</v>
+        <v>128406900</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B222" t="n">
-        <v>198.2182038580375</v>
+        <v>211.0638257011038</v>
       </c>
       <c r="C222" t="n">
-        <v>201.7742223680242</v>
+        <v>212.8218530009649</v>
       </c>
       <c r="D222" t="n">
-        <v>194.7320991825756</v>
+        <v>208.8163406042335</v>
       </c>
       <c r="E222" t="n">
-        <v>200.5256195068359</v>
+        <v>211.7031097412109</v>
       </c>
       <c r="F222" t="n">
-        <v>139961200</v>
+        <v>134922000</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B223" t="n">
-        <v>197.4690486270115</v>
+        <v>216.6176127852948</v>
       </c>
       <c r="C223" t="n">
-        <v>208.506701330784</v>
+        <v>221.9716224388697</v>
       </c>
       <c r="D223" t="n">
-        <v>196.6299911347511</v>
+        <v>216.1581202281489</v>
       </c>
       <c r="E223" t="n">
-        <v>206.4090423583984</v>
+        <v>218.9749755859375</v>
       </c>
       <c r="F223" t="n">
-        <v>128406900</v>
+        <v>158187400</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B224" t="n">
-        <v>211.0638257011038</v>
+        <v>221.2823935806188</v>
       </c>
       <c r="C224" t="n">
-        <v>212.8218530009649</v>
+        <v>223.3800524967045</v>
       </c>
       <c r="D224" t="n">
-        <v>208.8163406042335</v>
+        <v>216.7574580038405</v>
       </c>
       <c r="E224" t="n">
-        <v>211.7031097412109</v>
+        <v>218.7452392578125</v>
       </c>
       <c r="F224" t="n">
-        <v>134922000</v>
+        <v>113940600</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B225" t="n">
-        <v>216.6176127852948</v>
+        <v>221.2923777041913</v>
       </c>
       <c r="C225" t="n">
-        <v>221.9716224388697</v>
+        <v>224.5087799247126</v>
       </c>
       <c r="D225" t="n">
-        <v>216.1581202281489</v>
+        <v>220.4133716458871</v>
       </c>
       <c r="E225" t="n">
-        <v>218.9749755859375</v>
+        <v>223.7096862792969</v>
       </c>
       <c r="F225" t="n">
-        <v>158187400</v>
+        <v>105669400</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B226" t="n">
-        <v>221.2823935806188</v>
+        <v>223.1502910726907</v>
       </c>
       <c r="C226" t="n">
-        <v>223.3800524967045</v>
+        <v>223.8894694330602</v>
       </c>
       <c r="D226" t="n">
-        <v>216.7574580038405</v>
+        <v>216.5277120448001</v>
       </c>
       <c r="E226" t="n">
-        <v>218.7452392578125</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="F226" t="n">
-        <v>113940600</v>
+        <v>115846600</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B227" t="n">
-        <v>221.2923777041913</v>
+        <v>221.9216754142795</v>
       </c>
       <c r="C227" t="n">
-        <v>224.5087799247126</v>
+        <v>221.9516406634887</v>
       </c>
       <c r="D227" t="n">
-        <v>220.4133716458871</v>
+        <v>215.9583469538982</v>
       </c>
       <c r="E227" t="n">
-        <v>223.7096862792969</v>
+        <v>217.2568969726562</v>
       </c>
       <c r="F227" t="n">
-        <v>105669400</v>
+        <v>101273100</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B228" t="n">
-        <v>223.1502910726907</v>
+        <v>220.7929293559802</v>
       </c>
       <c r="C228" t="n">
-        <v>223.8894694330602</v>
+        <v>224.848404158734</v>
       </c>
       <c r="D228" t="n">
-        <v>216.5277120448001</v>
+        <v>219.9538719106106</v>
       </c>
       <c r="E228" t="n">
-        <v>217.3068389892578</v>
+        <v>223.8395233154297</v>
       </c>
       <c r="F228" t="n">
-        <v>115846600</v>
+        <v>108783600</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B229" t="n">
-        <v>221.9216754142795</v>
+        <v>224.8084500146858</v>
       </c>
       <c r="C229" t="n">
-        <v>221.9516406634887</v>
+        <v>226.9760227961096</v>
       </c>
       <c r="D229" t="n">
-        <v>215.9583469538982</v>
+        <v>223.4599680426375</v>
       </c>
       <c r="E229" t="n">
-        <v>217.2568969726562</v>
+        <v>225.0481872558594</v>
       </c>
       <c r="F229" t="n">
-        <v>101273100</v>
+        <v>98867200</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B230" t="n">
-        <v>220.7929293559802</v>
+        <v>226.5165415533859</v>
       </c>
       <c r="C230" t="n">
-        <v>224.848404158734</v>
+        <v>227.2357380227387</v>
       </c>
       <c r="D230" t="n">
-        <v>219.9538719106106</v>
+        <v>224.2490744835724</v>
       </c>
       <c r="E230" t="n">
-        <v>223.8395233154297</v>
+        <v>224.9083404541016</v>
       </c>
       <c r="F230" t="n">
-        <v>108783600</v>
+        <v>75680900</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B231" t="n">
-        <v>224.8084500146858</v>
+        <v>225.7274161885591</v>
       </c>
       <c r="C231" t="n">
-        <v>226.9760227961096</v>
+        <v>227.6652502746616</v>
       </c>
       <c r="D231" t="n">
-        <v>223.4599680426375</v>
+        <v>224.6086728983284</v>
       </c>
       <c r="E231" t="n">
-        <v>225.0481872558594</v>
+        <v>224.7584991455078</v>
       </c>
       <c r="F231" t="n">
-        <v>98867200</v>
+        <v>93678700</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B232" t="n">
-        <v>226.5165415533859</v>
+        <v>220.203597915372</v>
       </c>
       <c r="C232" t="n">
-        <v>227.2357380227387</v>
+        <v>221.3922702798686</v>
       </c>
       <c r="D232" t="n">
-        <v>224.2490744835724</v>
+        <v>218.4455705709327</v>
       </c>
       <c r="E232" t="n">
-        <v>224.9083404541016</v>
+        <v>219.4944000244141</v>
       </c>
       <c r="F232" t="n">
-        <v>75680900</v>
+        <v>103128200</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B233" t="n">
-        <v>225.7274161885591</v>
+        <v>221.4222404106533</v>
       </c>
       <c r="C233" t="n">
-        <v>227.6652502746616</v>
+        <v>222.6208961374568</v>
       </c>
       <c r="D233" t="n">
-        <v>224.6086728983284</v>
+        <v>216.5177245976465</v>
       </c>
       <c r="E233" t="n">
-        <v>224.7584991455078</v>
+        <v>217.3168334960938</v>
       </c>
       <c r="F233" t="n">
-        <v>93678700</v>
+        <v>96797300</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B234" t="n">
-        <v>220.203597915372</v>
+        <v>218.1159423024499</v>
       </c>
       <c r="C234" t="n">
-        <v>221.3922702798686</v>
+        <v>219.6142657707553</v>
       </c>
       <c r="D234" t="n">
-        <v>218.4455705709327</v>
+        <v>215.418963107847</v>
       </c>
       <c r="E234" t="n">
-        <v>219.4944000244141</v>
+        <v>216.6076354980469</v>
       </c>
       <c r="F234" t="n">
-        <v>103128200</v>
+        <v>92457000</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B235" t="n">
-        <v>221.4222404106533</v>
+        <v>218.1758724878036</v>
       </c>
       <c r="C235" t="n">
-        <v>222.6208961374568</v>
+        <v>218.4955221432803</v>
       </c>
       <c r="D235" t="n">
-        <v>216.5177245976465</v>
+        <v>214.2602556586216</v>
       </c>
       <c r="E235" t="n">
-        <v>217.3168334960938</v>
+        <v>214.4800109863281</v>
       </c>
       <c r="F235" t="n">
-        <v>96797300</v>
+        <v>98869300</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B236" t="n">
-        <v>218.1159423024499</v>
+        <v>215.2891020611033</v>
       </c>
       <c r="C236" t="n">
-        <v>219.6142657707553</v>
+        <v>215.3490325607492</v>
       </c>
       <c r="D236" t="n">
-        <v>215.418963107847</v>
+        <v>207.0183577918231</v>
       </c>
       <c r="E236" t="n">
-        <v>216.6076354980469</v>
+        <v>208.2469787597656</v>
       </c>
       <c r="F236" t="n">
-        <v>92457000</v>
+        <v>135187300</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B237" t="n">
-        <v>218.1758724878036</v>
+        <v>210.7941279013131</v>
       </c>
       <c r="C237" t="n">
-        <v>218.4955221432803</v>
+        <v>214.4899893165327</v>
       </c>
       <c r="D237" t="n">
-        <v>214.2602556586216</v>
+        <v>209.8751580258669</v>
       </c>
       <c r="E237" t="n">
-        <v>214.4800109863281</v>
+        <v>212.8118743896484</v>
       </c>
       <c r="F237" t="n">
-        <v>98869300</v>
+        <v>122309000</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B238" t="n">
-        <v>215.2891020611033</v>
+        <v>212.4023240594531</v>
       </c>
       <c r="C238" t="n">
-        <v>215.3490325607492</v>
+        <v>213.3612577394914</v>
       </c>
       <c r="D238" t="n">
-        <v>207.0183577918231</v>
+        <v>208.9961318803605</v>
       </c>
       <c r="E238" t="n">
-        <v>208.2469787597656</v>
+        <v>209.4256591796875</v>
       </c>
       <c r="F238" t="n">
-        <v>135187300</v>
+        <v>179900000</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B239" t="n">
-        <v>210.7941279013131</v>
+        <v>222.6109016432552</v>
       </c>
       <c r="C239" t="n">
-        <v>214.4899893165327</v>
+        <v>230.2123962709879</v>
       </c>
       <c r="D239" t="n">
-        <v>209.8751580258669</v>
+        <v>220.6530857022795</v>
       </c>
       <c r="E239" t="n">
-        <v>212.8118743896484</v>
+        <v>227.7251739501953</v>
       </c>
       <c r="F239" t="n">
-        <v>122309000</v>
+        <v>298909800</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B240" t="n">
-        <v>212.4023240594531</v>
+        <v>227.1058715337123</v>
       </c>
       <c r="C240" t="n">
-        <v>213.3612577394914</v>
+        <v>229.003741733446</v>
       </c>
       <c r="D240" t="n">
-        <v>208.9961318803605</v>
+        <v>216.5676606288883</v>
       </c>
       <c r="E240" t="n">
-        <v>209.4256591796875</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="F240" t="n">
-        <v>179900000</v>
+        <v>195116400</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B241" t="n">
-        <v>222.6109016432552</v>
+        <v>218.6253647857836</v>
       </c>
       <c r="C241" t="n">
-        <v>230.2123962709879</v>
+        <v>221.0526567078369</v>
       </c>
       <c r="D241" t="n">
-        <v>220.6530857022795</v>
+        <v>215.9683494434545</v>
       </c>
       <c r="E241" t="n">
-        <v>227.7251739501953</v>
+        <v>220.5332336425781</v>
       </c>
       <c r="F241" t="n">
-        <v>298909800</v>
+        <v>124702700</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B242" t="n">
-        <v>227.1058715337123</v>
+        <v>216.5077444634259</v>
       </c>
       <c r="C242" t="n">
-        <v>229.003741733446</v>
+        <v>220.1636574397174</v>
       </c>
       <c r="D242" t="n">
-        <v>216.5676606288883</v>
+        <v>214.8595947199138</v>
       </c>
       <c r="E242" t="n">
-        <v>217.3068389892578</v>
+        <v>217.1969757080078</v>
       </c>
       <c r="F242" t="n">
-        <v>195116400</v>
+        <v>109756200</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B243" t="n">
-        <v>218.6253647857836</v>
+        <v>218.5454508199983</v>
       </c>
       <c r="C243" t="n">
-        <v>221.0526567078369</v>
+        <v>227.6952163087265</v>
       </c>
       <c r="D243" t="n">
-        <v>215.9683494434545</v>
+        <v>218.2357997469377</v>
       </c>
       <c r="E243" t="n">
-        <v>220.5332336425781</v>
+        <v>224.1591796875</v>
       </c>
       <c r="F243" t="n">
-        <v>124702700</v>
+        <v>157104700</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B244" t="n">
-        <v>216.5077444634259</v>
+        <v>225.7673797205316</v>
       </c>
       <c r="C244" t="n">
-        <v>220.1636574397174</v>
+        <v>230.1424737915274</v>
       </c>
       <c r="D244" t="n">
-        <v>214.8595947199138</v>
+        <v>224.4987949430455</v>
       </c>
       <c r="E244" t="n">
-        <v>217.1969757080078</v>
+        <v>228.1946563720703</v>
       </c>
       <c r="F244" t="n">
-        <v>109756200</v>
+        <v>134681600</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B245" t="n">
-        <v>218.5454508199983</v>
+        <v>230.8317036041433</v>
       </c>
       <c r="C245" t="n">
-        <v>227.6952163087265</v>
+        <v>234.4975997614268</v>
       </c>
       <c r="D245" t="n">
-        <v>218.2357997469377</v>
+        <v>229.3733440032785</v>
       </c>
       <c r="E245" t="n">
-        <v>224.1591796875</v>
+        <v>230.1025238037109</v>
       </c>
       <c r="F245" t="n">
-        <v>157104700</v>
+        <v>135352400</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B246" t="n">
-        <v>225.7673797205316</v>
+        <v>232.8494477166676</v>
       </c>
       <c r="C246" t="n">
-        <v>230.1424737915274</v>
+        <v>233.4487831783142</v>
       </c>
       <c r="D246" t="n">
-        <v>224.4987949430455</v>
+        <v>224.5986856128386</v>
       </c>
       <c r="E246" t="n">
-        <v>228.1946563720703</v>
+        <v>225.4776916503906</v>
       </c>
       <c r="F246" t="n">
-        <v>134681600</v>
+        <v>122965600</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="B247" t="n">
-        <v>230.8317036041433</v>
+        <v>225.0281992525124</v>
       </c>
       <c r="C247" t="n">
-        <v>234.4975997614268</v>
+        <v>225.9271872095504</v>
       </c>
       <c r="D247" t="n">
-        <v>229.3733440032785</v>
+        <v>223.2102414251123</v>
       </c>
       <c r="E247" t="n">
-        <v>230.1025238037109</v>
+        <v>223.4199981689453</v>
       </c>
       <c r="F247" t="n">
-        <v>135352400</v>
+        <v>82955500</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,25 +6865,25 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B248" t="n">
-        <v>232.8494477166676</v>
+        <v>220.5299987792969</v>
       </c>
       <c r="C248" t="n">
-        <v>233.4487831783142</v>
+        <v>220.9900054931641</v>
       </c>
       <c r="D248" t="n">
-        <v>224.5986856128386</v>
+        <v>217.1999969482422</v>
       </c>
       <c r="E248" t="n">
-        <v>225.4776916503906</v>
+        <v>218.3600006103516</v>
       </c>
       <c r="F248" t="n">
-        <v>122965600</v>
+        <v>105768000</v>
       </c>
       <c r="G248" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B249" t="n">
-        <v>225.0281992525124</v>
+        <v>221.2400054931641</v>
       </c>
       <c r="C249" t="n">
-        <v>225.9271872095504</v>
+        <v>222</v>
       </c>
       <c r="D249" t="n">
-        <v>223.2102414251123</v>
+        <v>218.1499938964844</v>
       </c>
       <c r="E249" t="n">
-        <v>223.4199981689453</v>
+        <v>218.2899932861328</v>
       </c>
       <c r="F249" t="n">
-        <v>82955500</v>
+        <v>89060100</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,25 +6917,25 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B250" t="n">
-        <v>220.5299987792969</v>
+        <v>211.2400054931641</v>
       </c>
       <c r="C250" t="n">
-        <v>220.9900054931641</v>
+        <v>212.7700042724609</v>
       </c>
       <c r="D250" t="n">
-        <v>217.1999969482422</v>
+        <v>208.9299926757812</v>
       </c>
       <c r="E250" t="n">
-        <v>218.3600006103516</v>
+        <v>210.9600067138672</v>
       </c>
       <c r="F250" t="n">
-        <v>105768000</v>
+        <v>132267200</v>
       </c>
       <c r="G250" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B251" t="n">
-        <v>221.2400054931641</v>
+        <v>213.3800048828125</v>
       </c>
       <c r="C251" t="n">
-        <v>222</v>
+        <v>213.9400024414062</v>
       </c>
       <c r="D251" t="n">
-        <v>218.1499938964844</v>
+        <v>211.1600036621094</v>
       </c>
       <c r="E251" t="n">
-        <v>218.2899932861328</v>
+        <v>212.1699981689453</v>
       </c>
       <c r="F251" t="n">
-        <v>89060100</v>
+        <v>88059700</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,14 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B252" t="n">
-        <v>211.2400054931641</v>
-      </c>
-      <c r="C252" t="n">
-        <v>212.7700042724609</v>
-      </c>
-      <c r="D252" t="n">
-        <v>208.9299926757812</v>
-      </c>
-      <c r="E252" t="n">
-        <v>210.9600067138672</v>
-      </c>
+        <v>46281</v>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="n">
-        <v>131942300</v>
+        <v>96113489</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10884,37 +10876,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>210.96</v>
+        <v>213.9</v>
       </c>
       <c r="D2" t="n">
-        <v>218.29</v>
+        <v>212.17</v>
       </c>
       <c r="E2" t="n">
-        <v>211.08</v>
+        <v>214.14</v>
       </c>
       <c r="F2" t="n">
-        <v>212.77</v>
+        <v>216.76</v>
       </c>
       <c r="G2" t="n">
-        <v>208.93</v>
+        <v>212.5</v>
       </c>
       <c r="H2" t="n">
-        <v>131608711</v>
+        <v>96113489</v>
       </c>
       <c r="I2" t="n">
-        <v>131798644</v>
+        <v>131193816</v>
       </c>
       <c r="J2" t="n">
-        <v>5094050889728</v>
+        <v>5165043154944</v>
       </c>
       <c r="K2" t="n">
-        <v>26.703798</v>
+        <v>26.80451</v>
       </c>
       <c r="L2" t="n">
-        <v>13.510182</v>
+        <v>13.698463</v>
       </c>
       <c r="M2" t="n">
-        <v>7.9</v>
+        <v>7.98</v>
       </c>
       <c r="N2" t="n">
         <v>236.54</v>
@@ -10926,7 +10918,7 @@
         <v>2.217</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="R2" t="n">
         <v>0.63663</v>
@@ -10950,7 +10942,7 @@
         <v>9.483000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>22.246126</v>
+        <v>22.556152</v>
       </c>
       <c r="Z2" t="n">
         <v>1.278</v>
@@ -10962,7 +10954,7 @@
         <v>302970011648</v>
       </c>
       <c r="AC2" t="n">
-        <v>5060526866432</v>
+        <v>5131381243904</v>
       </c>
       <c r="AD2" t="n">
         <v>201266003968</v>
@@ -10989,7 +10981,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:14:09</t>
+          <t>2026-09-17 08:09:57</t>
         </is>
       </c>
     </row>

--- a/data/NVDA_data.xlsx
+++ b/data/NVDA_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B2" t="n">
-        <v>172.2273696616015</v>
+        <v>173.5641783462465</v>
       </c>
       <c r="C2" t="n">
-        <v>172.7860287607356</v>
+        <v>176.6767318043244</v>
       </c>
       <c r="D2" t="n">
-        <v>168.007484117061</v>
+        <v>172.5466271367534</v>
       </c>
       <c r="E2" t="n">
-        <v>169.8829803466797</v>
+        <v>175.8187866210938</v>
       </c>
       <c r="F2" t="n">
-        <v>211843800</v>
+        <v>191763300</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B3" t="n">
-        <v>173.5641632831282</v>
+        <v>175.349898865447</v>
       </c>
       <c r="C3" t="n">
-        <v>176.6767164710769</v>
+        <v>177.6543753314711</v>
       </c>
       <c r="D3" t="n">
-        <v>172.5466121619453</v>
+        <v>174.7612974471592</v>
       </c>
       <c r="E3" t="n">
-        <v>175.8187713623047</v>
+        <v>176.2477416992188</v>
       </c>
       <c r="F3" t="n">
-        <v>191763300</v>
+        <v>237182100</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B4" t="n">
-        <v>175.349898865447</v>
+        <v>174.8810218455756</v>
       </c>
       <c r="C4" t="n">
-        <v>177.6543753314711</v>
+        <v>184.1089135963474</v>
       </c>
       <c r="D4" t="n">
-        <v>174.7612974471592</v>
+        <v>174.2924356467209</v>
       </c>
       <c r="E4" t="n">
-        <v>176.2477416992188</v>
+        <v>183.1711578369141</v>
       </c>
       <c r="F4" t="n">
-        <v>237182100</v>
+        <v>269637000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B5" t="n">
-        <v>174.8810364137678</v>
+        <v>181.5350878652714</v>
       </c>
       <c r="C5" t="n">
-        <v>184.1089289332547</v>
+        <v>181.9840093083128</v>
       </c>
       <c r="D5" t="n">
-        <v>174.2924501658818</v>
+        <v>175.7888599052367</v>
       </c>
       <c r="E5" t="n">
-        <v>183.1711730957031</v>
+        <v>178.0035400390625</v>
       </c>
       <c r="F5" t="n">
-        <v>269637000</v>
+        <v>192559600</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B6" t="n">
-        <v>181.5350878652714</v>
+        <v>179.3403383898065</v>
       </c>
       <c r="C6" t="n">
-        <v>181.9840093083128</v>
+        <v>179.3503090089054</v>
       </c>
       <c r="D6" t="n">
-        <v>175.7888599052367</v>
+        <v>174.9807727171775</v>
       </c>
       <c r="E6" t="n">
-        <v>178.0035400390625</v>
+        <v>176.5470275878906</v>
       </c>
       <c r="F6" t="n">
-        <v>192559600</v>
+        <v>143564100</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B7" t="n">
-        <v>179.3403538900187</v>
+        <v>174.0629701066951</v>
       </c>
       <c r="C7" t="n">
-        <v>179.3503245099793</v>
+        <v>179.8291540783439</v>
       </c>
       <c r="D7" t="n">
-        <v>174.9807878405966</v>
+        <v>172.7162058826927</v>
       </c>
       <c r="E7" t="n">
-        <v>176.5470428466797</v>
+        <v>177.2653045654297</v>
       </c>
       <c r="F7" t="n">
-        <v>143564100</v>
+        <v>191586700</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B8" t="n">
-        <v>174.0629701066951</v>
+        <v>177.7441426621237</v>
       </c>
       <c r="C8" t="n">
-        <v>179.8291540783439</v>
+        <v>179.3403244887289</v>
       </c>
       <c r="D8" t="n">
-        <v>172.7162058826927</v>
+        <v>174.5118813132914</v>
       </c>
       <c r="E8" t="n">
-        <v>177.2653045654297</v>
+        <v>177.7640991210938</v>
       </c>
       <c r="F8" t="n">
-        <v>191586700</v>
+        <v>148573700</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B9" t="n">
-        <v>177.7441579191998</v>
+        <v>179.9987400973632</v>
       </c>
       <c r="C9" t="n">
-        <v>179.3403398828169</v>
+        <v>183.5602146114836</v>
       </c>
       <c r="D9" t="n">
-        <v>174.5118962929188</v>
+        <v>179.8890176259668</v>
       </c>
       <c r="E9" t="n">
-        <v>177.7641143798828</v>
+        <v>181.4153594970703</v>
       </c>
       <c r="F9" t="n">
-        <v>148573700</v>
+        <v>193063500</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B10" t="n">
-        <v>179.9987400973632</v>
+        <v>181.6448190078555</v>
       </c>
       <c r="C10" t="n">
-        <v>183.5602146114836</v>
+        <v>186.9022276338177</v>
       </c>
       <c r="D10" t="n">
-        <v>179.8890176259668</v>
+        <v>181.0462469572146</v>
       </c>
       <c r="E10" t="n">
-        <v>181.4153594970703</v>
+        <v>186.1340637207031</v>
       </c>
       <c r="F10" t="n">
-        <v>193063500</v>
+        <v>236981000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B11" t="n">
-        <v>181.6448190078555</v>
+        <v>184.7972606974542</v>
       </c>
       <c r="C11" t="n">
-        <v>186.9022276338177</v>
+        <v>187.6903232769056</v>
       </c>
       <c r="D11" t="n">
-        <v>181.0462469572146</v>
+        <v>183.4604518817237</v>
       </c>
       <c r="E11" t="n">
-        <v>186.1340637207031</v>
+        <v>186.79248046875</v>
       </c>
       <c r="F11" t="n">
-        <v>236981000</v>
+        <v>173844900</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B12" t="n">
-        <v>184.7972606974542</v>
+        <v>189.146847340247</v>
       </c>
       <c r="C12" t="n">
-        <v>187.6903232769056</v>
+        <v>190.59337868299</v>
       </c>
       <c r="D12" t="n">
-        <v>183.4604518817237</v>
+        <v>187.6105195355423</v>
       </c>
       <c r="E12" t="n">
-        <v>186.79248046875</v>
+        <v>188.4385375976562</v>
       </c>
       <c r="F12" t="n">
-        <v>173844900</v>
+        <v>136805800</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B13" t="n">
-        <v>189.146847340247</v>
+        <v>188.7378401044004</v>
       </c>
       <c r="C13" t="n">
-        <v>190.59337868299</v>
+        <v>189.9050419886609</v>
       </c>
       <c r="D13" t="n">
-        <v>187.6105195355423</v>
+        <v>184.9369484043502</v>
       </c>
       <c r="E13" t="n">
-        <v>188.4385375976562</v>
+        <v>187.1715850830078</v>
       </c>
       <c r="F13" t="n">
-        <v>136805800</v>
+        <v>137596900</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B14" t="n">
-        <v>188.7378247179256</v>
+        <v>185.0566446584491</v>
       </c>
       <c r="C14" t="n">
-        <v>189.9050265070322</v>
+        <v>186.7825055997528</v>
       </c>
       <c r="D14" t="n">
-        <v>184.9369333277354</v>
+        <v>182.8918329061041</v>
       </c>
       <c r="E14" t="n">
-        <v>187.1715698242188</v>
+        <v>185.0965423583984</v>
       </c>
       <c r="F14" t="n">
-        <v>137596900</v>
+        <v>157678100</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B15" t="n">
-        <v>185.0566294029491</v>
+        <v>185.7848907820332</v>
       </c>
       <c r="C15" t="n">
-        <v>186.7824902019781</v>
+        <v>188.6081286768816</v>
       </c>
       <c r="D15" t="n">
-        <v>182.8918178290645</v>
+        <v>183.5602249269612</v>
       </c>
       <c r="E15" t="n">
-        <v>185.0965270996094</v>
+        <v>184.5977325439453</v>
       </c>
       <c r="F15" t="n">
-        <v>157678100</v>
+        <v>140088000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B16" t="n">
-        <v>185.7848907820332</v>
+        <v>186.1240823667868</v>
       </c>
       <c r="C16" t="n">
-        <v>188.6081286768816</v>
+        <v>189.1468390813163</v>
       </c>
       <c r="D16" t="n">
-        <v>183.5602249269612</v>
+        <v>186.094140065894</v>
       </c>
       <c r="E16" t="n">
-        <v>184.5977325439453</v>
+        <v>188.6580047607422</v>
       </c>
       <c r="F16" t="n">
-        <v>140088000</v>
+        <v>130168900</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B17" t="n">
-        <v>186.1240974206304</v>
+        <v>191.7705422839889</v>
       </c>
       <c r="C17" t="n">
-        <v>189.1468543796426</v>
+        <v>194.8332119113436</v>
       </c>
       <c r="D17" t="n">
-        <v>186.0941551173159</v>
+        <v>190.6033405552435</v>
       </c>
       <c r="E17" t="n">
-        <v>188.6580200195312</v>
+        <v>192.1097412109375</v>
       </c>
       <c r="F17" t="n">
-        <v>130168900</v>
+        <v>182997200</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B18" t="n">
-        <v>191.7705575158363</v>
+        <v>193.0474821132437</v>
       </c>
       <c r="C18" t="n">
-        <v>194.833227386451</v>
+        <v>195.1524395658232</v>
       </c>
       <c r="D18" t="n">
-        <v>190.6033556943829</v>
+        <v>181.6148814298513</v>
       </c>
       <c r="E18" t="n">
-        <v>192.1097564697266</v>
+        <v>182.7222290039062</v>
       </c>
       <c r="F18" t="n">
-        <v>182997200</v>
+        <v>268774400</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B19" t="n">
-        <v>193.0474982342752</v>
+        <v>187.5207340107304</v>
       </c>
       <c r="C19" t="n">
-        <v>195.1524558626357</v>
+        <v>189.6556185865847</v>
       </c>
       <c r="D19" t="n">
-        <v>181.6148965961679</v>
+        <v>185.5155435929421</v>
       </c>
       <c r="E19" t="n">
-        <v>182.7222442626953</v>
+        <v>187.8699035644531</v>
       </c>
       <c r="F19" t="n">
-        <v>268774400</v>
+        <v>153482800</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B20" t="n">
-        <v>187.5207644715895</v>
+        <v>184.3283927796865</v>
       </c>
       <c r="C20" t="n">
-        <v>189.6556493942343</v>
+        <v>184.3583198600852</v>
       </c>
       <c r="D20" t="n">
-        <v>185.5155737280782</v>
+        <v>179.2705030798172</v>
       </c>
       <c r="E20" t="n">
-        <v>187.8699340820312</v>
+        <v>179.5997161865234</v>
       </c>
       <c r="F20" t="n">
-        <v>153482800</v>
+        <v>205641400</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B21" t="n">
-        <v>184.3283927796865</v>
+        <v>184.3582990595379</v>
       </c>
       <c r="C21" t="n">
-        <v>184.3583198600852</v>
+        <v>184.4281238318171</v>
       </c>
       <c r="D21" t="n">
-        <v>179.2705030798172</v>
+        <v>176.8662395170747</v>
       </c>
       <c r="E21" t="n">
-        <v>179.5997161865234</v>
+        <v>179.4001770019531</v>
       </c>
       <c r="F21" t="n">
-        <v>205641400</v>
+        <v>214450500</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B22" t="n">
-        <v>184.3583147400375</v>
+        <v>181.7944368108431</v>
       </c>
       <c r="C22" t="n">
-        <v>184.4281395182556</v>
+        <v>182.8419301869027</v>
       </c>
       <c r="D22" t="n">
-        <v>176.866254560341</v>
+        <v>179.3403251298876</v>
       </c>
       <c r="E22" t="n">
-        <v>179.4001922607422</v>
+        <v>181.3754425048828</v>
       </c>
       <c r="F22" t="n">
-        <v>214450500</v>
+        <v>179723300</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B23" t="n">
-        <v>181.7944521048813</v>
+        <v>179.7493465774322</v>
       </c>
       <c r="C23" t="n">
-        <v>182.8419455690647</v>
+        <v>183.6599908268075</v>
       </c>
       <c r="D23" t="n">
-        <v>179.3403402174659</v>
+        <v>179.3203816221287</v>
       </c>
       <c r="E23" t="n">
-        <v>181.3754577636719</v>
+        <v>182.7820892333984</v>
       </c>
       <c r="F23" t="n">
-        <v>179723300</v>
+        <v>173135200</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B24" t="n">
-        <v>179.7493465774322</v>
+        <v>182.6922949953283</v>
       </c>
       <c r="C24" t="n">
-        <v>183.6599908268075</v>
+        <v>184.7573394499357</v>
       </c>
       <c r="D24" t="n">
-        <v>179.3203816221287</v>
+        <v>181.2956320849819</v>
       </c>
       <c r="E24" t="n">
-        <v>182.7820892333984</v>
+        <v>182.2034606933594</v>
       </c>
       <c r="F24" t="n">
-        <v>173135200</v>
+        <v>128544700</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B25" t="n">
-        <v>182.6923102950553</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="C25" t="n">
-        <v>184.7573549226016</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="D25" t="n">
-        <v>181.2956472677441</v>
+        <v>179.3702701372806</v>
       </c>
       <c r="E25" t="n">
-        <v>182.2034759521484</v>
+        <v>180.7270202636719</v>
       </c>
       <c r="F25" t="n">
-        <v>128544700</v>
+        <v>124240200</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B26" t="n">
-        <v>182.3531141136141</v>
+        <v>180.7070662621498</v>
       </c>
       <c r="C26" t="n">
-        <v>182.3531141136141</v>
+        <v>183.0015721983185</v>
       </c>
       <c r="D26" t="n">
-        <v>179.3702701372806</v>
+        <v>176.3375297972393</v>
       </c>
       <c r="E26" t="n">
-        <v>180.7270202636719</v>
+        <v>179.84912109375</v>
       </c>
       <c r="F26" t="n">
-        <v>124240200</v>
+        <v>162249600</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B27" t="n">
-        <v>180.7070509305708</v>
+        <v>179.988793025541</v>
       </c>
       <c r="C27" t="n">
-        <v>183.0015566720687</v>
+        <v>182.5925557149365</v>
       </c>
       <c r="D27" t="n">
-        <v>176.3375148363812</v>
+        <v>179.3602938591047</v>
       </c>
       <c r="E27" t="n">
-        <v>179.8491058349609</v>
+        <v>181.7246398925781</v>
       </c>
       <c r="F27" t="n">
-        <v>162249600</v>
+        <v>111363700</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B28" t="n">
-        <v>179.988777912505</v>
+        <v>183.400590081168</v>
       </c>
       <c r="C28" t="n">
-        <v>182.5925403832715</v>
+        <v>187.0219186862977</v>
       </c>
       <c r="D28" t="n">
-        <v>179.3602787988416</v>
+        <v>183.0614063875393</v>
       </c>
       <c r="E28" t="n">
-        <v>181.7246246337891</v>
+        <v>185.8148040771484</v>
       </c>
       <c r="F28" t="n">
-        <v>111363700</v>
+        <v>131296700</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B29" t="n">
-        <v>183.4006051417061</v>
+        <v>189.5359184602369</v>
       </c>
       <c r="C29" t="n">
-        <v>187.0219340442129</v>
+        <v>191.5411089646758</v>
       </c>
       <c r="D29" t="n">
-        <v>183.0614214202242</v>
+        <v>187.9796341631504</v>
       </c>
       <c r="E29" t="n">
-        <v>185.8148193359375</v>
+        <v>191.0323333740234</v>
       </c>
       <c r="F29" t="n">
-        <v>131296700</v>
+        <v>153452700</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B30" t="n">
-        <v>189.5359033209746</v>
+        <v>192.588592118433</v>
       </c>
       <c r="C30" t="n">
-        <v>191.541093665248</v>
+        <v>202.6644428640734</v>
       </c>
       <c r="D30" t="n">
-        <v>187.979619148197</v>
+        <v>191.4513174538508</v>
       </c>
       <c r="E30" t="n">
-        <v>191.0323181152344</v>
+        <v>200.5495147705078</v>
       </c>
       <c r="F30" t="n">
-        <v>153452700</v>
+        <v>297986200</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B31" t="n">
-        <v>192.5886067715161</v>
+        <v>207.482906515472</v>
       </c>
       <c r="C31" t="n">
-        <v>202.6644582837766</v>
+        <v>211.6828509687219</v>
       </c>
       <c r="D31" t="n">
-        <v>191.4513320204045</v>
+        <v>204.2905578218423</v>
       </c>
       <c r="E31" t="n">
-        <v>200.5495300292969</v>
+        <v>206.5451507568359</v>
       </c>
       <c r="F31" t="n">
-        <v>297986200</v>
+        <v>308829600</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B32" t="n">
-        <v>207.482891187405</v>
+        <v>204.6596525726598</v>
       </c>
       <c r="C32" t="n">
-        <v>211.6828353303786</v>
+        <v>205.6672482532724</v>
       </c>
       <c r="D32" t="n">
-        <v>204.2905427296142</v>
+        <v>200.9286015136062</v>
       </c>
       <c r="E32" t="n">
-        <v>206.5451354980469</v>
+        <v>202.4050598144531</v>
       </c>
       <c r="F32" t="n">
-        <v>308829600</v>
+        <v>178864400</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B33" t="n">
-        <v>204.6596525726598</v>
+        <v>205.9565693232556</v>
       </c>
       <c r="C33" t="n">
-        <v>205.6672482532724</v>
+        <v>207.4729406961805</v>
       </c>
       <c r="D33" t="n">
-        <v>200.9286015136062</v>
+        <v>201.5870481318289</v>
       </c>
       <c r="E33" t="n">
-        <v>202.4050598144531</v>
+        <v>202.0060424804688</v>
       </c>
       <c r="F33" t="n">
-        <v>178864400</v>
+        <v>179802200</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B34" t="n">
-        <v>205.9565693232556</v>
+        <v>207.5826726752522</v>
       </c>
       <c r="C34" t="n">
-        <v>207.4729406961805</v>
+        <v>210.8348755139714</v>
       </c>
       <c r="D34" t="n">
-        <v>201.5870481318289</v>
+        <v>205.0686914304077</v>
       </c>
       <c r="E34" t="n">
-        <v>202.0060424804688</v>
+        <v>206.3855438232422</v>
       </c>
       <c r="F34" t="n">
-        <v>179802200</v>
+        <v>180267300</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B35" t="n">
-        <v>207.5826726752522</v>
+        <v>202.5148147488263</v>
       </c>
       <c r="C35" t="n">
-        <v>210.8348755139714</v>
+        <v>203.4824975937368</v>
       </c>
       <c r="D35" t="n">
-        <v>205.0686914304077</v>
+        <v>197.4569251230167</v>
       </c>
       <c r="E35" t="n">
-        <v>206.3855438232422</v>
+        <v>198.2151184082031</v>
       </c>
       <c r="F35" t="n">
-        <v>180267300</v>
+        <v>188919300</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B36" t="n">
-        <v>202.5148147488263</v>
+        <v>198.2949275919373</v>
       </c>
       <c r="C36" t="n">
-        <v>203.4824975937368</v>
+        <v>202.4350026612236</v>
       </c>
       <c r="D36" t="n">
-        <v>197.4569251230167</v>
+        <v>194.1847643800754</v>
       </c>
       <c r="E36" t="n">
-        <v>198.2151184082031</v>
+        <v>194.7434387207031</v>
       </c>
       <c r="F36" t="n">
-        <v>188919300</v>
+        <v>171350300</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B37" t="n">
-        <v>198.2949120548774</v>
+        <v>195.9505410878136</v>
       </c>
       <c r="C37" t="n">
-        <v>202.4349867997753</v>
+        <v>197.1476699621838</v>
       </c>
       <c r="D37" t="n">
-        <v>194.1847491650603</v>
+        <v>185.9345440647224</v>
       </c>
       <c r="E37" t="n">
-        <v>194.7434234619141</v>
+        <v>187.6304779052734</v>
       </c>
       <c r="F37" t="n">
-        <v>171350300</v>
+        <v>223029800</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B38" t="n">
-        <v>195.9505251524069</v>
+        <v>184.4580698535366</v>
       </c>
       <c r="C38" t="n">
-        <v>197.1476539294223</v>
+        <v>187.8699092076593</v>
       </c>
       <c r="D38" t="n">
-        <v>185.9345289438528</v>
+        <v>178.4823961188316</v>
       </c>
       <c r="E38" t="n">
-        <v>187.6304626464844</v>
+        <v>187.7003021240234</v>
       </c>
       <c r="F38" t="n">
-        <v>223029800</v>
+        <v>264942300</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B39" t="n">
-        <v>184.4580698535366</v>
+        <v>194.6436639125443</v>
       </c>
       <c r="C39" t="n">
-        <v>187.8699092076593</v>
+        <v>199.4621214501376</v>
       </c>
       <c r="D39" t="n">
-        <v>178.4823961188316</v>
+        <v>193.3268115668235</v>
       </c>
       <c r="E39" t="n">
-        <v>187.7003021240234</v>
+        <v>198.5742492675781</v>
       </c>
       <c r="F39" t="n">
-        <v>264942300</v>
+        <v>198897100</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B40" t="n">
-        <v>194.6436788693004</v>
+        <v>194.6935689756818</v>
       </c>
       <c r="C40" t="n">
-        <v>199.4621367771523</v>
+        <v>194.9529420926121</v>
       </c>
       <c r="D40" t="n">
-        <v>193.3268264223904</v>
+        <v>190.8427938118383</v>
       </c>
       <c r="E40" t="n">
-        <v>198.5742645263672</v>
+        <v>192.6983489990234</v>
       </c>
       <c r="F40" t="n">
-        <v>198897100</v>
+        <v>176483300</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B41" t="n">
-        <v>194.6935535589016</v>
+        <v>195.2522318976041</v>
       </c>
       <c r="C41" t="n">
-        <v>194.9529266552934</v>
+        <v>195.4218237722109</v>
       </c>
       <c r="D41" t="n">
-        <v>190.8427786999811</v>
+        <v>190.6732056162565</v>
       </c>
       <c r="E41" t="n">
-        <v>192.6983337402344</v>
+        <v>193.3368225097656</v>
       </c>
       <c r="F41" t="n">
-        <v>176483300</v>
+        <v>154935300</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B42" t="n">
-        <v>195.2522164876445</v>
+        <v>190.5933791327836</v>
       </c>
       <c r="C42" t="n">
-        <v>195.4218083488666</v>
+        <v>190.9824463944715</v>
       </c>
       <c r="D42" t="n">
-        <v>190.673190567689</v>
+        <v>183.4105907203728</v>
       </c>
       <c r="E42" t="n">
-        <v>193.3368072509766</v>
+        <v>186.4133911132812</v>
       </c>
       <c r="F42" t="n">
-        <v>154935300</v>
+        <v>207423100</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B43" t="n">
-        <v>190.5933947337238</v>
+        <v>182.4229435613052</v>
       </c>
       <c r="C43" t="n">
-        <v>190.9824620272586</v>
+        <v>190.553458007553</v>
       </c>
       <c r="D43" t="n">
-        <v>183.4106057333689</v>
+        <v>180.1483942490048</v>
       </c>
       <c r="E43" t="n">
-        <v>186.4134063720703</v>
+        <v>189.7154693603516</v>
       </c>
       <c r="F43" t="n">
-        <v>207423100</v>
+        <v>186591900</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B44" t="n">
-        <v>182.4229582335574</v>
+        <v>185.525507871713</v>
       </c>
       <c r="C44" t="n">
-        <v>190.5534733337414</v>
+        <v>188.5482645458532</v>
       </c>
       <c r="D44" t="n">
-        <v>180.1484087383153</v>
+        <v>183.8794576828592</v>
       </c>
       <c r="E44" t="n">
-        <v>189.7154846191406</v>
+        <v>186.1540069580078</v>
       </c>
       <c r="F44" t="n">
-        <v>186591900</v>
+        <v>173628900</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B45" t="n">
-        <v>185.5255382862568</v>
+        <v>182.9417205846578</v>
       </c>
       <c r="C45" t="n">
-        <v>188.5482954559393</v>
+        <v>184.3583249108488</v>
       </c>
       <c r="D45" t="n">
-        <v>183.879487827554</v>
+        <v>179.2206244483882</v>
       </c>
       <c r="E45" t="n">
-        <v>186.1540374755859</v>
+        <v>180.9265441894531</v>
       </c>
       <c r="F45" t="n">
-        <v>173628900</v>
+        <v>213598900</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B46" t="n">
-        <v>182.941705155915</v>
+        <v>184.3483273978252</v>
       </c>
       <c r="C46" t="n">
-        <v>184.3583093626339</v>
+        <v>187.4109971087465</v>
       </c>
       <c r="D46" t="n">
-        <v>179.2206093334711</v>
+        <v>182.3930205111681</v>
       </c>
       <c r="E46" t="n">
-        <v>180.9265289306641</v>
+        <v>186.0742034912109</v>
       </c>
       <c r="F46" t="n">
-        <v>213598900</v>
+        <v>247246400</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B47" t="n">
-        <v>184.3483273978252</v>
+        <v>195.4816571057099</v>
       </c>
       <c r="C47" t="n">
-        <v>187.4109971087465</v>
+        <v>195.5315406452363</v>
       </c>
       <c r="D47" t="n">
-        <v>182.3930205111681</v>
+        <v>179.4201468289569</v>
       </c>
       <c r="E47" t="n">
-        <v>186.0742034912109</v>
+        <v>180.208251953125</v>
       </c>
       <c r="F47" t="n">
-        <v>247246400</v>
+        <v>343504800</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B48" t="n">
-        <v>195.4816571057099</v>
+        <v>180.8068443722038</v>
       </c>
       <c r="C48" t="n">
-        <v>195.5315406452363</v>
+        <v>184.1189017022491</v>
       </c>
       <c r="D48" t="n">
-        <v>179.4201468289569</v>
+        <v>172.5166923711864</v>
       </c>
       <c r="E48" t="n">
-        <v>180.208251953125</v>
+        <v>178.4524841308594</v>
       </c>
       <c r="F48" t="n">
-        <v>343504800</v>
+        <v>346926200</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B49" t="n">
-        <v>180.8068289121023</v>
+        <v>179.0610243324759</v>
       </c>
       <c r="C49" t="n">
-        <v>184.1188859589464</v>
+        <v>183.0614349513779</v>
       </c>
       <c r="D49" t="n">
-        <v>172.5166776199441</v>
+        <v>176.0582084909882</v>
       </c>
       <c r="E49" t="n">
-        <v>178.4524688720703</v>
+        <v>182.1137084960938</v>
       </c>
       <c r="F49" t="n">
-        <v>346926200</v>
+        <v>256618300</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B50" t="n">
-        <v>179.0610093294625</v>
+        <v>174.4919407266003</v>
       </c>
       <c r="C50" t="n">
-        <v>183.0614196131816</v>
+        <v>177.7341727058355</v>
       </c>
       <c r="D50" t="n">
-        <v>176.0581937395723</v>
+        <v>169.1447513765687</v>
       </c>
       <c r="E50" t="n">
-        <v>182.1136932373047</v>
+        <v>177.3949890136719</v>
       </c>
       <c r="F50" t="n">
-        <v>256618300</v>
+        <v>320600300</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B51" t="n">
-        <v>174.4919707447618</v>
+        <v>181.1959139436215</v>
       </c>
       <c r="C51" t="n">
-        <v>177.734203281764</v>
+        <v>182.4728535594688</v>
       </c>
       <c r="D51" t="n">
-        <v>169.1447804748437</v>
+        <v>177.8140165634392</v>
       </c>
       <c r="E51" t="n">
-        <v>177.39501953125</v>
+        <v>179.8291778564453</v>
       </c>
       <c r="F51" t="n">
-        <v>320600300</v>
+        <v>183852000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B52" t="n">
-        <v>181.1958985688627</v>
+        <v>178.5821404669205</v>
       </c>
       <c r="C52" t="n">
-        <v>182.4728380763597</v>
+        <v>178.8614700176124</v>
       </c>
       <c r="D52" t="n">
-        <v>177.8140014756398</v>
+        <v>176.0781451295325</v>
       </c>
       <c r="E52" t="n">
-        <v>179.8291625976562</v>
+        <v>176.5769500732422</v>
       </c>
       <c r="F52" t="n">
-        <v>183852000</v>
+        <v>121332800</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B53" t="n">
-        <v>178.5821558989869</v>
+        <v>174.3423041351479</v>
       </c>
       <c r="C53" t="n">
-        <v>178.8614854738169</v>
+        <v>179.8690716163194</v>
       </c>
       <c r="D53" t="n">
-        <v>176.0781603452176</v>
+        <v>173.2648835948944</v>
       </c>
       <c r="E53" t="n">
-        <v>176.5769653320312</v>
+        <v>179.4899749755859</v>
       </c>
       <c r="F53" t="n">
-        <v>121332800</v>
+        <v>188131000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B54" t="n">
-        <v>174.3423041351479</v>
+        <v>181.3255769560617</v>
       </c>
       <c r="C54" t="n">
-        <v>179.8690716163194</v>
+        <v>185.2162648499111</v>
       </c>
       <c r="D54" t="n">
-        <v>173.2648835948944</v>
+        <v>179.569788944198</v>
       </c>
       <c r="E54" t="n">
-        <v>179.4899749755859</v>
+        <v>181.0263061523438</v>
       </c>
       <c r="F54" t="n">
-        <v>188131000</v>
+        <v>182632200</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B55" t="n">
-        <v>181.3255769560617</v>
+        <v>180.6472109015755</v>
       </c>
       <c r="C55" t="n">
-        <v>185.2162648499111</v>
+        <v>182.0139316568558</v>
       </c>
       <c r="D55" t="n">
-        <v>179.569788944198</v>
+        <v>178.681918089591</v>
       </c>
       <c r="E55" t="n">
-        <v>181.0263061523438</v>
+        <v>179.1607666015625</v>
       </c>
       <c r="F55" t="n">
-        <v>182632200</v>
+        <v>165138000</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,25 +1873,25 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B56" t="n">
-        <v>180.6471955161887</v>
+        <v>181.1960032737075</v>
       </c>
       <c r="C56" t="n">
-        <v>182.013916155068</v>
+        <v>184.0892423581687</v>
       </c>
       <c r="D56" t="n">
-        <v>178.6819028715845</v>
+        <v>179.5398901129937</v>
       </c>
       <c r="E56" t="n">
-        <v>179.1607513427734</v>
+        <v>182.951904296875</v>
       </c>
       <c r="F56" t="n">
-        <v>165138000</v>
+        <v>167364900</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -1899,25 +1899,25 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B57" t="n">
-        <v>181.1959881613664</v>
+        <v>183.4607020047171</v>
       </c>
       <c r="C57" t="n">
-        <v>184.089227004522</v>
+        <v>184.2289086763207</v>
       </c>
       <c r="D57" t="n">
-        <v>179.5398751387779</v>
+        <v>180.4876631773748</v>
       </c>
       <c r="E57" t="n">
-        <v>182.9518890380859</v>
+        <v>181.9841613769531</v>
       </c>
       <c r="F57" t="n">
-        <v>167364900</v>
+        <v>143971100</v>
       </c>
       <c r="G57" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B58" t="n">
-        <v>183.4606866221248</v>
+        <v>182.2136112701494</v>
       </c>
       <c r="C58" t="n">
-        <v>184.2288932293168</v>
+        <v>187.5610985176648</v>
       </c>
       <c r="D58" t="n">
-        <v>180.4876480440623</v>
+        <v>181.9741660895743</v>
       </c>
       <c r="E58" t="n">
-        <v>181.9841461181641</v>
+        <v>185.1168212890625</v>
       </c>
       <c r="F58" t="n">
-        <v>143971100</v>
+        <v>204378100</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B59" t="n">
-        <v>182.2136112701494</v>
+        <v>185.1268117532098</v>
       </c>
       <c r="C59" t="n">
-        <v>187.5610985176648</v>
+        <v>185.2864418902268</v>
       </c>
       <c r="D59" t="n">
-        <v>181.9741660895743</v>
+        <v>182.8920507276432</v>
       </c>
       <c r="E59" t="n">
-        <v>185.1168212890625</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="F59" t="n">
-        <v>204378100</v>
+        <v>144719700</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B60" t="n">
-        <v>185.12679644575</v>
+        <v>184.538176449994</v>
       </c>
       <c r="C60" t="n">
-        <v>185.2864265695677</v>
+        <v>185.0469803407326</v>
       </c>
       <c r="D60" t="n">
-        <v>182.8920356049676</v>
+        <v>181.6150088138297</v>
       </c>
       <c r="E60" t="n">
-        <v>184.5381774902344</v>
+        <v>183.3509521484375</v>
       </c>
       <c r="F60" t="n">
-        <v>144719700</v>
+        <v>162785400</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B61" t="n">
-        <v>184.5381918075859</v>
+        <v>179.8591224369562</v>
       </c>
       <c r="C61" t="n">
-        <v>185.0469957406681</v>
+        <v>180.8967030087509</v>
       </c>
       <c r="D61" t="n">
-        <v>181.6150239281505</v>
+        <v>176.2076633109278</v>
       </c>
       <c r="E61" t="n">
-        <v>183.3509674072266</v>
+        <v>180.5075988769531</v>
       </c>
       <c r="F61" t="n">
-        <v>162785400</v>
+        <v>182136600</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B62" t="n">
-        <v>179.8591376409278</v>
+        <v>180.6871831157045</v>
       </c>
       <c r="C62" t="n">
-        <v>180.896718300432</v>
+        <v>182.3931976659576</v>
       </c>
       <c r="D62" t="n">
-        <v>176.2076782062319</v>
+        <v>174.2123291208211</v>
       </c>
       <c r="E62" t="n">
-        <v>180.5076141357422</v>
+        <v>174.6114044189453</v>
       </c>
       <c r="F62" t="n">
-        <v>182136600</v>
+        <v>204274900</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B63" t="n">
-        <v>180.6871989054384</v>
+        <v>177.5245903328353</v>
       </c>
       <c r="C63" t="n">
-        <v>182.3932136047752</v>
+        <v>178.0034654802094</v>
       </c>
       <c r="D63" t="n">
-        <v>174.2123443447362</v>
+        <v>174.6213802569945</v>
       </c>
       <c r="E63" t="n">
-        <v>174.6114196777344</v>
+        <v>175.8784332275391</v>
       </c>
       <c r="F63" t="n">
-        <v>204274900</v>
+        <v>164775600</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B64" t="n">
-        <v>177.5245903328353</v>
+        <v>175.8485164107673</v>
       </c>
       <c r="C64" t="n">
-        <v>178.0034654802094</v>
+        <v>178.0733214473424</v>
       </c>
       <c r="D64" t="n">
-        <v>174.6213802569945</v>
+        <v>174.4916907151964</v>
       </c>
       <c r="E64" t="n">
-        <v>175.8784332275391</v>
+        <v>177.3051147460938</v>
       </c>
       <c r="F64" t="n">
-        <v>164775600</v>
+        <v>148588100</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B65" t="n">
-        <v>175.8485012773324</v>
+        <v>175.6888968536916</v>
       </c>
       <c r="C65" t="n">
-        <v>178.0733061224419</v>
+        <v>175.7188256001934</v>
       </c>
       <c r="D65" t="n">
-        <v>174.4916756985292</v>
+        <v>169.9124052081842</v>
       </c>
       <c r="E65" t="n">
-        <v>177.3050994873047</v>
+        <v>170.5409393310547</v>
       </c>
       <c r="F65" t="n">
-        <v>148588100</v>
+        <v>222775500</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B66" t="n">
-        <v>175.6888968536916</v>
+        <v>174.1225483861358</v>
       </c>
       <c r="C66" t="n">
-        <v>175.7188256001934</v>
+        <v>175.7387615308714</v>
       </c>
       <c r="D66" t="n">
-        <v>169.9124052081842</v>
+        <v>171.4188835631069</v>
       </c>
       <c r="E66" t="n">
-        <v>170.5409393310547</v>
+        <v>173.7334594726562</v>
       </c>
       <c r="F66" t="n">
-        <v>222775500</v>
+        <v>176096000</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B67" t="n">
-        <v>174.1225483861358</v>
+        <v>176.2575523358494</v>
       </c>
       <c r="C67" t="n">
-        <v>175.7387615308714</v>
+        <v>181.0263919449467</v>
       </c>
       <c r="D67" t="n">
-        <v>171.4188835631069</v>
+        <v>175.9283209122297</v>
       </c>
       <c r="E67" t="n">
-        <v>173.7334594726562</v>
+        <v>180.5674743652344</v>
       </c>
       <c r="F67" t="n">
-        <v>176096000</v>
+        <v>324925900</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B68" t="n">
-        <v>176.2575523358494</v>
+        <v>183.4906129473229</v>
       </c>
       <c r="C68" t="n">
-        <v>181.0263919449467</v>
+        <v>183.730058116363</v>
       </c>
       <c r="D68" t="n">
-        <v>175.9283209122297</v>
+        <v>181.9242862331203</v>
       </c>
       <c r="E68" t="n">
-        <v>180.5674743652344</v>
+        <v>183.2611541748047</v>
       </c>
       <c r="F68" t="n">
-        <v>324925900</v>
+        <v>129064400</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B69" t="n">
-        <v>183.4906282252173</v>
+        <v>182.5428571096804</v>
       </c>
       <c r="C69" t="n">
-        <v>183.7300734141942</v>
+        <v>188.8880102762506</v>
       </c>
       <c r="D69" t="n">
-        <v>181.9243013805983</v>
+        <v>182.4730132178061</v>
       </c>
       <c r="E69" t="n">
-        <v>183.2611694335938</v>
+        <v>188.7682952880859</v>
       </c>
       <c r="F69" t="n">
-        <v>129064400</v>
+        <v>174873600</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B70" t="n">
-        <v>182.5428423541149</v>
+        <v>187.5012437217294</v>
       </c>
       <c r="C70" t="n">
-        <v>188.8879950077845</v>
+        <v>188.4689804086018</v>
       </c>
       <c r="D70" t="n">
-        <v>182.4729984678863</v>
+        <v>186.154389299292</v>
       </c>
       <c r="E70" t="n">
-        <v>188.7682800292969</v>
+        <v>188.169677734375</v>
       </c>
       <c r="F70" t="n">
-        <v>174873600</v>
+        <v>65528500</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B71" t="n">
-        <v>187.5012437217294</v>
+        <v>189.4766133088049</v>
       </c>
       <c r="C71" t="n">
-        <v>188.4689804086018</v>
+        <v>192.2401507638228</v>
       </c>
       <c r="D71" t="n">
-        <v>186.154389299292</v>
+        <v>187.5610975436497</v>
       </c>
       <c r="E71" t="n">
-        <v>188.169677734375</v>
+        <v>190.0851898193359</v>
       </c>
       <c r="F71" t="n">
-        <v>65528500</v>
+        <v>139740300</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B72" t="n">
-        <v>189.4766285187414</v>
+        <v>187.2717899684254</v>
       </c>
       <c r="C72" t="n">
-        <v>192.240166195598</v>
+        <v>188.3193265216257</v>
       </c>
       <c r="D72" t="n">
-        <v>187.5611125998212</v>
+        <v>185.4759890979627</v>
       </c>
       <c r="E72" t="n">
-        <v>190.085205078125</v>
+        <v>187.7805938720703</v>
       </c>
       <c r="F72" t="n">
-        <v>139740300</v>
+        <v>120006100</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B73" t="n">
-        <v>187.2717899684254</v>
+        <v>187.8005508490403</v>
       </c>
       <c r="C73" t="n">
-        <v>188.3193265216257</v>
+        <v>188.5487999407664</v>
       </c>
       <c r="D73" t="n">
-        <v>185.4759890979627</v>
+        <v>186.4935963146986</v>
       </c>
       <c r="E73" t="n">
-        <v>187.7805938720703</v>
+        <v>187.1021728515625</v>
       </c>
       <c r="F73" t="n">
-        <v>120006100</v>
+        <v>97687300</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B74" t="n">
-        <v>187.8005508490403</v>
+        <v>189.127461449755</v>
       </c>
       <c r="C74" t="n">
-        <v>188.5487999407664</v>
+        <v>190.1151405796458</v>
       </c>
       <c r="D74" t="n">
-        <v>186.4935963146986</v>
+        <v>186.0546497967401</v>
       </c>
       <c r="E74" t="n">
-        <v>187.1021728515625</v>
+        <v>186.0646209716797</v>
       </c>
       <c r="F74" t="n">
-        <v>97687300</v>
+        <v>120100500</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B75" t="n">
-        <v>189.1274459397885</v>
+        <v>189.3967976648124</v>
       </c>
       <c r="C75" t="n">
-        <v>190.1151249886817</v>
+        <v>192.479580126264</v>
       </c>
       <c r="D75" t="n">
-        <v>186.0546345387688</v>
+        <v>187.8204844911982</v>
       </c>
       <c r="E75" t="n">
-        <v>186.0646057128906</v>
+        <v>188.4091186523438</v>
       </c>
       <c r="F75" t="n">
-        <v>120100500</v>
+        <v>148240500</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B76" t="n">
-        <v>189.3968130035911</v>
+        <v>191.3123337767646</v>
       </c>
       <c r="C76" t="n">
-        <v>192.4795957147097</v>
+        <v>193.1779786425506</v>
       </c>
       <c r="D76" t="n">
-        <v>187.8204997023152</v>
+        <v>185.7154296257417</v>
       </c>
       <c r="E76" t="n">
-        <v>188.4091339111328</v>
+        <v>187.6808319091797</v>
       </c>
       <c r="F76" t="n">
-        <v>148240500</v>
+        <v>183529700</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B77" t="n">
-        <v>191.3123182227279</v>
+        <v>190.0752284670132</v>
       </c>
       <c r="C77" t="n">
-        <v>193.1779629368336</v>
+        <v>191.7213703933745</v>
       </c>
       <c r="D77" t="n">
-        <v>185.7154145267434</v>
+        <v>186.3838692947835</v>
       </c>
       <c r="E77" t="n">
-        <v>187.6808166503906</v>
+        <v>186.8028869628906</v>
       </c>
       <c r="F77" t="n">
-        <v>183529700</v>
+        <v>176862600</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B78" t="n">
-        <v>190.0752284670132</v>
+        <v>188.1297701943655</v>
       </c>
       <c r="C78" t="n">
-        <v>191.7213703933745</v>
+        <v>190.9232211122124</v>
       </c>
       <c r="D78" t="n">
-        <v>186.3838692947835</v>
+        <v>186.1244530144955</v>
       </c>
       <c r="E78" t="n">
-        <v>186.8028869628906</v>
+        <v>188.6685028076172</v>
       </c>
       <c r="F78" t="n">
-        <v>176862600</v>
+        <v>153543200</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B79" t="n">
-        <v>188.1297854095839</v>
+        <v>188.6685228499072</v>
       </c>
       <c r="C79" t="n">
-        <v>190.9232365533545</v>
+        <v>189.1074981045344</v>
       </c>
       <c r="D79" t="n">
-        <v>186.1244680675316</v>
+        <v>183.2811352524241</v>
       </c>
       <c r="E79" t="n">
-        <v>188.6685180664062</v>
+        <v>184.6080169677734</v>
       </c>
       <c r="F79" t="n">
-        <v>153543200</v>
+        <v>172457000</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B80" t="n">
-        <v>188.6685228499072</v>
+        <v>184.6479238968445</v>
       </c>
       <c r="C80" t="n">
-        <v>189.1074981045344</v>
+        <v>185.9049768874807</v>
       </c>
       <c r="D80" t="n">
-        <v>183.2811352524241</v>
+        <v>183.2412119543349</v>
       </c>
       <c r="E80" t="n">
-        <v>184.6080169677734</v>
+        <v>184.4284362792969</v>
       </c>
       <c r="F80" t="n">
-        <v>172457000</v>
+        <v>131327500</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B81" t="n">
-        <v>184.6479238968445</v>
+        <v>182.7922691735387</v>
       </c>
       <c r="C81" t="n">
-        <v>185.9049768874807</v>
+        <v>186.6831584288149</v>
       </c>
       <c r="D81" t="n">
-        <v>183.2412119543349</v>
+        <v>182.5927391235801</v>
       </c>
       <c r="E81" t="n">
-        <v>184.4284362792969</v>
+        <v>184.5082550048828</v>
       </c>
       <c r="F81" t="n">
-        <v>131327500</v>
+        <v>137968500</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B82" t="n">
-        <v>182.7922691735387</v>
+        <v>184.5681140987238</v>
       </c>
       <c r="C82" t="n">
-        <v>186.6831584288149</v>
+        <v>187.6708543554723</v>
       </c>
       <c r="D82" t="n">
-        <v>182.5927391235801</v>
+        <v>182.9718432388734</v>
       </c>
       <c r="E82" t="n">
-        <v>184.5082550048828</v>
+        <v>185.376220703125</v>
       </c>
       <c r="F82" t="n">
-        <v>137968500</v>
+        <v>160128900</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B83" t="n">
-        <v>184.5680989064521</v>
+        <v>183.8897012556695</v>
       </c>
       <c r="C83" t="n">
-        <v>187.6708389078061</v>
+        <v>184.0293738083791</v>
       </c>
       <c r="D83" t="n">
-        <v>182.9718281779948</v>
+        <v>180.3779146434709</v>
       </c>
       <c r="E83" t="n">
-        <v>185.3762054443359</v>
+        <v>182.7124481201172</v>
       </c>
       <c r="F83" t="n">
-        <v>160128900</v>
+        <v>159586100</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B84" t="n">
-        <v>183.8897012556695</v>
+        <v>186.0646079796491</v>
       </c>
       <c r="C84" t="n">
-        <v>184.0293738083791</v>
+        <v>189.2571344016907</v>
       </c>
       <c r="D84" t="n">
-        <v>180.3779146434709</v>
+        <v>185.895006678512</v>
       </c>
       <c r="E84" t="n">
-        <v>182.7124481201172</v>
+        <v>186.6133270263672</v>
       </c>
       <c r="F84" t="n">
-        <v>159586100</v>
+        <v>206188600</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B85" t="n">
-        <v>186.0646079796491</v>
+        <v>188.6385795892923</v>
       </c>
       <c r="C85" t="n">
-        <v>189.2571344016907</v>
+        <v>189.99540517049</v>
       </c>
       <c r="D85" t="n">
-        <v>185.895006678512</v>
+        <v>185.6455833269296</v>
       </c>
       <c r="E85" t="n">
-        <v>186.6133270263672</v>
+        <v>185.7952270507812</v>
       </c>
       <c r="F85" t="n">
-        <v>206188600</v>
+        <v>187967200</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B86" t="n">
-        <v>188.6385950815971</v>
+        <v>181.4753266272146</v>
       </c>
       <c r="C86" t="n">
-        <v>189.9954207742267</v>
+        <v>181.9542169705431</v>
       </c>
       <c r="D86" t="n">
-        <v>185.6455985734289</v>
+        <v>177.1953488429791</v>
       </c>
       <c r="E86" t="n">
-        <v>185.7952423095703</v>
+        <v>177.6542816162109</v>
       </c>
       <c r="F86" t="n">
-        <v>187967200</v>
+        <v>223345300</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B87" t="n">
-        <v>181.4753422141945</v>
+        <v>178.6320081827799</v>
       </c>
       <c r="C87" t="n">
-        <v>181.9542325986551</v>
+        <v>184.9472325313386</v>
       </c>
       <c r="D87" t="n">
-        <v>177.1953640623503</v>
+        <v>177.9835164834521</v>
       </c>
       <c r="E87" t="n">
-        <v>177.654296875</v>
+        <v>182.8920440673828</v>
       </c>
       <c r="F87" t="n">
-        <v>223345300</v>
+        <v>200381000</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B88" t="n">
-        <v>178.6320081827799</v>
+        <v>184.3186915464293</v>
       </c>
       <c r="C88" t="n">
-        <v>184.9472325313386</v>
+        <v>185.7353746560278</v>
       </c>
       <c r="D88" t="n">
-        <v>177.9835164834521</v>
+        <v>183.5005985718231</v>
       </c>
       <c r="E88" t="n">
-        <v>182.8920440673828</v>
+        <v>184.4084777832031</v>
       </c>
       <c r="F88" t="n">
-        <v>200381000</v>
+        <v>139636600</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B89" t="n">
-        <v>184.3186915464293</v>
+        <v>187.0622712594319</v>
       </c>
       <c r="C89" t="n">
-        <v>185.7353746560278</v>
+        <v>189.1573747868041</v>
       </c>
       <c r="D89" t="n">
-        <v>183.5005985718231</v>
+        <v>186.3838660627843</v>
       </c>
       <c r="E89" t="n">
-        <v>184.4084777832031</v>
+        <v>187.2318725585938</v>
       </c>
       <c r="F89" t="n">
-        <v>139636600</v>
+        <v>142748100</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B90" t="n">
-        <v>187.0622712594319</v>
+        <v>186.7230748442759</v>
       </c>
       <c r="C90" t="n">
-        <v>189.1573747868041</v>
+        <v>188.6784906596197</v>
       </c>
       <c r="D90" t="n">
-        <v>186.3838660627843</v>
+        <v>185.555808059744</v>
       </c>
       <c r="E90" t="n">
-        <v>187.2318725585938</v>
+        <v>186.0346832275391</v>
       </c>
       <c r="F90" t="n">
-        <v>142748100</v>
+        <v>124799600</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B91" t="n">
-        <v>186.7230748442759</v>
+        <v>186.8028844605491</v>
       </c>
       <c r="C91" t="n">
-        <v>188.6784906596197</v>
+        <v>189.5564356240106</v>
       </c>
       <c r="D91" t="n">
-        <v>185.555808059744</v>
+        <v>185.2664711415707</v>
       </c>
       <c r="E91" t="n">
-        <v>186.0346832275391</v>
+        <v>188.0798950195312</v>
       </c>
       <c r="F91" t="n">
-        <v>124799600</v>
+        <v>143711600</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B92" t="n">
-        <v>186.8028844605491</v>
+        <v>190.8234748728661</v>
       </c>
       <c r="C92" t="n">
-        <v>189.5564356240106</v>
+        <v>191.9009553855833</v>
       </c>
       <c r="D92" t="n">
-        <v>185.2664711415707</v>
+        <v>189.3968053634026</v>
       </c>
       <c r="E92" t="n">
-        <v>188.0798950195312</v>
+        <v>191.0728912353516</v>
       </c>
       <c r="F92" t="n">
-        <v>143711600</v>
+        <v>148552700</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B93" t="n">
-        <v>190.8234748728661</v>
+        <v>190.8932954336949</v>
       </c>
       <c r="C93" t="n">
-        <v>191.9009553855833</v>
+        <v>193.0282987969995</v>
       </c>
       <c r="D93" t="n">
-        <v>189.3968053634026</v>
+        <v>185.625623299501</v>
       </c>
       <c r="E93" t="n">
-        <v>191.0728912353516</v>
+        <v>192.0605621337891</v>
       </c>
       <c r="F93" t="n">
-        <v>148552700</v>
+        <v>171764400</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B94" t="n">
-        <v>190.8933105997472</v>
+        <v>190.7636071727618</v>
       </c>
       <c r="C94" t="n">
-        <v>193.0283141326731</v>
+        <v>194.0359484555967</v>
       </c>
       <c r="D94" t="n">
-        <v>185.6256380470483</v>
+        <v>189.0276639024229</v>
       </c>
       <c r="E94" t="n">
-        <v>192.0605773925781</v>
+        <v>190.6837921142578</v>
       </c>
       <c r="F94" t="n">
-        <v>171764400</v>
+        <v>179489500</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B95" t="n">
-        <v>190.7636224379378</v>
+        <v>186.7629812920276</v>
       </c>
       <c r="C95" t="n">
-        <v>194.0359639826301</v>
+        <v>189.8557504766133</v>
       </c>
       <c r="D95" t="n">
-        <v>189.0276790286862</v>
+        <v>184.4484052141589</v>
       </c>
       <c r="E95" t="n">
-        <v>190.6838073730469</v>
+        <v>185.1766967773438</v>
       </c>
       <c r="F95" t="n">
-        <v>179489500</v>
+        <v>165794100</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B96" t="n">
-        <v>186.7629659025267</v>
+        <v>185.8052108647954</v>
       </c>
       <c r="C96" t="n">
-        <v>189.8557348322644</v>
+        <v>185.8351396091497</v>
       </c>
       <c r="D96" t="n">
-        <v>184.4483900153819</v>
+        <v>175.8185703987175</v>
       </c>
       <c r="E96" t="n">
-        <v>185.1766815185547</v>
+        <v>179.9189758300781</v>
       </c>
       <c r="F96" t="n">
-        <v>165794100</v>
+        <v>204019600</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B97" t="n">
-        <v>185.8052266227915</v>
+        <v>179.0410414348666</v>
       </c>
       <c r="C97" t="n">
-        <v>185.835155369684</v>
+        <v>179.160756412826</v>
       </c>
       <c r="D97" t="n">
-        <v>175.8185853097543</v>
+        <v>171.5086645338761</v>
       </c>
       <c r="E97" t="n">
-        <v>179.9189910888672</v>
+        <v>173.7833404541016</v>
       </c>
       <c r="F97" t="n">
-        <v>204019600</v>
+        <v>207014100</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B98" t="n">
-        <v>179.0410571553003</v>
+        <v>174.5215964583249</v>
       </c>
       <c r="C98" t="n">
-        <v>179.1607721437711</v>
+        <v>176.4071986282528</v>
       </c>
       <c r="D98" t="n">
-        <v>171.5086795929406</v>
+        <v>170.6307075914073</v>
       </c>
       <c r="E98" t="n">
-        <v>173.7833557128906</v>
+        <v>171.4787292480469</v>
       </c>
       <c r="F98" t="n">
-        <v>207014100</v>
+        <v>206312900</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B99" t="n">
-        <v>174.5216119878791</v>
+        <v>176.277498975506</v>
       </c>
       <c r="C99" t="n">
-        <v>176.4072143255947</v>
+        <v>186.5634266395524</v>
       </c>
       <c r="D99" t="n">
-        <v>170.6307227747363</v>
+        <v>174.1923819783884</v>
       </c>
       <c r="E99" t="n">
-        <v>171.4787445068359</v>
+        <v>184.9771423339844</v>
       </c>
       <c r="F99" t="n">
-        <v>206312900</v>
+        <v>231346200</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B100" t="n">
-        <v>176.2775135166603</v>
+        <v>183.8298238555102</v>
       </c>
       <c r="C100" t="n">
-        <v>186.5634420291942</v>
+        <v>193.2078878887748</v>
       </c>
       <c r="D100" t="n">
-        <v>174.1923963475411</v>
+        <v>183.5205500126207</v>
       </c>
       <c r="E100" t="n">
-        <v>184.9771575927734</v>
+        <v>189.5963287353516</v>
       </c>
       <c r="F100" t="n">
-        <v>231346200</v>
+        <v>196387400</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B101" t="n">
-        <v>183.8298238555102</v>
+        <v>190.933219719687</v>
       </c>
       <c r="C101" t="n">
-        <v>193.2078878887748</v>
+        <v>192.0306425866914</v>
       </c>
       <c r="D101" t="n">
-        <v>183.5205500126207</v>
+        <v>187.6808205923615</v>
       </c>
       <c r="E101" t="n">
-        <v>189.5963287353516</v>
+        <v>188.0998382568359</v>
       </c>
       <c r="F101" t="n">
-        <v>196387400</v>
+        <v>136764800</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B102" t="n">
-        <v>190.933219719687</v>
+        <v>192.0007297023972</v>
       </c>
       <c r="C102" t="n">
-        <v>192.0306425866914</v>
+        <v>192.8088363522974</v>
       </c>
       <c r="D102" t="n">
-        <v>187.6808205923615</v>
+        <v>188.3293278304631</v>
       </c>
       <c r="E102" t="n">
-        <v>188.0998382568359</v>
+        <v>189.6063385009766</v>
       </c>
       <c r="F102" t="n">
-        <v>136764800</v>
+        <v>144192700</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B103" t="n">
-        <v>192.0007142509167</v>
+        <v>192.5793648877844</v>
       </c>
       <c r="C103" t="n">
-        <v>192.8088208357837</v>
+        <v>193.1580126884611</v>
       </c>
       <c r="D103" t="n">
-        <v>188.329312674443</v>
+        <v>186.0745817463215</v>
       </c>
       <c r="E103" t="n">
-        <v>189.6063232421875</v>
+        <v>186.5035858154297</v>
       </c>
       <c r="F103" t="n">
-        <v>144192700</v>
+        <v>189932500</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B104" t="n">
-        <v>192.5793648877844</v>
+        <v>187.042320465516</v>
       </c>
       <c r="C104" t="n">
-        <v>193.1580126884611</v>
+        <v>187.0622780376601</v>
       </c>
       <c r="D104" t="n">
-        <v>186.0745817463215</v>
+        <v>181.1660713803529</v>
       </c>
       <c r="E104" t="n">
-        <v>186.5035858154297</v>
+        <v>182.3832244873047</v>
       </c>
       <c r="F104" t="n">
-        <v>189932500</v>
+        <v>161888000</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B105" t="n">
-        <v>187.0423048169314</v>
+        <v>181.3257085516038</v>
       </c>
       <c r="C105" t="n">
-        <v>187.0622623874058</v>
+        <v>186.7130962790006</v>
       </c>
       <c r="D105" t="n">
-        <v>181.1660562233949</v>
+        <v>178.7617008539599</v>
       </c>
       <c r="E105" t="n">
-        <v>182.3832092285156</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="F105" t="n">
-        <v>161888000</v>
+        <v>162276900</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B106" t="n">
-        <v>181.3256935584433</v>
+        <v>188.3093443160685</v>
       </c>
       <c r="C106" t="n">
-        <v>186.7130808403767</v>
+        <v>189.9255573932224</v>
       </c>
       <c r="D106" t="n">
-        <v>178.7616860728079</v>
+        <v>186.3239846890322</v>
       </c>
       <c r="E106" t="n">
-        <v>184.5381774902344</v>
+        <v>187.5411376953125</v>
       </c>
       <c r="F106" t="n">
-        <v>162276900</v>
+        <v>164749100</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B107" t="n">
-        <v>188.3093443160685</v>
+        <v>186.62329889396</v>
       </c>
       <c r="C107" t="n">
-        <v>189.9255573932224</v>
+        <v>187.9900957055448</v>
       </c>
       <c r="D107" t="n">
-        <v>186.3239846890322</v>
+        <v>185.2265733363672</v>
       </c>
       <c r="E107" t="n">
-        <v>187.5411376953125</v>
+        <v>187.4613342285156</v>
       </c>
       <c r="F107" t="n">
-        <v>164749100</v>
+        <v>126554500</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B108" t="n">
-        <v>186.62329889396</v>
+        <v>186.1344488846578</v>
       </c>
       <c r="C108" t="n">
-        <v>187.9900957055448</v>
+        <v>189.8856654675195</v>
       </c>
       <c r="D108" t="n">
-        <v>185.2265733363672</v>
+        <v>185.5059147845697</v>
       </c>
       <c r="E108" t="n">
-        <v>187.4613342285156</v>
+        <v>189.3768615722656</v>
       </c>
       <c r="F108" t="n">
-        <v>126554500</v>
+        <v>178422300</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B109" t="n">
-        <v>186.1344488846578</v>
+        <v>190.9531700210539</v>
       </c>
       <c r="C109" t="n">
-        <v>189.8856654675195</v>
+        <v>193.4972200828311</v>
       </c>
       <c r="D109" t="n">
-        <v>185.5059147845697</v>
+        <v>189.1374267327081</v>
       </c>
       <c r="E109" t="n">
-        <v>189.3768615722656</v>
+        <v>191.1028289794922</v>
       </c>
       <c r="F109" t="n">
-        <v>178422300</v>
+        <v>171584800</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B110" t="n">
-        <v>190.9531547742145</v>
+        <v>191.0429698590405</v>
       </c>
       <c r="C110" t="n">
-        <v>193.4972046328596</v>
+        <v>193.3176459547985</v>
       </c>
       <c r="D110" t="n">
-        <v>189.1374116308485</v>
+        <v>186.9625064417709</v>
       </c>
       <c r="E110" t="n">
-        <v>191.1028137207031</v>
+        <v>192.3997955322266</v>
       </c>
       <c r="F110" t="n">
-        <v>171584800</v>
+        <v>175123600</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B111" t="n">
-        <v>191.0429698590405</v>
+        <v>193.9960453222018</v>
       </c>
       <c r="C111" t="n">
-        <v>193.3176459547985</v>
+        <v>197.1686293956491</v>
       </c>
       <c r="D111" t="n">
-        <v>186.9625064417709</v>
+        <v>193.3375824661624</v>
       </c>
       <c r="E111" t="n">
-        <v>192.3997955322266</v>
+        <v>195.1034545898438</v>
       </c>
       <c r="F111" t="n">
-        <v>175123600</v>
+        <v>250637100</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B112" t="n">
-        <v>193.9960453222018</v>
+        <v>193.8164813019665</v>
       </c>
       <c r="C112" t="n">
-        <v>197.1686293956491</v>
+        <v>193.8364236513225</v>
       </c>
       <c r="D112" t="n">
-        <v>193.3375824661624</v>
+        <v>183.8897126034445</v>
       </c>
       <c r="E112" t="n">
-        <v>195.1034545898438</v>
+        <v>184.4583740234375</v>
       </c>
       <c r="F112" t="n">
-        <v>250637100</v>
+        <v>360807900</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B113" t="n">
-        <v>193.8164813019665</v>
+        <v>180.8268714126474</v>
       </c>
       <c r="C113" t="n">
-        <v>193.8364236513225</v>
+        <v>182.1637395256691</v>
       </c>
       <c r="D113" t="n">
-        <v>183.8897126034445</v>
+        <v>175.9682453114839</v>
       </c>
       <c r="E113" t="n">
-        <v>184.4583740234375</v>
+        <v>176.7763519287109</v>
       </c>
       <c r="F113" t="n">
-        <v>360807900</v>
+        <v>311636500</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B114" t="n">
-        <v>180.8268714126474</v>
+        <v>174.6014235260267</v>
       </c>
       <c r="C114" t="n">
-        <v>182.1637395256691</v>
+        <v>183.0317086895539</v>
       </c>
       <c r="D114" t="n">
-        <v>175.9682453114839</v>
+        <v>174.2322921838959</v>
       </c>
       <c r="E114" t="n">
-        <v>176.7763519287109</v>
+        <v>182.0539855957031</v>
       </c>
       <c r="F114" t="n">
-        <v>311636500</v>
+        <v>209095300</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B115" t="n">
-        <v>174.6014235260267</v>
+        <v>178.0733135069376</v>
       </c>
       <c r="C115" t="n">
-        <v>183.0317086895539</v>
+        <v>180.4776756968921</v>
       </c>
       <c r="D115" t="n">
-        <v>174.2322921838959</v>
+        <v>176.5069714269912</v>
       </c>
       <c r="E115" t="n">
-        <v>182.0539855957031</v>
+        <v>179.6296691894531</v>
       </c>
       <c r="F115" t="n">
-        <v>209095300</v>
+        <v>178099400</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B116" t="n">
-        <v>178.0733135069376</v>
+        <v>180.0187649948852</v>
       </c>
       <c r="C116" t="n">
-        <v>180.4776756968921</v>
+        <v>184.2688145383873</v>
       </c>
       <c r="D116" t="n">
-        <v>176.5069714269912</v>
+        <v>179.6396472340209</v>
       </c>
       <c r="E116" t="n">
-        <v>179.6296691894531</v>
+        <v>182.6126861572266</v>
       </c>
       <c r="F116" t="n">
-        <v>178099400</v>
+        <v>177731200</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B117" t="n">
-        <v>180.0187499528396</v>
+        <v>180.7470550179114</v>
       </c>
       <c r="C117" t="n">
-        <v>184.2687991412151</v>
+        <v>183.6303076754259</v>
       </c>
       <c r="D117" t="n">
-        <v>179.6396322236537</v>
+        <v>177.4647422536165</v>
       </c>
       <c r="E117" t="n">
-        <v>182.6126708984375</v>
+        <v>182.9119873046875</v>
       </c>
       <c r="F117" t="n">
-        <v>177731200</v>
+        <v>198779700</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B118" t="n">
-        <v>180.7470399397241</v>
+        <v>179.420134514761</v>
       </c>
       <c r="C118" t="n">
-        <v>183.6302923567135</v>
+        <v>182.3333155363547</v>
       </c>
       <c r="D118" t="n">
-        <v>177.4647274492447</v>
+        <v>176.4071960911633</v>
       </c>
       <c r="E118" t="n">
-        <v>182.9119720458984</v>
+        <v>177.4048614501953</v>
       </c>
       <c r="F118" t="n">
-        <v>198779700</v>
+        <v>189021900</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B119" t="n">
-        <v>179.4201653790109</v>
+        <v>176.4171820751478</v>
       </c>
       <c r="C119" t="n">
-        <v>182.3333469017365</v>
+        <v>182.4829897940845</v>
       </c>
       <c r="D119" t="n">
-        <v>176.4072264371208</v>
+        <v>175.1501427003192</v>
       </c>
       <c r="E119" t="n">
-        <v>177.4048919677734</v>
+        <v>182.2235870361328</v>
       </c>
       <c r="F119" t="n">
-        <v>189021900</v>
+        <v>177213600</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B120" t="n">
-        <v>176.4171968477281</v>
+        <v>181.9741760435397</v>
       </c>
       <c r="C120" t="n">
-        <v>182.4830050745951</v>
+        <v>186.0047530762794</v>
       </c>
       <c r="D120" t="n">
-        <v>175.1501573668019</v>
+        <v>181.5850871183009</v>
       </c>
       <c r="E120" t="n">
-        <v>182.2236022949219</v>
+        <v>184.3386535644531</v>
       </c>
       <c r="F120" t="n">
-        <v>177213600</v>
+        <v>179118500</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,25 +3563,25 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B121" t="n">
-        <v>181.9741760435397</v>
+        <v>185.4860219488843</v>
       </c>
       <c r="C121" t="n">
-        <v>186.0047530762794</v>
+        <v>187.1921136401388</v>
       </c>
       <c r="D121" t="n">
-        <v>181.5850871183009</v>
+        <v>184.0293448898806</v>
       </c>
       <c r="E121" t="n">
-        <v>184.3386535644531</v>
+        <v>185.6057434082031</v>
       </c>
       <c r="F121" t="n">
-        <v>179118500</v>
+        <v>145280400</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3589,25 +3589,25 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B122" t="n">
-        <v>185.4860219488843</v>
+        <v>183.6302641505579</v>
       </c>
       <c r="C122" t="n">
-        <v>187.1921136401388</v>
+        <v>184.5182338343672</v>
       </c>
       <c r="D122" t="n">
-        <v>184.0293448898806</v>
+        <v>181.3355064165816</v>
       </c>
       <c r="E122" t="n">
-        <v>185.6057434082031</v>
+        <v>182.7223358154297</v>
       </c>
       <c r="F122" t="n">
-        <v>145280400</v>
+        <v>155762700</v>
       </c>
       <c r="G122" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B123" t="n">
-        <v>183.6302641505579</v>
+        <v>184.4982918130038</v>
       </c>
       <c r="C123" t="n">
-        <v>184.5182338343672</v>
+        <v>185.6656218245341</v>
       </c>
       <c r="D123" t="n">
-        <v>181.3355064165816</v>
+        <v>179.5296528660815</v>
       </c>
       <c r="E123" t="n">
-        <v>182.7223358154297</v>
+        <v>179.8389434814453</v>
       </c>
       <c r="F123" t="n">
-        <v>155762700</v>
+        <v>160988400</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B124" t="n">
-        <v>184.4982918130038</v>
+        <v>182.5527246843909</v>
       </c>
       <c r="C124" t="n">
-        <v>185.6656218245341</v>
+        <v>188.4492501487561</v>
       </c>
       <c r="D124" t="n">
-        <v>179.5296528660815</v>
+        <v>180.9962848148914</v>
       </c>
       <c r="E124" t="n">
-        <v>179.8389434814453</v>
+        <v>182.8021545410156</v>
       </c>
       <c r="F124" t="n">
-        <v>160988400</v>
+        <v>217307400</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B125" t="n">
-        <v>182.5527246843909</v>
+        <v>184.6379731916982</v>
       </c>
       <c r="C125" t="n">
-        <v>188.4492501487561</v>
+        <v>184.9771941770484</v>
       </c>
       <c r="D125" t="n">
-        <v>180.9962848148914</v>
+        <v>181.2656763194747</v>
       </c>
       <c r="E125" t="n">
-        <v>182.8021545410156</v>
+        <v>181.5151062011719</v>
       </c>
       <c r="F125" t="n">
-        <v>217307400</v>
+        <v>182497800</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B126" t="n">
-        <v>184.6379731916982</v>
+        <v>182.0638447517288</v>
       </c>
       <c r="C126" t="n">
-        <v>184.9771941770484</v>
+        <v>182.9618014097589</v>
       </c>
       <c r="D126" t="n">
-        <v>181.2656763194747</v>
+        <v>179.9187539793071</v>
       </c>
       <c r="E126" t="n">
-        <v>181.5151062011719</v>
+        <v>179.9885864257812</v>
       </c>
       <c r="F126" t="n">
-        <v>182497800</v>
+        <v>156683100</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B127" t="n">
-        <v>182.0638447517288</v>
+        <v>177.6040222894031</v>
       </c>
       <c r="C127" t="n">
-        <v>182.9618014097589</v>
+        <v>179.5695306962835</v>
       </c>
       <c r="D127" t="n">
-        <v>179.9187539793071</v>
+        <v>175.3890840362079</v>
       </c>
       <c r="E127" t="n">
-        <v>179.9885864257812</v>
+        <v>178.1527709960938</v>
       </c>
       <c r="F127" t="n">
-        <v>156683100</v>
+        <v>170968500</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B128" t="n">
-        <v>177.6040222894031</v>
+        <v>177.5940686691464</v>
       </c>
       <c r="C128" t="n">
-        <v>179.5695306962835</v>
+        <v>177.853470255105</v>
       </c>
       <c r="D128" t="n">
-        <v>175.3890840362079</v>
+        <v>171.3283915093003</v>
       </c>
       <c r="E128" t="n">
-        <v>178.1527709960938</v>
+        <v>172.30615234375</v>
       </c>
       <c r="F128" t="n">
-        <v>170968500</v>
+        <v>241323500</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B129" t="n">
-        <v>177.5940686691464</v>
+        <v>176.8557415306554</v>
       </c>
       <c r="C129" t="n">
-        <v>177.853470255105</v>
+        <v>177.9632107122345</v>
       </c>
       <c r="D129" t="n">
-        <v>171.3283915093003</v>
+        <v>174.3614429436745</v>
       </c>
       <c r="E129" t="n">
-        <v>172.30615234375</v>
+        <v>175.2394409179688</v>
       </c>
       <c r="F129" t="n">
-        <v>241323500</v>
+        <v>182836300</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B130" t="n">
-        <v>176.8557415306554</v>
+        <v>174.4312942297872</v>
       </c>
       <c r="C130" t="n">
-        <v>177.9632107122345</v>
+        <v>175.8181236639554</v>
       </c>
       <c r="D130" t="n">
-        <v>174.3614429436745</v>
+        <v>173.5832266030264</v>
       </c>
       <c r="E130" t="n">
-        <v>175.2394409179688</v>
+        <v>174.8004455566406</v>
       </c>
       <c r="F130" t="n">
-        <v>182836300</v>
+        <v>147667800</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B131" t="n">
-        <v>174.4312942297872</v>
+        <v>176.6961233561449</v>
       </c>
       <c r="C131" t="n">
-        <v>175.8181236639554</v>
+        <v>180.8067226806179</v>
       </c>
       <c r="D131" t="n">
-        <v>173.5832266030264</v>
+        <v>176.4466934898736</v>
       </c>
       <c r="E131" t="n">
-        <v>174.8004455566406</v>
+        <v>178.2725067138672</v>
       </c>
       <c r="F131" t="n">
-        <v>147667800</v>
+        <v>162602100</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B132" t="n">
-        <v>176.6961233561449</v>
+        <v>175.6684741654964</v>
       </c>
       <c r="C132" t="n">
-        <v>180.8067226806179</v>
+        <v>176.1074579435819</v>
       </c>
       <c r="D132" t="n">
-        <v>176.4466934898736</v>
+        <v>170.7497092682189</v>
       </c>
       <c r="E132" t="n">
-        <v>178.2725067138672</v>
+        <v>170.8494873046875</v>
       </c>
       <c r="F132" t="n">
-        <v>162602100</v>
+        <v>186152200</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B133" t="n">
-        <v>175.6684741654964</v>
+        <v>169.6123099949711</v>
       </c>
       <c r="C133" t="n">
-        <v>176.1074579435819</v>
+        <v>170.5800990993323</v>
       </c>
       <c r="D133" t="n">
-        <v>170.7497092682189</v>
+        <v>166.629123297364</v>
       </c>
       <c r="E133" t="n">
-        <v>170.8494873046875</v>
+        <v>167.1379699707031</v>
       </c>
       <c r="F133" t="n">
-        <v>186152200</v>
+        <v>196212700</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B134" t="n">
-        <v>169.6123099949711</v>
+        <v>168.3950875250076</v>
       </c>
       <c r="C134" t="n">
-        <v>170.5800990993323</v>
+        <v>169.0635577295173</v>
       </c>
       <c r="D134" t="n">
-        <v>166.629123297364</v>
+        <v>163.8953782868944</v>
       </c>
       <c r="E134" t="n">
-        <v>167.1379699707031</v>
+        <v>164.7933197021484</v>
       </c>
       <c r="F134" t="n">
-        <v>196212700</v>
+        <v>185627000</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B135" t="n">
-        <v>168.3950875250076</v>
+        <v>166.589210422399</v>
       </c>
       <c r="C135" t="n">
-        <v>169.0635577295173</v>
+        <v>174.2217577880002</v>
       </c>
       <c r="D135" t="n">
-        <v>163.8953782868944</v>
+        <v>166.5792387089764</v>
       </c>
       <c r="E135" t="n">
-        <v>164.7933197021484</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="F135" t="n">
-        <v>185627000</v>
+        <v>226181300</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B136" t="n">
-        <v>166.589210422399</v>
+        <v>175.5986119754623</v>
       </c>
       <c r="C136" t="n">
-        <v>174.2217577880002</v>
+        <v>176.9654826629128</v>
       </c>
       <c r="D136" t="n">
-        <v>166.5792387089764</v>
+        <v>174.351462742682</v>
       </c>
       <c r="E136" t="n">
-        <v>174.0022583007812</v>
+        <v>175.3491821289062</v>
       </c>
       <c r="F136" t="n">
-        <v>226181300</v>
+        <v>168132000</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B137" t="n">
-        <v>175.5986119754623</v>
+        <v>171.787333172162</v>
       </c>
       <c r="C137" t="n">
-        <v>176.9654826629128</v>
+        <v>177.0852364118599</v>
       </c>
       <c r="D137" t="n">
-        <v>174.351462742682</v>
+        <v>170.9791828272563</v>
       </c>
       <c r="E137" t="n">
-        <v>175.3491821289062</v>
+        <v>176.9854583740234</v>
       </c>
       <c r="F137" t="n">
-        <v>168132000</v>
+        <v>143143200</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B138" t="n">
-        <v>171.787333172162</v>
+        <v>176.7559774774269</v>
       </c>
       <c r="C138" t="n">
-        <v>177.0852364118599</v>
+        <v>177.3845303646084</v>
       </c>
       <c r="D138" t="n">
-        <v>170.9791828272563</v>
+        <v>175.3591611441553</v>
       </c>
       <c r="E138" t="n">
-        <v>176.9854583740234</v>
+        <v>177.2348785400391</v>
       </c>
       <c r="F138" t="n">
-        <v>143143200</v>
+        <v>107564300</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B139" t="n">
-        <v>176.7559774774269</v>
+        <v>175.3292270516068</v>
       </c>
       <c r="C139" t="n">
-        <v>177.3845303646084</v>
+        <v>177.8235255680002</v>
       </c>
       <c r="D139" t="n">
-        <v>175.3591611441553</v>
+        <v>173.2639557965079</v>
       </c>
       <c r="E139" t="n">
-        <v>177.2348785400391</v>
+        <v>177.6938323974609</v>
       </c>
       <c r="F139" t="n">
-        <v>107564300</v>
+        <v>132534900</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B140" t="n">
-        <v>175.3292270516068</v>
+        <v>184.079243714486</v>
       </c>
       <c r="C140" t="n">
-        <v>177.8235255680002</v>
+        <v>184.837505037226</v>
       </c>
       <c r="D140" t="n">
-        <v>173.2639557965079</v>
+        <v>179.8888249511496</v>
       </c>
       <c r="E140" t="n">
-        <v>177.6938323974609</v>
+        <v>181.6647644042969</v>
       </c>
       <c r="F140" t="n">
-        <v>132534900</v>
+        <v>147732700</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B141" t="n">
-        <v>184.079243714486</v>
+        <v>181.4253138719204</v>
       </c>
       <c r="C141" t="n">
-        <v>184.837505037226</v>
+        <v>183.6602110774668</v>
       </c>
       <c r="D141" t="n">
-        <v>179.8888249511496</v>
+        <v>180.2080948395415</v>
       </c>
       <c r="E141" t="n">
-        <v>181.6647644042969</v>
+        <v>183.4906005859375</v>
       </c>
       <c r="F141" t="n">
-        <v>147732700</v>
+        <v>116428500</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B142" t="n">
-        <v>181.4253138719204</v>
+        <v>183.8896736698189</v>
       </c>
       <c r="C142" t="n">
-        <v>183.6602110774668</v>
+        <v>189.5666999081706</v>
       </c>
       <c r="D142" t="n">
-        <v>180.2080948395415</v>
+        <v>183.8797019557237</v>
       </c>
       <c r="E142" t="n">
-        <v>183.4906005859375</v>
+        <v>188.1998291015625</v>
       </c>
       <c r="F142" t="n">
-        <v>116428500</v>
+        <v>160459500</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B143" t="n">
-        <v>183.8896736698189</v>
+        <v>185.605746824658</v>
       </c>
       <c r="C143" t="n">
-        <v>189.5666999081706</v>
+        <v>189.2274732756209</v>
       </c>
       <c r="D143" t="n">
-        <v>183.8797019557237</v>
+        <v>185.3164148846483</v>
       </c>
       <c r="E143" t="n">
-        <v>188.1998291015625</v>
+        <v>188.8782653808594</v>
       </c>
       <c r="F143" t="n">
-        <v>160459500</v>
+        <v>133648200</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B144" t="n">
-        <v>185.605746824658</v>
+        <v>190.4047764107204</v>
       </c>
       <c r="C144" t="n">
-        <v>189.2274732756209</v>
+        <v>196.0618438720703</v>
       </c>
       <c r="D144" t="n">
-        <v>185.3164148846483</v>
+        <v>190.3349439656124</v>
       </c>
       <c r="E144" t="n">
-        <v>188.8782653808594</v>
+        <v>196.0618438720703</v>
       </c>
       <c r="F144" t="n">
-        <v>133648200</v>
+        <v>161307000</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B145" t="n">
-        <v>190.4047764107204</v>
+        <v>196.0917851116163</v>
       </c>
       <c r="C145" t="n">
-        <v>196.0618438720703</v>
+        <v>199.9429830157183</v>
       </c>
       <c r="D145" t="n">
-        <v>190.3349439656124</v>
+        <v>195.2936216855987</v>
       </c>
       <c r="E145" t="n">
-        <v>196.0618438720703</v>
+        <v>198.4164733886719</v>
       </c>
       <c r="F145" t="n">
-        <v>161307000</v>
+        <v>185338400</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B146" t="n">
-        <v>196.0917851116163</v>
+        <v>196.9797440092329</v>
       </c>
       <c r="C146" t="n">
-        <v>199.9429830157183</v>
+        <v>199.3942384790618</v>
       </c>
       <c r="D146" t="n">
-        <v>195.2936216855987</v>
+        <v>195.3634433694217</v>
       </c>
       <c r="E146" t="n">
-        <v>198.4164733886719</v>
+        <v>197.8976593017578</v>
       </c>
       <c r="F146" t="n">
-        <v>185338400</v>
+        <v>134012900</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B147" t="n">
-        <v>196.9797440092329</v>
+        <v>199.444107632571</v>
       </c>
       <c r="C147" t="n">
-        <v>199.3942384790618</v>
+        <v>201.2400056483541</v>
       </c>
       <c r="D147" t="n">
-        <v>195.3634433694217</v>
+        <v>198.8155547450397</v>
       </c>
       <c r="E147" t="n">
-        <v>197.8976593017578</v>
+        <v>201.2200469970703</v>
       </c>
       <c r="F147" t="n">
-        <v>134012900</v>
+        <v>160324400</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B148" t="n">
-        <v>199.444107632571</v>
+        <v>199.5239239232554</v>
       </c>
       <c r="C148" t="n">
-        <v>201.2400056483541</v>
+        <v>201.7089318732817</v>
       </c>
       <c r="D148" t="n">
-        <v>198.8155547450397</v>
+        <v>197.3888049886708</v>
       </c>
       <c r="E148" t="n">
-        <v>201.2200469970703</v>
+        <v>201.5991821289062</v>
       </c>
       <c r="F148" t="n">
-        <v>160324400</v>
+        <v>119381400</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B149" t="n">
-        <v>199.5239239232554</v>
+        <v>201.6690479582887</v>
       </c>
       <c r="C149" t="n">
-        <v>201.7089318732817</v>
+        <v>202.2876291783034</v>
       </c>
       <c r="D149" t="n">
-        <v>197.3888049886708</v>
+        <v>198.5461810430697</v>
       </c>
       <c r="E149" t="n">
-        <v>201.5991821289062</v>
+        <v>199.4241790771484</v>
       </c>
       <c r="F149" t="n">
-        <v>119381400</v>
+        <v>107945300</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B150" t="n">
-        <v>201.6690479582887</v>
+        <v>200.5316418294082</v>
       </c>
       <c r="C150" t="n">
-        <v>202.2876291783034</v>
+        <v>202.0381927490234</v>
       </c>
       <c r="D150" t="n">
-        <v>198.5461810430697</v>
+        <v>198.546174602744</v>
       </c>
       <c r="E150" t="n">
-        <v>199.4241790771484</v>
+        <v>202.0381927490234</v>
       </c>
       <c r="F150" t="n">
-        <v>107945300</v>
+        <v>107501000</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B151" t="n">
-        <v>200.5316418294082</v>
+        <v>201.9982837593082</v>
       </c>
       <c r="C151" t="n">
-        <v>202.0381927490234</v>
+        <v>203.3651545152774</v>
       </c>
       <c r="D151" t="n">
-        <v>198.546174602744</v>
+        <v>196.7702284327844</v>
       </c>
       <c r="E151" t="n">
-        <v>202.0381927490234</v>
+        <v>199.1847076416016</v>
       </c>
       <c r="F151" t="n">
-        <v>107501000</v>
+        <v>113561800</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B152" t="n">
-        <v>201.9982837593082</v>
+        <v>199.5039827094276</v>
       </c>
       <c r="C152" t="n">
-        <v>203.3651545152774</v>
+        <v>210.468909435165</v>
       </c>
       <c r="D152" t="n">
-        <v>196.7702284327844</v>
+        <v>199.3543156614425</v>
       </c>
       <c r="E152" t="n">
-        <v>199.1847076416016</v>
+        <v>207.7950286865234</v>
       </c>
       <c r="F152" t="n">
-        <v>113561800</v>
+        <v>214134400</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B153" t="n">
-        <v>199.5039827094276</v>
+        <v>209.1718784416434</v>
       </c>
       <c r="C153" t="n">
-        <v>210.468909435165</v>
+        <v>216.335512072091</v>
       </c>
       <c r="D153" t="n">
-        <v>199.3543156614425</v>
+        <v>206.9070662315077</v>
       </c>
       <c r="E153" t="n">
-        <v>207.7950286865234</v>
+        <v>216.1160125732422</v>
       </c>
       <c r="F153" t="n">
-        <v>214134400</v>
+        <v>187172400</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B154" t="n">
-        <v>209.1718784416434</v>
+        <v>209.0122528840405</v>
       </c>
       <c r="C154" t="n">
-        <v>216.335512072091</v>
+        <v>214.2402930542568</v>
       </c>
       <c r="D154" t="n">
-        <v>206.9070662315077</v>
+        <v>207.7251862691963</v>
       </c>
       <c r="E154" t="n">
-        <v>216.1160125732422</v>
+        <v>212.6838531494141</v>
       </c>
       <c r="F154" t="n">
-        <v>187172400</v>
+        <v>180275400</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B155" t="n">
-        <v>209.0122528840405</v>
+        <v>212.2149257168926</v>
       </c>
       <c r="C155" t="n">
-        <v>214.2402930542568</v>
+        <v>212.2348843687743</v>
       </c>
       <c r="D155" t="n">
-        <v>207.7251862691963</v>
+        <v>207.1066069625242</v>
       </c>
       <c r="E155" t="n">
-        <v>212.6838531494141</v>
+        <v>208.7727966308594</v>
       </c>
       <c r="F155" t="n">
-        <v>180275400</v>
+        <v>123711800</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B156" t="n">
-        <v>212.2149257168926</v>
+        <v>209.4512265433391</v>
       </c>
       <c r="C156" t="n">
-        <v>212.2348843687743</v>
+        <v>209.8203930740204</v>
       </c>
       <c r="D156" t="n">
-        <v>207.1066069625242</v>
+        <v>198.2468419328838</v>
       </c>
       <c r="E156" t="n">
-        <v>208.7727966308594</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="F156" t="n">
-        <v>123711800</v>
+        <v>225239200</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B157" t="n">
-        <v>209.4512265433391</v>
+        <v>200.8209846036705</v>
       </c>
       <c r="C157" t="n">
-        <v>209.8203930740204</v>
+        <v>202.5370634031337</v>
       </c>
       <c r="D157" t="n">
-        <v>198.2468419328838</v>
+        <v>196.6704677294345</v>
       </c>
       <c r="E157" t="n">
-        <v>199.1148681640625</v>
+        <v>197.9974365234375</v>
       </c>
       <c r="F157" t="n">
-        <v>225239200</v>
+        <v>128647000</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B158" t="n">
-        <v>200.8209846036705</v>
+        <v>199.0450218084295</v>
       </c>
       <c r="C158" t="n">
-        <v>202.5370634031337</v>
+        <v>201.2699318245734</v>
       </c>
       <c r="D158" t="n">
-        <v>196.6704677294345</v>
+        <v>194.2958829090753</v>
       </c>
       <c r="E158" t="n">
-        <v>197.9974365234375</v>
+        <v>198.02734375</v>
       </c>
       <c r="F158" t="n">
-        <v>128647000</v>
+        <v>125368100</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B159" t="n">
-        <v>199.0450218084295</v>
+        <v>198.8454820247872</v>
       </c>
       <c r="C159" t="n">
-        <v>201.2699318245734</v>
+        <v>199.7833407086998</v>
       </c>
       <c r="D159" t="n">
-        <v>194.2958829090753</v>
+        <v>195.5829352820671</v>
       </c>
       <c r="E159" t="n">
-        <v>198.02734375</v>
+        <v>196.0518646240234</v>
       </c>
       <c r="F159" t="n">
-        <v>125368100</v>
+        <v>113406600</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B160" t="n">
-        <v>198.8454820247872</v>
+        <v>199.4341385249406</v>
       </c>
       <c r="C160" t="n">
-        <v>199.7833407086998</v>
+        <v>207.7950323152332</v>
       </c>
       <c r="D160" t="n">
-        <v>195.5829352820671</v>
+        <v>198.1570588579161</v>
       </c>
       <c r="E160" t="n">
-        <v>196.0518646240234</v>
+        <v>207.3560333251953</v>
       </c>
       <c r="F160" t="n">
-        <v>113406600</v>
+        <v>188362800</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B161" t="n">
-        <v>199.4341385249406</v>
+        <v>207.8648724722903</v>
       </c>
       <c r="C161" t="n">
-        <v>207.7950323152332</v>
+        <v>213.7115092245668</v>
       </c>
       <c r="D161" t="n">
-        <v>198.1570588579161</v>
+        <v>206.0290722858257</v>
       </c>
       <c r="E161" t="n">
-        <v>207.3560333251953</v>
+        <v>211.0176696777344</v>
       </c>
       <c r="F161" t="n">
-        <v>188362800</v>
+        <v>168307900</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B162" t="n">
-        <v>207.8648724722903</v>
+        <v>212.5441790763045</v>
       </c>
       <c r="C162" t="n">
-        <v>213.7115092245668</v>
+        <v>217.3033052467507</v>
       </c>
       <c r="D162" t="n">
-        <v>206.0290722858257</v>
+        <v>212.4044989584125</v>
       </c>
       <c r="E162" t="n">
-        <v>211.0176696777344</v>
+        <v>214.709228515625</v>
       </c>
       <c r="F162" t="n">
-        <v>168307900</v>
+        <v>136421400</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B163" t="n">
-        <v>212.5441790763045</v>
+        <v>213.5518657378577</v>
       </c>
       <c r="C163" t="n">
-        <v>217.3033052467507</v>
+        <v>221.7930381906342</v>
       </c>
       <c r="D163" t="n">
-        <v>212.4044989584125</v>
+        <v>213.402213909002</v>
       </c>
       <c r="E163" t="n">
-        <v>214.709228515625</v>
+        <v>218.9395599365234</v>
       </c>
       <c r="F163" t="n">
-        <v>136421400</v>
+        <v>160685800</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B164" t="n">
-        <v>213.5518657378577</v>
+        <v>218.0515943496244</v>
       </c>
       <c r="C164" t="n">
-        <v>221.7930381906342</v>
+        <v>223.239732575863</v>
       </c>
       <c r="D164" t="n">
-        <v>213.402213909002</v>
+        <v>214.4298677829735</v>
       </c>
       <c r="E164" t="n">
-        <v>218.9395599365234</v>
+        <v>220.2765045166016</v>
       </c>
       <c r="F164" t="n">
-        <v>160685800</v>
+        <v>159176600</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B165" t="n">
-        <v>218.0515943496244</v>
+        <v>224.4170305354026</v>
       </c>
       <c r="C165" t="n">
-        <v>223.239732575863</v>
+        <v>227.3203978139454</v>
       </c>
       <c r="D165" t="n">
-        <v>214.4298677829735</v>
+        <v>221.0647077692387</v>
       </c>
       <c r="E165" t="n">
-        <v>220.2765045166016</v>
+        <v>225.3149871826172</v>
       </c>
       <c r="F165" t="n">
-        <v>159176600</v>
+        <v>150405400</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B166" t="n">
-        <v>224.4170305354026</v>
+        <v>229.3258255277811</v>
       </c>
       <c r="C166" t="n">
-        <v>227.3203978139454</v>
+        <v>236.0005559723521</v>
       </c>
       <c r="D166" t="n">
-        <v>221.0647077692387</v>
+        <v>228.7770767762568</v>
       </c>
       <c r="E166" t="n">
-        <v>225.3149871826172</v>
+        <v>235.202392578125</v>
       </c>
       <c r="F166" t="n">
-        <v>150405400</v>
+        <v>180782900</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B167" t="n">
-        <v>229.3258255277811</v>
+        <v>229.2360138852663</v>
       </c>
       <c r="C167" t="n">
-        <v>236.0005559723521</v>
+        <v>230.9720511978</v>
       </c>
       <c r="D167" t="n">
-        <v>228.7770767762568</v>
+        <v>223.7286135177626</v>
       </c>
       <c r="E167" t="n">
-        <v>235.202392578125</v>
+        <v>224.80615234375</v>
       </c>
       <c r="F167" t="n">
-        <v>180782900</v>
+        <v>180977600</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B168" t="n">
-        <v>229.2360138852663</v>
+        <v>229.345773483712</v>
       </c>
       <c r="C168" t="n">
-        <v>230.9720511978</v>
+        <v>229.4754818886306</v>
       </c>
       <c r="D168" t="n">
-        <v>223.7286135177626</v>
+        <v>217.8719993892805</v>
       </c>
       <c r="E168" t="n">
-        <v>224.80615234375</v>
+        <v>221.8130035400391</v>
       </c>
       <c r="F168" t="n">
-        <v>180977600</v>
+        <v>146280900</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B169" t="n">
-        <v>229.345773483712</v>
+        <v>219.1191400841904</v>
       </c>
       <c r="C169" t="n">
-        <v>229.4754818886306</v>
+        <v>223.9680572056967</v>
       </c>
       <c r="D169" t="n">
-        <v>217.8719993892805</v>
+        <v>217.4130483552105</v>
       </c>
       <c r="E169" t="n">
-        <v>221.8130035400391</v>
+        <v>220.1068878173828</v>
       </c>
       <c r="F169" t="n">
-        <v>146280900</v>
+        <v>140948200</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B170" t="n">
-        <v>219.1191400841904</v>
+        <v>222.6710257508039</v>
       </c>
       <c r="C170" t="n">
-        <v>223.9680572056967</v>
+        <v>225.6143103895453</v>
       </c>
       <c r="D170" t="n">
-        <v>217.4130483552105</v>
+        <v>219.9971448577806</v>
       </c>
       <c r="E170" t="n">
-        <v>220.1068878173828</v>
+        <v>222.9603729248047</v>
       </c>
       <c r="F170" t="n">
-        <v>140948200</v>
+        <v>184201600</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B171" t="n">
-        <v>222.6710257508039</v>
+        <v>221.7830583738447</v>
       </c>
       <c r="C171" t="n">
-        <v>225.6143103895453</v>
+        <v>226.8814055684356</v>
       </c>
       <c r="D171" t="n">
-        <v>219.9971448577806</v>
+        <v>217.4330007955402</v>
       </c>
       <c r="E171" t="n">
-        <v>222.9603729248047</v>
+        <v>219.0093994140625</v>
       </c>
       <c r="F171" t="n">
-        <v>184201600</v>
+        <v>203381800</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B172" t="n">
-        <v>221.7830583738447</v>
+        <v>220.3962175709585</v>
       </c>
       <c r="C172" t="n">
-        <v>226.8814055684356</v>
+        <v>220.5059673180016</v>
       </c>
       <c r="D172" t="n">
-        <v>217.4330007955402</v>
+        <v>214.3101381389001</v>
       </c>
       <c r="E172" t="n">
-        <v>219.0093994140625</v>
+        <v>214.8389282226562</v>
       </c>
       <c r="F172" t="n">
-        <v>203381800</v>
+        <v>169275700</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B173" t="n">
-        <v>220.3962175709585</v>
+        <v>216.0461718127993</v>
       </c>
       <c r="C173" t="n">
-        <v>220.5059673180016</v>
+        <v>217.6824311685512</v>
       </c>
       <c r="D173" t="n">
-        <v>214.3101381389001</v>
+        <v>211.5165320236786</v>
       </c>
       <c r="E173" t="n">
-        <v>214.8389282226562</v>
+        <v>214.3700103759766</v>
       </c>
       <c r="F173" t="n">
-        <v>169275700</v>
+        <v>187202600</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B174" t="n">
-        <v>216.0461718127993</v>
+        <v>213.6316806617713</v>
       </c>
       <c r="C174" t="n">
-        <v>217.6824311685512</v>
+        <v>213.6616110269177</v>
       </c>
       <c r="D174" t="n">
-        <v>211.5165320236786</v>
+        <v>208.3038625298546</v>
       </c>
       <c r="E174" t="n">
-        <v>214.3700103759766</v>
+        <v>212.1151580810547</v>
       </c>
       <c r="F174" t="n">
-        <v>187202600</v>
+        <v>167601200</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B175" t="n">
-        <v>213.6316806617713</v>
+        <v>210.7981702457166</v>
       </c>
       <c r="C175" t="n">
-        <v>213.6616110269177</v>
+        <v>215.0285063161196</v>
       </c>
       <c r="D175" t="n">
-        <v>208.3038625298546</v>
+        <v>210.738309512832</v>
       </c>
       <c r="E175" t="n">
-        <v>212.1151580810547</v>
+        <v>213.7613983154297</v>
       </c>
       <c r="F175" t="n">
-        <v>167601200</v>
+        <v>143996000</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B176" t="n">
-        <v>210.7981702457166</v>
+        <v>214.0906505321041</v>
       </c>
       <c r="C176" t="n">
-        <v>215.0285063161196</v>
+        <v>217.3631692496548</v>
       </c>
       <c r="D176" t="n">
-        <v>210.738309512832</v>
+        <v>210.6485213277038</v>
       </c>
       <c r="E176" t="n">
-        <v>213.7613983154297</v>
+        <v>210.6584930419922</v>
       </c>
       <c r="F176" t="n">
-        <v>143996000</v>
+        <v>289410600</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B177" t="n">
-        <v>214.0906505321041</v>
+        <v>215.2380189209027</v>
       </c>
       <c r="C177" t="n">
-        <v>217.3631692496548</v>
+        <v>224.3571743491113</v>
       </c>
       <c r="D177" t="n">
-        <v>210.6485213277038</v>
+        <v>215.2080885544549</v>
       </c>
       <c r="E177" t="n">
-        <v>210.6584930419922</v>
+        <v>223.8483428955078</v>
       </c>
       <c r="F177" t="n">
-        <v>289410600</v>
+        <v>212850700</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B178" t="n">
-        <v>215.2380189209027</v>
+        <v>226.6618858382332</v>
       </c>
       <c r="C178" t="n">
-        <v>224.3571743491113</v>
+        <v>231.7502608645459</v>
       </c>
       <c r="D178" t="n">
-        <v>215.2080885544549</v>
+        <v>220.8451951370975</v>
       </c>
       <c r="E178" t="n">
-        <v>223.8483428955078</v>
+        <v>222.3118438720703</v>
       </c>
       <c r="F178" t="n">
-        <v>212850700</v>
+        <v>193362900</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B179" t="n">
-        <v>226.6618858382332</v>
+        <v>221.2143597561905</v>
       </c>
       <c r="C179" t="n">
-        <v>231.7502608645459</v>
+        <v>222.3118572511273</v>
       </c>
       <c r="D179" t="n">
-        <v>220.8451951370975</v>
+        <v>214.0207957553572</v>
       </c>
       <c r="E179" t="n">
-        <v>222.3118438720703</v>
+        <v>214.26025390625</v>
       </c>
       <c r="F179" t="n">
-        <v>193362900</v>
+        <v>160907000</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,25 +5097,25 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B180" t="n">
-        <v>221.2143597561905</v>
+        <v>213.6709127939037</v>
       </c>
       <c r="C180" t="n">
-        <v>222.3118572511273</v>
+        <v>221.3523199881091</v>
       </c>
       <c r="D180" t="n">
-        <v>214.0207957553572</v>
+        <v>210.73419644349</v>
       </c>
       <c r="E180" t="n">
-        <v>214.26025390625</v>
+        <v>218.4156036376953</v>
       </c>
       <c r="F180" t="n">
-        <v>160907000</v>
+        <v>169022200</v>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5123,25 +5123,25 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B181" t="n">
-        <v>213.6709127939037</v>
+        <v>214.2902104723603</v>
       </c>
       <c r="C181" t="n">
-        <v>221.3523199881091</v>
+        <v>214.6298267834636</v>
       </c>
       <c r="D181" t="n">
-        <v>210.73419644349</v>
+        <v>204.101614447126</v>
       </c>
       <c r="E181" t="n">
-        <v>218.4156036376953</v>
+        <v>204.8707580566406</v>
       </c>
       <c r="F181" t="n">
-        <v>169022200</v>
+        <v>219655500</v>
       </c>
       <c r="G181" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B182" t="n">
-        <v>214.2902104723603</v>
+        <v>209.9450713288228</v>
       </c>
       <c r="C182" t="n">
-        <v>214.6298267834636</v>
+        <v>210.2347557268212</v>
       </c>
       <c r="D182" t="n">
-        <v>204.101614447126</v>
+        <v>205.7697506938822</v>
       </c>
       <c r="E182" t="n">
-        <v>204.8707580566406</v>
+        <v>208.4067993164062</v>
       </c>
       <c r="F182" t="n">
-        <v>219655500</v>
+        <v>138372800</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B183" t="n">
-        <v>209.9450713288228</v>
+        <v>210.3845825512031</v>
       </c>
       <c r="C183" t="n">
-        <v>210.2347557268212</v>
+        <v>211.1637095162451</v>
       </c>
       <c r="D183" t="n">
-        <v>205.7697506938822</v>
+        <v>199.1171915656509</v>
       </c>
       <c r="E183" t="n">
-        <v>208.4067993164062</v>
+        <v>207.9573059082031</v>
       </c>
       <c r="F183" t="n">
-        <v>138372800</v>
+        <v>180962500</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B184" t="n">
-        <v>210.3845825512031</v>
+        <v>204.2014963256503</v>
       </c>
       <c r="C184" t="n">
-        <v>211.1637095162451</v>
+        <v>206.9883864105018</v>
       </c>
       <c r="D184" t="n">
-        <v>199.1171915656509</v>
+        <v>199.696542748819</v>
       </c>
       <c r="E184" t="n">
-        <v>207.9573059082031</v>
+        <v>200.1959838867188</v>
       </c>
       <c r="F184" t="n">
-        <v>180962500</v>
+        <v>161746600</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B185" t="n">
-        <v>204.2014963256503</v>
+        <v>201.2647947500858</v>
       </c>
       <c r="C185" t="n">
-        <v>206.9883864105018</v>
+        <v>205.4301320010667</v>
       </c>
       <c r="D185" t="n">
-        <v>199.696542748819</v>
+        <v>199.3169621236104</v>
       </c>
       <c r="E185" t="n">
-        <v>200.1959838867188</v>
+        <v>204.6410064697266</v>
       </c>
       <c r="F185" t="n">
-        <v>161746600</v>
+        <v>158643200</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B186" t="n">
-        <v>201.2647947500858</v>
+        <v>204.6310298517525</v>
       </c>
       <c r="C186" t="n">
-        <v>205.4301320010667</v>
+        <v>206.8385664547524</v>
       </c>
       <c r="D186" t="n">
-        <v>199.3169621236104</v>
+        <v>203.2126188059985</v>
       </c>
       <c r="E186" t="n">
-        <v>204.6410064697266</v>
+        <v>204.9606628417969</v>
       </c>
       <c r="F186" t="n">
-        <v>158643200</v>
+        <v>112001800</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B187" t="n">
-        <v>204.6310298517525</v>
+        <v>208.6864864049894</v>
       </c>
       <c r="C187" t="n">
-        <v>206.8385664547524</v>
+        <v>212.4722588232193</v>
       </c>
       <c r="D187" t="n">
-        <v>203.2126188059985</v>
+        <v>208.1071328472061</v>
       </c>
       <c r="E187" t="n">
-        <v>204.9606628417969</v>
+        <v>212.2125396728516</v>
       </c>
       <c r="F187" t="n">
-        <v>112001800</v>
+        <v>149936700</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B188" t="n">
-        <v>208.6864864049894</v>
+        <v>210.9439520928381</v>
       </c>
       <c r="C188" t="n">
-        <v>212.4722588232193</v>
+        <v>211.2536184019877</v>
       </c>
       <c r="D188" t="n">
-        <v>208.1071328472061</v>
+        <v>207.0583006421773</v>
       </c>
       <c r="E188" t="n">
-        <v>212.2125396728516</v>
+        <v>207.1781768798828</v>
       </c>
       <c r="F188" t="n">
-        <v>149936700</v>
+        <v>125694100</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B189" t="n">
-        <v>210.9439520928381</v>
+        <v>208.2969174543329</v>
       </c>
       <c r="C189" t="n">
-        <v>211.2536184019877</v>
+        <v>208.9761653200819</v>
       </c>
       <c r="D189" t="n">
-        <v>207.0583006421773</v>
+        <v>202.8530121596522</v>
       </c>
       <c r="E189" t="n">
-        <v>207.1781768798828</v>
+        <v>204.4212493896484</v>
       </c>
       <c r="F189" t="n">
-        <v>125694100</v>
+        <v>128363500</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B190" t="n">
-        <v>208.2969174543329</v>
+        <v>207.0982684229139</v>
       </c>
       <c r="C190" t="n">
-        <v>208.9761653200819</v>
+        <v>211.1537281092123</v>
       </c>
       <c r="D190" t="n">
-        <v>202.8530121596522</v>
+        <v>206.2691942875683</v>
       </c>
       <c r="E190" t="n">
-        <v>204.4212493896484</v>
+        <v>210.4545135498047</v>
       </c>
       <c r="F190" t="n">
-        <v>128363500</v>
+        <v>241272000</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B191" t="n">
-        <v>207.0982684229139</v>
+        <v>211.2036686200953</v>
       </c>
       <c r="C191" t="n">
-        <v>211.1537281092123</v>
+        <v>213.7508214450341</v>
       </c>
       <c r="D191" t="n">
-        <v>206.2691942875683</v>
+        <v>207.4878253737282</v>
       </c>
       <c r="E191" t="n">
-        <v>210.4545135498047</v>
+        <v>208.4167785644531</v>
       </c>
       <c r="F191" t="n">
-        <v>241272000</v>
+        <v>122041400</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B192" t="n">
-        <v>211.2036686200953</v>
+        <v>201.9440304014853</v>
       </c>
       <c r="C192" t="n">
-        <v>213.7508214450341</v>
+        <v>203.5422481594977</v>
       </c>
       <c r="D192" t="n">
-        <v>207.4878253737282</v>
+        <v>199.77645766483</v>
       </c>
       <c r="E192" t="n">
-        <v>208.4167785644531</v>
+        <v>199.81640625</v>
       </c>
       <c r="F192" t="n">
-        <v>122041400</v>
+        <v>153496200</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B193" t="n">
-        <v>201.9440304014853</v>
+        <v>199.8963159019567</v>
       </c>
       <c r="C193" t="n">
-        <v>203.5422481594977</v>
+        <v>201.4445864758279</v>
       </c>
       <c r="D193" t="n">
-        <v>199.77645766483</v>
+        <v>196.360279356477</v>
       </c>
       <c r="E193" t="n">
-        <v>199.81640625</v>
+        <v>198.7775726318359</v>
       </c>
       <c r="F193" t="n">
-        <v>153496200</v>
+        <v>151810700</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B194" t="n">
-        <v>199.8963159019567</v>
+        <v>199.8563704571445</v>
       </c>
       <c r="C194" t="n">
-        <v>201.4445864758279</v>
+        <v>200.5755669254449</v>
       </c>
       <c r="D194" t="n">
-        <v>196.360279356477</v>
+        <v>191.9152592982058</v>
       </c>
       <c r="E194" t="n">
-        <v>198.7775726318359</v>
+        <v>195.5212249755859</v>
       </c>
       <c r="F194" t="n">
-        <v>151810700</v>
+        <v>149550000</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B195" t="n">
-        <v>199.8563704571445</v>
+        <v>192.9041409641119</v>
       </c>
       <c r="C195" t="n">
-        <v>200.5755669254449</v>
+        <v>195.331432829306</v>
       </c>
       <c r="D195" t="n">
-        <v>191.9152592982058</v>
+        <v>191.0062707295152</v>
       </c>
       <c r="E195" t="n">
-        <v>195.5212249755859</v>
+        <v>192.3148040771484</v>
       </c>
       <c r="F195" t="n">
-        <v>149550000</v>
+        <v>179304100</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B196" t="n">
-        <v>192.9041409641119</v>
+        <v>193.6333319429392</v>
       </c>
       <c r="C196" t="n">
-        <v>195.331432829306</v>
+        <v>195.9607141929515</v>
       </c>
       <c r="D196" t="n">
-        <v>191.0062707295152</v>
+        <v>189.5878557469149</v>
       </c>
       <c r="E196" t="n">
-        <v>192.3148040771484</v>
+        <v>194.7520751953125</v>
       </c>
       <c r="F196" t="n">
-        <v>179304100</v>
+        <v>148835700</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B197" t="n">
-        <v>193.6333319429392</v>
+        <v>197.0195429632178</v>
       </c>
       <c r="C197" t="n">
-        <v>195.9607141929515</v>
+        <v>200.4057532237791</v>
       </c>
       <c r="D197" t="n">
-        <v>189.5878557469149</v>
+        <v>194.8919188665145</v>
       </c>
       <c r="E197" t="n">
-        <v>194.7520751953125</v>
+        <v>199.8663482666016</v>
       </c>
       <c r="F197" t="n">
-        <v>148835700</v>
+        <v>166476700</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B198" t="n">
-        <v>197.0195429632178</v>
+        <v>195.9806989625188</v>
       </c>
       <c r="C198" t="n">
-        <v>200.4057532237791</v>
+        <v>199.626628404907</v>
       </c>
       <c r="D198" t="n">
-        <v>194.8919188665145</v>
+        <v>193.2337727110923</v>
       </c>
       <c r="E198" t="n">
-        <v>199.8663482666016</v>
+        <v>197.3591613769531</v>
       </c>
       <c r="F198" t="n">
-        <v>166476700</v>
+        <v>146147600</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B199" t="n">
-        <v>195.9806989625188</v>
+        <v>196.9196593659626</v>
       </c>
       <c r="C199" t="n">
-        <v>199.626628404907</v>
+        <v>199.8363939026278</v>
       </c>
       <c r="D199" t="n">
-        <v>193.2337727110923</v>
+        <v>192.1350197738411</v>
       </c>
       <c r="E199" t="n">
-        <v>197.3591613769531</v>
+        <v>194.6122436523438</v>
       </c>
       <c r="F199" t="n">
-        <v>146147600</v>
+        <v>142068700</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B200" t="n">
-        <v>196.9196593659626</v>
+        <v>194.202694284663</v>
       </c>
       <c r="C200" t="n">
-        <v>199.8363939026278</v>
+        <v>197.3292007505161</v>
       </c>
       <c r="D200" t="n">
-        <v>192.1350197738411</v>
+        <v>193.7731822131383</v>
       </c>
       <c r="E200" t="n">
-        <v>194.6122436523438</v>
+        <v>195.3314361572266</v>
       </c>
       <c r="F200" t="n">
-        <v>142068700</v>
+        <v>108999000</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B201" t="n">
-        <v>194.202694284663</v>
+        <v>192.1549837798622</v>
       </c>
       <c r="C201" t="n">
-        <v>197.3292007505161</v>
+        <v>198.1882414262674</v>
       </c>
       <c r="D201" t="n">
-        <v>193.7731822131383</v>
+        <v>190.9263628146717</v>
       </c>
       <c r="E201" t="n">
-        <v>195.3314361572266</v>
+        <v>196.7098846435547</v>
       </c>
       <c r="F201" t="n">
-        <v>108999000</v>
+        <v>124154600</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B202" t="n">
-        <v>192.1549837798622</v>
+        <v>194.9618356993413</v>
       </c>
       <c r="C202" t="n">
-        <v>198.1882414262674</v>
+        <v>204.9306918075912</v>
       </c>
       <c r="D202" t="n">
-        <v>190.9263628146717</v>
+        <v>194.841974703339</v>
       </c>
       <c r="E202" t="n">
-        <v>196.7098846435547</v>
+        <v>203.891845703125</v>
       </c>
       <c r="F202" t="n">
-        <v>124154600</v>
+        <v>147419100</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B203" t="n">
-        <v>194.9618356993413</v>
+        <v>204.2314748595287</v>
       </c>
       <c r="C203" t="n">
-        <v>204.9306918075912</v>
+        <v>204.3613191897594</v>
       </c>
       <c r="D203" t="n">
-        <v>194.841974703339</v>
+        <v>198.7376223952696</v>
       </c>
       <c r="E203" t="n">
-        <v>203.891845703125</v>
+        <v>202.5533447265625</v>
       </c>
       <c r="F203" t="n">
-        <v>147419100</v>
+        <v>132037400</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B204" t="n">
-        <v>204.2314748595287</v>
+        <v>201.7742207048944</v>
       </c>
       <c r="C204" t="n">
-        <v>204.3613191897594</v>
+        <v>210.7641612313501</v>
       </c>
       <c r="D204" t="n">
-        <v>198.7376223952696</v>
+        <v>201.6943082934289</v>
       </c>
       <c r="E204" t="n">
-        <v>202.5533447265625</v>
+        <v>210.7242126464844</v>
       </c>
       <c r="F204" t="n">
-        <v>132037400</v>
+        <v>148421000</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B205" t="n">
-        <v>201.7742207048944</v>
+        <v>208.3069001369788</v>
       </c>
       <c r="C205" t="n">
-        <v>210.7641612313501</v>
+        <v>210.3346451505122</v>
       </c>
       <c r="D205" t="n">
-        <v>201.6943082934289</v>
+        <v>202.7730991138312</v>
       </c>
       <c r="E205" t="n">
-        <v>210.7242126464844</v>
+        <v>203.3025054931641</v>
       </c>
       <c r="F205" t="n">
-        <v>148421000</v>
+        <v>121411000</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B206" t="n">
-        <v>208.3069001369788</v>
+        <v>207.9672957533915</v>
       </c>
       <c r="C206" t="n">
-        <v>210.3346451505122</v>
+        <v>212.3124399374416</v>
       </c>
       <c r="D206" t="n">
-        <v>202.7730991138312</v>
+        <v>203.5722196467825</v>
       </c>
       <c r="E206" t="n">
-        <v>203.3025054931641</v>
+        <v>211.5632781982422</v>
       </c>
       <c r="F206" t="n">
-        <v>121411000</v>
+        <v>124379600</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B207" t="n">
-        <v>207.9672957533915</v>
+        <v>211.7230919717581</v>
       </c>
       <c r="C207" t="n">
-        <v>212.3124399374416</v>
+        <v>213.5710150202495</v>
       </c>
       <c r="D207" t="n">
-        <v>203.5722196467825</v>
+        <v>205.8096955397309</v>
       </c>
       <c r="E207" t="n">
-        <v>211.5632781982422</v>
+        <v>212.2624816894531</v>
       </c>
       <c r="F207" t="n">
-        <v>124379600</v>
+        <v>124797200</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B208" t="n">
-        <v>211.7230919717581</v>
+        <v>209.9350906043833</v>
       </c>
       <c r="C208" t="n">
-        <v>213.5710150202495</v>
+        <v>210.8440771529852</v>
       </c>
       <c r="D208" t="n">
-        <v>205.8096955397309</v>
+        <v>205.6199270055466</v>
       </c>
       <c r="E208" t="n">
-        <v>212.2624816894531</v>
+        <v>207.1681823730469</v>
       </c>
       <c r="F208" t="n">
-        <v>124797200</v>
+        <v>122986100</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B209" t="n">
-        <v>209.9350906043833</v>
+        <v>202.4135048295048</v>
       </c>
       <c r="C209" t="n">
-        <v>210.8440771529852</v>
+        <v>206.4190172896336</v>
       </c>
       <c r="D209" t="n">
-        <v>205.6199270055466</v>
+        <v>197.7487264058434</v>
       </c>
       <c r="E209" t="n">
-        <v>207.1681823730469</v>
+        <v>202.5833129882812</v>
       </c>
       <c r="F209" t="n">
-        <v>122986100</v>
+        <v>144281900</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B210" t="n">
-        <v>202.4135048295048</v>
+        <v>205.639896943356</v>
       </c>
       <c r="C210" t="n">
-        <v>206.4190172896336</v>
+        <v>207.5078172334397</v>
       </c>
       <c r="D210" t="n">
-        <v>197.7487264058434</v>
+        <v>202.0539130969454</v>
       </c>
       <c r="E210" t="n">
-        <v>202.5833129882812</v>
+        <v>203.0527954101562</v>
       </c>
       <c r="F210" t="n">
-        <v>144281900</v>
+        <v>88701500</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B211" t="n">
-        <v>205.639896943356</v>
+        <v>207.308024406286</v>
       </c>
       <c r="C211" t="n">
-        <v>207.5078172334397</v>
+        <v>208.4167843613107</v>
       </c>
       <c r="D211" t="n">
-        <v>202.0539130969454</v>
+        <v>203.7819711309363</v>
       </c>
       <c r="E211" t="n">
-        <v>203.0527954101562</v>
+        <v>207.0583038330078</v>
       </c>
       <c r="F211" t="n">
-        <v>88701500</v>
+        <v>108685600</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B212" t="n">
-        <v>207.308024406286</v>
+        <v>205.579968274895</v>
       </c>
       <c r="C212" t="n">
-        <v>208.4167843613107</v>
+        <v>214.1503804276117</v>
       </c>
       <c r="D212" t="n">
-        <v>203.7819711309363</v>
+        <v>204.7209288682105</v>
       </c>
       <c r="E212" t="n">
-        <v>207.0583038330078</v>
+        <v>211.8229827880859</v>
       </c>
       <c r="F212" t="n">
-        <v>108685600</v>
+        <v>137645600</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B213" t="n">
-        <v>205.579968274895</v>
+        <v>209.2258868865651</v>
       </c>
       <c r="C213" t="n">
-        <v>214.1503804276117</v>
+        <v>210.6342993029147</v>
       </c>
       <c r="D213" t="n">
-        <v>204.7209288682105</v>
+        <v>205.7297989431358</v>
       </c>
       <c r="E213" t="n">
-        <v>211.8229827880859</v>
+        <v>208.5266571044922</v>
       </c>
       <c r="F213" t="n">
-        <v>137645600</v>
+        <v>110505300</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B214" t="n">
-        <v>209.2258868865651</v>
+        <v>207.2181292349697</v>
       </c>
       <c r="C214" t="n">
-        <v>210.6342993029147</v>
+        <v>211.6731509810223</v>
       </c>
       <c r="D214" t="n">
-        <v>205.7297989431358</v>
+        <v>204.5810805834776</v>
       </c>
       <c r="E214" t="n">
-        <v>208.5266571044922</v>
+        <v>206.6088104248047</v>
       </c>
       <c r="F214" t="n">
-        <v>110505300</v>
+        <v>114836800</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B215" t="n">
-        <v>207.2181292349697</v>
+        <v>207.9672962732577</v>
       </c>
       <c r="C215" t="n">
-        <v>211.6731509810223</v>
+        <v>208.5166845983908</v>
       </c>
       <c r="D215" t="n">
-        <v>204.5810805834776</v>
+        <v>195.2215633388429</v>
       </c>
       <c r="E215" t="n">
-        <v>206.6088104248047</v>
+        <v>196.2903594970703</v>
       </c>
       <c r="F215" t="n">
-        <v>114836800</v>
+        <v>154353700</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B216" t="n">
-        <v>207.9672962732577</v>
+        <v>194.782047001347</v>
       </c>
       <c r="C216" t="n">
-        <v>208.5166845983908</v>
+        <v>198.4779084345641</v>
       </c>
       <c r="D216" t="n">
-        <v>195.2215633388429</v>
+        <v>192.5245785077403</v>
       </c>
       <c r="E216" t="n">
-        <v>196.2903594970703</v>
+        <v>196.789794921875</v>
       </c>
       <c r="F216" t="n">
-        <v>154353700</v>
+        <v>134111500</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B217" t="n">
-        <v>194.782047001347</v>
+        <v>195.6311069684468</v>
       </c>
       <c r="C217" t="n">
-        <v>198.4779084345641</v>
+        <v>196.8497446088402</v>
       </c>
       <c r="D217" t="n">
-        <v>192.5245785077403</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="E217" t="n">
-        <v>196.789794921875</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="F217" t="n">
-        <v>134111500</v>
+        <v>147680800</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B218" t="n">
-        <v>195.6311069684468</v>
+        <v>193.2337718176948</v>
       </c>
       <c r="C218" t="n">
-        <v>196.8497446088402</v>
+        <v>197.0295274868271</v>
       </c>
       <c r="D218" t="n">
-        <v>189.7976226806641</v>
+        <v>191.3059363552755</v>
       </c>
       <c r="E218" t="n">
-        <v>189.7976226806641</v>
+        <v>194.8219909667969</v>
       </c>
       <c r="F218" t="n">
-        <v>147680800</v>
+        <v>129010200</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B219" t="n">
-        <v>193.2337718176948</v>
+        <v>198.2182038580375</v>
       </c>
       <c r="C219" t="n">
-        <v>197.0295274868271</v>
+        <v>201.7742223680242</v>
       </c>
       <c r="D219" t="n">
-        <v>191.3059363552755</v>
+        <v>194.7320991825756</v>
       </c>
       <c r="E219" t="n">
-        <v>194.8219909667969</v>
+        <v>200.5256195068359</v>
       </c>
       <c r="F219" t="n">
-        <v>129010200</v>
+        <v>139961200</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B220" t="n">
-        <v>198.2182038580375</v>
+        <v>197.4690486270115</v>
       </c>
       <c r="C220" t="n">
-        <v>201.7742223680242</v>
+        <v>208.506701330784</v>
       </c>
       <c r="D220" t="n">
-        <v>194.7320991825756</v>
+        <v>196.6299911347511</v>
       </c>
       <c r="E220" t="n">
-        <v>200.5256195068359</v>
+        <v>206.4090423583984</v>
       </c>
       <c r="F220" t="n">
-        <v>139961200</v>
+        <v>128406900</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B221" t="n">
-        <v>197.4690486270115</v>
+        <v>211.0638257011038</v>
       </c>
       <c r="C221" t="n">
-        <v>208.506701330784</v>
+        <v>212.8218530009649</v>
       </c>
       <c r="D221" t="n">
-        <v>196.6299911347511</v>
+        <v>208.8163406042335</v>
       </c>
       <c r="E221" t="n">
-        <v>206.4090423583984</v>
+        <v>211.7031097412109</v>
       </c>
       <c r="F221" t="n">
-        <v>128406900</v>
+        <v>134922000</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B222" t="n">
-        <v>211.0638257011038</v>
+        <v>216.6176127852948</v>
       </c>
       <c r="C222" t="n">
-        <v>212.8218530009649</v>
+        <v>221.9716224388697</v>
       </c>
       <c r="D222" t="n">
-        <v>208.8163406042335</v>
+        <v>216.1581202281489</v>
       </c>
       <c r="E222" t="n">
-        <v>211.7031097412109</v>
+        <v>218.9749755859375</v>
       </c>
       <c r="F222" t="n">
-        <v>134922000</v>
+        <v>158187400</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B223" t="n">
-        <v>216.6176127852948</v>
+        <v>221.2823935806188</v>
       </c>
       <c r="C223" t="n">
-        <v>221.9716224388697</v>
+        <v>223.3800524967045</v>
       </c>
       <c r="D223" t="n">
-        <v>216.1581202281489</v>
+        <v>216.7574580038405</v>
       </c>
       <c r="E223" t="n">
-        <v>218.9749755859375</v>
+        <v>218.7452392578125</v>
       </c>
       <c r="F223" t="n">
-        <v>158187400</v>
+        <v>113940600</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B224" t="n">
-        <v>221.2823935806188</v>
+        <v>221.2923777041913</v>
       </c>
       <c r="C224" t="n">
-        <v>223.3800524967045</v>
+        <v>224.5087799247126</v>
       </c>
       <c r="D224" t="n">
-        <v>216.7574580038405</v>
+        <v>220.4133716458871</v>
       </c>
       <c r="E224" t="n">
-        <v>218.7452392578125</v>
+        <v>223.7096862792969</v>
       </c>
       <c r="F224" t="n">
-        <v>113940600</v>
+        <v>105669400</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B225" t="n">
-        <v>221.2923777041913</v>
+        <v>223.1502910726907</v>
       </c>
       <c r="C225" t="n">
-        <v>224.5087799247126</v>
+        <v>223.8894694330602</v>
       </c>
       <c r="D225" t="n">
-        <v>220.4133716458871</v>
+        <v>216.5277120448001</v>
       </c>
       <c r="E225" t="n">
-        <v>223.7096862792969</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="F225" t="n">
-        <v>105669400</v>
+        <v>115846600</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B226" t="n">
-        <v>223.1502910726907</v>
+        <v>221.9216754142795</v>
       </c>
       <c r="C226" t="n">
-        <v>223.8894694330602</v>
+        <v>221.9516406634887</v>
       </c>
       <c r="D226" t="n">
-        <v>216.5277120448001</v>
+        <v>215.9583469538982</v>
       </c>
       <c r="E226" t="n">
-        <v>217.3068389892578</v>
+        <v>217.2568969726562</v>
       </c>
       <c r="F226" t="n">
-        <v>115846600</v>
+        <v>101273100</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B227" t="n">
-        <v>221.9216754142795</v>
+        <v>220.7929293559802</v>
       </c>
       <c r="C227" t="n">
-        <v>221.9516406634887</v>
+        <v>224.848404158734</v>
       </c>
       <c r="D227" t="n">
-        <v>215.9583469538982</v>
+        <v>219.9538719106106</v>
       </c>
       <c r="E227" t="n">
-        <v>217.2568969726562</v>
+        <v>223.8395233154297</v>
       </c>
       <c r="F227" t="n">
-        <v>101273100</v>
+        <v>108783600</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B228" t="n">
-        <v>220.7929293559802</v>
+        <v>224.8084500146858</v>
       </c>
       <c r="C228" t="n">
-        <v>224.848404158734</v>
+        <v>226.9760227961096</v>
       </c>
       <c r="D228" t="n">
-        <v>219.9538719106106</v>
+        <v>223.4599680426375</v>
       </c>
       <c r="E228" t="n">
-        <v>223.8395233154297</v>
+        <v>225.0481872558594</v>
       </c>
       <c r="F228" t="n">
-        <v>108783600</v>
+        <v>98867200</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B229" t="n">
-        <v>224.8084500146858</v>
+        <v>226.5165415533859</v>
       </c>
       <c r="C229" t="n">
-        <v>226.9760227961096</v>
+        <v>227.2357380227387</v>
       </c>
       <c r="D229" t="n">
-        <v>223.4599680426375</v>
+        <v>224.2490744835724</v>
       </c>
       <c r="E229" t="n">
-        <v>225.0481872558594</v>
+        <v>224.9083404541016</v>
       </c>
       <c r="F229" t="n">
-        <v>98867200</v>
+        <v>75680900</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B230" t="n">
-        <v>226.5165415533859</v>
+        <v>225.7274161885591</v>
       </c>
       <c r="C230" t="n">
-        <v>227.2357380227387</v>
+        <v>227.6652502746616</v>
       </c>
       <c r="D230" t="n">
-        <v>224.2490744835724</v>
+        <v>224.6086728983284</v>
       </c>
       <c r="E230" t="n">
-        <v>224.9083404541016</v>
+        <v>224.7584991455078</v>
       </c>
       <c r="F230" t="n">
-        <v>75680900</v>
+        <v>93678700</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B231" t="n">
-        <v>225.7274161885591</v>
+        <v>220.203597915372</v>
       </c>
       <c r="C231" t="n">
-        <v>227.6652502746616</v>
+        <v>221.3922702798686</v>
       </c>
       <c r="D231" t="n">
-        <v>224.6086728983284</v>
+        <v>218.4455705709327</v>
       </c>
       <c r="E231" t="n">
-        <v>224.7584991455078</v>
+        <v>219.4944000244141</v>
       </c>
       <c r="F231" t="n">
-        <v>93678700</v>
+        <v>103128200</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B232" t="n">
-        <v>220.203597915372</v>
+        <v>221.4222404106533</v>
       </c>
       <c r="C232" t="n">
-        <v>221.3922702798686</v>
+        <v>222.6208961374568</v>
       </c>
       <c r="D232" t="n">
-        <v>218.4455705709327</v>
+        <v>216.5177245976465</v>
       </c>
       <c r="E232" t="n">
-        <v>219.4944000244141</v>
+        <v>217.3168334960938</v>
       </c>
       <c r="F232" t="n">
-        <v>103128200</v>
+        <v>96797300</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B233" t="n">
-        <v>221.4222404106533</v>
+        <v>218.1159423024499</v>
       </c>
       <c r="C233" t="n">
-        <v>222.6208961374568</v>
+        <v>219.6142657707553</v>
       </c>
       <c r="D233" t="n">
-        <v>216.5177245976465</v>
+        <v>215.418963107847</v>
       </c>
       <c r="E233" t="n">
-        <v>217.3168334960938</v>
+        <v>216.6076354980469</v>
       </c>
       <c r="F233" t="n">
-        <v>96797300</v>
+        <v>92457000</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B234" t="n">
-        <v>218.1159423024499</v>
+        <v>218.1758724878036</v>
       </c>
       <c r="C234" t="n">
-        <v>219.6142657707553</v>
+        <v>218.4955221432803</v>
       </c>
       <c r="D234" t="n">
-        <v>215.418963107847</v>
+        <v>214.2602556586216</v>
       </c>
       <c r="E234" t="n">
-        <v>216.6076354980469</v>
+        <v>214.4800109863281</v>
       </c>
       <c r="F234" t="n">
-        <v>92457000</v>
+        <v>98869300</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B235" t="n">
-        <v>218.1758724878036</v>
+        <v>215.2891020611033</v>
       </c>
       <c r="C235" t="n">
-        <v>218.4955221432803</v>
+        <v>215.3490325607492</v>
       </c>
       <c r="D235" t="n">
-        <v>214.2602556586216</v>
+        <v>207.0183577918231</v>
       </c>
       <c r="E235" t="n">
-        <v>214.4800109863281</v>
+        <v>208.2469787597656</v>
       </c>
       <c r="F235" t="n">
-        <v>98869300</v>
+        <v>135187300</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B236" t="n">
-        <v>215.2891020611033</v>
+        <v>210.7941279013131</v>
       </c>
       <c r="C236" t="n">
-        <v>215.3490325607492</v>
+        <v>214.4899893165327</v>
       </c>
       <c r="D236" t="n">
-        <v>207.0183577918231</v>
+        <v>209.8751580258669</v>
       </c>
       <c r="E236" t="n">
-        <v>208.2469787597656</v>
+        <v>212.8118743896484</v>
       </c>
       <c r="F236" t="n">
-        <v>135187300</v>
+        <v>122309000</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B237" t="n">
-        <v>210.7941279013131</v>
+        <v>212.4023240594531</v>
       </c>
       <c r="C237" t="n">
-        <v>214.4899893165327</v>
+        <v>213.3612577394914</v>
       </c>
       <c r="D237" t="n">
-        <v>209.8751580258669</v>
+        <v>208.9961318803605</v>
       </c>
       <c r="E237" t="n">
-        <v>212.8118743896484</v>
+        <v>209.4256591796875</v>
       </c>
       <c r="F237" t="n">
-        <v>122309000</v>
+        <v>179900000</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B238" t="n">
-        <v>212.4023240594531</v>
+        <v>222.6109016432552</v>
       </c>
       <c r="C238" t="n">
-        <v>213.3612577394914</v>
+        <v>230.2123962709879</v>
       </c>
       <c r="D238" t="n">
-        <v>208.9961318803605</v>
+        <v>220.6530857022795</v>
       </c>
       <c r="E238" t="n">
-        <v>209.4256591796875</v>
+        <v>227.7251739501953</v>
       </c>
       <c r="F238" t="n">
-        <v>179900000</v>
+        <v>298909800</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B239" t="n">
-        <v>222.6109016432552</v>
+        <v>227.1058715337123</v>
       </c>
       <c r="C239" t="n">
-        <v>230.2123962709879</v>
+        <v>229.003741733446</v>
       </c>
       <c r="D239" t="n">
-        <v>220.6530857022795</v>
+        <v>216.5676606288883</v>
       </c>
       <c r="E239" t="n">
-        <v>227.7251739501953</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="F239" t="n">
-        <v>298909800</v>
+        <v>195116400</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B240" t="n">
-        <v>227.1058715337123</v>
+        <v>218.6253647857836</v>
       </c>
       <c r="C240" t="n">
-        <v>229.003741733446</v>
+        <v>221.0526567078369</v>
       </c>
       <c r="D240" t="n">
-        <v>216.5676606288883</v>
+        <v>215.9683494434545</v>
       </c>
       <c r="E240" t="n">
-        <v>217.3068389892578</v>
+        <v>220.5332336425781</v>
       </c>
       <c r="F240" t="n">
-        <v>195116400</v>
+        <v>124702700</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B241" t="n">
-        <v>218.6253647857836</v>
+        <v>216.5077444634259</v>
       </c>
       <c r="C241" t="n">
-        <v>221.0526567078369</v>
+        <v>220.1636574397174</v>
       </c>
       <c r="D241" t="n">
-        <v>215.9683494434545</v>
+        <v>214.8595947199138</v>
       </c>
       <c r="E241" t="n">
-        <v>220.5332336425781</v>
+        <v>217.1969757080078</v>
       </c>
       <c r="F241" t="n">
-        <v>124702700</v>
+        <v>109756200</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B242" t="n">
-        <v>216.5077444634259</v>
+        <v>218.5454508199983</v>
       </c>
       <c r="C242" t="n">
-        <v>220.1636574397174</v>
+        <v>227.6952163087265</v>
       </c>
       <c r="D242" t="n">
-        <v>214.8595947199138</v>
+        <v>218.2357997469377</v>
       </c>
       <c r="E242" t="n">
-        <v>217.1969757080078</v>
+        <v>224.1591796875</v>
       </c>
       <c r="F242" t="n">
-        <v>109756200</v>
+        <v>157104700</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B243" t="n">
-        <v>218.5454508199983</v>
+        <v>225.7673797205316</v>
       </c>
       <c r="C243" t="n">
-        <v>227.6952163087265</v>
+        <v>230.1424737915274</v>
       </c>
       <c r="D243" t="n">
-        <v>218.2357997469377</v>
+        <v>224.4987949430455</v>
       </c>
       <c r="E243" t="n">
-        <v>224.1591796875</v>
+        <v>228.1946563720703</v>
       </c>
       <c r="F243" t="n">
-        <v>157104700</v>
+        <v>134681600</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B244" t="n">
-        <v>225.7673797205316</v>
+        <v>230.8317036041433</v>
       </c>
       <c r="C244" t="n">
-        <v>230.1424737915274</v>
+        <v>234.4975997614268</v>
       </c>
       <c r="D244" t="n">
-        <v>224.4987949430455</v>
+        <v>229.3733440032785</v>
       </c>
       <c r="E244" t="n">
-        <v>228.1946563720703</v>
+        <v>230.1025238037109</v>
       </c>
       <c r="F244" t="n">
-        <v>134681600</v>
+        <v>135352400</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B245" t="n">
-        <v>230.8317036041433</v>
+        <v>232.8494477166676</v>
       </c>
       <c r="C245" t="n">
-        <v>234.4975997614268</v>
+        <v>233.4487831783142</v>
       </c>
       <c r="D245" t="n">
-        <v>229.3733440032785</v>
+        <v>224.5986856128386</v>
       </c>
       <c r="E245" t="n">
-        <v>230.1025238037109</v>
+        <v>225.4776916503906</v>
       </c>
       <c r="F245" t="n">
-        <v>135352400</v>
+        <v>122965600</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B246" t="n">
-        <v>232.8494477166676</v>
+        <v>225.0281992525124</v>
       </c>
       <c r="C246" t="n">
-        <v>233.4487831783142</v>
+        <v>225.9271872095504</v>
       </c>
       <c r="D246" t="n">
-        <v>224.5986856128386</v>
+        <v>223.2102414251123</v>
       </c>
       <c r="E246" t="n">
-        <v>225.4776916503906</v>
+        <v>223.4199981689453</v>
       </c>
       <c r="F246" t="n">
-        <v>122965600</v>
+        <v>82955500</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,25 +6839,25 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B247" t="n">
-        <v>225.0281992525124</v>
+        <v>220.5299987792969</v>
       </c>
       <c r="C247" t="n">
-        <v>225.9271872095504</v>
+        <v>220.9900054931641</v>
       </c>
       <c r="D247" t="n">
-        <v>223.2102414251123</v>
+        <v>217.1999969482422</v>
       </c>
       <c r="E247" t="n">
-        <v>223.4199981689453</v>
+        <v>218.3600006103516</v>
       </c>
       <c r="F247" t="n">
-        <v>82955500</v>
+        <v>105768000</v>
       </c>
       <c r="G247" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -6865,25 +6865,25 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B248" t="n">
-        <v>220.5299987792969</v>
+        <v>221.2400054931641</v>
       </c>
       <c r="C248" t="n">
-        <v>220.9900054931641</v>
+        <v>222</v>
       </c>
       <c r="D248" t="n">
-        <v>217.1999969482422</v>
+        <v>218.1499938964844</v>
       </c>
       <c r="E248" t="n">
-        <v>218.3600006103516</v>
+        <v>218.2899932861328</v>
       </c>
       <c r="F248" t="n">
-        <v>105768000</v>
+        <v>89060100</v>
       </c>
       <c r="G248" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B249" t="n">
-        <v>221.2400054931641</v>
+        <v>211.2400054931641</v>
       </c>
       <c r="C249" t="n">
-        <v>222</v>
+        <v>212.7700042724609</v>
       </c>
       <c r="D249" t="n">
-        <v>218.1499938964844</v>
+        <v>208.9299926757812</v>
       </c>
       <c r="E249" t="n">
-        <v>218.2899932861328</v>
+        <v>210.9600067138672</v>
       </c>
       <c r="F249" t="n">
-        <v>89060100</v>
+        <v>132267200</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B250" t="n">
-        <v>211.2400054931641</v>
+        <v>213.3800048828125</v>
       </c>
       <c r="C250" t="n">
-        <v>212.7700042724609</v>
+        <v>213.9400024414062</v>
       </c>
       <c r="D250" t="n">
-        <v>208.9299926757812</v>
+        <v>211.1600036621094</v>
       </c>
       <c r="E250" t="n">
-        <v>210.9600067138672</v>
+        <v>212.1699981689453</v>
       </c>
       <c r="F250" t="n">
-        <v>132267200</v>
+        <v>88059700</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B251" t="n">
-        <v>213.3800048828125</v>
+        <v>214.1399993896484</v>
       </c>
       <c r="C251" t="n">
-        <v>213.9400024414062</v>
+        <v>216.7599945068359</v>
       </c>
       <c r="D251" t="n">
-        <v>211.1600036621094</v>
+        <v>212.5</v>
       </c>
       <c r="E251" t="n">
-        <v>212.1699981689453</v>
+        <v>213.8999938964844</v>
       </c>
       <c r="F251" t="n">
-        <v>88059700</v>
+        <v>96563600</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,14 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B252" t="inlineStr"/>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
+        <v>46282</v>
+      </c>
+      <c r="B252" t="n">
+        <v>218.3800048828125</v>
+      </c>
+      <c r="C252" t="n">
+        <v>219.9100036621094</v>
+      </c>
+      <c r="D252" t="n">
+        <v>217.1499938964844</v>
+      </c>
+      <c r="E252" t="n">
+        <v>219.3399963378906</v>
+      </c>
       <c r="F252" t="n">
-        <v>96113489</v>
+        <v>93960500</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10876,37 +10884,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>219.34</v>
+      </c>
+      <c r="D2" t="n">
         <v>213.9</v>
       </c>
-      <c r="D2" t="n">
-        <v>212.17</v>
-      </c>
       <c r="E2" t="n">
-        <v>214.14</v>
+        <v>218.388</v>
       </c>
       <c r="F2" t="n">
-        <v>216.76</v>
+        <v>219.9</v>
       </c>
       <c r="G2" t="n">
-        <v>212.5</v>
+        <v>217.145</v>
       </c>
       <c r="H2" t="n">
-        <v>96113489</v>
+        <v>92845751</v>
       </c>
       <c r="I2" t="n">
-        <v>131193816</v>
+        <v>128873413</v>
       </c>
       <c r="J2" t="n">
-        <v>5165043154944</v>
+        <v>5296402989056</v>
       </c>
       <c r="K2" t="n">
-        <v>26.80451</v>
+        <v>27.012316</v>
       </c>
       <c r="L2" t="n">
-        <v>13.698463</v>
+        <v>14.046848</v>
       </c>
       <c r="M2" t="n">
-        <v>7.98</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="N2" t="n">
         <v>236.54</v>
@@ -10942,7 +10950,7 @@
         <v>9.483000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>22.556152</v>
+        <v>23.129812</v>
       </c>
       <c r="Z2" t="n">
         <v>1.278</v>
@@ -10954,7 +10962,7 @@
         <v>302970011648</v>
       </c>
       <c r="AC2" t="n">
-        <v>5131381243904</v>
+        <v>5262485225472</v>
       </c>
       <c r="AD2" t="n">
         <v>201266003968</v>
@@ -10981,7 +10989,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-17 08:09:57</t>
+          <t>2026-09-18 13:15:35</t>
         </is>
       </c>
     </row>

--- a/data/NVDA_data.xlsx
+++ b/data/NVDA_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B2" t="n">
-        <v>173.5641783462465</v>
+        <v>175.349898865447</v>
       </c>
       <c r="C2" t="n">
-        <v>176.6767318043244</v>
+        <v>177.6543753314711</v>
       </c>
       <c r="D2" t="n">
-        <v>172.5466271367534</v>
+        <v>174.7612974471592</v>
       </c>
       <c r="E2" t="n">
-        <v>175.8187866210938</v>
+        <v>176.2477416992188</v>
       </c>
       <c r="F2" t="n">
-        <v>191763300</v>
+        <v>237182100</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B3" t="n">
-        <v>175.349898865447</v>
+        <v>174.8810218455756</v>
       </c>
       <c r="C3" t="n">
-        <v>177.6543753314711</v>
+        <v>184.1089135963474</v>
       </c>
       <c r="D3" t="n">
-        <v>174.7612974471592</v>
+        <v>174.2924356467209</v>
       </c>
       <c r="E3" t="n">
-        <v>176.2477416992188</v>
+        <v>183.1711578369141</v>
       </c>
       <c r="F3" t="n">
-        <v>237182100</v>
+        <v>269637000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B4" t="n">
-        <v>174.8810218455756</v>
+        <v>181.5350878652714</v>
       </c>
       <c r="C4" t="n">
-        <v>184.1089135963474</v>
+        <v>181.9840093083128</v>
       </c>
       <c r="D4" t="n">
-        <v>174.2924356467209</v>
+        <v>175.7888599052367</v>
       </c>
       <c r="E4" t="n">
-        <v>183.1711578369141</v>
+        <v>178.0035400390625</v>
       </c>
       <c r="F4" t="n">
-        <v>269637000</v>
+        <v>192559600</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B5" t="n">
-        <v>181.5350878652714</v>
+        <v>179.3403383898065</v>
       </c>
       <c r="C5" t="n">
-        <v>181.9840093083128</v>
+        <v>179.3503090089054</v>
       </c>
       <c r="D5" t="n">
-        <v>175.7888599052367</v>
+        <v>174.9807727171775</v>
       </c>
       <c r="E5" t="n">
-        <v>178.0035400390625</v>
+        <v>176.5470275878906</v>
       </c>
       <c r="F5" t="n">
-        <v>192559600</v>
+        <v>143564100</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B6" t="n">
-        <v>179.3403383898065</v>
+        <v>174.0629701066951</v>
       </c>
       <c r="C6" t="n">
-        <v>179.3503090089054</v>
+        <v>179.8291540783439</v>
       </c>
       <c r="D6" t="n">
-        <v>174.9807727171775</v>
+        <v>172.7162058826927</v>
       </c>
       <c r="E6" t="n">
-        <v>176.5470275878906</v>
+        <v>177.2653045654297</v>
       </c>
       <c r="F6" t="n">
-        <v>143564100</v>
+        <v>191586700</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B7" t="n">
-        <v>174.0629701066951</v>
+        <v>177.7441579191998</v>
       </c>
       <c r="C7" t="n">
-        <v>179.8291540783439</v>
+        <v>179.3403398828169</v>
       </c>
       <c r="D7" t="n">
-        <v>172.7162058826927</v>
+        <v>174.5118962929188</v>
       </c>
       <c r="E7" t="n">
-        <v>177.2653045654297</v>
+        <v>177.7641143798828</v>
       </c>
       <c r="F7" t="n">
-        <v>191586700</v>
+        <v>148573700</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B8" t="n">
-        <v>177.7441426621237</v>
+        <v>179.9987552370008</v>
       </c>
       <c r="C8" t="n">
-        <v>179.3403244887289</v>
+        <v>183.5602300506758</v>
       </c>
       <c r="D8" t="n">
-        <v>174.5118813132914</v>
+        <v>179.8890327563757</v>
       </c>
       <c r="E8" t="n">
-        <v>177.7640991210938</v>
+        <v>181.4153747558594</v>
       </c>
       <c r="F8" t="n">
-        <v>148573700</v>
+        <v>193063500</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B9" t="n">
-        <v>179.9987400973632</v>
+        <v>181.6448190078555</v>
       </c>
       <c r="C9" t="n">
-        <v>183.5602146114836</v>
+        <v>186.9022276338177</v>
       </c>
       <c r="D9" t="n">
-        <v>179.8890176259668</v>
+        <v>181.0462469572146</v>
       </c>
       <c r="E9" t="n">
-        <v>181.4153594970703</v>
+        <v>186.1340637207031</v>
       </c>
       <c r="F9" t="n">
-        <v>193063500</v>
+        <v>236981000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B10" t="n">
-        <v>181.6448190078555</v>
+        <v>184.7972606974542</v>
       </c>
       <c r="C10" t="n">
-        <v>186.9022276338177</v>
+        <v>187.6903232769056</v>
       </c>
       <c r="D10" t="n">
-        <v>181.0462469572146</v>
+        <v>183.4604518817237</v>
       </c>
       <c r="E10" t="n">
-        <v>186.1340637207031</v>
+        <v>186.79248046875</v>
       </c>
       <c r="F10" t="n">
-        <v>236981000</v>
+        <v>173844900</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B11" t="n">
-        <v>184.7972606974542</v>
+        <v>189.1468626563914</v>
       </c>
       <c r="C11" t="n">
-        <v>187.6903232769056</v>
+        <v>190.593394116267</v>
       </c>
       <c r="D11" t="n">
-        <v>183.4604518817237</v>
+        <v>187.6105347272827</v>
       </c>
       <c r="E11" t="n">
-        <v>186.79248046875</v>
+        <v>188.4385528564453</v>
       </c>
       <c r="F11" t="n">
-        <v>173844900</v>
+        <v>136805800</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B12" t="n">
-        <v>189.146847340247</v>
+        <v>188.7378093314507</v>
       </c>
       <c r="C12" t="n">
-        <v>190.59337868299</v>
+        <v>189.9050110254035</v>
       </c>
       <c r="D12" t="n">
-        <v>187.6105195355423</v>
+        <v>184.9369182511207</v>
       </c>
       <c r="E12" t="n">
-        <v>188.4385375976562</v>
+        <v>187.1715545654297</v>
       </c>
       <c r="F12" t="n">
-        <v>136805800</v>
+        <v>137596900</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B13" t="n">
-        <v>188.7378401044004</v>
+        <v>185.0566446584491</v>
       </c>
       <c r="C13" t="n">
-        <v>189.9050419886609</v>
+        <v>186.7825055997528</v>
       </c>
       <c r="D13" t="n">
-        <v>184.9369484043502</v>
+        <v>182.8918329061041</v>
       </c>
       <c r="E13" t="n">
-        <v>187.1715850830078</v>
+        <v>185.0965423583984</v>
       </c>
       <c r="F13" t="n">
-        <v>137596900</v>
+        <v>157678100</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B14" t="n">
-        <v>185.0566446584491</v>
+        <v>185.7848907820332</v>
       </c>
       <c r="C14" t="n">
-        <v>186.7825055997528</v>
+        <v>188.6081286768816</v>
       </c>
       <c r="D14" t="n">
-        <v>182.8918329061041</v>
+        <v>183.5602249269612</v>
       </c>
       <c r="E14" t="n">
-        <v>185.0965423583984</v>
+        <v>184.5977325439453</v>
       </c>
       <c r="F14" t="n">
-        <v>157678100</v>
+        <v>140088000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B15" t="n">
-        <v>185.7848907820332</v>
+        <v>186.1240823667868</v>
       </c>
       <c r="C15" t="n">
-        <v>188.6081286768816</v>
+        <v>189.1468390813163</v>
       </c>
       <c r="D15" t="n">
-        <v>183.5602249269612</v>
+        <v>186.094140065894</v>
       </c>
       <c r="E15" t="n">
-        <v>184.5977325439453</v>
+        <v>188.6580047607422</v>
       </c>
       <c r="F15" t="n">
-        <v>140088000</v>
+        <v>130168900</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B16" t="n">
-        <v>186.1240823667868</v>
+        <v>191.7705422839889</v>
       </c>
       <c r="C16" t="n">
-        <v>189.1468390813163</v>
+        <v>194.8332119113436</v>
       </c>
       <c r="D16" t="n">
-        <v>186.094140065894</v>
+        <v>190.6033405552435</v>
       </c>
       <c r="E16" t="n">
-        <v>188.6580047607422</v>
+        <v>192.1097412109375</v>
       </c>
       <c r="F16" t="n">
-        <v>130168900</v>
+        <v>182997200</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B17" t="n">
-        <v>191.7705422839889</v>
+        <v>193.0474821132437</v>
       </c>
       <c r="C17" t="n">
-        <v>194.8332119113436</v>
+        <v>195.1524395658232</v>
       </c>
       <c r="D17" t="n">
-        <v>190.6033405552435</v>
+        <v>181.6148814298513</v>
       </c>
       <c r="E17" t="n">
-        <v>192.1097412109375</v>
+        <v>182.7222290039062</v>
       </c>
       <c r="F17" t="n">
-        <v>182997200</v>
+        <v>268774400</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B18" t="n">
-        <v>193.0474821132437</v>
+        <v>187.5207340107304</v>
       </c>
       <c r="C18" t="n">
-        <v>195.1524395658232</v>
+        <v>189.6556185865847</v>
       </c>
       <c r="D18" t="n">
-        <v>181.6148814298513</v>
+        <v>185.5155435929421</v>
       </c>
       <c r="E18" t="n">
-        <v>182.7222290039062</v>
+        <v>187.8699035644531</v>
       </c>
       <c r="F18" t="n">
-        <v>268774400</v>
+        <v>153482800</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B19" t="n">
-        <v>187.5207340107304</v>
+        <v>184.3283927796865</v>
       </c>
       <c r="C19" t="n">
-        <v>189.6556185865847</v>
+        <v>184.3583198600852</v>
       </c>
       <c r="D19" t="n">
-        <v>185.5155435929421</v>
+        <v>179.2705030798172</v>
       </c>
       <c r="E19" t="n">
-        <v>187.8699035644531</v>
+        <v>179.5997161865234</v>
       </c>
       <c r="F19" t="n">
-        <v>153482800</v>
+        <v>205641400</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B20" t="n">
-        <v>184.3283927796865</v>
+        <v>184.3583147400375</v>
       </c>
       <c r="C20" t="n">
-        <v>184.3583198600852</v>
+        <v>184.4281395182556</v>
       </c>
       <c r="D20" t="n">
-        <v>179.2705030798172</v>
+        <v>176.866254560341</v>
       </c>
       <c r="E20" t="n">
-        <v>179.5997161865234</v>
+        <v>179.4001922607422</v>
       </c>
       <c r="F20" t="n">
-        <v>205641400</v>
+        <v>214450500</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B21" t="n">
-        <v>184.3582990595379</v>
+        <v>181.7944521048813</v>
       </c>
       <c r="C21" t="n">
-        <v>184.4281238318171</v>
+        <v>182.8419455690647</v>
       </c>
       <c r="D21" t="n">
-        <v>176.8662395170747</v>
+        <v>179.3403402174659</v>
       </c>
       <c r="E21" t="n">
-        <v>179.4001770019531</v>
+        <v>181.3754577636719</v>
       </c>
       <c r="F21" t="n">
-        <v>214450500</v>
+        <v>179723300</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B22" t="n">
-        <v>181.7944368108431</v>
+        <v>179.7493615830456</v>
       </c>
       <c r="C22" t="n">
-        <v>182.8419301869027</v>
+        <v>183.6600061588844</v>
       </c>
       <c r="D22" t="n">
-        <v>179.3403251298876</v>
+        <v>179.3203965919317</v>
       </c>
       <c r="E22" t="n">
-        <v>181.3754425048828</v>
+        <v>182.7821044921875</v>
       </c>
       <c r="F22" t="n">
-        <v>179723300</v>
+        <v>173135200</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B23" t="n">
-        <v>179.7493465774322</v>
+        <v>182.6923102950553</v>
       </c>
       <c r="C23" t="n">
-        <v>183.6599908268075</v>
+        <v>184.7573549226016</v>
       </c>
       <c r="D23" t="n">
-        <v>179.3203816221287</v>
+        <v>181.2956472677441</v>
       </c>
       <c r="E23" t="n">
-        <v>182.7820892333984</v>
+        <v>182.2034759521484</v>
       </c>
       <c r="F23" t="n">
-        <v>173135200</v>
+        <v>128544700</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B24" t="n">
-        <v>182.6922949953283</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="C24" t="n">
-        <v>184.7573394499357</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="D24" t="n">
-        <v>181.2956320849819</v>
+        <v>179.3702701372806</v>
       </c>
       <c r="E24" t="n">
-        <v>182.2034606933594</v>
+        <v>180.7270202636719</v>
       </c>
       <c r="F24" t="n">
-        <v>128544700</v>
+        <v>124240200</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B25" t="n">
-        <v>182.3531141136141</v>
+        <v>180.7070509305708</v>
       </c>
       <c r="C25" t="n">
-        <v>182.3531141136141</v>
+        <v>183.0015566720687</v>
       </c>
       <c r="D25" t="n">
-        <v>179.3702701372806</v>
+        <v>176.3375148363812</v>
       </c>
       <c r="E25" t="n">
-        <v>180.7270202636719</v>
+        <v>179.8491058349609</v>
       </c>
       <c r="F25" t="n">
-        <v>124240200</v>
+        <v>162249600</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B26" t="n">
-        <v>180.7070662621498</v>
+        <v>179.988793025541</v>
       </c>
       <c r="C26" t="n">
-        <v>183.0015721983185</v>
+        <v>182.5925557149365</v>
       </c>
       <c r="D26" t="n">
-        <v>176.3375297972393</v>
+        <v>179.3602938591047</v>
       </c>
       <c r="E26" t="n">
-        <v>179.84912109375</v>
+        <v>181.7246398925781</v>
       </c>
       <c r="F26" t="n">
-        <v>162249600</v>
+        <v>111363700</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B27" t="n">
-        <v>179.988793025541</v>
+        <v>183.400590081168</v>
       </c>
       <c r="C27" t="n">
-        <v>182.5925557149365</v>
+        <v>187.0219186862977</v>
       </c>
       <c r="D27" t="n">
-        <v>179.3602938591047</v>
+        <v>183.0614063875393</v>
       </c>
       <c r="E27" t="n">
-        <v>181.7246398925781</v>
+        <v>185.8148040771484</v>
       </c>
       <c r="F27" t="n">
-        <v>111363700</v>
+        <v>131296700</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B28" t="n">
-        <v>183.400590081168</v>
+        <v>189.5359184602369</v>
       </c>
       <c r="C28" t="n">
-        <v>187.0219186862977</v>
+        <v>191.5411089646758</v>
       </c>
       <c r="D28" t="n">
-        <v>183.0614063875393</v>
+        <v>187.9796341631504</v>
       </c>
       <c r="E28" t="n">
-        <v>185.8148040771484</v>
+        <v>191.0323333740234</v>
       </c>
       <c r="F28" t="n">
-        <v>131296700</v>
+        <v>153452700</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B29" t="n">
-        <v>189.5359184602369</v>
+        <v>192.5886067715161</v>
       </c>
       <c r="C29" t="n">
-        <v>191.5411089646758</v>
+        <v>202.6644582837766</v>
       </c>
       <c r="D29" t="n">
-        <v>187.9796341631504</v>
+        <v>191.4513320204045</v>
       </c>
       <c r="E29" t="n">
-        <v>191.0323333740234</v>
+        <v>200.5495300292969</v>
       </c>
       <c r="F29" t="n">
-        <v>153452700</v>
+        <v>297986200</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B30" t="n">
-        <v>192.588592118433</v>
+        <v>207.482921843539</v>
       </c>
       <c r="C30" t="n">
-        <v>202.6644428640734</v>
+        <v>211.6828666070652</v>
       </c>
       <c r="D30" t="n">
-        <v>191.4513174538508</v>
+        <v>204.2905729140704</v>
       </c>
       <c r="E30" t="n">
-        <v>200.5495147705078</v>
+        <v>206.545166015625</v>
       </c>
       <c r="F30" t="n">
-        <v>297986200</v>
+        <v>308829600</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B31" t="n">
-        <v>207.482906515472</v>
+        <v>204.6596680014167</v>
       </c>
       <c r="C31" t="n">
-        <v>211.6828509687219</v>
+        <v>205.6672637579894</v>
       </c>
       <c r="D31" t="n">
-        <v>204.2905578218423</v>
+        <v>200.9286166610889</v>
       </c>
       <c r="E31" t="n">
-        <v>206.5451507568359</v>
+        <v>202.4050750732422</v>
       </c>
       <c r="F31" t="n">
-        <v>308829600</v>
+        <v>178864400</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B32" t="n">
-        <v>204.6596525726598</v>
+        <v>205.9565537660584</v>
       </c>
       <c r="C32" t="n">
-        <v>205.6672482532724</v>
+        <v>207.4729250244422</v>
       </c>
       <c r="D32" t="n">
-        <v>200.9286015136062</v>
+        <v>201.5870329046891</v>
       </c>
       <c r="E32" t="n">
-        <v>202.4050598144531</v>
+        <v>202.0060272216797</v>
       </c>
       <c r="F32" t="n">
-        <v>178864400</v>
+        <v>179802200</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B33" t="n">
-        <v>205.9565693232556</v>
+        <v>207.5826726752522</v>
       </c>
       <c r="C33" t="n">
-        <v>207.4729406961805</v>
+        <v>210.8348755139714</v>
       </c>
       <c r="D33" t="n">
-        <v>201.5870481318289</v>
+        <v>205.0686914304077</v>
       </c>
       <c r="E33" t="n">
-        <v>202.0060424804688</v>
+        <v>206.3855438232422</v>
       </c>
       <c r="F33" t="n">
-        <v>179802200</v>
+        <v>180267300</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B34" t="n">
-        <v>207.5826726752522</v>
+        <v>202.5148147488263</v>
       </c>
       <c r="C34" t="n">
-        <v>210.8348755139714</v>
+        <v>203.4824975937368</v>
       </c>
       <c r="D34" t="n">
-        <v>205.0686914304077</v>
+        <v>197.4569251230167</v>
       </c>
       <c r="E34" t="n">
-        <v>206.3855438232422</v>
+        <v>198.2151184082031</v>
       </c>
       <c r="F34" t="n">
-        <v>180267300</v>
+        <v>188919300</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B35" t="n">
-        <v>202.5148147488263</v>
+        <v>198.2949275919373</v>
       </c>
       <c r="C35" t="n">
-        <v>203.4824975937368</v>
+        <v>202.4350026612236</v>
       </c>
       <c r="D35" t="n">
-        <v>197.4569251230167</v>
+        <v>194.1847643800754</v>
       </c>
       <c r="E35" t="n">
-        <v>198.2151184082031</v>
+        <v>194.7434387207031</v>
       </c>
       <c r="F35" t="n">
-        <v>188919300</v>
+        <v>171350300</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B36" t="n">
-        <v>198.2949275919373</v>
+        <v>195.9505410878136</v>
       </c>
       <c r="C36" t="n">
-        <v>202.4350026612236</v>
+        <v>197.1476699621838</v>
       </c>
       <c r="D36" t="n">
-        <v>194.1847643800754</v>
+        <v>185.9345440647224</v>
       </c>
       <c r="E36" t="n">
-        <v>194.7434387207031</v>
+        <v>187.6304779052734</v>
       </c>
       <c r="F36" t="n">
-        <v>171350300</v>
+        <v>223029800</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B37" t="n">
-        <v>195.9505410878136</v>
+        <v>184.4580698535366</v>
       </c>
       <c r="C37" t="n">
-        <v>197.1476699621838</v>
+        <v>187.8699092076593</v>
       </c>
       <c r="D37" t="n">
-        <v>185.9345440647224</v>
+        <v>178.4823961188316</v>
       </c>
       <c r="E37" t="n">
-        <v>187.6304779052734</v>
+        <v>187.7003021240234</v>
       </c>
       <c r="F37" t="n">
-        <v>223029800</v>
+        <v>264942300</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B38" t="n">
-        <v>184.4580698535366</v>
+        <v>194.6436788693004</v>
       </c>
       <c r="C38" t="n">
-        <v>187.8699092076593</v>
+        <v>199.4621367771523</v>
       </c>
       <c r="D38" t="n">
-        <v>178.4823961188316</v>
+        <v>193.3268264223904</v>
       </c>
       <c r="E38" t="n">
-        <v>187.7003021240234</v>
+        <v>198.5742645263672</v>
       </c>
       <c r="F38" t="n">
-        <v>264942300</v>
+        <v>198897100</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B39" t="n">
-        <v>194.6436639125443</v>
+        <v>194.6935535589016</v>
       </c>
       <c r="C39" t="n">
-        <v>199.4621214501376</v>
+        <v>194.9529266552934</v>
       </c>
       <c r="D39" t="n">
-        <v>193.3268115668235</v>
+        <v>190.8427786999811</v>
       </c>
       <c r="E39" t="n">
-        <v>198.5742492675781</v>
+        <v>192.6983337402344</v>
       </c>
       <c r="F39" t="n">
-        <v>198897100</v>
+        <v>176483300</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B40" t="n">
-        <v>194.6935689756818</v>
+        <v>195.2522164876445</v>
       </c>
       <c r="C40" t="n">
-        <v>194.9529420926121</v>
+        <v>195.4218083488666</v>
       </c>
       <c r="D40" t="n">
-        <v>190.8427938118383</v>
+        <v>190.673190567689</v>
       </c>
       <c r="E40" t="n">
-        <v>192.6983489990234</v>
+        <v>193.3368072509766</v>
       </c>
       <c r="F40" t="n">
-        <v>176483300</v>
+        <v>154935300</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B41" t="n">
-        <v>195.2522318976041</v>
+        <v>190.5933635318434</v>
       </c>
       <c r="C41" t="n">
-        <v>195.4218237722109</v>
+        <v>190.9824307616844</v>
       </c>
       <c r="D41" t="n">
-        <v>190.6732056162565</v>
+        <v>183.4105757073767</v>
       </c>
       <c r="E41" t="n">
-        <v>193.3368225097656</v>
+        <v>186.4133758544922</v>
       </c>
       <c r="F41" t="n">
-        <v>154935300</v>
+        <v>207423100</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B42" t="n">
-        <v>190.5933791327836</v>
+        <v>182.4229435613052</v>
       </c>
       <c r="C42" t="n">
-        <v>190.9824463944715</v>
+        <v>190.553458007553</v>
       </c>
       <c r="D42" t="n">
-        <v>183.4105907203728</v>
+        <v>180.1483942490048</v>
       </c>
       <c r="E42" t="n">
-        <v>186.4133911132812</v>
+        <v>189.7154693603516</v>
       </c>
       <c r="F42" t="n">
-        <v>207423100</v>
+        <v>186591900</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B43" t="n">
-        <v>182.4229435613052</v>
+        <v>185.525507871713</v>
       </c>
       <c r="C43" t="n">
-        <v>190.553458007553</v>
+        <v>188.5482645458532</v>
       </c>
       <c r="D43" t="n">
-        <v>180.1483942490048</v>
+        <v>183.8794576828592</v>
       </c>
       <c r="E43" t="n">
-        <v>189.7154693603516</v>
+        <v>186.1540069580078</v>
       </c>
       <c r="F43" t="n">
-        <v>186591900</v>
+        <v>173628900</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B44" t="n">
-        <v>185.525507871713</v>
+        <v>182.9416897271721</v>
       </c>
       <c r="C44" t="n">
-        <v>188.5482645458532</v>
+        <v>184.358293814419</v>
       </c>
       <c r="D44" t="n">
-        <v>183.8794576828592</v>
+        <v>179.2205942185541</v>
       </c>
       <c r="E44" t="n">
-        <v>186.1540069580078</v>
+        <v>180.926513671875</v>
       </c>
       <c r="F44" t="n">
-        <v>173628900</v>
+        <v>213598900</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B45" t="n">
-        <v>182.9417205846578</v>
+        <v>184.3483122805645</v>
       </c>
       <c r="C45" t="n">
-        <v>184.3583249108488</v>
+        <v>187.4109817403353</v>
       </c>
       <c r="D45" t="n">
-        <v>179.2206244483882</v>
+        <v>182.39300555425</v>
       </c>
       <c r="E45" t="n">
-        <v>180.9265441894531</v>
+        <v>186.0741882324219</v>
       </c>
       <c r="F45" t="n">
-        <v>213598900</v>
+        <v>247246400</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B46" t="n">
-        <v>184.3483273978252</v>
+        <v>195.4816571057099</v>
       </c>
       <c r="C46" t="n">
-        <v>187.4109971087465</v>
+        <v>195.5315406452363</v>
       </c>
       <c r="D46" t="n">
-        <v>182.3930205111681</v>
+        <v>179.4201468289569</v>
       </c>
       <c r="E46" t="n">
-        <v>186.0742034912109</v>
+        <v>180.208251953125</v>
       </c>
       <c r="F46" t="n">
-        <v>247246400</v>
+        <v>343504800</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B47" t="n">
-        <v>195.4816571057099</v>
+        <v>180.806813452001</v>
       </c>
       <c r="C47" t="n">
-        <v>195.5315406452363</v>
+        <v>184.1188702156436</v>
       </c>
       <c r="D47" t="n">
-        <v>179.4201468289569</v>
+        <v>172.5166628687019</v>
       </c>
       <c r="E47" t="n">
-        <v>180.208251953125</v>
+        <v>178.4524536132812</v>
       </c>
       <c r="F47" t="n">
-        <v>343504800</v>
+        <v>346926200</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B48" t="n">
-        <v>180.8068443722038</v>
+        <v>179.0610093294625</v>
       </c>
       <c r="C48" t="n">
-        <v>184.1189017022491</v>
+        <v>183.0614196131816</v>
       </c>
       <c r="D48" t="n">
-        <v>172.5166923711864</v>
+        <v>176.0581937395723</v>
       </c>
       <c r="E48" t="n">
-        <v>178.4524841308594</v>
+        <v>182.1136932373047</v>
       </c>
       <c r="F48" t="n">
-        <v>346926200</v>
+        <v>256618300</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B49" t="n">
-        <v>179.0610243324759</v>
+        <v>174.4919407266003</v>
       </c>
       <c r="C49" t="n">
-        <v>183.0614349513779</v>
+        <v>177.7341727058355</v>
       </c>
       <c r="D49" t="n">
-        <v>176.0582084909882</v>
+        <v>169.1447513765687</v>
       </c>
       <c r="E49" t="n">
-        <v>182.1137084960938</v>
+        <v>177.3949890136719</v>
       </c>
       <c r="F49" t="n">
-        <v>256618300</v>
+        <v>320600300</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B50" t="n">
-        <v>174.4919407266003</v>
+        <v>181.1958831941039</v>
       </c>
       <c r="C50" t="n">
-        <v>177.7341727058355</v>
+        <v>182.4728225932506</v>
       </c>
       <c r="D50" t="n">
-        <v>169.1447513765687</v>
+        <v>177.8139863878403</v>
       </c>
       <c r="E50" t="n">
-        <v>177.3949890136719</v>
+        <v>179.8291473388672</v>
       </c>
       <c r="F50" t="n">
-        <v>320600300</v>
+        <v>183852000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B51" t="n">
-        <v>181.1959139436215</v>
+        <v>178.5821404669205</v>
       </c>
       <c r="C51" t="n">
-        <v>182.4728535594688</v>
+        <v>178.8614700176124</v>
       </c>
       <c r="D51" t="n">
-        <v>177.8140165634392</v>
+        <v>176.0781451295325</v>
       </c>
       <c r="E51" t="n">
-        <v>179.8291778564453</v>
+        <v>176.5769500732422</v>
       </c>
       <c r="F51" t="n">
-        <v>183852000</v>
+        <v>121332800</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B52" t="n">
-        <v>178.5821404669205</v>
+        <v>174.3423189563235</v>
       </c>
       <c r="C52" t="n">
-        <v>178.8614700176124</v>
+        <v>179.8690869073362</v>
       </c>
       <c r="D52" t="n">
-        <v>176.0781451295325</v>
+        <v>173.2648983244765</v>
       </c>
       <c r="E52" t="n">
-        <v>176.5769500732422</v>
+        <v>179.489990234375</v>
       </c>
       <c r="F52" t="n">
-        <v>121332800</v>
+        <v>188131000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B53" t="n">
-        <v>174.3423041351479</v>
+        <v>181.3255769560617</v>
       </c>
       <c r="C53" t="n">
-        <v>179.8690716163194</v>
+        <v>185.2162648499111</v>
       </c>
       <c r="D53" t="n">
-        <v>173.2648835948944</v>
+        <v>179.569788944198</v>
       </c>
       <c r="E53" t="n">
-        <v>179.4899749755859</v>
+        <v>181.0263061523438</v>
       </c>
       <c r="F53" t="n">
-        <v>188131000</v>
+        <v>182632200</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B54" t="n">
-        <v>181.3255769560617</v>
+        <v>180.6472109015755</v>
       </c>
       <c r="C54" t="n">
-        <v>185.2162648499111</v>
+        <v>182.0139316568558</v>
       </c>
       <c r="D54" t="n">
-        <v>179.569788944198</v>
+        <v>178.681918089591</v>
       </c>
       <c r="E54" t="n">
-        <v>181.0263061523438</v>
+        <v>179.1607666015625</v>
       </c>
       <c r="F54" t="n">
-        <v>182632200</v>
+        <v>165138000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,25 +1847,25 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B55" t="n">
-        <v>180.6472109015755</v>
+        <v>181.1959881613664</v>
       </c>
       <c r="C55" t="n">
-        <v>182.0139316568558</v>
+        <v>184.089227004522</v>
       </c>
       <c r="D55" t="n">
-        <v>178.681918089591</v>
+        <v>179.5398751387779</v>
       </c>
       <c r="E55" t="n">
-        <v>179.1607666015625</v>
+        <v>182.9518890380859</v>
       </c>
       <c r="F55" t="n">
-        <v>165138000</v>
+        <v>167364900</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1873,25 +1873,25 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B56" t="n">
-        <v>181.1960032737075</v>
+        <v>183.4607020047171</v>
       </c>
       <c r="C56" t="n">
-        <v>184.0892423581687</v>
+        <v>184.2289086763207</v>
       </c>
       <c r="D56" t="n">
-        <v>179.5398901129937</v>
+        <v>180.4876631773748</v>
       </c>
       <c r="E56" t="n">
-        <v>182.951904296875</v>
+        <v>181.9841613769531</v>
       </c>
       <c r="F56" t="n">
-        <v>167364900</v>
+        <v>143971100</v>
       </c>
       <c r="G56" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B57" t="n">
-        <v>183.4607020047171</v>
+        <v>182.2136112701494</v>
       </c>
       <c r="C57" t="n">
-        <v>184.2289086763207</v>
+        <v>187.5610985176648</v>
       </c>
       <c r="D57" t="n">
-        <v>180.4876631773748</v>
+        <v>181.9741660895743</v>
       </c>
       <c r="E57" t="n">
-        <v>181.9841613769531</v>
+        <v>185.1168212890625</v>
       </c>
       <c r="F57" t="n">
-        <v>143971100</v>
+        <v>204378100</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B58" t="n">
-        <v>182.2136112701494</v>
+        <v>185.1268117532098</v>
       </c>
       <c r="C58" t="n">
-        <v>187.5610985176648</v>
+        <v>185.2864418902268</v>
       </c>
       <c r="D58" t="n">
-        <v>181.9741660895743</v>
+        <v>182.8920507276432</v>
       </c>
       <c r="E58" t="n">
-        <v>185.1168212890625</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="F58" t="n">
-        <v>204378100</v>
+        <v>144719700</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B59" t="n">
-        <v>185.1268117532098</v>
+        <v>184.538176449994</v>
       </c>
       <c r="C59" t="n">
-        <v>185.2864418902268</v>
+        <v>185.0469803407326</v>
       </c>
       <c r="D59" t="n">
-        <v>182.8920507276432</v>
+        <v>181.6150088138297</v>
       </c>
       <c r="E59" t="n">
-        <v>184.5381927490234</v>
+        <v>183.3509521484375</v>
       </c>
       <c r="F59" t="n">
-        <v>144719700</v>
+        <v>162785400</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B60" t="n">
-        <v>184.538176449994</v>
+        <v>179.8591224369562</v>
       </c>
       <c r="C60" t="n">
-        <v>185.0469803407326</v>
+        <v>180.8967030087509</v>
       </c>
       <c r="D60" t="n">
-        <v>181.6150088138297</v>
+        <v>176.2076633109278</v>
       </c>
       <c r="E60" t="n">
-        <v>183.3509521484375</v>
+        <v>180.5075988769531</v>
       </c>
       <c r="F60" t="n">
-        <v>162785400</v>
+        <v>182136600</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B61" t="n">
-        <v>179.8591224369562</v>
+        <v>180.6871989054384</v>
       </c>
       <c r="C61" t="n">
-        <v>180.8967030087509</v>
+        <v>182.3932136047752</v>
       </c>
       <c r="D61" t="n">
-        <v>176.2076633109278</v>
+        <v>174.2123443447362</v>
       </c>
       <c r="E61" t="n">
-        <v>180.5075988769531</v>
+        <v>174.6114196777344</v>
       </c>
       <c r="F61" t="n">
-        <v>182136600</v>
+        <v>204274900</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B62" t="n">
-        <v>180.6871831157045</v>
+        <v>177.5245903328353</v>
       </c>
       <c r="C62" t="n">
-        <v>182.3931976659576</v>
+        <v>178.0034654802094</v>
       </c>
       <c r="D62" t="n">
-        <v>174.2123291208211</v>
+        <v>174.6213802569945</v>
       </c>
       <c r="E62" t="n">
-        <v>174.6114044189453</v>
+        <v>175.8784332275391</v>
       </c>
       <c r="F62" t="n">
-        <v>204274900</v>
+        <v>164775600</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B63" t="n">
-        <v>177.5245903328353</v>
+        <v>175.8485012773324</v>
       </c>
       <c r="C63" t="n">
-        <v>178.0034654802094</v>
+        <v>178.0733061224419</v>
       </c>
       <c r="D63" t="n">
-        <v>174.6213802569945</v>
+        <v>174.4916756985292</v>
       </c>
       <c r="E63" t="n">
-        <v>175.8784332275391</v>
+        <v>177.3050994873047</v>
       </c>
       <c r="F63" t="n">
-        <v>164775600</v>
+        <v>148588100</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B64" t="n">
-        <v>175.8485164107673</v>
+        <v>175.6888968536916</v>
       </c>
       <c r="C64" t="n">
-        <v>178.0733214473424</v>
+        <v>175.7188256001934</v>
       </c>
       <c r="D64" t="n">
-        <v>174.4916907151964</v>
+        <v>169.9124052081842</v>
       </c>
       <c r="E64" t="n">
-        <v>177.3051147460938</v>
+        <v>170.5409393310547</v>
       </c>
       <c r="F64" t="n">
-        <v>148588100</v>
+        <v>222775500</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B65" t="n">
-        <v>175.6888968536916</v>
+        <v>174.1225483861358</v>
       </c>
       <c r="C65" t="n">
-        <v>175.7188256001934</v>
+        <v>175.7387615308714</v>
       </c>
       <c r="D65" t="n">
-        <v>169.9124052081842</v>
+        <v>171.4188835631069</v>
       </c>
       <c r="E65" t="n">
-        <v>170.5409393310547</v>
+        <v>173.7334594726562</v>
       </c>
       <c r="F65" t="n">
-        <v>222775500</v>
+        <v>176096000</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B66" t="n">
-        <v>174.1225483861358</v>
+        <v>176.2575523358494</v>
       </c>
       <c r="C66" t="n">
-        <v>175.7387615308714</v>
+        <v>181.0263919449467</v>
       </c>
       <c r="D66" t="n">
-        <v>171.4188835631069</v>
+        <v>175.9283209122297</v>
       </c>
       <c r="E66" t="n">
-        <v>173.7334594726562</v>
+        <v>180.5674743652344</v>
       </c>
       <c r="F66" t="n">
-        <v>176096000</v>
+        <v>324925900</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B67" t="n">
-        <v>176.2575523358494</v>
+        <v>183.4906282252173</v>
       </c>
       <c r="C67" t="n">
-        <v>181.0263919449467</v>
+        <v>183.7300734141942</v>
       </c>
       <c r="D67" t="n">
-        <v>175.9283209122297</v>
+        <v>181.9243013805983</v>
       </c>
       <c r="E67" t="n">
-        <v>180.5674743652344</v>
+        <v>183.2611694335938</v>
       </c>
       <c r="F67" t="n">
-        <v>324925900</v>
+        <v>129064400</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B68" t="n">
-        <v>183.4906129473229</v>
+        <v>182.5428571096804</v>
       </c>
       <c r="C68" t="n">
-        <v>183.730058116363</v>
+        <v>188.8880102762506</v>
       </c>
       <c r="D68" t="n">
-        <v>181.9242862331203</v>
+        <v>182.4730132178061</v>
       </c>
       <c r="E68" t="n">
-        <v>183.2611541748047</v>
+        <v>188.7682952880859</v>
       </c>
       <c r="F68" t="n">
-        <v>129064400</v>
+        <v>174873600</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B69" t="n">
-        <v>182.5428571096804</v>
+        <v>187.5012437217294</v>
       </c>
       <c r="C69" t="n">
-        <v>188.8880102762506</v>
+        <v>188.4689804086018</v>
       </c>
       <c r="D69" t="n">
-        <v>182.4730132178061</v>
+        <v>186.154389299292</v>
       </c>
       <c r="E69" t="n">
-        <v>188.7682952880859</v>
+        <v>188.169677734375</v>
       </c>
       <c r="F69" t="n">
-        <v>174873600</v>
+        <v>65528500</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B70" t="n">
-        <v>187.5012437217294</v>
+        <v>189.4766285187414</v>
       </c>
       <c r="C70" t="n">
-        <v>188.4689804086018</v>
+        <v>192.240166195598</v>
       </c>
       <c r="D70" t="n">
-        <v>186.154389299292</v>
+        <v>187.5611125998212</v>
       </c>
       <c r="E70" t="n">
-        <v>188.169677734375</v>
+        <v>190.085205078125</v>
       </c>
       <c r="F70" t="n">
-        <v>65528500</v>
+        <v>139740300</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B71" t="n">
-        <v>189.4766133088049</v>
+        <v>187.2717899684254</v>
       </c>
       <c r="C71" t="n">
-        <v>192.2401507638228</v>
+        <v>188.3193265216257</v>
       </c>
       <c r="D71" t="n">
-        <v>187.5610975436497</v>
+        <v>185.4759890979627</v>
       </c>
       <c r="E71" t="n">
-        <v>190.0851898193359</v>
+        <v>187.7805938720703</v>
       </c>
       <c r="F71" t="n">
-        <v>139740300</v>
+        <v>120006100</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B72" t="n">
-        <v>187.2717899684254</v>
+        <v>187.8005661647843</v>
       </c>
       <c r="C72" t="n">
-        <v>188.3193265216257</v>
+        <v>188.5488153175326</v>
       </c>
       <c r="D72" t="n">
-        <v>185.4759890979627</v>
+        <v>186.4936115238563</v>
       </c>
       <c r="E72" t="n">
-        <v>187.7805938720703</v>
+        <v>187.1021881103516</v>
       </c>
       <c r="F72" t="n">
-        <v>120006100</v>
+        <v>97687300</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B73" t="n">
-        <v>187.8005508490403</v>
+        <v>189.1274459397885</v>
       </c>
       <c r="C73" t="n">
-        <v>188.5487999407664</v>
+        <v>190.1151249886817</v>
       </c>
       <c r="D73" t="n">
-        <v>186.4935963146986</v>
+        <v>186.0546345387688</v>
       </c>
       <c r="E73" t="n">
-        <v>187.1021728515625</v>
+        <v>186.0646057128906</v>
       </c>
       <c r="F73" t="n">
-        <v>97687300</v>
+        <v>120100500</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B74" t="n">
-        <v>189.127461449755</v>
+        <v>189.3968130035911</v>
       </c>
       <c r="C74" t="n">
-        <v>190.1151405796458</v>
+        <v>192.4795957147097</v>
       </c>
       <c r="D74" t="n">
-        <v>186.0546497967401</v>
+        <v>187.8204997023152</v>
       </c>
       <c r="E74" t="n">
-        <v>186.0646209716797</v>
+        <v>188.4091339111328</v>
       </c>
       <c r="F74" t="n">
-        <v>120100500</v>
+        <v>148240500</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B75" t="n">
-        <v>189.3967976648124</v>
+        <v>191.3123337767646</v>
       </c>
       <c r="C75" t="n">
-        <v>192.479580126264</v>
+        <v>193.1779786425506</v>
       </c>
       <c r="D75" t="n">
-        <v>187.8204844911982</v>
+        <v>185.7154296257417</v>
       </c>
       <c r="E75" t="n">
-        <v>188.4091186523438</v>
+        <v>187.6808319091797</v>
       </c>
       <c r="F75" t="n">
-        <v>148240500</v>
+        <v>183529700</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B76" t="n">
-        <v>191.3123337767646</v>
+        <v>190.0752439930999</v>
       </c>
       <c r="C76" t="n">
-        <v>193.1779786425506</v>
+        <v>191.7213860539245</v>
       </c>
       <c r="D76" t="n">
-        <v>185.7154296257417</v>
+        <v>186.3838845193456</v>
       </c>
       <c r="E76" t="n">
-        <v>187.6808319091797</v>
+        <v>186.8029022216797</v>
       </c>
       <c r="F76" t="n">
-        <v>183529700</v>
+        <v>176862600</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B77" t="n">
-        <v>190.0752284670132</v>
+        <v>188.1297854095839</v>
       </c>
       <c r="C77" t="n">
-        <v>191.7213703933745</v>
+        <v>190.9232365533545</v>
       </c>
       <c r="D77" t="n">
-        <v>186.3838692947835</v>
+        <v>186.1244680675316</v>
       </c>
       <c r="E77" t="n">
-        <v>186.8028869628906</v>
+        <v>188.6685180664062</v>
       </c>
       <c r="F77" t="n">
-        <v>176862600</v>
+        <v>153543200</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B78" t="n">
-        <v>188.1297701943655</v>
+        <v>188.6685072554968</v>
       </c>
       <c r="C78" t="n">
-        <v>190.9232211122124</v>
+        <v>189.1074824738404</v>
       </c>
       <c r="D78" t="n">
-        <v>186.1244530144955</v>
+        <v>183.2811201033086</v>
       </c>
       <c r="E78" t="n">
-        <v>188.6685028076172</v>
+        <v>184.6080017089844</v>
       </c>
       <c r="F78" t="n">
-        <v>153543200</v>
+        <v>172457000</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B79" t="n">
-        <v>188.6685228499072</v>
+        <v>184.6479238968445</v>
       </c>
       <c r="C79" t="n">
-        <v>189.1074981045344</v>
+        <v>185.9049768874807</v>
       </c>
       <c r="D79" t="n">
-        <v>183.2811352524241</v>
+        <v>183.2412119543349</v>
       </c>
       <c r="E79" t="n">
-        <v>184.6080169677734</v>
+        <v>184.4284362792969</v>
       </c>
       <c r="F79" t="n">
-        <v>172457000</v>
+        <v>131327500</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B80" t="n">
-        <v>184.6479238968445</v>
+        <v>182.7922691735387</v>
       </c>
       <c r="C80" t="n">
-        <v>185.9049768874807</v>
+        <v>186.6831584288149</v>
       </c>
       <c r="D80" t="n">
-        <v>183.2412119543349</v>
+        <v>182.5927391235801</v>
       </c>
       <c r="E80" t="n">
-        <v>184.4284362792969</v>
+        <v>184.5082550048828</v>
       </c>
       <c r="F80" t="n">
-        <v>131327500</v>
+        <v>137968500</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B81" t="n">
-        <v>182.7922691735387</v>
+        <v>184.5681140987238</v>
       </c>
       <c r="C81" t="n">
-        <v>186.6831584288149</v>
+        <v>187.6708543554723</v>
       </c>
       <c r="D81" t="n">
-        <v>182.5927391235801</v>
+        <v>182.9718432388734</v>
       </c>
       <c r="E81" t="n">
-        <v>184.5082550048828</v>
+        <v>185.376220703125</v>
       </c>
       <c r="F81" t="n">
-        <v>137968500</v>
+        <v>160128900</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B82" t="n">
-        <v>184.5681140987238</v>
+        <v>183.8897012556695</v>
       </c>
       <c r="C82" t="n">
-        <v>187.6708543554723</v>
+        <v>184.0293738083791</v>
       </c>
       <c r="D82" t="n">
-        <v>182.9718432388734</v>
+        <v>180.3779146434709</v>
       </c>
       <c r="E82" t="n">
-        <v>185.376220703125</v>
+        <v>182.7124481201172</v>
       </c>
       <c r="F82" t="n">
-        <v>160128900</v>
+        <v>159586100</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B83" t="n">
-        <v>183.8897012556695</v>
+        <v>186.0646079796491</v>
       </c>
       <c r="C83" t="n">
-        <v>184.0293738083791</v>
+        <v>189.2571344016907</v>
       </c>
       <c r="D83" t="n">
-        <v>180.3779146434709</v>
+        <v>185.895006678512</v>
       </c>
       <c r="E83" t="n">
-        <v>182.7124481201172</v>
+        <v>186.6133270263672</v>
       </c>
       <c r="F83" t="n">
-        <v>159586100</v>
+        <v>206188600</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B84" t="n">
-        <v>186.0646079796491</v>
+        <v>188.6385950815971</v>
       </c>
       <c r="C84" t="n">
-        <v>189.2571344016907</v>
+        <v>189.9954207742267</v>
       </c>
       <c r="D84" t="n">
-        <v>185.895006678512</v>
+        <v>185.6455985734289</v>
       </c>
       <c r="E84" t="n">
-        <v>186.6133270263672</v>
+        <v>185.7952423095703</v>
       </c>
       <c r="F84" t="n">
-        <v>206188600</v>
+        <v>187967200</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B85" t="n">
-        <v>188.6385795892923</v>
+        <v>181.4753266272146</v>
       </c>
       <c r="C85" t="n">
-        <v>189.99540517049</v>
+        <v>181.9542169705431</v>
       </c>
       <c r="D85" t="n">
-        <v>185.6455833269296</v>
+        <v>177.1953488429791</v>
       </c>
       <c r="E85" t="n">
-        <v>185.7952270507812</v>
+        <v>177.6542816162109</v>
       </c>
       <c r="F85" t="n">
-        <v>187967200</v>
+        <v>223345300</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B86" t="n">
-        <v>181.4753266272146</v>
+        <v>178.6320081827799</v>
       </c>
       <c r="C86" t="n">
-        <v>181.9542169705431</v>
+        <v>184.9472325313386</v>
       </c>
       <c r="D86" t="n">
-        <v>177.1953488429791</v>
+        <v>177.9835164834521</v>
       </c>
       <c r="E86" t="n">
-        <v>177.6542816162109</v>
+        <v>182.8920440673828</v>
       </c>
       <c r="F86" t="n">
-        <v>223345300</v>
+        <v>200381000</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B87" t="n">
-        <v>178.6320081827799</v>
+        <v>184.3186915464293</v>
       </c>
       <c r="C87" t="n">
-        <v>184.9472325313386</v>
+        <v>185.7353746560278</v>
       </c>
       <c r="D87" t="n">
-        <v>177.9835164834521</v>
+        <v>183.5005985718231</v>
       </c>
       <c r="E87" t="n">
-        <v>182.8920440673828</v>
+        <v>184.4084777832031</v>
       </c>
       <c r="F87" t="n">
-        <v>200381000</v>
+        <v>139636600</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B88" t="n">
-        <v>184.3186915464293</v>
+        <v>187.0622712594319</v>
       </c>
       <c r="C88" t="n">
-        <v>185.7353746560278</v>
+        <v>189.1573747868041</v>
       </c>
       <c r="D88" t="n">
-        <v>183.5005985718231</v>
+        <v>186.3838660627843</v>
       </c>
       <c r="E88" t="n">
-        <v>184.4084777832031</v>
+        <v>187.2318725585938</v>
       </c>
       <c r="F88" t="n">
-        <v>139636600</v>
+        <v>142748100</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B89" t="n">
-        <v>187.0622712594319</v>
+        <v>186.7230595290241</v>
       </c>
       <c r="C89" t="n">
-        <v>189.1573747868041</v>
+        <v>188.6784751839824</v>
       </c>
       <c r="D89" t="n">
-        <v>186.3838660627843</v>
+        <v>185.5557928402329</v>
       </c>
       <c r="E89" t="n">
-        <v>187.2318725585938</v>
+        <v>186.03466796875</v>
       </c>
       <c r="F89" t="n">
-        <v>142748100</v>
+        <v>124799600</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B90" t="n">
-        <v>186.7230748442759</v>
+        <v>186.8028844605491</v>
       </c>
       <c r="C90" t="n">
-        <v>188.6784906596197</v>
+        <v>189.5564356240106</v>
       </c>
       <c r="D90" t="n">
-        <v>185.555808059744</v>
+        <v>185.2664711415707</v>
       </c>
       <c r="E90" t="n">
-        <v>186.0346832275391</v>
+        <v>188.0798950195312</v>
       </c>
       <c r="F90" t="n">
-        <v>124799600</v>
+        <v>143711600</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B91" t="n">
-        <v>186.8028844605491</v>
+        <v>190.823459633995</v>
       </c>
       <c r="C91" t="n">
-        <v>189.5564356240106</v>
+        <v>191.9009400606663</v>
       </c>
       <c r="D91" t="n">
-        <v>185.2664711415707</v>
+        <v>189.3967902384632</v>
       </c>
       <c r="E91" t="n">
-        <v>188.0798950195312</v>
+        <v>191.0728759765625</v>
       </c>
       <c r="F91" t="n">
-        <v>143711600</v>
+        <v>148552700</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B92" t="n">
-        <v>190.8234748728661</v>
+        <v>190.8933105997472</v>
       </c>
       <c r="C92" t="n">
-        <v>191.9009553855833</v>
+        <v>193.0283141326731</v>
       </c>
       <c r="D92" t="n">
-        <v>189.3968053634026</v>
+        <v>185.6256380470483</v>
       </c>
       <c r="E92" t="n">
-        <v>191.0728912353516</v>
+        <v>192.0605773925781</v>
       </c>
       <c r="F92" t="n">
-        <v>148552700</v>
+        <v>171764400</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B93" t="n">
-        <v>190.8932954336949</v>
+        <v>190.7636224379378</v>
       </c>
       <c r="C93" t="n">
-        <v>193.0282987969995</v>
+        <v>194.0359639826301</v>
       </c>
       <c r="D93" t="n">
-        <v>185.625623299501</v>
+        <v>189.0276790286862</v>
       </c>
       <c r="E93" t="n">
-        <v>192.0605621337891</v>
+        <v>190.6838073730469</v>
       </c>
       <c r="F93" t="n">
-        <v>171764400</v>
+        <v>179489500</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B94" t="n">
-        <v>190.7636071727618</v>
+        <v>186.7629659025267</v>
       </c>
       <c r="C94" t="n">
-        <v>194.0359484555967</v>
+        <v>189.8557348322644</v>
       </c>
       <c r="D94" t="n">
-        <v>189.0276639024229</v>
+        <v>184.4483900153819</v>
       </c>
       <c r="E94" t="n">
-        <v>190.6837921142578</v>
+        <v>185.1766815185547</v>
       </c>
       <c r="F94" t="n">
-        <v>179489500</v>
+        <v>165794100</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B95" t="n">
-        <v>186.7629812920276</v>
+        <v>185.8052108647954</v>
       </c>
       <c r="C95" t="n">
-        <v>189.8557504766133</v>
+        <v>185.8351396091497</v>
       </c>
       <c r="D95" t="n">
-        <v>184.4484052141589</v>
+        <v>175.8185703987175</v>
       </c>
       <c r="E95" t="n">
-        <v>185.1766967773438</v>
+        <v>179.9189758300781</v>
       </c>
       <c r="F95" t="n">
-        <v>165794100</v>
+        <v>204019600</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B96" t="n">
-        <v>185.8052108647954</v>
+        <v>179.0410571553003</v>
       </c>
       <c r="C96" t="n">
-        <v>185.8351396091497</v>
+        <v>179.1607721437711</v>
       </c>
       <c r="D96" t="n">
-        <v>175.8185703987175</v>
+        <v>171.5086795929406</v>
       </c>
       <c r="E96" t="n">
-        <v>179.9189758300781</v>
+        <v>173.7833557128906</v>
       </c>
       <c r="F96" t="n">
-        <v>204019600</v>
+        <v>207014100</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B97" t="n">
-        <v>179.0410414348666</v>
+        <v>174.5216119878791</v>
       </c>
       <c r="C97" t="n">
-        <v>179.160756412826</v>
+        <v>176.4072143255947</v>
       </c>
       <c r="D97" t="n">
-        <v>171.5086645338761</v>
+        <v>170.6307227747363</v>
       </c>
       <c r="E97" t="n">
-        <v>173.7833404541016</v>
+        <v>171.4787445068359</v>
       </c>
       <c r="F97" t="n">
-        <v>207014100</v>
+        <v>206312900</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B98" t="n">
-        <v>174.5215964583249</v>
+        <v>176.2775135166603</v>
       </c>
       <c r="C98" t="n">
-        <v>176.4071986282528</v>
+        <v>186.5634420291942</v>
       </c>
       <c r="D98" t="n">
-        <v>170.6307075914073</v>
+        <v>174.1923963475411</v>
       </c>
       <c r="E98" t="n">
-        <v>171.4787292480469</v>
+        <v>184.9771575927734</v>
       </c>
       <c r="F98" t="n">
-        <v>206312900</v>
+        <v>231346200</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B99" t="n">
-        <v>176.277498975506</v>
+        <v>183.8298386502086</v>
       </c>
       <c r="C99" t="n">
-        <v>186.5634266395524</v>
+        <v>193.2079034382237</v>
       </c>
       <c r="D99" t="n">
-        <v>174.1923819783884</v>
+        <v>183.5205647824287</v>
       </c>
       <c r="E99" t="n">
-        <v>184.9771423339844</v>
+        <v>189.5963439941406</v>
       </c>
       <c r="F99" t="n">
-        <v>231346200</v>
+        <v>196387400</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B100" t="n">
-        <v>183.8298238555102</v>
+        <v>190.933219719687</v>
       </c>
       <c r="C100" t="n">
-        <v>193.2078878887748</v>
+        <v>192.0306425866914</v>
       </c>
       <c r="D100" t="n">
-        <v>183.5205500126207</v>
+        <v>187.6808205923615</v>
       </c>
       <c r="E100" t="n">
-        <v>189.5963287353516</v>
+        <v>188.0998382568359</v>
       </c>
       <c r="F100" t="n">
-        <v>196387400</v>
+        <v>136764800</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B101" t="n">
-        <v>190.933219719687</v>
+        <v>192.0007297023972</v>
       </c>
       <c r="C101" t="n">
-        <v>192.0306425866914</v>
+        <v>192.8088363522974</v>
       </c>
       <c r="D101" t="n">
-        <v>187.6808205923615</v>
+        <v>188.3293278304631</v>
       </c>
       <c r="E101" t="n">
-        <v>188.0998382568359</v>
+        <v>189.6063385009766</v>
       </c>
       <c r="F101" t="n">
-        <v>136764800</v>
+        <v>144192700</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B102" t="n">
-        <v>192.0007297023972</v>
+        <v>192.5793806436633</v>
       </c>
       <c r="C102" t="n">
-        <v>192.8088363522974</v>
+        <v>193.158028491682</v>
       </c>
       <c r="D102" t="n">
-        <v>188.3293278304631</v>
+        <v>186.0745969700116</v>
       </c>
       <c r="E102" t="n">
-        <v>189.6063385009766</v>
+        <v>186.5036010742188</v>
       </c>
       <c r="F102" t="n">
-        <v>144192700</v>
+        <v>189932500</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B103" t="n">
-        <v>192.5793648877844</v>
+        <v>187.0423048169314</v>
       </c>
       <c r="C103" t="n">
-        <v>193.1580126884611</v>
+        <v>187.0622623874058</v>
       </c>
       <c r="D103" t="n">
-        <v>186.0745817463215</v>
+        <v>181.1660562233949</v>
       </c>
       <c r="E103" t="n">
-        <v>186.5035858154297</v>
+        <v>182.3832092285156</v>
       </c>
       <c r="F103" t="n">
-        <v>189932500</v>
+        <v>161888000</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B104" t="n">
-        <v>187.042320465516</v>
+        <v>181.3257085516038</v>
       </c>
       <c r="C104" t="n">
-        <v>187.0622780376601</v>
+        <v>186.7130962790006</v>
       </c>
       <c r="D104" t="n">
-        <v>181.1660713803529</v>
+        <v>178.7617008539599</v>
       </c>
       <c r="E104" t="n">
-        <v>182.3832244873047</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="F104" t="n">
-        <v>161888000</v>
+        <v>162276900</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B105" t="n">
-        <v>181.3257085516038</v>
+        <v>188.3093443160685</v>
       </c>
       <c r="C105" t="n">
-        <v>186.7130962790006</v>
+        <v>189.9255573932224</v>
       </c>
       <c r="D105" t="n">
-        <v>178.7617008539599</v>
+        <v>186.3239846890322</v>
       </c>
       <c r="E105" t="n">
-        <v>184.5381927490234</v>
+        <v>187.5411376953125</v>
       </c>
       <c r="F105" t="n">
-        <v>162276900</v>
+        <v>164749100</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B106" t="n">
-        <v>188.3093443160685</v>
+        <v>186.6232837033845</v>
       </c>
       <c r="C106" t="n">
-        <v>189.9255573932224</v>
+        <v>187.9900804037161</v>
       </c>
       <c r="D106" t="n">
-        <v>186.3239846890322</v>
+        <v>185.226558259481</v>
       </c>
       <c r="E106" t="n">
-        <v>187.5411376953125</v>
+        <v>187.4613189697266</v>
       </c>
       <c r="F106" t="n">
-        <v>164749100</v>
+        <v>126554500</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B107" t="n">
-        <v>186.62329889396</v>
+        <v>186.1344488846578</v>
       </c>
       <c r="C107" t="n">
-        <v>187.9900957055448</v>
+        <v>189.8856654675195</v>
       </c>
       <c r="D107" t="n">
-        <v>185.2265733363672</v>
+        <v>185.5059147845697</v>
       </c>
       <c r="E107" t="n">
-        <v>187.4613342285156</v>
+        <v>189.3768615722656</v>
       </c>
       <c r="F107" t="n">
-        <v>126554500</v>
+        <v>178422300</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B108" t="n">
-        <v>186.1344488846578</v>
+        <v>190.9531547742145</v>
       </c>
       <c r="C108" t="n">
-        <v>189.8856654675195</v>
+        <v>193.4972046328596</v>
       </c>
       <c r="D108" t="n">
-        <v>185.5059147845697</v>
+        <v>189.1374116308485</v>
       </c>
       <c r="E108" t="n">
-        <v>189.3768615722656</v>
+        <v>191.1028137207031</v>
       </c>
       <c r="F108" t="n">
-        <v>178422300</v>
+        <v>171584800</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B109" t="n">
-        <v>190.9531700210539</v>
+        <v>191.0429698590405</v>
       </c>
       <c r="C109" t="n">
-        <v>193.4972200828311</v>
+        <v>193.3176459547985</v>
       </c>
       <c r="D109" t="n">
-        <v>189.1374267327081</v>
+        <v>186.9625064417709</v>
       </c>
       <c r="E109" t="n">
-        <v>191.1028289794922</v>
+        <v>192.3997955322266</v>
       </c>
       <c r="F109" t="n">
-        <v>171584800</v>
+        <v>175123600</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B110" t="n">
-        <v>191.0429698590405</v>
+        <v>193.9960453222018</v>
       </c>
       <c r="C110" t="n">
-        <v>193.3176459547985</v>
+        <v>197.1686293956491</v>
       </c>
       <c r="D110" t="n">
-        <v>186.9625064417709</v>
+        <v>193.3375824661624</v>
       </c>
       <c r="E110" t="n">
-        <v>192.3997955322266</v>
+        <v>195.1034545898438</v>
       </c>
       <c r="F110" t="n">
-        <v>175123600</v>
+        <v>250637100</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B111" t="n">
-        <v>193.9960453222018</v>
+        <v>193.8164813019665</v>
       </c>
       <c r="C111" t="n">
-        <v>197.1686293956491</v>
+        <v>193.8364236513225</v>
       </c>
       <c r="D111" t="n">
-        <v>193.3375824661624</v>
+        <v>183.8897126034445</v>
       </c>
       <c r="E111" t="n">
-        <v>195.1034545898438</v>
+        <v>184.4583740234375</v>
       </c>
       <c r="F111" t="n">
-        <v>250637100</v>
+        <v>360807900</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B112" t="n">
-        <v>193.8164813019665</v>
+        <v>180.82685580423</v>
       </c>
       <c r="C112" t="n">
-        <v>193.8364236513225</v>
+        <v>182.1637238018573</v>
       </c>
       <c r="D112" t="n">
-        <v>183.8897126034445</v>
+        <v>175.9682301224481</v>
       </c>
       <c r="E112" t="n">
-        <v>184.4583740234375</v>
+        <v>176.7763366699219</v>
       </c>
       <c r="F112" t="n">
-        <v>360807900</v>
+        <v>311636500</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B113" t="n">
-        <v>180.8268714126474</v>
+        <v>174.6014088918714</v>
       </c>
       <c r="C113" t="n">
-        <v>182.1637395256691</v>
+        <v>183.0316933488174</v>
       </c>
       <c r="D113" t="n">
-        <v>175.9682453114839</v>
+        <v>174.2322775806792</v>
       </c>
       <c r="E113" t="n">
-        <v>176.7763519287109</v>
+        <v>182.0539703369141</v>
       </c>
       <c r="F113" t="n">
-        <v>311636500</v>
+        <v>209095300</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B114" t="n">
-        <v>174.6014235260267</v>
+        <v>178.0733135069376</v>
       </c>
       <c r="C114" t="n">
-        <v>183.0317086895539</v>
+        <v>180.4776756968921</v>
       </c>
       <c r="D114" t="n">
-        <v>174.2322921838959</v>
+        <v>176.5069714269912</v>
       </c>
       <c r="E114" t="n">
-        <v>182.0539855957031</v>
+        <v>179.6296691894531</v>
       </c>
       <c r="F114" t="n">
-        <v>209095300</v>
+        <v>178099400</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B115" t="n">
-        <v>178.0733135069376</v>
+        <v>180.0187649948852</v>
       </c>
       <c r="C115" t="n">
-        <v>180.4776756968921</v>
+        <v>184.2688145383873</v>
       </c>
       <c r="D115" t="n">
-        <v>176.5069714269912</v>
+        <v>179.6396472340209</v>
       </c>
       <c r="E115" t="n">
-        <v>179.6296691894531</v>
+        <v>182.6126861572266</v>
       </c>
       <c r="F115" t="n">
-        <v>178099400</v>
+        <v>177731200</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B116" t="n">
-        <v>180.0187649948852</v>
+        <v>180.7470399397241</v>
       </c>
       <c r="C116" t="n">
-        <v>184.2688145383873</v>
+        <v>183.6302923567135</v>
       </c>
       <c r="D116" t="n">
-        <v>179.6396472340209</v>
+        <v>177.4647274492447</v>
       </c>
       <c r="E116" t="n">
-        <v>182.6126861572266</v>
+        <v>182.9119720458984</v>
       </c>
       <c r="F116" t="n">
-        <v>177731200</v>
+        <v>198779700</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B117" t="n">
-        <v>180.7470550179114</v>
+        <v>179.420149946886</v>
       </c>
       <c r="C117" t="n">
-        <v>183.6303076754259</v>
+        <v>182.3333312190456</v>
       </c>
       <c r="D117" t="n">
-        <v>177.4647422536165</v>
+        <v>176.407211264142</v>
       </c>
       <c r="E117" t="n">
-        <v>182.9119873046875</v>
+        <v>177.4048767089844</v>
       </c>
       <c r="F117" t="n">
-        <v>198779700</v>
+        <v>189021900</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B118" t="n">
-        <v>179.420134514761</v>
+        <v>176.4171820751478</v>
       </c>
       <c r="C118" t="n">
-        <v>182.3333155363547</v>
+        <v>182.4829897940845</v>
       </c>
       <c r="D118" t="n">
-        <v>176.4071960911633</v>
+        <v>175.1501427003192</v>
       </c>
       <c r="E118" t="n">
-        <v>177.4048614501953</v>
+        <v>182.2235870361328</v>
       </c>
       <c r="F118" t="n">
-        <v>189021900</v>
+        <v>177213600</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B119" t="n">
-        <v>176.4171820751478</v>
+        <v>181.9741760435397</v>
       </c>
       <c r="C119" t="n">
-        <v>182.4829897940845</v>
+        <v>186.0047530762794</v>
       </c>
       <c r="D119" t="n">
-        <v>175.1501427003192</v>
+        <v>181.5850871183009</v>
       </c>
       <c r="E119" t="n">
-        <v>182.2235870361328</v>
+        <v>184.3386535644531</v>
       </c>
       <c r="F119" t="n">
-        <v>177213600</v>
+        <v>179118500</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,25 +3537,25 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B120" t="n">
-        <v>181.9741760435397</v>
+        <v>185.4860219488843</v>
       </c>
       <c r="C120" t="n">
-        <v>186.0047530762794</v>
+        <v>187.1921136401388</v>
       </c>
       <c r="D120" t="n">
-        <v>181.5850871183009</v>
+        <v>184.0293448898806</v>
       </c>
       <c r="E120" t="n">
-        <v>184.3386535644531</v>
+        <v>185.6057434082031</v>
       </c>
       <c r="F120" t="n">
-        <v>179118500</v>
+        <v>145280400</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3563,25 +3563,25 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B121" t="n">
-        <v>185.4860219488843</v>
+        <v>183.6302641505579</v>
       </c>
       <c r="C121" t="n">
-        <v>187.1921136401388</v>
+        <v>184.5182338343672</v>
       </c>
       <c r="D121" t="n">
-        <v>184.0293448898806</v>
+        <v>181.3355064165816</v>
       </c>
       <c r="E121" t="n">
-        <v>185.6057434082031</v>
+        <v>182.7223358154297</v>
       </c>
       <c r="F121" t="n">
-        <v>145280400</v>
+        <v>155762700</v>
       </c>
       <c r="G121" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B122" t="n">
-        <v>183.6302641505579</v>
+        <v>184.4982918130038</v>
       </c>
       <c r="C122" t="n">
-        <v>184.5182338343672</v>
+        <v>185.6656218245341</v>
       </c>
       <c r="D122" t="n">
-        <v>181.3355064165816</v>
+        <v>179.5296528660815</v>
       </c>
       <c r="E122" t="n">
-        <v>182.7223358154297</v>
+        <v>179.8389434814453</v>
       </c>
       <c r="F122" t="n">
-        <v>155762700</v>
+        <v>160988400</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B123" t="n">
-        <v>184.4982918130038</v>
+        <v>182.5527246843909</v>
       </c>
       <c r="C123" t="n">
-        <v>185.6656218245341</v>
+        <v>188.4492501487561</v>
       </c>
       <c r="D123" t="n">
-        <v>179.5296528660815</v>
+        <v>180.9962848148914</v>
       </c>
       <c r="E123" t="n">
-        <v>179.8389434814453</v>
+        <v>182.8021545410156</v>
       </c>
       <c r="F123" t="n">
-        <v>160988400</v>
+        <v>217307400</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B124" t="n">
-        <v>182.5527246843909</v>
+        <v>184.6379731916982</v>
       </c>
       <c r="C124" t="n">
-        <v>188.4492501487561</v>
+        <v>184.9771941770484</v>
       </c>
       <c r="D124" t="n">
-        <v>180.9962848148914</v>
+        <v>181.2656763194747</v>
       </c>
       <c r="E124" t="n">
-        <v>182.8021545410156</v>
+        <v>181.5151062011719</v>
       </c>
       <c r="F124" t="n">
-        <v>217307400</v>
+        <v>182497800</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B125" t="n">
-        <v>184.6379731916982</v>
+        <v>182.0638447517288</v>
       </c>
       <c r="C125" t="n">
-        <v>184.9771941770484</v>
+        <v>182.9618014097589</v>
       </c>
       <c r="D125" t="n">
-        <v>181.2656763194747</v>
+        <v>179.9187539793071</v>
       </c>
       <c r="E125" t="n">
-        <v>181.5151062011719</v>
+        <v>179.9885864257812</v>
       </c>
       <c r="F125" t="n">
-        <v>182497800</v>
+        <v>156683100</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B126" t="n">
-        <v>182.0638447517288</v>
+        <v>177.6040222894031</v>
       </c>
       <c r="C126" t="n">
-        <v>182.9618014097589</v>
+        <v>179.5695306962835</v>
       </c>
       <c r="D126" t="n">
-        <v>179.9187539793071</v>
+        <v>175.3890840362079</v>
       </c>
       <c r="E126" t="n">
-        <v>179.9885864257812</v>
+        <v>178.1527709960938</v>
       </c>
       <c r="F126" t="n">
-        <v>156683100</v>
+        <v>170968500</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B127" t="n">
-        <v>177.6040222894031</v>
+        <v>177.5940686691464</v>
       </c>
       <c r="C127" t="n">
-        <v>179.5695306962835</v>
+        <v>177.853470255105</v>
       </c>
       <c r="D127" t="n">
-        <v>175.3890840362079</v>
+        <v>171.3283915093003</v>
       </c>
       <c r="E127" t="n">
-        <v>178.1527709960938</v>
+        <v>172.30615234375</v>
       </c>
       <c r="F127" t="n">
-        <v>170968500</v>
+        <v>241323500</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B128" t="n">
-        <v>177.5940686691464</v>
+        <v>176.8557415306554</v>
       </c>
       <c r="C128" t="n">
-        <v>177.853470255105</v>
+        <v>177.9632107122345</v>
       </c>
       <c r="D128" t="n">
-        <v>171.3283915093003</v>
+        <v>174.3614429436745</v>
       </c>
       <c r="E128" t="n">
-        <v>172.30615234375</v>
+        <v>175.2394409179688</v>
       </c>
       <c r="F128" t="n">
-        <v>241323500</v>
+        <v>182836300</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B129" t="n">
-        <v>176.8557415306554</v>
+        <v>174.4312942297872</v>
       </c>
       <c r="C129" t="n">
-        <v>177.9632107122345</v>
+        <v>175.8181236639554</v>
       </c>
       <c r="D129" t="n">
-        <v>174.3614429436745</v>
+        <v>173.5832266030264</v>
       </c>
       <c r="E129" t="n">
-        <v>175.2394409179688</v>
+        <v>174.8004455566406</v>
       </c>
       <c r="F129" t="n">
-        <v>182836300</v>
+        <v>147667800</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B130" t="n">
-        <v>174.4312942297872</v>
+        <v>176.6961233561449</v>
       </c>
       <c r="C130" t="n">
-        <v>175.8181236639554</v>
+        <v>180.8067226806179</v>
       </c>
       <c r="D130" t="n">
-        <v>173.5832266030264</v>
+        <v>176.4466934898736</v>
       </c>
       <c r="E130" t="n">
-        <v>174.8004455566406</v>
+        <v>178.2725067138672</v>
       </c>
       <c r="F130" t="n">
-        <v>147667800</v>
+        <v>162602100</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B131" t="n">
-        <v>176.6961233561449</v>
+        <v>175.6684741654964</v>
       </c>
       <c r="C131" t="n">
-        <v>180.8067226806179</v>
+        <v>176.1074579435819</v>
       </c>
       <c r="D131" t="n">
-        <v>176.4466934898736</v>
+        <v>170.7497092682189</v>
       </c>
       <c r="E131" t="n">
-        <v>178.2725067138672</v>
+        <v>170.8494873046875</v>
       </c>
       <c r="F131" t="n">
-        <v>162602100</v>
+        <v>186152200</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B132" t="n">
-        <v>175.6684741654964</v>
+        <v>169.6123099949711</v>
       </c>
       <c r="C132" t="n">
-        <v>176.1074579435819</v>
+        <v>170.5800990993323</v>
       </c>
       <c r="D132" t="n">
-        <v>170.7497092682189</v>
+        <v>166.629123297364</v>
       </c>
       <c r="E132" t="n">
-        <v>170.8494873046875</v>
+        <v>167.1379699707031</v>
       </c>
       <c r="F132" t="n">
-        <v>186152200</v>
+        <v>196212700</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B133" t="n">
-        <v>169.6123099949711</v>
+        <v>168.3950875250076</v>
       </c>
       <c r="C133" t="n">
-        <v>170.5800990993323</v>
+        <v>169.0635577295173</v>
       </c>
       <c r="D133" t="n">
-        <v>166.629123297364</v>
+        <v>163.8953782868944</v>
       </c>
       <c r="E133" t="n">
-        <v>167.1379699707031</v>
+        <v>164.7933197021484</v>
       </c>
       <c r="F133" t="n">
-        <v>196212700</v>
+        <v>185627000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B134" t="n">
-        <v>168.3950875250076</v>
+        <v>166.589210422399</v>
       </c>
       <c r="C134" t="n">
-        <v>169.0635577295173</v>
+        <v>174.2217577880002</v>
       </c>
       <c r="D134" t="n">
-        <v>163.8953782868944</v>
+        <v>166.5792387089764</v>
       </c>
       <c r="E134" t="n">
-        <v>164.7933197021484</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="F134" t="n">
-        <v>185627000</v>
+        <v>226181300</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B135" t="n">
-        <v>166.589210422399</v>
+        <v>175.5986119754623</v>
       </c>
       <c r="C135" t="n">
-        <v>174.2217577880002</v>
+        <v>176.9654826629128</v>
       </c>
       <c r="D135" t="n">
-        <v>166.5792387089764</v>
+        <v>174.351462742682</v>
       </c>
       <c r="E135" t="n">
-        <v>174.0022583007812</v>
+        <v>175.3491821289062</v>
       </c>
       <c r="F135" t="n">
-        <v>226181300</v>
+        <v>168132000</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B136" t="n">
-        <v>175.5986119754623</v>
+        <v>171.787333172162</v>
       </c>
       <c r="C136" t="n">
-        <v>176.9654826629128</v>
+        <v>177.0852364118599</v>
       </c>
       <c r="D136" t="n">
-        <v>174.351462742682</v>
+        <v>170.9791828272563</v>
       </c>
       <c r="E136" t="n">
-        <v>175.3491821289062</v>
+        <v>176.9854583740234</v>
       </c>
       <c r="F136" t="n">
-        <v>168132000</v>
+        <v>143143200</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B137" t="n">
-        <v>171.787333172162</v>
+        <v>176.7559774774269</v>
       </c>
       <c r="C137" t="n">
-        <v>177.0852364118599</v>
+        <v>177.3845303646084</v>
       </c>
       <c r="D137" t="n">
-        <v>170.9791828272563</v>
+        <v>175.3591611441553</v>
       </c>
       <c r="E137" t="n">
-        <v>176.9854583740234</v>
+        <v>177.2348785400391</v>
       </c>
       <c r="F137" t="n">
-        <v>143143200</v>
+        <v>107564300</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B138" t="n">
-        <v>176.7559774774269</v>
+        <v>175.3292270516068</v>
       </c>
       <c r="C138" t="n">
-        <v>177.3845303646084</v>
+        <v>177.8235255680002</v>
       </c>
       <c r="D138" t="n">
-        <v>175.3591611441553</v>
+        <v>173.2639557965079</v>
       </c>
       <c r="E138" t="n">
-        <v>177.2348785400391</v>
+        <v>177.6938323974609</v>
       </c>
       <c r="F138" t="n">
-        <v>107564300</v>
+        <v>132534900</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B139" t="n">
-        <v>175.3292270516068</v>
+        <v>184.079243714486</v>
       </c>
       <c r="C139" t="n">
-        <v>177.8235255680002</v>
+        <v>184.837505037226</v>
       </c>
       <c r="D139" t="n">
-        <v>173.2639557965079</v>
+        <v>179.8888249511496</v>
       </c>
       <c r="E139" t="n">
-        <v>177.6938323974609</v>
+        <v>181.6647644042969</v>
       </c>
       <c r="F139" t="n">
-        <v>132534900</v>
+        <v>147732700</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B140" t="n">
-        <v>184.079243714486</v>
+        <v>181.4253138719204</v>
       </c>
       <c r="C140" t="n">
-        <v>184.837505037226</v>
+        <v>183.6602110774668</v>
       </c>
       <c r="D140" t="n">
-        <v>179.8888249511496</v>
+        <v>180.2080948395415</v>
       </c>
       <c r="E140" t="n">
-        <v>181.6647644042969</v>
+        <v>183.4906005859375</v>
       </c>
       <c r="F140" t="n">
-        <v>147732700</v>
+        <v>116428500</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B141" t="n">
-        <v>181.4253138719204</v>
+        <v>183.8896736698189</v>
       </c>
       <c r="C141" t="n">
-        <v>183.6602110774668</v>
+        <v>189.5666999081706</v>
       </c>
       <c r="D141" t="n">
-        <v>180.2080948395415</v>
+        <v>183.8797019557237</v>
       </c>
       <c r="E141" t="n">
-        <v>183.4906005859375</v>
+        <v>188.1998291015625</v>
       </c>
       <c r="F141" t="n">
-        <v>116428500</v>
+        <v>160459500</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B142" t="n">
-        <v>183.8896736698189</v>
+        <v>185.605746824658</v>
       </c>
       <c r="C142" t="n">
-        <v>189.5666999081706</v>
+        <v>189.2274732756209</v>
       </c>
       <c r="D142" t="n">
-        <v>183.8797019557237</v>
+        <v>185.3164148846483</v>
       </c>
       <c r="E142" t="n">
-        <v>188.1998291015625</v>
+        <v>188.8782653808594</v>
       </c>
       <c r="F142" t="n">
-        <v>160459500</v>
+        <v>133648200</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B143" t="n">
-        <v>185.605746824658</v>
+        <v>190.4047764107204</v>
       </c>
       <c r="C143" t="n">
-        <v>189.2274732756209</v>
+        <v>196.0618438720703</v>
       </c>
       <c r="D143" t="n">
-        <v>185.3164148846483</v>
+        <v>190.3349439656124</v>
       </c>
       <c r="E143" t="n">
-        <v>188.8782653808594</v>
+        <v>196.0618438720703</v>
       </c>
       <c r="F143" t="n">
-        <v>133648200</v>
+        <v>161307000</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B144" t="n">
-        <v>190.4047764107204</v>
+        <v>196.0917851116163</v>
       </c>
       <c r="C144" t="n">
-        <v>196.0618438720703</v>
+        <v>199.9429830157183</v>
       </c>
       <c r="D144" t="n">
-        <v>190.3349439656124</v>
+        <v>195.2936216855987</v>
       </c>
       <c r="E144" t="n">
-        <v>196.0618438720703</v>
+        <v>198.4164733886719</v>
       </c>
       <c r="F144" t="n">
-        <v>161307000</v>
+        <v>185338400</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B145" t="n">
-        <v>196.0917851116163</v>
+        <v>196.9797440092329</v>
       </c>
       <c r="C145" t="n">
-        <v>199.9429830157183</v>
+        <v>199.3942384790618</v>
       </c>
       <c r="D145" t="n">
-        <v>195.2936216855987</v>
+        <v>195.3634433694217</v>
       </c>
       <c r="E145" t="n">
-        <v>198.4164733886719</v>
+        <v>197.8976593017578</v>
       </c>
       <c r="F145" t="n">
-        <v>185338400</v>
+        <v>134012900</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B146" t="n">
-        <v>196.9797440092329</v>
+        <v>199.444107632571</v>
       </c>
       <c r="C146" t="n">
-        <v>199.3942384790618</v>
+        <v>201.2400056483541</v>
       </c>
       <c r="D146" t="n">
-        <v>195.3634433694217</v>
+        <v>198.8155547450397</v>
       </c>
       <c r="E146" t="n">
-        <v>197.8976593017578</v>
+        <v>201.2200469970703</v>
       </c>
       <c r="F146" t="n">
-        <v>134012900</v>
+        <v>160324400</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B147" t="n">
-        <v>199.444107632571</v>
+        <v>199.5239239232554</v>
       </c>
       <c r="C147" t="n">
-        <v>201.2400056483541</v>
+        <v>201.7089318732817</v>
       </c>
       <c r="D147" t="n">
-        <v>198.8155547450397</v>
+        <v>197.3888049886708</v>
       </c>
       <c r="E147" t="n">
-        <v>201.2200469970703</v>
+        <v>201.5991821289062</v>
       </c>
       <c r="F147" t="n">
-        <v>160324400</v>
+        <v>119381400</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B148" t="n">
-        <v>199.5239239232554</v>
+        <v>201.6690479582887</v>
       </c>
       <c r="C148" t="n">
-        <v>201.7089318732817</v>
+        <v>202.2876291783034</v>
       </c>
       <c r="D148" t="n">
-        <v>197.3888049886708</v>
+        <v>198.5461810430697</v>
       </c>
       <c r="E148" t="n">
-        <v>201.5991821289062</v>
+        <v>199.4241790771484</v>
       </c>
       <c r="F148" t="n">
-        <v>119381400</v>
+        <v>107945300</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B149" t="n">
-        <v>201.6690479582887</v>
+        <v>200.5316418294082</v>
       </c>
       <c r="C149" t="n">
-        <v>202.2876291783034</v>
+        <v>202.0381927490234</v>
       </c>
       <c r="D149" t="n">
-        <v>198.5461810430697</v>
+        <v>198.546174602744</v>
       </c>
       <c r="E149" t="n">
-        <v>199.4241790771484</v>
+        <v>202.0381927490234</v>
       </c>
       <c r="F149" t="n">
-        <v>107945300</v>
+        <v>107501000</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B150" t="n">
-        <v>200.5316418294082</v>
+        <v>201.9982837593082</v>
       </c>
       <c r="C150" t="n">
-        <v>202.0381927490234</v>
+        <v>203.3651545152774</v>
       </c>
       <c r="D150" t="n">
-        <v>198.546174602744</v>
+        <v>196.7702284327844</v>
       </c>
       <c r="E150" t="n">
-        <v>202.0381927490234</v>
+        <v>199.1847076416016</v>
       </c>
       <c r="F150" t="n">
-        <v>107501000</v>
+        <v>113561800</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B151" t="n">
-        <v>201.9982837593082</v>
+        <v>199.5039827094276</v>
       </c>
       <c r="C151" t="n">
-        <v>203.3651545152774</v>
+        <v>210.468909435165</v>
       </c>
       <c r="D151" t="n">
-        <v>196.7702284327844</v>
+        <v>199.3543156614425</v>
       </c>
       <c r="E151" t="n">
-        <v>199.1847076416016</v>
+        <v>207.7950286865234</v>
       </c>
       <c r="F151" t="n">
-        <v>113561800</v>
+        <v>214134400</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B152" t="n">
-        <v>199.5039827094276</v>
+        <v>209.1718784416434</v>
       </c>
       <c r="C152" t="n">
-        <v>210.468909435165</v>
+        <v>216.335512072091</v>
       </c>
       <c r="D152" t="n">
-        <v>199.3543156614425</v>
+        <v>206.9070662315077</v>
       </c>
       <c r="E152" t="n">
-        <v>207.7950286865234</v>
+        <v>216.1160125732422</v>
       </c>
       <c r="F152" t="n">
-        <v>214134400</v>
+        <v>187172400</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B153" t="n">
-        <v>209.1718784416434</v>
+        <v>209.0122528840405</v>
       </c>
       <c r="C153" t="n">
-        <v>216.335512072091</v>
+        <v>214.2402930542568</v>
       </c>
       <c r="D153" t="n">
-        <v>206.9070662315077</v>
+        <v>207.7251862691963</v>
       </c>
       <c r="E153" t="n">
-        <v>216.1160125732422</v>
+        <v>212.6838531494141</v>
       </c>
       <c r="F153" t="n">
-        <v>187172400</v>
+        <v>180275400</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B154" t="n">
-        <v>209.0122528840405</v>
+        <v>212.2149257168926</v>
       </c>
       <c r="C154" t="n">
-        <v>214.2402930542568</v>
+        <v>212.2348843687743</v>
       </c>
       <c r="D154" t="n">
-        <v>207.7251862691963</v>
+        <v>207.1066069625242</v>
       </c>
       <c r="E154" t="n">
-        <v>212.6838531494141</v>
+        <v>208.7727966308594</v>
       </c>
       <c r="F154" t="n">
-        <v>180275400</v>
+        <v>123711800</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B155" t="n">
-        <v>212.2149257168926</v>
+        <v>209.4512265433391</v>
       </c>
       <c r="C155" t="n">
-        <v>212.2348843687743</v>
+        <v>209.8203930740204</v>
       </c>
       <c r="D155" t="n">
-        <v>207.1066069625242</v>
+        <v>198.2468419328838</v>
       </c>
       <c r="E155" t="n">
-        <v>208.7727966308594</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="F155" t="n">
-        <v>123711800</v>
+        <v>225239200</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B156" t="n">
-        <v>209.4512265433391</v>
+        <v>200.8209846036705</v>
       </c>
       <c r="C156" t="n">
-        <v>209.8203930740204</v>
+        <v>202.5370634031337</v>
       </c>
       <c r="D156" t="n">
-        <v>198.2468419328838</v>
+        <v>196.6704677294345</v>
       </c>
       <c r="E156" t="n">
-        <v>199.1148681640625</v>
+        <v>197.9974365234375</v>
       </c>
       <c r="F156" t="n">
-        <v>225239200</v>
+        <v>128647000</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B157" t="n">
-        <v>200.8209846036705</v>
+        <v>199.0450218084295</v>
       </c>
       <c r="C157" t="n">
-        <v>202.5370634031337</v>
+        <v>201.2699318245734</v>
       </c>
       <c r="D157" t="n">
-        <v>196.6704677294345</v>
+        <v>194.2958829090753</v>
       </c>
       <c r="E157" t="n">
-        <v>197.9974365234375</v>
+        <v>198.02734375</v>
       </c>
       <c r="F157" t="n">
-        <v>128647000</v>
+        <v>125368100</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B158" t="n">
-        <v>199.0450218084295</v>
+        <v>198.8454820247872</v>
       </c>
       <c r="C158" t="n">
-        <v>201.2699318245734</v>
+        <v>199.7833407086998</v>
       </c>
       <c r="D158" t="n">
-        <v>194.2958829090753</v>
+        <v>195.5829352820671</v>
       </c>
       <c r="E158" t="n">
-        <v>198.02734375</v>
+        <v>196.0518646240234</v>
       </c>
       <c r="F158" t="n">
-        <v>125368100</v>
+        <v>113406600</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B159" t="n">
-        <v>198.8454820247872</v>
+        <v>199.4341385249406</v>
       </c>
       <c r="C159" t="n">
-        <v>199.7833407086998</v>
+        <v>207.7950323152332</v>
       </c>
       <c r="D159" t="n">
-        <v>195.5829352820671</v>
+        <v>198.1570588579161</v>
       </c>
       <c r="E159" t="n">
-        <v>196.0518646240234</v>
+        <v>207.3560333251953</v>
       </c>
       <c r="F159" t="n">
-        <v>113406600</v>
+        <v>188362800</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B160" t="n">
-        <v>199.4341385249406</v>
+        <v>207.8648724722903</v>
       </c>
       <c r="C160" t="n">
-        <v>207.7950323152332</v>
+        <v>213.7115092245668</v>
       </c>
       <c r="D160" t="n">
-        <v>198.1570588579161</v>
+        <v>206.0290722858257</v>
       </c>
       <c r="E160" t="n">
-        <v>207.3560333251953</v>
+        <v>211.0176696777344</v>
       </c>
       <c r="F160" t="n">
-        <v>188362800</v>
+        <v>168307900</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B161" t="n">
-        <v>207.8648724722903</v>
+        <v>212.5441790763045</v>
       </c>
       <c r="C161" t="n">
-        <v>213.7115092245668</v>
+        <v>217.3033052467507</v>
       </c>
       <c r="D161" t="n">
-        <v>206.0290722858257</v>
+        <v>212.4044989584125</v>
       </c>
       <c r="E161" t="n">
-        <v>211.0176696777344</v>
+        <v>214.709228515625</v>
       </c>
       <c r="F161" t="n">
-        <v>168307900</v>
+        <v>136421400</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B162" t="n">
-        <v>212.5441790763045</v>
+        <v>213.5518657378577</v>
       </c>
       <c r="C162" t="n">
-        <v>217.3033052467507</v>
+        <v>221.7930381906342</v>
       </c>
       <c r="D162" t="n">
-        <v>212.4044989584125</v>
+        <v>213.402213909002</v>
       </c>
       <c r="E162" t="n">
-        <v>214.709228515625</v>
+        <v>218.9395599365234</v>
       </c>
       <c r="F162" t="n">
-        <v>136421400</v>
+        <v>160685800</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B163" t="n">
-        <v>213.5518657378577</v>
+        <v>218.0515943496244</v>
       </c>
       <c r="C163" t="n">
-        <v>221.7930381906342</v>
+        <v>223.239732575863</v>
       </c>
       <c r="D163" t="n">
-        <v>213.402213909002</v>
+        <v>214.4298677829735</v>
       </c>
       <c r="E163" t="n">
-        <v>218.9395599365234</v>
+        <v>220.2765045166016</v>
       </c>
       <c r="F163" t="n">
-        <v>160685800</v>
+        <v>159176600</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B164" t="n">
-        <v>218.0515943496244</v>
+        <v>224.4170305354026</v>
       </c>
       <c r="C164" t="n">
-        <v>223.239732575863</v>
+        <v>227.3203978139454</v>
       </c>
       <c r="D164" t="n">
-        <v>214.4298677829735</v>
+        <v>221.0647077692387</v>
       </c>
       <c r="E164" t="n">
-        <v>220.2765045166016</v>
+        <v>225.3149871826172</v>
       </c>
       <c r="F164" t="n">
-        <v>159176600</v>
+        <v>150405400</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B165" t="n">
-        <v>224.4170305354026</v>
+        <v>229.3258255277811</v>
       </c>
       <c r="C165" t="n">
-        <v>227.3203978139454</v>
+        <v>236.0005559723521</v>
       </c>
       <c r="D165" t="n">
-        <v>221.0647077692387</v>
+        <v>228.7770767762568</v>
       </c>
       <c r="E165" t="n">
-        <v>225.3149871826172</v>
+        <v>235.202392578125</v>
       </c>
       <c r="F165" t="n">
-        <v>150405400</v>
+        <v>180782900</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B166" t="n">
-        <v>229.3258255277811</v>
+        <v>229.2360138852663</v>
       </c>
       <c r="C166" t="n">
-        <v>236.0005559723521</v>
+        <v>230.9720511978</v>
       </c>
       <c r="D166" t="n">
-        <v>228.7770767762568</v>
+        <v>223.7286135177626</v>
       </c>
       <c r="E166" t="n">
-        <v>235.202392578125</v>
+        <v>224.80615234375</v>
       </c>
       <c r="F166" t="n">
-        <v>180782900</v>
+        <v>180977600</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B167" t="n">
-        <v>229.2360138852663</v>
+        <v>229.345773483712</v>
       </c>
       <c r="C167" t="n">
-        <v>230.9720511978</v>
+        <v>229.4754818886306</v>
       </c>
       <c r="D167" t="n">
-        <v>223.7286135177626</v>
+        <v>217.8719993892805</v>
       </c>
       <c r="E167" t="n">
-        <v>224.80615234375</v>
+        <v>221.8130035400391</v>
       </c>
       <c r="F167" t="n">
-        <v>180977600</v>
+        <v>146280900</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B168" t="n">
-        <v>229.345773483712</v>
+        <v>219.1191400841904</v>
       </c>
       <c r="C168" t="n">
-        <v>229.4754818886306</v>
+        <v>223.9680572056967</v>
       </c>
       <c r="D168" t="n">
-        <v>217.8719993892805</v>
+        <v>217.4130483552105</v>
       </c>
       <c r="E168" t="n">
-        <v>221.8130035400391</v>
+        <v>220.1068878173828</v>
       </c>
       <c r="F168" t="n">
-        <v>146280900</v>
+        <v>140948200</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B169" t="n">
-        <v>219.1191400841904</v>
+        <v>222.6710257508039</v>
       </c>
       <c r="C169" t="n">
-        <v>223.9680572056967</v>
+        <v>225.6143103895453</v>
       </c>
       <c r="D169" t="n">
-        <v>217.4130483552105</v>
+        <v>219.9971448577806</v>
       </c>
       <c r="E169" t="n">
-        <v>220.1068878173828</v>
+        <v>222.9603729248047</v>
       </c>
       <c r="F169" t="n">
-        <v>140948200</v>
+        <v>184201600</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B170" t="n">
-        <v>222.6710257508039</v>
+        <v>221.7830583738447</v>
       </c>
       <c r="C170" t="n">
-        <v>225.6143103895453</v>
+        <v>226.8814055684356</v>
       </c>
       <c r="D170" t="n">
-        <v>219.9971448577806</v>
+        <v>217.4330007955402</v>
       </c>
       <c r="E170" t="n">
-        <v>222.9603729248047</v>
+        <v>219.0093994140625</v>
       </c>
       <c r="F170" t="n">
-        <v>184201600</v>
+        <v>203381800</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B171" t="n">
-        <v>221.7830583738447</v>
+        <v>220.3962175709585</v>
       </c>
       <c r="C171" t="n">
-        <v>226.8814055684356</v>
+        <v>220.5059673180016</v>
       </c>
       <c r="D171" t="n">
-        <v>217.4330007955402</v>
+        <v>214.3101381389001</v>
       </c>
       <c r="E171" t="n">
-        <v>219.0093994140625</v>
+        <v>214.8389282226562</v>
       </c>
       <c r="F171" t="n">
-        <v>203381800</v>
+        <v>169275700</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B172" t="n">
-        <v>220.3962175709585</v>
+        <v>216.0461718127993</v>
       </c>
       <c r="C172" t="n">
-        <v>220.5059673180016</v>
+        <v>217.6824311685512</v>
       </c>
       <c r="D172" t="n">
-        <v>214.3101381389001</v>
+        <v>211.5165320236786</v>
       </c>
       <c r="E172" t="n">
-        <v>214.8389282226562</v>
+        <v>214.3700103759766</v>
       </c>
       <c r="F172" t="n">
-        <v>169275700</v>
+        <v>187202600</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B173" t="n">
-        <v>216.0461718127993</v>
+        <v>213.6316806617713</v>
       </c>
       <c r="C173" t="n">
-        <v>217.6824311685512</v>
+        <v>213.6616110269177</v>
       </c>
       <c r="D173" t="n">
-        <v>211.5165320236786</v>
+        <v>208.3038625298546</v>
       </c>
       <c r="E173" t="n">
-        <v>214.3700103759766</v>
+        <v>212.1151580810547</v>
       </c>
       <c r="F173" t="n">
-        <v>187202600</v>
+        <v>167601200</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B174" t="n">
-        <v>213.6316806617713</v>
+        <v>210.7981702457166</v>
       </c>
       <c r="C174" t="n">
-        <v>213.6616110269177</v>
+        <v>215.0285063161196</v>
       </c>
       <c r="D174" t="n">
-        <v>208.3038625298546</v>
+        <v>210.738309512832</v>
       </c>
       <c r="E174" t="n">
-        <v>212.1151580810547</v>
+        <v>213.7613983154297</v>
       </c>
       <c r="F174" t="n">
-        <v>167601200</v>
+        <v>143996000</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B175" t="n">
-        <v>210.7981702457166</v>
+        <v>214.0906505321041</v>
       </c>
       <c r="C175" t="n">
-        <v>215.0285063161196</v>
+        <v>217.3631692496548</v>
       </c>
       <c r="D175" t="n">
-        <v>210.738309512832</v>
+        <v>210.6485213277038</v>
       </c>
       <c r="E175" t="n">
-        <v>213.7613983154297</v>
+        <v>210.6584930419922</v>
       </c>
       <c r="F175" t="n">
-        <v>143996000</v>
+        <v>289410600</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B176" t="n">
-        <v>214.0906505321041</v>
+        <v>215.2380189209027</v>
       </c>
       <c r="C176" t="n">
-        <v>217.3631692496548</v>
+        <v>224.3571743491113</v>
       </c>
       <c r="D176" t="n">
-        <v>210.6485213277038</v>
+        <v>215.2080885544549</v>
       </c>
       <c r="E176" t="n">
-        <v>210.6584930419922</v>
+        <v>223.8483428955078</v>
       </c>
       <c r="F176" t="n">
-        <v>289410600</v>
+        <v>212850700</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B177" t="n">
-        <v>215.2380189209027</v>
+        <v>226.6618858382332</v>
       </c>
       <c r="C177" t="n">
-        <v>224.3571743491113</v>
+        <v>231.7502608645459</v>
       </c>
       <c r="D177" t="n">
-        <v>215.2080885544549</v>
+        <v>220.8451951370975</v>
       </c>
       <c r="E177" t="n">
-        <v>223.8483428955078</v>
+        <v>222.3118438720703</v>
       </c>
       <c r="F177" t="n">
-        <v>212850700</v>
+        <v>193362900</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B178" t="n">
-        <v>226.6618858382332</v>
+        <v>221.2143597561905</v>
       </c>
       <c r="C178" t="n">
-        <v>231.7502608645459</v>
+        <v>222.3118572511273</v>
       </c>
       <c r="D178" t="n">
-        <v>220.8451951370975</v>
+        <v>214.0207957553572</v>
       </c>
       <c r="E178" t="n">
-        <v>222.3118438720703</v>
+        <v>214.26025390625</v>
       </c>
       <c r="F178" t="n">
-        <v>193362900</v>
+        <v>160907000</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,25 +5071,25 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B179" t="n">
-        <v>221.2143597561905</v>
+        <v>213.6709127939037</v>
       </c>
       <c r="C179" t="n">
-        <v>222.3118572511273</v>
+        <v>221.3523199881091</v>
       </c>
       <c r="D179" t="n">
-        <v>214.0207957553572</v>
+        <v>210.73419644349</v>
       </c>
       <c r="E179" t="n">
-        <v>214.26025390625</v>
+        <v>218.4156036376953</v>
       </c>
       <c r="F179" t="n">
-        <v>160907000</v>
+        <v>169022200</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5097,25 +5097,25 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B180" t="n">
-        <v>213.6709127939037</v>
+        <v>214.2902104723603</v>
       </c>
       <c r="C180" t="n">
-        <v>221.3523199881091</v>
+        <v>214.6298267834636</v>
       </c>
       <c r="D180" t="n">
-        <v>210.73419644349</v>
+        <v>204.101614447126</v>
       </c>
       <c r="E180" t="n">
-        <v>218.4156036376953</v>
+        <v>204.8707580566406</v>
       </c>
       <c r="F180" t="n">
-        <v>169022200</v>
+        <v>219655500</v>
       </c>
       <c r="G180" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B181" t="n">
-        <v>214.2902104723603</v>
+        <v>209.9450713288228</v>
       </c>
       <c r="C181" t="n">
-        <v>214.6298267834636</v>
+        <v>210.2347557268212</v>
       </c>
       <c r="D181" t="n">
-        <v>204.101614447126</v>
+        <v>205.7697506938822</v>
       </c>
       <c r="E181" t="n">
-        <v>204.8707580566406</v>
+        <v>208.4067993164062</v>
       </c>
       <c r="F181" t="n">
-        <v>219655500</v>
+        <v>138372800</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B182" t="n">
-        <v>209.9450713288228</v>
+        <v>210.3845825512031</v>
       </c>
       <c r="C182" t="n">
-        <v>210.2347557268212</v>
+        <v>211.1637095162451</v>
       </c>
       <c r="D182" t="n">
-        <v>205.7697506938822</v>
+        <v>199.1171915656509</v>
       </c>
       <c r="E182" t="n">
-        <v>208.4067993164062</v>
+        <v>207.9573059082031</v>
       </c>
       <c r="F182" t="n">
-        <v>138372800</v>
+        <v>180962500</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B183" t="n">
-        <v>210.3845825512031</v>
+        <v>204.2014963256503</v>
       </c>
       <c r="C183" t="n">
-        <v>211.1637095162451</v>
+        <v>206.9883864105018</v>
       </c>
       <c r="D183" t="n">
-        <v>199.1171915656509</v>
+        <v>199.696542748819</v>
       </c>
       <c r="E183" t="n">
-        <v>207.9573059082031</v>
+        <v>200.1959838867188</v>
       </c>
       <c r="F183" t="n">
-        <v>180962500</v>
+        <v>161746600</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B184" t="n">
-        <v>204.2014963256503</v>
+        <v>201.2647947500858</v>
       </c>
       <c r="C184" t="n">
-        <v>206.9883864105018</v>
+        <v>205.4301320010667</v>
       </c>
       <c r="D184" t="n">
-        <v>199.696542748819</v>
+        <v>199.3169621236104</v>
       </c>
       <c r="E184" t="n">
-        <v>200.1959838867188</v>
+        <v>204.6410064697266</v>
       </c>
       <c r="F184" t="n">
-        <v>161746600</v>
+        <v>158643200</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B185" t="n">
-        <v>201.2647947500858</v>
+        <v>204.6310298517525</v>
       </c>
       <c r="C185" t="n">
-        <v>205.4301320010667</v>
+        <v>206.8385664547524</v>
       </c>
       <c r="D185" t="n">
-        <v>199.3169621236104</v>
+        <v>203.2126188059985</v>
       </c>
       <c r="E185" t="n">
-        <v>204.6410064697266</v>
+        <v>204.9606628417969</v>
       </c>
       <c r="F185" t="n">
-        <v>158643200</v>
+        <v>112001800</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B186" t="n">
-        <v>204.6310298517525</v>
+        <v>208.6864864049894</v>
       </c>
       <c r="C186" t="n">
-        <v>206.8385664547524</v>
+        <v>212.4722588232193</v>
       </c>
       <c r="D186" t="n">
-        <v>203.2126188059985</v>
+        <v>208.1071328472061</v>
       </c>
       <c r="E186" t="n">
-        <v>204.9606628417969</v>
+        <v>212.2125396728516</v>
       </c>
       <c r="F186" t="n">
-        <v>112001800</v>
+        <v>149936700</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B187" t="n">
-        <v>208.6864864049894</v>
+        <v>210.9439520928381</v>
       </c>
       <c r="C187" t="n">
-        <v>212.4722588232193</v>
+        <v>211.2536184019877</v>
       </c>
       <c r="D187" t="n">
-        <v>208.1071328472061</v>
+        <v>207.0583006421773</v>
       </c>
       <c r="E187" t="n">
-        <v>212.2125396728516</v>
+        <v>207.1781768798828</v>
       </c>
       <c r="F187" t="n">
-        <v>149936700</v>
+        <v>125694100</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B188" t="n">
-        <v>210.9439520928381</v>
+        <v>208.2969174543329</v>
       </c>
       <c r="C188" t="n">
-        <v>211.2536184019877</v>
+        <v>208.9761653200819</v>
       </c>
       <c r="D188" t="n">
-        <v>207.0583006421773</v>
+        <v>202.8530121596522</v>
       </c>
       <c r="E188" t="n">
-        <v>207.1781768798828</v>
+        <v>204.4212493896484</v>
       </c>
       <c r="F188" t="n">
-        <v>125694100</v>
+        <v>128363500</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B189" t="n">
-        <v>208.2969174543329</v>
+        <v>207.0982684229139</v>
       </c>
       <c r="C189" t="n">
-        <v>208.9761653200819</v>
+        <v>211.1537281092123</v>
       </c>
       <c r="D189" t="n">
-        <v>202.8530121596522</v>
+        <v>206.2691942875683</v>
       </c>
       <c r="E189" t="n">
-        <v>204.4212493896484</v>
+        <v>210.4545135498047</v>
       </c>
       <c r="F189" t="n">
-        <v>128363500</v>
+        <v>241272000</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B190" t="n">
-        <v>207.0982684229139</v>
+        <v>211.2036686200953</v>
       </c>
       <c r="C190" t="n">
-        <v>211.1537281092123</v>
+        <v>213.7508214450341</v>
       </c>
       <c r="D190" t="n">
-        <v>206.2691942875683</v>
+        <v>207.4878253737282</v>
       </c>
       <c r="E190" t="n">
-        <v>210.4545135498047</v>
+        <v>208.4167785644531</v>
       </c>
       <c r="F190" t="n">
-        <v>241272000</v>
+        <v>122041400</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B191" t="n">
-        <v>211.2036686200953</v>
+        <v>201.9440304014853</v>
       </c>
       <c r="C191" t="n">
-        <v>213.7508214450341</v>
+        <v>203.5422481594977</v>
       </c>
       <c r="D191" t="n">
-        <v>207.4878253737282</v>
+        <v>199.77645766483</v>
       </c>
       <c r="E191" t="n">
-        <v>208.4167785644531</v>
+        <v>199.81640625</v>
       </c>
       <c r="F191" t="n">
-        <v>122041400</v>
+        <v>153496200</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B192" t="n">
-        <v>201.9440304014853</v>
+        <v>199.8963159019567</v>
       </c>
       <c r="C192" t="n">
-        <v>203.5422481594977</v>
+        <v>201.4445864758279</v>
       </c>
       <c r="D192" t="n">
-        <v>199.77645766483</v>
+        <v>196.360279356477</v>
       </c>
       <c r="E192" t="n">
-        <v>199.81640625</v>
+        <v>198.7775726318359</v>
       </c>
       <c r="F192" t="n">
-        <v>153496200</v>
+        <v>151810700</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B193" t="n">
-        <v>199.8963159019567</v>
+        <v>199.8563704571445</v>
       </c>
       <c r="C193" t="n">
-        <v>201.4445864758279</v>
+        <v>200.5755669254449</v>
       </c>
       <c r="D193" t="n">
-        <v>196.360279356477</v>
+        <v>191.9152592982058</v>
       </c>
       <c r="E193" t="n">
-        <v>198.7775726318359</v>
+        <v>195.5212249755859</v>
       </c>
       <c r="F193" t="n">
-        <v>151810700</v>
+        <v>149550000</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B194" t="n">
-        <v>199.8563704571445</v>
+        <v>192.9041409641119</v>
       </c>
       <c r="C194" t="n">
-        <v>200.5755669254449</v>
+        <v>195.331432829306</v>
       </c>
       <c r="D194" t="n">
-        <v>191.9152592982058</v>
+        <v>191.0062707295152</v>
       </c>
       <c r="E194" t="n">
-        <v>195.5212249755859</v>
+        <v>192.3148040771484</v>
       </c>
       <c r="F194" t="n">
-        <v>149550000</v>
+        <v>179304100</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B195" t="n">
-        <v>192.9041409641119</v>
+        <v>193.6333319429392</v>
       </c>
       <c r="C195" t="n">
-        <v>195.331432829306</v>
+        <v>195.9607141929515</v>
       </c>
       <c r="D195" t="n">
-        <v>191.0062707295152</v>
+        <v>189.5878557469149</v>
       </c>
       <c r="E195" t="n">
-        <v>192.3148040771484</v>
+        <v>194.7520751953125</v>
       </c>
       <c r="F195" t="n">
-        <v>179304100</v>
+        <v>148835700</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B196" t="n">
-        <v>193.6333319429392</v>
+        <v>197.0195429632178</v>
       </c>
       <c r="C196" t="n">
-        <v>195.9607141929515</v>
+        <v>200.4057532237791</v>
       </c>
       <c r="D196" t="n">
-        <v>189.5878557469149</v>
+        <v>194.8919188665145</v>
       </c>
       <c r="E196" t="n">
-        <v>194.7520751953125</v>
+        <v>199.8663482666016</v>
       </c>
       <c r="F196" t="n">
-        <v>148835700</v>
+        <v>166476700</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B197" t="n">
-        <v>197.0195429632178</v>
+        <v>195.9806989625188</v>
       </c>
       <c r="C197" t="n">
-        <v>200.4057532237791</v>
+        <v>199.626628404907</v>
       </c>
       <c r="D197" t="n">
-        <v>194.8919188665145</v>
+        <v>193.2337727110923</v>
       </c>
       <c r="E197" t="n">
-        <v>199.8663482666016</v>
+        <v>197.3591613769531</v>
       </c>
       <c r="F197" t="n">
-        <v>166476700</v>
+        <v>146147600</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B198" t="n">
-        <v>195.9806989625188</v>
+        <v>196.9196593659626</v>
       </c>
       <c r="C198" t="n">
-        <v>199.626628404907</v>
+        <v>199.8363939026278</v>
       </c>
       <c r="D198" t="n">
-        <v>193.2337727110923</v>
+        <v>192.1350197738411</v>
       </c>
       <c r="E198" t="n">
-        <v>197.3591613769531</v>
+        <v>194.6122436523438</v>
       </c>
       <c r="F198" t="n">
-        <v>146147600</v>
+        <v>142068700</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B199" t="n">
-        <v>196.9196593659626</v>
+        <v>194.202694284663</v>
       </c>
       <c r="C199" t="n">
-        <v>199.8363939026278</v>
+        <v>197.3292007505161</v>
       </c>
       <c r="D199" t="n">
-        <v>192.1350197738411</v>
+        <v>193.7731822131383</v>
       </c>
       <c r="E199" t="n">
-        <v>194.6122436523438</v>
+        <v>195.3314361572266</v>
       </c>
       <c r="F199" t="n">
-        <v>142068700</v>
+        <v>108999000</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B200" t="n">
-        <v>194.202694284663</v>
+        <v>192.1549837798622</v>
       </c>
       <c r="C200" t="n">
-        <v>197.3292007505161</v>
+        <v>198.1882414262674</v>
       </c>
       <c r="D200" t="n">
-        <v>193.7731822131383</v>
+        <v>190.9263628146717</v>
       </c>
       <c r="E200" t="n">
-        <v>195.3314361572266</v>
+        <v>196.7098846435547</v>
       </c>
       <c r="F200" t="n">
-        <v>108999000</v>
+        <v>124154600</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B201" t="n">
-        <v>192.1549837798622</v>
+        <v>194.9618356993413</v>
       </c>
       <c r="C201" t="n">
-        <v>198.1882414262674</v>
+        <v>204.9306918075912</v>
       </c>
       <c r="D201" t="n">
-        <v>190.9263628146717</v>
+        <v>194.841974703339</v>
       </c>
       <c r="E201" t="n">
-        <v>196.7098846435547</v>
+        <v>203.891845703125</v>
       </c>
       <c r="F201" t="n">
-        <v>124154600</v>
+        <v>147419100</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B202" t="n">
-        <v>194.9618356993413</v>
+        <v>204.2314748595287</v>
       </c>
       <c r="C202" t="n">
-        <v>204.9306918075912</v>
+        <v>204.3613191897594</v>
       </c>
       <c r="D202" t="n">
-        <v>194.841974703339</v>
+        <v>198.7376223952696</v>
       </c>
       <c r="E202" t="n">
-        <v>203.891845703125</v>
+        <v>202.5533447265625</v>
       </c>
       <c r="F202" t="n">
-        <v>147419100</v>
+        <v>132037400</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B203" t="n">
-        <v>204.2314748595287</v>
+        <v>201.7742207048944</v>
       </c>
       <c r="C203" t="n">
-        <v>204.3613191897594</v>
+        <v>210.7641612313501</v>
       </c>
       <c r="D203" t="n">
-        <v>198.7376223952696</v>
+        <v>201.6943082934289</v>
       </c>
       <c r="E203" t="n">
-        <v>202.5533447265625</v>
+        <v>210.7242126464844</v>
       </c>
       <c r="F203" t="n">
-        <v>132037400</v>
+        <v>148421000</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B204" t="n">
-        <v>201.7742207048944</v>
+        <v>208.3069001369788</v>
       </c>
       <c r="C204" t="n">
-        <v>210.7641612313501</v>
+        <v>210.3346451505122</v>
       </c>
       <c r="D204" t="n">
-        <v>201.6943082934289</v>
+        <v>202.7730991138312</v>
       </c>
       <c r="E204" t="n">
-        <v>210.7242126464844</v>
+        <v>203.3025054931641</v>
       </c>
       <c r="F204" t="n">
-        <v>148421000</v>
+        <v>121411000</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B205" t="n">
-        <v>208.3069001369788</v>
+        <v>207.9672957533915</v>
       </c>
       <c r="C205" t="n">
-        <v>210.3346451505122</v>
+        <v>212.3124399374416</v>
       </c>
       <c r="D205" t="n">
-        <v>202.7730991138312</v>
+        <v>203.5722196467825</v>
       </c>
       <c r="E205" t="n">
-        <v>203.3025054931641</v>
+        <v>211.5632781982422</v>
       </c>
       <c r="F205" t="n">
-        <v>121411000</v>
+        <v>124379600</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B206" t="n">
-        <v>207.9672957533915</v>
+        <v>211.7230919717581</v>
       </c>
       <c r="C206" t="n">
-        <v>212.3124399374416</v>
+        <v>213.5710150202495</v>
       </c>
       <c r="D206" t="n">
-        <v>203.5722196467825</v>
+        <v>205.8096955397309</v>
       </c>
       <c r="E206" t="n">
-        <v>211.5632781982422</v>
+        <v>212.2624816894531</v>
       </c>
       <c r="F206" t="n">
-        <v>124379600</v>
+        <v>124797200</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B207" t="n">
-        <v>211.7230919717581</v>
+        <v>209.9350906043833</v>
       </c>
       <c r="C207" t="n">
-        <v>213.5710150202495</v>
+        <v>210.8440771529852</v>
       </c>
       <c r="D207" t="n">
-        <v>205.8096955397309</v>
+        <v>205.6199270055466</v>
       </c>
       <c r="E207" t="n">
-        <v>212.2624816894531</v>
+        <v>207.1681823730469</v>
       </c>
       <c r="F207" t="n">
-        <v>124797200</v>
+        <v>122986100</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B208" t="n">
-        <v>209.9350906043833</v>
+        <v>202.4135048295048</v>
       </c>
       <c r="C208" t="n">
-        <v>210.8440771529852</v>
+        <v>206.4190172896336</v>
       </c>
       <c r="D208" t="n">
-        <v>205.6199270055466</v>
+        <v>197.7487264058434</v>
       </c>
       <c r="E208" t="n">
-        <v>207.1681823730469</v>
+        <v>202.5833129882812</v>
       </c>
       <c r="F208" t="n">
-        <v>122986100</v>
+        <v>144281900</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B209" t="n">
-        <v>202.4135048295048</v>
+        <v>205.639896943356</v>
       </c>
       <c r="C209" t="n">
-        <v>206.4190172896336</v>
+        <v>207.5078172334397</v>
       </c>
       <c r="D209" t="n">
-        <v>197.7487264058434</v>
+        <v>202.0539130969454</v>
       </c>
       <c r="E209" t="n">
-        <v>202.5833129882812</v>
+        <v>203.0527954101562</v>
       </c>
       <c r="F209" t="n">
-        <v>144281900</v>
+        <v>88701500</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B210" t="n">
-        <v>205.639896943356</v>
+        <v>207.308024406286</v>
       </c>
       <c r="C210" t="n">
-        <v>207.5078172334397</v>
+        <v>208.4167843613107</v>
       </c>
       <c r="D210" t="n">
-        <v>202.0539130969454</v>
+        <v>203.7819711309363</v>
       </c>
       <c r="E210" t="n">
-        <v>203.0527954101562</v>
+        <v>207.0583038330078</v>
       </c>
       <c r="F210" t="n">
-        <v>88701500</v>
+        <v>108685600</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B211" t="n">
-        <v>207.308024406286</v>
+        <v>205.579968274895</v>
       </c>
       <c r="C211" t="n">
-        <v>208.4167843613107</v>
+        <v>214.1503804276117</v>
       </c>
       <c r="D211" t="n">
-        <v>203.7819711309363</v>
+        <v>204.7209288682105</v>
       </c>
       <c r="E211" t="n">
-        <v>207.0583038330078</v>
+        <v>211.8229827880859</v>
       </c>
       <c r="F211" t="n">
-        <v>108685600</v>
+        <v>137645600</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B212" t="n">
-        <v>205.579968274895</v>
+        <v>209.2258868865651</v>
       </c>
       <c r="C212" t="n">
-        <v>214.1503804276117</v>
+        <v>210.6342993029147</v>
       </c>
       <c r="D212" t="n">
-        <v>204.7209288682105</v>
+        <v>205.7297989431358</v>
       </c>
       <c r="E212" t="n">
-        <v>211.8229827880859</v>
+        <v>208.5266571044922</v>
       </c>
       <c r="F212" t="n">
-        <v>137645600</v>
+        <v>110505300</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B213" t="n">
-        <v>209.2258868865651</v>
+        <v>207.2181292349697</v>
       </c>
       <c r="C213" t="n">
-        <v>210.6342993029147</v>
+        <v>211.6731509810223</v>
       </c>
       <c r="D213" t="n">
-        <v>205.7297989431358</v>
+        <v>204.5810805834776</v>
       </c>
       <c r="E213" t="n">
-        <v>208.5266571044922</v>
+        <v>206.6088104248047</v>
       </c>
       <c r="F213" t="n">
-        <v>110505300</v>
+        <v>114836800</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B214" t="n">
-        <v>207.2181292349697</v>
+        <v>207.9672962732577</v>
       </c>
       <c r="C214" t="n">
-        <v>211.6731509810223</v>
+        <v>208.5166845983908</v>
       </c>
       <c r="D214" t="n">
-        <v>204.5810805834776</v>
+        <v>195.2215633388429</v>
       </c>
       <c r="E214" t="n">
-        <v>206.6088104248047</v>
+        <v>196.2903594970703</v>
       </c>
       <c r="F214" t="n">
-        <v>114836800</v>
+        <v>154353700</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B215" t="n">
-        <v>207.9672962732577</v>
+        <v>194.782047001347</v>
       </c>
       <c r="C215" t="n">
-        <v>208.5166845983908</v>
+        <v>198.4779084345641</v>
       </c>
       <c r="D215" t="n">
-        <v>195.2215633388429</v>
+        <v>192.5245785077403</v>
       </c>
       <c r="E215" t="n">
-        <v>196.2903594970703</v>
+        <v>196.789794921875</v>
       </c>
       <c r="F215" t="n">
-        <v>154353700</v>
+        <v>134111500</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B216" t="n">
-        <v>194.782047001347</v>
+        <v>195.6311069684468</v>
       </c>
       <c r="C216" t="n">
-        <v>198.4779084345641</v>
+        <v>196.8497446088402</v>
       </c>
       <c r="D216" t="n">
-        <v>192.5245785077403</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="E216" t="n">
-        <v>196.789794921875</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="F216" t="n">
-        <v>134111500</v>
+        <v>147680800</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B217" t="n">
-        <v>195.6311069684468</v>
+        <v>193.2337718176948</v>
       </c>
       <c r="C217" t="n">
-        <v>196.8497446088402</v>
+        <v>197.0295274868271</v>
       </c>
       <c r="D217" t="n">
-        <v>189.7976226806641</v>
+        <v>191.3059363552755</v>
       </c>
       <c r="E217" t="n">
-        <v>189.7976226806641</v>
+        <v>194.8219909667969</v>
       </c>
       <c r="F217" t="n">
-        <v>147680800</v>
+        <v>129010200</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B218" t="n">
-        <v>193.2337718176948</v>
+        <v>198.2182038580375</v>
       </c>
       <c r="C218" t="n">
-        <v>197.0295274868271</v>
+        <v>201.7742223680242</v>
       </c>
       <c r="D218" t="n">
-        <v>191.3059363552755</v>
+        <v>194.7320991825756</v>
       </c>
       <c r="E218" t="n">
-        <v>194.8219909667969</v>
+        <v>200.5256195068359</v>
       </c>
       <c r="F218" t="n">
-        <v>129010200</v>
+        <v>139961200</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B219" t="n">
-        <v>198.2182038580375</v>
+        <v>197.4690486270115</v>
       </c>
       <c r="C219" t="n">
-        <v>201.7742223680242</v>
+        <v>208.506701330784</v>
       </c>
       <c r="D219" t="n">
-        <v>194.7320991825756</v>
+        <v>196.6299911347511</v>
       </c>
       <c r="E219" t="n">
-        <v>200.5256195068359</v>
+        <v>206.4090423583984</v>
       </c>
       <c r="F219" t="n">
-        <v>139961200</v>
+        <v>128406900</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B220" t="n">
-        <v>197.4690486270115</v>
+        <v>211.0638257011038</v>
       </c>
       <c r="C220" t="n">
-        <v>208.506701330784</v>
+        <v>212.8218530009649</v>
       </c>
       <c r="D220" t="n">
-        <v>196.6299911347511</v>
+        <v>208.8163406042335</v>
       </c>
       <c r="E220" t="n">
-        <v>206.4090423583984</v>
+        <v>211.7031097412109</v>
       </c>
       <c r="F220" t="n">
-        <v>128406900</v>
+        <v>134922000</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B221" t="n">
-        <v>211.0638257011038</v>
+        <v>216.6176127852948</v>
       </c>
       <c r="C221" t="n">
-        <v>212.8218530009649</v>
+        <v>221.9716224388697</v>
       </c>
       <c r="D221" t="n">
-        <v>208.8163406042335</v>
+        <v>216.1581202281489</v>
       </c>
       <c r="E221" t="n">
-        <v>211.7031097412109</v>
+        <v>218.9749755859375</v>
       </c>
       <c r="F221" t="n">
-        <v>134922000</v>
+        <v>158187400</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B222" t="n">
-        <v>216.6176127852948</v>
+        <v>221.2823935806188</v>
       </c>
       <c r="C222" t="n">
-        <v>221.9716224388697</v>
+        <v>223.3800524967045</v>
       </c>
       <c r="D222" t="n">
-        <v>216.1581202281489</v>
+        <v>216.7574580038405</v>
       </c>
       <c r="E222" t="n">
-        <v>218.9749755859375</v>
+        <v>218.7452392578125</v>
       </c>
       <c r="F222" t="n">
-        <v>158187400</v>
+        <v>113940600</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B223" t="n">
-        <v>221.2823935806188</v>
+        <v>221.2923777041913</v>
       </c>
       <c r="C223" t="n">
-        <v>223.3800524967045</v>
+        <v>224.5087799247126</v>
       </c>
       <c r="D223" t="n">
-        <v>216.7574580038405</v>
+        <v>220.4133716458871</v>
       </c>
       <c r="E223" t="n">
-        <v>218.7452392578125</v>
+        <v>223.7096862792969</v>
       </c>
       <c r="F223" t="n">
-        <v>113940600</v>
+        <v>105669400</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B224" t="n">
-        <v>221.2923777041913</v>
+        <v>223.1502910726907</v>
       </c>
       <c r="C224" t="n">
-        <v>224.5087799247126</v>
+        <v>223.8894694330602</v>
       </c>
       <c r="D224" t="n">
-        <v>220.4133716458871</v>
+        <v>216.5277120448001</v>
       </c>
       <c r="E224" t="n">
-        <v>223.7096862792969</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="F224" t="n">
-        <v>105669400</v>
+        <v>115846600</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B225" t="n">
-        <v>223.1502910726907</v>
+        <v>221.9216754142795</v>
       </c>
       <c r="C225" t="n">
-        <v>223.8894694330602</v>
+        <v>221.9516406634887</v>
       </c>
       <c r="D225" t="n">
-        <v>216.5277120448001</v>
+        <v>215.9583469538982</v>
       </c>
       <c r="E225" t="n">
-        <v>217.3068389892578</v>
+        <v>217.2568969726562</v>
       </c>
       <c r="F225" t="n">
-        <v>115846600</v>
+        <v>101273100</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B226" t="n">
-        <v>221.9216754142795</v>
+        <v>220.7929293559802</v>
       </c>
       <c r="C226" t="n">
-        <v>221.9516406634887</v>
+        <v>224.848404158734</v>
       </c>
       <c r="D226" t="n">
-        <v>215.9583469538982</v>
+        <v>219.9538719106106</v>
       </c>
       <c r="E226" t="n">
-        <v>217.2568969726562</v>
+        <v>223.8395233154297</v>
       </c>
       <c r="F226" t="n">
-        <v>101273100</v>
+        <v>108783600</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B227" t="n">
-        <v>220.7929293559802</v>
+        <v>224.8084500146858</v>
       </c>
       <c r="C227" t="n">
-        <v>224.848404158734</v>
+        <v>226.9760227961096</v>
       </c>
       <c r="D227" t="n">
-        <v>219.9538719106106</v>
+        <v>223.4599680426375</v>
       </c>
       <c r="E227" t="n">
-        <v>223.8395233154297</v>
+        <v>225.0481872558594</v>
       </c>
       <c r="F227" t="n">
-        <v>108783600</v>
+        <v>98867200</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B228" t="n">
-        <v>224.8084500146858</v>
+        <v>226.5165415533859</v>
       </c>
       <c r="C228" t="n">
-        <v>226.9760227961096</v>
+        <v>227.2357380227387</v>
       </c>
       <c r="D228" t="n">
-        <v>223.4599680426375</v>
+        <v>224.2490744835724</v>
       </c>
       <c r="E228" t="n">
-        <v>225.0481872558594</v>
+        <v>224.9083404541016</v>
       </c>
       <c r="F228" t="n">
-        <v>98867200</v>
+        <v>75680900</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B229" t="n">
-        <v>226.5165415533859</v>
+        <v>225.7274161885591</v>
       </c>
       <c r="C229" t="n">
-        <v>227.2357380227387</v>
+        <v>227.6652502746616</v>
       </c>
       <c r="D229" t="n">
-        <v>224.2490744835724</v>
+        <v>224.6086728983284</v>
       </c>
       <c r="E229" t="n">
-        <v>224.9083404541016</v>
+        <v>224.7584991455078</v>
       </c>
       <c r="F229" t="n">
-        <v>75680900</v>
+        <v>93678700</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B230" t="n">
-        <v>225.7274161885591</v>
+        <v>220.203597915372</v>
       </c>
       <c r="C230" t="n">
-        <v>227.6652502746616</v>
+        <v>221.3922702798686</v>
       </c>
       <c r="D230" t="n">
-        <v>224.6086728983284</v>
+        <v>218.4455705709327</v>
       </c>
       <c r="E230" t="n">
-        <v>224.7584991455078</v>
+        <v>219.4944000244141</v>
       </c>
       <c r="F230" t="n">
-        <v>93678700</v>
+        <v>103128200</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B231" t="n">
-        <v>220.203597915372</v>
+        <v>221.4222404106533</v>
       </c>
       <c r="C231" t="n">
-        <v>221.3922702798686</v>
+        <v>222.6208961374568</v>
       </c>
       <c r="D231" t="n">
-        <v>218.4455705709327</v>
+        <v>216.5177245976465</v>
       </c>
       <c r="E231" t="n">
-        <v>219.4944000244141</v>
+        <v>217.3168334960938</v>
       </c>
       <c r="F231" t="n">
-        <v>103128200</v>
+        <v>96797300</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B232" t="n">
-        <v>221.4222404106533</v>
+        <v>218.1159423024499</v>
       </c>
       <c r="C232" t="n">
-        <v>222.6208961374568</v>
+        <v>219.6142657707553</v>
       </c>
       <c r="D232" t="n">
-        <v>216.5177245976465</v>
+        <v>215.418963107847</v>
       </c>
       <c r="E232" t="n">
-        <v>217.3168334960938</v>
+        <v>216.6076354980469</v>
       </c>
       <c r="F232" t="n">
-        <v>96797300</v>
+        <v>92457000</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B233" t="n">
-        <v>218.1159423024499</v>
+        <v>218.1758724878036</v>
       </c>
       <c r="C233" t="n">
-        <v>219.6142657707553</v>
+        <v>218.4955221432803</v>
       </c>
       <c r="D233" t="n">
-        <v>215.418963107847</v>
+        <v>214.2602556586216</v>
       </c>
       <c r="E233" t="n">
-        <v>216.6076354980469</v>
+        <v>214.4800109863281</v>
       </c>
       <c r="F233" t="n">
-        <v>92457000</v>
+        <v>98869300</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B234" t="n">
-        <v>218.1758724878036</v>
+        <v>215.2891020611033</v>
       </c>
       <c r="C234" t="n">
-        <v>218.4955221432803</v>
+        <v>215.3490325607492</v>
       </c>
       <c r="D234" t="n">
-        <v>214.2602556586216</v>
+        <v>207.0183577918231</v>
       </c>
       <c r="E234" t="n">
-        <v>214.4800109863281</v>
+        <v>208.2469787597656</v>
       </c>
       <c r="F234" t="n">
-        <v>98869300</v>
+        <v>135187300</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B235" t="n">
-        <v>215.2891020611033</v>
+        <v>210.7941279013131</v>
       </c>
       <c r="C235" t="n">
-        <v>215.3490325607492</v>
+        <v>214.4899893165327</v>
       </c>
       <c r="D235" t="n">
-        <v>207.0183577918231</v>
+        <v>209.8751580258669</v>
       </c>
       <c r="E235" t="n">
-        <v>208.2469787597656</v>
+        <v>212.8118743896484</v>
       </c>
       <c r="F235" t="n">
-        <v>135187300</v>
+        <v>122309000</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B236" t="n">
-        <v>210.7941279013131</v>
+        <v>212.4023240594531</v>
       </c>
       <c r="C236" t="n">
-        <v>214.4899893165327</v>
+        <v>213.3612577394914</v>
       </c>
       <c r="D236" t="n">
-        <v>209.8751580258669</v>
+        <v>208.9961318803605</v>
       </c>
       <c r="E236" t="n">
-        <v>212.8118743896484</v>
+        <v>209.4256591796875</v>
       </c>
       <c r="F236" t="n">
-        <v>122309000</v>
+        <v>179900000</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B237" t="n">
-        <v>212.4023240594531</v>
+        <v>222.6109016432552</v>
       </c>
       <c r="C237" t="n">
-        <v>213.3612577394914</v>
+        <v>230.2123962709879</v>
       </c>
       <c r="D237" t="n">
-        <v>208.9961318803605</v>
+        <v>220.6530857022795</v>
       </c>
       <c r="E237" t="n">
-        <v>209.4256591796875</v>
+        <v>227.7251739501953</v>
       </c>
       <c r="F237" t="n">
-        <v>179900000</v>
+        <v>298909800</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B238" t="n">
-        <v>222.6109016432552</v>
+        <v>227.1058715337123</v>
       </c>
       <c r="C238" t="n">
-        <v>230.2123962709879</v>
+        <v>229.003741733446</v>
       </c>
       <c r="D238" t="n">
-        <v>220.6530857022795</v>
+        <v>216.5676606288883</v>
       </c>
       <c r="E238" t="n">
-        <v>227.7251739501953</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="F238" t="n">
-        <v>298909800</v>
+        <v>195116400</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B239" t="n">
-        <v>227.1058715337123</v>
+        <v>218.6253647857836</v>
       </c>
       <c r="C239" t="n">
-        <v>229.003741733446</v>
+        <v>221.0526567078369</v>
       </c>
       <c r="D239" t="n">
-        <v>216.5676606288883</v>
+        <v>215.9683494434545</v>
       </c>
       <c r="E239" t="n">
-        <v>217.3068389892578</v>
+        <v>220.5332336425781</v>
       </c>
       <c r="F239" t="n">
-        <v>195116400</v>
+        <v>124702700</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B240" t="n">
-        <v>218.6253647857836</v>
+        <v>216.5077444634259</v>
       </c>
       <c r="C240" t="n">
-        <v>221.0526567078369</v>
+        <v>220.1636574397174</v>
       </c>
       <c r="D240" t="n">
-        <v>215.9683494434545</v>
+        <v>214.8595947199138</v>
       </c>
       <c r="E240" t="n">
-        <v>220.5332336425781</v>
+        <v>217.1969757080078</v>
       </c>
       <c r="F240" t="n">
-        <v>124702700</v>
+        <v>109756200</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B241" t="n">
-        <v>216.5077444634259</v>
+        <v>218.5454508199983</v>
       </c>
       <c r="C241" t="n">
-        <v>220.1636574397174</v>
+        <v>227.6952163087265</v>
       </c>
       <c r="D241" t="n">
-        <v>214.8595947199138</v>
+        <v>218.2357997469377</v>
       </c>
       <c r="E241" t="n">
-        <v>217.1969757080078</v>
+        <v>224.1591796875</v>
       </c>
       <c r="F241" t="n">
-        <v>109756200</v>
+        <v>157104700</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B242" t="n">
-        <v>218.5454508199983</v>
+        <v>225.7673797205316</v>
       </c>
       <c r="C242" t="n">
-        <v>227.6952163087265</v>
+        <v>230.1424737915274</v>
       </c>
       <c r="D242" t="n">
-        <v>218.2357997469377</v>
+        <v>224.4987949430455</v>
       </c>
       <c r="E242" t="n">
-        <v>224.1591796875</v>
+        <v>228.1946563720703</v>
       </c>
       <c r="F242" t="n">
-        <v>157104700</v>
+        <v>134681600</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B243" t="n">
-        <v>225.7673797205316</v>
+        <v>230.8317036041433</v>
       </c>
       <c r="C243" t="n">
-        <v>230.1424737915274</v>
+        <v>234.4975997614268</v>
       </c>
       <c r="D243" t="n">
-        <v>224.4987949430455</v>
+        <v>229.3733440032785</v>
       </c>
       <c r="E243" t="n">
-        <v>228.1946563720703</v>
+        <v>230.1025238037109</v>
       </c>
       <c r="F243" t="n">
-        <v>134681600</v>
+        <v>135352400</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B244" t="n">
-        <v>230.8317036041433</v>
+        <v>232.8494477166676</v>
       </c>
       <c r="C244" t="n">
-        <v>234.4975997614268</v>
+        <v>233.4487831783142</v>
       </c>
       <c r="D244" t="n">
-        <v>229.3733440032785</v>
+        <v>224.5986856128386</v>
       </c>
       <c r="E244" t="n">
-        <v>230.1025238037109</v>
+        <v>225.4776916503906</v>
       </c>
       <c r="F244" t="n">
-        <v>135352400</v>
+        <v>122965600</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B245" t="n">
-        <v>232.8494477166676</v>
+        <v>225.0281992525124</v>
       </c>
       <c r="C245" t="n">
-        <v>233.4487831783142</v>
+        <v>225.9271872095504</v>
       </c>
       <c r="D245" t="n">
-        <v>224.5986856128386</v>
+        <v>223.2102414251123</v>
       </c>
       <c r="E245" t="n">
-        <v>225.4776916503906</v>
+        <v>223.4199981689453</v>
       </c>
       <c r="F245" t="n">
-        <v>122965600</v>
+        <v>82955500</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,25 +6813,25 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B246" t="n">
-        <v>225.0281992525124</v>
+        <v>220.5299987792969</v>
       </c>
       <c r="C246" t="n">
-        <v>225.9271872095504</v>
+        <v>220.9900054931641</v>
       </c>
       <c r="D246" t="n">
-        <v>223.2102414251123</v>
+        <v>217.1999969482422</v>
       </c>
       <c r="E246" t="n">
-        <v>223.4199981689453</v>
+        <v>218.3600006103516</v>
       </c>
       <c r="F246" t="n">
-        <v>82955500</v>
+        <v>105768000</v>
       </c>
       <c r="G246" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -6839,25 +6839,25 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B247" t="n">
-        <v>220.5299987792969</v>
+        <v>221.2400054931641</v>
       </c>
       <c r="C247" t="n">
-        <v>220.9900054931641</v>
+        <v>222</v>
       </c>
       <c r="D247" t="n">
-        <v>217.1999969482422</v>
+        <v>218.1499938964844</v>
       </c>
       <c r="E247" t="n">
-        <v>218.3600006103516</v>
+        <v>218.2899932861328</v>
       </c>
       <c r="F247" t="n">
-        <v>105768000</v>
+        <v>89060100</v>
       </c>
       <c r="G247" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B248" t="n">
-        <v>221.2400054931641</v>
+        <v>211.2400054931641</v>
       </c>
       <c r="C248" t="n">
-        <v>222</v>
+        <v>212.7700042724609</v>
       </c>
       <c r="D248" t="n">
-        <v>218.1499938964844</v>
+        <v>208.9299926757812</v>
       </c>
       <c r="E248" t="n">
-        <v>218.2899932861328</v>
+        <v>210.9600067138672</v>
       </c>
       <c r="F248" t="n">
-        <v>89060100</v>
+        <v>132267200</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B249" t="n">
-        <v>211.2400054931641</v>
+        <v>213.3800048828125</v>
       </c>
       <c r="C249" t="n">
-        <v>212.7700042724609</v>
+        <v>213.9400024414062</v>
       </c>
       <c r="D249" t="n">
-        <v>208.9299926757812</v>
+        <v>211.1600036621094</v>
       </c>
       <c r="E249" t="n">
-        <v>210.9600067138672</v>
+        <v>212.1699981689453</v>
       </c>
       <c r="F249" t="n">
-        <v>132267200</v>
+        <v>88059700</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B250" t="n">
-        <v>213.3800048828125</v>
+        <v>214.1399993896484</v>
       </c>
       <c r="C250" t="n">
-        <v>213.9400024414062</v>
+        <v>216.7599945068359</v>
       </c>
       <c r="D250" t="n">
-        <v>211.1600036621094</v>
+        <v>212.5</v>
       </c>
       <c r="E250" t="n">
-        <v>212.1699981689453</v>
+        <v>213.8999938964844</v>
       </c>
       <c r="F250" t="n">
-        <v>88059700</v>
+        <v>96563600</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B251" t="n">
-        <v>214.1399993896484</v>
+        <v>218.3800048828125</v>
       </c>
       <c r="C251" t="n">
-        <v>216.7599945068359</v>
+        <v>219.9100036621094</v>
       </c>
       <c r="D251" t="n">
-        <v>212.5</v>
+        <v>217.1499938964844</v>
       </c>
       <c r="E251" t="n">
-        <v>213.8999938964844</v>
+        <v>219.3399963378906</v>
       </c>
       <c r="F251" t="n">
-        <v>96563600</v>
+        <v>94191300</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B252" t="n">
-        <v>218.3800048828125</v>
+        <v>219.3500061035156</v>
       </c>
       <c r="C252" t="n">
-        <v>219.9100036621094</v>
+        <v>222.7299957275391</v>
       </c>
       <c r="D252" t="n">
-        <v>217.1499938964844</v>
+        <v>218.0299987792969</v>
       </c>
       <c r="E252" t="n">
-        <v>219.3399963378906</v>
+        <v>222.2700042724609</v>
       </c>
       <c r="F252" t="n">
-        <v>93960500</v>
+        <v>189683500</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10884,37 +10884,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>222.27</v>
+      </c>
+      <c r="D2" t="n">
         <v>219.34</v>
       </c>
-      <c r="D2" t="n">
-        <v>213.9</v>
-      </c>
       <c r="E2" t="n">
-        <v>218.388</v>
+        <v>219.36</v>
       </c>
       <c r="F2" t="n">
-        <v>219.9</v>
+        <v>222.73</v>
       </c>
       <c r="G2" t="n">
-        <v>217.145</v>
+        <v>218.04</v>
       </c>
       <c r="H2" t="n">
-        <v>92845751</v>
+        <v>188794542</v>
       </c>
       <c r="I2" t="n">
-        <v>128873413</v>
+        <v>129288142</v>
       </c>
       <c r="J2" t="n">
-        <v>5296402989056</v>
+        <v>5367153557504</v>
       </c>
       <c r="K2" t="n">
-        <v>27.012316</v>
+        <v>27.714462</v>
       </c>
       <c r="L2" t="n">
-        <v>14.046848</v>
+        <v>14.173006</v>
       </c>
       <c r="M2" t="n">
-        <v>8.119999999999999</v>
+        <v>8.02</v>
       </c>
       <c r="N2" t="n">
         <v>236.54</v>
@@ -10926,7 +10926,7 @@
         <v>2.217</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="R2" t="n">
         <v>0.63663</v>
@@ -10950,7 +10950,7 @@
         <v>9.483000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>23.129812</v>
+        <v>23.438786</v>
       </c>
       <c r="Z2" t="n">
         <v>1.278</v>
@@ -10962,7 +10962,7 @@
         <v>302970011648</v>
       </c>
       <c r="AC2" t="n">
-        <v>5262485225472</v>
+        <v>5333097906176</v>
       </c>
       <c r="AD2" t="n">
         <v>201266003968</v>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:15:35</t>
+          <t>2026-09-19 15:21:20</t>
         </is>
       </c>
     </row>

--- a/data/NVDA_data.xlsx
+++ b/data/NVDA_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45919</v>
+        <v>45925</v>
       </c>
       <c r="B2" t="n">
-        <v>175.349898865447</v>
+        <v>174.0629701066951</v>
       </c>
       <c r="C2" t="n">
-        <v>177.6543753314711</v>
+        <v>179.8291540783439</v>
       </c>
       <c r="D2" t="n">
-        <v>174.7612974471592</v>
+        <v>172.7162058826927</v>
       </c>
       <c r="E2" t="n">
-        <v>176.2477416992188</v>
+        <v>177.2653045654297</v>
       </c>
       <c r="F2" t="n">
-        <v>237182100</v>
+        <v>191586700</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45922</v>
+        <v>45926</v>
       </c>
       <c r="B3" t="n">
-        <v>174.8810218455756</v>
+        <v>177.7441426621237</v>
       </c>
       <c r="C3" t="n">
-        <v>184.1089135963474</v>
+        <v>179.3403244887289</v>
       </c>
       <c r="D3" t="n">
-        <v>174.2924356467209</v>
+        <v>174.5118813132914</v>
       </c>
       <c r="E3" t="n">
-        <v>183.1711578369141</v>
+        <v>177.7640991210938</v>
       </c>
       <c r="F3" t="n">
-        <v>269637000</v>
+        <v>148573700</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45923</v>
+        <v>45929</v>
       </c>
       <c r="B4" t="n">
-        <v>181.5350878652714</v>
+        <v>179.9987400973632</v>
       </c>
       <c r="C4" t="n">
-        <v>181.9840093083128</v>
+        <v>183.5602146114836</v>
       </c>
       <c r="D4" t="n">
-        <v>175.7888599052367</v>
+        <v>179.8890176259668</v>
       </c>
       <c r="E4" t="n">
-        <v>178.0035400390625</v>
+        <v>181.4153594970703</v>
       </c>
       <c r="F4" t="n">
-        <v>192559600</v>
+        <v>193063500</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45924</v>
+        <v>45930</v>
       </c>
       <c r="B5" t="n">
-        <v>179.3403383898065</v>
+        <v>181.6448190078555</v>
       </c>
       <c r="C5" t="n">
-        <v>179.3503090089054</v>
+        <v>186.9022276338177</v>
       </c>
       <c r="D5" t="n">
-        <v>174.9807727171775</v>
+        <v>181.0462469572146</v>
       </c>
       <c r="E5" t="n">
-        <v>176.5470275878906</v>
+        <v>186.1340637207031</v>
       </c>
       <c r="F5" t="n">
-        <v>143564100</v>
+        <v>236981000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45925</v>
+        <v>45931</v>
       </c>
       <c r="B6" t="n">
-        <v>174.0629701066951</v>
+        <v>184.7972606974542</v>
       </c>
       <c r="C6" t="n">
-        <v>179.8291540783439</v>
+        <v>187.6903232769056</v>
       </c>
       <c r="D6" t="n">
-        <v>172.7162058826927</v>
+        <v>183.4604518817237</v>
       </c>
       <c r="E6" t="n">
-        <v>177.2653045654297</v>
+        <v>186.79248046875</v>
       </c>
       <c r="F6" t="n">
-        <v>191586700</v>
+        <v>173844900</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45926</v>
+        <v>45932</v>
       </c>
       <c r="B7" t="n">
-        <v>177.7441579191998</v>
+        <v>189.146847340247</v>
       </c>
       <c r="C7" t="n">
-        <v>179.3403398828169</v>
+        <v>190.59337868299</v>
       </c>
       <c r="D7" t="n">
-        <v>174.5118962929188</v>
+        <v>187.6105195355423</v>
       </c>
       <c r="E7" t="n">
-        <v>177.7641143798828</v>
+        <v>188.4385375976562</v>
       </c>
       <c r="F7" t="n">
-        <v>148573700</v>
+        <v>136805800</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45929</v>
+        <v>45933</v>
       </c>
       <c r="B8" t="n">
-        <v>179.9987552370008</v>
+        <v>188.7378247179256</v>
       </c>
       <c r="C8" t="n">
-        <v>183.5602300506758</v>
+        <v>189.9050265070322</v>
       </c>
       <c r="D8" t="n">
-        <v>179.8890327563757</v>
+        <v>184.9369333277354</v>
       </c>
       <c r="E8" t="n">
-        <v>181.4153747558594</v>
+        <v>187.1715698242188</v>
       </c>
       <c r="F8" t="n">
-        <v>193063500</v>
+        <v>137596900</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45930</v>
+        <v>45936</v>
       </c>
       <c r="B9" t="n">
-        <v>181.6448190078555</v>
+        <v>185.0566446584491</v>
       </c>
       <c r="C9" t="n">
-        <v>186.9022276338177</v>
+        <v>186.7825055997528</v>
       </c>
       <c r="D9" t="n">
-        <v>181.0462469572146</v>
+        <v>182.8918329061041</v>
       </c>
       <c r="E9" t="n">
-        <v>186.1340637207031</v>
+        <v>185.0965423583984</v>
       </c>
       <c r="F9" t="n">
-        <v>236981000</v>
+        <v>157678100</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45931</v>
+        <v>45937</v>
       </c>
       <c r="B10" t="n">
-        <v>184.7972606974542</v>
+        <v>185.7848907820332</v>
       </c>
       <c r="C10" t="n">
-        <v>187.6903232769056</v>
+        <v>188.6081286768816</v>
       </c>
       <c r="D10" t="n">
-        <v>183.4604518817237</v>
+        <v>183.5602249269612</v>
       </c>
       <c r="E10" t="n">
-        <v>186.79248046875</v>
+        <v>184.5977325439453</v>
       </c>
       <c r="F10" t="n">
-        <v>173844900</v>
+        <v>140088000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45932</v>
+        <v>45938</v>
       </c>
       <c r="B11" t="n">
-        <v>189.1468626563914</v>
+        <v>186.1240974206304</v>
       </c>
       <c r="C11" t="n">
-        <v>190.593394116267</v>
+        <v>189.1468543796426</v>
       </c>
       <c r="D11" t="n">
-        <v>187.6105347272827</v>
+        <v>186.0941551173159</v>
       </c>
       <c r="E11" t="n">
-        <v>188.4385528564453</v>
+        <v>188.6580200195312</v>
       </c>
       <c r="F11" t="n">
-        <v>136805800</v>
+        <v>130168900</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45933</v>
+        <v>45939</v>
       </c>
       <c r="B12" t="n">
-        <v>188.7378093314507</v>
+        <v>191.7705575158363</v>
       </c>
       <c r="C12" t="n">
-        <v>189.9050110254035</v>
+        <v>194.833227386451</v>
       </c>
       <c r="D12" t="n">
-        <v>184.9369182511207</v>
+        <v>190.6033556943829</v>
       </c>
       <c r="E12" t="n">
-        <v>187.1715545654297</v>
+        <v>192.1097564697266</v>
       </c>
       <c r="F12" t="n">
-        <v>137596900</v>
+        <v>182997200</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45936</v>
+        <v>45940</v>
       </c>
       <c r="B13" t="n">
-        <v>185.0566446584491</v>
+        <v>193.0474821132437</v>
       </c>
       <c r="C13" t="n">
-        <v>186.7825055997528</v>
+        <v>195.1524395658232</v>
       </c>
       <c r="D13" t="n">
-        <v>182.8918329061041</v>
+        <v>181.6148814298513</v>
       </c>
       <c r="E13" t="n">
-        <v>185.0965423583984</v>
+        <v>182.7222290039062</v>
       </c>
       <c r="F13" t="n">
-        <v>157678100</v>
+        <v>268774400</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45937</v>
+        <v>45943</v>
       </c>
       <c r="B14" t="n">
-        <v>185.7848907820332</v>
+        <v>187.5207644715895</v>
       </c>
       <c r="C14" t="n">
-        <v>188.6081286768816</v>
+        <v>189.6556493942343</v>
       </c>
       <c r="D14" t="n">
-        <v>183.5602249269612</v>
+        <v>185.5155737280782</v>
       </c>
       <c r="E14" t="n">
-        <v>184.5977325439453</v>
+        <v>187.8699340820312</v>
       </c>
       <c r="F14" t="n">
-        <v>140088000</v>
+        <v>153482800</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45938</v>
+        <v>45944</v>
       </c>
       <c r="B15" t="n">
-        <v>186.1240823667868</v>
+        <v>184.3283927796865</v>
       </c>
       <c r="C15" t="n">
-        <v>189.1468390813163</v>
+        <v>184.3583198600852</v>
       </c>
       <c r="D15" t="n">
-        <v>186.094140065894</v>
+        <v>179.2705030798172</v>
       </c>
       <c r="E15" t="n">
-        <v>188.6580047607422</v>
+        <v>179.5997161865234</v>
       </c>
       <c r="F15" t="n">
-        <v>130168900</v>
+        <v>205641400</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45939</v>
+        <v>45945</v>
       </c>
       <c r="B16" t="n">
-        <v>191.7705422839889</v>
+        <v>184.3583147400375</v>
       </c>
       <c r="C16" t="n">
-        <v>194.8332119113436</v>
+        <v>184.4281395182556</v>
       </c>
       <c r="D16" t="n">
-        <v>190.6033405552435</v>
+        <v>176.866254560341</v>
       </c>
       <c r="E16" t="n">
-        <v>192.1097412109375</v>
+        <v>179.4001922607422</v>
       </c>
       <c r="F16" t="n">
-        <v>182997200</v>
+        <v>214450500</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45940</v>
+        <v>45946</v>
       </c>
       <c r="B17" t="n">
-        <v>193.0474821132437</v>
+        <v>181.7944521048813</v>
       </c>
       <c r="C17" t="n">
-        <v>195.1524395658232</v>
+        <v>182.8419455690647</v>
       </c>
       <c r="D17" t="n">
-        <v>181.6148814298513</v>
+        <v>179.3403402174659</v>
       </c>
       <c r="E17" t="n">
-        <v>182.7222290039062</v>
+        <v>181.3754577636719</v>
       </c>
       <c r="F17" t="n">
-        <v>268774400</v>
+        <v>179723300</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45943</v>
+        <v>45947</v>
       </c>
       <c r="B18" t="n">
-        <v>187.5207340107304</v>
+        <v>179.7493615830456</v>
       </c>
       <c r="C18" t="n">
-        <v>189.6556185865847</v>
+        <v>183.6600061588844</v>
       </c>
       <c r="D18" t="n">
-        <v>185.5155435929421</v>
+        <v>179.3203965919317</v>
       </c>
       <c r="E18" t="n">
-        <v>187.8699035644531</v>
+        <v>182.7821044921875</v>
       </c>
       <c r="F18" t="n">
-        <v>153482800</v>
+        <v>173135200</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45944</v>
+        <v>45950</v>
       </c>
       <c r="B19" t="n">
-        <v>184.3283927796865</v>
+        <v>182.6923102950553</v>
       </c>
       <c r="C19" t="n">
-        <v>184.3583198600852</v>
+        <v>184.7573549226016</v>
       </c>
       <c r="D19" t="n">
-        <v>179.2705030798172</v>
+        <v>181.2956472677441</v>
       </c>
       <c r="E19" t="n">
-        <v>179.5997161865234</v>
+        <v>182.2034759521484</v>
       </c>
       <c r="F19" t="n">
-        <v>205641400</v>
+        <v>128544700</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45945</v>
+        <v>45951</v>
       </c>
       <c r="B20" t="n">
-        <v>184.3583147400375</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="C20" t="n">
-        <v>184.4281395182556</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="D20" t="n">
-        <v>176.866254560341</v>
+        <v>179.3702701372806</v>
       </c>
       <c r="E20" t="n">
-        <v>179.4001922607422</v>
+        <v>180.7270202636719</v>
       </c>
       <c r="F20" t="n">
-        <v>214450500</v>
+        <v>124240200</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45946</v>
+        <v>45952</v>
       </c>
       <c r="B21" t="n">
-        <v>181.7944521048813</v>
+        <v>180.7070662621498</v>
       </c>
       <c r="C21" t="n">
-        <v>182.8419455690647</v>
+        <v>183.0015721983185</v>
       </c>
       <c r="D21" t="n">
-        <v>179.3403402174659</v>
+        <v>176.3375297972393</v>
       </c>
       <c r="E21" t="n">
-        <v>181.3754577636719</v>
+        <v>179.84912109375</v>
       </c>
       <c r="F21" t="n">
-        <v>179723300</v>
+        <v>162249600</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45947</v>
+        <v>45953</v>
       </c>
       <c r="B22" t="n">
-        <v>179.7493615830456</v>
+        <v>179.988762799469</v>
       </c>
       <c r="C22" t="n">
-        <v>183.6600061588844</v>
+        <v>182.5925250516066</v>
       </c>
       <c r="D22" t="n">
-        <v>179.3203965919317</v>
+        <v>179.3602637385785</v>
       </c>
       <c r="E22" t="n">
-        <v>182.7821044921875</v>
+        <v>181.724609375</v>
       </c>
       <c r="F22" t="n">
-        <v>173135200</v>
+        <v>111363700</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45950</v>
+        <v>45954</v>
       </c>
       <c r="B23" t="n">
-        <v>182.6923102950553</v>
+        <v>183.4006051417061</v>
       </c>
       <c r="C23" t="n">
-        <v>184.7573549226016</v>
+        <v>187.0219340442129</v>
       </c>
       <c r="D23" t="n">
-        <v>181.2956472677441</v>
+        <v>183.0614214202242</v>
       </c>
       <c r="E23" t="n">
-        <v>182.2034759521484</v>
+        <v>185.8148193359375</v>
       </c>
       <c r="F23" t="n">
-        <v>128544700</v>
+        <v>131296700</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45951</v>
+        <v>45957</v>
       </c>
       <c r="B24" t="n">
-        <v>182.3531141136141</v>
+        <v>189.5359184602369</v>
       </c>
       <c r="C24" t="n">
-        <v>182.3531141136141</v>
+        <v>191.5411089646758</v>
       </c>
       <c r="D24" t="n">
-        <v>179.3702701372806</v>
+        <v>187.9796341631504</v>
       </c>
       <c r="E24" t="n">
-        <v>180.7270202636719</v>
+        <v>191.0323333740234</v>
       </c>
       <c r="F24" t="n">
-        <v>124240200</v>
+        <v>153452700</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45952</v>
+        <v>45958</v>
       </c>
       <c r="B25" t="n">
-        <v>180.7070509305708</v>
+        <v>192.5886067715161</v>
       </c>
       <c r="C25" t="n">
-        <v>183.0015566720687</v>
+        <v>202.6644582837766</v>
       </c>
       <c r="D25" t="n">
-        <v>176.3375148363812</v>
+        <v>191.4513320204045</v>
       </c>
       <c r="E25" t="n">
-        <v>179.8491058349609</v>
+        <v>200.5495300292969</v>
       </c>
       <c r="F25" t="n">
-        <v>162249600</v>
+        <v>297986200</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45953</v>
+        <v>45959</v>
       </c>
       <c r="B26" t="n">
-        <v>179.988793025541</v>
+        <v>207.482891187405</v>
       </c>
       <c r="C26" t="n">
-        <v>182.5925557149365</v>
+        <v>211.6828353303786</v>
       </c>
       <c r="D26" t="n">
-        <v>179.3602938591047</v>
+        <v>204.2905427296142</v>
       </c>
       <c r="E26" t="n">
-        <v>181.7246398925781</v>
+        <v>206.5451354980469</v>
       </c>
       <c r="F26" t="n">
-        <v>111363700</v>
+        <v>308829600</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45954</v>
+        <v>45960</v>
       </c>
       <c r="B27" t="n">
-        <v>183.400590081168</v>
+        <v>204.6596680014167</v>
       </c>
       <c r="C27" t="n">
-        <v>187.0219186862977</v>
+        <v>205.6672637579894</v>
       </c>
       <c r="D27" t="n">
-        <v>183.0614063875393</v>
+        <v>200.9286166610889</v>
       </c>
       <c r="E27" t="n">
-        <v>185.8148040771484</v>
+        <v>202.4050750732422</v>
       </c>
       <c r="F27" t="n">
-        <v>131296700</v>
+        <v>178864400</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45957</v>
+        <v>45961</v>
       </c>
       <c r="B28" t="n">
-        <v>189.5359184602369</v>
+        <v>205.9565537660584</v>
       </c>
       <c r="C28" t="n">
-        <v>191.5411089646758</v>
+        <v>207.4729250244422</v>
       </c>
       <c r="D28" t="n">
-        <v>187.9796341631504</v>
+        <v>201.5870329046891</v>
       </c>
       <c r="E28" t="n">
-        <v>191.0323333740234</v>
+        <v>202.0060272216797</v>
       </c>
       <c r="F28" t="n">
-        <v>153452700</v>
+        <v>179802200</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45958</v>
+        <v>45964</v>
       </c>
       <c r="B29" t="n">
-        <v>192.5886067715161</v>
+        <v>207.5826880225491</v>
       </c>
       <c r="C29" t="n">
-        <v>202.6644582837766</v>
+        <v>210.8348911017148</v>
       </c>
       <c r="D29" t="n">
-        <v>191.4513320204045</v>
+        <v>205.0687065918373</v>
       </c>
       <c r="E29" t="n">
-        <v>200.5495300292969</v>
+        <v>206.3855590820312</v>
       </c>
       <c r="F29" t="n">
-        <v>297986200</v>
+        <v>180267300</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45959</v>
+        <v>45965</v>
       </c>
       <c r="B30" t="n">
-        <v>207.482921843539</v>
+        <v>202.5148147488263</v>
       </c>
       <c r="C30" t="n">
-        <v>211.6828666070652</v>
+        <v>203.4824975937368</v>
       </c>
       <c r="D30" t="n">
-        <v>204.2905729140704</v>
+        <v>197.4569251230167</v>
       </c>
       <c r="E30" t="n">
-        <v>206.545166015625</v>
+        <v>198.2151184082031</v>
       </c>
       <c r="F30" t="n">
-        <v>308829600</v>
+        <v>188919300</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45960</v>
+        <v>45966</v>
       </c>
       <c r="B31" t="n">
-        <v>204.6596680014167</v>
+        <v>198.2949275919373</v>
       </c>
       <c r="C31" t="n">
-        <v>205.6672637579894</v>
+        <v>202.4350026612236</v>
       </c>
       <c r="D31" t="n">
-        <v>200.9286166610889</v>
+        <v>194.1847643800754</v>
       </c>
       <c r="E31" t="n">
-        <v>202.4050750732422</v>
+        <v>194.7434387207031</v>
       </c>
       <c r="F31" t="n">
-        <v>178864400</v>
+        <v>171350300</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45961</v>
+        <v>45967</v>
       </c>
       <c r="B32" t="n">
-        <v>205.9565537660584</v>
+        <v>195.9505251524069</v>
       </c>
       <c r="C32" t="n">
-        <v>207.4729250244422</v>
+        <v>197.1476539294223</v>
       </c>
       <c r="D32" t="n">
-        <v>201.5870329046891</v>
+        <v>185.9345289438528</v>
       </c>
       <c r="E32" t="n">
-        <v>202.0060272216797</v>
+        <v>187.6304626464844</v>
       </c>
       <c r="F32" t="n">
-        <v>179802200</v>
+        <v>223029800</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45964</v>
+        <v>45968</v>
       </c>
       <c r="B33" t="n">
-        <v>207.5826726752522</v>
+        <v>184.4580548583195</v>
       </c>
       <c r="C33" t="n">
-        <v>210.8348755139714</v>
+        <v>187.8698939350823</v>
       </c>
       <c r="D33" t="n">
-        <v>205.0686914304077</v>
+        <v>178.4823816093971</v>
       </c>
       <c r="E33" t="n">
-        <v>206.3855438232422</v>
+        <v>187.7002868652344</v>
       </c>
       <c r="F33" t="n">
-        <v>180267300</v>
+        <v>264942300</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45965</v>
+        <v>45971</v>
       </c>
       <c r="B34" t="n">
-        <v>202.5148147488263</v>
+        <v>194.6436788693004</v>
       </c>
       <c r="C34" t="n">
-        <v>203.4824975937368</v>
+        <v>199.4621367771523</v>
       </c>
       <c r="D34" t="n">
-        <v>197.4569251230167</v>
+        <v>193.3268264223904</v>
       </c>
       <c r="E34" t="n">
-        <v>198.2151184082031</v>
+        <v>198.5742645263672</v>
       </c>
       <c r="F34" t="n">
-        <v>188919300</v>
+        <v>198897100</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45966</v>
+        <v>45972</v>
       </c>
       <c r="B35" t="n">
-        <v>198.2949275919373</v>
+        <v>194.6935535589016</v>
       </c>
       <c r="C35" t="n">
-        <v>202.4350026612236</v>
+        <v>194.9529266552934</v>
       </c>
       <c r="D35" t="n">
-        <v>194.1847643800754</v>
+        <v>190.8427786999811</v>
       </c>
       <c r="E35" t="n">
-        <v>194.7434387207031</v>
+        <v>192.6983337402344</v>
       </c>
       <c r="F35" t="n">
-        <v>171350300</v>
+        <v>176483300</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45967</v>
+        <v>45973</v>
       </c>
       <c r="B36" t="n">
-        <v>195.9505410878136</v>
+        <v>195.2522164876445</v>
       </c>
       <c r="C36" t="n">
-        <v>197.1476699621838</v>
+        <v>195.4218083488666</v>
       </c>
       <c r="D36" t="n">
-        <v>185.9345440647224</v>
+        <v>190.673190567689</v>
       </c>
       <c r="E36" t="n">
-        <v>187.6304779052734</v>
+        <v>193.3368072509766</v>
       </c>
       <c r="F36" t="n">
-        <v>223029800</v>
+        <v>154935300</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45968</v>
+        <v>45974</v>
       </c>
       <c r="B37" t="n">
-        <v>184.4580698535366</v>
+        <v>190.5933791327836</v>
       </c>
       <c r="C37" t="n">
-        <v>187.8699092076593</v>
+        <v>190.9824463944715</v>
       </c>
       <c r="D37" t="n">
-        <v>178.4823961188316</v>
+        <v>183.4105907203728</v>
       </c>
       <c r="E37" t="n">
-        <v>187.7003021240234</v>
+        <v>186.4133911132812</v>
       </c>
       <c r="F37" t="n">
-        <v>264942300</v>
+        <v>207423100</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45971</v>
+        <v>45975</v>
       </c>
       <c r="B38" t="n">
-        <v>194.6436788693004</v>
+        <v>182.4229435613052</v>
       </c>
       <c r="C38" t="n">
-        <v>199.4621367771523</v>
+        <v>190.553458007553</v>
       </c>
       <c r="D38" t="n">
-        <v>193.3268264223904</v>
+        <v>180.1483942490048</v>
       </c>
       <c r="E38" t="n">
-        <v>198.5742645263672</v>
+        <v>189.7154693603516</v>
       </c>
       <c r="F38" t="n">
-        <v>198897100</v>
+        <v>186591900</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45972</v>
+        <v>45978</v>
       </c>
       <c r="B39" t="n">
-        <v>194.6935535589016</v>
+        <v>185.5255230789849</v>
       </c>
       <c r="C39" t="n">
-        <v>194.9529266552934</v>
+        <v>188.5482800008962</v>
       </c>
       <c r="D39" t="n">
-        <v>190.8427786999811</v>
+        <v>183.8794727552066</v>
       </c>
       <c r="E39" t="n">
-        <v>192.6983337402344</v>
+        <v>186.1540222167969</v>
       </c>
       <c r="F39" t="n">
-        <v>176483300</v>
+        <v>173628900</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45973</v>
+        <v>45979</v>
       </c>
       <c r="B40" t="n">
-        <v>195.2522164876445</v>
+        <v>182.9417205846578</v>
       </c>
       <c r="C40" t="n">
-        <v>195.4218083488666</v>
+        <v>184.3583249108488</v>
       </c>
       <c r="D40" t="n">
-        <v>190.673190567689</v>
+        <v>179.2206244483882</v>
       </c>
       <c r="E40" t="n">
-        <v>193.3368072509766</v>
+        <v>180.9265441894531</v>
       </c>
       <c r="F40" t="n">
-        <v>154935300</v>
+        <v>213598900</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45974</v>
+        <v>45980</v>
       </c>
       <c r="B41" t="n">
-        <v>190.5933635318434</v>
+        <v>184.3483273978252</v>
       </c>
       <c r="C41" t="n">
-        <v>190.9824307616844</v>
+        <v>187.4109971087465</v>
       </c>
       <c r="D41" t="n">
-        <v>183.4105757073767</v>
+        <v>182.3930205111681</v>
       </c>
       <c r="E41" t="n">
-        <v>186.4133758544922</v>
+        <v>186.0742034912109</v>
       </c>
       <c r="F41" t="n">
-        <v>207423100</v>
+        <v>247246400</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45975</v>
+        <v>45981</v>
       </c>
       <c r="B42" t="n">
-        <v>182.4229435613052</v>
+        <v>195.4816571057099</v>
       </c>
       <c r="C42" t="n">
-        <v>190.553458007553</v>
+        <v>195.5315406452363</v>
       </c>
       <c r="D42" t="n">
-        <v>180.1483942490048</v>
+        <v>179.4201468289569</v>
       </c>
       <c r="E42" t="n">
-        <v>189.7154693603516</v>
+        <v>180.208251953125</v>
       </c>
       <c r="F42" t="n">
-        <v>186591900</v>
+        <v>343504800</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45978</v>
+        <v>45982</v>
       </c>
       <c r="B43" t="n">
-        <v>185.525507871713</v>
+        <v>180.8068289121023</v>
       </c>
       <c r="C43" t="n">
-        <v>188.5482645458532</v>
+        <v>184.1188859589464</v>
       </c>
       <c r="D43" t="n">
-        <v>183.8794576828592</v>
+        <v>172.5166776199441</v>
       </c>
       <c r="E43" t="n">
-        <v>186.1540069580078</v>
+        <v>178.4524688720703</v>
       </c>
       <c r="F43" t="n">
-        <v>173628900</v>
+        <v>346926200</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45979</v>
+        <v>45985</v>
       </c>
       <c r="B44" t="n">
-        <v>182.9416897271721</v>
+        <v>179.0610243324759</v>
       </c>
       <c r="C44" t="n">
-        <v>184.358293814419</v>
+        <v>183.0614349513779</v>
       </c>
       <c r="D44" t="n">
-        <v>179.2205942185541</v>
+        <v>176.0582084909882</v>
       </c>
       <c r="E44" t="n">
-        <v>180.926513671875</v>
+        <v>182.1137084960938</v>
       </c>
       <c r="F44" t="n">
-        <v>213598900</v>
+        <v>256618300</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45980</v>
+        <v>45986</v>
       </c>
       <c r="B45" t="n">
-        <v>184.3483122805645</v>
+        <v>174.4919707447618</v>
       </c>
       <c r="C45" t="n">
-        <v>187.4109817403353</v>
+        <v>177.734203281764</v>
       </c>
       <c r="D45" t="n">
-        <v>182.39300555425</v>
+        <v>169.1447804748437</v>
       </c>
       <c r="E45" t="n">
-        <v>186.0741882324219</v>
+        <v>177.39501953125</v>
       </c>
       <c r="F45" t="n">
-        <v>247246400</v>
+        <v>320600300</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45981</v>
+        <v>45987</v>
       </c>
       <c r="B46" t="n">
-        <v>195.4816571057099</v>
+        <v>181.1958831941039</v>
       </c>
       <c r="C46" t="n">
-        <v>195.5315406452363</v>
+        <v>182.4728225932506</v>
       </c>
       <c r="D46" t="n">
-        <v>179.4201468289569</v>
+        <v>177.8139863878403</v>
       </c>
       <c r="E46" t="n">
-        <v>180.208251953125</v>
+        <v>179.8291473388672</v>
       </c>
       <c r="F46" t="n">
-        <v>343504800</v>
+        <v>183852000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45982</v>
+        <v>45989</v>
       </c>
       <c r="B47" t="n">
-        <v>180.806813452001</v>
+        <v>178.5821558989869</v>
       </c>
       <c r="C47" t="n">
-        <v>184.1188702156436</v>
+        <v>178.8614854738169</v>
       </c>
       <c r="D47" t="n">
-        <v>172.5166628687019</v>
+        <v>176.0781603452176</v>
       </c>
       <c r="E47" t="n">
-        <v>178.4524536132812</v>
+        <v>176.5769653320312</v>
       </c>
       <c r="F47" t="n">
-        <v>346926200</v>
+        <v>121332800</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45985</v>
+        <v>45992</v>
       </c>
       <c r="B48" t="n">
-        <v>179.0610093294625</v>
+        <v>174.3422893139723</v>
       </c>
       <c r="C48" t="n">
-        <v>183.0614196131816</v>
+        <v>179.8690563253026</v>
       </c>
       <c r="D48" t="n">
-        <v>176.0581937395723</v>
+        <v>173.2648688653124</v>
       </c>
       <c r="E48" t="n">
-        <v>182.1136932373047</v>
+        <v>179.4899597167969</v>
       </c>
       <c r="F48" t="n">
-        <v>256618300</v>
+        <v>188131000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45986</v>
+        <v>45993</v>
       </c>
       <c r="B49" t="n">
-        <v>174.4919407266003</v>
+        <v>181.3255922400764</v>
       </c>
       <c r="C49" t="n">
-        <v>177.7341727058355</v>
+        <v>185.2162804618737</v>
       </c>
       <c r="D49" t="n">
-        <v>169.1447513765687</v>
+        <v>179.5698040802165</v>
       </c>
       <c r="E49" t="n">
-        <v>177.3949890136719</v>
+        <v>181.0263214111328</v>
       </c>
       <c r="F49" t="n">
-        <v>320600300</v>
+        <v>182632200</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45987</v>
+        <v>45994</v>
       </c>
       <c r="B50" t="n">
-        <v>181.1958831941039</v>
+        <v>180.6471955161887</v>
       </c>
       <c r="C50" t="n">
-        <v>182.4728225932506</v>
+        <v>182.013916155068</v>
       </c>
       <c r="D50" t="n">
-        <v>177.8139863878403</v>
+        <v>178.6819028715845</v>
       </c>
       <c r="E50" t="n">
-        <v>179.8291473388672</v>
+        <v>179.1607513427734</v>
       </c>
       <c r="F50" t="n">
-        <v>183852000</v>
+        <v>165138000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,25 +1743,25 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45989</v>
+        <v>45995</v>
       </c>
       <c r="B51" t="n">
-        <v>178.5821404669205</v>
+        <v>181.1959881613664</v>
       </c>
       <c r="C51" t="n">
-        <v>178.8614700176124</v>
+        <v>184.089227004522</v>
       </c>
       <c r="D51" t="n">
-        <v>176.0781451295325</v>
+        <v>179.5398751387779</v>
       </c>
       <c r="E51" t="n">
-        <v>176.5769500732422</v>
+        <v>182.9518890380859</v>
       </c>
       <c r="F51" t="n">
-        <v>121332800</v>
+        <v>167364900</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45992</v>
+        <v>45996</v>
       </c>
       <c r="B52" t="n">
-        <v>174.3423189563235</v>
+        <v>183.4606866221248</v>
       </c>
       <c r="C52" t="n">
-        <v>179.8690869073362</v>
+        <v>184.2288932293168</v>
       </c>
       <c r="D52" t="n">
-        <v>173.2648983244765</v>
+        <v>180.4876480440623</v>
       </c>
       <c r="E52" t="n">
-        <v>179.489990234375</v>
+        <v>181.9841461181641</v>
       </c>
       <c r="F52" t="n">
-        <v>188131000</v>
+        <v>143971100</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45993</v>
+        <v>45999</v>
       </c>
       <c r="B53" t="n">
-        <v>181.3255769560617</v>
+        <v>182.2136112701494</v>
       </c>
       <c r="C53" t="n">
-        <v>185.2162648499111</v>
+        <v>187.5610985176648</v>
       </c>
       <c r="D53" t="n">
-        <v>179.569788944198</v>
+        <v>181.9741660895743</v>
       </c>
       <c r="E53" t="n">
-        <v>181.0263061523438</v>
+        <v>185.1168212890625</v>
       </c>
       <c r="F53" t="n">
-        <v>182632200</v>
+        <v>204378100</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45994</v>
+        <v>46000</v>
       </c>
       <c r="B54" t="n">
-        <v>180.6472109015755</v>
+        <v>185.12679644575</v>
       </c>
       <c r="C54" t="n">
-        <v>182.0139316568558</v>
+        <v>185.2864265695677</v>
       </c>
       <c r="D54" t="n">
-        <v>178.681918089591</v>
+        <v>182.8920356049676</v>
       </c>
       <c r="E54" t="n">
-        <v>179.1607666015625</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="F54" t="n">
-        <v>165138000</v>
+        <v>144719700</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,25 +1847,25 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45995</v>
+        <v>46001</v>
       </c>
       <c r="B55" t="n">
-        <v>181.1959881613664</v>
+        <v>184.5381918075859</v>
       </c>
       <c r="C55" t="n">
-        <v>184.089227004522</v>
+        <v>185.0469957406681</v>
       </c>
       <c r="D55" t="n">
-        <v>179.5398751387779</v>
+        <v>181.6150239281505</v>
       </c>
       <c r="E55" t="n">
-        <v>182.9518890380859</v>
+        <v>183.3509674072266</v>
       </c>
       <c r="F55" t="n">
-        <v>167364900</v>
+        <v>162785400</v>
       </c>
       <c r="G55" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45996</v>
+        <v>46002</v>
       </c>
       <c r="B56" t="n">
-        <v>183.4607020047171</v>
+        <v>179.8591224369562</v>
       </c>
       <c r="C56" t="n">
-        <v>184.2289086763207</v>
+        <v>180.8967030087509</v>
       </c>
       <c r="D56" t="n">
-        <v>180.4876631773748</v>
+        <v>176.2076633109278</v>
       </c>
       <c r="E56" t="n">
-        <v>181.9841613769531</v>
+        <v>180.5075988769531</v>
       </c>
       <c r="F56" t="n">
-        <v>143971100</v>
+        <v>182136600</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45999</v>
+        <v>46003</v>
       </c>
       <c r="B57" t="n">
-        <v>182.2136112701494</v>
+        <v>180.6871989054384</v>
       </c>
       <c r="C57" t="n">
-        <v>187.5610985176648</v>
+        <v>182.3932136047752</v>
       </c>
       <c r="D57" t="n">
-        <v>181.9741660895743</v>
+        <v>174.2123443447362</v>
       </c>
       <c r="E57" t="n">
-        <v>185.1168212890625</v>
+        <v>174.6114196777344</v>
       </c>
       <c r="F57" t="n">
-        <v>204378100</v>
+        <v>204274900</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46000</v>
+        <v>46006</v>
       </c>
       <c r="B58" t="n">
-        <v>185.1268117532098</v>
+        <v>177.5245903328353</v>
       </c>
       <c r="C58" t="n">
-        <v>185.2864418902268</v>
+        <v>178.0034654802094</v>
       </c>
       <c r="D58" t="n">
-        <v>182.8920507276432</v>
+        <v>174.6213802569945</v>
       </c>
       <c r="E58" t="n">
-        <v>184.5381927490234</v>
+        <v>175.8784332275391</v>
       </c>
       <c r="F58" t="n">
-        <v>144719700</v>
+        <v>164775600</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="B59" t="n">
-        <v>184.538176449994</v>
+        <v>175.8485012773324</v>
       </c>
       <c r="C59" t="n">
-        <v>185.0469803407326</v>
+        <v>178.0733061224419</v>
       </c>
       <c r="D59" t="n">
-        <v>181.6150088138297</v>
+        <v>174.4916756985292</v>
       </c>
       <c r="E59" t="n">
-        <v>183.3509521484375</v>
+        <v>177.3050994873047</v>
       </c>
       <c r="F59" t="n">
-        <v>162785400</v>
+        <v>148588100</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46002</v>
+        <v>46008</v>
       </c>
       <c r="B60" t="n">
-        <v>179.8591224369562</v>
+        <v>175.6888811343</v>
       </c>
       <c r="C60" t="n">
-        <v>180.8967030087509</v>
+        <v>175.7188098781239</v>
       </c>
       <c r="D60" t="n">
-        <v>176.2076633109278</v>
+        <v>169.9123900056319</v>
       </c>
       <c r="E60" t="n">
-        <v>180.5075988769531</v>
+        <v>170.5409240722656</v>
       </c>
       <c r="F60" t="n">
-        <v>182136600</v>
+        <v>222775500</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46003</v>
+        <v>46009</v>
       </c>
       <c r="B61" t="n">
-        <v>180.6871989054384</v>
+        <v>174.1225483861358</v>
       </c>
       <c r="C61" t="n">
-        <v>182.3932136047752</v>
+        <v>175.7387615308714</v>
       </c>
       <c r="D61" t="n">
-        <v>174.2123443447362</v>
+        <v>171.4188835631069</v>
       </c>
       <c r="E61" t="n">
-        <v>174.6114196777344</v>
+        <v>173.7334594726562</v>
       </c>
       <c r="F61" t="n">
-        <v>204274900</v>
+        <v>176096000</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="B62" t="n">
-        <v>177.5245903328353</v>
+        <v>176.2575672304301</v>
       </c>
       <c r="C62" t="n">
-        <v>178.0034654802094</v>
+        <v>181.0264072425164</v>
       </c>
       <c r="D62" t="n">
-        <v>174.6213802569945</v>
+        <v>175.9283357789888</v>
       </c>
       <c r="E62" t="n">
-        <v>175.8784332275391</v>
+        <v>180.5674896240234</v>
       </c>
       <c r="F62" t="n">
-        <v>164775600</v>
+        <v>324925900</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46007</v>
+        <v>46013</v>
       </c>
       <c r="B63" t="n">
-        <v>175.8485012773324</v>
+        <v>183.4906282252173</v>
       </c>
       <c r="C63" t="n">
-        <v>178.0733061224419</v>
+        <v>183.7300734141942</v>
       </c>
       <c r="D63" t="n">
-        <v>174.4916756985292</v>
+        <v>181.9243013805983</v>
       </c>
       <c r="E63" t="n">
-        <v>177.3050994873047</v>
+        <v>183.2611694335938</v>
       </c>
       <c r="F63" t="n">
-        <v>148588100</v>
+        <v>129064400</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="B64" t="n">
-        <v>175.6888968536916</v>
+        <v>182.5428571096804</v>
       </c>
       <c r="C64" t="n">
-        <v>175.7188256001934</v>
+        <v>188.8880102762506</v>
       </c>
       <c r="D64" t="n">
-        <v>169.9124052081842</v>
+        <v>182.4730132178061</v>
       </c>
       <c r="E64" t="n">
-        <v>170.5409393310547</v>
+        <v>188.7682952880859</v>
       </c>
       <c r="F64" t="n">
-        <v>222775500</v>
+        <v>174873600</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46009</v>
+        <v>46015</v>
       </c>
       <c r="B65" t="n">
-        <v>174.1225483861358</v>
+        <v>187.5012437217294</v>
       </c>
       <c r="C65" t="n">
-        <v>175.7387615308714</v>
+        <v>188.4689804086018</v>
       </c>
       <c r="D65" t="n">
-        <v>171.4188835631069</v>
+        <v>186.154389299292</v>
       </c>
       <c r="E65" t="n">
-        <v>173.7334594726562</v>
+        <v>188.169677734375</v>
       </c>
       <c r="F65" t="n">
-        <v>176096000</v>
+        <v>65528500</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46010</v>
+        <v>46017</v>
       </c>
       <c r="B66" t="n">
-        <v>176.2575523358494</v>
+        <v>189.4766285187414</v>
       </c>
       <c r="C66" t="n">
-        <v>181.0263919449467</v>
+        <v>192.240166195598</v>
       </c>
       <c r="D66" t="n">
-        <v>175.9283209122297</v>
+        <v>187.5611125998212</v>
       </c>
       <c r="E66" t="n">
-        <v>180.5674743652344</v>
+        <v>190.085205078125</v>
       </c>
       <c r="F66" t="n">
-        <v>324925900</v>
+        <v>139740300</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46013</v>
+        <v>46020</v>
       </c>
       <c r="B67" t="n">
-        <v>183.4906282252173</v>
+        <v>187.2717899684254</v>
       </c>
       <c r="C67" t="n">
-        <v>183.7300734141942</v>
+        <v>188.3193265216257</v>
       </c>
       <c r="D67" t="n">
-        <v>181.9243013805983</v>
+        <v>185.4759890979627</v>
       </c>
       <c r="E67" t="n">
-        <v>183.2611694335938</v>
+        <v>187.7805938720703</v>
       </c>
       <c r="F67" t="n">
-        <v>129064400</v>
+        <v>120006100</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46014</v>
+        <v>46021</v>
       </c>
       <c r="B68" t="n">
-        <v>182.5428571096804</v>
+        <v>187.8005508490403</v>
       </c>
       <c r="C68" t="n">
-        <v>188.8880102762506</v>
+        <v>188.5487999407664</v>
       </c>
       <c r="D68" t="n">
-        <v>182.4730132178061</v>
+        <v>186.4935963146986</v>
       </c>
       <c r="E68" t="n">
-        <v>188.7682952880859</v>
+        <v>187.1021728515625</v>
       </c>
       <c r="F68" t="n">
-        <v>174873600</v>
+        <v>97687300</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46015</v>
+        <v>46022</v>
       </c>
       <c r="B69" t="n">
-        <v>187.5012437217294</v>
+        <v>189.1274459397885</v>
       </c>
       <c r="C69" t="n">
-        <v>188.4689804086018</v>
+        <v>190.1151249886817</v>
       </c>
       <c r="D69" t="n">
-        <v>186.154389299292</v>
+        <v>186.0546345387688</v>
       </c>
       <c r="E69" t="n">
-        <v>188.169677734375</v>
+        <v>186.0646057128906</v>
       </c>
       <c r="F69" t="n">
-        <v>65528500</v>
+        <v>120100500</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46017</v>
+        <v>46024</v>
       </c>
       <c r="B70" t="n">
-        <v>189.4766285187414</v>
+        <v>189.3968130035911</v>
       </c>
       <c r="C70" t="n">
-        <v>192.240166195598</v>
+        <v>192.4795957147097</v>
       </c>
       <c r="D70" t="n">
-        <v>187.5611125998212</v>
+        <v>187.8204997023152</v>
       </c>
       <c r="E70" t="n">
-        <v>190.085205078125</v>
+        <v>188.4091339111328</v>
       </c>
       <c r="F70" t="n">
-        <v>139740300</v>
+        <v>148240500</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46020</v>
+        <v>46027</v>
       </c>
       <c r="B71" t="n">
-        <v>187.2717899684254</v>
+        <v>191.3123182227279</v>
       </c>
       <c r="C71" t="n">
-        <v>188.3193265216257</v>
+        <v>193.1779629368336</v>
       </c>
       <c r="D71" t="n">
-        <v>185.4759890979627</v>
+        <v>185.7154145267434</v>
       </c>
       <c r="E71" t="n">
-        <v>187.7805938720703</v>
+        <v>187.6808166503906</v>
       </c>
       <c r="F71" t="n">
-        <v>120006100</v>
+        <v>183529700</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46021</v>
+        <v>46028</v>
       </c>
       <c r="B72" t="n">
-        <v>187.8005661647843</v>
+        <v>190.0752284670132</v>
       </c>
       <c r="C72" t="n">
-        <v>188.5488153175326</v>
+        <v>191.7213703933745</v>
       </c>
       <c r="D72" t="n">
-        <v>186.4936115238563</v>
+        <v>186.3838692947835</v>
       </c>
       <c r="E72" t="n">
-        <v>187.1021881103516</v>
+        <v>186.8028869628906</v>
       </c>
       <c r="F72" t="n">
-        <v>97687300</v>
+        <v>176862600</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46022</v>
+        <v>46029</v>
       </c>
       <c r="B73" t="n">
-        <v>189.1274459397885</v>
+        <v>188.1297854095839</v>
       </c>
       <c r="C73" t="n">
-        <v>190.1151249886817</v>
+        <v>190.9232365533545</v>
       </c>
       <c r="D73" t="n">
-        <v>186.0546345387688</v>
+        <v>186.1244680675316</v>
       </c>
       <c r="E73" t="n">
-        <v>186.0646057128906</v>
+        <v>188.6685180664062</v>
       </c>
       <c r="F73" t="n">
-        <v>120100500</v>
+        <v>153543200</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46024</v>
+        <v>46030</v>
       </c>
       <c r="B74" t="n">
-        <v>189.3968130035911</v>
+        <v>188.6685228499072</v>
       </c>
       <c r="C74" t="n">
-        <v>192.4795957147097</v>
+        <v>189.1074981045344</v>
       </c>
       <c r="D74" t="n">
-        <v>187.8204997023152</v>
+        <v>183.2811352524241</v>
       </c>
       <c r="E74" t="n">
-        <v>188.4091339111328</v>
+        <v>184.6080169677734</v>
       </c>
       <c r="F74" t="n">
-        <v>148240500</v>
+        <v>172457000</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46027</v>
+        <v>46031</v>
       </c>
       <c r="B75" t="n">
-        <v>191.3123337767646</v>
+        <v>184.6479238968445</v>
       </c>
       <c r="C75" t="n">
-        <v>193.1779786425506</v>
+        <v>185.9049768874807</v>
       </c>
       <c r="D75" t="n">
-        <v>185.7154296257417</v>
+        <v>183.2412119543349</v>
       </c>
       <c r="E75" t="n">
-        <v>187.6808319091797</v>
+        <v>184.4284362792969</v>
       </c>
       <c r="F75" t="n">
-        <v>183529700</v>
+        <v>131327500</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46028</v>
+        <v>46034</v>
       </c>
       <c r="B76" t="n">
-        <v>190.0752439930999</v>
+        <v>182.7922691735387</v>
       </c>
       <c r="C76" t="n">
-        <v>191.7213860539245</v>
+        <v>186.6831584288149</v>
       </c>
       <c r="D76" t="n">
-        <v>186.3838845193456</v>
+        <v>182.5927391235801</v>
       </c>
       <c r="E76" t="n">
-        <v>186.8029022216797</v>
+        <v>184.5082550048828</v>
       </c>
       <c r="F76" t="n">
-        <v>176862600</v>
+        <v>137968500</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46029</v>
+        <v>46035</v>
       </c>
       <c r="B77" t="n">
-        <v>188.1297854095839</v>
+        <v>184.5680989064521</v>
       </c>
       <c r="C77" t="n">
-        <v>190.9232365533545</v>
+        <v>187.6708389078061</v>
       </c>
       <c r="D77" t="n">
-        <v>186.1244680675316</v>
+        <v>182.9718281779948</v>
       </c>
       <c r="E77" t="n">
-        <v>188.6685180664062</v>
+        <v>185.3762054443359</v>
       </c>
       <c r="F77" t="n">
-        <v>153543200</v>
+        <v>160128900</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46030</v>
+        <v>46036</v>
       </c>
       <c r="B78" t="n">
-        <v>188.6685072554968</v>
+        <v>183.889716612774</v>
       </c>
       <c r="C78" t="n">
-        <v>189.1074824738404</v>
+        <v>184.029389177148</v>
       </c>
       <c r="D78" t="n">
-        <v>183.2811201033086</v>
+        <v>180.3779297072971</v>
       </c>
       <c r="E78" t="n">
-        <v>184.6080017089844</v>
+        <v>182.7124633789062</v>
       </c>
       <c r="F78" t="n">
-        <v>172457000</v>
+        <v>159586100</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46031</v>
+        <v>46037</v>
       </c>
       <c r="B79" t="n">
-        <v>184.6479238968445</v>
+        <v>186.0646079796491</v>
       </c>
       <c r="C79" t="n">
-        <v>185.9049768874807</v>
+        <v>189.2571344016907</v>
       </c>
       <c r="D79" t="n">
-        <v>183.2412119543349</v>
+        <v>185.895006678512</v>
       </c>
       <c r="E79" t="n">
-        <v>184.4284362792969</v>
+        <v>186.6133270263672</v>
       </c>
       <c r="F79" t="n">
-        <v>131327500</v>
+        <v>206188600</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46034</v>
+        <v>46038</v>
       </c>
       <c r="B80" t="n">
-        <v>182.7922691735387</v>
+        <v>188.6385950815971</v>
       </c>
       <c r="C80" t="n">
-        <v>186.6831584288149</v>
+        <v>189.9954207742267</v>
       </c>
       <c r="D80" t="n">
-        <v>182.5927391235801</v>
+        <v>185.6455985734289</v>
       </c>
       <c r="E80" t="n">
-        <v>184.5082550048828</v>
+        <v>185.7952423095703</v>
       </c>
       <c r="F80" t="n">
-        <v>137968500</v>
+        <v>187967200</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46035</v>
+        <v>46042</v>
       </c>
       <c r="B81" t="n">
-        <v>184.5681140987238</v>
+        <v>181.4753578011745</v>
       </c>
       <c r="C81" t="n">
-        <v>187.6708543554723</v>
+        <v>181.9542482267672</v>
       </c>
       <c r="D81" t="n">
-        <v>182.9718432388734</v>
+        <v>177.1953792817215</v>
       </c>
       <c r="E81" t="n">
-        <v>185.376220703125</v>
+        <v>177.6543121337891</v>
       </c>
       <c r="F81" t="n">
-        <v>160128900</v>
+        <v>223345300</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="B82" t="n">
-        <v>183.8897012556695</v>
+        <v>178.6319932794081</v>
       </c>
       <c r="C82" t="n">
-        <v>184.0293738083791</v>
+        <v>184.947217101084</v>
       </c>
       <c r="D82" t="n">
-        <v>180.3779146434709</v>
+        <v>177.9835016341843</v>
       </c>
       <c r="E82" t="n">
-        <v>182.7124481201172</v>
+        <v>182.8920288085938</v>
       </c>
       <c r="F82" t="n">
-        <v>159586100</v>
+        <v>200381000</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46037</v>
+        <v>46044</v>
       </c>
       <c r="B83" t="n">
-        <v>186.0646079796491</v>
+        <v>184.3186915464293</v>
       </c>
       <c r="C83" t="n">
-        <v>189.2571344016907</v>
+        <v>185.7353746560278</v>
       </c>
       <c r="D83" t="n">
-        <v>185.895006678512</v>
+        <v>183.5005985718231</v>
       </c>
       <c r="E83" t="n">
-        <v>186.6133270263672</v>
+        <v>184.4084777832031</v>
       </c>
       <c r="F83" t="n">
-        <v>206188600</v>
+        <v>139636600</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46038</v>
+        <v>46045</v>
       </c>
       <c r="B84" t="n">
-        <v>188.6385950815971</v>
+        <v>187.0622712594319</v>
       </c>
       <c r="C84" t="n">
-        <v>189.9954207742267</v>
+        <v>189.1573747868041</v>
       </c>
       <c r="D84" t="n">
-        <v>185.6455985734289</v>
+        <v>186.3838660627843</v>
       </c>
       <c r="E84" t="n">
-        <v>185.7952423095703</v>
+        <v>187.2318725585938</v>
       </c>
       <c r="F84" t="n">
-        <v>187967200</v>
+        <v>142748100</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46042</v>
+        <v>46048</v>
       </c>
       <c r="B85" t="n">
-        <v>181.4753266272146</v>
+        <v>186.7230748442759</v>
       </c>
       <c r="C85" t="n">
-        <v>181.9542169705431</v>
+        <v>188.6784906596197</v>
       </c>
       <c r="D85" t="n">
-        <v>177.1953488429791</v>
+        <v>185.555808059744</v>
       </c>
       <c r="E85" t="n">
-        <v>177.6542816162109</v>
+        <v>186.0346832275391</v>
       </c>
       <c r="F85" t="n">
-        <v>223345300</v>
+        <v>124799600</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46043</v>
+        <v>46049</v>
       </c>
       <c r="B86" t="n">
-        <v>178.6320081827799</v>
+        <v>186.8028844605491</v>
       </c>
       <c r="C86" t="n">
-        <v>184.9472325313386</v>
+        <v>189.5564356240106</v>
       </c>
       <c r="D86" t="n">
-        <v>177.9835164834521</v>
+        <v>185.2664711415707</v>
       </c>
       <c r="E86" t="n">
-        <v>182.8920440673828</v>
+        <v>188.0798950195312</v>
       </c>
       <c r="F86" t="n">
-        <v>200381000</v>
+        <v>143711600</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="B87" t="n">
-        <v>184.3186915464293</v>
+        <v>190.823459633995</v>
       </c>
       <c r="C87" t="n">
-        <v>185.7353746560278</v>
+        <v>191.9009400606663</v>
       </c>
       <c r="D87" t="n">
-        <v>183.5005985718231</v>
+        <v>189.3967902384632</v>
       </c>
       <c r="E87" t="n">
-        <v>184.4084777832031</v>
+        <v>191.0728759765625</v>
       </c>
       <c r="F87" t="n">
-        <v>139636600</v>
+        <v>148552700</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46045</v>
+        <v>46051</v>
       </c>
       <c r="B88" t="n">
-        <v>187.0622712594319</v>
+        <v>190.8933105997472</v>
       </c>
       <c r="C88" t="n">
-        <v>189.1573747868041</v>
+        <v>193.0283141326731</v>
       </c>
       <c r="D88" t="n">
-        <v>186.3838660627843</v>
+        <v>185.6256380470483</v>
       </c>
       <c r="E88" t="n">
-        <v>187.2318725585938</v>
+        <v>192.0605773925781</v>
       </c>
       <c r="F88" t="n">
-        <v>142748100</v>
+        <v>171764400</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46048</v>
+        <v>46052</v>
       </c>
       <c r="B89" t="n">
-        <v>186.7230595290241</v>
+        <v>190.7636224379378</v>
       </c>
       <c r="C89" t="n">
-        <v>188.6784751839824</v>
+        <v>194.0359639826301</v>
       </c>
       <c r="D89" t="n">
-        <v>185.5557928402329</v>
+        <v>189.0276790286862</v>
       </c>
       <c r="E89" t="n">
-        <v>186.03466796875</v>
+        <v>190.6838073730469</v>
       </c>
       <c r="F89" t="n">
-        <v>124799600</v>
+        <v>179489500</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46049</v>
+        <v>46055</v>
       </c>
       <c r="B90" t="n">
-        <v>186.8028844605491</v>
+        <v>186.7629659025267</v>
       </c>
       <c r="C90" t="n">
-        <v>189.5564356240106</v>
+        <v>189.8557348322644</v>
       </c>
       <c r="D90" t="n">
-        <v>185.2664711415707</v>
+        <v>184.4483900153819</v>
       </c>
       <c r="E90" t="n">
-        <v>188.0798950195312</v>
+        <v>185.1766815185547</v>
       </c>
       <c r="F90" t="n">
-        <v>143711600</v>
+        <v>165794100</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46050</v>
+        <v>46056</v>
       </c>
       <c r="B91" t="n">
-        <v>190.823459633995</v>
+        <v>185.8052108647954</v>
       </c>
       <c r="C91" t="n">
-        <v>191.9009400606663</v>
+        <v>185.8351396091497</v>
       </c>
       <c r="D91" t="n">
-        <v>189.3967902384632</v>
+        <v>175.8185703987175</v>
       </c>
       <c r="E91" t="n">
-        <v>191.0728759765625</v>
+        <v>179.9189758300781</v>
       </c>
       <c r="F91" t="n">
-        <v>148552700</v>
+        <v>204019600</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46051</v>
+        <v>46057</v>
       </c>
       <c r="B92" t="n">
-        <v>190.8933105997472</v>
+        <v>179.0410571553003</v>
       </c>
       <c r="C92" t="n">
-        <v>193.0283141326731</v>
+        <v>179.1607721437711</v>
       </c>
       <c r="D92" t="n">
-        <v>185.6256380470483</v>
+        <v>171.5086795929406</v>
       </c>
       <c r="E92" t="n">
-        <v>192.0605773925781</v>
+        <v>173.7833557128906</v>
       </c>
       <c r="F92" t="n">
-        <v>171764400</v>
+        <v>207014100</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46052</v>
+        <v>46058</v>
       </c>
       <c r="B93" t="n">
-        <v>190.7636224379378</v>
+        <v>174.5216119878791</v>
       </c>
       <c r="C93" t="n">
-        <v>194.0359639826301</v>
+        <v>176.4072143255947</v>
       </c>
       <c r="D93" t="n">
-        <v>189.0276790286862</v>
+        <v>170.6307227747363</v>
       </c>
       <c r="E93" t="n">
-        <v>190.6838073730469</v>
+        <v>171.4787445068359</v>
       </c>
       <c r="F93" t="n">
-        <v>179489500</v>
+        <v>206312900</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46055</v>
+        <v>46059</v>
       </c>
       <c r="B94" t="n">
-        <v>186.7629659025267</v>
+        <v>176.2775280578147</v>
       </c>
       <c r="C94" t="n">
-        <v>189.8557348322644</v>
+        <v>186.5634574188361</v>
       </c>
       <c r="D94" t="n">
-        <v>184.4483900153819</v>
+        <v>174.1924107166939</v>
       </c>
       <c r="E94" t="n">
-        <v>185.1766815185547</v>
+        <v>184.9771728515625</v>
       </c>
       <c r="F94" t="n">
-        <v>165794100</v>
+        <v>231346200</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46056</v>
+        <v>46062</v>
       </c>
       <c r="B95" t="n">
-        <v>185.8052108647954</v>
+        <v>183.8298238555102</v>
       </c>
       <c r="C95" t="n">
-        <v>185.8351396091497</v>
+        <v>193.2078878887748</v>
       </c>
       <c r="D95" t="n">
-        <v>175.8185703987175</v>
+        <v>183.5205500126207</v>
       </c>
       <c r="E95" t="n">
-        <v>179.9189758300781</v>
+        <v>189.5963287353516</v>
       </c>
       <c r="F95" t="n">
-        <v>204019600</v>
+        <v>196387400</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46057</v>
+        <v>46063</v>
       </c>
       <c r="B96" t="n">
-        <v>179.0410571553003</v>
+        <v>190.9332352083219</v>
       </c>
       <c r="C96" t="n">
-        <v>179.1607721437711</v>
+        <v>192.0306581643501</v>
       </c>
       <c r="D96" t="n">
-        <v>171.5086795929406</v>
+        <v>187.6808358171596</v>
       </c>
       <c r="E96" t="n">
-        <v>173.7833557128906</v>
+        <v>188.099853515625</v>
       </c>
       <c r="F96" t="n">
-        <v>207014100</v>
+        <v>136764800</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46058</v>
+        <v>46064</v>
       </c>
       <c r="B97" t="n">
-        <v>174.5216119878791</v>
+        <v>192.0007142509167</v>
       </c>
       <c r="C97" t="n">
-        <v>176.4072143255947</v>
+        <v>192.8088208357837</v>
       </c>
       <c r="D97" t="n">
-        <v>170.6307227747363</v>
+        <v>188.329312674443</v>
       </c>
       <c r="E97" t="n">
-        <v>171.4787445068359</v>
+        <v>189.6063232421875</v>
       </c>
       <c r="F97" t="n">
-        <v>206312900</v>
+        <v>144192700</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46059</v>
+        <v>46065</v>
       </c>
       <c r="B98" t="n">
-        <v>176.2775135166603</v>
+        <v>192.5793648877844</v>
       </c>
       <c r="C98" t="n">
-        <v>186.5634420291942</v>
+        <v>193.1580126884611</v>
       </c>
       <c r="D98" t="n">
-        <v>174.1923963475411</v>
+        <v>186.0745817463215</v>
       </c>
       <c r="E98" t="n">
-        <v>184.9771575927734</v>
+        <v>186.5035858154297</v>
       </c>
       <c r="F98" t="n">
-        <v>231346200</v>
+        <v>189932500</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46062</v>
+        <v>46066</v>
       </c>
       <c r="B99" t="n">
-        <v>183.8298386502086</v>
+        <v>187.042320465516</v>
       </c>
       <c r="C99" t="n">
-        <v>193.2079034382237</v>
+        <v>187.0622780376601</v>
       </c>
       <c r="D99" t="n">
-        <v>183.5205647824287</v>
+        <v>181.1660713803529</v>
       </c>
       <c r="E99" t="n">
-        <v>189.5963439941406</v>
+        <v>182.3832244873047</v>
       </c>
       <c r="F99" t="n">
-        <v>196387400</v>
+        <v>161888000</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46063</v>
+        <v>46070</v>
       </c>
       <c r="B100" t="n">
-        <v>190.933219719687</v>
+        <v>181.3256935584433</v>
       </c>
       <c r="C100" t="n">
-        <v>192.0306425866914</v>
+        <v>186.7130808403767</v>
       </c>
       <c r="D100" t="n">
-        <v>187.6808205923615</v>
+        <v>178.7616860728079</v>
       </c>
       <c r="E100" t="n">
-        <v>188.0998382568359</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="F100" t="n">
-        <v>136764800</v>
+        <v>162276900</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46064</v>
+        <v>46071</v>
       </c>
       <c r="B101" t="n">
-        <v>192.0007297023972</v>
+        <v>188.3093443160685</v>
       </c>
       <c r="C101" t="n">
-        <v>192.8088363522974</v>
+        <v>189.9255573932224</v>
       </c>
       <c r="D101" t="n">
-        <v>188.3293278304631</v>
+        <v>186.3239846890322</v>
       </c>
       <c r="E101" t="n">
-        <v>189.6063385009766</v>
+        <v>187.5411376953125</v>
       </c>
       <c r="F101" t="n">
-        <v>144192700</v>
+        <v>164749100</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46065</v>
+        <v>46072</v>
       </c>
       <c r="B102" t="n">
-        <v>192.5793806436633</v>
+        <v>186.62329889396</v>
       </c>
       <c r="C102" t="n">
-        <v>193.158028491682</v>
+        <v>187.9900957055448</v>
       </c>
       <c r="D102" t="n">
-        <v>186.0745969700116</v>
+        <v>185.2265733363672</v>
       </c>
       <c r="E102" t="n">
-        <v>186.5036010742188</v>
+        <v>187.4613342285156</v>
       </c>
       <c r="F102" t="n">
-        <v>189932500</v>
+        <v>126554500</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46066</v>
+        <v>46073</v>
       </c>
       <c r="B103" t="n">
-        <v>187.0423048169314</v>
+        <v>186.1344488846578</v>
       </c>
       <c r="C103" t="n">
-        <v>187.0622623874058</v>
+        <v>189.8856654675195</v>
       </c>
       <c r="D103" t="n">
-        <v>181.1660562233949</v>
+        <v>185.5059147845697</v>
       </c>
       <c r="E103" t="n">
-        <v>182.3832092285156</v>
+        <v>189.3768615722656</v>
       </c>
       <c r="F103" t="n">
-        <v>161888000</v>
+        <v>178422300</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="B104" t="n">
-        <v>181.3257085516038</v>
+        <v>190.9531547742145</v>
       </c>
       <c r="C104" t="n">
-        <v>186.7130962790006</v>
+        <v>193.4972046328596</v>
       </c>
       <c r="D104" t="n">
-        <v>178.7617008539599</v>
+        <v>189.1374116308485</v>
       </c>
       <c r="E104" t="n">
-        <v>184.5381927490234</v>
+        <v>191.1028137207031</v>
       </c>
       <c r="F104" t="n">
-        <v>162276900</v>
+        <v>171584800</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46071</v>
+        <v>46077</v>
       </c>
       <c r="B105" t="n">
-        <v>188.3093443160685</v>
+        <v>191.0429698590405</v>
       </c>
       <c r="C105" t="n">
-        <v>189.9255573932224</v>
+        <v>193.3176459547985</v>
       </c>
       <c r="D105" t="n">
-        <v>186.3239846890322</v>
+        <v>186.9625064417709</v>
       </c>
       <c r="E105" t="n">
-        <v>187.5411376953125</v>
+        <v>192.3997955322266</v>
       </c>
       <c r="F105" t="n">
-        <v>164749100</v>
+        <v>175123600</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46072</v>
+        <v>46078</v>
       </c>
       <c r="B106" t="n">
-        <v>186.6232837033845</v>
+        <v>193.9960453222018</v>
       </c>
       <c r="C106" t="n">
-        <v>187.9900804037161</v>
+        <v>197.1686293956491</v>
       </c>
       <c r="D106" t="n">
-        <v>185.226558259481</v>
+        <v>193.3375824661624</v>
       </c>
       <c r="E106" t="n">
-        <v>187.4613189697266</v>
+        <v>195.1034545898438</v>
       </c>
       <c r="F106" t="n">
-        <v>126554500</v>
+        <v>250637100</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46073</v>
+        <v>46079</v>
       </c>
       <c r="B107" t="n">
-        <v>186.1344488846578</v>
+        <v>193.8164813019665</v>
       </c>
       <c r="C107" t="n">
-        <v>189.8856654675195</v>
+        <v>193.8364236513225</v>
       </c>
       <c r="D107" t="n">
-        <v>185.5059147845697</v>
+        <v>183.8897126034445</v>
       </c>
       <c r="E107" t="n">
-        <v>189.3768615722656</v>
+        <v>184.4583740234375</v>
       </c>
       <c r="F107" t="n">
-        <v>178422300</v>
+        <v>360807900</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46076</v>
+        <v>46080</v>
       </c>
       <c r="B108" t="n">
-        <v>190.9531547742145</v>
+        <v>180.8268714126474</v>
       </c>
       <c r="C108" t="n">
-        <v>193.4972046328596</v>
+        <v>182.1637395256691</v>
       </c>
       <c r="D108" t="n">
-        <v>189.1374116308485</v>
+        <v>175.9682453114839</v>
       </c>
       <c r="E108" t="n">
-        <v>191.1028137207031</v>
+        <v>176.7763519287109</v>
       </c>
       <c r="F108" t="n">
-        <v>171584800</v>
+        <v>311636500</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46077</v>
+        <v>46083</v>
       </c>
       <c r="B109" t="n">
-        <v>191.0429698590405</v>
+        <v>174.6014235260267</v>
       </c>
       <c r="C109" t="n">
-        <v>193.3176459547985</v>
+        <v>183.0317086895539</v>
       </c>
       <c r="D109" t="n">
-        <v>186.9625064417709</v>
+        <v>174.2322921838959</v>
       </c>
       <c r="E109" t="n">
-        <v>192.3997955322266</v>
+        <v>182.0539855957031</v>
       </c>
       <c r="F109" t="n">
-        <v>175123600</v>
+        <v>209095300</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46078</v>
+        <v>46084</v>
       </c>
       <c r="B110" t="n">
-        <v>193.9960453222018</v>
+        <v>178.0733135069376</v>
       </c>
       <c r="C110" t="n">
-        <v>197.1686293956491</v>
+        <v>180.4776756968921</v>
       </c>
       <c r="D110" t="n">
-        <v>193.3375824661624</v>
+        <v>176.5069714269912</v>
       </c>
       <c r="E110" t="n">
-        <v>195.1034545898438</v>
+        <v>179.6296691894531</v>
       </c>
       <c r="F110" t="n">
-        <v>250637100</v>
+        <v>178099400</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46079</v>
+        <v>46085</v>
       </c>
       <c r="B111" t="n">
-        <v>193.8164813019665</v>
+        <v>180.0187499528396</v>
       </c>
       <c r="C111" t="n">
-        <v>193.8364236513225</v>
+        <v>184.2687991412151</v>
       </c>
       <c r="D111" t="n">
-        <v>183.8897126034445</v>
+        <v>179.6396322236537</v>
       </c>
       <c r="E111" t="n">
-        <v>184.4583740234375</v>
+        <v>182.6126708984375</v>
       </c>
       <c r="F111" t="n">
-        <v>360807900</v>
+        <v>177731200</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46080</v>
+        <v>46086</v>
       </c>
       <c r="B112" t="n">
-        <v>180.82685580423</v>
+        <v>180.7470399397241</v>
       </c>
       <c r="C112" t="n">
-        <v>182.1637238018573</v>
+        <v>183.6302923567135</v>
       </c>
       <c r="D112" t="n">
-        <v>175.9682301224481</v>
+        <v>177.4647274492447</v>
       </c>
       <c r="E112" t="n">
-        <v>176.7763366699219</v>
+        <v>182.9119720458984</v>
       </c>
       <c r="F112" t="n">
-        <v>311636500</v>
+        <v>198779700</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46083</v>
+        <v>46087</v>
       </c>
       <c r="B113" t="n">
-        <v>174.6014088918714</v>
+        <v>179.4201653790109</v>
       </c>
       <c r="C113" t="n">
-        <v>183.0316933488174</v>
+        <v>182.3333469017365</v>
       </c>
       <c r="D113" t="n">
-        <v>174.2322775806792</v>
+        <v>176.4072264371208</v>
       </c>
       <c r="E113" t="n">
-        <v>182.0539703369141</v>
+        <v>177.4048919677734</v>
       </c>
       <c r="F113" t="n">
-        <v>209095300</v>
+        <v>189021900</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46084</v>
+        <v>46090</v>
       </c>
       <c r="B114" t="n">
-        <v>178.0733135069376</v>
+        <v>176.4171820751478</v>
       </c>
       <c r="C114" t="n">
-        <v>180.4776756968921</v>
+        <v>182.4829897940845</v>
       </c>
       <c r="D114" t="n">
-        <v>176.5069714269912</v>
+        <v>175.1501427003192</v>
       </c>
       <c r="E114" t="n">
-        <v>179.6296691894531</v>
+        <v>182.2235870361328</v>
       </c>
       <c r="F114" t="n">
-        <v>178099400</v>
+        <v>177213600</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46085</v>
+        <v>46091</v>
       </c>
       <c r="B115" t="n">
-        <v>180.0187649948852</v>
+        <v>181.9741609804723</v>
       </c>
       <c r="C115" t="n">
-        <v>184.2688145383873</v>
+        <v>186.0047376795775</v>
       </c>
       <c r="D115" t="n">
-        <v>179.6396472340209</v>
+        <v>181.5850720874406</v>
       </c>
       <c r="E115" t="n">
-        <v>182.6126861572266</v>
+        <v>184.3386383056641</v>
       </c>
       <c r="F115" t="n">
-        <v>177731200</v>
+        <v>179118500</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,25 +3433,25 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="B116" t="n">
-        <v>180.7470399397241</v>
+        <v>185.4860219488843</v>
       </c>
       <c r="C116" t="n">
-        <v>183.6302923567135</v>
+        <v>187.1921136401388</v>
       </c>
       <c r="D116" t="n">
-        <v>177.4647274492447</v>
+        <v>184.0293448898806</v>
       </c>
       <c r="E116" t="n">
-        <v>182.9119720458984</v>
+        <v>185.6057434082031</v>
       </c>
       <c r="F116" t="n">
-        <v>198779700</v>
+        <v>145280400</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46087</v>
+        <v>46093</v>
       </c>
       <c r="B117" t="n">
-        <v>179.420149946886</v>
+        <v>183.6302794851663</v>
       </c>
       <c r="C117" t="n">
-        <v>182.3333312190456</v>
+        <v>184.5182492431283</v>
       </c>
       <c r="D117" t="n">
-        <v>176.407211264142</v>
+        <v>181.3355215595592</v>
       </c>
       <c r="E117" t="n">
-        <v>177.4048767089844</v>
+        <v>182.7223510742188</v>
       </c>
       <c r="F117" t="n">
-        <v>189021900</v>
+        <v>155762700</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="B118" t="n">
-        <v>176.4171820751478</v>
+        <v>184.4982761588831</v>
       </c>
       <c r="C118" t="n">
-        <v>182.4829897940845</v>
+        <v>185.6656060713691</v>
       </c>
       <c r="D118" t="n">
-        <v>175.1501427003192</v>
+        <v>179.5296376335348</v>
       </c>
       <c r="E118" t="n">
-        <v>182.2235870361328</v>
+        <v>179.8389282226562</v>
       </c>
       <c r="F118" t="n">
-        <v>177213600</v>
+        <v>160988400</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46091</v>
+        <v>46097</v>
       </c>
       <c r="B119" t="n">
-        <v>181.9741760435397</v>
+        <v>182.5527399223597</v>
       </c>
       <c r="C119" t="n">
-        <v>186.0047530762794</v>
+        <v>188.4492658789173</v>
       </c>
       <c r="D119" t="n">
-        <v>181.5850871183009</v>
+        <v>180.9962999229416</v>
       </c>
       <c r="E119" t="n">
-        <v>184.3386535644531</v>
+        <v>182.8021697998047</v>
       </c>
       <c r="F119" t="n">
-        <v>179118500</v>
+        <v>217307400</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,25 +3537,25 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46092</v>
+        <v>46098</v>
       </c>
       <c r="B120" t="n">
-        <v>185.4860219488843</v>
+        <v>184.6379576703901</v>
       </c>
       <c r="C120" t="n">
-        <v>187.1921136401388</v>
+        <v>184.9771786272242</v>
       </c>
       <c r="D120" t="n">
-        <v>184.0293448898806</v>
+        <v>181.2656610816535</v>
       </c>
       <c r="E120" t="n">
-        <v>185.6057434082031</v>
+        <v>181.5150909423828</v>
       </c>
       <c r="F120" t="n">
-        <v>145280400</v>
+        <v>182497800</v>
       </c>
       <c r="G120" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46093</v>
+        <v>46099</v>
       </c>
       <c r="B121" t="n">
-        <v>183.6302641505579</v>
+        <v>182.0638447517288</v>
       </c>
       <c r="C121" t="n">
-        <v>184.5182338343672</v>
+        <v>182.9618014097589</v>
       </c>
       <c r="D121" t="n">
-        <v>181.3355064165816</v>
+        <v>179.9187539793071</v>
       </c>
       <c r="E121" t="n">
-        <v>182.7223358154297</v>
+        <v>179.9885864257812</v>
       </c>
       <c r="F121" t="n">
-        <v>155762700</v>
+        <v>156683100</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46094</v>
+        <v>46100</v>
       </c>
       <c r="B122" t="n">
-        <v>184.4982918130038</v>
+        <v>177.6040375011918</v>
       </c>
       <c r="C122" t="n">
-        <v>185.6656218245341</v>
+        <v>179.569546076418</v>
       </c>
       <c r="D122" t="n">
-        <v>179.5296528660815</v>
+        <v>175.3890990582871</v>
       </c>
       <c r="E122" t="n">
-        <v>179.8389434814453</v>
+        <v>178.1527862548828</v>
       </c>
       <c r="F122" t="n">
-        <v>160988400</v>
+        <v>170968500</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46097</v>
+        <v>46101</v>
       </c>
       <c r="B123" t="n">
-        <v>182.5527246843909</v>
+        <v>177.5940529420793</v>
       </c>
       <c r="C123" t="n">
-        <v>188.4492501487561</v>
+        <v>177.8534545050662</v>
       </c>
       <c r="D123" t="n">
-        <v>180.9962848148914</v>
+        <v>171.3283763370981</v>
       </c>
       <c r="E123" t="n">
-        <v>182.8021545410156</v>
+        <v>172.3061370849609</v>
       </c>
       <c r="F123" t="n">
-        <v>217307400</v>
+        <v>241323500</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46098</v>
+        <v>46104</v>
       </c>
       <c r="B124" t="n">
-        <v>184.6379731916982</v>
+        <v>176.8557415306554</v>
       </c>
       <c r="C124" t="n">
-        <v>184.9771941770484</v>
+        <v>177.9632107122345</v>
       </c>
       <c r="D124" t="n">
-        <v>181.2656763194747</v>
+        <v>174.3614429436745</v>
       </c>
       <c r="E124" t="n">
-        <v>181.5151062011719</v>
+        <v>175.2394409179688</v>
       </c>
       <c r="F124" t="n">
-        <v>182497800</v>
+        <v>182836300</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46099</v>
+        <v>46105</v>
       </c>
       <c r="B125" t="n">
-        <v>182.0638447517288</v>
+        <v>174.4312942297872</v>
       </c>
       <c r="C125" t="n">
-        <v>182.9618014097589</v>
+        <v>175.8181236639554</v>
       </c>
       <c r="D125" t="n">
-        <v>179.9187539793071</v>
+        <v>173.5832266030264</v>
       </c>
       <c r="E125" t="n">
-        <v>179.9885864257812</v>
+        <v>174.8004455566406</v>
       </c>
       <c r="F125" t="n">
-        <v>156683100</v>
+        <v>147667800</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46100</v>
+        <v>46106</v>
       </c>
       <c r="B126" t="n">
-        <v>177.6040222894031</v>
+        <v>176.6961233561449</v>
       </c>
       <c r="C126" t="n">
-        <v>179.5695306962835</v>
+        <v>180.8067226806179</v>
       </c>
       <c r="D126" t="n">
-        <v>175.3890840362079</v>
+        <v>176.4466934898736</v>
       </c>
       <c r="E126" t="n">
-        <v>178.1527709960938</v>
+        <v>178.2725067138672</v>
       </c>
       <c r="F126" t="n">
-        <v>170968500</v>
+        <v>162602100</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46101</v>
+        <v>46107</v>
       </c>
       <c r="B127" t="n">
-        <v>177.5940686691464</v>
+        <v>175.6684741654964</v>
       </c>
       <c r="C127" t="n">
-        <v>177.853470255105</v>
+        <v>176.1074579435819</v>
       </c>
       <c r="D127" t="n">
-        <v>171.3283915093003</v>
+        <v>170.7497092682189</v>
       </c>
       <c r="E127" t="n">
-        <v>172.30615234375</v>
+        <v>170.8494873046875</v>
       </c>
       <c r="F127" t="n">
-        <v>241323500</v>
+        <v>186152200</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46104</v>
+        <v>46108</v>
       </c>
       <c r="B128" t="n">
-        <v>176.8557415306554</v>
+        <v>169.6122945102883</v>
       </c>
       <c r="C128" t="n">
-        <v>177.9632107122345</v>
+        <v>170.5800835262955</v>
       </c>
       <c r="D128" t="n">
-        <v>174.3614429436745</v>
+        <v>166.6291080850299</v>
       </c>
       <c r="E128" t="n">
-        <v>175.2394409179688</v>
+        <v>167.1379547119141</v>
       </c>
       <c r="F128" t="n">
-        <v>182836300</v>
+        <v>196212700</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46105</v>
+        <v>46111</v>
       </c>
       <c r="B129" t="n">
-        <v>174.4312942297872</v>
+        <v>168.3950875250076</v>
       </c>
       <c r="C129" t="n">
-        <v>175.8181236639554</v>
+        <v>169.0635577295173</v>
       </c>
       <c r="D129" t="n">
-        <v>173.5832266030264</v>
+        <v>163.8953782868944</v>
       </c>
       <c r="E129" t="n">
-        <v>174.8004455566406</v>
+        <v>164.7933197021484</v>
       </c>
       <c r="F129" t="n">
-        <v>147667800</v>
+        <v>185627000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46106</v>
+        <v>46112</v>
       </c>
       <c r="B130" t="n">
-        <v>176.6961233561449</v>
+        <v>166.5892250311153</v>
       </c>
       <c r="C130" t="n">
-        <v>180.8067226806179</v>
+        <v>174.2217730660379</v>
       </c>
       <c r="D130" t="n">
-        <v>176.4466934898736</v>
+        <v>166.5792533168182</v>
       </c>
       <c r="E130" t="n">
-        <v>178.2725067138672</v>
+        <v>174.0022735595703</v>
       </c>
       <c r="F130" t="n">
-        <v>162602100</v>
+        <v>226181300</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="B131" t="n">
-        <v>175.6684741654964</v>
+        <v>175.5986272559566</v>
       </c>
       <c r="C131" t="n">
-        <v>176.1074579435819</v>
+        <v>176.9654980623514</v>
       </c>
       <c r="D131" t="n">
-        <v>170.7497092682189</v>
+        <v>174.3514779146501</v>
       </c>
       <c r="E131" t="n">
-        <v>170.8494873046875</v>
+        <v>175.3491973876953</v>
       </c>
       <c r="F131" t="n">
-        <v>186152200</v>
+        <v>168132000</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46108</v>
+        <v>46114</v>
       </c>
       <c r="B132" t="n">
-        <v>169.6123099949711</v>
+        <v>171.7873183615289</v>
       </c>
       <c r="C132" t="n">
-        <v>170.5800990993323</v>
+        <v>177.0852211444685</v>
       </c>
       <c r="D132" t="n">
-        <v>166.629123297364</v>
+        <v>170.9791680862979</v>
       </c>
       <c r="E132" t="n">
-        <v>167.1379699707031</v>
+        <v>176.9854431152344</v>
       </c>
       <c r="F132" t="n">
-        <v>196212700</v>
+        <v>143143200</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46111</v>
+        <v>46118</v>
       </c>
       <c r="B133" t="n">
-        <v>168.3950875250076</v>
+        <v>176.7559774774269</v>
       </c>
       <c r="C133" t="n">
-        <v>169.0635577295173</v>
+        <v>177.3845303646084</v>
       </c>
       <c r="D133" t="n">
-        <v>163.8953782868944</v>
+        <v>175.3591611441553</v>
       </c>
       <c r="E133" t="n">
-        <v>164.7933197021484</v>
+        <v>177.2348785400391</v>
       </c>
       <c r="F133" t="n">
-        <v>185627000</v>
+        <v>107564300</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="B134" t="n">
-        <v>166.589210422399</v>
+        <v>175.3292270516068</v>
       </c>
       <c r="C134" t="n">
-        <v>174.2217577880002</v>
+        <v>177.8235255680002</v>
       </c>
       <c r="D134" t="n">
-        <v>166.5792387089764</v>
+        <v>173.2639557965079</v>
       </c>
       <c r="E134" t="n">
-        <v>174.0022583007812</v>
+        <v>177.6938323974609</v>
       </c>
       <c r="F134" t="n">
-        <v>226181300</v>
+        <v>132534900</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46113</v>
+        <v>46120</v>
       </c>
       <c r="B135" t="n">
-        <v>175.5986119754623</v>
+        <v>184.079243714486</v>
       </c>
       <c r="C135" t="n">
-        <v>176.9654826629128</v>
+        <v>184.837505037226</v>
       </c>
       <c r="D135" t="n">
-        <v>174.351462742682</v>
+        <v>179.8888249511496</v>
       </c>
       <c r="E135" t="n">
-        <v>175.3491821289062</v>
+        <v>181.6647644042969</v>
       </c>
       <c r="F135" t="n">
-        <v>168132000</v>
+        <v>147732700</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46114</v>
+        <v>46121</v>
       </c>
       <c r="B136" t="n">
-        <v>171.787333172162</v>
+        <v>181.4252987848774</v>
       </c>
       <c r="C136" t="n">
-        <v>177.0852364118599</v>
+        <v>183.6601958045732</v>
       </c>
       <c r="D136" t="n">
-        <v>170.9791828272563</v>
+        <v>180.2080798537204</v>
       </c>
       <c r="E136" t="n">
-        <v>176.9854583740234</v>
+        <v>183.4905853271484</v>
       </c>
       <c r="F136" t="n">
-        <v>143143200</v>
+        <v>116428500</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46118</v>
+        <v>46122</v>
       </c>
       <c r="B137" t="n">
-        <v>176.7559774774269</v>
+        <v>183.8896736698189</v>
       </c>
       <c r="C137" t="n">
-        <v>177.3845303646084</v>
+        <v>189.5666999081706</v>
       </c>
       <c r="D137" t="n">
-        <v>175.3591611441553</v>
+        <v>183.8797019557237</v>
       </c>
       <c r="E137" t="n">
-        <v>177.2348785400391</v>
+        <v>188.1998291015625</v>
       </c>
       <c r="F137" t="n">
-        <v>107564300</v>
+        <v>160459500</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46119</v>
+        <v>46125</v>
       </c>
       <c r="B138" t="n">
-        <v>175.3292270516068</v>
+        <v>185.605746824658</v>
       </c>
       <c r="C138" t="n">
-        <v>177.8235255680002</v>
+        <v>189.2274732756209</v>
       </c>
       <c r="D138" t="n">
-        <v>173.2639557965079</v>
+        <v>185.3164148846483</v>
       </c>
       <c r="E138" t="n">
-        <v>177.6938323974609</v>
+        <v>188.8782653808594</v>
       </c>
       <c r="F138" t="n">
-        <v>132534900</v>
+        <v>133648200</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46120</v>
+        <v>46126</v>
       </c>
       <c r="B139" t="n">
-        <v>184.079243714486</v>
+        <v>190.4047764107204</v>
       </c>
       <c r="C139" t="n">
-        <v>184.837505037226</v>
+        <v>196.0618438720703</v>
       </c>
       <c r="D139" t="n">
-        <v>179.8888249511496</v>
+        <v>190.3349439656124</v>
       </c>
       <c r="E139" t="n">
-        <v>181.6647644042969</v>
+        <v>196.0618438720703</v>
       </c>
       <c r="F139" t="n">
-        <v>147732700</v>
+        <v>161307000</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46121</v>
+        <v>46127</v>
       </c>
       <c r="B140" t="n">
-        <v>181.4253138719204</v>
+        <v>196.0917851116163</v>
       </c>
       <c r="C140" t="n">
-        <v>183.6602110774668</v>
+        <v>199.9429830157183</v>
       </c>
       <c r="D140" t="n">
-        <v>180.2080948395415</v>
+        <v>195.2936216855987</v>
       </c>
       <c r="E140" t="n">
-        <v>183.4906005859375</v>
+        <v>198.4164733886719</v>
       </c>
       <c r="F140" t="n">
-        <v>116428500</v>
+        <v>185338400</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46122</v>
+        <v>46128</v>
       </c>
       <c r="B141" t="n">
-        <v>183.8896736698189</v>
+        <v>196.9797440092329</v>
       </c>
       <c r="C141" t="n">
-        <v>189.5666999081706</v>
+        <v>199.3942384790618</v>
       </c>
       <c r="D141" t="n">
-        <v>183.8797019557237</v>
+        <v>195.3634433694217</v>
       </c>
       <c r="E141" t="n">
-        <v>188.1998291015625</v>
+        <v>197.8976593017578</v>
       </c>
       <c r="F141" t="n">
-        <v>160459500</v>
+        <v>134012900</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="B142" t="n">
-        <v>185.605746824658</v>
+        <v>199.444107632571</v>
       </c>
       <c r="C142" t="n">
-        <v>189.2274732756209</v>
+        <v>201.2400056483541</v>
       </c>
       <c r="D142" t="n">
-        <v>185.3164148846483</v>
+        <v>198.8155547450397</v>
       </c>
       <c r="E142" t="n">
-        <v>188.8782653808594</v>
+        <v>201.2200469970703</v>
       </c>
       <c r="F142" t="n">
-        <v>133648200</v>
+        <v>160324400</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="B143" t="n">
-        <v>190.4047764107204</v>
+        <v>199.5239239232554</v>
       </c>
       <c r="C143" t="n">
-        <v>196.0618438720703</v>
+        <v>201.7089318732817</v>
       </c>
       <c r="D143" t="n">
-        <v>190.3349439656124</v>
+        <v>197.3888049886708</v>
       </c>
       <c r="E143" t="n">
-        <v>196.0618438720703</v>
+        <v>201.5991821289062</v>
       </c>
       <c r="F143" t="n">
-        <v>161307000</v>
+        <v>119381400</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46127</v>
+        <v>46133</v>
       </c>
       <c r="B144" t="n">
-        <v>196.0917851116163</v>
+        <v>201.6690479582887</v>
       </c>
       <c r="C144" t="n">
-        <v>199.9429830157183</v>
+        <v>202.2876291783034</v>
       </c>
       <c r="D144" t="n">
-        <v>195.2936216855987</v>
+        <v>198.5461810430697</v>
       </c>
       <c r="E144" t="n">
-        <v>198.4164733886719</v>
+        <v>199.4241790771484</v>
       </c>
       <c r="F144" t="n">
-        <v>185338400</v>
+        <v>107945300</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46128</v>
+        <v>46134</v>
       </c>
       <c r="B145" t="n">
-        <v>196.9797440092329</v>
+        <v>200.5316418294082</v>
       </c>
       <c r="C145" t="n">
-        <v>199.3942384790618</v>
+        <v>202.0381927490234</v>
       </c>
       <c r="D145" t="n">
-        <v>195.3634433694217</v>
+        <v>198.546174602744</v>
       </c>
       <c r="E145" t="n">
-        <v>197.8976593017578</v>
+        <v>202.0381927490234</v>
       </c>
       <c r="F145" t="n">
-        <v>134012900</v>
+        <v>107501000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46129</v>
+        <v>46135</v>
       </c>
       <c r="B146" t="n">
-        <v>199.444107632571</v>
+        <v>201.9982837593082</v>
       </c>
       <c r="C146" t="n">
-        <v>201.2400056483541</v>
+        <v>203.3651545152774</v>
       </c>
       <c r="D146" t="n">
-        <v>198.8155547450397</v>
+        <v>196.7702284327844</v>
       </c>
       <c r="E146" t="n">
-        <v>201.2200469970703</v>
+        <v>199.1847076416016</v>
       </c>
       <c r="F146" t="n">
-        <v>160324400</v>
+        <v>113561800</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46132</v>
+        <v>46136</v>
       </c>
       <c r="B147" t="n">
-        <v>199.5239239232554</v>
+        <v>199.5039827094276</v>
       </c>
       <c r="C147" t="n">
-        <v>201.7089318732817</v>
+        <v>210.468909435165</v>
       </c>
       <c r="D147" t="n">
-        <v>197.3888049886708</v>
+        <v>199.3543156614425</v>
       </c>
       <c r="E147" t="n">
-        <v>201.5991821289062</v>
+        <v>207.7950286865234</v>
       </c>
       <c r="F147" t="n">
-        <v>119381400</v>
+        <v>214134400</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="B148" t="n">
-        <v>201.6690479582887</v>
+        <v>209.1718784416434</v>
       </c>
       <c r="C148" t="n">
-        <v>202.2876291783034</v>
+        <v>216.335512072091</v>
       </c>
       <c r="D148" t="n">
-        <v>198.5461810430697</v>
+        <v>206.9070662315077</v>
       </c>
       <c r="E148" t="n">
-        <v>199.4241790771484</v>
+        <v>216.1160125732422</v>
       </c>
       <c r="F148" t="n">
-        <v>107945300</v>
+        <v>187172400</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="B149" t="n">
-        <v>200.5316418294082</v>
+        <v>209.0122528840405</v>
       </c>
       <c r="C149" t="n">
-        <v>202.0381927490234</v>
+        <v>214.2402930542568</v>
       </c>
       <c r="D149" t="n">
-        <v>198.546174602744</v>
+        <v>207.7251862691963</v>
       </c>
       <c r="E149" t="n">
-        <v>202.0381927490234</v>
+        <v>212.6838531494141</v>
       </c>
       <c r="F149" t="n">
-        <v>107501000</v>
+        <v>180275400</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46135</v>
+        <v>46141</v>
       </c>
       <c r="B150" t="n">
-        <v>201.9982837593082</v>
+        <v>212.2149257168926</v>
       </c>
       <c r="C150" t="n">
-        <v>203.3651545152774</v>
+        <v>212.2348843687743</v>
       </c>
       <c r="D150" t="n">
-        <v>196.7702284327844</v>
+        <v>207.1066069625242</v>
       </c>
       <c r="E150" t="n">
-        <v>199.1847076416016</v>
+        <v>208.7727966308594</v>
       </c>
       <c r="F150" t="n">
-        <v>113561800</v>
+        <v>123711800</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46136</v>
+        <v>46142</v>
       </c>
       <c r="B151" t="n">
-        <v>199.5039827094276</v>
+        <v>209.4512425942353</v>
       </c>
       <c r="C151" t="n">
-        <v>210.468909435165</v>
+        <v>209.820409153207</v>
       </c>
       <c r="D151" t="n">
-        <v>199.3543156614425</v>
+        <v>198.2468571251534</v>
       </c>
       <c r="E151" t="n">
-        <v>207.7950286865234</v>
+        <v>199.1148834228516</v>
       </c>
       <c r="F151" t="n">
-        <v>214134400</v>
+        <v>225239200</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46139</v>
+        <v>46143</v>
       </c>
       <c r="B152" t="n">
-        <v>209.1718784416434</v>
+        <v>200.8209691272831</v>
       </c>
       <c r="C152" t="n">
-        <v>216.335512072091</v>
+        <v>202.5370477944956</v>
       </c>
       <c r="D152" t="n">
-        <v>206.9070662315077</v>
+        <v>196.6704525729091</v>
       </c>
       <c r="E152" t="n">
-        <v>216.1160125732422</v>
+        <v>197.9974212646484</v>
       </c>
       <c r="F152" t="n">
-        <v>187172400</v>
+        <v>128647000</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="B153" t="n">
-        <v>209.0122528840405</v>
+        <v>199.0450218084295</v>
       </c>
       <c r="C153" t="n">
-        <v>214.2402930542568</v>
+        <v>201.2699318245734</v>
       </c>
       <c r="D153" t="n">
-        <v>207.7251862691963</v>
+        <v>194.2958829090753</v>
       </c>
       <c r="E153" t="n">
-        <v>212.6838531494141</v>
+        <v>198.02734375</v>
       </c>
       <c r="F153" t="n">
-        <v>180275400</v>
+        <v>125368100</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46141</v>
+        <v>46147</v>
       </c>
       <c r="B154" t="n">
-        <v>212.2149257168926</v>
+        <v>198.8454820247872</v>
       </c>
       <c r="C154" t="n">
-        <v>212.2348843687743</v>
+        <v>199.7833407086998</v>
       </c>
       <c r="D154" t="n">
-        <v>207.1066069625242</v>
+        <v>195.5829352820671</v>
       </c>
       <c r="E154" t="n">
-        <v>208.7727966308594</v>
+        <v>196.0518646240234</v>
       </c>
       <c r="F154" t="n">
-        <v>123711800</v>
+        <v>113406600</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="B155" t="n">
-        <v>209.4512265433391</v>
+        <v>199.4341385249406</v>
       </c>
       <c r="C155" t="n">
-        <v>209.8203930740204</v>
+        <v>207.7950323152332</v>
       </c>
       <c r="D155" t="n">
-        <v>198.2468419328838</v>
+        <v>198.1570588579161</v>
       </c>
       <c r="E155" t="n">
-        <v>199.1148681640625</v>
+        <v>207.3560333251953</v>
       </c>
       <c r="F155" t="n">
-        <v>225239200</v>
+        <v>188362800</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46143</v>
+        <v>46149</v>
       </c>
       <c r="B156" t="n">
-        <v>200.8209846036705</v>
+        <v>207.8648724722903</v>
       </c>
       <c r="C156" t="n">
-        <v>202.5370634031337</v>
+        <v>213.7115092245668</v>
       </c>
       <c r="D156" t="n">
-        <v>196.6704677294345</v>
+        <v>206.0290722858257</v>
       </c>
       <c r="E156" t="n">
-        <v>197.9974365234375</v>
+        <v>211.0176696777344</v>
       </c>
       <c r="F156" t="n">
-        <v>128647000</v>
+        <v>168307900</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="B157" t="n">
-        <v>199.0450218084295</v>
+        <v>212.5441790763045</v>
       </c>
       <c r="C157" t="n">
-        <v>201.2699318245734</v>
+        <v>217.3033052467507</v>
       </c>
       <c r="D157" t="n">
-        <v>194.2958829090753</v>
+        <v>212.4044989584125</v>
       </c>
       <c r="E157" t="n">
-        <v>198.02734375</v>
+        <v>214.709228515625</v>
       </c>
       <c r="F157" t="n">
-        <v>125368100</v>
+        <v>136421400</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46147</v>
+        <v>46153</v>
       </c>
       <c r="B158" t="n">
-        <v>198.8454820247872</v>
+        <v>213.5518657378577</v>
       </c>
       <c r="C158" t="n">
-        <v>199.7833407086998</v>
+        <v>221.7930381906342</v>
       </c>
       <c r="D158" t="n">
-        <v>195.5829352820671</v>
+        <v>213.402213909002</v>
       </c>
       <c r="E158" t="n">
-        <v>196.0518646240234</v>
+        <v>218.9395599365234</v>
       </c>
       <c r="F158" t="n">
-        <v>113406600</v>
+        <v>160685800</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46148</v>
+        <v>46154</v>
       </c>
       <c r="B159" t="n">
-        <v>199.4341385249406</v>
+        <v>218.0515943496244</v>
       </c>
       <c r="C159" t="n">
-        <v>207.7950323152332</v>
+        <v>223.239732575863</v>
       </c>
       <c r="D159" t="n">
-        <v>198.1570588579161</v>
+        <v>214.4298677829735</v>
       </c>
       <c r="E159" t="n">
-        <v>207.3560333251953</v>
+        <v>220.2765045166016</v>
       </c>
       <c r="F159" t="n">
-        <v>188362800</v>
+        <v>159176600</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46149</v>
+        <v>46155</v>
       </c>
       <c r="B160" t="n">
-        <v>207.8648724722903</v>
+        <v>224.4170305354026</v>
       </c>
       <c r="C160" t="n">
-        <v>213.7115092245668</v>
+        <v>227.3203978139454</v>
       </c>
       <c r="D160" t="n">
-        <v>206.0290722858257</v>
+        <v>221.0647077692387</v>
       </c>
       <c r="E160" t="n">
-        <v>211.0176696777344</v>
+        <v>225.3149871826172</v>
       </c>
       <c r="F160" t="n">
-        <v>168307900</v>
+        <v>150405400</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46150</v>
+        <v>46156</v>
       </c>
       <c r="B161" t="n">
-        <v>212.5441790763045</v>
+        <v>229.3258255277811</v>
       </c>
       <c r="C161" t="n">
-        <v>217.3033052467507</v>
+        <v>236.0005559723521</v>
       </c>
       <c r="D161" t="n">
-        <v>212.4044989584125</v>
+        <v>228.7770767762568</v>
       </c>
       <c r="E161" t="n">
-        <v>214.709228515625</v>
+        <v>235.202392578125</v>
       </c>
       <c r="F161" t="n">
-        <v>136421400</v>
+        <v>180782900</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="B162" t="n">
-        <v>213.5518657378577</v>
+        <v>229.2360294447337</v>
       </c>
       <c r="C162" t="n">
-        <v>221.7930381906342</v>
+        <v>230.9720668751014</v>
       </c>
       <c r="D162" t="n">
-        <v>213.402213909002</v>
+        <v>223.7286287034134</v>
       </c>
       <c r="E162" t="n">
-        <v>218.9395599365234</v>
+        <v>224.8061676025391</v>
       </c>
       <c r="F162" t="n">
-        <v>160685800</v>
+        <v>180977600</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="B163" t="n">
-        <v>218.0515943496244</v>
+        <v>229.345773483712</v>
       </c>
       <c r="C163" t="n">
-        <v>223.239732575863</v>
+        <v>229.4754818886306</v>
       </c>
       <c r="D163" t="n">
-        <v>214.4298677829735</v>
+        <v>217.8719993892805</v>
       </c>
       <c r="E163" t="n">
-        <v>220.2765045166016</v>
+        <v>221.8130035400391</v>
       </c>
       <c r="F163" t="n">
-        <v>159176600</v>
+        <v>146280900</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46155</v>
+        <v>46161</v>
       </c>
       <c r="B164" t="n">
-        <v>224.4170305354026</v>
+        <v>219.1191400841904</v>
       </c>
       <c r="C164" t="n">
-        <v>227.3203978139454</v>
+        <v>223.9680572056967</v>
       </c>
       <c r="D164" t="n">
-        <v>221.0647077692387</v>
+        <v>217.4130483552105</v>
       </c>
       <c r="E164" t="n">
-        <v>225.3149871826172</v>
+        <v>220.1068878173828</v>
       </c>
       <c r="F164" t="n">
-        <v>150405400</v>
+        <v>140948200</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="B165" t="n">
-        <v>229.3258255277811</v>
+        <v>222.6710257508039</v>
       </c>
       <c r="C165" t="n">
-        <v>236.0005559723521</v>
+        <v>225.6143103895453</v>
       </c>
       <c r="D165" t="n">
-        <v>228.7770767762568</v>
+        <v>219.9971448577806</v>
       </c>
       <c r="E165" t="n">
-        <v>235.202392578125</v>
+        <v>222.9603729248047</v>
       </c>
       <c r="F165" t="n">
-        <v>180782900</v>
+        <v>184201600</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46157</v>
+        <v>46163</v>
       </c>
       <c r="B166" t="n">
-        <v>229.2360138852663</v>
+        <v>221.7830583738447</v>
       </c>
       <c r="C166" t="n">
-        <v>230.9720511978</v>
+        <v>226.8814055684356</v>
       </c>
       <c r="D166" t="n">
-        <v>223.7286135177626</v>
+        <v>217.4330007955402</v>
       </c>
       <c r="E166" t="n">
-        <v>224.80615234375</v>
+        <v>219.0093994140625</v>
       </c>
       <c r="F166" t="n">
-        <v>180977600</v>
+        <v>203381800</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46160</v>
+        <v>46164</v>
       </c>
       <c r="B167" t="n">
-        <v>229.345773483712</v>
+        <v>220.3962175709585</v>
       </c>
       <c r="C167" t="n">
-        <v>229.4754818886306</v>
+        <v>220.5059673180016</v>
       </c>
       <c r="D167" t="n">
-        <v>217.8719993892805</v>
+        <v>214.3101381389001</v>
       </c>
       <c r="E167" t="n">
-        <v>221.8130035400391</v>
+        <v>214.8389282226562</v>
       </c>
       <c r="F167" t="n">
-        <v>146280900</v>
+        <v>169275700</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46161</v>
+        <v>46168</v>
       </c>
       <c r="B168" t="n">
-        <v>219.1191400841904</v>
+        <v>216.0461718127993</v>
       </c>
       <c r="C168" t="n">
-        <v>223.9680572056967</v>
+        <v>217.6824311685512</v>
       </c>
       <c r="D168" t="n">
-        <v>217.4130483552105</v>
+        <v>211.5165320236786</v>
       </c>
       <c r="E168" t="n">
-        <v>220.1068878173828</v>
+        <v>214.3700103759766</v>
       </c>
       <c r="F168" t="n">
-        <v>140948200</v>
+        <v>187202600</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="B169" t="n">
-        <v>222.6710257508039</v>
+        <v>213.6316806617713</v>
       </c>
       <c r="C169" t="n">
-        <v>225.6143103895453</v>
+        <v>213.6616110269177</v>
       </c>
       <c r="D169" t="n">
-        <v>219.9971448577806</v>
+        <v>208.3038625298546</v>
       </c>
       <c r="E169" t="n">
-        <v>222.9603729248047</v>
+        <v>212.1151580810547</v>
       </c>
       <c r="F169" t="n">
-        <v>184201600</v>
+        <v>167601200</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46163</v>
+        <v>46170</v>
       </c>
       <c r="B170" t="n">
-        <v>221.7830583738447</v>
+        <v>210.7981551984497</v>
       </c>
       <c r="C170" t="n">
-        <v>226.8814055684356</v>
+        <v>215.0284909668814</v>
       </c>
       <c r="D170" t="n">
-        <v>217.4330007955402</v>
+        <v>210.7382944698381</v>
       </c>
       <c r="E170" t="n">
-        <v>219.0093994140625</v>
+        <v>213.7613830566406</v>
       </c>
       <c r="F170" t="n">
-        <v>203381800</v>
+        <v>143996000</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46164</v>
+        <v>46171</v>
       </c>
       <c r="B171" t="n">
-        <v>220.3962175709585</v>
+        <v>214.0906505321041</v>
       </c>
       <c r="C171" t="n">
-        <v>220.5059673180016</v>
+        <v>217.3631692496548</v>
       </c>
       <c r="D171" t="n">
-        <v>214.3101381389001</v>
+        <v>210.6485213277038</v>
       </c>
       <c r="E171" t="n">
-        <v>214.8389282226562</v>
+        <v>210.6584930419922</v>
       </c>
       <c r="F171" t="n">
-        <v>169275700</v>
+        <v>289410600</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="B172" t="n">
-        <v>216.0461718127993</v>
+        <v>215.2380189209027</v>
       </c>
       <c r="C172" t="n">
-        <v>217.6824311685512</v>
+        <v>224.3571743491113</v>
       </c>
       <c r="D172" t="n">
-        <v>211.5165320236786</v>
+        <v>215.2080885544549</v>
       </c>
       <c r="E172" t="n">
-        <v>214.3700103759766</v>
+        <v>223.8483428955078</v>
       </c>
       <c r="F172" t="n">
-        <v>187202600</v>
+        <v>212850700</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46169</v>
+        <v>46175</v>
       </c>
       <c r="B173" t="n">
-        <v>213.6316806617713</v>
+        <v>226.6618858382332</v>
       </c>
       <c r="C173" t="n">
-        <v>213.6616110269177</v>
+        <v>231.7502608645459</v>
       </c>
       <c r="D173" t="n">
-        <v>208.3038625298546</v>
+        <v>220.8451951370975</v>
       </c>
       <c r="E173" t="n">
-        <v>212.1151580810547</v>
+        <v>222.3118438720703</v>
       </c>
       <c r="F173" t="n">
-        <v>167601200</v>
+        <v>193362900</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46170</v>
+        <v>46176</v>
       </c>
       <c r="B174" t="n">
-        <v>210.7981702457166</v>
+        <v>221.2143597561905</v>
       </c>
       <c r="C174" t="n">
-        <v>215.0285063161196</v>
+        <v>222.3118572511273</v>
       </c>
       <c r="D174" t="n">
-        <v>210.738309512832</v>
+        <v>214.0207957553572</v>
       </c>
       <c r="E174" t="n">
-        <v>213.7613983154297</v>
+        <v>214.26025390625</v>
       </c>
       <c r="F174" t="n">
-        <v>143996000</v>
+        <v>160907000</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,25 +4967,25 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46171</v>
+        <v>46177</v>
       </c>
       <c r="B175" t="n">
-        <v>214.0906505321041</v>
+        <v>213.6709127939037</v>
       </c>
       <c r="C175" t="n">
-        <v>217.3631692496548</v>
+        <v>221.3523199881091</v>
       </c>
       <c r="D175" t="n">
-        <v>210.6485213277038</v>
+        <v>210.73419644349</v>
       </c>
       <c r="E175" t="n">
-        <v>210.6584930419922</v>
+        <v>218.4156036376953</v>
       </c>
       <c r="F175" t="n">
-        <v>289410600</v>
+        <v>169022200</v>
       </c>
       <c r="G175" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46174</v>
+        <v>46178</v>
       </c>
       <c r="B176" t="n">
-        <v>215.2380189209027</v>
+        <v>214.2902104723603</v>
       </c>
       <c r="C176" t="n">
-        <v>224.3571743491113</v>
+        <v>214.6298267834636</v>
       </c>
       <c r="D176" t="n">
-        <v>215.2080885544549</v>
+        <v>204.101614447126</v>
       </c>
       <c r="E176" t="n">
-        <v>223.8483428955078</v>
+        <v>204.8707580566406</v>
       </c>
       <c r="F176" t="n">
-        <v>212850700</v>
+        <v>219655500</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="B177" t="n">
-        <v>226.6618858382332</v>
+        <v>209.9450713288228</v>
       </c>
       <c r="C177" t="n">
-        <v>231.7502608645459</v>
+        <v>210.2347557268212</v>
       </c>
       <c r="D177" t="n">
-        <v>220.8451951370975</v>
+        <v>205.7697506938822</v>
       </c>
       <c r="E177" t="n">
-        <v>222.3118438720703</v>
+        <v>208.4067993164062</v>
       </c>
       <c r="F177" t="n">
-        <v>193362900</v>
+        <v>138372800</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46176</v>
+        <v>46182</v>
       </c>
       <c r="B178" t="n">
-        <v>221.2143597561905</v>
+        <v>210.3845825512031</v>
       </c>
       <c r="C178" t="n">
-        <v>222.3118572511273</v>
+        <v>211.1637095162451</v>
       </c>
       <c r="D178" t="n">
-        <v>214.0207957553572</v>
+        <v>199.1171915656509</v>
       </c>
       <c r="E178" t="n">
-        <v>214.26025390625</v>
+        <v>207.9573059082031</v>
       </c>
       <c r="F178" t="n">
-        <v>160907000</v>
+        <v>180962500</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,25 +5071,25 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46177</v>
+        <v>46183</v>
       </c>
       <c r="B179" t="n">
-        <v>213.6709127939037</v>
+        <v>204.2014963256503</v>
       </c>
       <c r="C179" t="n">
-        <v>221.3523199881091</v>
+        <v>206.9883864105018</v>
       </c>
       <c r="D179" t="n">
-        <v>210.73419644349</v>
+        <v>199.696542748819</v>
       </c>
       <c r="E179" t="n">
-        <v>218.4156036376953</v>
+        <v>200.1959838867188</v>
       </c>
       <c r="F179" t="n">
-        <v>169022200</v>
+        <v>161746600</v>
       </c>
       <c r="G179" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46178</v>
+        <v>46184</v>
       </c>
       <c r="B180" t="n">
-        <v>214.2902104723603</v>
+        <v>201.2647947500858</v>
       </c>
       <c r="C180" t="n">
-        <v>214.6298267834636</v>
+        <v>205.4301320010667</v>
       </c>
       <c r="D180" t="n">
-        <v>204.101614447126</v>
+        <v>199.3169621236104</v>
       </c>
       <c r="E180" t="n">
-        <v>204.8707580566406</v>
+        <v>204.6410064697266</v>
       </c>
       <c r="F180" t="n">
-        <v>219655500</v>
+        <v>158643200</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46181</v>
+        <v>46185</v>
       </c>
       <c r="B181" t="n">
-        <v>209.9450713288228</v>
+        <v>204.6310298517525</v>
       </c>
       <c r="C181" t="n">
-        <v>210.2347557268212</v>
+        <v>206.8385664547524</v>
       </c>
       <c r="D181" t="n">
-        <v>205.7697506938822</v>
+        <v>203.2126188059985</v>
       </c>
       <c r="E181" t="n">
-        <v>208.4067993164062</v>
+        <v>204.9606628417969</v>
       </c>
       <c r="F181" t="n">
-        <v>138372800</v>
+        <v>112001800</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46182</v>
+        <v>46188</v>
       </c>
       <c r="B182" t="n">
-        <v>210.3845825512031</v>
+        <v>208.6864864049894</v>
       </c>
       <c r="C182" t="n">
-        <v>211.1637095162451</v>
+        <v>212.4722588232193</v>
       </c>
       <c r="D182" t="n">
-        <v>199.1171915656509</v>
+        <v>208.1071328472061</v>
       </c>
       <c r="E182" t="n">
-        <v>207.9573059082031</v>
+        <v>212.2125396728516</v>
       </c>
       <c r="F182" t="n">
-        <v>180962500</v>
+        <v>149936700</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46183</v>
+        <v>46189</v>
       </c>
       <c r="B183" t="n">
-        <v>204.2014963256503</v>
+        <v>210.9439520928381</v>
       </c>
       <c r="C183" t="n">
-        <v>206.9883864105018</v>
+        <v>211.2536184019877</v>
       </c>
       <c r="D183" t="n">
-        <v>199.696542748819</v>
+        <v>207.0583006421773</v>
       </c>
       <c r="E183" t="n">
-        <v>200.1959838867188</v>
+        <v>207.1781768798828</v>
       </c>
       <c r="F183" t="n">
-        <v>161746600</v>
+        <v>125694100</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46184</v>
+        <v>46190</v>
       </c>
       <c r="B184" t="n">
-        <v>201.2647947500858</v>
+        <v>208.2969174543329</v>
       </c>
       <c r="C184" t="n">
-        <v>205.4301320010667</v>
+        <v>208.9761653200819</v>
       </c>
       <c r="D184" t="n">
-        <v>199.3169621236104</v>
+        <v>202.8530121596522</v>
       </c>
       <c r="E184" t="n">
-        <v>204.6410064697266</v>
+        <v>204.4212493896484</v>
       </c>
       <c r="F184" t="n">
-        <v>158643200</v>
+        <v>128363500</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46185</v>
+        <v>46191</v>
       </c>
       <c r="B185" t="n">
-        <v>204.6310298517525</v>
+        <v>207.0982684229139</v>
       </c>
       <c r="C185" t="n">
-        <v>206.8385664547524</v>
+        <v>211.1537281092123</v>
       </c>
       <c r="D185" t="n">
-        <v>203.2126188059985</v>
+        <v>206.2691942875683</v>
       </c>
       <c r="E185" t="n">
-        <v>204.9606628417969</v>
+        <v>210.4545135498047</v>
       </c>
       <c r="F185" t="n">
-        <v>112001800</v>
+        <v>241272000</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="B186" t="n">
-        <v>208.6864864049894</v>
+        <v>211.2036686200953</v>
       </c>
       <c r="C186" t="n">
-        <v>212.4722588232193</v>
+        <v>213.7508214450341</v>
       </c>
       <c r="D186" t="n">
-        <v>208.1071328472061</v>
+        <v>207.4878253737282</v>
       </c>
       <c r="E186" t="n">
-        <v>212.2125396728516</v>
+        <v>208.4167785644531</v>
       </c>
       <c r="F186" t="n">
-        <v>149936700</v>
+        <v>122041400</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46189</v>
+        <v>46196</v>
       </c>
       <c r="B187" t="n">
-        <v>210.9439520928381</v>
+        <v>201.9440304014853</v>
       </c>
       <c r="C187" t="n">
-        <v>211.2536184019877</v>
+        <v>203.5422481594977</v>
       </c>
       <c r="D187" t="n">
-        <v>207.0583006421773</v>
+        <v>199.77645766483</v>
       </c>
       <c r="E187" t="n">
-        <v>207.1781768798828</v>
+        <v>199.81640625</v>
       </c>
       <c r="F187" t="n">
-        <v>125694100</v>
+        <v>153496200</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46190</v>
+        <v>46197</v>
       </c>
       <c r="B188" t="n">
-        <v>208.2969174543329</v>
+        <v>199.8963159019567</v>
       </c>
       <c r="C188" t="n">
-        <v>208.9761653200819</v>
+        <v>201.4445864758279</v>
       </c>
       <c r="D188" t="n">
-        <v>202.8530121596522</v>
+        <v>196.360279356477</v>
       </c>
       <c r="E188" t="n">
-        <v>204.4212493896484</v>
+        <v>198.7775726318359</v>
       </c>
       <c r="F188" t="n">
-        <v>128363500</v>
+        <v>151810700</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46191</v>
+        <v>46198</v>
       </c>
       <c r="B189" t="n">
-        <v>207.0982684229139</v>
+        <v>199.8563704571445</v>
       </c>
       <c r="C189" t="n">
-        <v>211.1537281092123</v>
+        <v>200.5755669254449</v>
       </c>
       <c r="D189" t="n">
-        <v>206.2691942875683</v>
+        <v>191.9152592982058</v>
       </c>
       <c r="E189" t="n">
-        <v>210.4545135498047</v>
+        <v>195.5212249755859</v>
       </c>
       <c r="F189" t="n">
-        <v>241272000</v>
+        <v>149550000</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46195</v>
+        <v>46199</v>
       </c>
       <c r="B190" t="n">
-        <v>211.2036686200953</v>
+        <v>192.9041409641119</v>
       </c>
       <c r="C190" t="n">
-        <v>213.7508214450341</v>
+        <v>195.331432829306</v>
       </c>
       <c r="D190" t="n">
-        <v>207.4878253737282</v>
+        <v>191.0062707295152</v>
       </c>
       <c r="E190" t="n">
-        <v>208.4167785644531</v>
+        <v>192.3148040771484</v>
       </c>
       <c r="F190" t="n">
-        <v>122041400</v>
+        <v>179304100</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="B191" t="n">
-        <v>201.9440304014853</v>
+        <v>193.6333319429392</v>
       </c>
       <c r="C191" t="n">
-        <v>203.5422481594977</v>
+        <v>195.9607141929515</v>
       </c>
       <c r="D191" t="n">
-        <v>199.77645766483</v>
+        <v>189.5878557469149</v>
       </c>
       <c r="E191" t="n">
-        <v>199.81640625</v>
+        <v>194.7520751953125</v>
       </c>
       <c r="F191" t="n">
-        <v>153496200</v>
+        <v>148835700</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46197</v>
+        <v>46203</v>
       </c>
       <c r="B192" t="n">
-        <v>199.8963159019567</v>
+        <v>197.0195429632178</v>
       </c>
       <c r="C192" t="n">
-        <v>201.4445864758279</v>
+        <v>200.4057532237791</v>
       </c>
       <c r="D192" t="n">
-        <v>196.360279356477</v>
+        <v>194.8919188665145</v>
       </c>
       <c r="E192" t="n">
-        <v>198.7775726318359</v>
+        <v>199.8663482666016</v>
       </c>
       <c r="F192" t="n">
-        <v>151810700</v>
+        <v>166476700</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46198</v>
+        <v>46204</v>
       </c>
       <c r="B193" t="n">
-        <v>199.8563704571445</v>
+        <v>195.9806989625188</v>
       </c>
       <c r="C193" t="n">
-        <v>200.5755669254449</v>
+        <v>199.626628404907</v>
       </c>
       <c r="D193" t="n">
-        <v>191.9152592982058</v>
+        <v>193.2337727110923</v>
       </c>
       <c r="E193" t="n">
-        <v>195.5212249755859</v>
+        <v>197.3591613769531</v>
       </c>
       <c r="F193" t="n">
-        <v>149550000</v>
+        <v>146147600</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46199</v>
+        <v>46205</v>
       </c>
       <c r="B194" t="n">
-        <v>192.9041409641119</v>
+        <v>196.9196593659626</v>
       </c>
       <c r="C194" t="n">
-        <v>195.331432829306</v>
+        <v>199.8363939026278</v>
       </c>
       <c r="D194" t="n">
-        <v>191.0062707295152</v>
+        <v>192.1350197738411</v>
       </c>
       <c r="E194" t="n">
-        <v>192.3148040771484</v>
+        <v>194.6122436523438</v>
       </c>
       <c r="F194" t="n">
-        <v>179304100</v>
+        <v>142068700</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46202</v>
+        <v>46209</v>
       </c>
       <c r="B195" t="n">
-        <v>193.6333319429392</v>
+        <v>194.202694284663</v>
       </c>
       <c r="C195" t="n">
-        <v>195.9607141929515</v>
+        <v>197.3292007505161</v>
       </c>
       <c r="D195" t="n">
-        <v>189.5878557469149</v>
+        <v>193.7731822131383</v>
       </c>
       <c r="E195" t="n">
-        <v>194.7520751953125</v>
+        <v>195.3314361572266</v>
       </c>
       <c r="F195" t="n">
-        <v>148835700</v>
+        <v>108999000</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46203</v>
+        <v>46210</v>
       </c>
       <c r="B196" t="n">
-        <v>197.0195429632178</v>
+        <v>192.1549837798622</v>
       </c>
       <c r="C196" t="n">
-        <v>200.4057532237791</v>
+        <v>198.1882414262674</v>
       </c>
       <c r="D196" t="n">
-        <v>194.8919188665145</v>
+        <v>190.9263628146717</v>
       </c>
       <c r="E196" t="n">
-        <v>199.8663482666016</v>
+        <v>196.7098846435547</v>
       </c>
       <c r="F196" t="n">
-        <v>166476700</v>
+        <v>124154600</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="B197" t="n">
-        <v>195.9806989625188</v>
+        <v>194.9618356993413</v>
       </c>
       <c r="C197" t="n">
-        <v>199.626628404907</v>
+        <v>204.9306918075912</v>
       </c>
       <c r="D197" t="n">
-        <v>193.2337727110923</v>
+        <v>194.841974703339</v>
       </c>
       <c r="E197" t="n">
-        <v>197.3591613769531</v>
+        <v>203.891845703125</v>
       </c>
       <c r="F197" t="n">
-        <v>146147600</v>
+        <v>147419100</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46205</v>
+        <v>46212</v>
       </c>
       <c r="B198" t="n">
-        <v>196.9196593659626</v>
+        <v>204.2314748595287</v>
       </c>
       <c r="C198" t="n">
-        <v>199.8363939026278</v>
+        <v>204.3613191897594</v>
       </c>
       <c r="D198" t="n">
-        <v>192.1350197738411</v>
+        <v>198.7376223952696</v>
       </c>
       <c r="E198" t="n">
-        <v>194.6122436523438</v>
+        <v>202.5533447265625</v>
       </c>
       <c r="F198" t="n">
-        <v>142068700</v>
+        <v>132037400</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="B199" t="n">
-        <v>194.202694284663</v>
+        <v>201.7742207048944</v>
       </c>
       <c r="C199" t="n">
-        <v>197.3292007505161</v>
+        <v>210.7641612313501</v>
       </c>
       <c r="D199" t="n">
-        <v>193.7731822131383</v>
+        <v>201.6943082934289</v>
       </c>
       <c r="E199" t="n">
-        <v>195.3314361572266</v>
+        <v>210.7242126464844</v>
       </c>
       <c r="F199" t="n">
-        <v>108999000</v>
+        <v>148421000</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46210</v>
+        <v>46216</v>
       </c>
       <c r="B200" t="n">
-        <v>192.1549837798622</v>
+        <v>208.3069001369788</v>
       </c>
       <c r="C200" t="n">
-        <v>198.1882414262674</v>
+        <v>210.3346451505122</v>
       </c>
       <c r="D200" t="n">
-        <v>190.9263628146717</v>
+        <v>202.7730991138312</v>
       </c>
       <c r="E200" t="n">
-        <v>196.7098846435547</v>
+        <v>203.3025054931641</v>
       </c>
       <c r="F200" t="n">
-        <v>124154600</v>
+        <v>121411000</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46211</v>
+        <v>46217</v>
       </c>
       <c r="B201" t="n">
-        <v>194.9618356993413</v>
+        <v>207.9672957533915</v>
       </c>
       <c r="C201" t="n">
-        <v>204.9306918075912</v>
+        <v>212.3124399374416</v>
       </c>
       <c r="D201" t="n">
-        <v>194.841974703339</v>
+        <v>203.5722196467825</v>
       </c>
       <c r="E201" t="n">
-        <v>203.891845703125</v>
+        <v>211.5632781982422</v>
       </c>
       <c r="F201" t="n">
-        <v>147419100</v>
+        <v>124379600</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46212</v>
+        <v>46218</v>
       </c>
       <c r="B202" t="n">
-        <v>204.2314748595287</v>
+        <v>211.7230919717581</v>
       </c>
       <c r="C202" t="n">
-        <v>204.3613191897594</v>
+        <v>213.5710150202495</v>
       </c>
       <c r="D202" t="n">
-        <v>198.7376223952696</v>
+        <v>205.8096955397309</v>
       </c>
       <c r="E202" t="n">
-        <v>202.5533447265625</v>
+        <v>212.2624816894531</v>
       </c>
       <c r="F202" t="n">
-        <v>132037400</v>
+        <v>124797200</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B203" t="n">
-        <v>201.7742207048944</v>
+        <v>209.9350906043833</v>
       </c>
       <c r="C203" t="n">
-        <v>210.7641612313501</v>
+        <v>210.8440771529852</v>
       </c>
       <c r="D203" t="n">
-        <v>201.6943082934289</v>
+        <v>205.6199270055466</v>
       </c>
       <c r="E203" t="n">
-        <v>210.7242126464844</v>
+        <v>207.1681823730469</v>
       </c>
       <c r="F203" t="n">
-        <v>148421000</v>
+        <v>122986100</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46216</v>
+        <v>46220</v>
       </c>
       <c r="B204" t="n">
-        <v>208.3069001369788</v>
+        <v>202.4135048295048</v>
       </c>
       <c r="C204" t="n">
-        <v>210.3346451505122</v>
+        <v>206.4190172896336</v>
       </c>
       <c r="D204" t="n">
-        <v>202.7730991138312</v>
+        <v>197.7487264058434</v>
       </c>
       <c r="E204" t="n">
-        <v>203.3025054931641</v>
+        <v>202.5833129882812</v>
       </c>
       <c r="F204" t="n">
-        <v>121411000</v>
+        <v>144281900</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46217</v>
+        <v>46223</v>
       </c>
       <c r="B205" t="n">
-        <v>207.9672957533915</v>
+        <v>205.639896943356</v>
       </c>
       <c r="C205" t="n">
-        <v>212.3124399374416</v>
+        <v>207.5078172334397</v>
       </c>
       <c r="D205" t="n">
-        <v>203.5722196467825</v>
+        <v>202.0539130969454</v>
       </c>
       <c r="E205" t="n">
-        <v>211.5632781982422</v>
+        <v>203.0527954101562</v>
       </c>
       <c r="F205" t="n">
-        <v>124379600</v>
+        <v>88701500</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46218</v>
+        <v>46224</v>
       </c>
       <c r="B206" t="n">
-        <v>211.7230919717581</v>
+        <v>207.308024406286</v>
       </c>
       <c r="C206" t="n">
-        <v>213.5710150202495</v>
+        <v>208.4167843613107</v>
       </c>
       <c r="D206" t="n">
-        <v>205.8096955397309</v>
+        <v>203.7819711309363</v>
       </c>
       <c r="E206" t="n">
-        <v>212.2624816894531</v>
+        <v>207.0583038330078</v>
       </c>
       <c r="F206" t="n">
-        <v>124797200</v>
+        <v>108685600</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46219</v>
+        <v>46225</v>
       </c>
       <c r="B207" t="n">
-        <v>209.9350906043833</v>
+        <v>205.579968274895</v>
       </c>
       <c r="C207" t="n">
-        <v>210.8440771529852</v>
+        <v>214.1503804276117</v>
       </c>
       <c r="D207" t="n">
-        <v>205.6199270055466</v>
+        <v>204.7209288682105</v>
       </c>
       <c r="E207" t="n">
-        <v>207.1681823730469</v>
+        <v>211.8229827880859</v>
       </c>
       <c r="F207" t="n">
-        <v>122986100</v>
+        <v>137645600</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46220</v>
+        <v>46226</v>
       </c>
       <c r="B208" t="n">
-        <v>202.4135048295048</v>
+        <v>209.2258868865651</v>
       </c>
       <c r="C208" t="n">
-        <v>206.4190172896336</v>
+        <v>210.6342993029147</v>
       </c>
       <c r="D208" t="n">
-        <v>197.7487264058434</v>
+        <v>205.7297989431358</v>
       </c>
       <c r="E208" t="n">
-        <v>202.5833129882812</v>
+        <v>208.5266571044922</v>
       </c>
       <c r="F208" t="n">
-        <v>144281900</v>
+        <v>110505300</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="B209" t="n">
-        <v>205.639896943356</v>
+        <v>207.2181292349697</v>
       </c>
       <c r="C209" t="n">
-        <v>207.5078172334397</v>
+        <v>211.6731509810223</v>
       </c>
       <c r="D209" t="n">
-        <v>202.0539130969454</v>
+        <v>204.5810805834776</v>
       </c>
       <c r="E209" t="n">
-        <v>203.0527954101562</v>
+        <v>206.6088104248047</v>
       </c>
       <c r="F209" t="n">
-        <v>88701500</v>
+        <v>114836800</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="B210" t="n">
-        <v>207.308024406286</v>
+        <v>207.9672962732577</v>
       </c>
       <c r="C210" t="n">
-        <v>208.4167843613107</v>
+        <v>208.5166845983908</v>
       </c>
       <c r="D210" t="n">
-        <v>203.7819711309363</v>
+        <v>195.2215633388429</v>
       </c>
       <c r="E210" t="n">
-        <v>207.0583038330078</v>
+        <v>196.2903594970703</v>
       </c>
       <c r="F210" t="n">
-        <v>108685600</v>
+        <v>154353700</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B211" t="n">
-        <v>205.579968274895</v>
+        <v>194.782047001347</v>
       </c>
       <c r="C211" t="n">
-        <v>214.1503804276117</v>
+        <v>198.4779084345641</v>
       </c>
       <c r="D211" t="n">
-        <v>204.7209288682105</v>
+        <v>192.5245785077403</v>
       </c>
       <c r="E211" t="n">
-        <v>211.8229827880859</v>
+        <v>196.789794921875</v>
       </c>
       <c r="F211" t="n">
-        <v>137645600</v>
+        <v>134111500</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46226</v>
+        <v>46232</v>
       </c>
       <c r="B212" t="n">
-        <v>209.2258868865651</v>
+        <v>195.6311069684468</v>
       </c>
       <c r="C212" t="n">
-        <v>210.6342993029147</v>
+        <v>196.8497446088402</v>
       </c>
       <c r="D212" t="n">
-        <v>205.7297989431358</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="E212" t="n">
-        <v>208.5266571044922</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="F212" t="n">
-        <v>110505300</v>
+        <v>147680800</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B213" t="n">
-        <v>207.2181292349697</v>
+        <v>193.2337718176948</v>
       </c>
       <c r="C213" t="n">
-        <v>211.6731509810223</v>
+        <v>197.0295274868271</v>
       </c>
       <c r="D213" t="n">
-        <v>204.5810805834776</v>
+        <v>191.3059363552755</v>
       </c>
       <c r="E213" t="n">
-        <v>206.6088104248047</v>
+        <v>194.8219909667969</v>
       </c>
       <c r="F213" t="n">
-        <v>114836800</v>
+        <v>129010200</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="B214" t="n">
-        <v>207.9672962732577</v>
+        <v>198.2182038580375</v>
       </c>
       <c r="C214" t="n">
-        <v>208.5166845983908</v>
+        <v>201.7742223680242</v>
       </c>
       <c r="D214" t="n">
-        <v>195.2215633388429</v>
+        <v>194.7320991825756</v>
       </c>
       <c r="E214" t="n">
-        <v>196.2903594970703</v>
+        <v>200.5256195068359</v>
       </c>
       <c r="F214" t="n">
-        <v>154353700</v>
+        <v>139961200</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46231</v>
+        <v>46237</v>
       </c>
       <c r="B215" t="n">
-        <v>194.782047001347</v>
+        <v>197.4690486270115</v>
       </c>
       <c r="C215" t="n">
-        <v>198.4779084345641</v>
+        <v>208.506701330784</v>
       </c>
       <c r="D215" t="n">
-        <v>192.5245785077403</v>
+        <v>196.6299911347511</v>
       </c>
       <c r="E215" t="n">
-        <v>196.789794921875</v>
+        <v>206.4090423583984</v>
       </c>
       <c r="F215" t="n">
-        <v>134111500</v>
+        <v>128406900</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="B216" t="n">
-        <v>195.6311069684468</v>
+        <v>211.0638257011038</v>
       </c>
       <c r="C216" t="n">
-        <v>196.8497446088402</v>
+        <v>212.8218530009649</v>
       </c>
       <c r="D216" t="n">
-        <v>189.7976226806641</v>
+        <v>208.8163406042335</v>
       </c>
       <c r="E216" t="n">
-        <v>189.7976226806641</v>
+        <v>211.7031097412109</v>
       </c>
       <c r="F216" t="n">
-        <v>147680800</v>
+        <v>134922000</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46233</v>
+        <v>46239</v>
       </c>
       <c r="B217" t="n">
-        <v>193.2337718176948</v>
+        <v>216.6176127852948</v>
       </c>
       <c r="C217" t="n">
-        <v>197.0295274868271</v>
+        <v>221.9716224388697</v>
       </c>
       <c r="D217" t="n">
-        <v>191.3059363552755</v>
+        <v>216.1581202281489</v>
       </c>
       <c r="E217" t="n">
-        <v>194.8219909667969</v>
+        <v>218.9749755859375</v>
       </c>
       <c r="F217" t="n">
-        <v>129010200</v>
+        <v>158187400</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46234</v>
+        <v>46240</v>
       </c>
       <c r="B218" t="n">
-        <v>198.2182038580375</v>
+        <v>221.2823935806188</v>
       </c>
       <c r="C218" t="n">
-        <v>201.7742223680242</v>
+        <v>223.3800524967045</v>
       </c>
       <c r="D218" t="n">
-        <v>194.7320991825756</v>
+        <v>216.7574580038405</v>
       </c>
       <c r="E218" t="n">
-        <v>200.5256195068359</v>
+        <v>218.7452392578125</v>
       </c>
       <c r="F218" t="n">
-        <v>139961200</v>
+        <v>113940600</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="B219" t="n">
-        <v>197.4690486270115</v>
+        <v>221.2923777041913</v>
       </c>
       <c r="C219" t="n">
-        <v>208.506701330784</v>
+        <v>224.5087799247126</v>
       </c>
       <c r="D219" t="n">
-        <v>196.6299911347511</v>
+        <v>220.4133716458871</v>
       </c>
       <c r="E219" t="n">
-        <v>206.4090423583984</v>
+        <v>223.7096862792969</v>
       </c>
       <c r="F219" t="n">
-        <v>128406900</v>
+        <v>105669400</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="B220" t="n">
-        <v>211.0638257011038</v>
+        <v>223.1502910726907</v>
       </c>
       <c r="C220" t="n">
-        <v>212.8218530009649</v>
+        <v>223.8894694330602</v>
       </c>
       <c r="D220" t="n">
-        <v>208.8163406042335</v>
+        <v>216.5277120448001</v>
       </c>
       <c r="E220" t="n">
-        <v>211.7031097412109</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="F220" t="n">
-        <v>134922000</v>
+        <v>115846600</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="B221" t="n">
-        <v>216.6176127852948</v>
+        <v>221.9216754142795</v>
       </c>
       <c r="C221" t="n">
-        <v>221.9716224388697</v>
+        <v>221.9516406634887</v>
       </c>
       <c r="D221" t="n">
-        <v>216.1581202281489</v>
+        <v>215.9583469538982</v>
       </c>
       <c r="E221" t="n">
-        <v>218.9749755859375</v>
+        <v>217.2568969726562</v>
       </c>
       <c r="F221" t="n">
-        <v>158187400</v>
+        <v>101273100</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46240</v>
+        <v>46246</v>
       </c>
       <c r="B222" t="n">
-        <v>221.2823935806188</v>
+        <v>220.7929293559802</v>
       </c>
       <c r="C222" t="n">
-        <v>223.3800524967045</v>
+        <v>224.848404158734</v>
       </c>
       <c r="D222" t="n">
-        <v>216.7574580038405</v>
+        <v>219.9538719106106</v>
       </c>
       <c r="E222" t="n">
-        <v>218.7452392578125</v>
+        <v>223.8395233154297</v>
       </c>
       <c r="F222" t="n">
-        <v>113940600</v>
+        <v>108783600</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="B223" t="n">
-        <v>221.2923777041913</v>
+        <v>224.8084500146858</v>
       </c>
       <c r="C223" t="n">
-        <v>224.5087799247126</v>
+        <v>226.9760227961096</v>
       </c>
       <c r="D223" t="n">
-        <v>220.4133716458871</v>
+        <v>223.4599680426375</v>
       </c>
       <c r="E223" t="n">
-        <v>223.7096862792969</v>
+        <v>225.0481872558594</v>
       </c>
       <c r="F223" t="n">
-        <v>105669400</v>
+        <v>98867200</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="B224" t="n">
-        <v>223.1502910726907</v>
+        <v>226.5165415533859</v>
       </c>
       <c r="C224" t="n">
-        <v>223.8894694330602</v>
+        <v>227.2357380227387</v>
       </c>
       <c r="D224" t="n">
-        <v>216.5277120448001</v>
+        <v>224.2490744835724</v>
       </c>
       <c r="E224" t="n">
-        <v>217.3068389892578</v>
+        <v>224.9083404541016</v>
       </c>
       <c r="F224" t="n">
-        <v>115846600</v>
+        <v>75680900</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46245</v>
+        <v>46251</v>
       </c>
       <c r="B225" t="n">
-        <v>221.9216754142795</v>
+        <v>225.7274161885591</v>
       </c>
       <c r="C225" t="n">
-        <v>221.9516406634887</v>
+        <v>227.6652502746616</v>
       </c>
       <c r="D225" t="n">
-        <v>215.9583469538982</v>
+        <v>224.6086728983284</v>
       </c>
       <c r="E225" t="n">
-        <v>217.2568969726562</v>
+        <v>224.7584991455078</v>
       </c>
       <c r="F225" t="n">
-        <v>101273100</v>
+        <v>93678700</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="B226" t="n">
-        <v>220.7929293559802</v>
+        <v>220.203597915372</v>
       </c>
       <c r="C226" t="n">
-        <v>224.848404158734</v>
+        <v>221.3922702798686</v>
       </c>
       <c r="D226" t="n">
-        <v>219.9538719106106</v>
+        <v>218.4455705709327</v>
       </c>
       <c r="E226" t="n">
-        <v>223.8395233154297</v>
+        <v>219.4944000244141</v>
       </c>
       <c r="F226" t="n">
-        <v>108783600</v>
+        <v>103128200</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="B227" t="n">
-        <v>224.8084500146858</v>
+        <v>221.4222404106533</v>
       </c>
       <c r="C227" t="n">
-        <v>226.9760227961096</v>
+        <v>222.6208961374568</v>
       </c>
       <c r="D227" t="n">
-        <v>223.4599680426375</v>
+        <v>216.5177245976465</v>
       </c>
       <c r="E227" t="n">
-        <v>225.0481872558594</v>
+        <v>217.3168334960938</v>
       </c>
       <c r="F227" t="n">
-        <v>98867200</v>
+        <v>96797300</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46248</v>
+        <v>46254</v>
       </c>
       <c r="B228" t="n">
-        <v>226.5165415533859</v>
+        <v>218.1159423024499</v>
       </c>
       <c r="C228" t="n">
-        <v>227.2357380227387</v>
+        <v>219.6142657707553</v>
       </c>
       <c r="D228" t="n">
-        <v>224.2490744835724</v>
+        <v>215.418963107847</v>
       </c>
       <c r="E228" t="n">
-        <v>224.9083404541016</v>
+        <v>216.6076354980469</v>
       </c>
       <c r="F228" t="n">
-        <v>75680900</v>
+        <v>92457000</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46251</v>
+        <v>46255</v>
       </c>
       <c r="B229" t="n">
-        <v>225.7274161885591</v>
+        <v>218.1758724878036</v>
       </c>
       <c r="C229" t="n">
-        <v>227.6652502746616</v>
+        <v>218.4955221432803</v>
       </c>
       <c r="D229" t="n">
-        <v>224.6086728983284</v>
+        <v>214.2602556586216</v>
       </c>
       <c r="E229" t="n">
-        <v>224.7584991455078</v>
+        <v>214.4800109863281</v>
       </c>
       <c r="F229" t="n">
-        <v>93678700</v>
+        <v>98869300</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46252</v>
+        <v>46258</v>
       </c>
       <c r="B230" t="n">
-        <v>220.203597915372</v>
+        <v>215.2891020611033</v>
       </c>
       <c r="C230" t="n">
-        <v>221.3922702798686</v>
+        <v>215.3490325607492</v>
       </c>
       <c r="D230" t="n">
-        <v>218.4455705709327</v>
+        <v>207.0183577918231</v>
       </c>
       <c r="E230" t="n">
-        <v>219.4944000244141</v>
+        <v>208.2469787597656</v>
       </c>
       <c r="F230" t="n">
-        <v>103128200</v>
+        <v>135187300</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46253</v>
+        <v>46259</v>
       </c>
       <c r="B231" t="n">
-        <v>221.4222404106533</v>
+        <v>210.7941279013131</v>
       </c>
       <c r="C231" t="n">
-        <v>222.6208961374568</v>
+        <v>214.4899893165327</v>
       </c>
       <c r="D231" t="n">
-        <v>216.5177245976465</v>
+        <v>209.8751580258669</v>
       </c>
       <c r="E231" t="n">
-        <v>217.3168334960938</v>
+        <v>212.8118743896484</v>
       </c>
       <c r="F231" t="n">
-        <v>96797300</v>
+        <v>122309000</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46254</v>
+        <v>46260</v>
       </c>
       <c r="B232" t="n">
-        <v>218.1159423024499</v>
+        <v>212.4023240594531</v>
       </c>
       <c r="C232" t="n">
-        <v>219.6142657707553</v>
+        <v>213.3612577394914</v>
       </c>
       <c r="D232" t="n">
-        <v>215.418963107847</v>
+        <v>208.9961318803605</v>
       </c>
       <c r="E232" t="n">
-        <v>216.6076354980469</v>
+        <v>209.4256591796875</v>
       </c>
       <c r="F232" t="n">
-        <v>92457000</v>
+        <v>179900000</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46255</v>
+        <v>46261</v>
       </c>
       <c r="B233" t="n">
-        <v>218.1758724878036</v>
+        <v>222.6109016432552</v>
       </c>
       <c r="C233" t="n">
-        <v>218.4955221432803</v>
+        <v>230.2123962709879</v>
       </c>
       <c r="D233" t="n">
-        <v>214.2602556586216</v>
+        <v>220.6530857022795</v>
       </c>
       <c r="E233" t="n">
-        <v>214.4800109863281</v>
+        <v>227.7251739501953</v>
       </c>
       <c r="F233" t="n">
-        <v>98869300</v>
+        <v>298909800</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B234" t="n">
-        <v>215.2891020611033</v>
+        <v>227.1058715337123</v>
       </c>
       <c r="C234" t="n">
-        <v>215.3490325607492</v>
+        <v>229.003741733446</v>
       </c>
       <c r="D234" t="n">
-        <v>207.0183577918231</v>
+        <v>216.5676606288883</v>
       </c>
       <c r="E234" t="n">
-        <v>208.2469787597656</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="F234" t="n">
-        <v>135187300</v>
+        <v>195116400</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="B235" t="n">
-        <v>210.7941279013131</v>
+        <v>218.6253647857836</v>
       </c>
       <c r="C235" t="n">
-        <v>214.4899893165327</v>
+        <v>221.0526567078369</v>
       </c>
       <c r="D235" t="n">
-        <v>209.8751580258669</v>
+        <v>215.9683494434545</v>
       </c>
       <c r="E235" t="n">
-        <v>212.8118743896484</v>
+        <v>220.5332336425781</v>
       </c>
       <c r="F235" t="n">
-        <v>122309000</v>
+        <v>124702700</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46260</v>
+        <v>46266</v>
       </c>
       <c r="B236" t="n">
-        <v>212.4023240594531</v>
+        <v>216.5077444634259</v>
       </c>
       <c r="C236" t="n">
-        <v>213.3612577394914</v>
+        <v>220.1636574397174</v>
       </c>
       <c r="D236" t="n">
-        <v>208.9961318803605</v>
+        <v>214.8595947199138</v>
       </c>
       <c r="E236" t="n">
-        <v>209.4256591796875</v>
+        <v>217.1969757080078</v>
       </c>
       <c r="F236" t="n">
-        <v>179900000</v>
+        <v>109756200</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46261</v>
+        <v>46267</v>
       </c>
       <c r="B237" t="n">
-        <v>222.6109016432552</v>
+        <v>218.5454508199983</v>
       </c>
       <c r="C237" t="n">
-        <v>230.2123962709879</v>
+        <v>227.6952163087265</v>
       </c>
       <c r="D237" t="n">
-        <v>220.6530857022795</v>
+        <v>218.2357997469377</v>
       </c>
       <c r="E237" t="n">
-        <v>227.7251739501953</v>
+        <v>224.1591796875</v>
       </c>
       <c r="F237" t="n">
-        <v>298909800</v>
+        <v>157104700</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46262</v>
+        <v>46268</v>
       </c>
       <c r="B238" t="n">
-        <v>227.1058715337123</v>
+        <v>225.7673797205316</v>
       </c>
       <c r="C238" t="n">
-        <v>229.003741733446</v>
+        <v>230.1424737915274</v>
       </c>
       <c r="D238" t="n">
-        <v>216.5676606288883</v>
+        <v>224.4987949430455</v>
       </c>
       <c r="E238" t="n">
-        <v>217.3068389892578</v>
+        <v>228.1946563720703</v>
       </c>
       <c r="F238" t="n">
-        <v>195116400</v>
+        <v>134681600</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="B239" t="n">
-        <v>218.6253647857836</v>
+        <v>230.8317036041433</v>
       </c>
       <c r="C239" t="n">
-        <v>221.0526567078369</v>
+        <v>234.4975997614268</v>
       </c>
       <c r="D239" t="n">
-        <v>215.9683494434545</v>
+        <v>229.3733440032785</v>
       </c>
       <c r="E239" t="n">
-        <v>220.5332336425781</v>
+        <v>230.1025238037109</v>
       </c>
       <c r="F239" t="n">
-        <v>124702700</v>
+        <v>135352400</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="B240" t="n">
-        <v>216.5077444634259</v>
+        <v>232.8494477166676</v>
       </c>
       <c r="C240" t="n">
-        <v>220.1636574397174</v>
+        <v>233.4487831783142</v>
       </c>
       <c r="D240" t="n">
-        <v>214.8595947199138</v>
+        <v>224.5986856128386</v>
       </c>
       <c r="E240" t="n">
-        <v>217.1969757080078</v>
+        <v>225.4776916503906</v>
       </c>
       <c r="F240" t="n">
-        <v>109756200</v>
+        <v>122965600</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="B241" t="n">
-        <v>218.5454508199983</v>
+        <v>225.0281992525124</v>
       </c>
       <c r="C241" t="n">
-        <v>227.6952163087265</v>
+        <v>225.9271872095504</v>
       </c>
       <c r="D241" t="n">
-        <v>218.2357997469377</v>
+        <v>223.2102414251123</v>
       </c>
       <c r="E241" t="n">
-        <v>224.1591796875</v>
+        <v>223.4199981689453</v>
       </c>
       <c r="F241" t="n">
-        <v>157104700</v>
+        <v>82955500</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,25 +6709,25 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46268</v>
+        <v>46275</v>
       </c>
       <c r="B242" t="n">
-        <v>225.7673797205316</v>
+        <v>220.5299987792969</v>
       </c>
       <c r="C242" t="n">
-        <v>230.1424737915274</v>
+        <v>220.9900054931641</v>
       </c>
       <c r="D242" t="n">
-        <v>224.4987949430455</v>
+        <v>217.1999969482422</v>
       </c>
       <c r="E242" t="n">
-        <v>228.1946563720703</v>
+        <v>218.3600006103516</v>
       </c>
       <c r="F242" t="n">
-        <v>134681600</v>
+        <v>105768000</v>
       </c>
       <c r="G242" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="B243" t="n">
-        <v>230.8317036041433</v>
+        <v>221.2400054931641</v>
       </c>
       <c r="C243" t="n">
-        <v>234.4975997614268</v>
+        <v>222</v>
       </c>
       <c r="D243" t="n">
-        <v>229.3733440032785</v>
+        <v>218.1499938964844</v>
       </c>
       <c r="E243" t="n">
-        <v>230.1025238037109</v>
+        <v>218.2899932861328</v>
       </c>
       <c r="F243" t="n">
-        <v>135352400</v>
+        <v>89060100</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="B244" t="n">
-        <v>232.8494477166676</v>
+        <v>211.2400054931641</v>
       </c>
       <c r="C244" t="n">
-        <v>233.4487831783142</v>
+        <v>212.7700042724609</v>
       </c>
       <c r="D244" t="n">
-        <v>224.5986856128386</v>
+        <v>208.9299926757812</v>
       </c>
       <c r="E244" t="n">
-        <v>225.4776916503906</v>
+        <v>210.9600067138672</v>
       </c>
       <c r="F244" t="n">
-        <v>122965600</v>
+        <v>132267200</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46274</v>
+        <v>46280</v>
       </c>
       <c r="B245" t="n">
-        <v>225.0281992525124</v>
+        <v>213.3800048828125</v>
       </c>
       <c r="C245" t="n">
-        <v>225.9271872095504</v>
+        <v>213.9400024414062</v>
       </c>
       <c r="D245" t="n">
-        <v>223.2102414251123</v>
+        <v>211.1600036621094</v>
       </c>
       <c r="E245" t="n">
-        <v>223.4199981689453</v>
+        <v>212.1699981689453</v>
       </c>
       <c r="F245" t="n">
-        <v>82955500</v>
+        <v>88059700</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,25 +6813,25 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46275</v>
+        <v>46281</v>
       </c>
       <c r="B246" t="n">
-        <v>220.5299987792969</v>
+        <v>214.1399993896484</v>
       </c>
       <c r="C246" t="n">
-        <v>220.9900054931641</v>
+        <v>216.7599945068359</v>
       </c>
       <c r="D246" t="n">
-        <v>217.1999969482422</v>
+        <v>212.5</v>
       </c>
       <c r="E246" t="n">
-        <v>218.3600006103516</v>
+        <v>213.8999938964844</v>
       </c>
       <c r="F246" t="n">
-        <v>105768000</v>
+        <v>96563600</v>
       </c>
       <c r="G246" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46276</v>
+        <v>46282</v>
       </c>
       <c r="B247" t="n">
-        <v>221.2400054931641</v>
+        <v>218.3800048828125</v>
       </c>
       <c r="C247" t="n">
-        <v>222</v>
+        <v>219.9100036621094</v>
       </c>
       <c r="D247" t="n">
-        <v>218.1499938964844</v>
+        <v>217.1499938964844</v>
       </c>
       <c r="E247" t="n">
-        <v>218.2899932861328</v>
+        <v>219.3399963378906</v>
       </c>
       <c r="F247" t="n">
-        <v>89060100</v>
+        <v>94191300</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B248" t="n">
-        <v>211.2400054931641</v>
+        <v>219.3500061035156</v>
       </c>
       <c r="C248" t="n">
-        <v>212.7700042724609</v>
+        <v>222.7299957275391</v>
       </c>
       <c r="D248" t="n">
-        <v>208.9299926757812</v>
+        <v>218.0299987792969</v>
       </c>
       <c r="E248" t="n">
-        <v>210.9600067138672</v>
+        <v>222.2700042724609</v>
       </c>
       <c r="F248" t="n">
-        <v>132267200</v>
+        <v>190287400</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B249" t="n">
-        <v>213.3800048828125</v>
+        <v>222.9400024414062</v>
       </c>
       <c r="C249" t="n">
-        <v>213.9400024414062</v>
+        <v>228.5</v>
       </c>
       <c r="D249" t="n">
-        <v>211.1600036621094</v>
+        <v>221.5599975585938</v>
       </c>
       <c r="E249" t="n">
-        <v>212.1699981689453</v>
+        <v>227.3800048828125</v>
       </c>
       <c r="F249" t="n">
-        <v>88059700</v>
+        <v>109806100</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="B250" t="n">
-        <v>214.1399993896484</v>
+        <v>226.8500061035156</v>
       </c>
       <c r="C250" t="n">
-        <v>216.7599945068359</v>
+        <v>229.9799957275391</v>
       </c>
       <c r="D250" t="n">
-        <v>212.5</v>
+        <v>226.5</v>
       </c>
       <c r="E250" t="n">
-        <v>213.8999938964844</v>
+        <v>228.8699951171875</v>
       </c>
       <c r="F250" t="n">
-        <v>96563600</v>
+        <v>95746700</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="B251" t="n">
-        <v>218.3800048828125</v>
+        <v>228.0299987792969</v>
       </c>
       <c r="C251" t="n">
-        <v>219.9100036621094</v>
+        <v>228.9499969482422</v>
       </c>
       <c r="D251" t="n">
-        <v>217.1499938964844</v>
+        <v>224.0200042724609</v>
       </c>
       <c r="E251" t="n">
-        <v>219.3399963378906</v>
+        <v>225.5099945068359</v>
       </c>
       <c r="F251" t="n">
-        <v>94191300</v>
+        <v>89547300</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="B252" t="n">
-        <v>219.3500061035156</v>
+        <v>222.0800018310547</v>
       </c>
       <c r="C252" t="n">
-        <v>222.7299957275391</v>
+        <v>224.9400024414062</v>
       </c>
       <c r="D252" t="n">
-        <v>218.0299987792969</v>
+        <v>221.0899963378906</v>
       </c>
       <c r="E252" t="n">
-        <v>222.2700042724609</v>
+        <v>224.5800018310547</v>
       </c>
       <c r="F252" t="n">
-        <v>189683500</v>
+        <v>77305200</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10884,37 +10884,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>222.27</v>
+        <v>224.58</v>
       </c>
       <c r="D2" t="n">
-        <v>219.34</v>
+        <v>225.51</v>
       </c>
       <c r="E2" t="n">
-        <v>219.36</v>
+        <v>222.116</v>
       </c>
       <c r="F2" t="n">
-        <v>222.73</v>
+        <v>224.9</v>
       </c>
       <c r="G2" t="n">
-        <v>218.04</v>
+        <v>221.0908</v>
       </c>
       <c r="H2" t="n">
-        <v>188794542</v>
+        <v>76420503</v>
       </c>
       <c r="I2" t="n">
-        <v>129288142</v>
+        <v>126051807</v>
       </c>
       <c r="J2" t="n">
-        <v>5367153557504</v>
+        <v>5422933082112</v>
       </c>
       <c r="K2" t="n">
-        <v>27.714462</v>
+        <v>28.5</v>
       </c>
       <c r="L2" t="n">
-        <v>14.173006</v>
+        <v>14.320303</v>
       </c>
       <c r="M2" t="n">
-        <v>8.02</v>
+        <v>7.88</v>
       </c>
       <c r="N2" t="n">
         <v>236.54</v>
@@ -10926,7 +10926,7 @@
         <v>2.217</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="R2" t="n">
         <v>0.63663</v>
@@ -10950,7 +10950,7 @@
         <v>9.483000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>23.438786</v>
+        <v>23.682379</v>
       </c>
       <c r="Z2" t="n">
         <v>1.278</v>
@@ -10962,7 +10962,7 @@
         <v>302970011648</v>
       </c>
       <c r="AC2" t="n">
-        <v>5333097906176</v>
+        <v>5388768903168</v>
       </c>
       <c r="AD2" t="n">
         <v>201266003968</v>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-19 15:21:20</t>
+          <t>2026-09-25 14:29:07</t>
         </is>
       </c>
     </row>

--- a/data/NVDA_data.xlsx
+++ b/data/NVDA_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B2" t="n">
-        <v>174.0629701066951</v>
+        <v>177.7441579191998</v>
       </c>
       <c r="C2" t="n">
-        <v>179.8291540783439</v>
+        <v>179.3403398828169</v>
       </c>
       <c r="D2" t="n">
-        <v>172.7162058826927</v>
+        <v>174.5118962929188</v>
       </c>
       <c r="E2" t="n">
-        <v>177.2653045654297</v>
+        <v>177.7641143798828</v>
       </c>
       <c r="F2" t="n">
-        <v>191586700</v>
+        <v>148573700</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B3" t="n">
-        <v>177.7441426621237</v>
+        <v>179.9987400973632</v>
       </c>
       <c r="C3" t="n">
-        <v>179.3403244887289</v>
+        <v>183.5602146114836</v>
       </c>
       <c r="D3" t="n">
-        <v>174.5118813132914</v>
+        <v>179.8890176259668</v>
       </c>
       <c r="E3" t="n">
-        <v>177.7640991210938</v>
+        <v>181.4153594970703</v>
       </c>
       <c r="F3" t="n">
-        <v>148573700</v>
+        <v>193063500</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B4" t="n">
-        <v>179.9987400973632</v>
+        <v>181.6448041170831</v>
       </c>
       <c r="C4" t="n">
-        <v>183.5602146114836</v>
+        <v>186.9022123120565</v>
       </c>
       <c r="D4" t="n">
-        <v>179.8890176259668</v>
+        <v>181.0462321155116</v>
       </c>
       <c r="E4" t="n">
-        <v>181.4153594970703</v>
+        <v>186.1340484619141</v>
       </c>
       <c r="F4" t="n">
-        <v>193063500</v>
+        <v>236981000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B5" t="n">
-        <v>181.6448190078555</v>
+        <v>184.7972757932568</v>
       </c>
       <c r="C5" t="n">
-        <v>186.9022276338177</v>
+        <v>187.690338609038</v>
       </c>
       <c r="D5" t="n">
-        <v>181.0462469572146</v>
+        <v>183.4604668683245</v>
       </c>
       <c r="E5" t="n">
-        <v>186.1340637207031</v>
+        <v>186.7924957275391</v>
       </c>
       <c r="F5" t="n">
-        <v>236981000</v>
+        <v>173844900</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B6" t="n">
-        <v>184.7972606974542</v>
+        <v>189.146847340247</v>
       </c>
       <c r="C6" t="n">
-        <v>187.6903232769056</v>
+        <v>190.59337868299</v>
       </c>
       <c r="D6" t="n">
-        <v>183.4604518817237</v>
+        <v>187.6105195355423</v>
       </c>
       <c r="E6" t="n">
-        <v>186.79248046875</v>
+        <v>188.4385375976562</v>
       </c>
       <c r="F6" t="n">
-        <v>173844900</v>
+        <v>136805800</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B7" t="n">
-        <v>189.146847340247</v>
+        <v>188.7378247179256</v>
       </c>
       <c r="C7" t="n">
-        <v>190.59337868299</v>
+        <v>189.9050265070322</v>
       </c>
       <c r="D7" t="n">
-        <v>187.6105195355423</v>
+        <v>184.9369333277354</v>
       </c>
       <c r="E7" t="n">
-        <v>188.4385375976562</v>
+        <v>187.1715698242188</v>
       </c>
       <c r="F7" t="n">
-        <v>136805800</v>
+        <v>137596900</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B8" t="n">
-        <v>188.7378247179256</v>
+        <v>185.0566446584491</v>
       </c>
       <c r="C8" t="n">
-        <v>189.9050265070322</v>
+        <v>186.7825055997528</v>
       </c>
       <c r="D8" t="n">
-        <v>184.9369333277354</v>
+        <v>182.8918329061041</v>
       </c>
       <c r="E8" t="n">
-        <v>187.1715698242188</v>
+        <v>185.0965423583984</v>
       </c>
       <c r="F8" t="n">
-        <v>137596900</v>
+        <v>157678100</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B9" t="n">
-        <v>185.0566446584491</v>
+        <v>185.7849061389523</v>
       </c>
       <c r="C9" t="n">
-        <v>186.7825055997528</v>
+        <v>188.6081442671687</v>
       </c>
       <c r="D9" t="n">
-        <v>182.8918329061041</v>
+        <v>183.5602400999903</v>
       </c>
       <c r="E9" t="n">
-        <v>185.0965423583984</v>
+        <v>184.5977478027344</v>
       </c>
       <c r="F9" t="n">
-        <v>157678100</v>
+        <v>140088000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B10" t="n">
-        <v>185.7848907820332</v>
+        <v>186.1240823667868</v>
       </c>
       <c r="C10" t="n">
-        <v>188.6081286768816</v>
+        <v>189.1468390813163</v>
       </c>
       <c r="D10" t="n">
-        <v>183.5602249269612</v>
+        <v>186.094140065894</v>
       </c>
       <c r="E10" t="n">
-        <v>184.5977325439453</v>
+        <v>188.6580047607422</v>
       </c>
       <c r="F10" t="n">
-        <v>140088000</v>
+        <v>130168900</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B11" t="n">
-        <v>186.1240974206304</v>
+        <v>191.7705422839889</v>
       </c>
       <c r="C11" t="n">
-        <v>189.1468543796426</v>
+        <v>194.8332119113436</v>
       </c>
       <c r="D11" t="n">
-        <v>186.0941551173159</v>
+        <v>190.6033405552435</v>
       </c>
       <c r="E11" t="n">
-        <v>188.6580200195312</v>
+        <v>192.1097412109375</v>
       </c>
       <c r="F11" t="n">
-        <v>130168900</v>
+        <v>182997200</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B12" t="n">
-        <v>191.7705575158363</v>
+        <v>193.0474982342752</v>
       </c>
       <c r="C12" t="n">
-        <v>194.833227386451</v>
+        <v>195.1524558626357</v>
       </c>
       <c r="D12" t="n">
-        <v>190.6033556943829</v>
+        <v>181.6148965961679</v>
       </c>
       <c r="E12" t="n">
-        <v>192.1097564697266</v>
+        <v>182.7222442626953</v>
       </c>
       <c r="F12" t="n">
-        <v>182997200</v>
+        <v>268774400</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B13" t="n">
-        <v>193.0474821132437</v>
+        <v>187.5207340107304</v>
       </c>
       <c r="C13" t="n">
-        <v>195.1524395658232</v>
+        <v>189.6556185865847</v>
       </c>
       <c r="D13" t="n">
-        <v>181.6148814298513</v>
+        <v>185.5155435929421</v>
       </c>
       <c r="E13" t="n">
-        <v>182.7222290039062</v>
+        <v>187.8699035644531</v>
       </c>
       <c r="F13" t="n">
-        <v>268774400</v>
+        <v>153482800</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B14" t="n">
-        <v>187.5207644715895</v>
+        <v>184.3283927796865</v>
       </c>
       <c r="C14" t="n">
-        <v>189.6556493942343</v>
+        <v>184.3583198600852</v>
       </c>
       <c r="D14" t="n">
-        <v>185.5155737280782</v>
+        <v>179.2705030798172</v>
       </c>
       <c r="E14" t="n">
-        <v>187.8699340820312</v>
+        <v>179.5997161865234</v>
       </c>
       <c r="F14" t="n">
-        <v>153482800</v>
+        <v>205641400</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B15" t="n">
-        <v>184.3283927796865</v>
+        <v>184.3583147400375</v>
       </c>
       <c r="C15" t="n">
-        <v>184.3583198600852</v>
+        <v>184.4281395182556</v>
       </c>
       <c r="D15" t="n">
-        <v>179.2705030798172</v>
+        <v>176.866254560341</v>
       </c>
       <c r="E15" t="n">
-        <v>179.5997161865234</v>
+        <v>179.4001922607422</v>
       </c>
       <c r="F15" t="n">
-        <v>205641400</v>
+        <v>214450500</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B16" t="n">
-        <v>184.3583147400375</v>
+        <v>181.7944368108431</v>
       </c>
       <c r="C16" t="n">
-        <v>184.4281395182556</v>
+        <v>182.8419301869027</v>
       </c>
       <c r="D16" t="n">
-        <v>176.866254560341</v>
+        <v>179.3403251298876</v>
       </c>
       <c r="E16" t="n">
-        <v>179.4001922607422</v>
+        <v>181.3754425048828</v>
       </c>
       <c r="F16" t="n">
-        <v>214450500</v>
+        <v>179723300</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B17" t="n">
-        <v>181.7944521048813</v>
+        <v>179.7493315718189</v>
       </c>
       <c r="C17" t="n">
-        <v>182.8419455690647</v>
+        <v>183.6599754947305</v>
       </c>
       <c r="D17" t="n">
-        <v>179.3403402174659</v>
+        <v>179.3203666523256</v>
       </c>
       <c r="E17" t="n">
-        <v>181.3754577636719</v>
+        <v>182.7820739746094</v>
       </c>
       <c r="F17" t="n">
-        <v>179723300</v>
+        <v>173135200</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B18" t="n">
-        <v>179.7493615830456</v>
+        <v>182.6923102950553</v>
       </c>
       <c r="C18" t="n">
-        <v>183.6600061588844</v>
+        <v>184.7573549226016</v>
       </c>
       <c r="D18" t="n">
-        <v>179.3203965919317</v>
+        <v>181.2956472677441</v>
       </c>
       <c r="E18" t="n">
-        <v>182.7821044921875</v>
+        <v>182.2034759521484</v>
       </c>
       <c r="F18" t="n">
-        <v>173135200</v>
+        <v>128544700</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B19" t="n">
-        <v>182.6923102950553</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="C19" t="n">
-        <v>184.7573549226016</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="D19" t="n">
-        <v>181.2956472677441</v>
+        <v>179.3702701372806</v>
       </c>
       <c r="E19" t="n">
-        <v>182.2034759521484</v>
+        <v>180.7270202636719</v>
       </c>
       <c r="F19" t="n">
-        <v>128544700</v>
+        <v>124240200</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B20" t="n">
-        <v>182.3531141136141</v>
+        <v>180.7070662621498</v>
       </c>
       <c r="C20" t="n">
-        <v>182.3531141136141</v>
+        <v>183.0015721983185</v>
       </c>
       <c r="D20" t="n">
-        <v>179.3702701372806</v>
+        <v>176.3375297972393</v>
       </c>
       <c r="E20" t="n">
-        <v>180.7270202636719</v>
+        <v>179.84912109375</v>
       </c>
       <c r="F20" t="n">
-        <v>124240200</v>
+        <v>162249600</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B21" t="n">
-        <v>180.7070662621498</v>
+        <v>179.988777912505</v>
       </c>
       <c r="C21" t="n">
-        <v>183.0015721983185</v>
+        <v>182.5925403832715</v>
       </c>
       <c r="D21" t="n">
-        <v>176.3375297972393</v>
+        <v>179.3602787988416</v>
       </c>
       <c r="E21" t="n">
-        <v>179.84912109375</v>
+        <v>181.7246246337891</v>
       </c>
       <c r="F21" t="n">
-        <v>162249600</v>
+        <v>111363700</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B22" t="n">
-        <v>179.988762799469</v>
+        <v>183.400590081168</v>
       </c>
       <c r="C22" t="n">
-        <v>182.5925250516066</v>
+        <v>187.0219186862977</v>
       </c>
       <c r="D22" t="n">
-        <v>179.3602637385785</v>
+        <v>183.0614063875393</v>
       </c>
       <c r="E22" t="n">
-        <v>181.724609375</v>
+        <v>185.8148040771484</v>
       </c>
       <c r="F22" t="n">
-        <v>111363700</v>
+        <v>131296700</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B23" t="n">
-        <v>183.4006051417061</v>
+        <v>189.5359033209746</v>
       </c>
       <c r="C23" t="n">
-        <v>187.0219340442129</v>
+        <v>191.541093665248</v>
       </c>
       <c r="D23" t="n">
-        <v>183.0614214202242</v>
+        <v>187.979619148197</v>
       </c>
       <c r="E23" t="n">
-        <v>185.8148193359375</v>
+        <v>191.0323181152344</v>
       </c>
       <c r="F23" t="n">
-        <v>131296700</v>
+        <v>153452700</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B24" t="n">
-        <v>189.5359184602369</v>
+        <v>192.588592118433</v>
       </c>
       <c r="C24" t="n">
-        <v>191.5411089646758</v>
+        <v>202.6644428640734</v>
       </c>
       <c r="D24" t="n">
-        <v>187.9796341631504</v>
+        <v>191.4513174538508</v>
       </c>
       <c r="E24" t="n">
-        <v>191.0323333740234</v>
+        <v>200.5495147705078</v>
       </c>
       <c r="F24" t="n">
-        <v>153452700</v>
+        <v>297986200</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B25" t="n">
-        <v>192.5886067715161</v>
+        <v>207.482921843539</v>
       </c>
       <c r="C25" t="n">
-        <v>202.6644582837766</v>
+        <v>211.6828666070652</v>
       </c>
       <c r="D25" t="n">
-        <v>191.4513320204045</v>
+        <v>204.2905729140704</v>
       </c>
       <c r="E25" t="n">
-        <v>200.5495300292969</v>
+        <v>206.545166015625</v>
       </c>
       <c r="F25" t="n">
-        <v>297986200</v>
+        <v>308829600</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B26" t="n">
-        <v>207.482891187405</v>
+        <v>204.6596680014167</v>
       </c>
       <c r="C26" t="n">
-        <v>211.6828353303786</v>
+        <v>205.6672637579894</v>
       </c>
       <c r="D26" t="n">
-        <v>204.2905427296142</v>
+        <v>200.9286166610889</v>
       </c>
       <c r="E26" t="n">
-        <v>206.5451354980469</v>
+        <v>202.4050750732422</v>
       </c>
       <c r="F26" t="n">
-        <v>308829600</v>
+        <v>178864400</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B27" t="n">
-        <v>204.6596680014167</v>
+        <v>205.9565693232556</v>
       </c>
       <c r="C27" t="n">
-        <v>205.6672637579894</v>
+        <v>207.4729406961805</v>
       </c>
       <c r="D27" t="n">
-        <v>200.9286166610889</v>
+        <v>201.5870481318289</v>
       </c>
       <c r="E27" t="n">
-        <v>202.4050750732422</v>
+        <v>202.0060424804688</v>
       </c>
       <c r="F27" t="n">
-        <v>178864400</v>
+        <v>179802200</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B28" t="n">
-        <v>205.9565537660584</v>
+        <v>207.5826573279554</v>
       </c>
       <c r="C28" t="n">
-        <v>207.4729250244422</v>
+        <v>210.834859926228</v>
       </c>
       <c r="D28" t="n">
-        <v>201.5870329046891</v>
+        <v>205.068676268978</v>
       </c>
       <c r="E28" t="n">
-        <v>202.0060272216797</v>
+        <v>206.3855285644531</v>
       </c>
       <c r="F28" t="n">
-        <v>179802200</v>
+        <v>180267300</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B29" t="n">
-        <v>207.5826880225491</v>
+        <v>202.5147991590425</v>
       </c>
       <c r="C29" t="n">
-        <v>210.8348911017148</v>
+        <v>203.4824819294599</v>
       </c>
       <c r="D29" t="n">
-        <v>205.0687065918373</v>
+        <v>197.4569099225941</v>
       </c>
       <c r="E29" t="n">
-        <v>206.3855590820312</v>
+        <v>198.2151031494141</v>
       </c>
       <c r="F29" t="n">
-        <v>180267300</v>
+        <v>188919300</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B30" t="n">
-        <v>202.5148147488263</v>
+        <v>198.2949431289972</v>
       </c>
       <c r="C30" t="n">
-        <v>203.4824975937368</v>
+        <v>202.4350185226721</v>
       </c>
       <c r="D30" t="n">
-        <v>197.4569251230167</v>
+        <v>194.1847795950905</v>
       </c>
       <c r="E30" t="n">
-        <v>198.2151184082031</v>
+        <v>194.7434539794922</v>
       </c>
       <c r="F30" t="n">
-        <v>188919300</v>
+        <v>171350300</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B31" t="n">
-        <v>198.2949275919373</v>
+        <v>195.9505570232203</v>
       </c>
       <c r="C31" t="n">
-        <v>202.4350026612236</v>
+        <v>197.1476859949454</v>
       </c>
       <c r="D31" t="n">
-        <v>194.1847643800754</v>
+        <v>185.934559185592</v>
       </c>
       <c r="E31" t="n">
-        <v>194.7434387207031</v>
+        <v>187.6304931640625</v>
       </c>
       <c r="F31" t="n">
-        <v>171350300</v>
+        <v>223029800</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B32" t="n">
-        <v>195.9505251524069</v>
+        <v>184.4580698535366</v>
       </c>
       <c r="C32" t="n">
-        <v>197.1476539294223</v>
+        <v>187.8699092076593</v>
       </c>
       <c r="D32" t="n">
-        <v>185.9345289438528</v>
+        <v>178.4823961188316</v>
       </c>
       <c r="E32" t="n">
-        <v>187.6304626464844</v>
+        <v>187.7003021240234</v>
       </c>
       <c r="F32" t="n">
-        <v>223029800</v>
+        <v>264942300</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B33" t="n">
-        <v>184.4580548583195</v>
+        <v>194.6436788693004</v>
       </c>
       <c r="C33" t="n">
-        <v>187.8698939350823</v>
+        <v>199.4621367771523</v>
       </c>
       <c r="D33" t="n">
-        <v>178.4823816093971</v>
+        <v>193.3268264223904</v>
       </c>
       <c r="E33" t="n">
-        <v>187.7002868652344</v>
+        <v>198.5742645263672</v>
       </c>
       <c r="F33" t="n">
-        <v>264942300</v>
+        <v>198897100</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B34" t="n">
-        <v>194.6436788693004</v>
+        <v>194.6935535589016</v>
       </c>
       <c r="C34" t="n">
-        <v>199.4621367771523</v>
+        <v>194.9529266552934</v>
       </c>
       <c r="D34" t="n">
-        <v>193.3268264223904</v>
+        <v>190.8427786999811</v>
       </c>
       <c r="E34" t="n">
-        <v>198.5742645263672</v>
+        <v>192.6983337402344</v>
       </c>
       <c r="F34" t="n">
-        <v>198897100</v>
+        <v>176483300</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B35" t="n">
-        <v>194.6935535589016</v>
+        <v>195.2522164876445</v>
       </c>
       <c r="C35" t="n">
-        <v>194.9529266552934</v>
+        <v>195.4218083488666</v>
       </c>
       <c r="D35" t="n">
-        <v>190.8427786999811</v>
+        <v>190.673190567689</v>
       </c>
       <c r="E35" t="n">
-        <v>192.6983337402344</v>
+        <v>193.3368072509766</v>
       </c>
       <c r="F35" t="n">
-        <v>176483300</v>
+        <v>154935300</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B36" t="n">
-        <v>195.2522164876445</v>
+        <v>190.5933791327836</v>
       </c>
       <c r="C36" t="n">
-        <v>195.4218083488666</v>
+        <v>190.9824463944715</v>
       </c>
       <c r="D36" t="n">
-        <v>190.673190567689</v>
+        <v>183.4105907203728</v>
       </c>
       <c r="E36" t="n">
-        <v>193.3368072509766</v>
+        <v>186.4133911132812</v>
       </c>
       <c r="F36" t="n">
-        <v>154935300</v>
+        <v>207423100</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B37" t="n">
-        <v>190.5933791327836</v>
+        <v>182.4229435613052</v>
       </c>
       <c r="C37" t="n">
-        <v>190.9824463944715</v>
+        <v>190.553458007553</v>
       </c>
       <c r="D37" t="n">
-        <v>183.4105907203728</v>
+        <v>180.1483942490048</v>
       </c>
       <c r="E37" t="n">
-        <v>186.4133911132812</v>
+        <v>189.7154693603516</v>
       </c>
       <c r="F37" t="n">
-        <v>207423100</v>
+        <v>186591900</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B38" t="n">
-        <v>182.4229435613052</v>
+        <v>185.5255230789849</v>
       </c>
       <c r="C38" t="n">
-        <v>190.553458007553</v>
+        <v>188.5482800008962</v>
       </c>
       <c r="D38" t="n">
-        <v>180.1483942490048</v>
+        <v>183.8794727552066</v>
       </c>
       <c r="E38" t="n">
-        <v>189.7154693603516</v>
+        <v>186.1540222167969</v>
       </c>
       <c r="F38" t="n">
-        <v>186591900</v>
+        <v>173628900</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B39" t="n">
-        <v>185.5255230789849</v>
+        <v>182.941705155915</v>
       </c>
       <c r="C39" t="n">
-        <v>188.5482800008962</v>
+        <v>184.3583093626339</v>
       </c>
       <c r="D39" t="n">
-        <v>183.8794727552066</v>
+        <v>179.2206093334711</v>
       </c>
       <c r="E39" t="n">
-        <v>186.1540222167969</v>
+        <v>180.9265289306641</v>
       </c>
       <c r="F39" t="n">
-        <v>173628900</v>
+        <v>213598900</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B40" t="n">
-        <v>182.9417205846578</v>
+        <v>184.3483273978252</v>
       </c>
       <c r="C40" t="n">
-        <v>184.3583249108488</v>
+        <v>187.4109971087465</v>
       </c>
       <c r="D40" t="n">
-        <v>179.2206244483882</v>
+        <v>182.3930205111681</v>
       </c>
       <c r="E40" t="n">
-        <v>180.9265441894531</v>
+        <v>186.0742034912109</v>
       </c>
       <c r="F40" t="n">
-        <v>213598900</v>
+        <v>247246400</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B41" t="n">
-        <v>184.3483273978252</v>
+        <v>195.4816571057099</v>
       </c>
       <c r="C41" t="n">
-        <v>187.4109971087465</v>
+        <v>195.5315406452363</v>
       </c>
       <c r="D41" t="n">
-        <v>182.3930205111681</v>
+        <v>179.4201468289569</v>
       </c>
       <c r="E41" t="n">
-        <v>186.0742034912109</v>
+        <v>180.208251953125</v>
       </c>
       <c r="F41" t="n">
-        <v>247246400</v>
+        <v>343504800</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B42" t="n">
-        <v>195.4816571057099</v>
+        <v>180.8068289121023</v>
       </c>
       <c r="C42" t="n">
-        <v>195.5315406452363</v>
+        <v>184.1188859589464</v>
       </c>
       <c r="D42" t="n">
-        <v>179.4201468289569</v>
+        <v>172.5166776199441</v>
       </c>
       <c r="E42" t="n">
-        <v>180.208251953125</v>
+        <v>178.4524688720703</v>
       </c>
       <c r="F42" t="n">
-        <v>343504800</v>
+        <v>346926200</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B43" t="n">
-        <v>180.8068289121023</v>
+        <v>179.0610093294625</v>
       </c>
       <c r="C43" t="n">
-        <v>184.1188859589464</v>
+        <v>183.0614196131816</v>
       </c>
       <c r="D43" t="n">
-        <v>172.5166776199441</v>
+        <v>176.0581937395723</v>
       </c>
       <c r="E43" t="n">
-        <v>178.4524688720703</v>
+        <v>182.1136932373047</v>
       </c>
       <c r="F43" t="n">
-        <v>346926200</v>
+        <v>256618300</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B44" t="n">
-        <v>179.0610243324759</v>
+        <v>174.4919407266003</v>
       </c>
       <c r="C44" t="n">
-        <v>183.0614349513779</v>
+        <v>177.7341727058355</v>
       </c>
       <c r="D44" t="n">
-        <v>176.0582084909882</v>
+        <v>169.1447513765687</v>
       </c>
       <c r="E44" t="n">
-        <v>182.1137084960938</v>
+        <v>177.3949890136719</v>
       </c>
       <c r="F44" t="n">
-        <v>256618300</v>
+        <v>320600300</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B45" t="n">
-        <v>174.4919707447618</v>
+        <v>181.1958985688627</v>
       </c>
       <c r="C45" t="n">
-        <v>177.734203281764</v>
+        <v>182.4728380763597</v>
       </c>
       <c r="D45" t="n">
-        <v>169.1447804748437</v>
+        <v>177.8140014756398</v>
       </c>
       <c r="E45" t="n">
-        <v>177.39501953125</v>
+        <v>179.8291625976562</v>
       </c>
       <c r="F45" t="n">
-        <v>320600300</v>
+        <v>183852000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B46" t="n">
-        <v>181.1958831941039</v>
+        <v>178.5821404669205</v>
       </c>
       <c r="C46" t="n">
-        <v>182.4728225932506</v>
+        <v>178.8614700176124</v>
       </c>
       <c r="D46" t="n">
-        <v>177.8139863878403</v>
+        <v>176.0781451295325</v>
       </c>
       <c r="E46" t="n">
-        <v>179.8291473388672</v>
+        <v>176.5769500732422</v>
       </c>
       <c r="F46" t="n">
-        <v>183852000</v>
+        <v>121332800</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B47" t="n">
-        <v>178.5821558989869</v>
+        <v>174.3423041351479</v>
       </c>
       <c r="C47" t="n">
-        <v>178.8614854738169</v>
+        <v>179.8690716163194</v>
       </c>
       <c r="D47" t="n">
-        <v>176.0781603452176</v>
+        <v>173.2648835948944</v>
       </c>
       <c r="E47" t="n">
-        <v>176.5769653320312</v>
+        <v>179.4899749755859</v>
       </c>
       <c r="F47" t="n">
-        <v>121332800</v>
+        <v>188131000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B48" t="n">
-        <v>174.3422893139723</v>
+        <v>181.3255769560617</v>
       </c>
       <c r="C48" t="n">
-        <v>179.8690563253026</v>
+        <v>185.2162648499111</v>
       </c>
       <c r="D48" t="n">
-        <v>173.2648688653124</v>
+        <v>179.569788944198</v>
       </c>
       <c r="E48" t="n">
-        <v>179.4899597167969</v>
+        <v>181.0263061523438</v>
       </c>
       <c r="F48" t="n">
-        <v>188131000</v>
+        <v>182632200</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B49" t="n">
-        <v>181.3255922400764</v>
+        <v>180.6472109015755</v>
       </c>
       <c r="C49" t="n">
-        <v>185.2162804618737</v>
+        <v>182.0139316568558</v>
       </c>
       <c r="D49" t="n">
-        <v>179.5698040802165</v>
+        <v>178.681918089591</v>
       </c>
       <c r="E49" t="n">
-        <v>181.0263214111328</v>
+        <v>179.1607666015625</v>
       </c>
       <c r="F49" t="n">
-        <v>182632200</v>
+        <v>165138000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,25 +1717,25 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B50" t="n">
-        <v>180.6471955161887</v>
+        <v>181.1960032737075</v>
       </c>
       <c r="C50" t="n">
-        <v>182.013916155068</v>
+        <v>184.0892423581687</v>
       </c>
       <c r="D50" t="n">
-        <v>178.6819028715845</v>
+        <v>179.5398901129937</v>
       </c>
       <c r="E50" t="n">
-        <v>179.1607513427734</v>
+        <v>182.951904296875</v>
       </c>
       <c r="F50" t="n">
-        <v>165138000</v>
+        <v>167364900</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1743,25 +1743,25 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B51" t="n">
-        <v>181.1959881613664</v>
+        <v>183.4607020047171</v>
       </c>
       <c r="C51" t="n">
-        <v>184.089227004522</v>
+        <v>184.2289086763207</v>
       </c>
       <c r="D51" t="n">
-        <v>179.5398751387779</v>
+        <v>180.4876631773748</v>
       </c>
       <c r="E51" t="n">
-        <v>182.9518890380859</v>
+        <v>181.9841613769531</v>
       </c>
       <c r="F51" t="n">
-        <v>167364900</v>
+        <v>143971100</v>
       </c>
       <c r="G51" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B52" t="n">
-        <v>183.4606866221248</v>
+        <v>182.213626289633</v>
       </c>
       <c r="C52" t="n">
-        <v>184.2288932293168</v>
+        <v>187.5611139779305</v>
       </c>
       <c r="D52" t="n">
-        <v>180.4876480440623</v>
+        <v>181.9741810893209</v>
       </c>
       <c r="E52" t="n">
-        <v>181.9841461181641</v>
+        <v>185.1168365478516</v>
       </c>
       <c r="F52" t="n">
-        <v>143971100</v>
+        <v>204378100</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B53" t="n">
-        <v>182.2136112701494</v>
+        <v>185.12679644575</v>
       </c>
       <c r="C53" t="n">
-        <v>187.5610985176648</v>
+        <v>185.2864265695677</v>
       </c>
       <c r="D53" t="n">
-        <v>181.9741660895743</v>
+        <v>182.8920356049676</v>
       </c>
       <c r="E53" t="n">
-        <v>185.1168212890625</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="F53" t="n">
-        <v>204378100</v>
+        <v>144719700</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B54" t="n">
-        <v>185.12679644575</v>
+        <v>184.5381918075859</v>
       </c>
       <c r="C54" t="n">
-        <v>185.2864265695677</v>
+        <v>185.0469957406681</v>
       </c>
       <c r="D54" t="n">
-        <v>182.8920356049676</v>
+        <v>181.6150239281505</v>
       </c>
       <c r="E54" t="n">
-        <v>184.5381774902344</v>
+        <v>183.3509674072266</v>
       </c>
       <c r="F54" t="n">
-        <v>144719700</v>
+        <v>162785400</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B55" t="n">
-        <v>184.5381918075859</v>
+        <v>179.8591224369562</v>
       </c>
       <c r="C55" t="n">
-        <v>185.0469957406681</v>
+        <v>180.8967030087509</v>
       </c>
       <c r="D55" t="n">
-        <v>181.6150239281505</v>
+        <v>176.2076633109278</v>
       </c>
       <c r="E55" t="n">
-        <v>183.3509674072266</v>
+        <v>180.5075988769531</v>
       </c>
       <c r="F55" t="n">
-        <v>162785400</v>
+        <v>182136600</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B56" t="n">
-        <v>179.8591224369562</v>
+        <v>180.6871831157045</v>
       </c>
       <c r="C56" t="n">
-        <v>180.8967030087509</v>
+        <v>182.3931976659576</v>
       </c>
       <c r="D56" t="n">
-        <v>176.2076633109278</v>
+        <v>174.2123291208211</v>
       </c>
       <c r="E56" t="n">
-        <v>180.5075988769531</v>
+        <v>174.6114044189453</v>
       </c>
       <c r="F56" t="n">
-        <v>182136600</v>
+        <v>204274900</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B57" t="n">
-        <v>180.6871989054384</v>
+        <v>177.5245903328353</v>
       </c>
       <c r="C57" t="n">
-        <v>182.3932136047752</v>
+        <v>178.0034654802094</v>
       </c>
       <c r="D57" t="n">
-        <v>174.2123443447362</v>
+        <v>174.6213802569945</v>
       </c>
       <c r="E57" t="n">
-        <v>174.6114196777344</v>
+        <v>175.8784332275391</v>
       </c>
       <c r="F57" t="n">
-        <v>204274900</v>
+        <v>164775600</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B58" t="n">
-        <v>177.5245903328353</v>
+        <v>175.8485164107673</v>
       </c>
       <c r="C58" t="n">
-        <v>178.0034654802094</v>
+        <v>178.0733214473424</v>
       </c>
       <c r="D58" t="n">
-        <v>174.6213802569945</v>
+        <v>174.4916907151964</v>
       </c>
       <c r="E58" t="n">
-        <v>175.8784332275391</v>
+        <v>177.3051147460938</v>
       </c>
       <c r="F58" t="n">
-        <v>164775600</v>
+        <v>148588100</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B59" t="n">
-        <v>175.8485012773324</v>
+        <v>175.6888968536916</v>
       </c>
       <c r="C59" t="n">
-        <v>178.0733061224419</v>
+        <v>175.7188256001934</v>
       </c>
       <c r="D59" t="n">
-        <v>174.4916756985292</v>
+        <v>169.9124052081842</v>
       </c>
       <c r="E59" t="n">
-        <v>177.3050994873047</v>
+        <v>170.5409393310547</v>
       </c>
       <c r="F59" t="n">
-        <v>148588100</v>
+        <v>222775500</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B60" t="n">
-        <v>175.6888811343</v>
+        <v>174.1225483861358</v>
       </c>
       <c r="C60" t="n">
-        <v>175.7188098781239</v>
+        <v>175.7387615308714</v>
       </c>
       <c r="D60" t="n">
-        <v>169.9123900056319</v>
+        <v>171.4188835631069</v>
       </c>
       <c r="E60" t="n">
-        <v>170.5409240722656</v>
+        <v>173.7334594726562</v>
       </c>
       <c r="F60" t="n">
-        <v>222775500</v>
+        <v>176096000</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B61" t="n">
-        <v>174.1225483861358</v>
+        <v>176.2575523358494</v>
       </c>
       <c r="C61" t="n">
-        <v>175.7387615308714</v>
+        <v>181.0263919449467</v>
       </c>
       <c r="D61" t="n">
-        <v>171.4188835631069</v>
+        <v>175.9283209122297</v>
       </c>
       <c r="E61" t="n">
-        <v>173.7334594726562</v>
+        <v>180.5674743652344</v>
       </c>
       <c r="F61" t="n">
-        <v>176096000</v>
+        <v>324925900</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B62" t="n">
-        <v>176.2575672304301</v>
+        <v>183.4906282252173</v>
       </c>
       <c r="C62" t="n">
-        <v>181.0264072425164</v>
+        <v>183.7300734141942</v>
       </c>
       <c r="D62" t="n">
-        <v>175.9283357789888</v>
+        <v>181.9243013805983</v>
       </c>
       <c r="E62" t="n">
-        <v>180.5674896240234</v>
+        <v>183.2611694335938</v>
       </c>
       <c r="F62" t="n">
-        <v>324925900</v>
+        <v>129064400</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B63" t="n">
-        <v>183.4906282252173</v>
+        <v>182.5428423541149</v>
       </c>
       <c r="C63" t="n">
-        <v>183.7300734141942</v>
+        <v>188.8879950077845</v>
       </c>
       <c r="D63" t="n">
-        <v>181.9243013805983</v>
+        <v>182.4729984678863</v>
       </c>
       <c r="E63" t="n">
-        <v>183.2611694335938</v>
+        <v>188.7682800292969</v>
       </c>
       <c r="F63" t="n">
-        <v>129064400</v>
+        <v>174873600</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B64" t="n">
-        <v>182.5428571096804</v>
+        <v>187.5012437217294</v>
       </c>
       <c r="C64" t="n">
-        <v>188.8880102762506</v>
+        <v>188.4689804086018</v>
       </c>
       <c r="D64" t="n">
-        <v>182.4730132178061</v>
+        <v>186.154389299292</v>
       </c>
       <c r="E64" t="n">
-        <v>188.7682952880859</v>
+        <v>188.169677734375</v>
       </c>
       <c r="F64" t="n">
-        <v>174873600</v>
+        <v>65528500</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B65" t="n">
-        <v>187.5012437217294</v>
+        <v>189.4766285187414</v>
       </c>
       <c r="C65" t="n">
-        <v>188.4689804086018</v>
+        <v>192.240166195598</v>
       </c>
       <c r="D65" t="n">
-        <v>186.154389299292</v>
+        <v>187.5611125998212</v>
       </c>
       <c r="E65" t="n">
-        <v>188.169677734375</v>
+        <v>190.085205078125</v>
       </c>
       <c r="F65" t="n">
-        <v>65528500</v>
+        <v>139740300</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B66" t="n">
-        <v>189.4766285187414</v>
+        <v>187.2717899684254</v>
       </c>
       <c r="C66" t="n">
-        <v>192.240166195598</v>
+        <v>188.3193265216257</v>
       </c>
       <c r="D66" t="n">
-        <v>187.5611125998212</v>
+        <v>185.4759890979627</v>
       </c>
       <c r="E66" t="n">
-        <v>190.085205078125</v>
+        <v>187.7805938720703</v>
       </c>
       <c r="F66" t="n">
-        <v>139740300</v>
+        <v>120006100</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B67" t="n">
-        <v>187.2717899684254</v>
+        <v>187.8005508490403</v>
       </c>
       <c r="C67" t="n">
-        <v>188.3193265216257</v>
+        <v>188.5487999407664</v>
       </c>
       <c r="D67" t="n">
-        <v>185.4759890979627</v>
+        <v>186.4935963146986</v>
       </c>
       <c r="E67" t="n">
-        <v>187.7805938720703</v>
+        <v>187.1021728515625</v>
       </c>
       <c r="F67" t="n">
-        <v>120006100</v>
+        <v>97687300</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B68" t="n">
-        <v>187.8005508490403</v>
+        <v>189.127461449755</v>
       </c>
       <c r="C68" t="n">
-        <v>188.5487999407664</v>
+        <v>190.1151405796458</v>
       </c>
       <c r="D68" t="n">
-        <v>186.4935963146986</v>
+        <v>186.0546497967401</v>
       </c>
       <c r="E68" t="n">
-        <v>187.1021728515625</v>
+        <v>186.0646209716797</v>
       </c>
       <c r="F68" t="n">
-        <v>97687300</v>
+        <v>120100500</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B69" t="n">
-        <v>189.1274459397885</v>
+        <v>189.3968130035911</v>
       </c>
       <c r="C69" t="n">
-        <v>190.1151249886817</v>
+        <v>192.4795957147097</v>
       </c>
       <c r="D69" t="n">
-        <v>186.0546345387688</v>
+        <v>187.8204997023152</v>
       </c>
       <c r="E69" t="n">
-        <v>186.0646057128906</v>
+        <v>188.4091339111328</v>
       </c>
       <c r="F69" t="n">
-        <v>120100500</v>
+        <v>148240500</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B70" t="n">
-        <v>189.3968130035911</v>
+        <v>191.3123337767646</v>
       </c>
       <c r="C70" t="n">
-        <v>192.4795957147097</v>
+        <v>193.1779786425506</v>
       </c>
       <c r="D70" t="n">
-        <v>187.8204997023152</v>
+        <v>185.7154296257417</v>
       </c>
       <c r="E70" t="n">
-        <v>188.4091339111328</v>
+        <v>187.6808319091797</v>
       </c>
       <c r="F70" t="n">
-        <v>148240500</v>
+        <v>183529700</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B71" t="n">
-        <v>191.3123182227279</v>
+        <v>190.0752284670132</v>
       </c>
       <c r="C71" t="n">
-        <v>193.1779629368336</v>
+        <v>191.7213703933745</v>
       </c>
       <c r="D71" t="n">
-        <v>185.7154145267434</v>
+        <v>186.3838692947835</v>
       </c>
       <c r="E71" t="n">
-        <v>187.6808166503906</v>
+        <v>186.8028869628906</v>
       </c>
       <c r="F71" t="n">
-        <v>183529700</v>
+        <v>176862600</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B72" t="n">
-        <v>190.0752284670132</v>
+        <v>188.1297854095839</v>
       </c>
       <c r="C72" t="n">
-        <v>191.7213703933745</v>
+        <v>190.9232365533545</v>
       </c>
       <c r="D72" t="n">
-        <v>186.3838692947835</v>
+        <v>186.1244680675316</v>
       </c>
       <c r="E72" t="n">
-        <v>186.8028869628906</v>
+        <v>188.6685180664062</v>
       </c>
       <c r="F72" t="n">
-        <v>176862600</v>
+        <v>153543200</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B73" t="n">
-        <v>188.1297854095839</v>
+        <v>188.6685228499072</v>
       </c>
       <c r="C73" t="n">
-        <v>190.9232365533545</v>
+        <v>189.1074981045344</v>
       </c>
       <c r="D73" t="n">
-        <v>186.1244680675316</v>
+        <v>183.2811352524241</v>
       </c>
       <c r="E73" t="n">
-        <v>188.6685180664062</v>
+        <v>184.6080169677734</v>
       </c>
       <c r="F73" t="n">
-        <v>153543200</v>
+        <v>172457000</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B74" t="n">
-        <v>188.6685228499072</v>
+        <v>184.6479238968445</v>
       </c>
       <c r="C74" t="n">
-        <v>189.1074981045344</v>
+        <v>185.9049768874807</v>
       </c>
       <c r="D74" t="n">
-        <v>183.2811352524241</v>
+        <v>183.2412119543349</v>
       </c>
       <c r="E74" t="n">
-        <v>184.6080169677734</v>
+        <v>184.4284362792969</v>
       </c>
       <c r="F74" t="n">
-        <v>172457000</v>
+        <v>131327500</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B75" t="n">
-        <v>184.6479238968445</v>
+        <v>182.7922691735387</v>
       </c>
       <c r="C75" t="n">
-        <v>185.9049768874807</v>
+        <v>186.6831584288149</v>
       </c>
       <c r="D75" t="n">
-        <v>183.2412119543349</v>
+        <v>182.5927391235801</v>
       </c>
       <c r="E75" t="n">
-        <v>184.4284362792969</v>
+        <v>184.5082550048828</v>
       </c>
       <c r="F75" t="n">
-        <v>131327500</v>
+        <v>137968500</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B76" t="n">
-        <v>182.7922691735387</v>
+        <v>184.5681140987238</v>
       </c>
       <c r="C76" t="n">
-        <v>186.6831584288149</v>
+        <v>187.6708543554723</v>
       </c>
       <c r="D76" t="n">
-        <v>182.5927391235801</v>
+        <v>182.9718432388734</v>
       </c>
       <c r="E76" t="n">
-        <v>184.5082550048828</v>
+        <v>185.376220703125</v>
       </c>
       <c r="F76" t="n">
-        <v>137968500</v>
+        <v>160128900</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B77" t="n">
-        <v>184.5680989064521</v>
+        <v>183.8896858985649</v>
       </c>
       <c r="C77" t="n">
-        <v>187.6708389078061</v>
+        <v>184.0293584396101</v>
       </c>
       <c r="D77" t="n">
-        <v>182.9718281779948</v>
+        <v>180.3778995796448</v>
       </c>
       <c r="E77" t="n">
-        <v>185.3762054443359</v>
+        <v>182.7124328613281</v>
       </c>
       <c r="F77" t="n">
-        <v>160128900</v>
+        <v>159586100</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B78" t="n">
-        <v>183.889716612774</v>
+        <v>186.0646079796491</v>
       </c>
       <c r="C78" t="n">
-        <v>184.029389177148</v>
+        <v>189.2571344016907</v>
       </c>
       <c r="D78" t="n">
-        <v>180.3779297072971</v>
+        <v>185.895006678512</v>
       </c>
       <c r="E78" t="n">
-        <v>182.7124633789062</v>
+        <v>186.6133270263672</v>
       </c>
       <c r="F78" t="n">
-        <v>159586100</v>
+        <v>206188600</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B79" t="n">
-        <v>186.0646079796491</v>
+        <v>188.6385795892923</v>
       </c>
       <c r="C79" t="n">
-        <v>189.2571344016907</v>
+        <v>189.99540517049</v>
       </c>
       <c r="D79" t="n">
-        <v>185.895006678512</v>
+        <v>185.6455833269296</v>
       </c>
       <c r="E79" t="n">
-        <v>186.6133270263672</v>
+        <v>185.7952270507812</v>
       </c>
       <c r="F79" t="n">
-        <v>206188600</v>
+        <v>187967200</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B80" t="n">
-        <v>188.6385950815971</v>
+        <v>181.4753266272146</v>
       </c>
       <c r="C80" t="n">
-        <v>189.9954207742267</v>
+        <v>181.9542169705431</v>
       </c>
       <c r="D80" t="n">
-        <v>185.6455985734289</v>
+        <v>177.1953488429791</v>
       </c>
       <c r="E80" t="n">
-        <v>185.7952423095703</v>
+        <v>177.6542816162109</v>
       </c>
       <c r="F80" t="n">
-        <v>187967200</v>
+        <v>223345300</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B81" t="n">
-        <v>181.4753578011745</v>
+        <v>178.6320081827799</v>
       </c>
       <c r="C81" t="n">
-        <v>181.9542482267672</v>
+        <v>184.9472325313386</v>
       </c>
       <c r="D81" t="n">
-        <v>177.1953792817215</v>
+        <v>177.9835164834521</v>
       </c>
       <c r="E81" t="n">
-        <v>177.6543121337891</v>
+        <v>182.8920440673828</v>
       </c>
       <c r="F81" t="n">
-        <v>223345300</v>
+        <v>200381000</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B82" t="n">
-        <v>178.6319932794081</v>
+        <v>184.3186915464293</v>
       </c>
       <c r="C82" t="n">
-        <v>184.947217101084</v>
+        <v>185.7353746560278</v>
       </c>
       <c r="D82" t="n">
-        <v>177.9835016341843</v>
+        <v>183.5005985718231</v>
       </c>
       <c r="E82" t="n">
-        <v>182.8920288085938</v>
+        <v>184.4084777832031</v>
       </c>
       <c r="F82" t="n">
-        <v>200381000</v>
+        <v>139636600</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B83" t="n">
-        <v>184.3186915464293</v>
+        <v>187.0622712594319</v>
       </c>
       <c r="C83" t="n">
-        <v>185.7353746560278</v>
+        <v>189.1573747868041</v>
       </c>
       <c r="D83" t="n">
-        <v>183.5005985718231</v>
+        <v>186.3838660627843</v>
       </c>
       <c r="E83" t="n">
-        <v>184.4084777832031</v>
+        <v>187.2318725585938</v>
       </c>
       <c r="F83" t="n">
-        <v>139636600</v>
+        <v>142748100</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B84" t="n">
-        <v>187.0622712594319</v>
+        <v>186.7230748442759</v>
       </c>
       <c r="C84" t="n">
-        <v>189.1573747868041</v>
+        <v>188.6784906596197</v>
       </c>
       <c r="D84" t="n">
-        <v>186.3838660627843</v>
+        <v>185.555808059744</v>
       </c>
       <c r="E84" t="n">
-        <v>187.2318725585938</v>
+        <v>186.0346832275391</v>
       </c>
       <c r="F84" t="n">
-        <v>142748100</v>
+        <v>124799600</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B85" t="n">
-        <v>186.7230748442759</v>
+        <v>186.8028844605491</v>
       </c>
       <c r="C85" t="n">
-        <v>188.6784906596197</v>
+        <v>189.5564356240106</v>
       </c>
       <c r="D85" t="n">
-        <v>185.555808059744</v>
+        <v>185.2664711415707</v>
       </c>
       <c r="E85" t="n">
-        <v>186.0346832275391</v>
+        <v>188.0798950195312</v>
       </c>
       <c r="F85" t="n">
-        <v>124799600</v>
+        <v>143711600</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B86" t="n">
-        <v>186.8028844605491</v>
+        <v>190.8234748728661</v>
       </c>
       <c r="C86" t="n">
-        <v>189.5564356240106</v>
+        <v>191.9009553855833</v>
       </c>
       <c r="D86" t="n">
-        <v>185.2664711415707</v>
+        <v>189.3968053634026</v>
       </c>
       <c r="E86" t="n">
-        <v>188.0798950195312</v>
+        <v>191.0728912353516</v>
       </c>
       <c r="F86" t="n">
-        <v>143711600</v>
+        <v>148552700</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B87" t="n">
-        <v>190.823459633995</v>
+        <v>190.8933105997472</v>
       </c>
       <c r="C87" t="n">
-        <v>191.9009400606663</v>
+        <v>193.0283141326731</v>
       </c>
       <c r="D87" t="n">
-        <v>189.3967902384632</v>
+        <v>185.6256380470483</v>
       </c>
       <c r="E87" t="n">
-        <v>191.0728759765625</v>
+        <v>192.0605773925781</v>
       </c>
       <c r="F87" t="n">
-        <v>148552700</v>
+        <v>171764400</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B88" t="n">
-        <v>190.8933105997472</v>
+        <v>190.7636224379378</v>
       </c>
       <c r="C88" t="n">
-        <v>193.0283141326731</v>
+        <v>194.0359639826301</v>
       </c>
       <c r="D88" t="n">
-        <v>185.6256380470483</v>
+        <v>189.0276790286862</v>
       </c>
       <c r="E88" t="n">
-        <v>192.0605773925781</v>
+        <v>190.6838073730469</v>
       </c>
       <c r="F88" t="n">
-        <v>171764400</v>
+        <v>179489500</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B89" t="n">
-        <v>190.7636224379378</v>
+        <v>186.7629812920276</v>
       </c>
       <c r="C89" t="n">
-        <v>194.0359639826301</v>
+        <v>189.8557504766133</v>
       </c>
       <c r="D89" t="n">
-        <v>189.0276790286862</v>
+        <v>184.4484052141589</v>
       </c>
       <c r="E89" t="n">
-        <v>190.6838073730469</v>
+        <v>185.1766967773438</v>
       </c>
       <c r="F89" t="n">
-        <v>179489500</v>
+        <v>165794100</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B90" t="n">
-        <v>186.7629659025267</v>
+        <v>185.8052108647954</v>
       </c>
       <c r="C90" t="n">
-        <v>189.8557348322644</v>
+        <v>185.8351396091497</v>
       </c>
       <c r="D90" t="n">
-        <v>184.4483900153819</v>
+        <v>175.8185703987175</v>
       </c>
       <c r="E90" t="n">
-        <v>185.1766815185547</v>
+        <v>179.9189758300781</v>
       </c>
       <c r="F90" t="n">
-        <v>165794100</v>
+        <v>204019600</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B91" t="n">
-        <v>185.8052108647954</v>
+        <v>179.0410414348666</v>
       </c>
       <c r="C91" t="n">
-        <v>185.8351396091497</v>
+        <v>179.160756412826</v>
       </c>
       <c r="D91" t="n">
-        <v>175.8185703987175</v>
+        <v>171.5086645338761</v>
       </c>
       <c r="E91" t="n">
-        <v>179.9189758300781</v>
+        <v>173.7833404541016</v>
       </c>
       <c r="F91" t="n">
-        <v>204019600</v>
+        <v>207014100</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B92" t="n">
-        <v>179.0410571553003</v>
+        <v>174.5215964583249</v>
       </c>
       <c r="C92" t="n">
-        <v>179.1607721437711</v>
+        <v>176.4071986282528</v>
       </c>
       <c r="D92" t="n">
-        <v>171.5086795929406</v>
+        <v>170.6307075914073</v>
       </c>
       <c r="E92" t="n">
-        <v>173.7833557128906</v>
+        <v>171.4787292480469</v>
       </c>
       <c r="F92" t="n">
-        <v>207014100</v>
+        <v>206312900</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B93" t="n">
-        <v>174.5216119878791</v>
+        <v>176.277498975506</v>
       </c>
       <c r="C93" t="n">
-        <v>176.4072143255947</v>
+        <v>186.5634266395524</v>
       </c>
       <c r="D93" t="n">
-        <v>170.6307227747363</v>
+        <v>174.1923819783884</v>
       </c>
       <c r="E93" t="n">
-        <v>171.4787445068359</v>
+        <v>184.9771423339844</v>
       </c>
       <c r="F93" t="n">
-        <v>206312900</v>
+        <v>231346200</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B94" t="n">
-        <v>176.2775280578147</v>
+        <v>183.8298386502086</v>
       </c>
       <c r="C94" t="n">
-        <v>186.5634574188361</v>
+        <v>193.2079034382237</v>
       </c>
       <c r="D94" t="n">
-        <v>174.1924107166939</v>
+        <v>183.5205647824287</v>
       </c>
       <c r="E94" t="n">
-        <v>184.9771728515625</v>
+        <v>189.5963439941406</v>
       </c>
       <c r="F94" t="n">
-        <v>231346200</v>
+        <v>196387400</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B95" t="n">
-        <v>183.8298238555102</v>
+        <v>190.933219719687</v>
       </c>
       <c r="C95" t="n">
-        <v>193.2078878887748</v>
+        <v>192.0306425866914</v>
       </c>
       <c r="D95" t="n">
-        <v>183.5205500126207</v>
+        <v>187.6808205923615</v>
       </c>
       <c r="E95" t="n">
-        <v>189.5963287353516</v>
+        <v>188.0998382568359</v>
       </c>
       <c r="F95" t="n">
-        <v>196387400</v>
+        <v>136764800</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B96" t="n">
-        <v>190.9332352083219</v>
+        <v>192.0007142509167</v>
       </c>
       <c r="C96" t="n">
-        <v>192.0306581643501</v>
+        <v>192.8088208357837</v>
       </c>
       <c r="D96" t="n">
-        <v>187.6808358171596</v>
+        <v>188.329312674443</v>
       </c>
       <c r="E96" t="n">
-        <v>188.099853515625</v>
+        <v>189.6063232421875</v>
       </c>
       <c r="F96" t="n">
-        <v>136764800</v>
+        <v>144192700</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B97" t="n">
-        <v>192.0007142509167</v>
+        <v>192.5793648877844</v>
       </c>
       <c r="C97" t="n">
-        <v>192.8088208357837</v>
+        <v>193.1580126884611</v>
       </c>
       <c r="D97" t="n">
-        <v>188.329312674443</v>
+        <v>186.0745817463215</v>
       </c>
       <c r="E97" t="n">
-        <v>189.6063232421875</v>
+        <v>186.5035858154297</v>
       </c>
       <c r="F97" t="n">
-        <v>144192700</v>
+        <v>189932500</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B98" t="n">
-        <v>192.5793648877844</v>
+        <v>187.042320465516</v>
       </c>
       <c r="C98" t="n">
-        <v>193.1580126884611</v>
+        <v>187.0622780376601</v>
       </c>
       <c r="D98" t="n">
-        <v>186.0745817463215</v>
+        <v>181.1660713803529</v>
       </c>
       <c r="E98" t="n">
-        <v>186.5035858154297</v>
+        <v>182.3832244873047</v>
       </c>
       <c r="F98" t="n">
-        <v>189932500</v>
+        <v>161888000</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B99" t="n">
-        <v>187.042320465516</v>
+        <v>181.3256935584433</v>
       </c>
       <c r="C99" t="n">
-        <v>187.0622780376601</v>
+        <v>186.7130808403767</v>
       </c>
       <c r="D99" t="n">
-        <v>181.1660713803529</v>
+        <v>178.7616860728079</v>
       </c>
       <c r="E99" t="n">
-        <v>182.3832244873047</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="F99" t="n">
-        <v>161888000</v>
+        <v>162276900</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B100" t="n">
-        <v>181.3256935584433</v>
+        <v>188.3093443160685</v>
       </c>
       <c r="C100" t="n">
-        <v>186.7130808403767</v>
+        <v>189.9255573932224</v>
       </c>
       <c r="D100" t="n">
-        <v>178.7616860728079</v>
+        <v>186.3239846890322</v>
       </c>
       <c r="E100" t="n">
-        <v>184.5381774902344</v>
+        <v>187.5411376953125</v>
       </c>
       <c r="F100" t="n">
-        <v>162276900</v>
+        <v>164749100</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B101" t="n">
-        <v>188.3093443160685</v>
+        <v>186.62329889396</v>
       </c>
       <c r="C101" t="n">
-        <v>189.9255573932224</v>
+        <v>187.9900957055448</v>
       </c>
       <c r="D101" t="n">
-        <v>186.3239846890322</v>
+        <v>185.2265733363672</v>
       </c>
       <c r="E101" t="n">
-        <v>187.5411376953125</v>
+        <v>187.4613342285156</v>
       </c>
       <c r="F101" t="n">
-        <v>164749100</v>
+        <v>126554500</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B102" t="n">
-        <v>186.62329889396</v>
+        <v>186.1344638821937</v>
       </c>
       <c r="C102" t="n">
-        <v>187.9900957055448</v>
+        <v>189.8856807673048</v>
       </c>
       <c r="D102" t="n">
-        <v>185.2265733363672</v>
+        <v>185.5059297314624</v>
       </c>
       <c r="E102" t="n">
-        <v>187.4613342285156</v>
+        <v>189.3768768310547</v>
       </c>
       <c r="F102" t="n">
-        <v>126554500</v>
+        <v>178422300</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B103" t="n">
-        <v>186.1344488846578</v>
+        <v>190.9531700210539</v>
       </c>
       <c r="C103" t="n">
-        <v>189.8856654675195</v>
+        <v>193.4972200828311</v>
       </c>
       <c r="D103" t="n">
-        <v>185.5059147845697</v>
+        <v>189.1374267327081</v>
       </c>
       <c r="E103" t="n">
-        <v>189.3768615722656</v>
+        <v>191.1028289794922</v>
       </c>
       <c r="F103" t="n">
-        <v>178422300</v>
+        <v>171584800</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B104" t="n">
-        <v>190.9531547742145</v>
+        <v>191.0429698590405</v>
       </c>
       <c r="C104" t="n">
-        <v>193.4972046328596</v>
+        <v>193.3176459547985</v>
       </c>
       <c r="D104" t="n">
-        <v>189.1374116308485</v>
+        <v>186.9625064417709</v>
       </c>
       <c r="E104" t="n">
-        <v>191.1028137207031</v>
+        <v>192.3997955322266</v>
       </c>
       <c r="F104" t="n">
-        <v>171584800</v>
+        <v>175123600</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B105" t="n">
-        <v>191.0429698590405</v>
+        <v>193.9960453222018</v>
       </c>
       <c r="C105" t="n">
-        <v>193.3176459547985</v>
+        <v>197.1686293956491</v>
       </c>
       <c r="D105" t="n">
-        <v>186.9625064417709</v>
+        <v>193.3375824661624</v>
       </c>
       <c r="E105" t="n">
-        <v>192.3997955322266</v>
+        <v>195.1034545898438</v>
       </c>
       <c r="F105" t="n">
-        <v>175123600</v>
+        <v>250637100</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B106" t="n">
-        <v>193.9960453222018</v>
+        <v>193.8164652690549</v>
       </c>
       <c r="C106" t="n">
-        <v>197.1686293956491</v>
+        <v>193.8364076167612</v>
       </c>
       <c r="D106" t="n">
-        <v>193.3375824661624</v>
+        <v>183.8896973916963</v>
       </c>
       <c r="E106" t="n">
-        <v>195.1034545898438</v>
+        <v>184.4583587646484</v>
       </c>
       <c r="F106" t="n">
-        <v>250637100</v>
+        <v>360807900</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B107" t="n">
-        <v>193.8164813019665</v>
+        <v>180.8268714126474</v>
       </c>
       <c r="C107" t="n">
-        <v>193.8364236513225</v>
+        <v>182.1637395256691</v>
       </c>
       <c r="D107" t="n">
-        <v>183.8897126034445</v>
+        <v>175.9682453114839</v>
       </c>
       <c r="E107" t="n">
-        <v>184.4583740234375</v>
+        <v>176.7763519287109</v>
       </c>
       <c r="F107" t="n">
-        <v>360807900</v>
+        <v>311636500</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B108" t="n">
-        <v>180.8268714126474</v>
+        <v>174.601438160182</v>
       </c>
       <c r="C108" t="n">
-        <v>182.1637395256691</v>
+        <v>183.0317240302905</v>
       </c>
       <c r="D108" t="n">
-        <v>175.9682453114839</v>
+        <v>174.2323067871125</v>
       </c>
       <c r="E108" t="n">
-        <v>176.7763519287109</v>
+        <v>182.0540008544922</v>
       </c>
       <c r="F108" t="n">
-        <v>311636500</v>
+        <v>209095300</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B109" t="n">
-        <v>174.6014235260267</v>
+        <v>178.0732983803544</v>
       </c>
       <c r="C109" t="n">
-        <v>183.0317086895539</v>
+        <v>180.4776603660684</v>
       </c>
       <c r="D109" t="n">
-        <v>174.2322921838959</v>
+        <v>176.5069564334623</v>
       </c>
       <c r="E109" t="n">
-        <v>182.0539855957031</v>
+        <v>179.6296539306641</v>
       </c>
       <c r="F109" t="n">
-        <v>209095300</v>
+        <v>178099400</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B110" t="n">
-        <v>178.0733135069376</v>
+        <v>180.0187649948852</v>
       </c>
       <c r="C110" t="n">
-        <v>180.4776756968921</v>
+        <v>184.2688145383873</v>
       </c>
       <c r="D110" t="n">
-        <v>176.5069714269912</v>
+        <v>179.6396472340209</v>
       </c>
       <c r="E110" t="n">
-        <v>179.6296691894531</v>
+        <v>182.6126861572266</v>
       </c>
       <c r="F110" t="n">
-        <v>178099400</v>
+        <v>177731200</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B111" t="n">
-        <v>180.0187499528396</v>
+        <v>180.7470550179114</v>
       </c>
       <c r="C111" t="n">
-        <v>184.2687991412151</v>
+        <v>183.6303076754259</v>
       </c>
       <c r="D111" t="n">
-        <v>179.6396322236537</v>
+        <v>177.4647422536165</v>
       </c>
       <c r="E111" t="n">
-        <v>182.6126708984375</v>
+        <v>182.9119873046875</v>
       </c>
       <c r="F111" t="n">
-        <v>177731200</v>
+        <v>198779700</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B112" t="n">
-        <v>180.7470399397241</v>
+        <v>179.420149946886</v>
       </c>
       <c r="C112" t="n">
-        <v>183.6302923567135</v>
+        <v>182.3333312190456</v>
       </c>
       <c r="D112" t="n">
-        <v>177.4647274492447</v>
+        <v>176.407211264142</v>
       </c>
       <c r="E112" t="n">
-        <v>182.9119720458984</v>
+        <v>177.4048767089844</v>
       </c>
       <c r="F112" t="n">
-        <v>198779700</v>
+        <v>189021900</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B113" t="n">
-        <v>179.4201653790109</v>
+        <v>176.4171820751478</v>
       </c>
       <c r="C113" t="n">
-        <v>182.3333469017365</v>
+        <v>182.4829897940845</v>
       </c>
       <c r="D113" t="n">
-        <v>176.4072264371208</v>
+        <v>175.1501427003192</v>
       </c>
       <c r="E113" t="n">
-        <v>177.4048919677734</v>
+        <v>182.2235870361328</v>
       </c>
       <c r="F113" t="n">
-        <v>189021900</v>
+        <v>177213600</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B114" t="n">
-        <v>176.4171820751478</v>
+        <v>181.9741760435397</v>
       </c>
       <c r="C114" t="n">
-        <v>182.4829897940845</v>
+        <v>186.0047530762794</v>
       </c>
       <c r="D114" t="n">
-        <v>175.1501427003192</v>
+        <v>181.5850871183009</v>
       </c>
       <c r="E114" t="n">
-        <v>182.2235870361328</v>
+        <v>184.3386535644531</v>
       </c>
       <c r="F114" t="n">
-        <v>177213600</v>
+        <v>179118500</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,25 +3407,25 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B115" t="n">
-        <v>181.9741609804723</v>
+        <v>185.4860219488843</v>
       </c>
       <c r="C115" t="n">
-        <v>186.0047376795775</v>
+        <v>187.1921136401388</v>
       </c>
       <c r="D115" t="n">
-        <v>181.5850720874406</v>
+        <v>184.0293448898806</v>
       </c>
       <c r="E115" t="n">
-        <v>184.3386383056641</v>
+        <v>185.6057434082031</v>
       </c>
       <c r="F115" t="n">
-        <v>179118500</v>
+        <v>145280400</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -3433,25 +3433,25 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B116" t="n">
-        <v>185.4860219488843</v>
+        <v>183.6302794851663</v>
       </c>
       <c r="C116" t="n">
-        <v>187.1921136401388</v>
+        <v>184.5182492431283</v>
       </c>
       <c r="D116" t="n">
-        <v>184.0293448898806</v>
+        <v>181.3355215595592</v>
       </c>
       <c r="E116" t="n">
-        <v>185.6057434082031</v>
+        <v>182.7223510742188</v>
       </c>
       <c r="F116" t="n">
-        <v>145280400</v>
+        <v>155762700</v>
       </c>
       <c r="G116" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B117" t="n">
-        <v>183.6302794851663</v>
+        <v>184.4982761588831</v>
       </c>
       <c r="C117" t="n">
-        <v>184.5182492431283</v>
+        <v>185.6656060713691</v>
       </c>
       <c r="D117" t="n">
-        <v>181.3355215595592</v>
+        <v>179.5296376335348</v>
       </c>
       <c r="E117" t="n">
-        <v>182.7223510742188</v>
+        <v>179.8389282226562</v>
       </c>
       <c r="F117" t="n">
-        <v>155762700</v>
+        <v>160988400</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B118" t="n">
-        <v>184.4982761588831</v>
+        <v>182.5527399223597</v>
       </c>
       <c r="C118" t="n">
-        <v>185.6656060713691</v>
+        <v>188.4492658789173</v>
       </c>
       <c r="D118" t="n">
-        <v>179.5296376335348</v>
+        <v>180.9962999229416</v>
       </c>
       <c r="E118" t="n">
-        <v>179.8389282226562</v>
+        <v>182.8021697998047</v>
       </c>
       <c r="F118" t="n">
-        <v>160988400</v>
+        <v>217307400</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B119" t="n">
-        <v>182.5527399223597</v>
+        <v>184.6379576703901</v>
       </c>
       <c r="C119" t="n">
-        <v>188.4492658789173</v>
+        <v>184.9771786272242</v>
       </c>
       <c r="D119" t="n">
-        <v>180.9962999229416</v>
+        <v>181.2656610816535</v>
       </c>
       <c r="E119" t="n">
-        <v>182.8021697998047</v>
+        <v>181.5150909423828</v>
       </c>
       <c r="F119" t="n">
-        <v>217307400</v>
+        <v>182497800</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B120" t="n">
-        <v>184.6379576703901</v>
+        <v>182.0638447517288</v>
       </c>
       <c r="C120" t="n">
-        <v>184.9771786272242</v>
+        <v>182.9618014097589</v>
       </c>
       <c r="D120" t="n">
-        <v>181.2656610816535</v>
+        <v>179.9187539793071</v>
       </c>
       <c r="E120" t="n">
-        <v>181.5150909423828</v>
+        <v>179.9885864257812</v>
       </c>
       <c r="F120" t="n">
-        <v>182497800</v>
+        <v>156683100</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B121" t="n">
-        <v>182.0638447517288</v>
+        <v>177.6040375011918</v>
       </c>
       <c r="C121" t="n">
-        <v>182.9618014097589</v>
+        <v>179.569546076418</v>
       </c>
       <c r="D121" t="n">
-        <v>179.9187539793071</v>
+        <v>175.3890990582871</v>
       </c>
       <c r="E121" t="n">
-        <v>179.9885864257812</v>
+        <v>178.1527862548828</v>
       </c>
       <c r="F121" t="n">
-        <v>156683100</v>
+        <v>170968500</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B122" t="n">
-        <v>177.6040375011918</v>
+        <v>177.5940529420793</v>
       </c>
       <c r="C122" t="n">
-        <v>179.569546076418</v>
+        <v>177.8534545050662</v>
       </c>
       <c r="D122" t="n">
-        <v>175.3890990582871</v>
+        <v>171.3283763370981</v>
       </c>
       <c r="E122" t="n">
-        <v>178.1527862548828</v>
+        <v>172.3061370849609</v>
       </c>
       <c r="F122" t="n">
-        <v>170968500</v>
+        <v>241323500</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B123" t="n">
-        <v>177.5940529420793</v>
+        <v>176.8557415306554</v>
       </c>
       <c r="C123" t="n">
-        <v>177.8534545050662</v>
+        <v>177.9632107122345</v>
       </c>
       <c r="D123" t="n">
-        <v>171.3283763370981</v>
+        <v>174.3614429436745</v>
       </c>
       <c r="E123" t="n">
-        <v>172.3061370849609</v>
+        <v>175.2394409179688</v>
       </c>
       <c r="F123" t="n">
-        <v>241323500</v>
+        <v>182836300</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B124" t="n">
-        <v>176.8557415306554</v>
+        <v>174.4312942297872</v>
       </c>
       <c r="C124" t="n">
-        <v>177.9632107122345</v>
+        <v>175.8181236639554</v>
       </c>
       <c r="D124" t="n">
-        <v>174.3614429436745</v>
+        <v>173.5832266030264</v>
       </c>
       <c r="E124" t="n">
-        <v>175.2394409179688</v>
+        <v>174.8004455566406</v>
       </c>
       <c r="F124" t="n">
-        <v>182836300</v>
+        <v>147667800</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B125" t="n">
-        <v>174.4312942297872</v>
+        <v>176.6961233561449</v>
       </c>
       <c r="C125" t="n">
-        <v>175.8181236639554</v>
+        <v>180.8067226806179</v>
       </c>
       <c r="D125" t="n">
-        <v>173.5832266030264</v>
+        <v>176.4466934898736</v>
       </c>
       <c r="E125" t="n">
-        <v>174.8004455566406</v>
+        <v>178.2725067138672</v>
       </c>
       <c r="F125" t="n">
-        <v>147667800</v>
+        <v>162602100</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B126" t="n">
-        <v>176.6961233561449</v>
+        <v>175.6684741654964</v>
       </c>
       <c r="C126" t="n">
-        <v>180.8067226806179</v>
+        <v>176.1074579435819</v>
       </c>
       <c r="D126" t="n">
-        <v>176.4466934898736</v>
+        <v>170.7497092682189</v>
       </c>
       <c r="E126" t="n">
-        <v>178.2725067138672</v>
+        <v>170.8494873046875</v>
       </c>
       <c r="F126" t="n">
-        <v>162602100</v>
+        <v>186152200</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B127" t="n">
-        <v>175.6684741654964</v>
+        <v>169.6122945102883</v>
       </c>
       <c r="C127" t="n">
-        <v>176.1074579435819</v>
+        <v>170.5800835262955</v>
       </c>
       <c r="D127" t="n">
-        <v>170.7497092682189</v>
+        <v>166.6291080850299</v>
       </c>
       <c r="E127" t="n">
-        <v>170.8494873046875</v>
+        <v>167.1379547119141</v>
       </c>
       <c r="F127" t="n">
-        <v>186152200</v>
+        <v>196212700</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B128" t="n">
-        <v>169.6122945102883</v>
+        <v>168.3950875250076</v>
       </c>
       <c r="C128" t="n">
-        <v>170.5800835262955</v>
+        <v>169.0635577295173</v>
       </c>
       <c r="D128" t="n">
-        <v>166.6291080850299</v>
+        <v>163.8953782868944</v>
       </c>
       <c r="E128" t="n">
-        <v>167.1379547119141</v>
+        <v>164.7933197021484</v>
       </c>
       <c r="F128" t="n">
-        <v>196212700</v>
+        <v>185627000</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B129" t="n">
-        <v>168.3950875250076</v>
+        <v>166.5892250311153</v>
       </c>
       <c r="C129" t="n">
-        <v>169.0635577295173</v>
+        <v>174.2217730660379</v>
       </c>
       <c r="D129" t="n">
-        <v>163.8953782868944</v>
+        <v>166.5792533168182</v>
       </c>
       <c r="E129" t="n">
-        <v>164.7933197021484</v>
+        <v>174.0022735595703</v>
       </c>
       <c r="F129" t="n">
-        <v>185627000</v>
+        <v>226181300</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B130" t="n">
-        <v>166.5892250311153</v>
+        <v>175.5986272559566</v>
       </c>
       <c r="C130" t="n">
-        <v>174.2217730660379</v>
+        <v>176.9654980623514</v>
       </c>
       <c r="D130" t="n">
-        <v>166.5792533168182</v>
+        <v>174.3514779146501</v>
       </c>
       <c r="E130" t="n">
-        <v>174.0022735595703</v>
+        <v>175.3491973876953</v>
       </c>
       <c r="F130" t="n">
-        <v>226181300</v>
+        <v>168132000</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B131" t="n">
-        <v>175.5986272559566</v>
+        <v>171.7873183615289</v>
       </c>
       <c r="C131" t="n">
-        <v>176.9654980623514</v>
+        <v>177.0852211444685</v>
       </c>
       <c r="D131" t="n">
-        <v>174.3514779146501</v>
+        <v>170.9791680862979</v>
       </c>
       <c r="E131" t="n">
-        <v>175.3491973876953</v>
+        <v>176.9854431152344</v>
       </c>
       <c r="F131" t="n">
-        <v>168132000</v>
+        <v>143143200</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B132" t="n">
-        <v>171.7873183615289</v>
+        <v>176.7559774774269</v>
       </c>
       <c r="C132" t="n">
-        <v>177.0852211444685</v>
+        <v>177.3845303646084</v>
       </c>
       <c r="D132" t="n">
-        <v>170.9791680862979</v>
+        <v>175.3591611441553</v>
       </c>
       <c r="E132" t="n">
-        <v>176.9854431152344</v>
+        <v>177.2348785400391</v>
       </c>
       <c r="F132" t="n">
-        <v>143143200</v>
+        <v>107564300</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B133" t="n">
-        <v>176.7559774774269</v>
+        <v>175.3292270516068</v>
       </c>
       <c r="C133" t="n">
-        <v>177.3845303646084</v>
+        <v>177.8235255680002</v>
       </c>
       <c r="D133" t="n">
-        <v>175.3591611441553</v>
+        <v>173.2639557965079</v>
       </c>
       <c r="E133" t="n">
-        <v>177.2348785400391</v>
+        <v>177.6938323974609</v>
       </c>
       <c r="F133" t="n">
-        <v>107564300</v>
+        <v>132534900</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B134" t="n">
-        <v>175.3292270516068</v>
+        <v>184.079243714486</v>
       </c>
       <c r="C134" t="n">
-        <v>177.8235255680002</v>
+        <v>184.837505037226</v>
       </c>
       <c r="D134" t="n">
-        <v>173.2639557965079</v>
+        <v>179.8888249511496</v>
       </c>
       <c r="E134" t="n">
-        <v>177.6938323974609</v>
+        <v>181.6647644042969</v>
       </c>
       <c r="F134" t="n">
-        <v>132534900</v>
+        <v>147732700</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B135" t="n">
-        <v>184.079243714486</v>
+        <v>181.4252987848774</v>
       </c>
       <c r="C135" t="n">
-        <v>184.837505037226</v>
+        <v>183.6601958045732</v>
       </c>
       <c r="D135" t="n">
-        <v>179.8888249511496</v>
+        <v>180.2080798537204</v>
       </c>
       <c r="E135" t="n">
-        <v>181.6647644042969</v>
+        <v>183.4905853271484</v>
       </c>
       <c r="F135" t="n">
-        <v>147732700</v>
+        <v>116428500</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B136" t="n">
-        <v>181.4252987848774</v>
+        <v>183.8896736698189</v>
       </c>
       <c r="C136" t="n">
-        <v>183.6601958045732</v>
+        <v>189.5666999081706</v>
       </c>
       <c r="D136" t="n">
-        <v>180.2080798537204</v>
+        <v>183.8797019557237</v>
       </c>
       <c r="E136" t="n">
-        <v>183.4905853271484</v>
+        <v>188.1998291015625</v>
       </c>
       <c r="F136" t="n">
-        <v>116428500</v>
+        <v>160459500</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B137" t="n">
-        <v>183.8896736698189</v>
+        <v>185.605746824658</v>
       </c>
       <c r="C137" t="n">
-        <v>189.5666999081706</v>
+        <v>189.2274732756209</v>
       </c>
       <c r="D137" t="n">
-        <v>183.8797019557237</v>
+        <v>185.3164148846483</v>
       </c>
       <c r="E137" t="n">
-        <v>188.1998291015625</v>
+        <v>188.8782653808594</v>
       </c>
       <c r="F137" t="n">
-        <v>160459500</v>
+        <v>133648200</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B138" t="n">
-        <v>185.605746824658</v>
+        <v>190.4047764107204</v>
       </c>
       <c r="C138" t="n">
-        <v>189.2274732756209</v>
+        <v>196.0618438720703</v>
       </c>
       <c r="D138" t="n">
-        <v>185.3164148846483</v>
+        <v>190.3349439656124</v>
       </c>
       <c r="E138" t="n">
-        <v>188.8782653808594</v>
+        <v>196.0618438720703</v>
       </c>
       <c r="F138" t="n">
-        <v>133648200</v>
+        <v>161307000</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B139" t="n">
-        <v>190.4047764107204</v>
+        <v>196.0917851116163</v>
       </c>
       <c r="C139" t="n">
-        <v>196.0618438720703</v>
+        <v>199.9429830157183</v>
       </c>
       <c r="D139" t="n">
-        <v>190.3349439656124</v>
+        <v>195.2936216855987</v>
       </c>
       <c r="E139" t="n">
-        <v>196.0618438720703</v>
+        <v>198.4164733886719</v>
       </c>
       <c r="F139" t="n">
-        <v>161307000</v>
+        <v>185338400</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B140" t="n">
-        <v>196.0917851116163</v>
+        <v>196.9797440092329</v>
       </c>
       <c r="C140" t="n">
-        <v>199.9429830157183</v>
+        <v>199.3942384790618</v>
       </c>
       <c r="D140" t="n">
-        <v>195.2936216855987</v>
+        <v>195.3634433694217</v>
       </c>
       <c r="E140" t="n">
-        <v>198.4164733886719</v>
+        <v>197.8976593017578</v>
       </c>
       <c r="F140" t="n">
-        <v>185338400</v>
+        <v>134012900</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B141" t="n">
-        <v>196.9797440092329</v>
+        <v>199.444107632571</v>
       </c>
       <c r="C141" t="n">
-        <v>199.3942384790618</v>
+        <v>201.2400056483541</v>
       </c>
       <c r="D141" t="n">
-        <v>195.3634433694217</v>
+        <v>198.8155547450397</v>
       </c>
       <c r="E141" t="n">
-        <v>197.8976593017578</v>
+        <v>201.2200469970703</v>
       </c>
       <c r="F141" t="n">
-        <v>134012900</v>
+        <v>160324400</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B142" t="n">
-        <v>199.444107632571</v>
+        <v>199.5239239232554</v>
       </c>
       <c r="C142" t="n">
-        <v>201.2400056483541</v>
+        <v>201.7089318732817</v>
       </c>
       <c r="D142" t="n">
-        <v>198.8155547450397</v>
+        <v>197.3888049886708</v>
       </c>
       <c r="E142" t="n">
-        <v>201.2200469970703</v>
+        <v>201.5991821289062</v>
       </c>
       <c r="F142" t="n">
-        <v>160324400</v>
+        <v>119381400</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B143" t="n">
-        <v>199.5239239232554</v>
+        <v>201.6690479582887</v>
       </c>
       <c r="C143" t="n">
-        <v>201.7089318732817</v>
+        <v>202.2876291783034</v>
       </c>
       <c r="D143" t="n">
-        <v>197.3888049886708</v>
+        <v>198.5461810430697</v>
       </c>
       <c r="E143" t="n">
-        <v>201.5991821289062</v>
+        <v>199.4241790771484</v>
       </c>
       <c r="F143" t="n">
-        <v>119381400</v>
+        <v>107945300</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B144" t="n">
-        <v>201.6690479582887</v>
+        <v>200.5316418294082</v>
       </c>
       <c r="C144" t="n">
-        <v>202.2876291783034</v>
+        <v>202.0381927490234</v>
       </c>
       <c r="D144" t="n">
-        <v>198.5461810430697</v>
+        <v>198.546174602744</v>
       </c>
       <c r="E144" t="n">
-        <v>199.4241790771484</v>
+        <v>202.0381927490234</v>
       </c>
       <c r="F144" t="n">
-        <v>107945300</v>
+        <v>107501000</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B145" t="n">
-        <v>200.5316418294082</v>
+        <v>201.9982837593082</v>
       </c>
       <c r="C145" t="n">
-        <v>202.0381927490234</v>
+        <v>203.3651545152774</v>
       </c>
       <c r="D145" t="n">
-        <v>198.546174602744</v>
+        <v>196.7702284327844</v>
       </c>
       <c r="E145" t="n">
-        <v>202.0381927490234</v>
+        <v>199.1847076416016</v>
       </c>
       <c r="F145" t="n">
-        <v>107501000</v>
+        <v>113561800</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B146" t="n">
-        <v>201.9982837593082</v>
+        <v>199.5039827094276</v>
       </c>
       <c r="C146" t="n">
-        <v>203.3651545152774</v>
+        <v>210.468909435165</v>
       </c>
       <c r="D146" t="n">
-        <v>196.7702284327844</v>
+        <v>199.3543156614425</v>
       </c>
       <c r="E146" t="n">
-        <v>199.1847076416016</v>
+        <v>207.7950286865234</v>
       </c>
       <c r="F146" t="n">
-        <v>113561800</v>
+        <v>214134400</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B147" t="n">
-        <v>199.5039827094276</v>
+        <v>209.1718784416434</v>
       </c>
       <c r="C147" t="n">
-        <v>210.468909435165</v>
+        <v>216.335512072091</v>
       </c>
       <c r="D147" t="n">
-        <v>199.3543156614425</v>
+        <v>206.9070662315077</v>
       </c>
       <c r="E147" t="n">
-        <v>207.7950286865234</v>
+        <v>216.1160125732422</v>
       </c>
       <c r="F147" t="n">
-        <v>214134400</v>
+        <v>187172400</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B148" t="n">
-        <v>209.1718784416434</v>
+        <v>209.0122528840405</v>
       </c>
       <c r="C148" t="n">
-        <v>216.335512072091</v>
+        <v>214.2402930542568</v>
       </c>
       <c r="D148" t="n">
-        <v>206.9070662315077</v>
+        <v>207.7251862691963</v>
       </c>
       <c r="E148" t="n">
-        <v>216.1160125732422</v>
+        <v>212.6838531494141</v>
       </c>
       <c r="F148" t="n">
-        <v>187172400</v>
+        <v>180275400</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B149" t="n">
-        <v>209.0122528840405</v>
+        <v>212.2149257168926</v>
       </c>
       <c r="C149" t="n">
-        <v>214.2402930542568</v>
+        <v>212.2348843687743</v>
       </c>
       <c r="D149" t="n">
-        <v>207.7251862691963</v>
+        <v>207.1066069625242</v>
       </c>
       <c r="E149" t="n">
-        <v>212.6838531494141</v>
+        <v>208.7727966308594</v>
       </c>
       <c r="F149" t="n">
-        <v>180275400</v>
+        <v>123711800</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B150" t="n">
-        <v>212.2149257168926</v>
+        <v>209.4512425942353</v>
       </c>
       <c r="C150" t="n">
-        <v>212.2348843687743</v>
+        <v>209.820409153207</v>
       </c>
       <c r="D150" t="n">
-        <v>207.1066069625242</v>
+        <v>198.2468571251534</v>
       </c>
       <c r="E150" t="n">
-        <v>208.7727966308594</v>
+        <v>199.1148834228516</v>
       </c>
       <c r="F150" t="n">
-        <v>123711800</v>
+        <v>225239200</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B151" t="n">
-        <v>209.4512425942353</v>
+        <v>200.8209691272831</v>
       </c>
       <c r="C151" t="n">
-        <v>209.820409153207</v>
+        <v>202.5370477944956</v>
       </c>
       <c r="D151" t="n">
-        <v>198.2468571251534</v>
+        <v>196.6704525729091</v>
       </c>
       <c r="E151" t="n">
-        <v>199.1148834228516</v>
+        <v>197.9974212646484</v>
       </c>
       <c r="F151" t="n">
-        <v>225239200</v>
+        <v>128647000</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B152" t="n">
-        <v>200.8209691272831</v>
+        <v>199.0450218084295</v>
       </c>
       <c r="C152" t="n">
-        <v>202.5370477944956</v>
+        <v>201.2699318245734</v>
       </c>
       <c r="D152" t="n">
-        <v>196.6704525729091</v>
+        <v>194.2958829090753</v>
       </c>
       <c r="E152" t="n">
-        <v>197.9974212646484</v>
+        <v>198.02734375</v>
       </c>
       <c r="F152" t="n">
-        <v>128647000</v>
+        <v>125368100</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B153" t="n">
-        <v>199.0450218084295</v>
+        <v>198.8454820247872</v>
       </c>
       <c r="C153" t="n">
-        <v>201.2699318245734</v>
+        <v>199.7833407086998</v>
       </c>
       <c r="D153" t="n">
-        <v>194.2958829090753</v>
+        <v>195.5829352820671</v>
       </c>
       <c r="E153" t="n">
-        <v>198.02734375</v>
+        <v>196.0518646240234</v>
       </c>
       <c r="F153" t="n">
-        <v>125368100</v>
+        <v>113406600</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B154" t="n">
-        <v>198.8454820247872</v>
+        <v>199.4341385249406</v>
       </c>
       <c r="C154" t="n">
-        <v>199.7833407086998</v>
+        <v>207.7950323152332</v>
       </c>
       <c r="D154" t="n">
-        <v>195.5829352820671</v>
+        <v>198.1570588579161</v>
       </c>
       <c r="E154" t="n">
-        <v>196.0518646240234</v>
+        <v>207.3560333251953</v>
       </c>
       <c r="F154" t="n">
-        <v>113406600</v>
+        <v>188362800</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B155" t="n">
-        <v>199.4341385249406</v>
+        <v>207.8648724722903</v>
       </c>
       <c r="C155" t="n">
-        <v>207.7950323152332</v>
+        <v>213.7115092245668</v>
       </c>
       <c r="D155" t="n">
-        <v>198.1570588579161</v>
+        <v>206.0290722858257</v>
       </c>
       <c r="E155" t="n">
-        <v>207.3560333251953</v>
+        <v>211.0176696777344</v>
       </c>
       <c r="F155" t="n">
-        <v>188362800</v>
+        <v>168307900</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B156" t="n">
-        <v>207.8648724722903</v>
+        <v>212.5441790763045</v>
       </c>
       <c r="C156" t="n">
-        <v>213.7115092245668</v>
+        <v>217.3033052467507</v>
       </c>
       <c r="D156" t="n">
-        <v>206.0290722858257</v>
+        <v>212.4044989584125</v>
       </c>
       <c r="E156" t="n">
-        <v>211.0176696777344</v>
+        <v>214.709228515625</v>
       </c>
       <c r="F156" t="n">
-        <v>168307900</v>
+        <v>136421400</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B157" t="n">
-        <v>212.5441790763045</v>
+        <v>213.5518657378577</v>
       </c>
       <c r="C157" t="n">
-        <v>217.3033052467507</v>
+        <v>221.7930381906342</v>
       </c>
       <c r="D157" t="n">
-        <v>212.4044989584125</v>
+        <v>213.402213909002</v>
       </c>
       <c r="E157" t="n">
-        <v>214.709228515625</v>
+        <v>218.9395599365234</v>
       </c>
       <c r="F157" t="n">
-        <v>136421400</v>
+        <v>160685800</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B158" t="n">
-        <v>213.5518657378577</v>
+        <v>218.0515943496244</v>
       </c>
       <c r="C158" t="n">
-        <v>221.7930381906342</v>
+        <v>223.239732575863</v>
       </c>
       <c r="D158" t="n">
-        <v>213.402213909002</v>
+        <v>214.4298677829735</v>
       </c>
       <c r="E158" t="n">
-        <v>218.9395599365234</v>
+        <v>220.2765045166016</v>
       </c>
       <c r="F158" t="n">
-        <v>160685800</v>
+        <v>159176600</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B159" t="n">
-        <v>218.0515943496244</v>
+        <v>224.4170305354026</v>
       </c>
       <c r="C159" t="n">
-        <v>223.239732575863</v>
+        <v>227.3203978139454</v>
       </c>
       <c r="D159" t="n">
-        <v>214.4298677829735</v>
+        <v>221.0647077692387</v>
       </c>
       <c r="E159" t="n">
-        <v>220.2765045166016</v>
+        <v>225.3149871826172</v>
       </c>
       <c r="F159" t="n">
-        <v>159176600</v>
+        <v>150405400</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B160" t="n">
-        <v>224.4170305354026</v>
+        <v>229.3258255277811</v>
       </c>
       <c r="C160" t="n">
-        <v>227.3203978139454</v>
+        <v>236.0005559723521</v>
       </c>
       <c r="D160" t="n">
-        <v>221.0647077692387</v>
+        <v>228.7770767762568</v>
       </c>
       <c r="E160" t="n">
-        <v>225.3149871826172</v>
+        <v>235.202392578125</v>
       </c>
       <c r="F160" t="n">
-        <v>150405400</v>
+        <v>180782900</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B161" t="n">
-        <v>229.3258255277811</v>
+        <v>229.2360294447337</v>
       </c>
       <c r="C161" t="n">
-        <v>236.0005559723521</v>
+        <v>230.9720668751014</v>
       </c>
       <c r="D161" t="n">
-        <v>228.7770767762568</v>
+        <v>223.7286287034134</v>
       </c>
       <c r="E161" t="n">
-        <v>235.202392578125</v>
+        <v>224.8061676025391</v>
       </c>
       <c r="F161" t="n">
-        <v>180782900</v>
+        <v>180977600</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B162" t="n">
-        <v>229.2360294447337</v>
+        <v>229.345773483712</v>
       </c>
       <c r="C162" t="n">
-        <v>230.9720668751014</v>
+        <v>229.4754818886306</v>
       </c>
       <c r="D162" t="n">
-        <v>223.7286287034134</v>
+        <v>217.8719993892805</v>
       </c>
       <c r="E162" t="n">
-        <v>224.8061676025391</v>
+        <v>221.8130035400391</v>
       </c>
       <c r="F162" t="n">
-        <v>180977600</v>
+        <v>146280900</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B163" t="n">
-        <v>229.345773483712</v>
+        <v>219.1191400841904</v>
       </c>
       <c r="C163" t="n">
-        <v>229.4754818886306</v>
+        <v>223.9680572056967</v>
       </c>
       <c r="D163" t="n">
-        <v>217.8719993892805</v>
+        <v>217.4130483552105</v>
       </c>
       <c r="E163" t="n">
-        <v>221.8130035400391</v>
+        <v>220.1068878173828</v>
       </c>
       <c r="F163" t="n">
-        <v>146280900</v>
+        <v>140948200</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B164" t="n">
-        <v>219.1191400841904</v>
+        <v>222.6710257508039</v>
       </c>
       <c r="C164" t="n">
-        <v>223.9680572056967</v>
+        <v>225.6143103895453</v>
       </c>
       <c r="D164" t="n">
-        <v>217.4130483552105</v>
+        <v>219.9971448577806</v>
       </c>
       <c r="E164" t="n">
-        <v>220.1068878173828</v>
+        <v>222.9603729248047</v>
       </c>
       <c r="F164" t="n">
-        <v>140948200</v>
+        <v>184201600</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B165" t="n">
-        <v>222.6710257508039</v>
+        <v>221.7830583738447</v>
       </c>
       <c r="C165" t="n">
-        <v>225.6143103895453</v>
+        <v>226.8814055684356</v>
       </c>
       <c r="D165" t="n">
-        <v>219.9971448577806</v>
+        <v>217.4330007955402</v>
       </c>
       <c r="E165" t="n">
-        <v>222.9603729248047</v>
+        <v>219.0093994140625</v>
       </c>
       <c r="F165" t="n">
-        <v>184201600</v>
+        <v>203381800</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B166" t="n">
-        <v>221.7830583738447</v>
+        <v>220.3962175709585</v>
       </c>
       <c r="C166" t="n">
-        <v>226.8814055684356</v>
+        <v>220.5059673180016</v>
       </c>
       <c r="D166" t="n">
-        <v>217.4330007955402</v>
+        <v>214.3101381389001</v>
       </c>
       <c r="E166" t="n">
-        <v>219.0093994140625</v>
+        <v>214.8389282226562</v>
       </c>
       <c r="F166" t="n">
-        <v>203381800</v>
+        <v>169275700</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B167" t="n">
-        <v>220.3962175709585</v>
+        <v>216.0461718127993</v>
       </c>
       <c r="C167" t="n">
-        <v>220.5059673180016</v>
+        <v>217.6824311685512</v>
       </c>
       <c r="D167" t="n">
-        <v>214.3101381389001</v>
+        <v>211.5165320236786</v>
       </c>
       <c r="E167" t="n">
-        <v>214.8389282226562</v>
+        <v>214.3700103759766</v>
       </c>
       <c r="F167" t="n">
-        <v>169275700</v>
+        <v>187202600</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B168" t="n">
-        <v>216.0461718127993</v>
+        <v>213.6316806617713</v>
       </c>
       <c r="C168" t="n">
-        <v>217.6824311685512</v>
+        <v>213.6616110269177</v>
       </c>
       <c r="D168" t="n">
-        <v>211.5165320236786</v>
+        <v>208.3038625298546</v>
       </c>
       <c r="E168" t="n">
-        <v>214.3700103759766</v>
+        <v>212.1151580810547</v>
       </c>
       <c r="F168" t="n">
-        <v>187202600</v>
+        <v>167601200</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B169" t="n">
-        <v>213.6316806617713</v>
+        <v>210.7981551984497</v>
       </c>
       <c r="C169" t="n">
-        <v>213.6616110269177</v>
+        <v>215.0284909668814</v>
       </c>
       <c r="D169" t="n">
-        <v>208.3038625298546</v>
+        <v>210.7382944698381</v>
       </c>
       <c r="E169" t="n">
-        <v>212.1151580810547</v>
+        <v>213.7613830566406</v>
       </c>
       <c r="F169" t="n">
-        <v>167601200</v>
+        <v>143996000</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B170" t="n">
-        <v>210.7981551984497</v>
+        <v>214.0906505321041</v>
       </c>
       <c r="C170" t="n">
-        <v>215.0284909668814</v>
+        <v>217.3631692496548</v>
       </c>
       <c r="D170" t="n">
-        <v>210.7382944698381</v>
+        <v>210.6485213277038</v>
       </c>
       <c r="E170" t="n">
-        <v>213.7613830566406</v>
+        <v>210.6584930419922</v>
       </c>
       <c r="F170" t="n">
-        <v>143996000</v>
+        <v>289410600</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B171" t="n">
-        <v>214.0906505321041</v>
+        <v>215.2380189209027</v>
       </c>
       <c r="C171" t="n">
-        <v>217.3631692496548</v>
+        <v>224.3571743491113</v>
       </c>
       <c r="D171" t="n">
-        <v>210.6485213277038</v>
+        <v>215.2080885544549</v>
       </c>
       <c r="E171" t="n">
-        <v>210.6584930419922</v>
+        <v>223.8483428955078</v>
       </c>
       <c r="F171" t="n">
-        <v>289410600</v>
+        <v>212850700</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B172" t="n">
-        <v>215.2380189209027</v>
+        <v>226.6618858382332</v>
       </c>
       <c r="C172" t="n">
-        <v>224.3571743491113</v>
+        <v>231.7502608645459</v>
       </c>
       <c r="D172" t="n">
-        <v>215.2080885544549</v>
+        <v>220.8451951370975</v>
       </c>
       <c r="E172" t="n">
-        <v>223.8483428955078</v>
+        <v>222.3118438720703</v>
       </c>
       <c r="F172" t="n">
-        <v>212850700</v>
+        <v>193362900</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B173" t="n">
-        <v>226.6618858382332</v>
+        <v>221.2143597561905</v>
       </c>
       <c r="C173" t="n">
-        <v>231.7502608645459</v>
+        <v>222.3118572511273</v>
       </c>
       <c r="D173" t="n">
-        <v>220.8451951370975</v>
+        <v>214.0207957553572</v>
       </c>
       <c r="E173" t="n">
-        <v>222.3118438720703</v>
+        <v>214.26025390625</v>
       </c>
       <c r="F173" t="n">
-        <v>193362900</v>
+        <v>160907000</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,25 +4941,25 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B174" t="n">
-        <v>221.2143597561905</v>
+        <v>213.6709127939037</v>
       </c>
       <c r="C174" t="n">
-        <v>222.3118572511273</v>
+        <v>221.3523199881091</v>
       </c>
       <c r="D174" t="n">
-        <v>214.0207957553572</v>
+        <v>210.73419644349</v>
       </c>
       <c r="E174" t="n">
-        <v>214.26025390625</v>
+        <v>218.4156036376953</v>
       </c>
       <c r="F174" t="n">
-        <v>160907000</v>
+        <v>169022200</v>
       </c>
       <c r="G174" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -4967,25 +4967,25 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B175" t="n">
-        <v>213.6709127939037</v>
+        <v>214.2902104723603</v>
       </c>
       <c r="C175" t="n">
-        <v>221.3523199881091</v>
+        <v>214.6298267834636</v>
       </c>
       <c r="D175" t="n">
-        <v>210.73419644349</v>
+        <v>204.101614447126</v>
       </c>
       <c r="E175" t="n">
-        <v>218.4156036376953</v>
+        <v>204.8707580566406</v>
       </c>
       <c r="F175" t="n">
-        <v>169022200</v>
+        <v>219655500</v>
       </c>
       <c r="G175" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B176" t="n">
-        <v>214.2902104723603</v>
+        <v>209.9450713288228</v>
       </c>
       <c r="C176" t="n">
-        <v>214.6298267834636</v>
+        <v>210.2347557268212</v>
       </c>
       <c r="D176" t="n">
-        <v>204.101614447126</v>
+        <v>205.7697506938822</v>
       </c>
       <c r="E176" t="n">
-        <v>204.8707580566406</v>
+        <v>208.4067993164062</v>
       </c>
       <c r="F176" t="n">
-        <v>219655500</v>
+        <v>138372800</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B177" t="n">
-        <v>209.9450713288228</v>
+        <v>210.3845825512031</v>
       </c>
       <c r="C177" t="n">
-        <v>210.2347557268212</v>
+        <v>211.1637095162451</v>
       </c>
       <c r="D177" t="n">
-        <v>205.7697506938822</v>
+        <v>199.1171915656509</v>
       </c>
       <c r="E177" t="n">
-        <v>208.4067993164062</v>
+        <v>207.9573059082031</v>
       </c>
       <c r="F177" t="n">
-        <v>138372800</v>
+        <v>180962500</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B178" t="n">
-        <v>210.3845825512031</v>
+        <v>204.2014963256503</v>
       </c>
       <c r="C178" t="n">
-        <v>211.1637095162451</v>
+        <v>206.9883864105018</v>
       </c>
       <c r="D178" t="n">
-        <v>199.1171915656509</v>
+        <v>199.696542748819</v>
       </c>
       <c r="E178" t="n">
-        <v>207.9573059082031</v>
+        <v>200.1959838867188</v>
       </c>
       <c r="F178" t="n">
-        <v>180962500</v>
+        <v>161746600</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B179" t="n">
-        <v>204.2014963256503</v>
+        <v>201.2647947500858</v>
       </c>
       <c r="C179" t="n">
-        <v>206.9883864105018</v>
+        <v>205.4301320010667</v>
       </c>
       <c r="D179" t="n">
-        <v>199.696542748819</v>
+        <v>199.3169621236104</v>
       </c>
       <c r="E179" t="n">
-        <v>200.1959838867188</v>
+        <v>204.6410064697266</v>
       </c>
       <c r="F179" t="n">
-        <v>161746600</v>
+        <v>158643200</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B180" t="n">
-        <v>201.2647947500858</v>
+        <v>204.6310298517525</v>
       </c>
       <c r="C180" t="n">
-        <v>205.4301320010667</v>
+        <v>206.8385664547524</v>
       </c>
       <c r="D180" t="n">
-        <v>199.3169621236104</v>
+        <v>203.2126188059985</v>
       </c>
       <c r="E180" t="n">
-        <v>204.6410064697266</v>
+        <v>204.9606628417969</v>
       </c>
       <c r="F180" t="n">
-        <v>158643200</v>
+        <v>112001800</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B181" t="n">
-        <v>204.6310298517525</v>
+        <v>208.6864864049894</v>
       </c>
       <c r="C181" t="n">
-        <v>206.8385664547524</v>
+        <v>212.4722588232193</v>
       </c>
       <c r="D181" t="n">
-        <v>203.2126188059985</v>
+        <v>208.1071328472061</v>
       </c>
       <c r="E181" t="n">
-        <v>204.9606628417969</v>
+        <v>212.2125396728516</v>
       </c>
       <c r="F181" t="n">
-        <v>112001800</v>
+        <v>149936700</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B182" t="n">
-        <v>208.6864864049894</v>
+        <v>210.9439520928381</v>
       </c>
       <c r="C182" t="n">
-        <v>212.4722588232193</v>
+        <v>211.2536184019877</v>
       </c>
       <c r="D182" t="n">
-        <v>208.1071328472061</v>
+        <v>207.0583006421773</v>
       </c>
       <c r="E182" t="n">
-        <v>212.2125396728516</v>
+        <v>207.1781768798828</v>
       </c>
       <c r="F182" t="n">
-        <v>149936700</v>
+        <v>125694100</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B183" t="n">
-        <v>210.9439520928381</v>
+        <v>208.2969174543329</v>
       </c>
       <c r="C183" t="n">
-        <v>211.2536184019877</v>
+        <v>208.9761653200819</v>
       </c>
       <c r="D183" t="n">
-        <v>207.0583006421773</v>
+        <v>202.8530121596522</v>
       </c>
       <c r="E183" t="n">
-        <v>207.1781768798828</v>
+        <v>204.4212493896484</v>
       </c>
       <c r="F183" t="n">
-        <v>125694100</v>
+        <v>128363500</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B184" t="n">
-        <v>208.2969174543329</v>
+        <v>207.0982684229139</v>
       </c>
       <c r="C184" t="n">
-        <v>208.9761653200819</v>
+        <v>211.1537281092123</v>
       </c>
       <c r="D184" t="n">
-        <v>202.8530121596522</v>
+        <v>206.2691942875683</v>
       </c>
       <c r="E184" t="n">
-        <v>204.4212493896484</v>
+        <v>210.4545135498047</v>
       </c>
       <c r="F184" t="n">
-        <v>128363500</v>
+        <v>241272000</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B185" t="n">
-        <v>207.0982684229139</v>
+        <v>211.2036686200953</v>
       </c>
       <c r="C185" t="n">
-        <v>211.1537281092123</v>
+        <v>213.7508214450341</v>
       </c>
       <c r="D185" t="n">
-        <v>206.2691942875683</v>
+        <v>207.4878253737282</v>
       </c>
       <c r="E185" t="n">
-        <v>210.4545135498047</v>
+        <v>208.4167785644531</v>
       </c>
       <c r="F185" t="n">
-        <v>241272000</v>
+        <v>122041400</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B186" t="n">
-        <v>211.2036686200953</v>
+        <v>201.9440304014853</v>
       </c>
       <c r="C186" t="n">
-        <v>213.7508214450341</v>
+        <v>203.5422481594977</v>
       </c>
       <c r="D186" t="n">
-        <v>207.4878253737282</v>
+        <v>199.77645766483</v>
       </c>
       <c r="E186" t="n">
-        <v>208.4167785644531</v>
+        <v>199.81640625</v>
       </c>
       <c r="F186" t="n">
-        <v>122041400</v>
+        <v>153496200</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B187" t="n">
-        <v>201.9440304014853</v>
+        <v>199.8963159019567</v>
       </c>
       <c r="C187" t="n">
-        <v>203.5422481594977</v>
+        <v>201.4445864758279</v>
       </c>
       <c r="D187" t="n">
-        <v>199.77645766483</v>
+        <v>196.360279356477</v>
       </c>
       <c r="E187" t="n">
-        <v>199.81640625</v>
+        <v>198.7775726318359</v>
       </c>
       <c r="F187" t="n">
-        <v>153496200</v>
+        <v>151810700</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B188" t="n">
-        <v>199.8963159019567</v>
+        <v>199.8563704571445</v>
       </c>
       <c r="C188" t="n">
-        <v>201.4445864758279</v>
+        <v>200.5755669254449</v>
       </c>
       <c r="D188" t="n">
-        <v>196.360279356477</v>
+        <v>191.9152592982058</v>
       </c>
       <c r="E188" t="n">
-        <v>198.7775726318359</v>
+        <v>195.5212249755859</v>
       </c>
       <c r="F188" t="n">
-        <v>151810700</v>
+        <v>149550000</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B189" t="n">
-        <v>199.8563704571445</v>
+        <v>192.9041409641119</v>
       </c>
       <c r="C189" t="n">
-        <v>200.5755669254449</v>
+        <v>195.331432829306</v>
       </c>
       <c r="D189" t="n">
-        <v>191.9152592982058</v>
+        <v>191.0062707295152</v>
       </c>
       <c r="E189" t="n">
-        <v>195.5212249755859</v>
+        <v>192.3148040771484</v>
       </c>
       <c r="F189" t="n">
-        <v>149550000</v>
+        <v>179304100</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B190" t="n">
-        <v>192.9041409641119</v>
+        <v>193.6333319429392</v>
       </c>
       <c r="C190" t="n">
-        <v>195.331432829306</v>
+        <v>195.9607141929515</v>
       </c>
       <c r="D190" t="n">
-        <v>191.0062707295152</v>
+        <v>189.5878557469149</v>
       </c>
       <c r="E190" t="n">
-        <v>192.3148040771484</v>
+        <v>194.7520751953125</v>
       </c>
       <c r="F190" t="n">
-        <v>179304100</v>
+        <v>148835700</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B191" t="n">
-        <v>193.6333319429392</v>
+        <v>197.0195429632178</v>
       </c>
       <c r="C191" t="n">
-        <v>195.9607141929515</v>
+        <v>200.4057532237791</v>
       </c>
       <c r="D191" t="n">
-        <v>189.5878557469149</v>
+        <v>194.8919188665145</v>
       </c>
       <c r="E191" t="n">
-        <v>194.7520751953125</v>
+        <v>199.8663482666016</v>
       </c>
       <c r="F191" t="n">
-        <v>148835700</v>
+        <v>166476700</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B192" t="n">
-        <v>197.0195429632178</v>
+        <v>195.9806989625188</v>
       </c>
       <c r="C192" t="n">
-        <v>200.4057532237791</v>
+        <v>199.626628404907</v>
       </c>
       <c r="D192" t="n">
-        <v>194.8919188665145</v>
+        <v>193.2337727110923</v>
       </c>
       <c r="E192" t="n">
-        <v>199.8663482666016</v>
+        <v>197.3591613769531</v>
       </c>
       <c r="F192" t="n">
-        <v>166476700</v>
+        <v>146147600</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B193" t="n">
-        <v>195.9806989625188</v>
+        <v>196.9196593659626</v>
       </c>
       <c r="C193" t="n">
-        <v>199.626628404907</v>
+        <v>199.8363939026278</v>
       </c>
       <c r="D193" t="n">
-        <v>193.2337727110923</v>
+        <v>192.1350197738411</v>
       </c>
       <c r="E193" t="n">
-        <v>197.3591613769531</v>
+        <v>194.6122436523438</v>
       </c>
       <c r="F193" t="n">
-        <v>146147600</v>
+        <v>142068700</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B194" t="n">
-        <v>196.9196593659626</v>
+        <v>194.202694284663</v>
       </c>
       <c r="C194" t="n">
-        <v>199.8363939026278</v>
+        <v>197.3292007505161</v>
       </c>
       <c r="D194" t="n">
-        <v>192.1350197738411</v>
+        <v>193.7731822131383</v>
       </c>
       <c r="E194" t="n">
-        <v>194.6122436523438</v>
+        <v>195.3314361572266</v>
       </c>
       <c r="F194" t="n">
-        <v>142068700</v>
+        <v>108999000</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B195" t="n">
-        <v>194.202694284663</v>
+        <v>192.1549837798622</v>
       </c>
       <c r="C195" t="n">
-        <v>197.3292007505161</v>
+        <v>198.1882414262674</v>
       </c>
       <c r="D195" t="n">
-        <v>193.7731822131383</v>
+        <v>190.9263628146717</v>
       </c>
       <c r="E195" t="n">
-        <v>195.3314361572266</v>
+        <v>196.7098846435547</v>
       </c>
       <c r="F195" t="n">
-        <v>108999000</v>
+        <v>124154600</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B196" t="n">
-        <v>192.1549837798622</v>
+        <v>194.9618356993413</v>
       </c>
       <c r="C196" t="n">
-        <v>198.1882414262674</v>
+        <v>204.9306918075912</v>
       </c>
       <c r="D196" t="n">
-        <v>190.9263628146717</v>
+        <v>194.841974703339</v>
       </c>
       <c r="E196" t="n">
-        <v>196.7098846435547</v>
+        <v>203.891845703125</v>
       </c>
       <c r="F196" t="n">
-        <v>124154600</v>
+        <v>147419100</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B197" t="n">
-        <v>194.9618356993413</v>
+        <v>204.2314748595287</v>
       </c>
       <c r="C197" t="n">
-        <v>204.9306918075912</v>
+        <v>204.3613191897594</v>
       </c>
       <c r="D197" t="n">
-        <v>194.841974703339</v>
+        <v>198.7376223952696</v>
       </c>
       <c r="E197" t="n">
-        <v>203.891845703125</v>
+        <v>202.5533447265625</v>
       </c>
       <c r="F197" t="n">
-        <v>147419100</v>
+        <v>132037400</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B198" t="n">
-        <v>204.2314748595287</v>
+        <v>201.7742207048944</v>
       </c>
       <c r="C198" t="n">
-        <v>204.3613191897594</v>
+        <v>210.7641612313501</v>
       </c>
       <c r="D198" t="n">
-        <v>198.7376223952696</v>
+        <v>201.6943082934289</v>
       </c>
       <c r="E198" t="n">
-        <v>202.5533447265625</v>
+        <v>210.7242126464844</v>
       </c>
       <c r="F198" t="n">
-        <v>132037400</v>
+        <v>148421000</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B199" t="n">
-        <v>201.7742207048944</v>
+        <v>208.3069001369788</v>
       </c>
       <c r="C199" t="n">
-        <v>210.7641612313501</v>
+        <v>210.3346451505122</v>
       </c>
       <c r="D199" t="n">
-        <v>201.6943082934289</v>
+        <v>202.7730991138312</v>
       </c>
       <c r="E199" t="n">
-        <v>210.7242126464844</v>
+        <v>203.3025054931641</v>
       </c>
       <c r="F199" t="n">
-        <v>148421000</v>
+        <v>121411000</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B200" t="n">
-        <v>208.3069001369788</v>
+        <v>207.9672957533915</v>
       </c>
       <c r="C200" t="n">
-        <v>210.3346451505122</v>
+        <v>212.3124399374416</v>
       </c>
       <c r="D200" t="n">
-        <v>202.7730991138312</v>
+        <v>203.5722196467825</v>
       </c>
       <c r="E200" t="n">
-        <v>203.3025054931641</v>
+        <v>211.5632781982422</v>
       </c>
       <c r="F200" t="n">
-        <v>121411000</v>
+        <v>124379600</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B201" t="n">
-        <v>207.9672957533915</v>
+        <v>211.7230919717581</v>
       </c>
       <c r="C201" t="n">
-        <v>212.3124399374416</v>
+        <v>213.5710150202495</v>
       </c>
       <c r="D201" t="n">
-        <v>203.5722196467825</v>
+        <v>205.8096955397309</v>
       </c>
       <c r="E201" t="n">
-        <v>211.5632781982422</v>
+        <v>212.2624816894531</v>
       </c>
       <c r="F201" t="n">
-        <v>124379600</v>
+        <v>124797200</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B202" t="n">
-        <v>211.7230919717581</v>
+        <v>209.9350906043833</v>
       </c>
       <c r="C202" t="n">
-        <v>213.5710150202495</v>
+        <v>210.8440771529852</v>
       </c>
       <c r="D202" t="n">
-        <v>205.8096955397309</v>
+        <v>205.6199270055466</v>
       </c>
       <c r="E202" t="n">
-        <v>212.2624816894531</v>
+        <v>207.1681823730469</v>
       </c>
       <c r="F202" t="n">
-        <v>124797200</v>
+        <v>122986100</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B203" t="n">
-        <v>209.9350906043833</v>
+        <v>202.4135048295048</v>
       </c>
       <c r="C203" t="n">
-        <v>210.8440771529852</v>
+        <v>206.4190172896336</v>
       </c>
       <c r="D203" t="n">
-        <v>205.6199270055466</v>
+        <v>197.7487264058434</v>
       </c>
       <c r="E203" t="n">
-        <v>207.1681823730469</v>
+        <v>202.5833129882812</v>
       </c>
       <c r="F203" t="n">
-        <v>122986100</v>
+        <v>144281900</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B204" t="n">
-        <v>202.4135048295048</v>
+        <v>205.639896943356</v>
       </c>
       <c r="C204" t="n">
-        <v>206.4190172896336</v>
+        <v>207.5078172334397</v>
       </c>
       <c r="D204" t="n">
-        <v>197.7487264058434</v>
+        <v>202.0539130969454</v>
       </c>
       <c r="E204" t="n">
-        <v>202.5833129882812</v>
+        <v>203.0527954101562</v>
       </c>
       <c r="F204" t="n">
-        <v>144281900</v>
+        <v>88701500</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B205" t="n">
-        <v>205.639896943356</v>
+        <v>207.308024406286</v>
       </c>
       <c r="C205" t="n">
-        <v>207.5078172334397</v>
+        <v>208.4167843613107</v>
       </c>
       <c r="D205" t="n">
-        <v>202.0539130969454</v>
+        <v>203.7819711309363</v>
       </c>
       <c r="E205" t="n">
-        <v>203.0527954101562</v>
+        <v>207.0583038330078</v>
       </c>
       <c r="F205" t="n">
-        <v>88701500</v>
+        <v>108685600</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B206" t="n">
-        <v>207.308024406286</v>
+        <v>205.579968274895</v>
       </c>
       <c r="C206" t="n">
-        <v>208.4167843613107</v>
+        <v>214.1503804276117</v>
       </c>
       <c r="D206" t="n">
-        <v>203.7819711309363</v>
+        <v>204.7209288682105</v>
       </c>
       <c r="E206" t="n">
-        <v>207.0583038330078</v>
+        <v>211.8229827880859</v>
       </c>
       <c r="F206" t="n">
-        <v>108685600</v>
+        <v>137645600</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B207" t="n">
-        <v>205.579968274895</v>
+        <v>209.2258868865651</v>
       </c>
       <c r="C207" t="n">
-        <v>214.1503804276117</v>
+        <v>210.6342993029147</v>
       </c>
       <c r="D207" t="n">
-        <v>204.7209288682105</v>
+        <v>205.7297989431358</v>
       </c>
       <c r="E207" t="n">
-        <v>211.8229827880859</v>
+        <v>208.5266571044922</v>
       </c>
       <c r="F207" t="n">
-        <v>137645600</v>
+        <v>110505300</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B208" t="n">
-        <v>209.2258868865651</v>
+        <v>207.2181292349697</v>
       </c>
       <c r="C208" t="n">
-        <v>210.6342993029147</v>
+        <v>211.6731509810223</v>
       </c>
       <c r="D208" t="n">
-        <v>205.7297989431358</v>
+        <v>204.5810805834776</v>
       </c>
       <c r="E208" t="n">
-        <v>208.5266571044922</v>
+        <v>206.6088104248047</v>
       </c>
       <c r="F208" t="n">
-        <v>110505300</v>
+        <v>114836800</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B209" t="n">
-        <v>207.2181292349697</v>
+        <v>207.9672962732577</v>
       </c>
       <c r="C209" t="n">
-        <v>211.6731509810223</v>
+        <v>208.5166845983908</v>
       </c>
       <c r="D209" t="n">
-        <v>204.5810805834776</v>
+        <v>195.2215633388429</v>
       </c>
       <c r="E209" t="n">
-        <v>206.6088104248047</v>
+        <v>196.2903594970703</v>
       </c>
       <c r="F209" t="n">
-        <v>114836800</v>
+        <v>154353700</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B210" t="n">
-        <v>207.9672962732577</v>
+        <v>194.782047001347</v>
       </c>
       <c r="C210" t="n">
-        <v>208.5166845983908</v>
+        <v>198.4779084345641</v>
       </c>
       <c r="D210" t="n">
-        <v>195.2215633388429</v>
+        <v>192.5245785077403</v>
       </c>
       <c r="E210" t="n">
-        <v>196.2903594970703</v>
+        <v>196.789794921875</v>
       </c>
       <c r="F210" t="n">
-        <v>154353700</v>
+        <v>134111500</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B211" t="n">
-        <v>194.782047001347</v>
+        <v>195.6311069684468</v>
       </c>
       <c r="C211" t="n">
-        <v>198.4779084345641</v>
+        <v>196.8497446088402</v>
       </c>
       <c r="D211" t="n">
-        <v>192.5245785077403</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="E211" t="n">
-        <v>196.789794921875</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="F211" t="n">
-        <v>134111500</v>
+        <v>147680800</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B212" t="n">
-        <v>195.6311069684468</v>
+        <v>193.2337718176948</v>
       </c>
       <c r="C212" t="n">
-        <v>196.8497446088402</v>
+        <v>197.0295274868271</v>
       </c>
       <c r="D212" t="n">
-        <v>189.7976226806641</v>
+        <v>191.3059363552755</v>
       </c>
       <c r="E212" t="n">
-        <v>189.7976226806641</v>
+        <v>194.8219909667969</v>
       </c>
       <c r="F212" t="n">
-        <v>147680800</v>
+        <v>129010200</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B213" t="n">
-        <v>193.2337718176948</v>
+        <v>198.2182038580375</v>
       </c>
       <c r="C213" t="n">
-        <v>197.0295274868271</v>
+        <v>201.7742223680242</v>
       </c>
       <c r="D213" t="n">
-        <v>191.3059363552755</v>
+        <v>194.7320991825756</v>
       </c>
       <c r="E213" t="n">
-        <v>194.8219909667969</v>
+        <v>200.5256195068359</v>
       </c>
       <c r="F213" t="n">
-        <v>129010200</v>
+        <v>139961200</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B214" t="n">
-        <v>198.2182038580375</v>
+        <v>197.4690486270115</v>
       </c>
       <c r="C214" t="n">
-        <v>201.7742223680242</v>
+        <v>208.506701330784</v>
       </c>
       <c r="D214" t="n">
-        <v>194.7320991825756</v>
+        <v>196.6299911347511</v>
       </c>
       <c r="E214" t="n">
-        <v>200.5256195068359</v>
+        <v>206.4090423583984</v>
       </c>
       <c r="F214" t="n">
-        <v>139961200</v>
+        <v>128406900</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B215" t="n">
-        <v>197.4690486270115</v>
+        <v>211.0638257011038</v>
       </c>
       <c r="C215" t="n">
-        <v>208.506701330784</v>
+        <v>212.8218530009649</v>
       </c>
       <c r="D215" t="n">
-        <v>196.6299911347511</v>
+        <v>208.8163406042335</v>
       </c>
       <c r="E215" t="n">
-        <v>206.4090423583984</v>
+        <v>211.7031097412109</v>
       </c>
       <c r="F215" t="n">
-        <v>128406900</v>
+        <v>134922000</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B216" t="n">
-        <v>211.0638257011038</v>
+        <v>216.6176127852948</v>
       </c>
       <c r="C216" t="n">
-        <v>212.8218530009649</v>
+        <v>221.9716224388697</v>
       </c>
       <c r="D216" t="n">
-        <v>208.8163406042335</v>
+        <v>216.1581202281489</v>
       </c>
       <c r="E216" t="n">
-        <v>211.7031097412109</v>
+        <v>218.9749755859375</v>
       </c>
       <c r="F216" t="n">
-        <v>134922000</v>
+        <v>158187400</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B217" t="n">
-        <v>216.6176127852948</v>
+        <v>221.2823935806188</v>
       </c>
       <c r="C217" t="n">
-        <v>221.9716224388697</v>
+        <v>223.3800524967045</v>
       </c>
       <c r="D217" t="n">
-        <v>216.1581202281489</v>
+        <v>216.7574580038405</v>
       </c>
       <c r="E217" t="n">
-        <v>218.9749755859375</v>
+        <v>218.7452392578125</v>
       </c>
       <c r="F217" t="n">
-        <v>158187400</v>
+        <v>113940600</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B218" t="n">
-        <v>221.2823935806188</v>
+        <v>221.2923777041913</v>
       </c>
       <c r="C218" t="n">
-        <v>223.3800524967045</v>
+        <v>224.5087799247126</v>
       </c>
       <c r="D218" t="n">
-        <v>216.7574580038405</v>
+        <v>220.4133716458871</v>
       </c>
       <c r="E218" t="n">
-        <v>218.7452392578125</v>
+        <v>223.7096862792969</v>
       </c>
       <c r="F218" t="n">
-        <v>113940600</v>
+        <v>105669400</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B219" t="n">
-        <v>221.2923777041913</v>
+        <v>223.1502910726907</v>
       </c>
       <c r="C219" t="n">
-        <v>224.5087799247126</v>
+        <v>223.8894694330602</v>
       </c>
       <c r="D219" t="n">
-        <v>220.4133716458871</v>
+        <v>216.5277120448001</v>
       </c>
       <c r="E219" t="n">
-        <v>223.7096862792969</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="F219" t="n">
-        <v>105669400</v>
+        <v>115846600</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B220" t="n">
-        <v>223.1502910726907</v>
+        <v>221.9216754142795</v>
       </c>
       <c r="C220" t="n">
-        <v>223.8894694330602</v>
+        <v>221.9516406634887</v>
       </c>
       <c r="D220" t="n">
-        <v>216.5277120448001</v>
+        <v>215.9583469538982</v>
       </c>
       <c r="E220" t="n">
-        <v>217.3068389892578</v>
+        <v>217.2568969726562</v>
       </c>
       <c r="F220" t="n">
-        <v>115846600</v>
+        <v>101273100</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B221" t="n">
-        <v>221.9216754142795</v>
+        <v>220.7929293559802</v>
       </c>
       <c r="C221" t="n">
-        <v>221.9516406634887</v>
+        <v>224.848404158734</v>
       </c>
       <c r="D221" t="n">
-        <v>215.9583469538982</v>
+        <v>219.9538719106106</v>
       </c>
       <c r="E221" t="n">
-        <v>217.2568969726562</v>
+        <v>223.8395233154297</v>
       </c>
       <c r="F221" t="n">
-        <v>101273100</v>
+        <v>108783600</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B222" t="n">
-        <v>220.7929293559802</v>
+        <v>224.8084500146858</v>
       </c>
       <c r="C222" t="n">
-        <v>224.848404158734</v>
+        <v>226.9760227961096</v>
       </c>
       <c r="D222" t="n">
-        <v>219.9538719106106</v>
+        <v>223.4599680426375</v>
       </c>
       <c r="E222" t="n">
-        <v>223.8395233154297</v>
+        <v>225.0481872558594</v>
       </c>
       <c r="F222" t="n">
-        <v>108783600</v>
+        <v>98867200</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B223" t="n">
-        <v>224.8084500146858</v>
+        <v>226.5165415533859</v>
       </c>
       <c r="C223" t="n">
-        <v>226.9760227961096</v>
+        <v>227.2357380227387</v>
       </c>
       <c r="D223" t="n">
-        <v>223.4599680426375</v>
+        <v>224.2490744835724</v>
       </c>
       <c r="E223" t="n">
-        <v>225.0481872558594</v>
+        <v>224.9083404541016</v>
       </c>
       <c r="F223" t="n">
-        <v>98867200</v>
+        <v>75680900</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B224" t="n">
-        <v>226.5165415533859</v>
+        <v>225.7274161885591</v>
       </c>
       <c r="C224" t="n">
-        <v>227.2357380227387</v>
+        <v>227.6652502746616</v>
       </c>
       <c r="D224" t="n">
-        <v>224.2490744835724</v>
+        <v>224.6086728983284</v>
       </c>
       <c r="E224" t="n">
-        <v>224.9083404541016</v>
+        <v>224.7584991455078</v>
       </c>
       <c r="F224" t="n">
-        <v>75680900</v>
+        <v>93678700</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B225" t="n">
-        <v>225.7274161885591</v>
+        <v>220.203597915372</v>
       </c>
       <c r="C225" t="n">
-        <v>227.6652502746616</v>
+        <v>221.3922702798686</v>
       </c>
       <c r="D225" t="n">
-        <v>224.6086728983284</v>
+        <v>218.4455705709327</v>
       </c>
       <c r="E225" t="n">
-        <v>224.7584991455078</v>
+        <v>219.4944000244141</v>
       </c>
       <c r="F225" t="n">
-        <v>93678700</v>
+        <v>103128200</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B226" t="n">
-        <v>220.203597915372</v>
+        <v>221.4222404106533</v>
       </c>
       <c r="C226" t="n">
-        <v>221.3922702798686</v>
+        <v>222.6208961374568</v>
       </c>
       <c r="D226" t="n">
-        <v>218.4455705709327</v>
+        <v>216.5177245976465</v>
       </c>
       <c r="E226" t="n">
-        <v>219.4944000244141</v>
+        <v>217.3168334960938</v>
       </c>
       <c r="F226" t="n">
-        <v>103128200</v>
+        <v>96797300</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B227" t="n">
-        <v>221.4222404106533</v>
+        <v>218.1159423024499</v>
       </c>
       <c r="C227" t="n">
-        <v>222.6208961374568</v>
+        <v>219.6142657707553</v>
       </c>
       <c r="D227" t="n">
-        <v>216.5177245976465</v>
+        <v>215.418963107847</v>
       </c>
       <c r="E227" t="n">
-        <v>217.3168334960938</v>
+        <v>216.6076354980469</v>
       </c>
       <c r="F227" t="n">
-        <v>96797300</v>
+        <v>92457000</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B228" t="n">
-        <v>218.1159423024499</v>
+        <v>218.1758724878036</v>
       </c>
       <c r="C228" t="n">
-        <v>219.6142657707553</v>
+        <v>218.4955221432803</v>
       </c>
       <c r="D228" t="n">
-        <v>215.418963107847</v>
+        <v>214.2602556586216</v>
       </c>
       <c r="E228" t="n">
-        <v>216.6076354980469</v>
+        <v>214.4800109863281</v>
       </c>
       <c r="F228" t="n">
-        <v>92457000</v>
+        <v>98869300</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B229" t="n">
-        <v>218.1758724878036</v>
+        <v>215.2891020611033</v>
       </c>
       <c r="C229" t="n">
-        <v>218.4955221432803</v>
+        <v>215.3490325607492</v>
       </c>
       <c r="D229" t="n">
-        <v>214.2602556586216</v>
+        <v>207.0183577918231</v>
       </c>
       <c r="E229" t="n">
-        <v>214.4800109863281</v>
+        <v>208.2469787597656</v>
       </c>
       <c r="F229" t="n">
-        <v>98869300</v>
+        <v>135187300</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B230" t="n">
-        <v>215.2891020611033</v>
+        <v>210.7941279013131</v>
       </c>
       <c r="C230" t="n">
-        <v>215.3490325607492</v>
+        <v>214.4899893165327</v>
       </c>
       <c r="D230" t="n">
-        <v>207.0183577918231</v>
+        <v>209.8751580258669</v>
       </c>
       <c r="E230" t="n">
-        <v>208.2469787597656</v>
+        <v>212.8118743896484</v>
       </c>
       <c r="F230" t="n">
-        <v>135187300</v>
+        <v>122309000</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B231" t="n">
-        <v>210.7941279013131</v>
+        <v>212.4023240594531</v>
       </c>
       <c r="C231" t="n">
-        <v>214.4899893165327</v>
+        <v>213.3612577394914</v>
       </c>
       <c r="D231" t="n">
-        <v>209.8751580258669</v>
+        <v>208.9961318803605</v>
       </c>
       <c r="E231" t="n">
-        <v>212.8118743896484</v>
+        <v>209.4256591796875</v>
       </c>
       <c r="F231" t="n">
-        <v>122309000</v>
+        <v>179900000</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B232" t="n">
-        <v>212.4023240594531</v>
+        <v>222.6109016432552</v>
       </c>
       <c r="C232" t="n">
-        <v>213.3612577394914</v>
+        <v>230.2123962709879</v>
       </c>
       <c r="D232" t="n">
-        <v>208.9961318803605</v>
+        <v>220.6530857022795</v>
       </c>
       <c r="E232" t="n">
-        <v>209.4256591796875</v>
+        <v>227.7251739501953</v>
       </c>
       <c r="F232" t="n">
-        <v>179900000</v>
+        <v>298909800</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B233" t="n">
-        <v>222.6109016432552</v>
+        <v>227.1058715337123</v>
       </c>
       <c r="C233" t="n">
-        <v>230.2123962709879</v>
+        <v>229.003741733446</v>
       </c>
       <c r="D233" t="n">
-        <v>220.6530857022795</v>
+        <v>216.5676606288883</v>
       </c>
       <c r="E233" t="n">
-        <v>227.7251739501953</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="F233" t="n">
-        <v>298909800</v>
+        <v>195116400</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B234" t="n">
-        <v>227.1058715337123</v>
+        <v>218.6253647857836</v>
       </c>
       <c r="C234" t="n">
-        <v>229.003741733446</v>
+        <v>221.0526567078369</v>
       </c>
       <c r="D234" t="n">
-        <v>216.5676606288883</v>
+        <v>215.9683494434545</v>
       </c>
       <c r="E234" t="n">
-        <v>217.3068389892578</v>
+        <v>220.5332336425781</v>
       </c>
       <c r="F234" t="n">
-        <v>195116400</v>
+        <v>124702700</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B235" t="n">
-        <v>218.6253647857836</v>
+        <v>216.5077444634259</v>
       </c>
       <c r="C235" t="n">
-        <v>221.0526567078369</v>
+        <v>220.1636574397174</v>
       </c>
       <c r="D235" t="n">
-        <v>215.9683494434545</v>
+        <v>214.8595947199138</v>
       </c>
       <c r="E235" t="n">
-        <v>220.5332336425781</v>
+        <v>217.1969757080078</v>
       </c>
       <c r="F235" t="n">
-        <v>124702700</v>
+        <v>109756200</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B236" t="n">
-        <v>216.5077444634259</v>
+        <v>218.5454508199983</v>
       </c>
       <c r="C236" t="n">
-        <v>220.1636574397174</v>
+        <v>227.6952163087265</v>
       </c>
       <c r="D236" t="n">
-        <v>214.8595947199138</v>
+        <v>218.2357997469377</v>
       </c>
       <c r="E236" t="n">
-        <v>217.1969757080078</v>
+        <v>224.1591796875</v>
       </c>
       <c r="F236" t="n">
-        <v>109756200</v>
+        <v>157104700</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B237" t="n">
-        <v>218.5454508199983</v>
+        <v>225.7673797205316</v>
       </c>
       <c r="C237" t="n">
-        <v>227.6952163087265</v>
+        <v>230.1424737915274</v>
       </c>
       <c r="D237" t="n">
-        <v>218.2357997469377</v>
+        <v>224.4987949430455</v>
       </c>
       <c r="E237" t="n">
-        <v>224.1591796875</v>
+        <v>228.1946563720703</v>
       </c>
       <c r="F237" t="n">
-        <v>157104700</v>
+        <v>134681600</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B238" t="n">
-        <v>225.7673797205316</v>
+        <v>230.8317036041433</v>
       </c>
       <c r="C238" t="n">
-        <v>230.1424737915274</v>
+        <v>234.4975997614268</v>
       </c>
       <c r="D238" t="n">
-        <v>224.4987949430455</v>
+        <v>229.3733440032785</v>
       </c>
       <c r="E238" t="n">
-        <v>228.1946563720703</v>
+        <v>230.1025238037109</v>
       </c>
       <c r="F238" t="n">
-        <v>134681600</v>
+        <v>135352400</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B239" t="n">
-        <v>230.8317036041433</v>
+        <v>232.8494477166676</v>
       </c>
       <c r="C239" t="n">
-        <v>234.4975997614268</v>
+        <v>233.4487831783142</v>
       </c>
       <c r="D239" t="n">
-        <v>229.3733440032785</v>
+        <v>224.5986856128386</v>
       </c>
       <c r="E239" t="n">
-        <v>230.1025238037109</v>
+        <v>225.4776916503906</v>
       </c>
       <c r="F239" t="n">
-        <v>135352400</v>
+        <v>122965600</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B240" t="n">
-        <v>232.8494477166676</v>
+        <v>225.0281992525124</v>
       </c>
       <c r="C240" t="n">
-        <v>233.4487831783142</v>
+        <v>225.9271872095504</v>
       </c>
       <c r="D240" t="n">
-        <v>224.5986856128386</v>
+        <v>223.2102414251123</v>
       </c>
       <c r="E240" t="n">
-        <v>225.4776916503906</v>
+        <v>223.4199981689453</v>
       </c>
       <c r="F240" t="n">
-        <v>122965600</v>
+        <v>82955500</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,25 +6683,25 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B241" t="n">
-        <v>225.0281992525124</v>
+        <v>220.5299987792969</v>
       </c>
       <c r="C241" t="n">
-        <v>225.9271872095504</v>
+        <v>220.9900054931641</v>
       </c>
       <c r="D241" t="n">
-        <v>223.2102414251123</v>
+        <v>217.1999969482422</v>
       </c>
       <c r="E241" t="n">
-        <v>223.4199981689453</v>
+        <v>218.3600006103516</v>
       </c>
       <c r="F241" t="n">
-        <v>82955500</v>
+        <v>105768000</v>
       </c>
       <c r="G241" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -6709,25 +6709,25 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B242" t="n">
-        <v>220.5299987792969</v>
+        <v>221.2400054931641</v>
       </c>
       <c r="C242" t="n">
-        <v>220.9900054931641</v>
+        <v>222</v>
       </c>
       <c r="D242" t="n">
-        <v>217.1999969482422</v>
+        <v>218.1499938964844</v>
       </c>
       <c r="E242" t="n">
-        <v>218.3600006103516</v>
+        <v>218.2899932861328</v>
       </c>
       <c r="F242" t="n">
-        <v>105768000</v>
+        <v>89060100</v>
       </c>
       <c r="G242" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B243" t="n">
-        <v>221.2400054931641</v>
+        <v>211.2400054931641</v>
       </c>
       <c r="C243" t="n">
-        <v>222</v>
+        <v>212.7700042724609</v>
       </c>
       <c r="D243" t="n">
-        <v>218.1499938964844</v>
+        <v>208.9299926757812</v>
       </c>
       <c r="E243" t="n">
-        <v>218.2899932861328</v>
+        <v>210.9600067138672</v>
       </c>
       <c r="F243" t="n">
-        <v>89060100</v>
+        <v>132267200</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B244" t="n">
-        <v>211.2400054931641</v>
+        <v>213.3800048828125</v>
       </c>
       <c r="C244" t="n">
-        <v>212.7700042724609</v>
+        <v>213.9400024414062</v>
       </c>
       <c r="D244" t="n">
-        <v>208.9299926757812</v>
+        <v>211.1600036621094</v>
       </c>
       <c r="E244" t="n">
-        <v>210.9600067138672</v>
+        <v>212.1699981689453</v>
       </c>
       <c r="F244" t="n">
-        <v>132267200</v>
+        <v>88059700</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B245" t="n">
-        <v>213.3800048828125</v>
+        <v>214.1399993896484</v>
       </c>
       <c r="C245" t="n">
-        <v>213.9400024414062</v>
+        <v>216.7599945068359</v>
       </c>
       <c r="D245" t="n">
-        <v>211.1600036621094</v>
+        <v>212.5</v>
       </c>
       <c r="E245" t="n">
-        <v>212.1699981689453</v>
+        <v>213.8999938964844</v>
       </c>
       <c r="F245" t="n">
-        <v>88059700</v>
+        <v>96563600</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B246" t="n">
-        <v>214.1399993896484</v>
+        <v>218.3800048828125</v>
       </c>
       <c r="C246" t="n">
-        <v>216.7599945068359</v>
+        <v>219.9100036621094</v>
       </c>
       <c r="D246" t="n">
-        <v>212.5</v>
+        <v>217.1499938964844</v>
       </c>
       <c r="E246" t="n">
-        <v>213.8999938964844</v>
+        <v>219.3399963378906</v>
       </c>
       <c r="F246" t="n">
-        <v>96563600</v>
+        <v>94191300</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B247" t="n">
-        <v>218.3800048828125</v>
+        <v>219.3500061035156</v>
       </c>
       <c r="C247" t="n">
-        <v>219.9100036621094</v>
+        <v>222.7299957275391</v>
       </c>
       <c r="D247" t="n">
-        <v>217.1499938964844</v>
+        <v>218.0299987792969</v>
       </c>
       <c r="E247" t="n">
-        <v>219.3399963378906</v>
+        <v>222.2700042724609</v>
       </c>
       <c r="F247" t="n">
-        <v>94191300</v>
+        <v>190287400</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B248" t="n">
-        <v>219.3500061035156</v>
+        <v>222.9400024414062</v>
       </c>
       <c r="C248" t="n">
-        <v>222.7299957275391</v>
+        <v>228.5</v>
       </c>
       <c r="D248" t="n">
-        <v>218.0299987792969</v>
+        <v>221.5599975585938</v>
       </c>
       <c r="E248" t="n">
-        <v>222.2700042724609</v>
+        <v>227.3800048828125</v>
       </c>
       <c r="F248" t="n">
-        <v>190287400</v>
+        <v>109806100</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B249" t="n">
-        <v>222.9400024414062</v>
+        <v>226.8500061035156</v>
       </c>
       <c r="C249" t="n">
-        <v>228.5</v>
+        <v>229.9799957275391</v>
       </c>
       <c r="D249" t="n">
-        <v>221.5599975585938</v>
+        <v>226.5</v>
       </c>
       <c r="E249" t="n">
-        <v>227.3800048828125</v>
+        <v>228.8699951171875</v>
       </c>
       <c r="F249" t="n">
-        <v>109806100</v>
+        <v>95746700</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B250" t="n">
-        <v>226.8500061035156</v>
+        <v>228.0299987792969</v>
       </c>
       <c r="C250" t="n">
-        <v>229.9799957275391</v>
+        <v>228.9499969482422</v>
       </c>
       <c r="D250" t="n">
-        <v>226.5</v>
+        <v>224.0200042724609</v>
       </c>
       <c r="E250" t="n">
-        <v>228.8699951171875</v>
+        <v>225.5099945068359</v>
       </c>
       <c r="F250" t="n">
-        <v>95746700</v>
+        <v>89547300</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B251" t="n">
-        <v>228.0299987792969</v>
+        <v>222.0800018310547</v>
       </c>
       <c r="C251" t="n">
-        <v>228.9499969482422</v>
+        <v>224.9400024414062</v>
       </c>
       <c r="D251" t="n">
-        <v>224.0200042724609</v>
+        <v>221.0899963378906</v>
       </c>
       <c r="E251" t="n">
-        <v>225.5099945068359</v>
+        <v>224.5800018310547</v>
       </c>
       <c r="F251" t="n">
-        <v>89547300</v>
+        <v>77469900</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B252" t="n">
-        <v>222.0800018310547</v>
+        <v>225.1300048828125</v>
       </c>
       <c r="C252" t="n">
-        <v>224.9400024414062</v>
+        <v>226.9400024414062</v>
       </c>
       <c r="D252" t="n">
-        <v>221.0899963378906</v>
+        <v>223.1300048828125</v>
       </c>
       <c r="E252" t="n">
-        <v>224.5800018310547</v>
+        <v>225.0700073242188</v>
       </c>
       <c r="F252" t="n">
-        <v>77305200</v>
+        <v>89808400</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10884,37 +10884,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>225.07</v>
+      </c>
+      <c r="D2" t="n">
         <v>224.58</v>
       </c>
-      <c r="D2" t="n">
-        <v>225.51</v>
-      </c>
       <c r="E2" t="n">
-        <v>222.116</v>
+        <v>225.15</v>
       </c>
       <c r="F2" t="n">
-        <v>224.9</v>
+        <v>226.94</v>
       </c>
       <c r="G2" t="n">
-        <v>221.0908</v>
+        <v>223.1329</v>
       </c>
       <c r="H2" t="n">
-        <v>76420503</v>
+        <v>87931936</v>
       </c>
       <c r="I2" t="n">
-        <v>126051807</v>
+        <v>125195556</v>
       </c>
       <c r="J2" t="n">
-        <v>5422933082112</v>
+        <v>5434765213696</v>
       </c>
       <c r="K2" t="n">
-        <v>28.5</v>
+        <v>28.453857</v>
       </c>
       <c r="L2" t="n">
-        <v>14.320303</v>
+        <v>14.351548</v>
       </c>
       <c r="M2" t="n">
-        <v>7.88</v>
+        <v>7.91</v>
       </c>
       <c r="N2" t="n">
         <v>236.54</v>
@@ -10926,7 +10926,7 @@
         <v>2.217</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="R2" t="n">
         <v>0.63663</v>
@@ -10950,7 +10950,7 @@
         <v>9.483000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>23.682379</v>
+        <v>23.73405</v>
       </c>
       <c r="Z2" t="n">
         <v>1.278</v>
@@ -10962,7 +10962,7 @@
         <v>302970011648</v>
       </c>
       <c r="AC2" t="n">
-        <v>5388768903168</v>
+        <v>5400577966080</v>
       </c>
       <c r="AD2" t="n">
         <v>201266003968</v>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-25 14:29:07</t>
+          <t>2026-09-26 14:49:40</t>
         </is>
       </c>
     </row>

--- a/data/NVDA_data.xlsx
+++ b/data/NVDA_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B2" t="n">
-        <v>177.7441579191998</v>
+        <v>179.9987400973632</v>
       </c>
       <c r="C2" t="n">
-        <v>179.3403398828169</v>
+        <v>183.5602146114836</v>
       </c>
       <c r="D2" t="n">
-        <v>174.5118962929188</v>
+        <v>179.8890176259668</v>
       </c>
       <c r="E2" t="n">
-        <v>177.7641143798828</v>
+        <v>181.4153594970703</v>
       </c>
       <c r="F2" t="n">
-        <v>148573700</v>
+        <v>193063500</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B3" t="n">
-        <v>179.9987400973632</v>
+        <v>181.6448190078555</v>
       </c>
       <c r="C3" t="n">
-        <v>183.5602146114836</v>
+        <v>186.9022276338177</v>
       </c>
       <c r="D3" t="n">
-        <v>179.8890176259668</v>
+        <v>181.0462469572146</v>
       </c>
       <c r="E3" t="n">
-        <v>181.4153594970703</v>
+        <v>186.1340637207031</v>
       </c>
       <c r="F3" t="n">
-        <v>193063500</v>
+        <v>236981000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B4" t="n">
-        <v>181.6448041170831</v>
+        <v>184.7972757932568</v>
       </c>
       <c r="C4" t="n">
-        <v>186.9022123120565</v>
+        <v>187.690338609038</v>
       </c>
       <c r="D4" t="n">
-        <v>181.0462321155116</v>
+        <v>183.4604668683245</v>
       </c>
       <c r="E4" t="n">
-        <v>186.1340484619141</v>
+        <v>186.7924957275391</v>
       </c>
       <c r="F4" t="n">
-        <v>236981000</v>
+        <v>173844900</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B5" t="n">
-        <v>184.7972757932568</v>
+        <v>189.146847340247</v>
       </c>
       <c r="C5" t="n">
-        <v>187.690338609038</v>
+        <v>190.59337868299</v>
       </c>
       <c r="D5" t="n">
-        <v>183.4604668683245</v>
+        <v>187.6105195355423</v>
       </c>
       <c r="E5" t="n">
-        <v>186.7924957275391</v>
+        <v>188.4385375976562</v>
       </c>
       <c r="F5" t="n">
-        <v>173844900</v>
+        <v>136805800</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B6" t="n">
-        <v>189.146847340247</v>
+        <v>188.7378247179256</v>
       </c>
       <c r="C6" t="n">
-        <v>190.59337868299</v>
+        <v>189.9050265070322</v>
       </c>
       <c r="D6" t="n">
-        <v>187.6105195355423</v>
+        <v>184.9369333277354</v>
       </c>
       <c r="E6" t="n">
-        <v>188.4385375976562</v>
+        <v>187.1715698242188</v>
       </c>
       <c r="F6" t="n">
-        <v>136805800</v>
+        <v>137596900</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B7" t="n">
-        <v>188.7378247179256</v>
+        <v>185.0566446584491</v>
       </c>
       <c r="C7" t="n">
-        <v>189.9050265070322</v>
+        <v>186.7825055997528</v>
       </c>
       <c r="D7" t="n">
-        <v>184.9369333277354</v>
+        <v>182.8918329061041</v>
       </c>
       <c r="E7" t="n">
-        <v>187.1715698242188</v>
+        <v>185.0965423583984</v>
       </c>
       <c r="F7" t="n">
-        <v>137596900</v>
+        <v>157678100</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B8" t="n">
-        <v>185.0566446584491</v>
+        <v>185.784875425114</v>
       </c>
       <c r="C8" t="n">
-        <v>186.7825055997528</v>
+        <v>188.6081130865945</v>
       </c>
       <c r="D8" t="n">
-        <v>182.8918329061041</v>
+        <v>183.5602097539322</v>
       </c>
       <c r="E8" t="n">
-        <v>185.0965423583984</v>
+        <v>184.5977172851562</v>
       </c>
       <c r="F8" t="n">
-        <v>157678100</v>
+        <v>140088000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B9" t="n">
-        <v>185.7849061389523</v>
+        <v>186.1240974206304</v>
       </c>
       <c r="C9" t="n">
-        <v>188.6081442671687</v>
+        <v>189.1468543796426</v>
       </c>
       <c r="D9" t="n">
-        <v>183.5602400999903</v>
+        <v>186.0941551173159</v>
       </c>
       <c r="E9" t="n">
-        <v>184.5977478027344</v>
+        <v>188.6580200195312</v>
       </c>
       <c r="F9" t="n">
-        <v>140088000</v>
+        <v>130168900</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B10" t="n">
-        <v>186.1240823667868</v>
+        <v>191.7705422839889</v>
       </c>
       <c r="C10" t="n">
-        <v>189.1468390813163</v>
+        <v>194.8332119113436</v>
       </c>
       <c r="D10" t="n">
-        <v>186.094140065894</v>
+        <v>190.6033405552435</v>
       </c>
       <c r="E10" t="n">
-        <v>188.6580047607422</v>
+        <v>192.1097412109375</v>
       </c>
       <c r="F10" t="n">
-        <v>130168900</v>
+        <v>182997200</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B11" t="n">
-        <v>191.7705422839889</v>
+        <v>193.0474982342752</v>
       </c>
       <c r="C11" t="n">
-        <v>194.8332119113436</v>
+        <v>195.1524558626357</v>
       </c>
       <c r="D11" t="n">
-        <v>190.6033405552435</v>
+        <v>181.6148965961679</v>
       </c>
       <c r="E11" t="n">
-        <v>192.1097412109375</v>
+        <v>182.7222442626953</v>
       </c>
       <c r="F11" t="n">
-        <v>182997200</v>
+        <v>268774400</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B12" t="n">
-        <v>193.0474982342752</v>
+        <v>187.52074924116</v>
       </c>
       <c r="C12" t="n">
-        <v>195.1524558626357</v>
+        <v>189.6556339904095</v>
       </c>
       <c r="D12" t="n">
-        <v>181.6148965961679</v>
+        <v>185.5155586605101</v>
       </c>
       <c r="E12" t="n">
-        <v>182.7222442626953</v>
+        <v>187.8699188232422</v>
       </c>
       <c r="F12" t="n">
-        <v>268774400</v>
+        <v>153482800</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B13" t="n">
-        <v>187.5207340107304</v>
+        <v>184.3283927796865</v>
       </c>
       <c r="C13" t="n">
-        <v>189.6556185865847</v>
+        <v>184.3583198600852</v>
       </c>
       <c r="D13" t="n">
-        <v>185.5155435929421</v>
+        <v>179.2705030798172</v>
       </c>
       <c r="E13" t="n">
-        <v>187.8699035644531</v>
+        <v>179.5997161865234</v>
       </c>
       <c r="F13" t="n">
-        <v>153482800</v>
+        <v>205641400</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B14" t="n">
-        <v>184.3283927796865</v>
+        <v>184.3582990595379</v>
       </c>
       <c r="C14" t="n">
-        <v>184.3583198600852</v>
+        <v>184.4281238318171</v>
       </c>
       <c r="D14" t="n">
-        <v>179.2705030798172</v>
+        <v>176.8662395170747</v>
       </c>
       <c r="E14" t="n">
-        <v>179.5997161865234</v>
+        <v>179.4001770019531</v>
       </c>
       <c r="F14" t="n">
-        <v>205641400</v>
+        <v>214450500</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B15" t="n">
-        <v>184.3583147400375</v>
+        <v>181.7944368108431</v>
       </c>
       <c r="C15" t="n">
-        <v>184.4281395182556</v>
+        <v>182.8419301869027</v>
       </c>
       <c r="D15" t="n">
-        <v>176.866254560341</v>
+        <v>179.3403251298876</v>
       </c>
       <c r="E15" t="n">
-        <v>179.4001922607422</v>
+        <v>181.3754425048828</v>
       </c>
       <c r="F15" t="n">
-        <v>214450500</v>
+        <v>179723300</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B16" t="n">
-        <v>181.7944368108431</v>
+        <v>179.7493465774322</v>
       </c>
       <c r="C16" t="n">
-        <v>182.8419301869027</v>
+        <v>183.6599908268075</v>
       </c>
       <c r="D16" t="n">
-        <v>179.3403251298876</v>
+        <v>179.3203816221287</v>
       </c>
       <c r="E16" t="n">
-        <v>181.3754425048828</v>
+        <v>182.7820892333984</v>
       </c>
       <c r="F16" t="n">
-        <v>179723300</v>
+        <v>173135200</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B17" t="n">
-        <v>179.7493315718189</v>
+        <v>182.6923102950553</v>
       </c>
       <c r="C17" t="n">
-        <v>183.6599754947305</v>
+        <v>184.7573549226016</v>
       </c>
       <c r="D17" t="n">
-        <v>179.3203666523256</v>
+        <v>181.2956472677441</v>
       </c>
       <c r="E17" t="n">
-        <v>182.7820739746094</v>
+        <v>182.2034759521484</v>
       </c>
       <c r="F17" t="n">
-        <v>173135200</v>
+        <v>128544700</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B18" t="n">
-        <v>182.6923102950553</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="C18" t="n">
-        <v>184.7573549226016</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="D18" t="n">
-        <v>181.2956472677441</v>
+        <v>179.3702701372806</v>
       </c>
       <c r="E18" t="n">
-        <v>182.2034759521484</v>
+        <v>180.7270202636719</v>
       </c>
       <c r="F18" t="n">
-        <v>128544700</v>
+        <v>124240200</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B19" t="n">
-        <v>182.3531141136141</v>
+        <v>180.7070509305708</v>
       </c>
       <c r="C19" t="n">
-        <v>182.3531141136141</v>
+        <v>183.0015566720687</v>
       </c>
       <c r="D19" t="n">
-        <v>179.3702701372806</v>
+        <v>176.3375148363812</v>
       </c>
       <c r="E19" t="n">
-        <v>180.7270202636719</v>
+        <v>179.8491058349609</v>
       </c>
       <c r="F19" t="n">
-        <v>124240200</v>
+        <v>162249600</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B20" t="n">
-        <v>180.7070662621498</v>
+        <v>179.988793025541</v>
       </c>
       <c r="C20" t="n">
-        <v>183.0015721983185</v>
+        <v>182.5925557149365</v>
       </c>
       <c r="D20" t="n">
-        <v>176.3375297972393</v>
+        <v>179.3602938591047</v>
       </c>
       <c r="E20" t="n">
-        <v>179.84912109375</v>
+        <v>181.7246398925781</v>
       </c>
       <c r="F20" t="n">
-        <v>162249600</v>
+        <v>111363700</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B21" t="n">
-        <v>179.988777912505</v>
+        <v>183.400590081168</v>
       </c>
       <c r="C21" t="n">
-        <v>182.5925403832715</v>
+        <v>187.0219186862977</v>
       </c>
       <c r="D21" t="n">
-        <v>179.3602787988416</v>
+        <v>183.0614063875393</v>
       </c>
       <c r="E21" t="n">
-        <v>181.7246246337891</v>
+        <v>185.8148040771484</v>
       </c>
       <c r="F21" t="n">
-        <v>111363700</v>
+        <v>131296700</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B22" t="n">
-        <v>183.400590081168</v>
+        <v>189.5359184602369</v>
       </c>
       <c r="C22" t="n">
-        <v>187.0219186862977</v>
+        <v>191.5411089646758</v>
       </c>
       <c r="D22" t="n">
-        <v>183.0614063875393</v>
+        <v>187.9796341631504</v>
       </c>
       <c r="E22" t="n">
-        <v>185.8148040771484</v>
+        <v>191.0323333740234</v>
       </c>
       <c r="F22" t="n">
-        <v>131296700</v>
+        <v>153452700</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B23" t="n">
-        <v>189.5359033209746</v>
+        <v>192.5886067715161</v>
       </c>
       <c r="C23" t="n">
-        <v>191.541093665248</v>
+        <v>202.6644582837766</v>
       </c>
       <c r="D23" t="n">
-        <v>187.979619148197</v>
+        <v>191.4513320204045</v>
       </c>
       <c r="E23" t="n">
-        <v>191.0323181152344</v>
+        <v>200.5495300292969</v>
       </c>
       <c r="F23" t="n">
-        <v>153452700</v>
+        <v>297986200</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B24" t="n">
-        <v>192.588592118433</v>
+        <v>207.482891187405</v>
       </c>
       <c r="C24" t="n">
-        <v>202.6644428640734</v>
+        <v>211.6828353303786</v>
       </c>
       <c r="D24" t="n">
-        <v>191.4513174538508</v>
+        <v>204.2905427296142</v>
       </c>
       <c r="E24" t="n">
-        <v>200.5495147705078</v>
+        <v>206.5451354980469</v>
       </c>
       <c r="F24" t="n">
-        <v>297986200</v>
+        <v>308829600</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B25" t="n">
-        <v>207.482921843539</v>
+        <v>204.6596525726598</v>
       </c>
       <c r="C25" t="n">
-        <v>211.6828666070652</v>
+        <v>205.6672482532724</v>
       </c>
       <c r="D25" t="n">
-        <v>204.2905729140704</v>
+        <v>200.9286015136062</v>
       </c>
       <c r="E25" t="n">
-        <v>206.545166015625</v>
+        <v>202.4050598144531</v>
       </c>
       <c r="F25" t="n">
-        <v>308829600</v>
+        <v>178864400</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B26" t="n">
-        <v>204.6596680014167</v>
+        <v>205.9565848804529</v>
       </c>
       <c r="C26" t="n">
-        <v>205.6672637579894</v>
+        <v>207.4729563679188</v>
       </c>
       <c r="D26" t="n">
-        <v>200.9286166610889</v>
+        <v>201.5870633589687</v>
       </c>
       <c r="E26" t="n">
-        <v>202.4050750732422</v>
+        <v>202.0060577392578</v>
       </c>
       <c r="F26" t="n">
-        <v>178864400</v>
+        <v>179802200</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B27" t="n">
-        <v>205.9565693232556</v>
+        <v>207.5826726752522</v>
       </c>
       <c r="C27" t="n">
-        <v>207.4729406961805</v>
+        <v>210.8348755139714</v>
       </c>
       <c r="D27" t="n">
-        <v>201.5870481318289</v>
+        <v>205.0686914304077</v>
       </c>
       <c r="E27" t="n">
-        <v>202.0060424804688</v>
+        <v>206.3855438232422</v>
       </c>
       <c r="F27" t="n">
-        <v>179802200</v>
+        <v>180267300</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B28" t="n">
-        <v>207.5826573279554</v>
+        <v>202.5148147488263</v>
       </c>
       <c r="C28" t="n">
-        <v>210.834859926228</v>
+        <v>203.4824975937368</v>
       </c>
       <c r="D28" t="n">
-        <v>205.068676268978</v>
+        <v>197.4569251230167</v>
       </c>
       <c r="E28" t="n">
-        <v>206.3855285644531</v>
+        <v>198.2151184082031</v>
       </c>
       <c r="F28" t="n">
-        <v>180267300</v>
+        <v>188919300</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B29" t="n">
-        <v>202.5147991590425</v>
+        <v>198.2949120548774</v>
       </c>
       <c r="C29" t="n">
-        <v>203.4824819294599</v>
+        <v>202.4349867997753</v>
       </c>
       <c r="D29" t="n">
-        <v>197.4569099225941</v>
+        <v>194.1847491650603</v>
       </c>
       <c r="E29" t="n">
-        <v>198.2151031494141</v>
+        <v>194.7434234619141</v>
       </c>
       <c r="F29" t="n">
-        <v>188919300</v>
+        <v>171350300</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B30" t="n">
-        <v>198.2949431289972</v>
+        <v>195.9505410878136</v>
       </c>
       <c r="C30" t="n">
-        <v>202.4350185226721</v>
+        <v>197.1476699621838</v>
       </c>
       <c r="D30" t="n">
-        <v>194.1847795950905</v>
+        <v>185.9345440647224</v>
       </c>
       <c r="E30" t="n">
-        <v>194.7434539794922</v>
+        <v>187.6304779052734</v>
       </c>
       <c r="F30" t="n">
-        <v>171350300</v>
+        <v>223029800</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B31" t="n">
-        <v>195.9505570232203</v>
+        <v>184.4580548583195</v>
       </c>
       <c r="C31" t="n">
-        <v>197.1476859949454</v>
+        <v>187.8698939350823</v>
       </c>
       <c r="D31" t="n">
-        <v>185.934559185592</v>
+        <v>178.4823816093971</v>
       </c>
       <c r="E31" t="n">
-        <v>187.6304931640625</v>
+        <v>187.7002868652344</v>
       </c>
       <c r="F31" t="n">
-        <v>223029800</v>
+        <v>264942300</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B32" t="n">
-        <v>184.4580698535366</v>
+        <v>194.6436788693004</v>
       </c>
       <c r="C32" t="n">
-        <v>187.8699092076593</v>
+        <v>199.4621367771523</v>
       </c>
       <c r="D32" t="n">
-        <v>178.4823961188316</v>
+        <v>193.3268264223904</v>
       </c>
       <c r="E32" t="n">
-        <v>187.7003021240234</v>
+        <v>198.5742645263672</v>
       </c>
       <c r="F32" t="n">
-        <v>264942300</v>
+        <v>198897100</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B33" t="n">
-        <v>194.6436788693004</v>
+        <v>194.6935689756818</v>
       </c>
       <c r="C33" t="n">
-        <v>199.4621367771523</v>
+        <v>194.9529420926121</v>
       </c>
       <c r="D33" t="n">
-        <v>193.3268264223904</v>
+        <v>190.8427938118383</v>
       </c>
       <c r="E33" t="n">
-        <v>198.5742645263672</v>
+        <v>192.6983489990234</v>
       </c>
       <c r="F33" t="n">
-        <v>198897100</v>
+        <v>176483300</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B34" t="n">
-        <v>194.6935535589016</v>
+        <v>195.2522164876445</v>
       </c>
       <c r="C34" t="n">
-        <v>194.9529266552934</v>
+        <v>195.4218083488666</v>
       </c>
       <c r="D34" t="n">
-        <v>190.8427786999811</v>
+        <v>190.673190567689</v>
       </c>
       <c r="E34" t="n">
-        <v>192.6983337402344</v>
+        <v>193.3368072509766</v>
       </c>
       <c r="F34" t="n">
-        <v>176483300</v>
+        <v>154935300</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B35" t="n">
-        <v>195.2522164876445</v>
+        <v>190.5933947337238</v>
       </c>
       <c r="C35" t="n">
-        <v>195.4218083488666</v>
+        <v>190.9824620272586</v>
       </c>
       <c r="D35" t="n">
-        <v>190.673190567689</v>
+        <v>183.4106057333689</v>
       </c>
       <c r="E35" t="n">
-        <v>193.3368072509766</v>
+        <v>186.4134063720703</v>
       </c>
       <c r="F35" t="n">
-        <v>154935300</v>
+        <v>207423100</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B36" t="n">
-        <v>190.5933791327836</v>
+        <v>182.4229435613052</v>
       </c>
       <c r="C36" t="n">
-        <v>190.9824463944715</v>
+        <v>190.553458007553</v>
       </c>
       <c r="D36" t="n">
-        <v>183.4105907203728</v>
+        <v>180.1483942490048</v>
       </c>
       <c r="E36" t="n">
-        <v>186.4133911132812</v>
+        <v>189.7154693603516</v>
       </c>
       <c r="F36" t="n">
-        <v>207423100</v>
+        <v>186591900</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B37" t="n">
-        <v>182.4229435613052</v>
+        <v>185.5255230789849</v>
       </c>
       <c r="C37" t="n">
-        <v>190.553458007553</v>
+        <v>188.5482800008962</v>
       </c>
       <c r="D37" t="n">
-        <v>180.1483942490048</v>
+        <v>183.8794727552066</v>
       </c>
       <c r="E37" t="n">
-        <v>189.7154693603516</v>
+        <v>186.1540222167969</v>
       </c>
       <c r="F37" t="n">
-        <v>186591900</v>
+        <v>173628900</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B38" t="n">
-        <v>185.5255230789849</v>
+        <v>182.941705155915</v>
       </c>
       <c r="C38" t="n">
-        <v>188.5482800008962</v>
+        <v>184.3583093626339</v>
       </c>
       <c r="D38" t="n">
-        <v>183.8794727552066</v>
+        <v>179.2206093334711</v>
       </c>
       <c r="E38" t="n">
-        <v>186.1540222167969</v>
+        <v>180.9265289306641</v>
       </c>
       <c r="F38" t="n">
-        <v>173628900</v>
+        <v>213598900</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B39" t="n">
-        <v>182.941705155915</v>
+        <v>184.3483273978252</v>
       </c>
       <c r="C39" t="n">
-        <v>184.3583093626339</v>
+        <v>187.4109971087465</v>
       </c>
       <c r="D39" t="n">
-        <v>179.2206093334711</v>
+        <v>182.3930205111681</v>
       </c>
       <c r="E39" t="n">
-        <v>180.9265289306641</v>
+        <v>186.0742034912109</v>
       </c>
       <c r="F39" t="n">
-        <v>213598900</v>
+        <v>247246400</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B40" t="n">
-        <v>184.3483273978252</v>
+        <v>195.4816571057099</v>
       </c>
       <c r="C40" t="n">
-        <v>187.4109971087465</v>
+        <v>195.5315406452363</v>
       </c>
       <c r="D40" t="n">
-        <v>182.3930205111681</v>
+        <v>179.4201468289569</v>
       </c>
       <c r="E40" t="n">
-        <v>186.0742034912109</v>
+        <v>180.208251953125</v>
       </c>
       <c r="F40" t="n">
-        <v>247246400</v>
+        <v>343504800</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B41" t="n">
-        <v>195.4816571057099</v>
+        <v>180.8068289121023</v>
       </c>
       <c r="C41" t="n">
-        <v>195.5315406452363</v>
+        <v>184.1188859589464</v>
       </c>
       <c r="D41" t="n">
-        <v>179.4201468289569</v>
+        <v>172.5166776199441</v>
       </c>
       <c r="E41" t="n">
-        <v>180.208251953125</v>
+        <v>178.4524688720703</v>
       </c>
       <c r="F41" t="n">
-        <v>343504800</v>
+        <v>346926200</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B42" t="n">
-        <v>180.8068289121023</v>
+        <v>179.0610093294625</v>
       </c>
       <c r="C42" t="n">
-        <v>184.1188859589464</v>
+        <v>183.0614196131816</v>
       </c>
       <c r="D42" t="n">
-        <v>172.5166776199441</v>
+        <v>176.0581937395723</v>
       </c>
       <c r="E42" t="n">
-        <v>178.4524688720703</v>
+        <v>182.1136932373047</v>
       </c>
       <c r="F42" t="n">
-        <v>346926200</v>
+        <v>256618300</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B43" t="n">
-        <v>179.0610093294625</v>
+        <v>174.491955735681</v>
       </c>
       <c r="C43" t="n">
-        <v>183.0614196131816</v>
+        <v>177.7341879937998</v>
       </c>
       <c r="D43" t="n">
-        <v>176.0581937395723</v>
+        <v>169.1447659257062</v>
       </c>
       <c r="E43" t="n">
-        <v>182.1136932373047</v>
+        <v>177.3950042724609</v>
       </c>
       <c r="F43" t="n">
-        <v>256618300</v>
+        <v>320600300</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B44" t="n">
-        <v>174.4919407266003</v>
+        <v>181.1958985688627</v>
       </c>
       <c r="C44" t="n">
-        <v>177.7341727058355</v>
+        <v>182.4728380763597</v>
       </c>
       <c r="D44" t="n">
-        <v>169.1447513765687</v>
+        <v>177.8140014756398</v>
       </c>
       <c r="E44" t="n">
-        <v>177.3949890136719</v>
+        <v>179.8291625976562</v>
       </c>
       <c r="F44" t="n">
-        <v>320600300</v>
+        <v>183852000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B45" t="n">
-        <v>181.1958985688627</v>
+        <v>178.5821558989869</v>
       </c>
       <c r="C45" t="n">
-        <v>182.4728380763597</v>
+        <v>178.8614854738169</v>
       </c>
       <c r="D45" t="n">
-        <v>177.8140014756398</v>
+        <v>176.0781603452176</v>
       </c>
       <c r="E45" t="n">
-        <v>179.8291625976562</v>
+        <v>176.5769653320312</v>
       </c>
       <c r="F45" t="n">
-        <v>183852000</v>
+        <v>121332800</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B46" t="n">
-        <v>178.5821404669205</v>
+        <v>174.3423041351479</v>
       </c>
       <c r="C46" t="n">
-        <v>178.8614700176124</v>
+        <v>179.8690716163194</v>
       </c>
       <c r="D46" t="n">
-        <v>176.0781451295325</v>
+        <v>173.2648835948944</v>
       </c>
       <c r="E46" t="n">
-        <v>176.5769500732422</v>
+        <v>179.4899749755859</v>
       </c>
       <c r="F46" t="n">
-        <v>121332800</v>
+        <v>188131000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B47" t="n">
-        <v>174.3423041351479</v>
+        <v>181.3255769560617</v>
       </c>
       <c r="C47" t="n">
-        <v>179.8690716163194</v>
+        <v>185.2162648499111</v>
       </c>
       <c r="D47" t="n">
-        <v>173.2648835948944</v>
+        <v>179.569788944198</v>
       </c>
       <c r="E47" t="n">
-        <v>179.4899749755859</v>
+        <v>181.0263061523438</v>
       </c>
       <c r="F47" t="n">
-        <v>188131000</v>
+        <v>182632200</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B48" t="n">
-        <v>181.3255769560617</v>
+        <v>180.6472109015755</v>
       </c>
       <c r="C48" t="n">
-        <v>185.2162648499111</v>
+        <v>182.0139316568558</v>
       </c>
       <c r="D48" t="n">
-        <v>179.569788944198</v>
+        <v>178.681918089591</v>
       </c>
       <c r="E48" t="n">
-        <v>181.0263061523438</v>
+        <v>179.1607666015625</v>
       </c>
       <c r="F48" t="n">
-        <v>182632200</v>
+        <v>165138000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,25 +1691,25 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B49" t="n">
-        <v>180.6472109015755</v>
+        <v>181.1959881613664</v>
       </c>
       <c r="C49" t="n">
-        <v>182.0139316568558</v>
+        <v>184.089227004522</v>
       </c>
       <c r="D49" t="n">
-        <v>178.681918089591</v>
+        <v>179.5398751387779</v>
       </c>
       <c r="E49" t="n">
-        <v>179.1607666015625</v>
+        <v>182.9518890380859</v>
       </c>
       <c r="F49" t="n">
-        <v>165138000</v>
+        <v>167364900</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1717,25 +1717,25 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B50" t="n">
-        <v>181.1960032737075</v>
+        <v>183.4607020047171</v>
       </c>
       <c r="C50" t="n">
-        <v>184.0892423581687</v>
+        <v>184.2289086763207</v>
       </c>
       <c r="D50" t="n">
-        <v>179.5398901129937</v>
+        <v>180.4876631773748</v>
       </c>
       <c r="E50" t="n">
-        <v>182.951904296875</v>
+        <v>181.9841613769531</v>
       </c>
       <c r="F50" t="n">
-        <v>167364900</v>
+        <v>143971100</v>
       </c>
       <c r="G50" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B51" t="n">
-        <v>183.4607020047171</v>
+        <v>182.2136112701494</v>
       </c>
       <c r="C51" t="n">
-        <v>184.2289086763207</v>
+        <v>187.5610985176648</v>
       </c>
       <c r="D51" t="n">
-        <v>180.4876631773748</v>
+        <v>181.9741660895743</v>
       </c>
       <c r="E51" t="n">
-        <v>181.9841613769531</v>
+        <v>185.1168212890625</v>
       </c>
       <c r="F51" t="n">
-        <v>143971100</v>
+        <v>204378100</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B52" t="n">
-        <v>182.213626289633</v>
+        <v>185.1268117532098</v>
       </c>
       <c r="C52" t="n">
-        <v>187.5611139779305</v>
+        <v>185.2864418902268</v>
       </c>
       <c r="D52" t="n">
-        <v>181.9741810893209</v>
+        <v>182.8920507276432</v>
       </c>
       <c r="E52" t="n">
-        <v>185.1168365478516</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="F52" t="n">
-        <v>204378100</v>
+        <v>144719700</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B53" t="n">
-        <v>185.12679644575</v>
+        <v>184.538176449994</v>
       </c>
       <c r="C53" t="n">
-        <v>185.2864265695677</v>
+        <v>185.0469803407326</v>
       </c>
       <c r="D53" t="n">
-        <v>182.8920356049676</v>
+        <v>181.6150088138297</v>
       </c>
       <c r="E53" t="n">
-        <v>184.5381774902344</v>
+        <v>183.3509521484375</v>
       </c>
       <c r="F53" t="n">
-        <v>144719700</v>
+        <v>162785400</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B54" t="n">
-        <v>184.5381918075859</v>
+        <v>179.8591224369562</v>
       </c>
       <c r="C54" t="n">
-        <v>185.0469957406681</v>
+        <v>180.8967030087509</v>
       </c>
       <c r="D54" t="n">
-        <v>181.6150239281505</v>
+        <v>176.2076633109278</v>
       </c>
       <c r="E54" t="n">
-        <v>183.3509674072266</v>
+        <v>180.5075988769531</v>
       </c>
       <c r="F54" t="n">
-        <v>162785400</v>
+        <v>182136600</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B55" t="n">
-        <v>179.8591224369562</v>
+        <v>180.6871989054384</v>
       </c>
       <c r="C55" t="n">
-        <v>180.8967030087509</v>
+        <v>182.3932136047752</v>
       </c>
       <c r="D55" t="n">
-        <v>176.2076633109278</v>
+        <v>174.2123443447362</v>
       </c>
       <c r="E55" t="n">
-        <v>180.5075988769531</v>
+        <v>174.6114196777344</v>
       </c>
       <c r="F55" t="n">
-        <v>182136600</v>
+        <v>204274900</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B56" t="n">
-        <v>180.6871831157045</v>
+        <v>177.5245903328353</v>
       </c>
       <c r="C56" t="n">
-        <v>182.3931976659576</v>
+        <v>178.0034654802094</v>
       </c>
       <c r="D56" t="n">
-        <v>174.2123291208211</v>
+        <v>174.6213802569945</v>
       </c>
       <c r="E56" t="n">
-        <v>174.6114044189453</v>
+        <v>175.8784332275391</v>
       </c>
       <c r="F56" t="n">
-        <v>204274900</v>
+        <v>164775600</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B57" t="n">
-        <v>177.5245903328353</v>
+        <v>175.8485012773324</v>
       </c>
       <c r="C57" t="n">
-        <v>178.0034654802094</v>
+        <v>178.0733061224419</v>
       </c>
       <c r="D57" t="n">
-        <v>174.6213802569945</v>
+        <v>174.4916756985292</v>
       </c>
       <c r="E57" t="n">
-        <v>175.8784332275391</v>
+        <v>177.3050994873047</v>
       </c>
       <c r="F57" t="n">
-        <v>164775600</v>
+        <v>148588100</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B58" t="n">
-        <v>175.8485164107673</v>
+        <v>175.6888968536916</v>
       </c>
       <c r="C58" t="n">
-        <v>178.0733214473424</v>
+        <v>175.7188256001934</v>
       </c>
       <c r="D58" t="n">
-        <v>174.4916907151964</v>
+        <v>169.9124052081842</v>
       </c>
       <c r="E58" t="n">
-        <v>177.3051147460938</v>
+        <v>170.5409393310547</v>
       </c>
       <c r="F58" t="n">
-        <v>148588100</v>
+        <v>222775500</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B59" t="n">
-        <v>175.6888968536916</v>
+        <v>174.1225483861358</v>
       </c>
       <c r="C59" t="n">
-        <v>175.7188256001934</v>
+        <v>175.7387615308714</v>
       </c>
       <c r="D59" t="n">
-        <v>169.9124052081842</v>
+        <v>171.4188835631069</v>
       </c>
       <c r="E59" t="n">
-        <v>170.5409393310547</v>
+        <v>173.7334594726562</v>
       </c>
       <c r="F59" t="n">
-        <v>222775500</v>
+        <v>176096000</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B60" t="n">
-        <v>174.1225483861358</v>
+        <v>176.2575523358494</v>
       </c>
       <c r="C60" t="n">
-        <v>175.7387615308714</v>
+        <v>181.0263919449467</v>
       </c>
       <c r="D60" t="n">
-        <v>171.4188835631069</v>
+        <v>175.9283209122297</v>
       </c>
       <c r="E60" t="n">
-        <v>173.7334594726562</v>
+        <v>180.5674743652344</v>
       </c>
       <c r="F60" t="n">
-        <v>176096000</v>
+        <v>324925900</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B61" t="n">
-        <v>176.2575523358494</v>
+        <v>183.4906282252173</v>
       </c>
       <c r="C61" t="n">
-        <v>181.0263919449467</v>
+        <v>183.7300734141942</v>
       </c>
       <c r="D61" t="n">
-        <v>175.9283209122297</v>
+        <v>181.9243013805983</v>
       </c>
       <c r="E61" t="n">
-        <v>180.5674743652344</v>
+        <v>183.2611694335938</v>
       </c>
       <c r="F61" t="n">
-        <v>324925900</v>
+        <v>129064400</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B62" t="n">
-        <v>183.4906282252173</v>
+        <v>182.5428571096804</v>
       </c>
       <c r="C62" t="n">
-        <v>183.7300734141942</v>
+        <v>188.8880102762506</v>
       </c>
       <c r="D62" t="n">
-        <v>181.9243013805983</v>
+        <v>182.4730132178061</v>
       </c>
       <c r="E62" t="n">
-        <v>183.2611694335938</v>
+        <v>188.7682952880859</v>
       </c>
       <c r="F62" t="n">
-        <v>129064400</v>
+        <v>174873600</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B63" t="n">
-        <v>182.5428423541149</v>
+        <v>187.5012437217294</v>
       </c>
       <c r="C63" t="n">
-        <v>188.8879950077845</v>
+        <v>188.4689804086018</v>
       </c>
       <c r="D63" t="n">
-        <v>182.4729984678863</v>
+        <v>186.154389299292</v>
       </c>
       <c r="E63" t="n">
-        <v>188.7682800292969</v>
+        <v>188.169677734375</v>
       </c>
       <c r="F63" t="n">
-        <v>174873600</v>
+        <v>65528500</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B64" t="n">
-        <v>187.5012437217294</v>
+        <v>189.4766285187414</v>
       </c>
       <c r="C64" t="n">
-        <v>188.4689804086018</v>
+        <v>192.240166195598</v>
       </c>
       <c r="D64" t="n">
-        <v>186.154389299292</v>
+        <v>187.5611125998212</v>
       </c>
       <c r="E64" t="n">
-        <v>188.169677734375</v>
+        <v>190.085205078125</v>
       </c>
       <c r="F64" t="n">
-        <v>65528500</v>
+        <v>139740300</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B65" t="n">
-        <v>189.4766285187414</v>
+        <v>187.2717899684254</v>
       </c>
       <c r="C65" t="n">
-        <v>192.240166195598</v>
+        <v>188.3193265216257</v>
       </c>
       <c r="D65" t="n">
-        <v>187.5611125998212</v>
+        <v>185.4759890979627</v>
       </c>
       <c r="E65" t="n">
-        <v>190.085205078125</v>
+        <v>187.7805938720703</v>
       </c>
       <c r="F65" t="n">
-        <v>139740300</v>
+        <v>120006100</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B66" t="n">
-        <v>187.2717899684254</v>
+        <v>187.8005661647843</v>
       </c>
       <c r="C66" t="n">
-        <v>188.3193265216257</v>
+        <v>188.5488153175326</v>
       </c>
       <c r="D66" t="n">
-        <v>185.4759890979627</v>
+        <v>186.4936115238563</v>
       </c>
       <c r="E66" t="n">
-        <v>187.7805938720703</v>
+        <v>187.1021881103516</v>
       </c>
       <c r="F66" t="n">
-        <v>120006100</v>
+        <v>97687300</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B67" t="n">
-        <v>187.8005508490403</v>
+        <v>189.1274459397885</v>
       </c>
       <c r="C67" t="n">
-        <v>188.5487999407664</v>
+        <v>190.1151249886817</v>
       </c>
       <c r="D67" t="n">
-        <v>186.4935963146986</v>
+        <v>186.0546345387688</v>
       </c>
       <c r="E67" t="n">
-        <v>187.1021728515625</v>
+        <v>186.0646057128906</v>
       </c>
       <c r="F67" t="n">
-        <v>97687300</v>
+        <v>120100500</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B68" t="n">
-        <v>189.127461449755</v>
+        <v>189.3968130035911</v>
       </c>
       <c r="C68" t="n">
-        <v>190.1151405796458</v>
+        <v>192.4795957147097</v>
       </c>
       <c r="D68" t="n">
-        <v>186.0546497967401</v>
+        <v>187.8204997023152</v>
       </c>
       <c r="E68" t="n">
-        <v>186.0646209716797</v>
+        <v>188.4091339111328</v>
       </c>
       <c r="F68" t="n">
-        <v>120100500</v>
+        <v>148240500</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B69" t="n">
-        <v>189.3968130035911</v>
+        <v>191.3123337767646</v>
       </c>
       <c r="C69" t="n">
-        <v>192.4795957147097</v>
+        <v>193.1779786425506</v>
       </c>
       <c r="D69" t="n">
-        <v>187.8204997023152</v>
+        <v>185.7154296257417</v>
       </c>
       <c r="E69" t="n">
-        <v>188.4091339111328</v>
+        <v>187.6808319091797</v>
       </c>
       <c r="F69" t="n">
-        <v>148240500</v>
+        <v>183529700</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B70" t="n">
-        <v>191.3123337767646</v>
+        <v>190.0752439930999</v>
       </c>
       <c r="C70" t="n">
-        <v>193.1779786425506</v>
+        <v>191.7213860539245</v>
       </c>
       <c r="D70" t="n">
-        <v>185.7154296257417</v>
+        <v>186.3838845193456</v>
       </c>
       <c r="E70" t="n">
-        <v>187.6808319091797</v>
+        <v>186.8029022216797</v>
       </c>
       <c r="F70" t="n">
-        <v>183529700</v>
+        <v>176862600</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B71" t="n">
-        <v>190.0752284670132</v>
+        <v>188.1297854095839</v>
       </c>
       <c r="C71" t="n">
-        <v>191.7213703933745</v>
+        <v>190.9232365533545</v>
       </c>
       <c r="D71" t="n">
-        <v>186.3838692947835</v>
+        <v>186.1244680675316</v>
       </c>
       <c r="E71" t="n">
-        <v>186.8028869628906</v>
+        <v>188.6685180664062</v>
       </c>
       <c r="F71" t="n">
-        <v>176862600</v>
+        <v>153543200</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B72" t="n">
-        <v>188.1297854095839</v>
+        <v>188.6685072554968</v>
       </c>
       <c r="C72" t="n">
-        <v>190.9232365533545</v>
+        <v>189.1074824738404</v>
       </c>
       <c r="D72" t="n">
-        <v>186.1244680675316</v>
+        <v>183.2811201033086</v>
       </c>
       <c r="E72" t="n">
-        <v>188.6685180664062</v>
+        <v>184.6080017089844</v>
       </c>
       <c r="F72" t="n">
-        <v>153543200</v>
+        <v>172457000</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B73" t="n">
-        <v>188.6685228499072</v>
+        <v>184.6479238968445</v>
       </c>
       <c r="C73" t="n">
-        <v>189.1074981045344</v>
+        <v>185.9049768874807</v>
       </c>
       <c r="D73" t="n">
-        <v>183.2811352524241</v>
+        <v>183.2412119543349</v>
       </c>
       <c r="E73" t="n">
-        <v>184.6080169677734</v>
+        <v>184.4284362792969</v>
       </c>
       <c r="F73" t="n">
-        <v>172457000</v>
+        <v>131327500</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B74" t="n">
-        <v>184.6479238968445</v>
+        <v>182.7922691735387</v>
       </c>
       <c r="C74" t="n">
-        <v>185.9049768874807</v>
+        <v>186.6831584288149</v>
       </c>
       <c r="D74" t="n">
-        <v>183.2412119543349</v>
+        <v>182.5927391235801</v>
       </c>
       <c r="E74" t="n">
-        <v>184.4284362792969</v>
+        <v>184.5082550048828</v>
       </c>
       <c r="F74" t="n">
-        <v>131327500</v>
+        <v>137968500</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B75" t="n">
-        <v>182.7922691735387</v>
+        <v>184.5681140987238</v>
       </c>
       <c r="C75" t="n">
-        <v>186.6831584288149</v>
+        <v>187.6708543554723</v>
       </c>
       <c r="D75" t="n">
-        <v>182.5927391235801</v>
+        <v>182.9718432388734</v>
       </c>
       <c r="E75" t="n">
-        <v>184.5082550048828</v>
+        <v>185.376220703125</v>
       </c>
       <c r="F75" t="n">
-        <v>137968500</v>
+        <v>160128900</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B76" t="n">
-        <v>184.5681140987238</v>
+        <v>183.8897012556695</v>
       </c>
       <c r="C76" t="n">
-        <v>187.6708543554723</v>
+        <v>184.0293738083791</v>
       </c>
       <c r="D76" t="n">
-        <v>182.9718432388734</v>
+        <v>180.3779146434709</v>
       </c>
       <c r="E76" t="n">
-        <v>185.376220703125</v>
+        <v>182.7124481201172</v>
       </c>
       <c r="F76" t="n">
-        <v>160128900</v>
+        <v>159586100</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B77" t="n">
-        <v>183.8896858985649</v>
+        <v>186.0646079796491</v>
       </c>
       <c r="C77" t="n">
-        <v>184.0293584396101</v>
+        <v>189.2571344016907</v>
       </c>
       <c r="D77" t="n">
-        <v>180.3778995796448</v>
+        <v>185.895006678512</v>
       </c>
       <c r="E77" t="n">
-        <v>182.7124328613281</v>
+        <v>186.6133270263672</v>
       </c>
       <c r="F77" t="n">
-        <v>159586100</v>
+        <v>206188600</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B78" t="n">
-        <v>186.0646079796491</v>
+        <v>188.6385950815971</v>
       </c>
       <c r="C78" t="n">
-        <v>189.2571344016907</v>
+        <v>189.9954207742267</v>
       </c>
       <c r="D78" t="n">
-        <v>185.895006678512</v>
+        <v>185.6455985734289</v>
       </c>
       <c r="E78" t="n">
-        <v>186.6133270263672</v>
+        <v>185.7952423095703</v>
       </c>
       <c r="F78" t="n">
-        <v>206188600</v>
+        <v>187967200</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B79" t="n">
-        <v>188.6385795892923</v>
+        <v>181.4753266272146</v>
       </c>
       <c r="C79" t="n">
-        <v>189.99540517049</v>
+        <v>181.9542169705431</v>
       </c>
       <c r="D79" t="n">
-        <v>185.6455833269296</v>
+        <v>177.1953488429791</v>
       </c>
       <c r="E79" t="n">
-        <v>185.7952270507812</v>
+        <v>177.6542816162109</v>
       </c>
       <c r="F79" t="n">
-        <v>187967200</v>
+        <v>223345300</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B80" t="n">
-        <v>181.4753266272146</v>
+        <v>178.6320081827799</v>
       </c>
       <c r="C80" t="n">
-        <v>181.9542169705431</v>
+        <v>184.9472325313386</v>
       </c>
       <c r="D80" t="n">
-        <v>177.1953488429791</v>
+        <v>177.9835164834521</v>
       </c>
       <c r="E80" t="n">
-        <v>177.6542816162109</v>
+        <v>182.8920440673828</v>
       </c>
       <c r="F80" t="n">
-        <v>223345300</v>
+        <v>200381000</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B81" t="n">
-        <v>178.6320081827799</v>
+        <v>184.3186915464293</v>
       </c>
       <c r="C81" t="n">
-        <v>184.9472325313386</v>
+        <v>185.7353746560278</v>
       </c>
       <c r="D81" t="n">
-        <v>177.9835164834521</v>
+        <v>183.5005985718231</v>
       </c>
       <c r="E81" t="n">
-        <v>182.8920440673828</v>
+        <v>184.4084777832031</v>
       </c>
       <c r="F81" t="n">
-        <v>200381000</v>
+        <v>139636600</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B82" t="n">
-        <v>184.3186915464293</v>
+        <v>187.0622712594319</v>
       </c>
       <c r="C82" t="n">
-        <v>185.7353746560278</v>
+        <v>189.1573747868041</v>
       </c>
       <c r="D82" t="n">
-        <v>183.5005985718231</v>
+        <v>186.3838660627843</v>
       </c>
       <c r="E82" t="n">
-        <v>184.4084777832031</v>
+        <v>187.2318725585938</v>
       </c>
       <c r="F82" t="n">
-        <v>139636600</v>
+        <v>142748100</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B83" t="n">
-        <v>187.0622712594319</v>
+        <v>186.7230595290241</v>
       </c>
       <c r="C83" t="n">
-        <v>189.1573747868041</v>
+        <v>188.6784751839824</v>
       </c>
       <c r="D83" t="n">
-        <v>186.3838660627843</v>
+        <v>185.5557928402329</v>
       </c>
       <c r="E83" t="n">
-        <v>187.2318725585938</v>
+        <v>186.03466796875</v>
       </c>
       <c r="F83" t="n">
-        <v>142748100</v>
+        <v>124799600</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B84" t="n">
-        <v>186.7230748442759</v>
+        <v>186.8028844605491</v>
       </c>
       <c r="C84" t="n">
-        <v>188.6784906596197</v>
+        <v>189.5564356240106</v>
       </c>
       <c r="D84" t="n">
-        <v>185.555808059744</v>
+        <v>185.2664711415707</v>
       </c>
       <c r="E84" t="n">
-        <v>186.0346832275391</v>
+        <v>188.0798950195312</v>
       </c>
       <c r="F84" t="n">
-        <v>124799600</v>
+        <v>143711600</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B85" t="n">
-        <v>186.8028844605491</v>
+        <v>190.823459633995</v>
       </c>
       <c r="C85" t="n">
-        <v>189.5564356240106</v>
+        <v>191.9009400606663</v>
       </c>
       <c r="D85" t="n">
-        <v>185.2664711415707</v>
+        <v>189.3967902384632</v>
       </c>
       <c r="E85" t="n">
-        <v>188.0798950195312</v>
+        <v>191.0728759765625</v>
       </c>
       <c r="F85" t="n">
-        <v>143711600</v>
+        <v>148552700</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B86" t="n">
-        <v>190.8234748728661</v>
+        <v>190.8933105997472</v>
       </c>
       <c r="C86" t="n">
-        <v>191.9009553855833</v>
+        <v>193.0283141326731</v>
       </c>
       <c r="D86" t="n">
-        <v>189.3968053634026</v>
+        <v>185.6256380470483</v>
       </c>
       <c r="E86" t="n">
-        <v>191.0728912353516</v>
+        <v>192.0605773925781</v>
       </c>
       <c r="F86" t="n">
-        <v>148552700</v>
+        <v>171764400</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B87" t="n">
-        <v>190.8933105997472</v>
+        <v>190.7636224379378</v>
       </c>
       <c r="C87" t="n">
-        <v>193.0283141326731</v>
+        <v>194.0359639826301</v>
       </c>
       <c r="D87" t="n">
-        <v>185.6256380470483</v>
+        <v>189.0276790286862</v>
       </c>
       <c r="E87" t="n">
-        <v>192.0605773925781</v>
+        <v>190.6838073730469</v>
       </c>
       <c r="F87" t="n">
-        <v>171764400</v>
+        <v>179489500</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B88" t="n">
-        <v>190.7636224379378</v>
+        <v>186.7629659025267</v>
       </c>
       <c r="C88" t="n">
-        <v>194.0359639826301</v>
+        <v>189.8557348322644</v>
       </c>
       <c r="D88" t="n">
-        <v>189.0276790286862</v>
+        <v>184.4483900153819</v>
       </c>
       <c r="E88" t="n">
-        <v>190.6838073730469</v>
+        <v>185.1766815185547</v>
       </c>
       <c r="F88" t="n">
-        <v>179489500</v>
+        <v>165794100</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B89" t="n">
-        <v>186.7629812920276</v>
+        <v>185.8052108647954</v>
       </c>
       <c r="C89" t="n">
-        <v>189.8557504766133</v>
+        <v>185.8351396091497</v>
       </c>
       <c r="D89" t="n">
-        <v>184.4484052141589</v>
+        <v>175.8185703987175</v>
       </c>
       <c r="E89" t="n">
-        <v>185.1766967773438</v>
+        <v>179.9189758300781</v>
       </c>
       <c r="F89" t="n">
-        <v>165794100</v>
+        <v>204019600</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B90" t="n">
-        <v>185.8052108647954</v>
+        <v>179.0410571553003</v>
       </c>
       <c r="C90" t="n">
-        <v>185.8351396091497</v>
+        <v>179.1607721437711</v>
       </c>
       <c r="D90" t="n">
-        <v>175.8185703987175</v>
+        <v>171.5086795929406</v>
       </c>
       <c r="E90" t="n">
-        <v>179.9189758300781</v>
+        <v>173.7833557128906</v>
       </c>
       <c r="F90" t="n">
-        <v>204019600</v>
+        <v>207014100</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B91" t="n">
-        <v>179.0410414348666</v>
+        <v>174.5216119878791</v>
       </c>
       <c r="C91" t="n">
-        <v>179.160756412826</v>
+        <v>176.4072143255947</v>
       </c>
       <c r="D91" t="n">
-        <v>171.5086645338761</v>
+        <v>170.6307227747363</v>
       </c>
       <c r="E91" t="n">
-        <v>173.7833404541016</v>
+        <v>171.4787445068359</v>
       </c>
       <c r="F91" t="n">
-        <v>207014100</v>
+        <v>206312900</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B92" t="n">
-        <v>174.5215964583249</v>
+        <v>176.2775135166603</v>
       </c>
       <c r="C92" t="n">
-        <v>176.4071986282528</v>
+        <v>186.5634420291942</v>
       </c>
       <c r="D92" t="n">
-        <v>170.6307075914073</v>
+        <v>174.1923963475411</v>
       </c>
       <c r="E92" t="n">
-        <v>171.4787292480469</v>
+        <v>184.9771575927734</v>
       </c>
       <c r="F92" t="n">
-        <v>206312900</v>
+        <v>231346200</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B93" t="n">
-        <v>176.277498975506</v>
+        <v>183.8298386502086</v>
       </c>
       <c r="C93" t="n">
-        <v>186.5634266395524</v>
+        <v>193.2079034382237</v>
       </c>
       <c r="D93" t="n">
-        <v>174.1923819783884</v>
+        <v>183.5205647824287</v>
       </c>
       <c r="E93" t="n">
-        <v>184.9771423339844</v>
+        <v>189.5963439941406</v>
       </c>
       <c r="F93" t="n">
-        <v>231346200</v>
+        <v>196387400</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B94" t="n">
-        <v>183.8298386502086</v>
+        <v>190.933219719687</v>
       </c>
       <c r="C94" t="n">
-        <v>193.2079034382237</v>
+        <v>192.0306425866914</v>
       </c>
       <c r="D94" t="n">
-        <v>183.5205647824287</v>
+        <v>187.6808205923615</v>
       </c>
       <c r="E94" t="n">
-        <v>189.5963439941406</v>
+        <v>188.0998382568359</v>
       </c>
       <c r="F94" t="n">
-        <v>196387400</v>
+        <v>136764800</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B95" t="n">
-        <v>190.933219719687</v>
+        <v>192.0007297023972</v>
       </c>
       <c r="C95" t="n">
-        <v>192.0306425866914</v>
+        <v>192.8088363522974</v>
       </c>
       <c r="D95" t="n">
-        <v>187.6808205923615</v>
+        <v>188.3293278304631</v>
       </c>
       <c r="E95" t="n">
-        <v>188.0998382568359</v>
+        <v>189.6063385009766</v>
       </c>
       <c r="F95" t="n">
-        <v>136764800</v>
+        <v>144192700</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B96" t="n">
-        <v>192.0007142509167</v>
+        <v>192.5793806436633</v>
       </c>
       <c r="C96" t="n">
-        <v>192.8088208357837</v>
+        <v>193.158028491682</v>
       </c>
       <c r="D96" t="n">
-        <v>188.329312674443</v>
+        <v>186.0745969700116</v>
       </c>
       <c r="E96" t="n">
-        <v>189.6063232421875</v>
+        <v>186.5036010742188</v>
       </c>
       <c r="F96" t="n">
-        <v>144192700</v>
+        <v>189932500</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B97" t="n">
-        <v>192.5793648877844</v>
+        <v>187.0423048169314</v>
       </c>
       <c r="C97" t="n">
-        <v>193.1580126884611</v>
+        <v>187.0622623874058</v>
       </c>
       <c r="D97" t="n">
-        <v>186.0745817463215</v>
+        <v>181.1660562233949</v>
       </c>
       <c r="E97" t="n">
-        <v>186.5035858154297</v>
+        <v>182.3832092285156</v>
       </c>
       <c r="F97" t="n">
-        <v>189932500</v>
+        <v>161888000</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B98" t="n">
-        <v>187.042320465516</v>
+        <v>181.3257085516038</v>
       </c>
       <c r="C98" t="n">
-        <v>187.0622780376601</v>
+        <v>186.7130962790006</v>
       </c>
       <c r="D98" t="n">
-        <v>181.1660713803529</v>
+        <v>178.7617008539599</v>
       </c>
       <c r="E98" t="n">
-        <v>182.3832244873047</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="F98" t="n">
-        <v>161888000</v>
+        <v>162276900</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B99" t="n">
-        <v>181.3256935584433</v>
+        <v>188.3093443160685</v>
       </c>
       <c r="C99" t="n">
-        <v>186.7130808403767</v>
+        <v>189.9255573932224</v>
       </c>
       <c r="D99" t="n">
-        <v>178.7616860728079</v>
+        <v>186.3239846890322</v>
       </c>
       <c r="E99" t="n">
-        <v>184.5381774902344</v>
+        <v>187.5411376953125</v>
       </c>
       <c r="F99" t="n">
-        <v>162276900</v>
+        <v>164749100</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B100" t="n">
-        <v>188.3093443160685</v>
+        <v>186.6232837033845</v>
       </c>
       <c r="C100" t="n">
-        <v>189.9255573932224</v>
+        <v>187.9900804037161</v>
       </c>
       <c r="D100" t="n">
-        <v>186.3239846890322</v>
+        <v>185.226558259481</v>
       </c>
       <c r="E100" t="n">
-        <v>187.5411376953125</v>
+        <v>187.4613189697266</v>
       </c>
       <c r="F100" t="n">
-        <v>164749100</v>
+        <v>126554500</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B101" t="n">
-        <v>186.62329889396</v>
+        <v>186.1344488846578</v>
       </c>
       <c r="C101" t="n">
-        <v>187.9900957055448</v>
+        <v>189.8856654675195</v>
       </c>
       <c r="D101" t="n">
-        <v>185.2265733363672</v>
+        <v>185.5059147845697</v>
       </c>
       <c r="E101" t="n">
-        <v>187.4613342285156</v>
+        <v>189.3768615722656</v>
       </c>
       <c r="F101" t="n">
-        <v>126554500</v>
+        <v>178422300</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B102" t="n">
-        <v>186.1344638821937</v>
+        <v>190.9531547742145</v>
       </c>
       <c r="C102" t="n">
-        <v>189.8856807673048</v>
+        <v>193.4972046328596</v>
       </c>
       <c r="D102" t="n">
-        <v>185.5059297314624</v>
+        <v>189.1374116308485</v>
       </c>
       <c r="E102" t="n">
-        <v>189.3768768310547</v>
+        <v>191.1028137207031</v>
       </c>
       <c r="F102" t="n">
-        <v>178422300</v>
+        <v>171584800</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B103" t="n">
-        <v>190.9531700210539</v>
+        <v>191.0429698590405</v>
       </c>
       <c r="C103" t="n">
-        <v>193.4972200828311</v>
+        <v>193.3176459547985</v>
       </c>
       <c r="D103" t="n">
-        <v>189.1374267327081</v>
+        <v>186.9625064417709</v>
       </c>
       <c r="E103" t="n">
-        <v>191.1028289794922</v>
+        <v>192.3997955322266</v>
       </c>
       <c r="F103" t="n">
-        <v>171584800</v>
+        <v>175123600</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B104" t="n">
-        <v>191.0429698590405</v>
+        <v>193.9960453222018</v>
       </c>
       <c r="C104" t="n">
-        <v>193.3176459547985</v>
+        <v>197.1686293956491</v>
       </c>
       <c r="D104" t="n">
-        <v>186.9625064417709</v>
+        <v>193.3375824661624</v>
       </c>
       <c r="E104" t="n">
-        <v>192.3997955322266</v>
+        <v>195.1034545898438</v>
       </c>
       <c r="F104" t="n">
-        <v>175123600</v>
+        <v>250637100</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B105" t="n">
-        <v>193.9960453222018</v>
+        <v>193.8164813019665</v>
       </c>
       <c r="C105" t="n">
-        <v>197.1686293956491</v>
+        <v>193.8364236513225</v>
       </c>
       <c r="D105" t="n">
-        <v>193.3375824661624</v>
+        <v>183.8897126034445</v>
       </c>
       <c r="E105" t="n">
-        <v>195.1034545898438</v>
+        <v>184.4583740234375</v>
       </c>
       <c r="F105" t="n">
-        <v>250637100</v>
+        <v>360807900</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B106" t="n">
-        <v>193.8164652690549</v>
+        <v>180.82685580423</v>
       </c>
       <c r="C106" t="n">
-        <v>193.8364076167612</v>
+        <v>182.1637238018573</v>
       </c>
       <c r="D106" t="n">
-        <v>183.8896973916963</v>
+        <v>175.9682301224481</v>
       </c>
       <c r="E106" t="n">
-        <v>184.4583587646484</v>
+        <v>176.7763366699219</v>
       </c>
       <c r="F106" t="n">
-        <v>360807900</v>
+        <v>311636500</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B107" t="n">
-        <v>180.8268714126474</v>
+        <v>174.6014088918714</v>
       </c>
       <c r="C107" t="n">
-        <v>182.1637395256691</v>
+        <v>183.0316933488174</v>
       </c>
       <c r="D107" t="n">
-        <v>175.9682453114839</v>
+        <v>174.2322775806792</v>
       </c>
       <c r="E107" t="n">
-        <v>176.7763519287109</v>
+        <v>182.0539703369141</v>
       </c>
       <c r="F107" t="n">
-        <v>311636500</v>
+        <v>209095300</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B108" t="n">
-        <v>174.601438160182</v>
+        <v>178.0733135069376</v>
       </c>
       <c r="C108" t="n">
-        <v>183.0317240302905</v>
+        <v>180.4776756968921</v>
       </c>
       <c r="D108" t="n">
-        <v>174.2323067871125</v>
+        <v>176.5069714269912</v>
       </c>
       <c r="E108" t="n">
-        <v>182.0540008544922</v>
+        <v>179.6296691894531</v>
       </c>
       <c r="F108" t="n">
-        <v>209095300</v>
+        <v>178099400</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B109" t="n">
-        <v>178.0732983803544</v>
+        <v>180.0187649948852</v>
       </c>
       <c r="C109" t="n">
-        <v>180.4776603660684</v>
+        <v>184.2688145383873</v>
       </c>
       <c r="D109" t="n">
-        <v>176.5069564334623</v>
+        <v>179.6396472340209</v>
       </c>
       <c r="E109" t="n">
-        <v>179.6296539306641</v>
+        <v>182.6126861572266</v>
       </c>
       <c r="F109" t="n">
-        <v>178099400</v>
+        <v>177731200</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B110" t="n">
-        <v>180.0187649948852</v>
+        <v>180.7470399397241</v>
       </c>
       <c r="C110" t="n">
-        <v>184.2688145383873</v>
+        <v>183.6302923567135</v>
       </c>
       <c r="D110" t="n">
-        <v>179.6396472340209</v>
+        <v>177.4647274492447</v>
       </c>
       <c r="E110" t="n">
-        <v>182.6126861572266</v>
+        <v>182.9119720458984</v>
       </c>
       <c r="F110" t="n">
-        <v>177731200</v>
+        <v>198779700</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B111" t="n">
-        <v>180.7470550179114</v>
+        <v>179.420149946886</v>
       </c>
       <c r="C111" t="n">
-        <v>183.6303076754259</v>
+        <v>182.3333312190456</v>
       </c>
       <c r="D111" t="n">
-        <v>177.4647422536165</v>
+        <v>176.407211264142</v>
       </c>
       <c r="E111" t="n">
-        <v>182.9119873046875</v>
+        <v>177.4048767089844</v>
       </c>
       <c r="F111" t="n">
-        <v>198779700</v>
+        <v>189021900</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B112" t="n">
-        <v>179.420149946886</v>
+        <v>176.4171820751478</v>
       </c>
       <c r="C112" t="n">
-        <v>182.3333312190456</v>
+        <v>182.4829897940845</v>
       </c>
       <c r="D112" t="n">
-        <v>176.407211264142</v>
+        <v>175.1501427003192</v>
       </c>
       <c r="E112" t="n">
-        <v>177.4048767089844</v>
+        <v>182.2235870361328</v>
       </c>
       <c r="F112" t="n">
-        <v>189021900</v>
+        <v>177213600</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B113" t="n">
-        <v>176.4171820751478</v>
+        <v>181.9741760435397</v>
       </c>
       <c r="C113" t="n">
-        <v>182.4829897940845</v>
+        <v>186.0047530762794</v>
       </c>
       <c r="D113" t="n">
-        <v>175.1501427003192</v>
+        <v>181.5850871183009</v>
       </c>
       <c r="E113" t="n">
-        <v>182.2235870361328</v>
+        <v>184.3386535644531</v>
       </c>
       <c r="F113" t="n">
-        <v>177213600</v>
+        <v>179118500</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,25 +3381,25 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B114" t="n">
-        <v>181.9741760435397</v>
+        <v>185.4860219488843</v>
       </c>
       <c r="C114" t="n">
-        <v>186.0047530762794</v>
+        <v>187.1921136401388</v>
       </c>
       <c r="D114" t="n">
-        <v>181.5850871183009</v>
+        <v>184.0293448898806</v>
       </c>
       <c r="E114" t="n">
-        <v>184.3386535644531</v>
+        <v>185.6057434082031</v>
       </c>
       <c r="F114" t="n">
-        <v>179118500</v>
+        <v>145280400</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3407,25 +3407,25 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B115" t="n">
-        <v>185.4860219488843</v>
+        <v>183.6302641505579</v>
       </c>
       <c r="C115" t="n">
-        <v>187.1921136401388</v>
+        <v>184.5182338343672</v>
       </c>
       <c r="D115" t="n">
-        <v>184.0293448898806</v>
+        <v>181.3355064165816</v>
       </c>
       <c r="E115" t="n">
-        <v>185.6057434082031</v>
+        <v>182.7223358154297</v>
       </c>
       <c r="F115" t="n">
-        <v>145280400</v>
+        <v>155762700</v>
       </c>
       <c r="G115" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B116" t="n">
-        <v>183.6302794851663</v>
+        <v>184.4982918130038</v>
       </c>
       <c r="C116" t="n">
-        <v>184.5182492431283</v>
+        <v>185.6656218245341</v>
       </c>
       <c r="D116" t="n">
-        <v>181.3355215595592</v>
+        <v>179.5296528660815</v>
       </c>
       <c r="E116" t="n">
-        <v>182.7223510742188</v>
+        <v>179.8389434814453</v>
       </c>
       <c r="F116" t="n">
-        <v>155762700</v>
+        <v>160988400</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B117" t="n">
-        <v>184.4982761588831</v>
+        <v>182.5527246843909</v>
       </c>
       <c r="C117" t="n">
-        <v>185.6656060713691</v>
+        <v>188.4492501487561</v>
       </c>
       <c r="D117" t="n">
-        <v>179.5296376335348</v>
+        <v>180.9962848148914</v>
       </c>
       <c r="E117" t="n">
-        <v>179.8389282226562</v>
+        <v>182.8021545410156</v>
       </c>
       <c r="F117" t="n">
-        <v>160988400</v>
+        <v>217307400</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B118" t="n">
-        <v>182.5527399223597</v>
+        <v>184.6379731916982</v>
       </c>
       <c r="C118" t="n">
-        <v>188.4492658789173</v>
+        <v>184.9771941770484</v>
       </c>
       <c r="D118" t="n">
-        <v>180.9962999229416</v>
+        <v>181.2656763194747</v>
       </c>
       <c r="E118" t="n">
-        <v>182.8021697998047</v>
+        <v>181.5151062011719</v>
       </c>
       <c r="F118" t="n">
-        <v>217307400</v>
+        <v>182497800</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B119" t="n">
-        <v>184.6379576703901</v>
+        <v>182.0638447517288</v>
       </c>
       <c r="C119" t="n">
-        <v>184.9771786272242</v>
+        <v>182.9618014097589</v>
       </c>
       <c r="D119" t="n">
-        <v>181.2656610816535</v>
+        <v>179.9187539793071</v>
       </c>
       <c r="E119" t="n">
-        <v>181.5150909423828</v>
+        <v>179.9885864257812</v>
       </c>
       <c r="F119" t="n">
-        <v>182497800</v>
+        <v>156683100</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B120" t="n">
-        <v>182.0638447517288</v>
+        <v>177.6040222894031</v>
       </c>
       <c r="C120" t="n">
-        <v>182.9618014097589</v>
+        <v>179.5695306962835</v>
       </c>
       <c r="D120" t="n">
-        <v>179.9187539793071</v>
+        <v>175.3890840362079</v>
       </c>
       <c r="E120" t="n">
-        <v>179.9885864257812</v>
+        <v>178.1527709960938</v>
       </c>
       <c r="F120" t="n">
-        <v>156683100</v>
+        <v>170968500</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B121" t="n">
-        <v>177.6040375011918</v>
+        <v>177.5940686691464</v>
       </c>
       <c r="C121" t="n">
-        <v>179.569546076418</v>
+        <v>177.853470255105</v>
       </c>
       <c r="D121" t="n">
-        <v>175.3890990582871</v>
+        <v>171.3283915093003</v>
       </c>
       <c r="E121" t="n">
-        <v>178.1527862548828</v>
+        <v>172.30615234375</v>
       </c>
       <c r="F121" t="n">
-        <v>170968500</v>
+        <v>241323500</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B122" t="n">
-        <v>177.5940529420793</v>
+        <v>176.8557415306554</v>
       </c>
       <c r="C122" t="n">
-        <v>177.8534545050662</v>
+        <v>177.9632107122345</v>
       </c>
       <c r="D122" t="n">
-        <v>171.3283763370981</v>
+        <v>174.3614429436745</v>
       </c>
       <c r="E122" t="n">
-        <v>172.3061370849609</v>
+        <v>175.2394409179688</v>
       </c>
       <c r="F122" t="n">
-        <v>241323500</v>
+        <v>182836300</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B123" t="n">
-        <v>176.8557415306554</v>
+        <v>174.4312942297872</v>
       </c>
       <c r="C123" t="n">
-        <v>177.9632107122345</v>
+        <v>175.8181236639554</v>
       </c>
       <c r="D123" t="n">
-        <v>174.3614429436745</v>
+        <v>173.5832266030264</v>
       </c>
       <c r="E123" t="n">
-        <v>175.2394409179688</v>
+        <v>174.8004455566406</v>
       </c>
       <c r="F123" t="n">
-        <v>182836300</v>
+        <v>147667800</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B124" t="n">
-        <v>174.4312942297872</v>
+        <v>176.6961233561449</v>
       </c>
       <c r="C124" t="n">
-        <v>175.8181236639554</v>
+        <v>180.8067226806179</v>
       </c>
       <c r="D124" t="n">
-        <v>173.5832266030264</v>
+        <v>176.4466934898736</v>
       </c>
       <c r="E124" t="n">
-        <v>174.8004455566406</v>
+        <v>178.2725067138672</v>
       </c>
       <c r="F124" t="n">
-        <v>147667800</v>
+        <v>162602100</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B125" t="n">
-        <v>176.6961233561449</v>
+        <v>175.6684741654964</v>
       </c>
       <c r="C125" t="n">
-        <v>180.8067226806179</v>
+        <v>176.1074579435819</v>
       </c>
       <c r="D125" t="n">
-        <v>176.4466934898736</v>
+        <v>170.7497092682189</v>
       </c>
       <c r="E125" t="n">
-        <v>178.2725067138672</v>
+        <v>170.8494873046875</v>
       </c>
       <c r="F125" t="n">
-        <v>162602100</v>
+        <v>186152200</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B126" t="n">
-        <v>175.6684741654964</v>
+        <v>169.6123099949711</v>
       </c>
       <c r="C126" t="n">
-        <v>176.1074579435819</v>
+        <v>170.5800990993323</v>
       </c>
       <c r="D126" t="n">
-        <v>170.7497092682189</v>
+        <v>166.629123297364</v>
       </c>
       <c r="E126" t="n">
-        <v>170.8494873046875</v>
+        <v>167.1379699707031</v>
       </c>
       <c r="F126" t="n">
-        <v>186152200</v>
+        <v>196212700</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B127" t="n">
-        <v>169.6122945102883</v>
+        <v>168.3950875250076</v>
       </c>
       <c r="C127" t="n">
-        <v>170.5800835262955</v>
+        <v>169.0635577295173</v>
       </c>
       <c r="D127" t="n">
-        <v>166.6291080850299</v>
+        <v>163.8953782868944</v>
       </c>
       <c r="E127" t="n">
-        <v>167.1379547119141</v>
+        <v>164.7933197021484</v>
       </c>
       <c r="F127" t="n">
-        <v>196212700</v>
+        <v>185627000</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B128" t="n">
-        <v>168.3950875250076</v>
+        <v>166.589210422399</v>
       </c>
       <c r="C128" t="n">
-        <v>169.0635577295173</v>
+        <v>174.2217577880002</v>
       </c>
       <c r="D128" t="n">
-        <v>163.8953782868944</v>
+        <v>166.5792387089764</v>
       </c>
       <c r="E128" t="n">
-        <v>164.7933197021484</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="F128" t="n">
-        <v>185627000</v>
+        <v>226181300</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B129" t="n">
-        <v>166.5892250311153</v>
+        <v>175.5986119754623</v>
       </c>
       <c r="C129" t="n">
-        <v>174.2217730660379</v>
+        <v>176.9654826629128</v>
       </c>
       <c r="D129" t="n">
-        <v>166.5792533168182</v>
+        <v>174.351462742682</v>
       </c>
       <c r="E129" t="n">
-        <v>174.0022735595703</v>
+        <v>175.3491821289062</v>
       </c>
       <c r="F129" t="n">
-        <v>226181300</v>
+        <v>168132000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B130" t="n">
-        <v>175.5986272559566</v>
+        <v>171.787333172162</v>
       </c>
       <c r="C130" t="n">
-        <v>176.9654980623514</v>
+        <v>177.0852364118599</v>
       </c>
       <c r="D130" t="n">
-        <v>174.3514779146501</v>
+        <v>170.9791828272563</v>
       </c>
       <c r="E130" t="n">
-        <v>175.3491973876953</v>
+        <v>176.9854583740234</v>
       </c>
       <c r="F130" t="n">
-        <v>168132000</v>
+        <v>143143200</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B131" t="n">
-        <v>171.7873183615289</v>
+        <v>176.7559774774269</v>
       </c>
       <c r="C131" t="n">
-        <v>177.0852211444685</v>
+        <v>177.3845303646084</v>
       </c>
       <c r="D131" t="n">
-        <v>170.9791680862979</v>
+        <v>175.3591611441553</v>
       </c>
       <c r="E131" t="n">
-        <v>176.9854431152344</v>
+        <v>177.2348785400391</v>
       </c>
       <c r="F131" t="n">
-        <v>143143200</v>
+        <v>107564300</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B132" t="n">
-        <v>176.7559774774269</v>
+        <v>175.3292270516068</v>
       </c>
       <c r="C132" t="n">
-        <v>177.3845303646084</v>
+        <v>177.8235255680002</v>
       </c>
       <c r="D132" t="n">
-        <v>175.3591611441553</v>
+        <v>173.2639557965079</v>
       </c>
       <c r="E132" t="n">
-        <v>177.2348785400391</v>
+        <v>177.6938323974609</v>
       </c>
       <c r="F132" t="n">
-        <v>107564300</v>
+        <v>132534900</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B133" t="n">
-        <v>175.3292270516068</v>
+        <v>184.079243714486</v>
       </c>
       <c r="C133" t="n">
-        <v>177.8235255680002</v>
+        <v>184.837505037226</v>
       </c>
       <c r="D133" t="n">
-        <v>173.2639557965079</v>
+        <v>179.8888249511496</v>
       </c>
       <c r="E133" t="n">
-        <v>177.6938323974609</v>
+        <v>181.6647644042969</v>
       </c>
       <c r="F133" t="n">
-        <v>132534900</v>
+        <v>147732700</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B134" t="n">
-        <v>184.079243714486</v>
+        <v>181.4253138719204</v>
       </c>
       <c r="C134" t="n">
-        <v>184.837505037226</v>
+        <v>183.6602110774668</v>
       </c>
       <c r="D134" t="n">
-        <v>179.8888249511496</v>
+        <v>180.2080948395415</v>
       </c>
       <c r="E134" t="n">
-        <v>181.6647644042969</v>
+        <v>183.4906005859375</v>
       </c>
       <c r="F134" t="n">
-        <v>147732700</v>
+        <v>116428500</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B135" t="n">
-        <v>181.4252987848774</v>
+        <v>183.8896736698189</v>
       </c>
       <c r="C135" t="n">
-        <v>183.6601958045732</v>
+        <v>189.5666999081706</v>
       </c>
       <c r="D135" t="n">
-        <v>180.2080798537204</v>
+        <v>183.8797019557237</v>
       </c>
       <c r="E135" t="n">
-        <v>183.4905853271484</v>
+        <v>188.1998291015625</v>
       </c>
       <c r="F135" t="n">
-        <v>116428500</v>
+        <v>160459500</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B136" t="n">
-        <v>183.8896736698189</v>
+        <v>185.605746824658</v>
       </c>
       <c r="C136" t="n">
-        <v>189.5666999081706</v>
+        <v>189.2274732756209</v>
       </c>
       <c r="D136" t="n">
-        <v>183.8797019557237</v>
+        <v>185.3164148846483</v>
       </c>
       <c r="E136" t="n">
-        <v>188.1998291015625</v>
+        <v>188.8782653808594</v>
       </c>
       <c r="F136" t="n">
-        <v>160459500</v>
+        <v>133648200</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B137" t="n">
-        <v>185.605746824658</v>
+        <v>190.4047764107204</v>
       </c>
       <c r="C137" t="n">
-        <v>189.2274732756209</v>
+        <v>196.0618438720703</v>
       </c>
       <c r="D137" t="n">
-        <v>185.3164148846483</v>
+        <v>190.3349439656124</v>
       </c>
       <c r="E137" t="n">
-        <v>188.8782653808594</v>
+        <v>196.0618438720703</v>
       </c>
       <c r="F137" t="n">
-        <v>133648200</v>
+        <v>161307000</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B138" t="n">
-        <v>190.4047764107204</v>
+        <v>196.0917851116163</v>
       </c>
       <c r="C138" t="n">
-        <v>196.0618438720703</v>
+        <v>199.9429830157183</v>
       </c>
       <c r="D138" t="n">
-        <v>190.3349439656124</v>
+        <v>195.2936216855987</v>
       </c>
       <c r="E138" t="n">
-        <v>196.0618438720703</v>
+        <v>198.4164733886719</v>
       </c>
       <c r="F138" t="n">
-        <v>161307000</v>
+        <v>185338400</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B139" t="n">
-        <v>196.0917851116163</v>
+        <v>196.9797440092329</v>
       </c>
       <c r="C139" t="n">
-        <v>199.9429830157183</v>
+        <v>199.3942384790618</v>
       </c>
       <c r="D139" t="n">
-        <v>195.2936216855987</v>
+        <v>195.3634433694217</v>
       </c>
       <c r="E139" t="n">
-        <v>198.4164733886719</v>
+        <v>197.8976593017578</v>
       </c>
       <c r="F139" t="n">
-        <v>185338400</v>
+        <v>134012900</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B140" t="n">
-        <v>196.9797440092329</v>
+        <v>199.444107632571</v>
       </c>
       <c r="C140" t="n">
-        <v>199.3942384790618</v>
+        <v>201.2400056483541</v>
       </c>
       <c r="D140" t="n">
-        <v>195.3634433694217</v>
+        <v>198.8155547450397</v>
       </c>
       <c r="E140" t="n">
-        <v>197.8976593017578</v>
+        <v>201.2200469970703</v>
       </c>
       <c r="F140" t="n">
-        <v>134012900</v>
+        <v>160324400</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B141" t="n">
-        <v>199.444107632571</v>
+        <v>199.5239239232554</v>
       </c>
       <c r="C141" t="n">
-        <v>201.2400056483541</v>
+        <v>201.7089318732817</v>
       </c>
       <c r="D141" t="n">
-        <v>198.8155547450397</v>
+        <v>197.3888049886708</v>
       </c>
       <c r="E141" t="n">
-        <v>201.2200469970703</v>
+        <v>201.5991821289062</v>
       </c>
       <c r="F141" t="n">
-        <v>160324400</v>
+        <v>119381400</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B142" t="n">
-        <v>199.5239239232554</v>
+        <v>201.6690479582887</v>
       </c>
       <c r="C142" t="n">
-        <v>201.7089318732817</v>
+        <v>202.2876291783034</v>
       </c>
       <c r="D142" t="n">
-        <v>197.3888049886708</v>
+        <v>198.5461810430697</v>
       </c>
       <c r="E142" t="n">
-        <v>201.5991821289062</v>
+        <v>199.4241790771484</v>
       </c>
       <c r="F142" t="n">
-        <v>119381400</v>
+        <v>107945300</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B143" t="n">
-        <v>201.6690479582887</v>
+        <v>200.5316418294082</v>
       </c>
       <c r="C143" t="n">
-        <v>202.2876291783034</v>
+        <v>202.0381927490234</v>
       </c>
       <c r="D143" t="n">
-        <v>198.5461810430697</v>
+        <v>198.546174602744</v>
       </c>
       <c r="E143" t="n">
-        <v>199.4241790771484</v>
+        <v>202.0381927490234</v>
       </c>
       <c r="F143" t="n">
-        <v>107945300</v>
+        <v>107501000</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B144" t="n">
-        <v>200.5316418294082</v>
+        <v>201.9982837593082</v>
       </c>
       <c r="C144" t="n">
-        <v>202.0381927490234</v>
+        <v>203.3651545152774</v>
       </c>
       <c r="D144" t="n">
-        <v>198.546174602744</v>
+        <v>196.7702284327844</v>
       </c>
       <c r="E144" t="n">
-        <v>202.0381927490234</v>
+        <v>199.1847076416016</v>
       </c>
       <c r="F144" t="n">
-        <v>107501000</v>
+        <v>113561800</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B145" t="n">
-        <v>201.9982837593082</v>
+        <v>199.5039827094276</v>
       </c>
       <c r="C145" t="n">
-        <v>203.3651545152774</v>
+        <v>210.468909435165</v>
       </c>
       <c r="D145" t="n">
-        <v>196.7702284327844</v>
+        <v>199.3543156614425</v>
       </c>
       <c r="E145" t="n">
-        <v>199.1847076416016</v>
+        <v>207.7950286865234</v>
       </c>
       <c r="F145" t="n">
-        <v>113561800</v>
+        <v>214134400</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B146" t="n">
-        <v>199.5039827094276</v>
+        <v>209.1718784416434</v>
       </c>
       <c r="C146" t="n">
-        <v>210.468909435165</v>
+        <v>216.335512072091</v>
       </c>
       <c r="D146" t="n">
-        <v>199.3543156614425</v>
+        <v>206.9070662315077</v>
       </c>
       <c r="E146" t="n">
-        <v>207.7950286865234</v>
+        <v>216.1160125732422</v>
       </c>
       <c r="F146" t="n">
-        <v>214134400</v>
+        <v>187172400</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B147" t="n">
-        <v>209.1718784416434</v>
+        <v>209.0122528840405</v>
       </c>
       <c r="C147" t="n">
-        <v>216.335512072091</v>
+        <v>214.2402930542568</v>
       </c>
       <c r="D147" t="n">
-        <v>206.9070662315077</v>
+        <v>207.7251862691963</v>
       </c>
       <c r="E147" t="n">
-        <v>216.1160125732422</v>
+        <v>212.6838531494141</v>
       </c>
       <c r="F147" t="n">
-        <v>187172400</v>
+        <v>180275400</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B148" t="n">
-        <v>209.0122528840405</v>
+        <v>212.2149257168926</v>
       </c>
       <c r="C148" t="n">
-        <v>214.2402930542568</v>
+        <v>212.2348843687743</v>
       </c>
       <c r="D148" t="n">
-        <v>207.7251862691963</v>
+        <v>207.1066069625242</v>
       </c>
       <c r="E148" t="n">
-        <v>212.6838531494141</v>
+        <v>208.7727966308594</v>
       </c>
       <c r="F148" t="n">
-        <v>180275400</v>
+        <v>123711800</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B149" t="n">
-        <v>212.2149257168926</v>
+        <v>209.4512265433391</v>
       </c>
       <c r="C149" t="n">
-        <v>212.2348843687743</v>
+        <v>209.8203930740204</v>
       </c>
       <c r="D149" t="n">
-        <v>207.1066069625242</v>
+        <v>198.2468419328838</v>
       </c>
       <c r="E149" t="n">
-        <v>208.7727966308594</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="F149" t="n">
-        <v>123711800</v>
+        <v>225239200</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B150" t="n">
-        <v>209.4512425942353</v>
+        <v>200.8209846036705</v>
       </c>
       <c r="C150" t="n">
-        <v>209.820409153207</v>
+        <v>202.5370634031337</v>
       </c>
       <c r="D150" t="n">
-        <v>198.2468571251534</v>
+        <v>196.6704677294345</v>
       </c>
       <c r="E150" t="n">
-        <v>199.1148834228516</v>
+        <v>197.9974365234375</v>
       </c>
       <c r="F150" t="n">
-        <v>225239200</v>
+        <v>128647000</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B151" t="n">
-        <v>200.8209691272831</v>
+        <v>199.0450218084295</v>
       </c>
       <c r="C151" t="n">
-        <v>202.5370477944956</v>
+        <v>201.2699318245734</v>
       </c>
       <c r="D151" t="n">
-        <v>196.6704525729091</v>
+        <v>194.2958829090753</v>
       </c>
       <c r="E151" t="n">
-        <v>197.9974212646484</v>
+        <v>198.02734375</v>
       </c>
       <c r="F151" t="n">
-        <v>128647000</v>
+        <v>125368100</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B152" t="n">
-        <v>199.0450218084295</v>
+        <v>198.8454820247872</v>
       </c>
       <c r="C152" t="n">
-        <v>201.2699318245734</v>
+        <v>199.7833407086998</v>
       </c>
       <c r="D152" t="n">
-        <v>194.2958829090753</v>
+        <v>195.5829352820671</v>
       </c>
       <c r="E152" t="n">
-        <v>198.02734375</v>
+        <v>196.0518646240234</v>
       </c>
       <c r="F152" t="n">
-        <v>125368100</v>
+        <v>113406600</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B153" t="n">
-        <v>198.8454820247872</v>
+        <v>199.4341385249406</v>
       </c>
       <c r="C153" t="n">
-        <v>199.7833407086998</v>
+        <v>207.7950323152332</v>
       </c>
       <c r="D153" t="n">
-        <v>195.5829352820671</v>
+        <v>198.1570588579161</v>
       </c>
       <c r="E153" t="n">
-        <v>196.0518646240234</v>
+        <v>207.3560333251953</v>
       </c>
       <c r="F153" t="n">
-        <v>113406600</v>
+        <v>188362800</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B154" t="n">
-        <v>199.4341385249406</v>
+        <v>207.8648724722903</v>
       </c>
       <c r="C154" t="n">
-        <v>207.7950323152332</v>
+        <v>213.7115092245668</v>
       </c>
       <c r="D154" t="n">
-        <v>198.1570588579161</v>
+        <v>206.0290722858257</v>
       </c>
       <c r="E154" t="n">
-        <v>207.3560333251953</v>
+        <v>211.0176696777344</v>
       </c>
       <c r="F154" t="n">
-        <v>188362800</v>
+        <v>168307900</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B155" t="n">
-        <v>207.8648724722903</v>
+        <v>212.5441790763045</v>
       </c>
       <c r="C155" t="n">
-        <v>213.7115092245668</v>
+        <v>217.3033052467507</v>
       </c>
       <c r="D155" t="n">
-        <v>206.0290722858257</v>
+        <v>212.4044989584125</v>
       </c>
       <c r="E155" t="n">
-        <v>211.0176696777344</v>
+        <v>214.709228515625</v>
       </c>
       <c r="F155" t="n">
-        <v>168307900</v>
+        <v>136421400</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B156" t="n">
-        <v>212.5441790763045</v>
+        <v>213.5518657378577</v>
       </c>
       <c r="C156" t="n">
-        <v>217.3033052467507</v>
+        <v>221.7930381906342</v>
       </c>
       <c r="D156" t="n">
-        <v>212.4044989584125</v>
+        <v>213.402213909002</v>
       </c>
       <c r="E156" t="n">
-        <v>214.709228515625</v>
+        <v>218.9395599365234</v>
       </c>
       <c r="F156" t="n">
-        <v>136421400</v>
+        <v>160685800</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B157" t="n">
-        <v>213.5518657378577</v>
+        <v>218.0515943496244</v>
       </c>
       <c r="C157" t="n">
-        <v>221.7930381906342</v>
+        <v>223.239732575863</v>
       </c>
       <c r="D157" t="n">
-        <v>213.402213909002</v>
+        <v>214.4298677829735</v>
       </c>
       <c r="E157" t="n">
-        <v>218.9395599365234</v>
+        <v>220.2765045166016</v>
       </c>
       <c r="F157" t="n">
-        <v>160685800</v>
+        <v>159176600</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B158" t="n">
-        <v>218.0515943496244</v>
+        <v>224.4170305354026</v>
       </c>
       <c r="C158" t="n">
-        <v>223.239732575863</v>
+        <v>227.3203978139454</v>
       </c>
       <c r="D158" t="n">
-        <v>214.4298677829735</v>
+        <v>221.0647077692387</v>
       </c>
       <c r="E158" t="n">
-        <v>220.2765045166016</v>
+        <v>225.3149871826172</v>
       </c>
       <c r="F158" t="n">
-        <v>159176600</v>
+        <v>150405400</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B159" t="n">
-        <v>224.4170305354026</v>
+        <v>229.3258255277811</v>
       </c>
       <c r="C159" t="n">
-        <v>227.3203978139454</v>
+        <v>236.0005559723521</v>
       </c>
       <c r="D159" t="n">
-        <v>221.0647077692387</v>
+        <v>228.7770767762568</v>
       </c>
       <c r="E159" t="n">
-        <v>225.3149871826172</v>
+        <v>235.202392578125</v>
       </c>
       <c r="F159" t="n">
-        <v>150405400</v>
+        <v>180782900</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B160" t="n">
-        <v>229.3258255277811</v>
+        <v>229.2360138852663</v>
       </c>
       <c r="C160" t="n">
-        <v>236.0005559723521</v>
+        <v>230.9720511978</v>
       </c>
       <c r="D160" t="n">
-        <v>228.7770767762568</v>
+        <v>223.7286135177626</v>
       </c>
       <c r="E160" t="n">
-        <v>235.202392578125</v>
+        <v>224.80615234375</v>
       </c>
       <c r="F160" t="n">
-        <v>180782900</v>
+        <v>180977600</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B161" t="n">
-        <v>229.2360294447337</v>
+        <v>229.345773483712</v>
       </c>
       <c r="C161" t="n">
-        <v>230.9720668751014</v>
+        <v>229.4754818886306</v>
       </c>
       <c r="D161" t="n">
-        <v>223.7286287034134</v>
+        <v>217.8719993892805</v>
       </c>
       <c r="E161" t="n">
-        <v>224.8061676025391</v>
+        <v>221.8130035400391</v>
       </c>
       <c r="F161" t="n">
-        <v>180977600</v>
+        <v>146280900</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B162" t="n">
-        <v>229.345773483712</v>
+        <v>219.1191400841904</v>
       </c>
       <c r="C162" t="n">
-        <v>229.4754818886306</v>
+        <v>223.9680572056967</v>
       </c>
       <c r="D162" t="n">
-        <v>217.8719993892805</v>
+        <v>217.4130483552105</v>
       </c>
       <c r="E162" t="n">
-        <v>221.8130035400391</v>
+        <v>220.1068878173828</v>
       </c>
       <c r="F162" t="n">
-        <v>146280900</v>
+        <v>140948200</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B163" t="n">
-        <v>219.1191400841904</v>
+        <v>222.6710257508039</v>
       </c>
       <c r="C163" t="n">
-        <v>223.9680572056967</v>
+        <v>225.6143103895453</v>
       </c>
       <c r="D163" t="n">
-        <v>217.4130483552105</v>
+        <v>219.9971448577806</v>
       </c>
       <c r="E163" t="n">
-        <v>220.1068878173828</v>
+        <v>222.9603729248047</v>
       </c>
       <c r="F163" t="n">
-        <v>140948200</v>
+        <v>184201600</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B164" t="n">
-        <v>222.6710257508039</v>
+        <v>221.7830583738447</v>
       </c>
       <c r="C164" t="n">
-        <v>225.6143103895453</v>
+        <v>226.8814055684356</v>
       </c>
       <c r="D164" t="n">
-        <v>219.9971448577806</v>
+        <v>217.4330007955402</v>
       </c>
       <c r="E164" t="n">
-        <v>222.9603729248047</v>
+        <v>219.0093994140625</v>
       </c>
       <c r="F164" t="n">
-        <v>184201600</v>
+        <v>203381800</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B165" t="n">
-        <v>221.7830583738447</v>
+        <v>220.3962175709585</v>
       </c>
       <c r="C165" t="n">
-        <v>226.8814055684356</v>
+        <v>220.5059673180016</v>
       </c>
       <c r="D165" t="n">
-        <v>217.4330007955402</v>
+        <v>214.3101381389001</v>
       </c>
       <c r="E165" t="n">
-        <v>219.0093994140625</v>
+        <v>214.8389282226562</v>
       </c>
       <c r="F165" t="n">
-        <v>203381800</v>
+        <v>169275700</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B166" t="n">
-        <v>220.3962175709585</v>
+        <v>216.0461718127993</v>
       </c>
       <c r="C166" t="n">
-        <v>220.5059673180016</v>
+        <v>217.6824311685512</v>
       </c>
       <c r="D166" t="n">
-        <v>214.3101381389001</v>
+        <v>211.5165320236786</v>
       </c>
       <c r="E166" t="n">
-        <v>214.8389282226562</v>
+        <v>214.3700103759766</v>
       </c>
       <c r="F166" t="n">
-        <v>169275700</v>
+        <v>187202600</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B167" t="n">
-        <v>216.0461718127993</v>
+        <v>213.6316806617713</v>
       </c>
       <c r="C167" t="n">
-        <v>217.6824311685512</v>
+        <v>213.6616110269177</v>
       </c>
       <c r="D167" t="n">
-        <v>211.5165320236786</v>
+        <v>208.3038625298546</v>
       </c>
       <c r="E167" t="n">
-        <v>214.3700103759766</v>
+        <v>212.1151580810547</v>
       </c>
       <c r="F167" t="n">
-        <v>187202600</v>
+        <v>167601200</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B168" t="n">
-        <v>213.6316806617713</v>
+        <v>210.7981702457166</v>
       </c>
       <c r="C168" t="n">
-        <v>213.6616110269177</v>
+        <v>215.0285063161196</v>
       </c>
       <c r="D168" t="n">
-        <v>208.3038625298546</v>
+        <v>210.738309512832</v>
       </c>
       <c r="E168" t="n">
-        <v>212.1151580810547</v>
+        <v>213.7613983154297</v>
       </c>
       <c r="F168" t="n">
-        <v>167601200</v>
+        <v>143996000</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B169" t="n">
-        <v>210.7981551984497</v>
+        <v>214.0906505321041</v>
       </c>
       <c r="C169" t="n">
-        <v>215.0284909668814</v>
+        <v>217.3631692496548</v>
       </c>
       <c r="D169" t="n">
-        <v>210.7382944698381</v>
+        <v>210.6485213277038</v>
       </c>
       <c r="E169" t="n">
-        <v>213.7613830566406</v>
+        <v>210.6584930419922</v>
       </c>
       <c r="F169" t="n">
-        <v>143996000</v>
+        <v>289410600</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B170" t="n">
-        <v>214.0906505321041</v>
+        <v>215.2380189209027</v>
       </c>
       <c r="C170" t="n">
-        <v>217.3631692496548</v>
+        <v>224.3571743491113</v>
       </c>
       <c r="D170" t="n">
-        <v>210.6485213277038</v>
+        <v>215.2080885544549</v>
       </c>
       <c r="E170" t="n">
-        <v>210.6584930419922</v>
+        <v>223.8483428955078</v>
       </c>
       <c r="F170" t="n">
-        <v>289410600</v>
+        <v>212850700</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B171" t="n">
-        <v>215.2380189209027</v>
+        <v>226.6618858382332</v>
       </c>
       <c r="C171" t="n">
-        <v>224.3571743491113</v>
+        <v>231.7502608645459</v>
       </c>
       <c r="D171" t="n">
-        <v>215.2080885544549</v>
+        <v>220.8451951370975</v>
       </c>
       <c r="E171" t="n">
-        <v>223.8483428955078</v>
+        <v>222.3118438720703</v>
       </c>
       <c r="F171" t="n">
-        <v>212850700</v>
+        <v>193362900</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B172" t="n">
-        <v>226.6618858382332</v>
+        <v>221.2143597561905</v>
       </c>
       <c r="C172" t="n">
-        <v>231.7502608645459</v>
+        <v>222.3118572511273</v>
       </c>
       <c r="D172" t="n">
-        <v>220.8451951370975</v>
+        <v>214.0207957553572</v>
       </c>
       <c r="E172" t="n">
-        <v>222.3118438720703</v>
+        <v>214.26025390625</v>
       </c>
       <c r="F172" t="n">
-        <v>193362900</v>
+        <v>160907000</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,25 +4915,25 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B173" t="n">
-        <v>221.2143597561905</v>
+        <v>213.6709127939037</v>
       </c>
       <c r="C173" t="n">
-        <v>222.3118572511273</v>
+        <v>221.3523199881091</v>
       </c>
       <c r="D173" t="n">
-        <v>214.0207957553572</v>
+        <v>210.73419644349</v>
       </c>
       <c r="E173" t="n">
-        <v>214.26025390625</v>
+        <v>218.4156036376953</v>
       </c>
       <c r="F173" t="n">
-        <v>160907000</v>
+        <v>169022200</v>
       </c>
       <c r="G173" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -4941,25 +4941,25 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B174" t="n">
-        <v>213.6709127939037</v>
+        <v>214.2902104723603</v>
       </c>
       <c r="C174" t="n">
-        <v>221.3523199881091</v>
+        <v>214.6298267834636</v>
       </c>
       <c r="D174" t="n">
-        <v>210.73419644349</v>
+        <v>204.101614447126</v>
       </c>
       <c r="E174" t="n">
-        <v>218.4156036376953</v>
+        <v>204.8707580566406</v>
       </c>
       <c r="F174" t="n">
-        <v>169022200</v>
+        <v>219655500</v>
       </c>
       <c r="G174" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B175" t="n">
-        <v>214.2902104723603</v>
+        <v>209.9450713288228</v>
       </c>
       <c r="C175" t="n">
-        <v>214.6298267834636</v>
+        <v>210.2347557268212</v>
       </c>
       <c r="D175" t="n">
-        <v>204.101614447126</v>
+        <v>205.7697506938822</v>
       </c>
       <c r="E175" t="n">
-        <v>204.8707580566406</v>
+        <v>208.4067993164062</v>
       </c>
       <c r="F175" t="n">
-        <v>219655500</v>
+        <v>138372800</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B176" t="n">
-        <v>209.9450713288228</v>
+        <v>210.3845825512031</v>
       </c>
       <c r="C176" t="n">
-        <v>210.2347557268212</v>
+        <v>211.1637095162451</v>
       </c>
       <c r="D176" t="n">
-        <v>205.7697506938822</v>
+        <v>199.1171915656509</v>
       </c>
       <c r="E176" t="n">
-        <v>208.4067993164062</v>
+        <v>207.9573059082031</v>
       </c>
       <c r="F176" t="n">
-        <v>138372800</v>
+        <v>180962500</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B177" t="n">
-        <v>210.3845825512031</v>
+        <v>204.2014963256503</v>
       </c>
       <c r="C177" t="n">
-        <v>211.1637095162451</v>
+        <v>206.9883864105018</v>
       </c>
       <c r="D177" t="n">
-        <v>199.1171915656509</v>
+        <v>199.696542748819</v>
       </c>
       <c r="E177" t="n">
-        <v>207.9573059082031</v>
+        <v>200.1959838867188</v>
       </c>
       <c r="F177" t="n">
-        <v>180962500</v>
+        <v>161746600</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B178" t="n">
-        <v>204.2014963256503</v>
+        <v>201.2647947500858</v>
       </c>
       <c r="C178" t="n">
-        <v>206.9883864105018</v>
+        <v>205.4301320010667</v>
       </c>
       <c r="D178" t="n">
-        <v>199.696542748819</v>
+        <v>199.3169621236104</v>
       </c>
       <c r="E178" t="n">
-        <v>200.1959838867188</v>
+        <v>204.6410064697266</v>
       </c>
       <c r="F178" t="n">
-        <v>161746600</v>
+        <v>158643200</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B179" t="n">
-        <v>201.2647947500858</v>
+        <v>204.6310298517525</v>
       </c>
       <c r="C179" t="n">
-        <v>205.4301320010667</v>
+        <v>206.8385664547524</v>
       </c>
       <c r="D179" t="n">
-        <v>199.3169621236104</v>
+        <v>203.2126188059985</v>
       </c>
       <c r="E179" t="n">
-        <v>204.6410064697266</v>
+        <v>204.9606628417969</v>
       </c>
       <c r="F179" t="n">
-        <v>158643200</v>
+        <v>112001800</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B180" t="n">
-        <v>204.6310298517525</v>
+        <v>208.6864864049894</v>
       </c>
       <c r="C180" t="n">
-        <v>206.8385664547524</v>
+        <v>212.4722588232193</v>
       </c>
       <c r="D180" t="n">
-        <v>203.2126188059985</v>
+        <v>208.1071328472061</v>
       </c>
       <c r="E180" t="n">
-        <v>204.9606628417969</v>
+        <v>212.2125396728516</v>
       </c>
       <c r="F180" t="n">
-        <v>112001800</v>
+        <v>149936700</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B181" t="n">
-        <v>208.6864864049894</v>
+        <v>210.9439520928381</v>
       </c>
       <c r="C181" t="n">
-        <v>212.4722588232193</v>
+        <v>211.2536184019877</v>
       </c>
       <c r="D181" t="n">
-        <v>208.1071328472061</v>
+        <v>207.0583006421773</v>
       </c>
       <c r="E181" t="n">
-        <v>212.2125396728516</v>
+        <v>207.1781768798828</v>
       </c>
       <c r="F181" t="n">
-        <v>149936700</v>
+        <v>125694100</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B182" t="n">
-        <v>210.9439520928381</v>
+        <v>208.2969174543329</v>
       </c>
       <c r="C182" t="n">
-        <v>211.2536184019877</v>
+        <v>208.9761653200819</v>
       </c>
       <c r="D182" t="n">
-        <v>207.0583006421773</v>
+        <v>202.8530121596522</v>
       </c>
       <c r="E182" t="n">
-        <v>207.1781768798828</v>
+        <v>204.4212493896484</v>
       </c>
       <c r="F182" t="n">
-        <v>125694100</v>
+        <v>128363500</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B183" t="n">
-        <v>208.2969174543329</v>
+        <v>207.0982684229139</v>
       </c>
       <c r="C183" t="n">
-        <v>208.9761653200819</v>
+        <v>211.1537281092123</v>
       </c>
       <c r="D183" t="n">
-        <v>202.8530121596522</v>
+        <v>206.2691942875683</v>
       </c>
       <c r="E183" t="n">
-        <v>204.4212493896484</v>
+        <v>210.4545135498047</v>
       </c>
       <c r="F183" t="n">
-        <v>128363500</v>
+        <v>241272000</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B184" t="n">
-        <v>207.0982684229139</v>
+        <v>211.2036686200953</v>
       </c>
       <c r="C184" t="n">
-        <v>211.1537281092123</v>
+        <v>213.7508214450341</v>
       </c>
       <c r="D184" t="n">
-        <v>206.2691942875683</v>
+        <v>207.4878253737282</v>
       </c>
       <c r="E184" t="n">
-        <v>210.4545135498047</v>
+        <v>208.4167785644531</v>
       </c>
       <c r="F184" t="n">
-        <v>241272000</v>
+        <v>122041400</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B185" t="n">
-        <v>211.2036686200953</v>
+        <v>201.9440304014853</v>
       </c>
       <c r="C185" t="n">
-        <v>213.7508214450341</v>
+        <v>203.5422481594977</v>
       </c>
       <c r="D185" t="n">
-        <v>207.4878253737282</v>
+        <v>199.77645766483</v>
       </c>
       <c r="E185" t="n">
-        <v>208.4167785644531</v>
+        <v>199.81640625</v>
       </c>
       <c r="F185" t="n">
-        <v>122041400</v>
+        <v>153496200</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B186" t="n">
-        <v>201.9440304014853</v>
+        <v>199.8963159019567</v>
       </c>
       <c r="C186" t="n">
-        <v>203.5422481594977</v>
+        <v>201.4445864758279</v>
       </c>
       <c r="D186" t="n">
-        <v>199.77645766483</v>
+        <v>196.360279356477</v>
       </c>
       <c r="E186" t="n">
-        <v>199.81640625</v>
+        <v>198.7775726318359</v>
       </c>
       <c r="F186" t="n">
-        <v>153496200</v>
+        <v>151810700</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B187" t="n">
-        <v>199.8963159019567</v>
+        <v>199.8563704571445</v>
       </c>
       <c r="C187" t="n">
-        <v>201.4445864758279</v>
+        <v>200.5755669254449</v>
       </c>
       <c r="D187" t="n">
-        <v>196.360279356477</v>
+        <v>191.9152592982058</v>
       </c>
       <c r="E187" t="n">
-        <v>198.7775726318359</v>
+        <v>195.5212249755859</v>
       </c>
       <c r="F187" t="n">
-        <v>151810700</v>
+        <v>149550000</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B188" t="n">
-        <v>199.8563704571445</v>
+        <v>192.9041409641119</v>
       </c>
       <c r="C188" t="n">
-        <v>200.5755669254449</v>
+        <v>195.331432829306</v>
       </c>
       <c r="D188" t="n">
-        <v>191.9152592982058</v>
+        <v>191.0062707295152</v>
       </c>
       <c r="E188" t="n">
-        <v>195.5212249755859</v>
+        <v>192.3148040771484</v>
       </c>
       <c r="F188" t="n">
-        <v>149550000</v>
+        <v>179304100</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B189" t="n">
-        <v>192.9041409641119</v>
+        <v>193.6333319429392</v>
       </c>
       <c r="C189" t="n">
-        <v>195.331432829306</v>
+        <v>195.9607141929515</v>
       </c>
       <c r="D189" t="n">
-        <v>191.0062707295152</v>
+        <v>189.5878557469149</v>
       </c>
       <c r="E189" t="n">
-        <v>192.3148040771484</v>
+        <v>194.7520751953125</v>
       </c>
       <c r="F189" t="n">
-        <v>179304100</v>
+        <v>148835700</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B190" t="n">
-        <v>193.6333319429392</v>
+        <v>197.0195429632178</v>
       </c>
       <c r="C190" t="n">
-        <v>195.9607141929515</v>
+        <v>200.4057532237791</v>
       </c>
       <c r="D190" t="n">
-        <v>189.5878557469149</v>
+        <v>194.8919188665145</v>
       </c>
       <c r="E190" t="n">
-        <v>194.7520751953125</v>
+        <v>199.8663482666016</v>
       </c>
       <c r="F190" t="n">
-        <v>148835700</v>
+        <v>166476700</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B191" t="n">
-        <v>197.0195429632178</v>
+        <v>195.9806989625188</v>
       </c>
       <c r="C191" t="n">
-        <v>200.4057532237791</v>
+        <v>199.626628404907</v>
       </c>
       <c r="D191" t="n">
-        <v>194.8919188665145</v>
+        <v>193.2337727110923</v>
       </c>
       <c r="E191" t="n">
-        <v>199.8663482666016</v>
+        <v>197.3591613769531</v>
       </c>
       <c r="F191" t="n">
-        <v>166476700</v>
+        <v>146147600</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B192" t="n">
-        <v>195.9806989625188</v>
+        <v>196.9196593659626</v>
       </c>
       <c r="C192" t="n">
-        <v>199.626628404907</v>
+        <v>199.8363939026278</v>
       </c>
       <c r="D192" t="n">
-        <v>193.2337727110923</v>
+        <v>192.1350197738411</v>
       </c>
       <c r="E192" t="n">
-        <v>197.3591613769531</v>
+        <v>194.6122436523438</v>
       </c>
       <c r="F192" t="n">
-        <v>146147600</v>
+        <v>142068700</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B193" t="n">
-        <v>196.9196593659626</v>
+        <v>194.202694284663</v>
       </c>
       <c r="C193" t="n">
-        <v>199.8363939026278</v>
+        <v>197.3292007505161</v>
       </c>
       <c r="D193" t="n">
-        <v>192.1350197738411</v>
+        <v>193.7731822131383</v>
       </c>
       <c r="E193" t="n">
-        <v>194.6122436523438</v>
+        <v>195.3314361572266</v>
       </c>
       <c r="F193" t="n">
-        <v>142068700</v>
+        <v>108999000</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B194" t="n">
-        <v>194.202694284663</v>
+        <v>192.1549837798622</v>
       </c>
       <c r="C194" t="n">
-        <v>197.3292007505161</v>
+        <v>198.1882414262674</v>
       </c>
       <c r="D194" t="n">
-        <v>193.7731822131383</v>
+        <v>190.9263628146717</v>
       </c>
       <c r="E194" t="n">
-        <v>195.3314361572266</v>
+        <v>196.7098846435547</v>
       </c>
       <c r="F194" t="n">
-        <v>108999000</v>
+        <v>124154600</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B195" t="n">
-        <v>192.1549837798622</v>
+        <v>194.9618356993413</v>
       </c>
       <c r="C195" t="n">
-        <v>198.1882414262674</v>
+        <v>204.9306918075912</v>
       </c>
       <c r="D195" t="n">
-        <v>190.9263628146717</v>
+        <v>194.841974703339</v>
       </c>
       <c r="E195" t="n">
-        <v>196.7098846435547</v>
+        <v>203.891845703125</v>
       </c>
       <c r="F195" t="n">
-        <v>124154600</v>
+        <v>147419100</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B196" t="n">
-        <v>194.9618356993413</v>
+        <v>204.2314748595287</v>
       </c>
       <c r="C196" t="n">
-        <v>204.9306918075912</v>
+        <v>204.3613191897594</v>
       </c>
       <c r="D196" t="n">
-        <v>194.841974703339</v>
+        <v>198.7376223952696</v>
       </c>
       <c r="E196" t="n">
-        <v>203.891845703125</v>
+        <v>202.5533447265625</v>
       </c>
       <c r="F196" t="n">
-        <v>147419100</v>
+        <v>132037400</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B197" t="n">
-        <v>204.2314748595287</v>
+        <v>201.7742207048944</v>
       </c>
       <c r="C197" t="n">
-        <v>204.3613191897594</v>
+        <v>210.7641612313501</v>
       </c>
       <c r="D197" t="n">
-        <v>198.7376223952696</v>
+        <v>201.6943082934289</v>
       </c>
       <c r="E197" t="n">
-        <v>202.5533447265625</v>
+        <v>210.7242126464844</v>
       </c>
       <c r="F197" t="n">
-        <v>132037400</v>
+        <v>148421000</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B198" t="n">
-        <v>201.7742207048944</v>
+        <v>208.3069001369788</v>
       </c>
       <c r="C198" t="n">
-        <v>210.7641612313501</v>
+        <v>210.3346451505122</v>
       </c>
       <c r="D198" t="n">
-        <v>201.6943082934289</v>
+        <v>202.7730991138312</v>
       </c>
       <c r="E198" t="n">
-        <v>210.7242126464844</v>
+        <v>203.3025054931641</v>
       </c>
       <c r="F198" t="n">
-        <v>148421000</v>
+        <v>121411000</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B199" t="n">
-        <v>208.3069001369788</v>
+        <v>207.9672957533915</v>
       </c>
       <c r="C199" t="n">
-        <v>210.3346451505122</v>
+        <v>212.3124399374416</v>
       </c>
       <c r="D199" t="n">
-        <v>202.7730991138312</v>
+        <v>203.5722196467825</v>
       </c>
       <c r="E199" t="n">
-        <v>203.3025054931641</v>
+        <v>211.5632781982422</v>
       </c>
       <c r="F199" t="n">
-        <v>121411000</v>
+        <v>124379600</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B200" t="n">
-        <v>207.9672957533915</v>
+        <v>211.7230919717581</v>
       </c>
       <c r="C200" t="n">
-        <v>212.3124399374416</v>
+        <v>213.5710150202495</v>
       </c>
       <c r="D200" t="n">
-        <v>203.5722196467825</v>
+        <v>205.8096955397309</v>
       </c>
       <c r="E200" t="n">
-        <v>211.5632781982422</v>
+        <v>212.2624816894531</v>
       </c>
       <c r="F200" t="n">
-        <v>124379600</v>
+        <v>124797200</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B201" t="n">
-        <v>211.7230919717581</v>
+        <v>209.9350906043833</v>
       </c>
       <c r="C201" t="n">
-        <v>213.5710150202495</v>
+        <v>210.8440771529852</v>
       </c>
       <c r="D201" t="n">
-        <v>205.8096955397309</v>
+        <v>205.6199270055466</v>
       </c>
       <c r="E201" t="n">
-        <v>212.2624816894531</v>
+        <v>207.1681823730469</v>
       </c>
       <c r="F201" t="n">
-        <v>124797200</v>
+        <v>122986100</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B202" t="n">
-        <v>209.9350906043833</v>
+        <v>202.4135048295048</v>
       </c>
       <c r="C202" t="n">
-        <v>210.8440771529852</v>
+        <v>206.4190172896336</v>
       </c>
       <c r="D202" t="n">
-        <v>205.6199270055466</v>
+        <v>197.7487264058434</v>
       </c>
       <c r="E202" t="n">
-        <v>207.1681823730469</v>
+        <v>202.5833129882812</v>
       </c>
       <c r="F202" t="n">
-        <v>122986100</v>
+        <v>144281900</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B203" t="n">
-        <v>202.4135048295048</v>
+        <v>205.639896943356</v>
       </c>
       <c r="C203" t="n">
-        <v>206.4190172896336</v>
+        <v>207.5078172334397</v>
       </c>
       <c r="D203" t="n">
-        <v>197.7487264058434</v>
+        <v>202.0539130969454</v>
       </c>
       <c r="E203" t="n">
-        <v>202.5833129882812</v>
+        <v>203.0527954101562</v>
       </c>
       <c r="F203" t="n">
-        <v>144281900</v>
+        <v>88701500</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B204" t="n">
-        <v>205.639896943356</v>
+        <v>207.308024406286</v>
       </c>
       <c r="C204" t="n">
-        <v>207.5078172334397</v>
+        <v>208.4167843613107</v>
       </c>
       <c r="D204" t="n">
-        <v>202.0539130969454</v>
+        <v>203.7819711309363</v>
       </c>
       <c r="E204" t="n">
-        <v>203.0527954101562</v>
+        <v>207.0583038330078</v>
       </c>
       <c r="F204" t="n">
-        <v>88701500</v>
+        <v>108685600</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B205" t="n">
-        <v>207.308024406286</v>
+        <v>205.579968274895</v>
       </c>
       <c r="C205" t="n">
-        <v>208.4167843613107</v>
+        <v>214.1503804276117</v>
       </c>
       <c r="D205" t="n">
-        <v>203.7819711309363</v>
+        <v>204.7209288682105</v>
       </c>
       <c r="E205" t="n">
-        <v>207.0583038330078</v>
+        <v>211.8229827880859</v>
       </c>
       <c r="F205" t="n">
-        <v>108685600</v>
+        <v>137645600</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B206" t="n">
-        <v>205.579968274895</v>
+        <v>209.2258868865651</v>
       </c>
       <c r="C206" t="n">
-        <v>214.1503804276117</v>
+        <v>210.6342993029147</v>
       </c>
       <c r="D206" t="n">
-        <v>204.7209288682105</v>
+        <v>205.7297989431358</v>
       </c>
       <c r="E206" t="n">
-        <v>211.8229827880859</v>
+        <v>208.5266571044922</v>
       </c>
       <c r="F206" t="n">
-        <v>137645600</v>
+        <v>110505300</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B207" t="n">
-        <v>209.2258868865651</v>
+        <v>207.2181292349697</v>
       </c>
       <c r="C207" t="n">
-        <v>210.6342993029147</v>
+        <v>211.6731509810223</v>
       </c>
       <c r="D207" t="n">
-        <v>205.7297989431358</v>
+        <v>204.5810805834776</v>
       </c>
       <c r="E207" t="n">
-        <v>208.5266571044922</v>
+        <v>206.6088104248047</v>
       </c>
       <c r="F207" t="n">
-        <v>110505300</v>
+        <v>114836800</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B208" t="n">
-        <v>207.2181292349697</v>
+        <v>207.9672962732577</v>
       </c>
       <c r="C208" t="n">
-        <v>211.6731509810223</v>
+        <v>208.5166845983908</v>
       </c>
       <c r="D208" t="n">
-        <v>204.5810805834776</v>
+        <v>195.2215633388429</v>
       </c>
       <c r="E208" t="n">
-        <v>206.6088104248047</v>
+        <v>196.2903594970703</v>
       </c>
       <c r="F208" t="n">
-        <v>114836800</v>
+        <v>154353700</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B209" t="n">
-        <v>207.9672962732577</v>
+        <v>194.782047001347</v>
       </c>
       <c r="C209" t="n">
-        <v>208.5166845983908</v>
+        <v>198.4779084345641</v>
       </c>
       <c r="D209" t="n">
-        <v>195.2215633388429</v>
+        <v>192.5245785077403</v>
       </c>
       <c r="E209" t="n">
-        <v>196.2903594970703</v>
+        <v>196.789794921875</v>
       </c>
       <c r="F209" t="n">
-        <v>154353700</v>
+        <v>134111500</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B210" t="n">
-        <v>194.782047001347</v>
+        <v>195.6311069684468</v>
       </c>
       <c r="C210" t="n">
-        <v>198.4779084345641</v>
+        <v>196.8497446088402</v>
       </c>
       <c r="D210" t="n">
-        <v>192.5245785077403</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="E210" t="n">
-        <v>196.789794921875</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="F210" t="n">
-        <v>134111500</v>
+        <v>147680800</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B211" t="n">
-        <v>195.6311069684468</v>
+        <v>193.2337718176948</v>
       </c>
       <c r="C211" t="n">
-        <v>196.8497446088402</v>
+        <v>197.0295274868271</v>
       </c>
       <c r="D211" t="n">
-        <v>189.7976226806641</v>
+        <v>191.3059363552755</v>
       </c>
       <c r="E211" t="n">
-        <v>189.7976226806641</v>
+        <v>194.8219909667969</v>
       </c>
       <c r="F211" t="n">
-        <v>147680800</v>
+        <v>129010200</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B212" t="n">
-        <v>193.2337718176948</v>
+        <v>198.2182038580375</v>
       </c>
       <c r="C212" t="n">
-        <v>197.0295274868271</v>
+        <v>201.7742223680242</v>
       </c>
       <c r="D212" t="n">
-        <v>191.3059363552755</v>
+        <v>194.7320991825756</v>
       </c>
       <c r="E212" t="n">
-        <v>194.8219909667969</v>
+        <v>200.5256195068359</v>
       </c>
       <c r="F212" t="n">
-        <v>129010200</v>
+        <v>139961200</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B213" t="n">
-        <v>198.2182038580375</v>
+        <v>197.4690486270115</v>
       </c>
       <c r="C213" t="n">
-        <v>201.7742223680242</v>
+        <v>208.506701330784</v>
       </c>
       <c r="D213" t="n">
-        <v>194.7320991825756</v>
+        <v>196.6299911347511</v>
       </c>
       <c r="E213" t="n">
-        <v>200.5256195068359</v>
+        <v>206.4090423583984</v>
       </c>
       <c r="F213" t="n">
-        <v>139961200</v>
+        <v>128406900</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B214" t="n">
-        <v>197.4690486270115</v>
+        <v>211.0638257011038</v>
       </c>
       <c r="C214" t="n">
-        <v>208.506701330784</v>
+        <v>212.8218530009649</v>
       </c>
       <c r="D214" t="n">
-        <v>196.6299911347511</v>
+        <v>208.8163406042335</v>
       </c>
       <c r="E214" t="n">
-        <v>206.4090423583984</v>
+        <v>211.7031097412109</v>
       </c>
       <c r="F214" t="n">
-        <v>128406900</v>
+        <v>134922000</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B215" t="n">
-        <v>211.0638257011038</v>
+        <v>216.6176127852948</v>
       </c>
       <c r="C215" t="n">
-        <v>212.8218530009649</v>
+        <v>221.9716224388697</v>
       </c>
       <c r="D215" t="n">
-        <v>208.8163406042335</v>
+        <v>216.1581202281489</v>
       </c>
       <c r="E215" t="n">
-        <v>211.7031097412109</v>
+        <v>218.9749755859375</v>
       </c>
       <c r="F215" t="n">
-        <v>134922000</v>
+        <v>158187400</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B216" t="n">
-        <v>216.6176127852948</v>
+        <v>221.2823935806188</v>
       </c>
       <c r="C216" t="n">
-        <v>221.9716224388697</v>
+        <v>223.3800524967045</v>
       </c>
       <c r="D216" t="n">
-        <v>216.1581202281489</v>
+        <v>216.7574580038405</v>
       </c>
       <c r="E216" t="n">
-        <v>218.9749755859375</v>
+        <v>218.7452392578125</v>
       </c>
       <c r="F216" t="n">
-        <v>158187400</v>
+        <v>113940600</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B217" t="n">
-        <v>221.2823935806188</v>
+        <v>221.2923777041913</v>
       </c>
       <c r="C217" t="n">
-        <v>223.3800524967045</v>
+        <v>224.5087799247126</v>
       </c>
       <c r="D217" t="n">
-        <v>216.7574580038405</v>
+        <v>220.4133716458871</v>
       </c>
       <c r="E217" t="n">
-        <v>218.7452392578125</v>
+        <v>223.7096862792969</v>
       </c>
       <c r="F217" t="n">
-        <v>113940600</v>
+        <v>105669400</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B218" t="n">
-        <v>221.2923777041913</v>
+        <v>223.1502910726907</v>
       </c>
       <c r="C218" t="n">
-        <v>224.5087799247126</v>
+        <v>223.8894694330602</v>
       </c>
       <c r="D218" t="n">
-        <v>220.4133716458871</v>
+        <v>216.5277120448001</v>
       </c>
       <c r="E218" t="n">
-        <v>223.7096862792969</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="F218" t="n">
-        <v>105669400</v>
+        <v>115846600</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B219" t="n">
-        <v>223.1502910726907</v>
+        <v>221.9216754142795</v>
       </c>
       <c r="C219" t="n">
-        <v>223.8894694330602</v>
+        <v>221.9516406634887</v>
       </c>
       <c r="D219" t="n">
-        <v>216.5277120448001</v>
+        <v>215.9583469538982</v>
       </c>
       <c r="E219" t="n">
-        <v>217.3068389892578</v>
+        <v>217.2568969726562</v>
       </c>
       <c r="F219" t="n">
-        <v>115846600</v>
+        <v>101273100</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B220" t="n">
-        <v>221.9216754142795</v>
+        <v>220.7929293559802</v>
       </c>
       <c r="C220" t="n">
-        <v>221.9516406634887</v>
+        <v>224.848404158734</v>
       </c>
       <c r="D220" t="n">
-        <v>215.9583469538982</v>
+        <v>219.9538719106106</v>
       </c>
       <c r="E220" t="n">
-        <v>217.2568969726562</v>
+        <v>223.8395233154297</v>
       </c>
       <c r="F220" t="n">
-        <v>101273100</v>
+        <v>108783600</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B221" t="n">
-        <v>220.7929293559802</v>
+        <v>224.8084500146858</v>
       </c>
       <c r="C221" t="n">
-        <v>224.848404158734</v>
+        <v>226.9760227961096</v>
       </c>
       <c r="D221" t="n">
-        <v>219.9538719106106</v>
+        <v>223.4599680426375</v>
       </c>
       <c r="E221" t="n">
-        <v>223.8395233154297</v>
+        <v>225.0481872558594</v>
       </c>
       <c r="F221" t="n">
-        <v>108783600</v>
+        <v>98867200</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B222" t="n">
-        <v>224.8084500146858</v>
+        <v>226.5165415533859</v>
       </c>
       <c r="C222" t="n">
-        <v>226.9760227961096</v>
+        <v>227.2357380227387</v>
       </c>
       <c r="D222" t="n">
-        <v>223.4599680426375</v>
+        <v>224.2490744835724</v>
       </c>
       <c r="E222" t="n">
-        <v>225.0481872558594</v>
+        <v>224.9083404541016</v>
       </c>
       <c r="F222" t="n">
-        <v>98867200</v>
+        <v>75680900</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B223" t="n">
-        <v>226.5165415533859</v>
+        <v>225.7274161885591</v>
       </c>
       <c r="C223" t="n">
-        <v>227.2357380227387</v>
+        <v>227.6652502746616</v>
       </c>
       <c r="D223" t="n">
-        <v>224.2490744835724</v>
+        <v>224.6086728983284</v>
       </c>
       <c r="E223" t="n">
-        <v>224.9083404541016</v>
+        <v>224.7584991455078</v>
       </c>
       <c r="F223" t="n">
-        <v>75680900</v>
+        <v>93678700</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B224" t="n">
-        <v>225.7274161885591</v>
+        <v>220.203597915372</v>
       </c>
       <c r="C224" t="n">
-        <v>227.6652502746616</v>
+        <v>221.3922702798686</v>
       </c>
       <c r="D224" t="n">
-        <v>224.6086728983284</v>
+        <v>218.4455705709327</v>
       </c>
       <c r="E224" t="n">
-        <v>224.7584991455078</v>
+        <v>219.4944000244141</v>
       </c>
       <c r="F224" t="n">
-        <v>93678700</v>
+        <v>103128200</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B225" t="n">
-        <v>220.203597915372</v>
+        <v>221.4222404106533</v>
       </c>
       <c r="C225" t="n">
-        <v>221.3922702798686</v>
+        <v>222.6208961374568</v>
       </c>
       <c r="D225" t="n">
-        <v>218.4455705709327</v>
+        <v>216.5177245976465</v>
       </c>
       <c r="E225" t="n">
-        <v>219.4944000244141</v>
+        <v>217.3168334960938</v>
       </c>
       <c r="F225" t="n">
-        <v>103128200</v>
+        <v>96797300</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B226" t="n">
-        <v>221.4222404106533</v>
+        <v>218.1159423024499</v>
       </c>
       <c r="C226" t="n">
-        <v>222.6208961374568</v>
+        <v>219.6142657707553</v>
       </c>
       <c r="D226" t="n">
-        <v>216.5177245976465</v>
+        <v>215.418963107847</v>
       </c>
       <c r="E226" t="n">
-        <v>217.3168334960938</v>
+        <v>216.6076354980469</v>
       </c>
       <c r="F226" t="n">
-        <v>96797300</v>
+        <v>92457000</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B227" t="n">
-        <v>218.1159423024499</v>
+        <v>218.1758724878036</v>
       </c>
       <c r="C227" t="n">
-        <v>219.6142657707553</v>
+        <v>218.4955221432803</v>
       </c>
       <c r="D227" t="n">
-        <v>215.418963107847</v>
+        <v>214.2602556586216</v>
       </c>
       <c r="E227" t="n">
-        <v>216.6076354980469</v>
+        <v>214.4800109863281</v>
       </c>
       <c r="F227" t="n">
-        <v>92457000</v>
+        <v>98869300</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B228" t="n">
-        <v>218.1758724878036</v>
+        <v>215.2891020611033</v>
       </c>
       <c r="C228" t="n">
-        <v>218.4955221432803</v>
+        <v>215.3490325607492</v>
       </c>
       <c r="D228" t="n">
-        <v>214.2602556586216</v>
+        <v>207.0183577918231</v>
       </c>
       <c r="E228" t="n">
-        <v>214.4800109863281</v>
+        <v>208.2469787597656</v>
       </c>
       <c r="F228" t="n">
-        <v>98869300</v>
+        <v>135187300</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B229" t="n">
-        <v>215.2891020611033</v>
+        <v>210.7941279013131</v>
       </c>
       <c r="C229" t="n">
-        <v>215.3490325607492</v>
+        <v>214.4899893165327</v>
       </c>
       <c r="D229" t="n">
-        <v>207.0183577918231</v>
+        <v>209.8751580258669</v>
       </c>
       <c r="E229" t="n">
-        <v>208.2469787597656</v>
+        <v>212.8118743896484</v>
       </c>
       <c r="F229" t="n">
-        <v>135187300</v>
+        <v>122309000</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B230" t="n">
-        <v>210.7941279013131</v>
+        <v>212.4023240594531</v>
       </c>
       <c r="C230" t="n">
-        <v>214.4899893165327</v>
+        <v>213.3612577394914</v>
       </c>
       <c r="D230" t="n">
-        <v>209.8751580258669</v>
+        <v>208.9961318803605</v>
       </c>
       <c r="E230" t="n">
-        <v>212.8118743896484</v>
+        <v>209.4256591796875</v>
       </c>
       <c r="F230" t="n">
-        <v>122309000</v>
+        <v>179900000</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B231" t="n">
-        <v>212.4023240594531</v>
+        <v>222.6109016432552</v>
       </c>
       <c r="C231" t="n">
-        <v>213.3612577394914</v>
+        <v>230.2123962709879</v>
       </c>
       <c r="D231" t="n">
-        <v>208.9961318803605</v>
+        <v>220.6530857022795</v>
       </c>
       <c r="E231" t="n">
-        <v>209.4256591796875</v>
+        <v>227.7251739501953</v>
       </c>
       <c r="F231" t="n">
-        <v>179900000</v>
+        <v>298909800</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B232" t="n">
-        <v>222.6109016432552</v>
+        <v>227.1058715337123</v>
       </c>
       <c r="C232" t="n">
-        <v>230.2123962709879</v>
+        <v>229.003741733446</v>
       </c>
       <c r="D232" t="n">
-        <v>220.6530857022795</v>
+        <v>216.5676606288883</v>
       </c>
       <c r="E232" t="n">
-        <v>227.7251739501953</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="F232" t="n">
-        <v>298909800</v>
+        <v>195116400</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B233" t="n">
-        <v>227.1058715337123</v>
+        <v>218.6253647857836</v>
       </c>
       <c r="C233" t="n">
-        <v>229.003741733446</v>
+        <v>221.0526567078369</v>
       </c>
       <c r="D233" t="n">
-        <v>216.5676606288883</v>
+        <v>215.9683494434545</v>
       </c>
       <c r="E233" t="n">
-        <v>217.3068389892578</v>
+        <v>220.5332336425781</v>
       </c>
       <c r="F233" t="n">
-        <v>195116400</v>
+        <v>124702700</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B234" t="n">
-        <v>218.6253647857836</v>
+        <v>216.5077444634259</v>
       </c>
       <c r="C234" t="n">
-        <v>221.0526567078369</v>
+        <v>220.1636574397174</v>
       </c>
       <c r="D234" t="n">
-        <v>215.9683494434545</v>
+        <v>214.8595947199138</v>
       </c>
       <c r="E234" t="n">
-        <v>220.5332336425781</v>
+        <v>217.1969757080078</v>
       </c>
       <c r="F234" t="n">
-        <v>124702700</v>
+        <v>109756200</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B235" t="n">
-        <v>216.5077444634259</v>
+        <v>218.5454508199983</v>
       </c>
       <c r="C235" t="n">
-        <v>220.1636574397174</v>
+        <v>227.6952163087265</v>
       </c>
       <c r="D235" t="n">
-        <v>214.8595947199138</v>
+        <v>218.2357997469377</v>
       </c>
       <c r="E235" t="n">
-        <v>217.1969757080078</v>
+        <v>224.1591796875</v>
       </c>
       <c r="F235" t="n">
-        <v>109756200</v>
+        <v>157104700</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B236" t="n">
-        <v>218.5454508199983</v>
+        <v>225.7673797205316</v>
       </c>
       <c r="C236" t="n">
-        <v>227.6952163087265</v>
+        <v>230.1424737915274</v>
       </c>
       <c r="D236" t="n">
-        <v>218.2357997469377</v>
+        <v>224.4987949430455</v>
       </c>
       <c r="E236" t="n">
-        <v>224.1591796875</v>
+        <v>228.1946563720703</v>
       </c>
       <c r="F236" t="n">
-        <v>157104700</v>
+        <v>134681600</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B237" t="n">
-        <v>225.7673797205316</v>
+        <v>230.8317036041433</v>
       </c>
       <c r="C237" t="n">
-        <v>230.1424737915274</v>
+        <v>234.4975997614268</v>
       </c>
       <c r="D237" t="n">
-        <v>224.4987949430455</v>
+        <v>229.3733440032785</v>
       </c>
       <c r="E237" t="n">
-        <v>228.1946563720703</v>
+        <v>230.1025238037109</v>
       </c>
       <c r="F237" t="n">
-        <v>134681600</v>
+        <v>135352400</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B238" t="n">
-        <v>230.8317036041433</v>
+        <v>232.8494477166676</v>
       </c>
       <c r="C238" t="n">
-        <v>234.4975997614268</v>
+        <v>233.4487831783142</v>
       </c>
       <c r="D238" t="n">
-        <v>229.3733440032785</v>
+        <v>224.5986856128386</v>
       </c>
       <c r="E238" t="n">
-        <v>230.1025238037109</v>
+        <v>225.4776916503906</v>
       </c>
       <c r="F238" t="n">
-        <v>135352400</v>
+        <v>122965600</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B239" t="n">
-        <v>232.8494477166676</v>
+        <v>225.0281992525124</v>
       </c>
       <c r="C239" t="n">
-        <v>233.4487831783142</v>
+        <v>225.9271872095504</v>
       </c>
       <c r="D239" t="n">
-        <v>224.5986856128386</v>
+        <v>223.2102414251123</v>
       </c>
       <c r="E239" t="n">
-        <v>225.4776916503906</v>
+        <v>223.4199981689453</v>
       </c>
       <c r="F239" t="n">
-        <v>122965600</v>
+        <v>82955500</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,25 +6657,25 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B240" t="n">
-        <v>225.0281992525124</v>
+        <v>220.5299987792969</v>
       </c>
       <c r="C240" t="n">
-        <v>225.9271872095504</v>
+        <v>220.9900054931641</v>
       </c>
       <c r="D240" t="n">
-        <v>223.2102414251123</v>
+        <v>217.1999969482422</v>
       </c>
       <c r="E240" t="n">
-        <v>223.4199981689453</v>
+        <v>218.3600006103516</v>
       </c>
       <c r="F240" t="n">
-        <v>82955500</v>
+        <v>105768000</v>
       </c>
       <c r="G240" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -6683,25 +6683,25 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B241" t="n">
-        <v>220.5299987792969</v>
+        <v>221.2400054931641</v>
       </c>
       <c r="C241" t="n">
-        <v>220.9900054931641</v>
+        <v>222</v>
       </c>
       <c r="D241" t="n">
-        <v>217.1999969482422</v>
+        <v>218.1499938964844</v>
       </c>
       <c r="E241" t="n">
-        <v>218.3600006103516</v>
+        <v>218.2899932861328</v>
       </c>
       <c r="F241" t="n">
-        <v>105768000</v>
+        <v>89060100</v>
       </c>
       <c r="G241" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B242" t="n">
-        <v>221.2400054931641</v>
+        <v>211.2400054931641</v>
       </c>
       <c r="C242" t="n">
-        <v>222</v>
+        <v>212.7700042724609</v>
       </c>
       <c r="D242" t="n">
-        <v>218.1499938964844</v>
+        <v>208.9299926757812</v>
       </c>
       <c r="E242" t="n">
-        <v>218.2899932861328</v>
+        <v>210.9600067138672</v>
       </c>
       <c r="F242" t="n">
-        <v>89060100</v>
+        <v>132267200</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B243" t="n">
-        <v>211.2400054931641</v>
+        <v>213.3800048828125</v>
       </c>
       <c r="C243" t="n">
-        <v>212.7700042724609</v>
+        <v>213.9400024414062</v>
       </c>
       <c r="D243" t="n">
-        <v>208.9299926757812</v>
+        <v>211.1600036621094</v>
       </c>
       <c r="E243" t="n">
-        <v>210.9600067138672</v>
+        <v>212.1699981689453</v>
       </c>
       <c r="F243" t="n">
-        <v>132267200</v>
+        <v>88059700</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B244" t="n">
-        <v>213.3800048828125</v>
+        <v>214.1399993896484</v>
       </c>
       <c r="C244" t="n">
-        <v>213.9400024414062</v>
+        <v>216.7599945068359</v>
       </c>
       <c r="D244" t="n">
-        <v>211.1600036621094</v>
+        <v>212.5</v>
       </c>
       <c r="E244" t="n">
-        <v>212.1699981689453</v>
+        <v>213.8999938964844</v>
       </c>
       <c r="F244" t="n">
-        <v>88059700</v>
+        <v>96563600</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B245" t="n">
-        <v>214.1399993896484</v>
+        <v>218.3800048828125</v>
       </c>
       <c r="C245" t="n">
-        <v>216.7599945068359</v>
+        <v>219.9100036621094</v>
       </c>
       <c r="D245" t="n">
-        <v>212.5</v>
+        <v>217.1499938964844</v>
       </c>
       <c r="E245" t="n">
-        <v>213.8999938964844</v>
+        <v>219.3399963378906</v>
       </c>
       <c r="F245" t="n">
-        <v>96563600</v>
+        <v>94191300</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B246" t="n">
-        <v>218.3800048828125</v>
+        <v>219.3500061035156</v>
       </c>
       <c r="C246" t="n">
-        <v>219.9100036621094</v>
+        <v>222.7299957275391</v>
       </c>
       <c r="D246" t="n">
-        <v>217.1499938964844</v>
+        <v>218.0299987792969</v>
       </c>
       <c r="E246" t="n">
-        <v>219.3399963378906</v>
+        <v>222.2700042724609</v>
       </c>
       <c r="F246" t="n">
-        <v>94191300</v>
+        <v>190287400</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B247" t="n">
-        <v>219.3500061035156</v>
+        <v>222.9400024414062</v>
       </c>
       <c r="C247" t="n">
-        <v>222.7299957275391</v>
+        <v>228.5</v>
       </c>
       <c r="D247" t="n">
-        <v>218.0299987792969</v>
+        <v>221.5599975585938</v>
       </c>
       <c r="E247" t="n">
-        <v>222.2700042724609</v>
+        <v>227.3800048828125</v>
       </c>
       <c r="F247" t="n">
-        <v>190287400</v>
+        <v>109806100</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B248" t="n">
-        <v>222.9400024414062</v>
+        <v>226.8500061035156</v>
       </c>
       <c r="C248" t="n">
-        <v>228.5</v>
+        <v>229.9799957275391</v>
       </c>
       <c r="D248" t="n">
-        <v>221.5599975585938</v>
+        <v>226.5</v>
       </c>
       <c r="E248" t="n">
-        <v>227.3800048828125</v>
+        <v>228.8699951171875</v>
       </c>
       <c r="F248" t="n">
-        <v>109806100</v>
+        <v>95746700</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B249" t="n">
-        <v>226.8500061035156</v>
+        <v>228.0299987792969</v>
       </c>
       <c r="C249" t="n">
-        <v>229.9799957275391</v>
+        <v>228.9499969482422</v>
       </c>
       <c r="D249" t="n">
-        <v>226.5</v>
+        <v>224.0200042724609</v>
       </c>
       <c r="E249" t="n">
-        <v>228.8699951171875</v>
+        <v>225.5099945068359</v>
       </c>
       <c r="F249" t="n">
-        <v>95746700</v>
+        <v>89547300</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B250" t="n">
-        <v>228.0299987792969</v>
+        <v>222.0800018310547</v>
       </c>
       <c r="C250" t="n">
-        <v>228.9499969482422</v>
+        <v>224.9400024414062</v>
       </c>
       <c r="D250" t="n">
-        <v>224.0200042724609</v>
+        <v>221.0899963378906</v>
       </c>
       <c r="E250" t="n">
-        <v>225.5099945068359</v>
+        <v>224.5800018310547</v>
       </c>
       <c r="F250" t="n">
-        <v>89547300</v>
+        <v>77469900</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B251" t="n">
-        <v>222.0800018310547</v>
+        <v>225.1300048828125</v>
       </c>
       <c r="C251" t="n">
-        <v>224.9400024414062</v>
+        <v>226.9400024414062</v>
       </c>
       <c r="D251" t="n">
-        <v>221.0899963378906</v>
+        <v>223.1300048828125</v>
       </c>
       <c r="E251" t="n">
-        <v>224.5800018310547</v>
+        <v>225.0700073242188</v>
       </c>
       <c r="F251" t="n">
-        <v>77469900</v>
+        <v>89947700</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B252" t="n">
-        <v>225.1300048828125</v>
+        <v>229.75</v>
       </c>
       <c r="C252" t="n">
-        <v>226.9400024414062</v>
+        <v>233.2100067138672</v>
       </c>
       <c r="D252" t="n">
-        <v>223.1300048828125</v>
+        <v>228.0399932861328</v>
       </c>
       <c r="E252" t="n">
-        <v>225.0700073242188</v>
+        <v>228.8600006103516</v>
       </c>
       <c r="F252" t="n">
-        <v>89808400</v>
+        <v>141544300</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10884,37 +10884,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>228.86</v>
+      </c>
+      <c r="D2" t="n">
         <v>225.07</v>
       </c>
-      <c r="D2" t="n">
-        <v>224.58</v>
-      </c>
       <c r="E2" t="n">
-        <v>225.15</v>
+        <v>229.7</v>
       </c>
       <c r="F2" t="n">
-        <v>226.94</v>
+        <v>233.21</v>
       </c>
       <c r="G2" t="n">
-        <v>223.1329</v>
+        <v>228.04</v>
       </c>
       <c r="H2" t="n">
-        <v>87931936</v>
+        <v>141276939</v>
       </c>
       <c r="I2" t="n">
-        <v>125195556</v>
+        <v>124520330</v>
       </c>
       <c r="J2" t="n">
-        <v>5434765213696</v>
+        <v>5526282305536</v>
       </c>
       <c r="K2" t="n">
-        <v>28.453857</v>
+        <v>28.500624</v>
       </c>
       <c r="L2" t="n">
-        <v>14.351548</v>
+        <v>14.593216</v>
       </c>
       <c r="M2" t="n">
-        <v>7.91</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="N2" t="n">
         <v>236.54</v>
@@ -10926,7 +10926,7 @@
         <v>2.217</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="R2" t="n">
         <v>0.63663</v>
@@ -10950,7 +10950,7 @@
         <v>9.483000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>23.73405</v>
+        <v>24.133713</v>
       </c>
       <c r="Z2" t="n">
         <v>1.278</v>
@@ -10962,7 +10962,7 @@
         <v>302970011648</v>
       </c>
       <c r="AC2" t="n">
-        <v>5400577966080</v>
+        <v>5491916800000</v>
       </c>
       <c r="AD2" t="n">
         <v>201266003968</v>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:40</t>
+          <t>2026-09-29 13:24:35</t>
         </is>
       </c>
     </row>

--- a/data/NVDA_data.xlsx
+++ b/data/NVDA_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B2" t="n">
-        <v>179.9987400973632</v>
+        <v>181.6448190078555</v>
       </c>
       <c r="C2" t="n">
-        <v>183.5602146114836</v>
+        <v>186.9022276338177</v>
       </c>
       <c r="D2" t="n">
-        <v>179.8890176259668</v>
+        <v>181.0462469572146</v>
       </c>
       <c r="E2" t="n">
-        <v>181.4153594970703</v>
+        <v>186.1340637207031</v>
       </c>
       <c r="F2" t="n">
-        <v>193063500</v>
+        <v>236981000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B3" t="n">
-        <v>181.6448190078555</v>
+        <v>184.7972606974542</v>
       </c>
       <c r="C3" t="n">
-        <v>186.9022276338177</v>
+        <v>187.6903232769056</v>
       </c>
       <c r="D3" t="n">
-        <v>181.0462469572146</v>
+        <v>183.4604518817237</v>
       </c>
       <c r="E3" t="n">
-        <v>186.1340637207031</v>
+        <v>186.79248046875</v>
       </c>
       <c r="F3" t="n">
-        <v>236981000</v>
+        <v>173844900</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B4" t="n">
-        <v>184.7972757932568</v>
+        <v>189.1468626563914</v>
       </c>
       <c r="C4" t="n">
-        <v>187.690338609038</v>
+        <v>190.593394116267</v>
       </c>
       <c r="D4" t="n">
-        <v>183.4604668683245</v>
+        <v>187.6105347272827</v>
       </c>
       <c r="E4" t="n">
-        <v>186.7924957275391</v>
+        <v>188.4385528564453</v>
       </c>
       <c r="F4" t="n">
-        <v>173844900</v>
+        <v>136805800</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B5" t="n">
-        <v>189.146847340247</v>
+        <v>188.7378247179256</v>
       </c>
       <c r="C5" t="n">
-        <v>190.59337868299</v>
+        <v>189.9050265070322</v>
       </c>
       <c r="D5" t="n">
-        <v>187.6105195355423</v>
+        <v>184.9369333277354</v>
       </c>
       <c r="E5" t="n">
-        <v>188.4385375976562</v>
+        <v>187.1715698242188</v>
       </c>
       <c r="F5" t="n">
-        <v>136805800</v>
+        <v>137596900</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B6" t="n">
-        <v>188.7378247179256</v>
+        <v>185.0566446584491</v>
       </c>
       <c r="C6" t="n">
-        <v>189.9050265070322</v>
+        <v>186.7825055997528</v>
       </c>
       <c r="D6" t="n">
-        <v>184.9369333277354</v>
+        <v>182.8918329061041</v>
       </c>
       <c r="E6" t="n">
-        <v>187.1715698242188</v>
+        <v>185.0965423583984</v>
       </c>
       <c r="F6" t="n">
-        <v>137596900</v>
+        <v>157678100</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B7" t="n">
-        <v>185.0566446584491</v>
+        <v>185.7848907820332</v>
       </c>
       <c r="C7" t="n">
-        <v>186.7825055997528</v>
+        <v>188.6081286768816</v>
       </c>
       <c r="D7" t="n">
-        <v>182.8918329061041</v>
+        <v>183.5602249269612</v>
       </c>
       <c r="E7" t="n">
-        <v>185.0965423583984</v>
+        <v>184.5977325439453</v>
       </c>
       <c r="F7" t="n">
-        <v>157678100</v>
+        <v>140088000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B8" t="n">
-        <v>185.784875425114</v>
+        <v>186.1240974206304</v>
       </c>
       <c r="C8" t="n">
-        <v>188.6081130865945</v>
+        <v>189.1468543796426</v>
       </c>
       <c r="D8" t="n">
-        <v>183.5602097539322</v>
+        <v>186.0941551173159</v>
       </c>
       <c r="E8" t="n">
-        <v>184.5977172851562</v>
+        <v>188.6580200195312</v>
       </c>
       <c r="F8" t="n">
-        <v>140088000</v>
+        <v>130168900</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B9" t="n">
-        <v>186.1240974206304</v>
+        <v>191.7705422839889</v>
       </c>
       <c r="C9" t="n">
-        <v>189.1468543796426</v>
+        <v>194.8332119113436</v>
       </c>
       <c r="D9" t="n">
-        <v>186.0941551173159</v>
+        <v>190.6033405552435</v>
       </c>
       <c r="E9" t="n">
-        <v>188.6580200195312</v>
+        <v>192.1097412109375</v>
       </c>
       <c r="F9" t="n">
-        <v>130168900</v>
+        <v>182997200</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B10" t="n">
-        <v>191.7705422839889</v>
+        <v>193.0474982342752</v>
       </c>
       <c r="C10" t="n">
-        <v>194.8332119113436</v>
+        <v>195.1524558626357</v>
       </c>
       <c r="D10" t="n">
-        <v>190.6033405552435</v>
+        <v>181.6148965961679</v>
       </c>
       <c r="E10" t="n">
-        <v>192.1097412109375</v>
+        <v>182.7222442626953</v>
       </c>
       <c r="F10" t="n">
-        <v>182997200</v>
+        <v>268774400</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B11" t="n">
-        <v>193.0474982342752</v>
+        <v>187.52074924116</v>
       </c>
       <c r="C11" t="n">
-        <v>195.1524558626357</v>
+        <v>189.6556339904095</v>
       </c>
       <c r="D11" t="n">
-        <v>181.6148965961679</v>
+        <v>185.5155586605101</v>
       </c>
       <c r="E11" t="n">
-        <v>182.7222442626953</v>
+        <v>187.8699188232422</v>
       </c>
       <c r="F11" t="n">
-        <v>268774400</v>
+        <v>153482800</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B12" t="n">
-        <v>187.52074924116</v>
+        <v>184.3283927796865</v>
       </c>
       <c r="C12" t="n">
-        <v>189.6556339904095</v>
+        <v>184.3583198600852</v>
       </c>
       <c r="D12" t="n">
-        <v>185.5155586605101</v>
+        <v>179.2705030798172</v>
       </c>
       <c r="E12" t="n">
-        <v>187.8699188232422</v>
+        <v>179.5997161865234</v>
       </c>
       <c r="F12" t="n">
-        <v>153482800</v>
+        <v>205641400</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B13" t="n">
-        <v>184.3283927796865</v>
+        <v>184.358330420537</v>
       </c>
       <c r="C13" t="n">
-        <v>184.3583198600852</v>
+        <v>184.428155204694</v>
       </c>
       <c r="D13" t="n">
-        <v>179.2705030798172</v>
+        <v>176.8662696036074</v>
       </c>
       <c r="E13" t="n">
-        <v>179.5997161865234</v>
+        <v>179.4002075195312</v>
       </c>
       <c r="F13" t="n">
-        <v>205641400</v>
+        <v>214450500</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B14" t="n">
-        <v>184.3582990595379</v>
+        <v>181.7944521048813</v>
       </c>
       <c r="C14" t="n">
-        <v>184.4281238318171</v>
+        <v>182.8419455690647</v>
       </c>
       <c r="D14" t="n">
-        <v>176.8662395170747</v>
+        <v>179.3403402174659</v>
       </c>
       <c r="E14" t="n">
-        <v>179.4001770019531</v>
+        <v>181.3754577636719</v>
       </c>
       <c r="F14" t="n">
-        <v>214450500</v>
+        <v>179723300</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B15" t="n">
-        <v>181.7944368108431</v>
+        <v>179.7493615830456</v>
       </c>
       <c r="C15" t="n">
-        <v>182.8419301869027</v>
+        <v>183.6600061588844</v>
       </c>
       <c r="D15" t="n">
-        <v>179.3403251298876</v>
+        <v>179.3203965919317</v>
       </c>
       <c r="E15" t="n">
-        <v>181.3754425048828</v>
+        <v>182.7821044921875</v>
       </c>
       <c r="F15" t="n">
-        <v>179723300</v>
+        <v>173135200</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B16" t="n">
-        <v>179.7493465774322</v>
+        <v>182.6923102950553</v>
       </c>
       <c r="C16" t="n">
-        <v>183.6599908268075</v>
+        <v>184.7573549226016</v>
       </c>
       <c r="D16" t="n">
-        <v>179.3203816221287</v>
+        <v>181.2956472677441</v>
       </c>
       <c r="E16" t="n">
-        <v>182.7820892333984</v>
+        <v>182.2034759521484</v>
       </c>
       <c r="F16" t="n">
-        <v>173135200</v>
+        <v>128544700</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B17" t="n">
-        <v>182.6923102950553</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="C17" t="n">
-        <v>184.7573549226016</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="D17" t="n">
-        <v>181.2956472677441</v>
+        <v>179.3702701372806</v>
       </c>
       <c r="E17" t="n">
-        <v>182.2034759521484</v>
+        <v>180.7270202636719</v>
       </c>
       <c r="F17" t="n">
-        <v>128544700</v>
+        <v>124240200</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B18" t="n">
-        <v>182.3531141136141</v>
+        <v>180.7070662621498</v>
       </c>
       <c r="C18" t="n">
-        <v>182.3531141136141</v>
+        <v>183.0015721983185</v>
       </c>
       <c r="D18" t="n">
-        <v>179.3702701372806</v>
+        <v>176.3375297972393</v>
       </c>
       <c r="E18" t="n">
-        <v>180.7270202636719</v>
+        <v>179.84912109375</v>
       </c>
       <c r="F18" t="n">
-        <v>124240200</v>
+        <v>162249600</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B19" t="n">
-        <v>180.7070509305708</v>
+        <v>179.988762799469</v>
       </c>
       <c r="C19" t="n">
-        <v>183.0015566720687</v>
+        <v>182.5925250516066</v>
       </c>
       <c r="D19" t="n">
-        <v>176.3375148363812</v>
+        <v>179.3602637385785</v>
       </c>
       <c r="E19" t="n">
-        <v>179.8491058349609</v>
+        <v>181.724609375</v>
       </c>
       <c r="F19" t="n">
-        <v>162249600</v>
+        <v>111363700</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B20" t="n">
-        <v>179.988793025541</v>
+        <v>183.4006051417061</v>
       </c>
       <c r="C20" t="n">
-        <v>182.5925557149365</v>
+        <v>187.0219340442129</v>
       </c>
       <c r="D20" t="n">
-        <v>179.3602938591047</v>
+        <v>183.0614214202242</v>
       </c>
       <c r="E20" t="n">
-        <v>181.7246398925781</v>
+        <v>185.8148193359375</v>
       </c>
       <c r="F20" t="n">
-        <v>111363700</v>
+        <v>131296700</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B21" t="n">
-        <v>183.400590081168</v>
+        <v>189.5359033209746</v>
       </c>
       <c r="C21" t="n">
-        <v>187.0219186862977</v>
+        <v>191.541093665248</v>
       </c>
       <c r="D21" t="n">
-        <v>183.0614063875393</v>
+        <v>187.979619148197</v>
       </c>
       <c r="E21" t="n">
-        <v>185.8148040771484</v>
+        <v>191.0323181152344</v>
       </c>
       <c r="F21" t="n">
-        <v>131296700</v>
+        <v>153452700</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B22" t="n">
-        <v>189.5359184602369</v>
+        <v>192.5886067715161</v>
       </c>
       <c r="C22" t="n">
-        <v>191.5411089646758</v>
+        <v>202.6644582837766</v>
       </c>
       <c r="D22" t="n">
-        <v>187.9796341631504</v>
+        <v>191.4513320204045</v>
       </c>
       <c r="E22" t="n">
-        <v>191.0323333740234</v>
+        <v>200.5495300292969</v>
       </c>
       <c r="F22" t="n">
-        <v>153452700</v>
+        <v>297986200</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B23" t="n">
-        <v>192.5886067715161</v>
+        <v>207.482906515472</v>
       </c>
       <c r="C23" t="n">
-        <v>202.6644582837766</v>
+        <v>211.6828509687219</v>
       </c>
       <c r="D23" t="n">
-        <v>191.4513320204045</v>
+        <v>204.2905578218423</v>
       </c>
       <c r="E23" t="n">
-        <v>200.5495300292969</v>
+        <v>206.5451507568359</v>
       </c>
       <c r="F23" t="n">
-        <v>297986200</v>
+        <v>308829600</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B24" t="n">
-        <v>207.482891187405</v>
+        <v>204.6596680014167</v>
       </c>
       <c r="C24" t="n">
-        <v>211.6828353303786</v>
+        <v>205.6672637579894</v>
       </c>
       <c r="D24" t="n">
-        <v>204.2905427296142</v>
+        <v>200.9286166610889</v>
       </c>
       <c r="E24" t="n">
-        <v>206.5451354980469</v>
+        <v>202.4050750732422</v>
       </c>
       <c r="F24" t="n">
-        <v>308829600</v>
+        <v>178864400</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B25" t="n">
-        <v>204.6596525726598</v>
+        <v>205.9565537660584</v>
       </c>
       <c r="C25" t="n">
-        <v>205.6672482532724</v>
+        <v>207.4729250244422</v>
       </c>
       <c r="D25" t="n">
-        <v>200.9286015136062</v>
+        <v>201.5870329046891</v>
       </c>
       <c r="E25" t="n">
-        <v>202.4050598144531</v>
+        <v>202.0060272216797</v>
       </c>
       <c r="F25" t="n">
-        <v>178864400</v>
+        <v>179802200</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B26" t="n">
-        <v>205.9565848804529</v>
+        <v>207.5826880225491</v>
       </c>
       <c r="C26" t="n">
-        <v>207.4729563679188</v>
+        <v>210.8348911017148</v>
       </c>
       <c r="D26" t="n">
-        <v>201.5870633589687</v>
+        <v>205.0687065918373</v>
       </c>
       <c r="E26" t="n">
-        <v>202.0060577392578</v>
+        <v>206.3855590820312</v>
       </c>
       <c r="F26" t="n">
-        <v>179802200</v>
+        <v>180267300</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B27" t="n">
-        <v>207.5826726752522</v>
+        <v>202.5148147488263</v>
       </c>
       <c r="C27" t="n">
-        <v>210.8348755139714</v>
+        <v>203.4824975937368</v>
       </c>
       <c r="D27" t="n">
-        <v>205.0686914304077</v>
+        <v>197.4569251230167</v>
       </c>
       <c r="E27" t="n">
-        <v>206.3855438232422</v>
+        <v>198.2151184082031</v>
       </c>
       <c r="F27" t="n">
-        <v>180267300</v>
+        <v>188919300</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B28" t="n">
-        <v>202.5148147488263</v>
+        <v>198.2949275919373</v>
       </c>
       <c r="C28" t="n">
-        <v>203.4824975937368</v>
+        <v>202.4350026612236</v>
       </c>
       <c r="D28" t="n">
-        <v>197.4569251230167</v>
+        <v>194.1847643800754</v>
       </c>
       <c r="E28" t="n">
-        <v>198.2151184082031</v>
+        <v>194.7434387207031</v>
       </c>
       <c r="F28" t="n">
-        <v>188919300</v>
+        <v>171350300</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B29" t="n">
-        <v>198.2949120548774</v>
+        <v>195.9505410878136</v>
       </c>
       <c r="C29" t="n">
-        <v>202.4349867997753</v>
+        <v>197.1476699621838</v>
       </c>
       <c r="D29" t="n">
-        <v>194.1847491650603</v>
+        <v>185.9345440647224</v>
       </c>
       <c r="E29" t="n">
-        <v>194.7434234619141</v>
+        <v>187.6304779052734</v>
       </c>
       <c r="F29" t="n">
-        <v>171350300</v>
+        <v>223029800</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B30" t="n">
-        <v>195.9505410878136</v>
+        <v>184.4580548583195</v>
       </c>
       <c r="C30" t="n">
-        <v>197.1476699621838</v>
+        <v>187.8698939350823</v>
       </c>
       <c r="D30" t="n">
-        <v>185.9345440647224</v>
+        <v>178.4823816093971</v>
       </c>
       <c r="E30" t="n">
-        <v>187.6304779052734</v>
+        <v>187.7002868652344</v>
       </c>
       <c r="F30" t="n">
-        <v>223029800</v>
+        <v>264942300</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B31" t="n">
-        <v>184.4580548583195</v>
+        <v>194.6436788693004</v>
       </c>
       <c r="C31" t="n">
-        <v>187.8698939350823</v>
+        <v>199.4621367771523</v>
       </c>
       <c r="D31" t="n">
-        <v>178.4823816093971</v>
+        <v>193.3268264223904</v>
       </c>
       <c r="E31" t="n">
-        <v>187.7002868652344</v>
+        <v>198.5742645263672</v>
       </c>
       <c r="F31" t="n">
-        <v>264942300</v>
+        <v>198897100</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B32" t="n">
-        <v>194.6436788693004</v>
+        <v>194.6935381421213</v>
       </c>
       <c r="C32" t="n">
-        <v>199.4621367771523</v>
+        <v>194.9529112179747</v>
       </c>
       <c r="D32" t="n">
-        <v>193.3268264223904</v>
+        <v>190.8427635881239</v>
       </c>
       <c r="E32" t="n">
-        <v>198.5742645263672</v>
+        <v>192.6983184814453</v>
       </c>
       <c r="F32" t="n">
-        <v>198897100</v>
+        <v>176483300</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B33" t="n">
-        <v>194.6935689756818</v>
+        <v>195.2522010776849</v>
       </c>
       <c r="C33" t="n">
-        <v>194.9529420926121</v>
+        <v>195.4217929255223</v>
       </c>
       <c r="D33" t="n">
-        <v>190.8427938118383</v>
+        <v>190.6731755191215</v>
       </c>
       <c r="E33" t="n">
-        <v>192.6983489990234</v>
+        <v>193.3367919921875</v>
       </c>
       <c r="F33" t="n">
-        <v>176483300</v>
+        <v>154935300</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B34" t="n">
-        <v>195.2522164876445</v>
+        <v>190.5933791327836</v>
       </c>
       <c r="C34" t="n">
-        <v>195.4218083488666</v>
+        <v>190.9824463944715</v>
       </c>
       <c r="D34" t="n">
-        <v>190.673190567689</v>
+        <v>183.4105907203728</v>
       </c>
       <c r="E34" t="n">
-        <v>193.3368072509766</v>
+        <v>186.4133911132812</v>
       </c>
       <c r="F34" t="n">
-        <v>154935300</v>
+        <v>207423100</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B35" t="n">
-        <v>190.5933947337238</v>
+        <v>182.4229435613052</v>
       </c>
       <c r="C35" t="n">
-        <v>190.9824620272586</v>
+        <v>190.553458007553</v>
       </c>
       <c r="D35" t="n">
-        <v>183.4106057333689</v>
+        <v>180.1483942490048</v>
       </c>
       <c r="E35" t="n">
-        <v>186.4134063720703</v>
+        <v>189.7154693603516</v>
       </c>
       <c r="F35" t="n">
-        <v>207423100</v>
+        <v>186591900</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B36" t="n">
-        <v>182.4229435613052</v>
+        <v>185.5255230789849</v>
       </c>
       <c r="C36" t="n">
-        <v>190.553458007553</v>
+        <v>188.5482800008962</v>
       </c>
       <c r="D36" t="n">
-        <v>180.1483942490048</v>
+        <v>183.8794727552066</v>
       </c>
       <c r="E36" t="n">
-        <v>189.7154693603516</v>
+        <v>186.1540222167969</v>
       </c>
       <c r="F36" t="n">
-        <v>186591900</v>
+        <v>173628900</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B37" t="n">
-        <v>185.5255230789849</v>
+        <v>182.9417205846578</v>
       </c>
       <c r="C37" t="n">
-        <v>188.5482800008962</v>
+        <v>184.3583249108488</v>
       </c>
       <c r="D37" t="n">
-        <v>183.8794727552066</v>
+        <v>179.2206244483882</v>
       </c>
       <c r="E37" t="n">
-        <v>186.1540222167969</v>
+        <v>180.9265441894531</v>
       </c>
       <c r="F37" t="n">
-        <v>173628900</v>
+        <v>213598900</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B38" t="n">
-        <v>182.941705155915</v>
+        <v>184.3483273978252</v>
       </c>
       <c r="C38" t="n">
-        <v>184.3583093626339</v>
+        <v>187.4109971087465</v>
       </c>
       <c r="D38" t="n">
-        <v>179.2206093334711</v>
+        <v>182.3930205111681</v>
       </c>
       <c r="E38" t="n">
-        <v>180.9265289306641</v>
+        <v>186.0742034912109</v>
       </c>
       <c r="F38" t="n">
-        <v>213598900</v>
+        <v>247246400</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B39" t="n">
-        <v>184.3483273978252</v>
+        <v>195.4816571057099</v>
       </c>
       <c r="C39" t="n">
-        <v>187.4109971087465</v>
+        <v>195.5315406452363</v>
       </c>
       <c r="D39" t="n">
-        <v>182.3930205111681</v>
+        <v>179.4201468289569</v>
       </c>
       <c r="E39" t="n">
-        <v>186.0742034912109</v>
+        <v>180.208251953125</v>
       </c>
       <c r="F39" t="n">
-        <v>247246400</v>
+        <v>343504800</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B40" t="n">
-        <v>195.4816571057099</v>
+        <v>180.8068289121023</v>
       </c>
       <c r="C40" t="n">
-        <v>195.5315406452363</v>
+        <v>184.1188859589464</v>
       </c>
       <c r="D40" t="n">
-        <v>179.4201468289569</v>
+        <v>172.5166776199441</v>
       </c>
       <c r="E40" t="n">
-        <v>180.208251953125</v>
+        <v>178.4524688720703</v>
       </c>
       <c r="F40" t="n">
-        <v>343504800</v>
+        <v>346926200</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B41" t="n">
-        <v>180.8068289121023</v>
+        <v>179.0610243324759</v>
       </c>
       <c r="C41" t="n">
-        <v>184.1188859589464</v>
+        <v>183.0614349513779</v>
       </c>
       <c r="D41" t="n">
-        <v>172.5166776199441</v>
+        <v>176.0582084909882</v>
       </c>
       <c r="E41" t="n">
-        <v>178.4524688720703</v>
+        <v>182.1137084960938</v>
       </c>
       <c r="F41" t="n">
-        <v>346926200</v>
+        <v>256618300</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B42" t="n">
-        <v>179.0610093294625</v>
+        <v>174.4919707447618</v>
       </c>
       <c r="C42" t="n">
-        <v>183.0614196131816</v>
+        <v>177.734203281764</v>
       </c>
       <c r="D42" t="n">
-        <v>176.0581937395723</v>
+        <v>169.1447804748437</v>
       </c>
       <c r="E42" t="n">
-        <v>182.1136932373047</v>
+        <v>177.39501953125</v>
       </c>
       <c r="F42" t="n">
-        <v>256618300</v>
+        <v>320600300</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B43" t="n">
-        <v>174.491955735681</v>
+        <v>181.1958831941039</v>
       </c>
       <c r="C43" t="n">
-        <v>177.7341879937998</v>
+        <v>182.4728225932506</v>
       </c>
       <c r="D43" t="n">
-        <v>169.1447659257062</v>
+        <v>177.8139863878403</v>
       </c>
       <c r="E43" t="n">
-        <v>177.3950042724609</v>
+        <v>179.8291473388672</v>
       </c>
       <c r="F43" t="n">
-        <v>320600300</v>
+        <v>183852000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B44" t="n">
-        <v>181.1958985688627</v>
+        <v>178.5821558989869</v>
       </c>
       <c r="C44" t="n">
-        <v>182.4728380763597</v>
+        <v>178.8614854738169</v>
       </c>
       <c r="D44" t="n">
-        <v>177.8140014756398</v>
+        <v>176.0781603452176</v>
       </c>
       <c r="E44" t="n">
-        <v>179.8291625976562</v>
+        <v>176.5769653320312</v>
       </c>
       <c r="F44" t="n">
-        <v>183852000</v>
+        <v>121332800</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B45" t="n">
-        <v>178.5821558989869</v>
+        <v>174.3422893139723</v>
       </c>
       <c r="C45" t="n">
-        <v>178.8614854738169</v>
+        <v>179.8690563253026</v>
       </c>
       <c r="D45" t="n">
-        <v>176.0781603452176</v>
+        <v>173.2648688653124</v>
       </c>
       <c r="E45" t="n">
-        <v>176.5769653320312</v>
+        <v>179.4899597167969</v>
       </c>
       <c r="F45" t="n">
-        <v>121332800</v>
+        <v>188131000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B46" t="n">
-        <v>174.3423041351479</v>
+        <v>181.3255769560617</v>
       </c>
       <c r="C46" t="n">
-        <v>179.8690716163194</v>
+        <v>185.2162648499111</v>
       </c>
       <c r="D46" t="n">
-        <v>173.2648835948944</v>
+        <v>179.569788944198</v>
       </c>
       <c r="E46" t="n">
-        <v>179.4899749755859</v>
+        <v>181.0263061523438</v>
       </c>
       <c r="F46" t="n">
-        <v>188131000</v>
+        <v>182632200</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B47" t="n">
-        <v>181.3255769560617</v>
+        <v>180.6472262869623</v>
       </c>
       <c r="C47" t="n">
-        <v>185.2162648499111</v>
+        <v>182.0139471586436</v>
       </c>
       <c r="D47" t="n">
-        <v>179.569788944198</v>
+        <v>178.6819333075974</v>
       </c>
       <c r="E47" t="n">
-        <v>181.0263061523438</v>
+        <v>179.1607818603516</v>
       </c>
       <c r="F47" t="n">
-        <v>182632200</v>
+        <v>165138000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,25 +1665,25 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B48" t="n">
-        <v>180.6472109015755</v>
+        <v>181.1959881613664</v>
       </c>
       <c r="C48" t="n">
-        <v>182.0139316568558</v>
+        <v>184.089227004522</v>
       </c>
       <c r="D48" t="n">
-        <v>178.681918089591</v>
+        <v>179.5398751387779</v>
       </c>
       <c r="E48" t="n">
-        <v>179.1607666015625</v>
+        <v>182.9518890380859</v>
       </c>
       <c r="F48" t="n">
-        <v>165138000</v>
+        <v>167364900</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1691,25 +1691,25 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B49" t="n">
-        <v>181.1959881613664</v>
+        <v>183.4606866221248</v>
       </c>
       <c r="C49" t="n">
-        <v>184.089227004522</v>
+        <v>184.2288932293168</v>
       </c>
       <c r="D49" t="n">
-        <v>179.5398751387779</v>
+        <v>180.4876480440623</v>
       </c>
       <c r="E49" t="n">
-        <v>182.9518890380859</v>
+        <v>181.9841461181641</v>
       </c>
       <c r="F49" t="n">
-        <v>167364900</v>
+        <v>143971100</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B50" t="n">
-        <v>183.4607020047171</v>
+        <v>182.2136112701494</v>
       </c>
       <c r="C50" t="n">
-        <v>184.2289086763207</v>
+        <v>187.5610985176648</v>
       </c>
       <c r="D50" t="n">
-        <v>180.4876631773748</v>
+        <v>181.9741660895743</v>
       </c>
       <c r="E50" t="n">
-        <v>181.9841613769531</v>
+        <v>185.1168212890625</v>
       </c>
       <c r="F50" t="n">
-        <v>143971100</v>
+        <v>204378100</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B51" t="n">
-        <v>182.2136112701494</v>
+        <v>185.12679644575</v>
       </c>
       <c r="C51" t="n">
-        <v>187.5610985176648</v>
+        <v>185.2864265695677</v>
       </c>
       <c r="D51" t="n">
-        <v>181.9741660895743</v>
+        <v>182.8920356049676</v>
       </c>
       <c r="E51" t="n">
-        <v>185.1168212890625</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="F51" t="n">
-        <v>204378100</v>
+        <v>144719700</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B52" t="n">
-        <v>185.1268117532098</v>
+        <v>184.5381918075859</v>
       </c>
       <c r="C52" t="n">
-        <v>185.2864418902268</v>
+        <v>185.0469957406681</v>
       </c>
       <c r="D52" t="n">
-        <v>182.8920507276432</v>
+        <v>181.6150239281505</v>
       </c>
       <c r="E52" t="n">
-        <v>184.5381927490234</v>
+        <v>183.3509674072266</v>
       </c>
       <c r="F52" t="n">
-        <v>144719700</v>
+        <v>162785400</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B53" t="n">
-        <v>184.538176449994</v>
+        <v>179.8591224369562</v>
       </c>
       <c r="C53" t="n">
-        <v>185.0469803407326</v>
+        <v>180.8967030087509</v>
       </c>
       <c r="D53" t="n">
-        <v>181.6150088138297</v>
+        <v>176.2076633109278</v>
       </c>
       <c r="E53" t="n">
-        <v>183.3509521484375</v>
+        <v>180.5075988769531</v>
       </c>
       <c r="F53" t="n">
-        <v>162785400</v>
+        <v>182136600</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B54" t="n">
-        <v>179.8591224369562</v>
+        <v>180.6871989054384</v>
       </c>
       <c r="C54" t="n">
-        <v>180.8967030087509</v>
+        <v>182.3932136047752</v>
       </c>
       <c r="D54" t="n">
-        <v>176.2076633109278</v>
+        <v>174.2123443447362</v>
       </c>
       <c r="E54" t="n">
-        <v>180.5075988769531</v>
+        <v>174.6114196777344</v>
       </c>
       <c r="F54" t="n">
-        <v>182136600</v>
+        <v>204274900</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B55" t="n">
-        <v>180.6871989054384</v>
+        <v>177.5245903328353</v>
       </c>
       <c r="C55" t="n">
-        <v>182.3932136047752</v>
+        <v>178.0034654802094</v>
       </c>
       <c r="D55" t="n">
-        <v>174.2123443447362</v>
+        <v>174.6213802569945</v>
       </c>
       <c r="E55" t="n">
-        <v>174.6114196777344</v>
+        <v>175.8784332275391</v>
       </c>
       <c r="F55" t="n">
-        <v>204274900</v>
+        <v>164775600</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B56" t="n">
-        <v>177.5245903328353</v>
+        <v>175.8485012773324</v>
       </c>
       <c r="C56" t="n">
-        <v>178.0034654802094</v>
+        <v>178.0733061224419</v>
       </c>
       <c r="D56" t="n">
-        <v>174.6213802569945</v>
+        <v>174.4916756985292</v>
       </c>
       <c r="E56" t="n">
-        <v>175.8784332275391</v>
+        <v>177.3050994873047</v>
       </c>
       <c r="F56" t="n">
-        <v>164775600</v>
+        <v>148588100</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B57" t="n">
-        <v>175.8485012773324</v>
+        <v>175.6888811343</v>
       </c>
       <c r="C57" t="n">
-        <v>178.0733061224419</v>
+        <v>175.7188098781239</v>
       </c>
       <c r="D57" t="n">
-        <v>174.4916756985292</v>
+        <v>169.9123900056319</v>
       </c>
       <c r="E57" t="n">
-        <v>177.3050994873047</v>
+        <v>170.5409240722656</v>
       </c>
       <c r="F57" t="n">
-        <v>148588100</v>
+        <v>222775500</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B58" t="n">
-        <v>175.6888968536916</v>
+        <v>174.1225483861358</v>
       </c>
       <c r="C58" t="n">
-        <v>175.7188256001934</v>
+        <v>175.7387615308714</v>
       </c>
       <c r="D58" t="n">
-        <v>169.9124052081842</v>
+        <v>171.4188835631069</v>
       </c>
       <c r="E58" t="n">
-        <v>170.5409393310547</v>
+        <v>173.7334594726562</v>
       </c>
       <c r="F58" t="n">
-        <v>222775500</v>
+        <v>176096000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B59" t="n">
-        <v>174.1225483861358</v>
+        <v>176.2575672304301</v>
       </c>
       <c r="C59" t="n">
-        <v>175.7387615308714</v>
+        <v>181.0264072425164</v>
       </c>
       <c r="D59" t="n">
-        <v>171.4188835631069</v>
+        <v>175.9283357789888</v>
       </c>
       <c r="E59" t="n">
-        <v>173.7334594726562</v>
+        <v>180.5674896240234</v>
       </c>
       <c r="F59" t="n">
-        <v>176096000</v>
+        <v>324925900</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B60" t="n">
-        <v>176.2575523358494</v>
+        <v>183.4906282252173</v>
       </c>
       <c r="C60" t="n">
-        <v>181.0263919449467</v>
+        <v>183.7300734141942</v>
       </c>
       <c r="D60" t="n">
-        <v>175.9283209122297</v>
+        <v>181.9243013805983</v>
       </c>
       <c r="E60" t="n">
-        <v>180.5674743652344</v>
+        <v>183.2611694335938</v>
       </c>
       <c r="F60" t="n">
-        <v>324925900</v>
+        <v>129064400</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B61" t="n">
-        <v>183.4906282252173</v>
+        <v>182.5428571096804</v>
       </c>
       <c r="C61" t="n">
-        <v>183.7300734141942</v>
+        <v>188.8880102762506</v>
       </c>
       <c r="D61" t="n">
-        <v>181.9243013805983</v>
+        <v>182.4730132178061</v>
       </c>
       <c r="E61" t="n">
-        <v>183.2611694335938</v>
+        <v>188.7682952880859</v>
       </c>
       <c r="F61" t="n">
-        <v>129064400</v>
+        <v>174873600</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B62" t="n">
-        <v>182.5428571096804</v>
+        <v>187.5012437217294</v>
       </c>
       <c r="C62" t="n">
-        <v>188.8880102762506</v>
+        <v>188.4689804086018</v>
       </c>
       <c r="D62" t="n">
-        <v>182.4730132178061</v>
+        <v>186.154389299292</v>
       </c>
       <c r="E62" t="n">
-        <v>188.7682952880859</v>
+        <v>188.169677734375</v>
       </c>
       <c r="F62" t="n">
-        <v>174873600</v>
+        <v>65528500</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B63" t="n">
-        <v>187.5012437217294</v>
+        <v>189.4766285187414</v>
       </c>
       <c r="C63" t="n">
-        <v>188.4689804086018</v>
+        <v>192.240166195598</v>
       </c>
       <c r="D63" t="n">
-        <v>186.154389299292</v>
+        <v>187.5611125998212</v>
       </c>
       <c r="E63" t="n">
-        <v>188.169677734375</v>
+        <v>190.085205078125</v>
       </c>
       <c r="F63" t="n">
-        <v>65528500</v>
+        <v>139740300</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B64" t="n">
-        <v>189.4766285187414</v>
+        <v>187.2717899684254</v>
       </c>
       <c r="C64" t="n">
-        <v>192.240166195598</v>
+        <v>188.3193265216257</v>
       </c>
       <c r="D64" t="n">
-        <v>187.5611125998212</v>
+        <v>185.4759890979627</v>
       </c>
       <c r="E64" t="n">
-        <v>190.085205078125</v>
+        <v>187.7805938720703</v>
       </c>
       <c r="F64" t="n">
-        <v>139740300</v>
+        <v>120006100</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B65" t="n">
-        <v>187.2717899684254</v>
+        <v>187.8005508490403</v>
       </c>
       <c r="C65" t="n">
-        <v>188.3193265216257</v>
+        <v>188.5487999407664</v>
       </c>
       <c r="D65" t="n">
-        <v>185.4759890979627</v>
+        <v>186.4935963146986</v>
       </c>
       <c r="E65" t="n">
-        <v>187.7805938720703</v>
+        <v>187.1021728515625</v>
       </c>
       <c r="F65" t="n">
-        <v>120006100</v>
+        <v>97687300</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B66" t="n">
-        <v>187.8005661647843</v>
+        <v>189.1274459397885</v>
       </c>
       <c r="C66" t="n">
-        <v>188.5488153175326</v>
+        <v>190.1151249886817</v>
       </c>
       <c r="D66" t="n">
-        <v>186.4936115238563</v>
+        <v>186.0546345387688</v>
       </c>
       <c r="E66" t="n">
-        <v>187.1021881103516</v>
+        <v>186.0646057128906</v>
       </c>
       <c r="F66" t="n">
-        <v>97687300</v>
+        <v>120100500</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B67" t="n">
-        <v>189.1274459397885</v>
+        <v>189.3968130035911</v>
       </c>
       <c r="C67" t="n">
-        <v>190.1151249886817</v>
+        <v>192.4795957147097</v>
       </c>
       <c r="D67" t="n">
-        <v>186.0546345387688</v>
+        <v>187.8204997023152</v>
       </c>
       <c r="E67" t="n">
-        <v>186.0646057128906</v>
+        <v>188.4091339111328</v>
       </c>
       <c r="F67" t="n">
-        <v>120100500</v>
+        <v>148240500</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B68" t="n">
-        <v>189.3968130035911</v>
+        <v>191.3123182227279</v>
       </c>
       <c r="C68" t="n">
-        <v>192.4795957147097</v>
+        <v>193.1779629368336</v>
       </c>
       <c r="D68" t="n">
-        <v>187.8204997023152</v>
+        <v>185.7154145267434</v>
       </c>
       <c r="E68" t="n">
-        <v>188.4091339111328</v>
+        <v>187.6808166503906</v>
       </c>
       <c r="F68" t="n">
-        <v>148240500</v>
+        <v>183529700</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B69" t="n">
-        <v>191.3123337767646</v>
+        <v>190.0752284670132</v>
       </c>
       <c r="C69" t="n">
-        <v>193.1779786425506</v>
+        <v>191.7213703933745</v>
       </c>
       <c r="D69" t="n">
-        <v>185.7154296257417</v>
+        <v>186.3838692947835</v>
       </c>
       <c r="E69" t="n">
-        <v>187.6808319091797</v>
+        <v>186.8028869628906</v>
       </c>
       <c r="F69" t="n">
-        <v>183529700</v>
+        <v>176862600</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B70" t="n">
-        <v>190.0752439930999</v>
+        <v>188.1297854095839</v>
       </c>
       <c r="C70" t="n">
-        <v>191.7213860539245</v>
+        <v>190.9232365533545</v>
       </c>
       <c r="D70" t="n">
-        <v>186.3838845193456</v>
+        <v>186.1244680675316</v>
       </c>
       <c r="E70" t="n">
-        <v>186.8029022216797</v>
+        <v>188.6685180664062</v>
       </c>
       <c r="F70" t="n">
-        <v>176862600</v>
+        <v>153543200</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B71" t="n">
-        <v>188.1297854095839</v>
+        <v>188.6685228499072</v>
       </c>
       <c r="C71" t="n">
-        <v>190.9232365533545</v>
+        <v>189.1074981045344</v>
       </c>
       <c r="D71" t="n">
-        <v>186.1244680675316</v>
+        <v>183.2811352524241</v>
       </c>
       <c r="E71" t="n">
-        <v>188.6685180664062</v>
+        <v>184.6080169677734</v>
       </c>
       <c r="F71" t="n">
-        <v>153543200</v>
+        <v>172457000</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B72" t="n">
-        <v>188.6685072554968</v>
+        <v>184.6479238968445</v>
       </c>
       <c r="C72" t="n">
-        <v>189.1074824738404</v>
+        <v>185.9049768874807</v>
       </c>
       <c r="D72" t="n">
-        <v>183.2811201033086</v>
+        <v>183.2412119543349</v>
       </c>
       <c r="E72" t="n">
-        <v>184.6080017089844</v>
+        <v>184.4284362792969</v>
       </c>
       <c r="F72" t="n">
-        <v>172457000</v>
+        <v>131327500</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B73" t="n">
-        <v>184.6479238968445</v>
+        <v>182.7922691735387</v>
       </c>
       <c r="C73" t="n">
-        <v>185.9049768874807</v>
+        <v>186.6831584288149</v>
       </c>
       <c r="D73" t="n">
-        <v>183.2412119543349</v>
+        <v>182.5927391235801</v>
       </c>
       <c r="E73" t="n">
-        <v>184.4284362792969</v>
+        <v>184.5082550048828</v>
       </c>
       <c r="F73" t="n">
-        <v>131327500</v>
+        <v>137968500</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B74" t="n">
-        <v>182.7922691735387</v>
+        <v>184.5680989064521</v>
       </c>
       <c r="C74" t="n">
-        <v>186.6831584288149</v>
+        <v>187.6708389078061</v>
       </c>
       <c r="D74" t="n">
-        <v>182.5927391235801</v>
+        <v>182.9718281779948</v>
       </c>
       <c r="E74" t="n">
-        <v>184.5082550048828</v>
+        <v>185.3762054443359</v>
       </c>
       <c r="F74" t="n">
-        <v>137968500</v>
+        <v>160128900</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B75" t="n">
-        <v>184.5681140987238</v>
+        <v>183.889716612774</v>
       </c>
       <c r="C75" t="n">
-        <v>187.6708543554723</v>
+        <v>184.029389177148</v>
       </c>
       <c r="D75" t="n">
-        <v>182.9718432388734</v>
+        <v>180.3779297072971</v>
       </c>
       <c r="E75" t="n">
-        <v>185.376220703125</v>
+        <v>182.7124633789062</v>
       </c>
       <c r="F75" t="n">
-        <v>160128900</v>
+        <v>159586100</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B76" t="n">
-        <v>183.8897012556695</v>
+        <v>186.0646079796491</v>
       </c>
       <c r="C76" t="n">
-        <v>184.0293738083791</v>
+        <v>189.2571344016907</v>
       </c>
       <c r="D76" t="n">
-        <v>180.3779146434709</v>
+        <v>185.895006678512</v>
       </c>
       <c r="E76" t="n">
-        <v>182.7124481201172</v>
+        <v>186.6133270263672</v>
       </c>
       <c r="F76" t="n">
-        <v>159586100</v>
+        <v>206188600</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B77" t="n">
-        <v>186.0646079796491</v>
+        <v>188.6385950815971</v>
       </c>
       <c r="C77" t="n">
-        <v>189.2571344016907</v>
+        <v>189.9954207742267</v>
       </c>
       <c r="D77" t="n">
-        <v>185.895006678512</v>
+        <v>185.6455985734289</v>
       </c>
       <c r="E77" t="n">
-        <v>186.6133270263672</v>
+        <v>185.7952423095703</v>
       </c>
       <c r="F77" t="n">
-        <v>206188600</v>
+        <v>187967200</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B78" t="n">
-        <v>188.6385950815971</v>
+        <v>181.4753578011745</v>
       </c>
       <c r="C78" t="n">
-        <v>189.9954207742267</v>
+        <v>181.9542482267672</v>
       </c>
       <c r="D78" t="n">
-        <v>185.6455985734289</v>
+        <v>177.1953792817215</v>
       </c>
       <c r="E78" t="n">
-        <v>185.7952423095703</v>
+        <v>177.6543121337891</v>
       </c>
       <c r="F78" t="n">
-        <v>187967200</v>
+        <v>223345300</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B79" t="n">
-        <v>181.4753266272146</v>
+        <v>178.6319932794081</v>
       </c>
       <c r="C79" t="n">
-        <v>181.9542169705431</v>
+        <v>184.947217101084</v>
       </c>
       <c r="D79" t="n">
-        <v>177.1953488429791</v>
+        <v>177.9835016341843</v>
       </c>
       <c r="E79" t="n">
-        <v>177.6542816162109</v>
+        <v>182.8920288085938</v>
       </c>
       <c r="F79" t="n">
-        <v>223345300</v>
+        <v>200381000</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B80" t="n">
-        <v>178.6320081827799</v>
+        <v>184.3186915464293</v>
       </c>
       <c r="C80" t="n">
-        <v>184.9472325313386</v>
+        <v>185.7353746560278</v>
       </c>
       <c r="D80" t="n">
-        <v>177.9835164834521</v>
+        <v>183.5005985718231</v>
       </c>
       <c r="E80" t="n">
-        <v>182.8920440673828</v>
+        <v>184.4084777832031</v>
       </c>
       <c r="F80" t="n">
-        <v>200381000</v>
+        <v>139636600</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B81" t="n">
-        <v>184.3186915464293</v>
+        <v>187.0622712594319</v>
       </c>
       <c r="C81" t="n">
-        <v>185.7353746560278</v>
+        <v>189.1573747868041</v>
       </c>
       <c r="D81" t="n">
-        <v>183.5005985718231</v>
+        <v>186.3838660627843</v>
       </c>
       <c r="E81" t="n">
-        <v>184.4084777832031</v>
+        <v>187.2318725585938</v>
       </c>
       <c r="F81" t="n">
-        <v>139636600</v>
+        <v>142748100</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B82" t="n">
-        <v>187.0622712594319</v>
+        <v>186.7230748442759</v>
       </c>
       <c r="C82" t="n">
-        <v>189.1573747868041</v>
+        <v>188.6784906596197</v>
       </c>
       <c r="D82" t="n">
-        <v>186.3838660627843</v>
+        <v>185.555808059744</v>
       </c>
       <c r="E82" t="n">
-        <v>187.2318725585938</v>
+        <v>186.0346832275391</v>
       </c>
       <c r="F82" t="n">
-        <v>142748100</v>
+        <v>124799600</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B83" t="n">
-        <v>186.7230595290241</v>
+        <v>186.8028844605491</v>
       </c>
       <c r="C83" t="n">
-        <v>188.6784751839824</v>
+        <v>189.5564356240106</v>
       </c>
       <c r="D83" t="n">
-        <v>185.5557928402329</v>
+        <v>185.2664711415707</v>
       </c>
       <c r="E83" t="n">
-        <v>186.03466796875</v>
+        <v>188.0798950195312</v>
       </c>
       <c r="F83" t="n">
-        <v>124799600</v>
+        <v>143711600</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B84" t="n">
-        <v>186.8028844605491</v>
+        <v>190.823459633995</v>
       </c>
       <c r="C84" t="n">
-        <v>189.5564356240106</v>
+        <v>191.9009400606663</v>
       </c>
       <c r="D84" t="n">
-        <v>185.2664711415707</v>
+        <v>189.3967902384632</v>
       </c>
       <c r="E84" t="n">
-        <v>188.0798950195312</v>
+        <v>191.0728759765625</v>
       </c>
       <c r="F84" t="n">
-        <v>143711600</v>
+        <v>148552700</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B85" t="n">
-        <v>190.823459633995</v>
+        <v>190.8933105997472</v>
       </c>
       <c r="C85" t="n">
-        <v>191.9009400606663</v>
+        <v>193.0283141326731</v>
       </c>
       <c r="D85" t="n">
-        <v>189.3967902384632</v>
+        <v>185.6256380470483</v>
       </c>
       <c r="E85" t="n">
-        <v>191.0728759765625</v>
+        <v>192.0605773925781</v>
       </c>
       <c r="F85" t="n">
-        <v>148552700</v>
+        <v>171764400</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B86" t="n">
-        <v>190.8933105997472</v>
+        <v>190.7636224379378</v>
       </c>
       <c r="C86" t="n">
-        <v>193.0283141326731</v>
+        <v>194.0359639826301</v>
       </c>
       <c r="D86" t="n">
-        <v>185.6256380470483</v>
+        <v>189.0276790286862</v>
       </c>
       <c r="E86" t="n">
-        <v>192.0605773925781</v>
+        <v>190.6838073730469</v>
       </c>
       <c r="F86" t="n">
-        <v>171764400</v>
+        <v>179489500</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B87" t="n">
-        <v>190.7636224379378</v>
+        <v>186.7629659025267</v>
       </c>
       <c r="C87" t="n">
-        <v>194.0359639826301</v>
+        <v>189.8557348322644</v>
       </c>
       <c r="D87" t="n">
-        <v>189.0276790286862</v>
+        <v>184.4483900153819</v>
       </c>
       <c r="E87" t="n">
-        <v>190.6838073730469</v>
+        <v>185.1766815185547</v>
       </c>
       <c r="F87" t="n">
-        <v>179489500</v>
+        <v>165794100</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B88" t="n">
-        <v>186.7629659025267</v>
+        <v>185.8052108647954</v>
       </c>
       <c r="C88" t="n">
-        <v>189.8557348322644</v>
+        <v>185.8351396091497</v>
       </c>
       <c r="D88" t="n">
-        <v>184.4483900153819</v>
+        <v>175.8185703987175</v>
       </c>
       <c r="E88" t="n">
-        <v>185.1766815185547</v>
+        <v>179.9189758300781</v>
       </c>
       <c r="F88" t="n">
-        <v>165794100</v>
+        <v>204019600</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B89" t="n">
-        <v>185.8052108647954</v>
+        <v>179.0410571553003</v>
       </c>
       <c r="C89" t="n">
-        <v>185.8351396091497</v>
+        <v>179.1607721437711</v>
       </c>
       <c r="D89" t="n">
-        <v>175.8185703987175</v>
+        <v>171.5086795929406</v>
       </c>
       <c r="E89" t="n">
-        <v>179.9189758300781</v>
+        <v>173.7833557128906</v>
       </c>
       <c r="F89" t="n">
-        <v>204019600</v>
+        <v>207014100</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B90" t="n">
-        <v>179.0410571553003</v>
+        <v>174.5216119878791</v>
       </c>
       <c r="C90" t="n">
-        <v>179.1607721437711</v>
+        <v>176.4072143255947</v>
       </c>
       <c r="D90" t="n">
-        <v>171.5086795929406</v>
+        <v>170.6307227747363</v>
       </c>
       <c r="E90" t="n">
-        <v>173.7833557128906</v>
+        <v>171.4787445068359</v>
       </c>
       <c r="F90" t="n">
-        <v>207014100</v>
+        <v>206312900</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B91" t="n">
-        <v>174.5216119878791</v>
+        <v>176.2775280578147</v>
       </c>
       <c r="C91" t="n">
-        <v>176.4072143255947</v>
+        <v>186.5634574188361</v>
       </c>
       <c r="D91" t="n">
-        <v>170.6307227747363</v>
+        <v>174.1924107166939</v>
       </c>
       <c r="E91" t="n">
-        <v>171.4787445068359</v>
+        <v>184.9771728515625</v>
       </c>
       <c r="F91" t="n">
-        <v>206312900</v>
+        <v>231346200</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B92" t="n">
-        <v>176.2775135166603</v>
+        <v>183.8298238555102</v>
       </c>
       <c r="C92" t="n">
-        <v>186.5634420291942</v>
+        <v>193.2078878887748</v>
       </c>
       <c r="D92" t="n">
-        <v>174.1923963475411</v>
+        <v>183.5205500126207</v>
       </c>
       <c r="E92" t="n">
-        <v>184.9771575927734</v>
+        <v>189.5963287353516</v>
       </c>
       <c r="F92" t="n">
-        <v>231346200</v>
+        <v>196387400</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B93" t="n">
-        <v>183.8298386502086</v>
+        <v>190.9332352083219</v>
       </c>
       <c r="C93" t="n">
-        <v>193.2079034382237</v>
+        <v>192.0306581643501</v>
       </c>
       <c r="D93" t="n">
-        <v>183.5205647824287</v>
+        <v>187.6808358171596</v>
       </c>
       <c r="E93" t="n">
-        <v>189.5963439941406</v>
+        <v>188.099853515625</v>
       </c>
       <c r="F93" t="n">
-        <v>196387400</v>
+        <v>136764800</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B94" t="n">
-        <v>190.933219719687</v>
+        <v>192.0007142509167</v>
       </c>
       <c r="C94" t="n">
-        <v>192.0306425866914</v>
+        <v>192.8088208357837</v>
       </c>
       <c r="D94" t="n">
-        <v>187.6808205923615</v>
+        <v>188.329312674443</v>
       </c>
       <c r="E94" t="n">
-        <v>188.0998382568359</v>
+        <v>189.6063232421875</v>
       </c>
       <c r="F94" t="n">
-        <v>136764800</v>
+        <v>144192700</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B95" t="n">
-        <v>192.0007297023972</v>
+        <v>192.5793648877844</v>
       </c>
       <c r="C95" t="n">
-        <v>192.8088363522974</v>
+        <v>193.1580126884611</v>
       </c>
       <c r="D95" t="n">
-        <v>188.3293278304631</v>
+        <v>186.0745817463215</v>
       </c>
       <c r="E95" t="n">
-        <v>189.6063385009766</v>
+        <v>186.5035858154297</v>
       </c>
       <c r="F95" t="n">
-        <v>144192700</v>
+        <v>189932500</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B96" t="n">
-        <v>192.5793806436633</v>
+        <v>187.042320465516</v>
       </c>
       <c r="C96" t="n">
-        <v>193.158028491682</v>
+        <v>187.0622780376601</v>
       </c>
       <c r="D96" t="n">
-        <v>186.0745969700116</v>
+        <v>181.1660713803529</v>
       </c>
       <c r="E96" t="n">
-        <v>186.5036010742188</v>
+        <v>182.3832244873047</v>
       </c>
       <c r="F96" t="n">
-        <v>189932500</v>
+        <v>161888000</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B97" t="n">
-        <v>187.0423048169314</v>
+        <v>181.3256935584433</v>
       </c>
       <c r="C97" t="n">
-        <v>187.0622623874058</v>
+        <v>186.7130808403767</v>
       </c>
       <c r="D97" t="n">
-        <v>181.1660562233949</v>
+        <v>178.7616860728079</v>
       </c>
       <c r="E97" t="n">
-        <v>182.3832092285156</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="F97" t="n">
-        <v>161888000</v>
+        <v>162276900</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B98" t="n">
-        <v>181.3257085516038</v>
+        <v>188.3093443160685</v>
       </c>
       <c r="C98" t="n">
-        <v>186.7130962790006</v>
+        <v>189.9255573932224</v>
       </c>
       <c r="D98" t="n">
-        <v>178.7617008539599</v>
+        <v>186.3239846890322</v>
       </c>
       <c r="E98" t="n">
-        <v>184.5381927490234</v>
+        <v>187.5411376953125</v>
       </c>
       <c r="F98" t="n">
-        <v>162276900</v>
+        <v>164749100</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B99" t="n">
-        <v>188.3093443160685</v>
+        <v>186.62329889396</v>
       </c>
       <c r="C99" t="n">
-        <v>189.9255573932224</v>
+        <v>187.9900957055448</v>
       </c>
       <c r="D99" t="n">
-        <v>186.3239846890322</v>
+        <v>185.2265733363672</v>
       </c>
       <c r="E99" t="n">
-        <v>187.5411376953125</v>
+        <v>187.4613342285156</v>
       </c>
       <c r="F99" t="n">
-        <v>164749100</v>
+        <v>126554500</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B100" t="n">
-        <v>186.6232837033845</v>
+        <v>186.1344488846578</v>
       </c>
       <c r="C100" t="n">
-        <v>187.9900804037161</v>
+        <v>189.8856654675195</v>
       </c>
       <c r="D100" t="n">
-        <v>185.226558259481</v>
+        <v>185.5059147845697</v>
       </c>
       <c r="E100" t="n">
-        <v>187.4613189697266</v>
+        <v>189.3768615722656</v>
       </c>
       <c r="F100" t="n">
-        <v>126554500</v>
+        <v>178422300</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B101" t="n">
-        <v>186.1344488846578</v>
+        <v>190.9531547742145</v>
       </c>
       <c r="C101" t="n">
-        <v>189.8856654675195</v>
+        <v>193.4972046328596</v>
       </c>
       <c r="D101" t="n">
-        <v>185.5059147845697</v>
+        <v>189.1374116308485</v>
       </c>
       <c r="E101" t="n">
-        <v>189.3768615722656</v>
+        <v>191.1028137207031</v>
       </c>
       <c r="F101" t="n">
-        <v>178422300</v>
+        <v>171584800</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B102" t="n">
-        <v>190.9531547742145</v>
+        <v>191.0429698590405</v>
       </c>
       <c r="C102" t="n">
-        <v>193.4972046328596</v>
+        <v>193.3176459547985</v>
       </c>
       <c r="D102" t="n">
-        <v>189.1374116308485</v>
+        <v>186.9625064417709</v>
       </c>
       <c r="E102" t="n">
-        <v>191.1028137207031</v>
+        <v>192.3997955322266</v>
       </c>
       <c r="F102" t="n">
-        <v>171584800</v>
+        <v>175123600</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B103" t="n">
-        <v>191.0429698590405</v>
+        <v>193.9960453222018</v>
       </c>
       <c r="C103" t="n">
-        <v>193.3176459547985</v>
+        <v>197.1686293956491</v>
       </c>
       <c r="D103" t="n">
-        <v>186.9625064417709</v>
+        <v>193.3375824661624</v>
       </c>
       <c r="E103" t="n">
-        <v>192.3997955322266</v>
+        <v>195.1034545898438</v>
       </c>
       <c r="F103" t="n">
-        <v>175123600</v>
+        <v>250637100</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B104" t="n">
-        <v>193.9960453222018</v>
+        <v>193.8164813019665</v>
       </c>
       <c r="C104" t="n">
-        <v>197.1686293956491</v>
+        <v>193.8364236513225</v>
       </c>
       <c r="D104" t="n">
-        <v>193.3375824661624</v>
+        <v>183.8897126034445</v>
       </c>
       <c r="E104" t="n">
-        <v>195.1034545898438</v>
+        <v>184.4583740234375</v>
       </c>
       <c r="F104" t="n">
-        <v>250637100</v>
+        <v>360807900</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B105" t="n">
-        <v>193.8164813019665</v>
+        <v>180.8268714126474</v>
       </c>
       <c r="C105" t="n">
-        <v>193.8364236513225</v>
+        <v>182.1637395256691</v>
       </c>
       <c r="D105" t="n">
-        <v>183.8897126034445</v>
+        <v>175.9682453114839</v>
       </c>
       <c r="E105" t="n">
-        <v>184.4583740234375</v>
+        <v>176.7763519287109</v>
       </c>
       <c r="F105" t="n">
-        <v>360807900</v>
+        <v>311636500</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B106" t="n">
-        <v>180.82685580423</v>
+        <v>174.6014235260267</v>
       </c>
       <c r="C106" t="n">
-        <v>182.1637238018573</v>
+        <v>183.0317086895539</v>
       </c>
       <c r="D106" t="n">
-        <v>175.9682301224481</v>
+        <v>174.2322921838959</v>
       </c>
       <c r="E106" t="n">
-        <v>176.7763366699219</v>
+        <v>182.0539855957031</v>
       </c>
       <c r="F106" t="n">
-        <v>311636500</v>
+        <v>209095300</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B107" t="n">
-        <v>174.6014088918714</v>
+        <v>178.0733135069376</v>
       </c>
       <c r="C107" t="n">
-        <v>183.0316933488174</v>
+        <v>180.4776756968921</v>
       </c>
       <c r="D107" t="n">
-        <v>174.2322775806792</v>
+        <v>176.5069714269912</v>
       </c>
       <c r="E107" t="n">
-        <v>182.0539703369141</v>
+        <v>179.6296691894531</v>
       </c>
       <c r="F107" t="n">
-        <v>209095300</v>
+        <v>178099400</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B108" t="n">
-        <v>178.0733135069376</v>
+        <v>180.0187499528396</v>
       </c>
       <c r="C108" t="n">
-        <v>180.4776756968921</v>
+        <v>184.2687991412151</v>
       </c>
       <c r="D108" t="n">
-        <v>176.5069714269912</v>
+        <v>179.6396322236537</v>
       </c>
       <c r="E108" t="n">
-        <v>179.6296691894531</v>
+        <v>182.6126708984375</v>
       </c>
       <c r="F108" t="n">
-        <v>178099400</v>
+        <v>177731200</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B109" t="n">
-        <v>180.0187649948852</v>
+        <v>180.7470399397241</v>
       </c>
       <c r="C109" t="n">
-        <v>184.2688145383873</v>
+        <v>183.6302923567135</v>
       </c>
       <c r="D109" t="n">
-        <v>179.6396472340209</v>
+        <v>177.4647274492447</v>
       </c>
       <c r="E109" t="n">
-        <v>182.6126861572266</v>
+        <v>182.9119720458984</v>
       </c>
       <c r="F109" t="n">
-        <v>177731200</v>
+        <v>198779700</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B110" t="n">
-        <v>180.7470399397241</v>
+        <v>179.4201653790109</v>
       </c>
       <c r="C110" t="n">
-        <v>183.6302923567135</v>
+        <v>182.3333469017365</v>
       </c>
       <c r="D110" t="n">
-        <v>177.4647274492447</v>
+        <v>176.4072264371208</v>
       </c>
       <c r="E110" t="n">
-        <v>182.9119720458984</v>
+        <v>177.4048919677734</v>
       </c>
       <c r="F110" t="n">
-        <v>198779700</v>
+        <v>189021900</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B111" t="n">
-        <v>179.420149946886</v>
+        <v>176.4171820751478</v>
       </c>
       <c r="C111" t="n">
-        <v>182.3333312190456</v>
+        <v>182.4829897940845</v>
       </c>
       <c r="D111" t="n">
-        <v>176.407211264142</v>
+        <v>175.1501427003192</v>
       </c>
       <c r="E111" t="n">
-        <v>177.4048767089844</v>
+        <v>182.2235870361328</v>
       </c>
       <c r="F111" t="n">
-        <v>189021900</v>
+        <v>177213600</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B112" t="n">
-        <v>176.4171820751478</v>
+        <v>181.9741609804723</v>
       </c>
       <c r="C112" t="n">
-        <v>182.4829897940845</v>
+        <v>186.0047376795775</v>
       </c>
       <c r="D112" t="n">
-        <v>175.1501427003192</v>
+        <v>181.5850720874406</v>
       </c>
       <c r="E112" t="n">
-        <v>182.2235870361328</v>
+        <v>184.3386383056641</v>
       </c>
       <c r="F112" t="n">
-        <v>177213600</v>
+        <v>179118500</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,25 +3355,25 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B113" t="n">
-        <v>181.9741760435397</v>
+        <v>185.4860219488843</v>
       </c>
       <c r="C113" t="n">
-        <v>186.0047530762794</v>
+        <v>187.1921136401388</v>
       </c>
       <c r="D113" t="n">
-        <v>181.5850871183009</v>
+        <v>184.0293448898806</v>
       </c>
       <c r="E113" t="n">
-        <v>184.3386535644531</v>
+        <v>185.6057434082031</v>
       </c>
       <c r="F113" t="n">
-        <v>179118500</v>
+        <v>145280400</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3381,25 +3381,25 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B114" t="n">
-        <v>185.4860219488843</v>
+        <v>183.6302794851663</v>
       </c>
       <c r="C114" t="n">
-        <v>187.1921136401388</v>
+        <v>184.5182492431283</v>
       </c>
       <c r="D114" t="n">
-        <v>184.0293448898806</v>
+        <v>181.3355215595592</v>
       </c>
       <c r="E114" t="n">
-        <v>185.6057434082031</v>
+        <v>182.7223510742188</v>
       </c>
       <c r="F114" t="n">
-        <v>145280400</v>
+        <v>155762700</v>
       </c>
       <c r="G114" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B115" t="n">
-        <v>183.6302641505579</v>
+        <v>184.4982761588831</v>
       </c>
       <c r="C115" t="n">
-        <v>184.5182338343672</v>
+        <v>185.6656060713691</v>
       </c>
       <c r="D115" t="n">
-        <v>181.3355064165816</v>
+        <v>179.5296376335348</v>
       </c>
       <c r="E115" t="n">
-        <v>182.7223358154297</v>
+        <v>179.8389282226562</v>
       </c>
       <c r="F115" t="n">
-        <v>155762700</v>
+        <v>160988400</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B116" t="n">
-        <v>184.4982918130038</v>
+        <v>182.5527399223597</v>
       </c>
       <c r="C116" t="n">
-        <v>185.6656218245341</v>
+        <v>188.4492658789173</v>
       </c>
       <c r="D116" t="n">
-        <v>179.5296528660815</v>
+        <v>180.9962999229416</v>
       </c>
       <c r="E116" t="n">
-        <v>179.8389434814453</v>
+        <v>182.8021697998047</v>
       </c>
       <c r="F116" t="n">
-        <v>160988400</v>
+        <v>217307400</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B117" t="n">
-        <v>182.5527246843909</v>
+        <v>184.6379576703901</v>
       </c>
       <c r="C117" t="n">
-        <v>188.4492501487561</v>
+        <v>184.9771786272242</v>
       </c>
       <c r="D117" t="n">
-        <v>180.9962848148914</v>
+        <v>181.2656610816535</v>
       </c>
       <c r="E117" t="n">
-        <v>182.8021545410156</v>
+        <v>181.5150909423828</v>
       </c>
       <c r="F117" t="n">
-        <v>217307400</v>
+        <v>182497800</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B118" t="n">
-        <v>184.6379731916982</v>
+        <v>182.0638447517288</v>
       </c>
       <c r="C118" t="n">
-        <v>184.9771941770484</v>
+        <v>182.9618014097589</v>
       </c>
       <c r="D118" t="n">
-        <v>181.2656763194747</v>
+        <v>179.9187539793071</v>
       </c>
       <c r="E118" t="n">
-        <v>181.5151062011719</v>
+        <v>179.9885864257812</v>
       </c>
       <c r="F118" t="n">
-        <v>182497800</v>
+        <v>156683100</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B119" t="n">
-        <v>182.0638447517288</v>
+        <v>177.6040375011918</v>
       </c>
       <c r="C119" t="n">
-        <v>182.9618014097589</v>
+        <v>179.569546076418</v>
       </c>
       <c r="D119" t="n">
-        <v>179.9187539793071</v>
+        <v>175.3890990582871</v>
       </c>
       <c r="E119" t="n">
-        <v>179.9885864257812</v>
+        <v>178.1527862548828</v>
       </c>
       <c r="F119" t="n">
-        <v>156683100</v>
+        <v>170968500</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B120" t="n">
-        <v>177.6040222894031</v>
+        <v>177.5940529420793</v>
       </c>
       <c r="C120" t="n">
-        <v>179.5695306962835</v>
+        <v>177.8534545050662</v>
       </c>
       <c r="D120" t="n">
-        <v>175.3890840362079</v>
+        <v>171.3283763370981</v>
       </c>
       <c r="E120" t="n">
-        <v>178.1527709960938</v>
+        <v>172.3061370849609</v>
       </c>
       <c r="F120" t="n">
-        <v>170968500</v>
+        <v>241323500</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B121" t="n">
-        <v>177.5940686691464</v>
+        <v>176.8557415306554</v>
       </c>
       <c r="C121" t="n">
-        <v>177.853470255105</v>
+        <v>177.9632107122345</v>
       </c>
       <c r="D121" t="n">
-        <v>171.3283915093003</v>
+        <v>174.3614429436745</v>
       </c>
       <c r="E121" t="n">
-        <v>172.30615234375</v>
+        <v>175.2394409179688</v>
       </c>
       <c r="F121" t="n">
-        <v>241323500</v>
+        <v>182836300</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B122" t="n">
-        <v>176.8557415306554</v>
+        <v>174.4312942297872</v>
       </c>
       <c r="C122" t="n">
-        <v>177.9632107122345</v>
+        <v>175.8181236639554</v>
       </c>
       <c r="D122" t="n">
-        <v>174.3614429436745</v>
+        <v>173.5832266030264</v>
       </c>
       <c r="E122" t="n">
-        <v>175.2394409179688</v>
+        <v>174.8004455566406</v>
       </c>
       <c r="F122" t="n">
-        <v>182836300</v>
+        <v>147667800</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B123" t="n">
-        <v>174.4312942297872</v>
+        <v>176.6961233561449</v>
       </c>
       <c r="C123" t="n">
-        <v>175.8181236639554</v>
+        <v>180.8067226806179</v>
       </c>
       <c r="D123" t="n">
-        <v>173.5832266030264</v>
+        <v>176.4466934898736</v>
       </c>
       <c r="E123" t="n">
-        <v>174.8004455566406</v>
+        <v>178.2725067138672</v>
       </c>
       <c r="F123" t="n">
-        <v>147667800</v>
+        <v>162602100</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B124" t="n">
-        <v>176.6961233561449</v>
+        <v>175.6684741654964</v>
       </c>
       <c r="C124" t="n">
-        <v>180.8067226806179</v>
+        <v>176.1074579435819</v>
       </c>
       <c r="D124" t="n">
-        <v>176.4466934898736</v>
+        <v>170.7497092682189</v>
       </c>
       <c r="E124" t="n">
-        <v>178.2725067138672</v>
+        <v>170.8494873046875</v>
       </c>
       <c r="F124" t="n">
-        <v>162602100</v>
+        <v>186152200</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B125" t="n">
-        <v>175.6684741654964</v>
+        <v>169.6122945102883</v>
       </c>
       <c r="C125" t="n">
-        <v>176.1074579435819</v>
+        <v>170.5800835262955</v>
       </c>
       <c r="D125" t="n">
-        <v>170.7497092682189</v>
+        <v>166.6291080850299</v>
       </c>
       <c r="E125" t="n">
-        <v>170.8494873046875</v>
+        <v>167.1379547119141</v>
       </c>
       <c r="F125" t="n">
-        <v>186152200</v>
+        <v>196212700</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B126" t="n">
-        <v>169.6123099949711</v>
+        <v>168.3950875250076</v>
       </c>
       <c r="C126" t="n">
-        <v>170.5800990993323</v>
+        <v>169.0635577295173</v>
       </c>
       <c r="D126" t="n">
-        <v>166.629123297364</v>
+        <v>163.8953782868944</v>
       </c>
       <c r="E126" t="n">
-        <v>167.1379699707031</v>
+        <v>164.7933197021484</v>
       </c>
       <c r="F126" t="n">
-        <v>196212700</v>
+        <v>185627000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B127" t="n">
-        <v>168.3950875250076</v>
+        <v>166.5892250311153</v>
       </c>
       <c r="C127" t="n">
-        <v>169.0635577295173</v>
+        <v>174.2217730660379</v>
       </c>
       <c r="D127" t="n">
-        <v>163.8953782868944</v>
+        <v>166.5792533168182</v>
       </c>
       <c r="E127" t="n">
-        <v>164.7933197021484</v>
+        <v>174.0022735595703</v>
       </c>
       <c r="F127" t="n">
-        <v>185627000</v>
+        <v>226181300</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B128" t="n">
-        <v>166.589210422399</v>
+        <v>175.5986272559566</v>
       </c>
       <c r="C128" t="n">
-        <v>174.2217577880002</v>
+        <v>176.9654980623514</v>
       </c>
       <c r="D128" t="n">
-        <v>166.5792387089764</v>
+        <v>174.3514779146501</v>
       </c>
       <c r="E128" t="n">
-        <v>174.0022583007812</v>
+        <v>175.3491973876953</v>
       </c>
       <c r="F128" t="n">
-        <v>226181300</v>
+        <v>168132000</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B129" t="n">
-        <v>175.5986119754623</v>
+        <v>171.7873183615289</v>
       </c>
       <c r="C129" t="n">
-        <v>176.9654826629128</v>
+        <v>177.0852211444685</v>
       </c>
       <c r="D129" t="n">
-        <v>174.351462742682</v>
+        <v>170.9791680862979</v>
       </c>
       <c r="E129" t="n">
-        <v>175.3491821289062</v>
+        <v>176.9854431152344</v>
       </c>
       <c r="F129" t="n">
-        <v>168132000</v>
+        <v>143143200</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B130" t="n">
-        <v>171.787333172162</v>
+        <v>176.7559774774269</v>
       </c>
       <c r="C130" t="n">
-        <v>177.0852364118599</v>
+        <v>177.3845303646084</v>
       </c>
       <c r="D130" t="n">
-        <v>170.9791828272563</v>
+        <v>175.3591611441553</v>
       </c>
       <c r="E130" t="n">
-        <v>176.9854583740234</v>
+        <v>177.2348785400391</v>
       </c>
       <c r="F130" t="n">
-        <v>143143200</v>
+        <v>107564300</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B131" t="n">
-        <v>176.7559774774269</v>
+        <v>175.3292270516068</v>
       </c>
       <c r="C131" t="n">
-        <v>177.3845303646084</v>
+        <v>177.8235255680002</v>
       </c>
       <c r="D131" t="n">
-        <v>175.3591611441553</v>
+        <v>173.2639557965079</v>
       </c>
       <c r="E131" t="n">
-        <v>177.2348785400391</v>
+        <v>177.6938323974609</v>
       </c>
       <c r="F131" t="n">
-        <v>107564300</v>
+        <v>132534900</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B132" t="n">
-        <v>175.3292270516068</v>
+        <v>184.079243714486</v>
       </c>
       <c r="C132" t="n">
-        <v>177.8235255680002</v>
+        <v>184.837505037226</v>
       </c>
       <c r="D132" t="n">
-        <v>173.2639557965079</v>
+        <v>179.8888249511496</v>
       </c>
       <c r="E132" t="n">
-        <v>177.6938323974609</v>
+        <v>181.6647644042969</v>
       </c>
       <c r="F132" t="n">
-        <v>132534900</v>
+        <v>147732700</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B133" t="n">
-        <v>184.079243714486</v>
+        <v>181.4252987848774</v>
       </c>
       <c r="C133" t="n">
-        <v>184.837505037226</v>
+        <v>183.6601958045732</v>
       </c>
       <c r="D133" t="n">
-        <v>179.8888249511496</v>
+        <v>180.2080798537204</v>
       </c>
       <c r="E133" t="n">
-        <v>181.6647644042969</v>
+        <v>183.4905853271484</v>
       </c>
       <c r="F133" t="n">
-        <v>147732700</v>
+        <v>116428500</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B134" t="n">
-        <v>181.4253138719204</v>
+        <v>183.8896736698189</v>
       </c>
       <c r="C134" t="n">
-        <v>183.6602110774668</v>
+        <v>189.5666999081706</v>
       </c>
       <c r="D134" t="n">
-        <v>180.2080948395415</v>
+        <v>183.8797019557237</v>
       </c>
       <c r="E134" t="n">
-        <v>183.4906005859375</v>
+        <v>188.1998291015625</v>
       </c>
       <c r="F134" t="n">
-        <v>116428500</v>
+        <v>160459500</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B135" t="n">
-        <v>183.8896736698189</v>
+        <v>185.605746824658</v>
       </c>
       <c r="C135" t="n">
-        <v>189.5666999081706</v>
+        <v>189.2274732756209</v>
       </c>
       <c r="D135" t="n">
-        <v>183.8797019557237</v>
+        <v>185.3164148846483</v>
       </c>
       <c r="E135" t="n">
-        <v>188.1998291015625</v>
+        <v>188.8782653808594</v>
       </c>
       <c r="F135" t="n">
-        <v>160459500</v>
+        <v>133648200</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B136" t="n">
-        <v>185.605746824658</v>
+        <v>190.4047764107204</v>
       </c>
       <c r="C136" t="n">
-        <v>189.2274732756209</v>
+        <v>196.0618438720703</v>
       </c>
       <c r="D136" t="n">
-        <v>185.3164148846483</v>
+        <v>190.3349439656124</v>
       </c>
       <c r="E136" t="n">
-        <v>188.8782653808594</v>
+        <v>196.0618438720703</v>
       </c>
       <c r="F136" t="n">
-        <v>133648200</v>
+        <v>161307000</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B137" t="n">
-        <v>190.4047764107204</v>
+        <v>196.0917851116163</v>
       </c>
       <c r="C137" t="n">
-        <v>196.0618438720703</v>
+        <v>199.9429830157183</v>
       </c>
       <c r="D137" t="n">
-        <v>190.3349439656124</v>
+        <v>195.2936216855987</v>
       </c>
       <c r="E137" t="n">
-        <v>196.0618438720703</v>
+        <v>198.4164733886719</v>
       </c>
       <c r="F137" t="n">
-        <v>161307000</v>
+        <v>185338400</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B138" t="n">
-        <v>196.0917851116163</v>
+        <v>196.9797440092329</v>
       </c>
       <c r="C138" t="n">
-        <v>199.9429830157183</v>
+        <v>199.3942384790618</v>
       </c>
       <c r="D138" t="n">
-        <v>195.2936216855987</v>
+        <v>195.3634433694217</v>
       </c>
       <c r="E138" t="n">
-        <v>198.4164733886719</v>
+        <v>197.8976593017578</v>
       </c>
       <c r="F138" t="n">
-        <v>185338400</v>
+        <v>134012900</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B139" t="n">
-        <v>196.9797440092329</v>
+        <v>199.444107632571</v>
       </c>
       <c r="C139" t="n">
-        <v>199.3942384790618</v>
+        <v>201.2400056483541</v>
       </c>
       <c r="D139" t="n">
-        <v>195.3634433694217</v>
+        <v>198.8155547450397</v>
       </c>
       <c r="E139" t="n">
-        <v>197.8976593017578</v>
+        <v>201.2200469970703</v>
       </c>
       <c r="F139" t="n">
-        <v>134012900</v>
+        <v>160324400</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B140" t="n">
-        <v>199.444107632571</v>
+        <v>199.5239239232554</v>
       </c>
       <c r="C140" t="n">
-        <v>201.2400056483541</v>
+        <v>201.7089318732817</v>
       </c>
       <c r="D140" t="n">
-        <v>198.8155547450397</v>
+        <v>197.3888049886708</v>
       </c>
       <c r="E140" t="n">
-        <v>201.2200469970703</v>
+        <v>201.5991821289062</v>
       </c>
       <c r="F140" t="n">
-        <v>160324400</v>
+        <v>119381400</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B141" t="n">
-        <v>199.5239239232554</v>
+        <v>201.6690479582887</v>
       </c>
       <c r="C141" t="n">
-        <v>201.7089318732817</v>
+        <v>202.2876291783034</v>
       </c>
       <c r="D141" t="n">
-        <v>197.3888049886708</v>
+        <v>198.5461810430697</v>
       </c>
       <c r="E141" t="n">
-        <v>201.5991821289062</v>
+        <v>199.4241790771484</v>
       </c>
       <c r="F141" t="n">
-        <v>119381400</v>
+        <v>107945300</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B142" t="n">
-        <v>201.6690479582887</v>
+        <v>200.5316418294082</v>
       </c>
       <c r="C142" t="n">
-        <v>202.2876291783034</v>
+        <v>202.0381927490234</v>
       </c>
       <c r="D142" t="n">
-        <v>198.5461810430697</v>
+        <v>198.546174602744</v>
       </c>
       <c r="E142" t="n">
-        <v>199.4241790771484</v>
+        <v>202.0381927490234</v>
       </c>
       <c r="F142" t="n">
-        <v>107945300</v>
+        <v>107501000</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B143" t="n">
-        <v>200.5316418294082</v>
+        <v>201.9982837593082</v>
       </c>
       <c r="C143" t="n">
-        <v>202.0381927490234</v>
+        <v>203.3651545152774</v>
       </c>
       <c r="D143" t="n">
-        <v>198.546174602744</v>
+        <v>196.7702284327844</v>
       </c>
       <c r="E143" t="n">
-        <v>202.0381927490234</v>
+        <v>199.1847076416016</v>
       </c>
       <c r="F143" t="n">
-        <v>107501000</v>
+        <v>113561800</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B144" t="n">
-        <v>201.9982837593082</v>
+        <v>199.5039827094276</v>
       </c>
       <c r="C144" t="n">
-        <v>203.3651545152774</v>
+        <v>210.468909435165</v>
       </c>
       <c r="D144" t="n">
-        <v>196.7702284327844</v>
+        <v>199.3543156614425</v>
       </c>
       <c r="E144" t="n">
-        <v>199.1847076416016</v>
+        <v>207.7950286865234</v>
       </c>
       <c r="F144" t="n">
-        <v>113561800</v>
+        <v>214134400</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B145" t="n">
-        <v>199.5039827094276</v>
+        <v>209.1718784416434</v>
       </c>
       <c r="C145" t="n">
-        <v>210.468909435165</v>
+        <v>216.335512072091</v>
       </c>
       <c r="D145" t="n">
-        <v>199.3543156614425</v>
+        <v>206.9070662315077</v>
       </c>
       <c r="E145" t="n">
-        <v>207.7950286865234</v>
+        <v>216.1160125732422</v>
       </c>
       <c r="F145" t="n">
-        <v>214134400</v>
+        <v>187172400</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B146" t="n">
-        <v>209.1718784416434</v>
+        <v>209.0122528840405</v>
       </c>
       <c r="C146" t="n">
-        <v>216.335512072091</v>
+        <v>214.2402930542568</v>
       </c>
       <c r="D146" t="n">
-        <v>206.9070662315077</v>
+        <v>207.7251862691963</v>
       </c>
       <c r="E146" t="n">
-        <v>216.1160125732422</v>
+        <v>212.6838531494141</v>
       </c>
       <c r="F146" t="n">
-        <v>187172400</v>
+        <v>180275400</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B147" t="n">
-        <v>209.0122528840405</v>
+        <v>212.2149257168926</v>
       </c>
       <c r="C147" t="n">
-        <v>214.2402930542568</v>
+        <v>212.2348843687743</v>
       </c>
       <c r="D147" t="n">
-        <v>207.7251862691963</v>
+        <v>207.1066069625242</v>
       </c>
       <c r="E147" t="n">
-        <v>212.6838531494141</v>
+        <v>208.7727966308594</v>
       </c>
       <c r="F147" t="n">
-        <v>180275400</v>
+        <v>123711800</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B148" t="n">
-        <v>212.2149257168926</v>
+        <v>209.4512425942353</v>
       </c>
       <c r="C148" t="n">
-        <v>212.2348843687743</v>
+        <v>209.820409153207</v>
       </c>
       <c r="D148" t="n">
-        <v>207.1066069625242</v>
+        <v>198.2468571251534</v>
       </c>
       <c r="E148" t="n">
-        <v>208.7727966308594</v>
+        <v>199.1148834228516</v>
       </c>
       <c r="F148" t="n">
-        <v>123711800</v>
+        <v>225239200</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B149" t="n">
-        <v>209.4512265433391</v>
+        <v>200.8209691272831</v>
       </c>
       <c r="C149" t="n">
-        <v>209.8203930740204</v>
+        <v>202.5370477944956</v>
       </c>
       <c r="D149" t="n">
-        <v>198.2468419328838</v>
+        <v>196.6704525729091</v>
       </c>
       <c r="E149" t="n">
-        <v>199.1148681640625</v>
+        <v>197.9974212646484</v>
       </c>
       <c r="F149" t="n">
-        <v>225239200</v>
+        <v>128647000</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B150" t="n">
-        <v>200.8209846036705</v>
+        <v>199.0450218084295</v>
       </c>
       <c r="C150" t="n">
-        <v>202.5370634031337</v>
+        <v>201.2699318245734</v>
       </c>
       <c r="D150" t="n">
-        <v>196.6704677294345</v>
+        <v>194.2958829090753</v>
       </c>
       <c r="E150" t="n">
-        <v>197.9974365234375</v>
+        <v>198.02734375</v>
       </c>
       <c r="F150" t="n">
-        <v>128647000</v>
+        <v>125368100</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B151" t="n">
-        <v>199.0450218084295</v>
+        <v>198.8454820247872</v>
       </c>
       <c r="C151" t="n">
-        <v>201.2699318245734</v>
+        <v>199.7833407086998</v>
       </c>
       <c r="D151" t="n">
-        <v>194.2958829090753</v>
+        <v>195.5829352820671</v>
       </c>
       <c r="E151" t="n">
-        <v>198.02734375</v>
+        <v>196.0518646240234</v>
       </c>
       <c r="F151" t="n">
-        <v>125368100</v>
+        <v>113406600</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B152" t="n">
-        <v>198.8454820247872</v>
+        <v>199.4341385249406</v>
       </c>
       <c r="C152" t="n">
-        <v>199.7833407086998</v>
+        <v>207.7950323152332</v>
       </c>
       <c r="D152" t="n">
-        <v>195.5829352820671</v>
+        <v>198.1570588579161</v>
       </c>
       <c r="E152" t="n">
-        <v>196.0518646240234</v>
+        <v>207.3560333251953</v>
       </c>
       <c r="F152" t="n">
-        <v>113406600</v>
+        <v>188362800</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B153" t="n">
-        <v>199.4341385249406</v>
+        <v>207.8648724722903</v>
       </c>
       <c r="C153" t="n">
-        <v>207.7950323152332</v>
+        <v>213.7115092245668</v>
       </c>
       <c r="D153" t="n">
-        <v>198.1570588579161</v>
+        <v>206.0290722858257</v>
       </c>
       <c r="E153" t="n">
-        <v>207.3560333251953</v>
+        <v>211.0176696777344</v>
       </c>
       <c r="F153" t="n">
-        <v>188362800</v>
+        <v>168307900</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B154" t="n">
-        <v>207.8648724722903</v>
+        <v>212.5441790763045</v>
       </c>
       <c r="C154" t="n">
-        <v>213.7115092245668</v>
+        <v>217.3033052467507</v>
       </c>
       <c r="D154" t="n">
-        <v>206.0290722858257</v>
+        <v>212.4044989584125</v>
       </c>
       <c r="E154" t="n">
-        <v>211.0176696777344</v>
+        <v>214.709228515625</v>
       </c>
       <c r="F154" t="n">
-        <v>168307900</v>
+        <v>136421400</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B155" t="n">
-        <v>212.5441790763045</v>
+        <v>213.5518657378577</v>
       </c>
       <c r="C155" t="n">
-        <v>217.3033052467507</v>
+        <v>221.7930381906342</v>
       </c>
       <c r="D155" t="n">
-        <v>212.4044989584125</v>
+        <v>213.402213909002</v>
       </c>
       <c r="E155" t="n">
-        <v>214.709228515625</v>
+        <v>218.9395599365234</v>
       </c>
       <c r="F155" t="n">
-        <v>136421400</v>
+        <v>160685800</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B156" t="n">
-        <v>213.5518657378577</v>
+        <v>218.0515943496244</v>
       </c>
       <c r="C156" t="n">
-        <v>221.7930381906342</v>
+        <v>223.239732575863</v>
       </c>
       <c r="D156" t="n">
-        <v>213.402213909002</v>
+        <v>214.4298677829735</v>
       </c>
       <c r="E156" t="n">
-        <v>218.9395599365234</v>
+        <v>220.2765045166016</v>
       </c>
       <c r="F156" t="n">
-        <v>160685800</v>
+        <v>159176600</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B157" t="n">
-        <v>218.0515943496244</v>
+        <v>224.4170305354026</v>
       </c>
       <c r="C157" t="n">
-        <v>223.239732575863</v>
+        <v>227.3203978139454</v>
       </c>
       <c r="D157" t="n">
-        <v>214.4298677829735</v>
+        <v>221.0647077692387</v>
       </c>
       <c r="E157" t="n">
-        <v>220.2765045166016</v>
+        <v>225.3149871826172</v>
       </c>
       <c r="F157" t="n">
-        <v>159176600</v>
+        <v>150405400</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B158" t="n">
-        <v>224.4170305354026</v>
+        <v>229.3258255277811</v>
       </c>
       <c r="C158" t="n">
-        <v>227.3203978139454</v>
+        <v>236.0005559723521</v>
       </c>
       <c r="D158" t="n">
-        <v>221.0647077692387</v>
+        <v>228.7770767762568</v>
       </c>
       <c r="E158" t="n">
-        <v>225.3149871826172</v>
+        <v>235.202392578125</v>
       </c>
       <c r="F158" t="n">
-        <v>150405400</v>
+        <v>180782900</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B159" t="n">
-        <v>229.3258255277811</v>
+        <v>229.2360294447337</v>
       </c>
       <c r="C159" t="n">
-        <v>236.0005559723521</v>
+        <v>230.9720668751014</v>
       </c>
       <c r="D159" t="n">
-        <v>228.7770767762568</v>
+        <v>223.7286287034134</v>
       </c>
       <c r="E159" t="n">
-        <v>235.202392578125</v>
+        <v>224.8061676025391</v>
       </c>
       <c r="F159" t="n">
-        <v>180782900</v>
+        <v>180977600</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B160" t="n">
-        <v>229.2360138852663</v>
+        <v>229.345773483712</v>
       </c>
       <c r="C160" t="n">
-        <v>230.9720511978</v>
+        <v>229.4754818886306</v>
       </c>
       <c r="D160" t="n">
-        <v>223.7286135177626</v>
+        <v>217.8719993892805</v>
       </c>
       <c r="E160" t="n">
-        <v>224.80615234375</v>
+        <v>221.8130035400391</v>
       </c>
       <c r="F160" t="n">
-        <v>180977600</v>
+        <v>146280900</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B161" t="n">
-        <v>229.345773483712</v>
+        <v>219.1191400841904</v>
       </c>
       <c r="C161" t="n">
-        <v>229.4754818886306</v>
+        <v>223.9680572056967</v>
       </c>
       <c r="D161" t="n">
-        <v>217.8719993892805</v>
+        <v>217.4130483552105</v>
       </c>
       <c r="E161" t="n">
-        <v>221.8130035400391</v>
+        <v>220.1068878173828</v>
       </c>
       <c r="F161" t="n">
-        <v>146280900</v>
+        <v>140948200</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B162" t="n">
-        <v>219.1191400841904</v>
+        <v>222.6710257508039</v>
       </c>
       <c r="C162" t="n">
-        <v>223.9680572056967</v>
+        <v>225.6143103895453</v>
       </c>
       <c r="D162" t="n">
-        <v>217.4130483552105</v>
+        <v>219.9971448577806</v>
       </c>
       <c r="E162" t="n">
-        <v>220.1068878173828</v>
+        <v>222.9603729248047</v>
       </c>
       <c r="F162" t="n">
-        <v>140948200</v>
+        <v>184201600</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B163" t="n">
-        <v>222.6710257508039</v>
+        <v>221.7830583738447</v>
       </c>
       <c r="C163" t="n">
-        <v>225.6143103895453</v>
+        <v>226.8814055684356</v>
       </c>
       <c r="D163" t="n">
-        <v>219.9971448577806</v>
+        <v>217.4330007955402</v>
       </c>
       <c r="E163" t="n">
-        <v>222.9603729248047</v>
+        <v>219.0093994140625</v>
       </c>
       <c r="F163" t="n">
-        <v>184201600</v>
+        <v>203381800</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B164" t="n">
-        <v>221.7830583738447</v>
+        <v>220.3962175709585</v>
       </c>
       <c r="C164" t="n">
-        <v>226.8814055684356</v>
+        <v>220.5059673180016</v>
       </c>
       <c r="D164" t="n">
-        <v>217.4330007955402</v>
+        <v>214.3101381389001</v>
       </c>
       <c r="E164" t="n">
-        <v>219.0093994140625</v>
+        <v>214.8389282226562</v>
       </c>
       <c r="F164" t="n">
-        <v>203381800</v>
+        <v>169275700</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B165" t="n">
-        <v>220.3962175709585</v>
+        <v>216.0461718127993</v>
       </c>
       <c r="C165" t="n">
-        <v>220.5059673180016</v>
+        <v>217.6824311685512</v>
       </c>
       <c r="D165" t="n">
-        <v>214.3101381389001</v>
+        <v>211.5165320236786</v>
       </c>
       <c r="E165" t="n">
-        <v>214.8389282226562</v>
+        <v>214.3700103759766</v>
       </c>
       <c r="F165" t="n">
-        <v>169275700</v>
+        <v>187202600</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B166" t="n">
-        <v>216.0461718127993</v>
+        <v>213.6316806617713</v>
       </c>
       <c r="C166" t="n">
-        <v>217.6824311685512</v>
+        <v>213.6616110269177</v>
       </c>
       <c r="D166" t="n">
-        <v>211.5165320236786</v>
+        <v>208.3038625298546</v>
       </c>
       <c r="E166" t="n">
-        <v>214.3700103759766</v>
+        <v>212.1151580810547</v>
       </c>
       <c r="F166" t="n">
-        <v>187202600</v>
+        <v>167601200</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B167" t="n">
-        <v>213.6316806617713</v>
+        <v>210.7981551984497</v>
       </c>
       <c r="C167" t="n">
-        <v>213.6616110269177</v>
+        <v>215.0284909668814</v>
       </c>
       <c r="D167" t="n">
-        <v>208.3038625298546</v>
+        <v>210.7382944698381</v>
       </c>
       <c r="E167" t="n">
-        <v>212.1151580810547</v>
+        <v>213.7613830566406</v>
       </c>
       <c r="F167" t="n">
-        <v>167601200</v>
+        <v>143996000</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B168" t="n">
-        <v>210.7981702457166</v>
+        <v>214.0906505321041</v>
       </c>
       <c r="C168" t="n">
-        <v>215.0285063161196</v>
+        <v>217.3631692496548</v>
       </c>
       <c r="D168" t="n">
-        <v>210.738309512832</v>
+        <v>210.6485213277038</v>
       </c>
       <c r="E168" t="n">
-        <v>213.7613983154297</v>
+        <v>210.6584930419922</v>
       </c>
       <c r="F168" t="n">
-        <v>143996000</v>
+        <v>289410600</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B169" t="n">
-        <v>214.0906505321041</v>
+        <v>215.2380189209027</v>
       </c>
       <c r="C169" t="n">
-        <v>217.3631692496548</v>
+        <v>224.3571743491113</v>
       </c>
       <c r="D169" t="n">
-        <v>210.6485213277038</v>
+        <v>215.2080885544549</v>
       </c>
       <c r="E169" t="n">
-        <v>210.6584930419922</v>
+        <v>223.8483428955078</v>
       </c>
       <c r="F169" t="n">
-        <v>289410600</v>
+        <v>212850700</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B170" t="n">
-        <v>215.2380189209027</v>
+        <v>226.6618858382332</v>
       </c>
       <c r="C170" t="n">
-        <v>224.3571743491113</v>
+        <v>231.7502608645459</v>
       </c>
       <c r="D170" t="n">
-        <v>215.2080885544549</v>
+        <v>220.8451951370975</v>
       </c>
       <c r="E170" t="n">
-        <v>223.8483428955078</v>
+        <v>222.3118438720703</v>
       </c>
       <c r="F170" t="n">
-        <v>212850700</v>
+        <v>193362900</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B171" t="n">
-        <v>226.6618858382332</v>
+        <v>221.2143597561905</v>
       </c>
       <c r="C171" t="n">
-        <v>231.7502608645459</v>
+        <v>222.3118572511273</v>
       </c>
       <c r="D171" t="n">
-        <v>220.8451951370975</v>
+        <v>214.0207957553572</v>
       </c>
       <c r="E171" t="n">
-        <v>222.3118438720703</v>
+        <v>214.26025390625</v>
       </c>
       <c r="F171" t="n">
-        <v>193362900</v>
+        <v>160907000</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,25 +4889,25 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B172" t="n">
-        <v>221.2143597561905</v>
+        <v>213.6709127939037</v>
       </c>
       <c r="C172" t="n">
-        <v>222.3118572511273</v>
+        <v>221.3523199881091</v>
       </c>
       <c r="D172" t="n">
-        <v>214.0207957553572</v>
+        <v>210.73419644349</v>
       </c>
       <c r="E172" t="n">
-        <v>214.26025390625</v>
+        <v>218.4156036376953</v>
       </c>
       <c r="F172" t="n">
-        <v>160907000</v>
+        <v>169022200</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -4915,25 +4915,25 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B173" t="n">
-        <v>213.6709127939037</v>
+        <v>214.2902104723603</v>
       </c>
       <c r="C173" t="n">
-        <v>221.3523199881091</v>
+        <v>214.6298267834636</v>
       </c>
       <c r="D173" t="n">
-        <v>210.73419644349</v>
+        <v>204.101614447126</v>
       </c>
       <c r="E173" t="n">
-        <v>218.4156036376953</v>
+        <v>204.8707580566406</v>
       </c>
       <c r="F173" t="n">
-        <v>169022200</v>
+        <v>219655500</v>
       </c>
       <c r="G173" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B174" t="n">
-        <v>214.2902104723603</v>
+        <v>209.9450713288228</v>
       </c>
       <c r="C174" t="n">
-        <v>214.6298267834636</v>
+        <v>210.2347557268212</v>
       </c>
       <c r="D174" t="n">
-        <v>204.101614447126</v>
+        <v>205.7697506938822</v>
       </c>
       <c r="E174" t="n">
-        <v>204.8707580566406</v>
+        <v>208.4067993164062</v>
       </c>
       <c r="F174" t="n">
-        <v>219655500</v>
+        <v>138372800</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B175" t="n">
-        <v>209.9450713288228</v>
+        <v>210.3845825512031</v>
       </c>
       <c r="C175" t="n">
-        <v>210.2347557268212</v>
+        <v>211.1637095162451</v>
       </c>
       <c r="D175" t="n">
-        <v>205.7697506938822</v>
+        <v>199.1171915656509</v>
       </c>
       <c r="E175" t="n">
-        <v>208.4067993164062</v>
+        <v>207.9573059082031</v>
       </c>
       <c r="F175" t="n">
-        <v>138372800</v>
+        <v>180962500</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B176" t="n">
-        <v>210.3845825512031</v>
+        <v>204.2014963256503</v>
       </c>
       <c r="C176" t="n">
-        <v>211.1637095162451</v>
+        <v>206.9883864105018</v>
       </c>
       <c r="D176" t="n">
-        <v>199.1171915656509</v>
+        <v>199.696542748819</v>
       </c>
       <c r="E176" t="n">
-        <v>207.9573059082031</v>
+        <v>200.1959838867188</v>
       </c>
       <c r="F176" t="n">
-        <v>180962500</v>
+        <v>161746600</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B177" t="n">
-        <v>204.2014963256503</v>
+        <v>201.2647947500858</v>
       </c>
       <c r="C177" t="n">
-        <v>206.9883864105018</v>
+        <v>205.4301320010667</v>
       </c>
       <c r="D177" t="n">
-        <v>199.696542748819</v>
+        <v>199.3169621236104</v>
       </c>
       <c r="E177" t="n">
-        <v>200.1959838867188</v>
+        <v>204.6410064697266</v>
       </c>
       <c r="F177" t="n">
-        <v>161746600</v>
+        <v>158643200</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B178" t="n">
-        <v>201.2647947500858</v>
+        <v>204.6310298517525</v>
       </c>
       <c r="C178" t="n">
-        <v>205.4301320010667</v>
+        <v>206.8385664547524</v>
       </c>
       <c r="D178" t="n">
-        <v>199.3169621236104</v>
+        <v>203.2126188059985</v>
       </c>
       <c r="E178" t="n">
-        <v>204.6410064697266</v>
+        <v>204.9606628417969</v>
       </c>
       <c r="F178" t="n">
-        <v>158643200</v>
+        <v>112001800</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B179" t="n">
-        <v>204.6310298517525</v>
+        <v>208.6864864049894</v>
       </c>
       <c r="C179" t="n">
-        <v>206.8385664547524</v>
+        <v>212.4722588232193</v>
       </c>
       <c r="D179" t="n">
-        <v>203.2126188059985</v>
+        <v>208.1071328472061</v>
       </c>
       <c r="E179" t="n">
-        <v>204.9606628417969</v>
+        <v>212.2125396728516</v>
       </c>
       <c r="F179" t="n">
-        <v>112001800</v>
+        <v>149936700</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B180" t="n">
-        <v>208.6864864049894</v>
+        <v>210.9439520928381</v>
       </c>
       <c r="C180" t="n">
-        <v>212.4722588232193</v>
+        <v>211.2536184019877</v>
       </c>
       <c r="D180" t="n">
-        <v>208.1071328472061</v>
+        <v>207.0583006421773</v>
       </c>
       <c r="E180" t="n">
-        <v>212.2125396728516</v>
+        <v>207.1781768798828</v>
       </c>
       <c r="F180" t="n">
-        <v>149936700</v>
+        <v>125694100</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B181" t="n">
-        <v>210.9439520928381</v>
+        <v>208.2969174543329</v>
       </c>
       <c r="C181" t="n">
-        <v>211.2536184019877</v>
+        <v>208.9761653200819</v>
       </c>
       <c r="D181" t="n">
-        <v>207.0583006421773</v>
+        <v>202.8530121596522</v>
       </c>
       <c r="E181" t="n">
-        <v>207.1781768798828</v>
+        <v>204.4212493896484</v>
       </c>
       <c r="F181" t="n">
-        <v>125694100</v>
+        <v>128363500</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B182" t="n">
-        <v>208.2969174543329</v>
+        <v>207.0982684229139</v>
       </c>
       <c r="C182" t="n">
-        <v>208.9761653200819</v>
+        <v>211.1537281092123</v>
       </c>
       <c r="D182" t="n">
-        <v>202.8530121596522</v>
+        <v>206.2691942875683</v>
       </c>
       <c r="E182" t="n">
-        <v>204.4212493896484</v>
+        <v>210.4545135498047</v>
       </c>
       <c r="F182" t="n">
-        <v>128363500</v>
+        <v>241272000</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B183" t="n">
-        <v>207.0982684229139</v>
+        <v>211.2036686200953</v>
       </c>
       <c r="C183" t="n">
-        <v>211.1537281092123</v>
+        <v>213.7508214450341</v>
       </c>
       <c r="D183" t="n">
-        <v>206.2691942875683</v>
+        <v>207.4878253737282</v>
       </c>
       <c r="E183" t="n">
-        <v>210.4545135498047</v>
+        <v>208.4167785644531</v>
       </c>
       <c r="F183" t="n">
-        <v>241272000</v>
+        <v>122041400</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B184" t="n">
-        <v>211.2036686200953</v>
+        <v>201.9440304014853</v>
       </c>
       <c r="C184" t="n">
-        <v>213.7508214450341</v>
+        <v>203.5422481594977</v>
       </c>
       <c r="D184" t="n">
-        <v>207.4878253737282</v>
+        <v>199.77645766483</v>
       </c>
       <c r="E184" t="n">
-        <v>208.4167785644531</v>
+        <v>199.81640625</v>
       </c>
       <c r="F184" t="n">
-        <v>122041400</v>
+        <v>153496200</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B185" t="n">
-        <v>201.9440304014853</v>
+        <v>199.8963159019567</v>
       </c>
       <c r="C185" t="n">
-        <v>203.5422481594977</v>
+        <v>201.4445864758279</v>
       </c>
       <c r="D185" t="n">
-        <v>199.77645766483</v>
+        <v>196.360279356477</v>
       </c>
       <c r="E185" t="n">
-        <v>199.81640625</v>
+        <v>198.7775726318359</v>
       </c>
       <c r="F185" t="n">
-        <v>153496200</v>
+        <v>151810700</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B186" t="n">
-        <v>199.8963159019567</v>
+        <v>199.8563704571445</v>
       </c>
       <c r="C186" t="n">
-        <v>201.4445864758279</v>
+        <v>200.5755669254449</v>
       </c>
       <c r="D186" t="n">
-        <v>196.360279356477</v>
+        <v>191.9152592982058</v>
       </c>
       <c r="E186" t="n">
-        <v>198.7775726318359</v>
+        <v>195.5212249755859</v>
       </c>
       <c r="F186" t="n">
-        <v>151810700</v>
+        <v>149550000</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B187" t="n">
-        <v>199.8563704571445</v>
+        <v>192.9041409641119</v>
       </c>
       <c r="C187" t="n">
-        <v>200.5755669254449</v>
+        <v>195.331432829306</v>
       </c>
       <c r="D187" t="n">
-        <v>191.9152592982058</v>
+        <v>191.0062707295152</v>
       </c>
       <c r="E187" t="n">
-        <v>195.5212249755859</v>
+        <v>192.3148040771484</v>
       </c>
       <c r="F187" t="n">
-        <v>149550000</v>
+        <v>179304100</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B188" t="n">
-        <v>192.9041409641119</v>
+        <v>193.6333319429392</v>
       </c>
       <c r="C188" t="n">
-        <v>195.331432829306</v>
+        <v>195.9607141929515</v>
       </c>
       <c r="D188" t="n">
-        <v>191.0062707295152</v>
+        <v>189.5878557469149</v>
       </c>
       <c r="E188" t="n">
-        <v>192.3148040771484</v>
+        <v>194.7520751953125</v>
       </c>
       <c r="F188" t="n">
-        <v>179304100</v>
+        <v>148835700</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B189" t="n">
-        <v>193.6333319429392</v>
+        <v>197.0195429632178</v>
       </c>
       <c r="C189" t="n">
-        <v>195.9607141929515</v>
+        <v>200.4057532237791</v>
       </c>
       <c r="D189" t="n">
-        <v>189.5878557469149</v>
+        <v>194.8919188665145</v>
       </c>
       <c r="E189" t="n">
-        <v>194.7520751953125</v>
+        <v>199.8663482666016</v>
       </c>
       <c r="F189" t="n">
-        <v>148835700</v>
+        <v>166476700</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B190" t="n">
-        <v>197.0195429632178</v>
+        <v>195.9806989625188</v>
       </c>
       <c r="C190" t="n">
-        <v>200.4057532237791</v>
+        <v>199.626628404907</v>
       </c>
       <c r="D190" t="n">
-        <v>194.8919188665145</v>
+        <v>193.2337727110923</v>
       </c>
       <c r="E190" t="n">
-        <v>199.8663482666016</v>
+        <v>197.3591613769531</v>
       </c>
       <c r="F190" t="n">
-        <v>166476700</v>
+        <v>146147600</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B191" t="n">
-        <v>195.9806989625188</v>
+        <v>196.9196593659626</v>
       </c>
       <c r="C191" t="n">
-        <v>199.626628404907</v>
+        <v>199.8363939026278</v>
       </c>
       <c r="D191" t="n">
-        <v>193.2337727110923</v>
+        <v>192.1350197738411</v>
       </c>
       <c r="E191" t="n">
-        <v>197.3591613769531</v>
+        <v>194.6122436523438</v>
       </c>
       <c r="F191" t="n">
-        <v>146147600</v>
+        <v>142068700</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B192" t="n">
-        <v>196.9196593659626</v>
+        <v>194.202694284663</v>
       </c>
       <c r="C192" t="n">
-        <v>199.8363939026278</v>
+        <v>197.3292007505161</v>
       </c>
       <c r="D192" t="n">
-        <v>192.1350197738411</v>
+        <v>193.7731822131383</v>
       </c>
       <c r="E192" t="n">
-        <v>194.6122436523438</v>
+        <v>195.3314361572266</v>
       </c>
       <c r="F192" t="n">
-        <v>142068700</v>
+        <v>108999000</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B193" t="n">
-        <v>194.202694284663</v>
+        <v>192.1549837798622</v>
       </c>
       <c r="C193" t="n">
-        <v>197.3292007505161</v>
+        <v>198.1882414262674</v>
       </c>
       <c r="D193" t="n">
-        <v>193.7731822131383</v>
+        <v>190.9263628146717</v>
       </c>
       <c r="E193" t="n">
-        <v>195.3314361572266</v>
+        <v>196.7098846435547</v>
       </c>
       <c r="F193" t="n">
-        <v>108999000</v>
+        <v>124154600</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B194" t="n">
-        <v>192.1549837798622</v>
+        <v>194.9618356993413</v>
       </c>
       <c r="C194" t="n">
-        <v>198.1882414262674</v>
+        <v>204.9306918075912</v>
       </c>
       <c r="D194" t="n">
-        <v>190.9263628146717</v>
+        <v>194.841974703339</v>
       </c>
       <c r="E194" t="n">
-        <v>196.7098846435547</v>
+        <v>203.891845703125</v>
       </c>
       <c r="F194" t="n">
-        <v>124154600</v>
+        <v>147419100</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B195" t="n">
-        <v>194.9618356993413</v>
+        <v>204.2314748595287</v>
       </c>
       <c r="C195" t="n">
-        <v>204.9306918075912</v>
+        <v>204.3613191897594</v>
       </c>
       <c r="D195" t="n">
-        <v>194.841974703339</v>
+        <v>198.7376223952696</v>
       </c>
       <c r="E195" t="n">
-        <v>203.891845703125</v>
+        <v>202.5533447265625</v>
       </c>
       <c r="F195" t="n">
-        <v>147419100</v>
+        <v>132037400</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B196" t="n">
-        <v>204.2314748595287</v>
+        <v>201.7742207048944</v>
       </c>
       <c r="C196" t="n">
-        <v>204.3613191897594</v>
+        <v>210.7641612313501</v>
       </c>
       <c r="D196" t="n">
-        <v>198.7376223952696</v>
+        <v>201.6943082934289</v>
       </c>
       <c r="E196" t="n">
-        <v>202.5533447265625</v>
+        <v>210.7242126464844</v>
       </c>
       <c r="F196" t="n">
-        <v>132037400</v>
+        <v>148421000</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B197" t="n">
-        <v>201.7742207048944</v>
+        <v>208.3069001369788</v>
       </c>
       <c r="C197" t="n">
-        <v>210.7641612313501</v>
+        <v>210.3346451505122</v>
       </c>
       <c r="D197" t="n">
-        <v>201.6943082934289</v>
+        <v>202.7730991138312</v>
       </c>
       <c r="E197" t="n">
-        <v>210.7242126464844</v>
+        <v>203.3025054931641</v>
       </c>
       <c r="F197" t="n">
-        <v>148421000</v>
+        <v>121411000</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B198" t="n">
-        <v>208.3069001369788</v>
+        <v>207.9672957533915</v>
       </c>
       <c r="C198" t="n">
-        <v>210.3346451505122</v>
+        <v>212.3124399374416</v>
       </c>
       <c r="D198" t="n">
-        <v>202.7730991138312</v>
+        <v>203.5722196467825</v>
       </c>
       <c r="E198" t="n">
-        <v>203.3025054931641</v>
+        <v>211.5632781982422</v>
       </c>
       <c r="F198" t="n">
-        <v>121411000</v>
+        <v>124379600</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B199" t="n">
-        <v>207.9672957533915</v>
+        <v>211.7230919717581</v>
       </c>
       <c r="C199" t="n">
-        <v>212.3124399374416</v>
+        <v>213.5710150202495</v>
       </c>
       <c r="D199" t="n">
-        <v>203.5722196467825</v>
+        <v>205.8096955397309</v>
       </c>
       <c r="E199" t="n">
-        <v>211.5632781982422</v>
+        <v>212.2624816894531</v>
       </c>
       <c r="F199" t="n">
-        <v>124379600</v>
+        <v>124797200</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B200" t="n">
-        <v>211.7230919717581</v>
+        <v>209.9350906043833</v>
       </c>
       <c r="C200" t="n">
-        <v>213.5710150202495</v>
+        <v>210.8440771529852</v>
       </c>
       <c r="D200" t="n">
-        <v>205.8096955397309</v>
+        <v>205.6199270055466</v>
       </c>
       <c r="E200" t="n">
-        <v>212.2624816894531</v>
+        <v>207.1681823730469</v>
       </c>
       <c r="F200" t="n">
-        <v>124797200</v>
+        <v>122986100</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B201" t="n">
-        <v>209.9350906043833</v>
+        <v>202.4135048295048</v>
       </c>
       <c r="C201" t="n">
-        <v>210.8440771529852</v>
+        <v>206.4190172896336</v>
       </c>
       <c r="D201" t="n">
-        <v>205.6199270055466</v>
+        <v>197.7487264058434</v>
       </c>
       <c r="E201" t="n">
-        <v>207.1681823730469</v>
+        <v>202.5833129882812</v>
       </c>
       <c r="F201" t="n">
-        <v>122986100</v>
+        <v>144281900</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B202" t="n">
-        <v>202.4135048295048</v>
+        <v>205.639896943356</v>
       </c>
       <c r="C202" t="n">
-        <v>206.4190172896336</v>
+        <v>207.5078172334397</v>
       </c>
       <c r="D202" t="n">
-        <v>197.7487264058434</v>
+        <v>202.0539130969454</v>
       </c>
       <c r="E202" t="n">
-        <v>202.5833129882812</v>
+        <v>203.0527954101562</v>
       </c>
       <c r="F202" t="n">
-        <v>144281900</v>
+        <v>88701500</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B203" t="n">
-        <v>205.639896943356</v>
+        <v>207.308024406286</v>
       </c>
       <c r="C203" t="n">
-        <v>207.5078172334397</v>
+        <v>208.4167843613107</v>
       </c>
       <c r="D203" t="n">
-        <v>202.0539130969454</v>
+        <v>203.7819711309363</v>
       </c>
       <c r="E203" t="n">
-        <v>203.0527954101562</v>
+        <v>207.0583038330078</v>
       </c>
       <c r="F203" t="n">
-        <v>88701500</v>
+        <v>108685600</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B204" t="n">
-        <v>207.308024406286</v>
+        <v>205.579968274895</v>
       </c>
       <c r="C204" t="n">
-        <v>208.4167843613107</v>
+        <v>214.1503804276117</v>
       </c>
       <c r="D204" t="n">
-        <v>203.7819711309363</v>
+        <v>204.7209288682105</v>
       </c>
       <c r="E204" t="n">
-        <v>207.0583038330078</v>
+        <v>211.8229827880859</v>
       </c>
       <c r="F204" t="n">
-        <v>108685600</v>
+        <v>137645600</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B205" t="n">
-        <v>205.579968274895</v>
+        <v>209.2258868865651</v>
       </c>
       <c r="C205" t="n">
-        <v>214.1503804276117</v>
+        <v>210.6342993029147</v>
       </c>
       <c r="D205" t="n">
-        <v>204.7209288682105</v>
+        <v>205.7297989431358</v>
       </c>
       <c r="E205" t="n">
-        <v>211.8229827880859</v>
+        <v>208.5266571044922</v>
       </c>
       <c r="F205" t="n">
-        <v>137645600</v>
+        <v>110505300</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B206" t="n">
-        <v>209.2258868865651</v>
+        <v>207.2181292349697</v>
       </c>
       <c r="C206" t="n">
-        <v>210.6342993029147</v>
+        <v>211.6731509810223</v>
       </c>
       <c r="D206" t="n">
-        <v>205.7297989431358</v>
+        <v>204.5810805834776</v>
       </c>
       <c r="E206" t="n">
-        <v>208.5266571044922</v>
+        <v>206.6088104248047</v>
       </c>
       <c r="F206" t="n">
-        <v>110505300</v>
+        <v>114836800</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B207" t="n">
-        <v>207.2181292349697</v>
+        <v>207.9672962732577</v>
       </c>
       <c r="C207" t="n">
-        <v>211.6731509810223</v>
+        <v>208.5166845983908</v>
       </c>
       <c r="D207" t="n">
-        <v>204.5810805834776</v>
+        <v>195.2215633388429</v>
       </c>
       <c r="E207" t="n">
-        <v>206.6088104248047</v>
+        <v>196.2903594970703</v>
       </c>
       <c r="F207" t="n">
-        <v>114836800</v>
+        <v>154353700</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B208" t="n">
-        <v>207.9672962732577</v>
+        <v>194.782047001347</v>
       </c>
       <c r="C208" t="n">
-        <v>208.5166845983908</v>
+        <v>198.4779084345641</v>
       </c>
       <c r="D208" t="n">
-        <v>195.2215633388429</v>
+        <v>192.5245785077403</v>
       </c>
       <c r="E208" t="n">
-        <v>196.2903594970703</v>
+        <v>196.789794921875</v>
       </c>
       <c r="F208" t="n">
-        <v>154353700</v>
+        <v>134111500</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B209" t="n">
-        <v>194.782047001347</v>
+        <v>195.6311069684468</v>
       </c>
       <c r="C209" t="n">
-        <v>198.4779084345641</v>
+        <v>196.8497446088402</v>
       </c>
       <c r="D209" t="n">
-        <v>192.5245785077403</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="E209" t="n">
-        <v>196.789794921875</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="F209" t="n">
-        <v>134111500</v>
+        <v>147680800</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B210" t="n">
-        <v>195.6311069684468</v>
+        <v>193.2337718176948</v>
       </c>
       <c r="C210" t="n">
-        <v>196.8497446088402</v>
+        <v>197.0295274868271</v>
       </c>
       <c r="D210" t="n">
-        <v>189.7976226806641</v>
+        <v>191.3059363552755</v>
       </c>
       <c r="E210" t="n">
-        <v>189.7976226806641</v>
+        <v>194.8219909667969</v>
       </c>
       <c r="F210" t="n">
-        <v>147680800</v>
+        <v>129010200</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B211" t="n">
-        <v>193.2337718176948</v>
+        <v>198.2182038580375</v>
       </c>
       <c r="C211" t="n">
-        <v>197.0295274868271</v>
+        <v>201.7742223680242</v>
       </c>
       <c r="D211" t="n">
-        <v>191.3059363552755</v>
+        <v>194.7320991825756</v>
       </c>
       <c r="E211" t="n">
-        <v>194.8219909667969</v>
+        <v>200.5256195068359</v>
       </c>
       <c r="F211" t="n">
-        <v>129010200</v>
+        <v>139961200</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B212" t="n">
-        <v>198.2182038580375</v>
+        <v>197.4690486270115</v>
       </c>
       <c r="C212" t="n">
-        <v>201.7742223680242</v>
+        <v>208.506701330784</v>
       </c>
       <c r="D212" t="n">
-        <v>194.7320991825756</v>
+        <v>196.6299911347511</v>
       </c>
       <c r="E212" t="n">
-        <v>200.5256195068359</v>
+        <v>206.4090423583984</v>
       </c>
       <c r="F212" t="n">
-        <v>139961200</v>
+        <v>128406900</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B213" t="n">
-        <v>197.4690486270115</v>
+        <v>211.0638257011038</v>
       </c>
       <c r="C213" t="n">
-        <v>208.506701330784</v>
+        <v>212.8218530009649</v>
       </c>
       <c r="D213" t="n">
-        <v>196.6299911347511</v>
+        <v>208.8163406042335</v>
       </c>
       <c r="E213" t="n">
-        <v>206.4090423583984</v>
+        <v>211.7031097412109</v>
       </c>
       <c r="F213" t="n">
-        <v>128406900</v>
+        <v>134922000</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B214" t="n">
-        <v>211.0638257011038</v>
+        <v>216.6176127852948</v>
       </c>
       <c r="C214" t="n">
-        <v>212.8218530009649</v>
+        <v>221.9716224388697</v>
       </c>
       <c r="D214" t="n">
-        <v>208.8163406042335</v>
+        <v>216.1581202281489</v>
       </c>
       <c r="E214" t="n">
-        <v>211.7031097412109</v>
+        <v>218.9749755859375</v>
       </c>
       <c r="F214" t="n">
-        <v>134922000</v>
+        <v>158187400</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B215" t="n">
-        <v>216.6176127852948</v>
+        <v>221.2823935806188</v>
       </c>
       <c r="C215" t="n">
-        <v>221.9716224388697</v>
+        <v>223.3800524967045</v>
       </c>
       <c r="D215" t="n">
-        <v>216.1581202281489</v>
+        <v>216.7574580038405</v>
       </c>
       <c r="E215" t="n">
-        <v>218.9749755859375</v>
+        <v>218.7452392578125</v>
       </c>
       <c r="F215" t="n">
-        <v>158187400</v>
+        <v>113940600</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B216" t="n">
-        <v>221.2823935806188</v>
+        <v>221.2923777041913</v>
       </c>
       <c r="C216" t="n">
-        <v>223.3800524967045</v>
+        <v>224.5087799247126</v>
       </c>
       <c r="D216" t="n">
-        <v>216.7574580038405</v>
+        <v>220.4133716458871</v>
       </c>
       <c r="E216" t="n">
-        <v>218.7452392578125</v>
+        <v>223.7096862792969</v>
       </c>
       <c r="F216" t="n">
-        <v>113940600</v>
+        <v>105669400</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B217" t="n">
-        <v>221.2923777041913</v>
+        <v>223.1502910726907</v>
       </c>
       <c r="C217" t="n">
-        <v>224.5087799247126</v>
+        <v>223.8894694330602</v>
       </c>
       <c r="D217" t="n">
-        <v>220.4133716458871</v>
+        <v>216.5277120448001</v>
       </c>
       <c r="E217" t="n">
-        <v>223.7096862792969</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="F217" t="n">
-        <v>105669400</v>
+        <v>115846600</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B218" t="n">
-        <v>223.1502910726907</v>
+        <v>221.9216754142795</v>
       </c>
       <c r="C218" t="n">
-        <v>223.8894694330602</v>
+        <v>221.9516406634887</v>
       </c>
       <c r="D218" t="n">
-        <v>216.5277120448001</v>
+        <v>215.9583469538982</v>
       </c>
       <c r="E218" t="n">
-        <v>217.3068389892578</v>
+        <v>217.2568969726562</v>
       </c>
       <c r="F218" t="n">
-        <v>115846600</v>
+        <v>101273100</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B219" t="n">
-        <v>221.9216754142795</v>
+        <v>220.7929293559802</v>
       </c>
       <c r="C219" t="n">
-        <v>221.9516406634887</v>
+        <v>224.848404158734</v>
       </c>
       <c r="D219" t="n">
-        <v>215.9583469538982</v>
+        <v>219.9538719106106</v>
       </c>
       <c r="E219" t="n">
-        <v>217.2568969726562</v>
+        <v>223.8395233154297</v>
       </c>
       <c r="F219" t="n">
-        <v>101273100</v>
+        <v>108783600</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B220" t="n">
-        <v>220.7929293559802</v>
+        <v>224.8084500146858</v>
       </c>
       <c r="C220" t="n">
-        <v>224.848404158734</v>
+        <v>226.9760227961096</v>
       </c>
       <c r="D220" t="n">
-        <v>219.9538719106106</v>
+        <v>223.4599680426375</v>
       </c>
       <c r="E220" t="n">
-        <v>223.8395233154297</v>
+        <v>225.0481872558594</v>
       </c>
       <c r="F220" t="n">
-        <v>108783600</v>
+        <v>98867200</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B221" t="n">
-        <v>224.8084500146858</v>
+        <v>226.5165415533859</v>
       </c>
       <c r="C221" t="n">
-        <v>226.9760227961096</v>
+        <v>227.2357380227387</v>
       </c>
       <c r="D221" t="n">
-        <v>223.4599680426375</v>
+        <v>224.2490744835724</v>
       </c>
       <c r="E221" t="n">
-        <v>225.0481872558594</v>
+        <v>224.9083404541016</v>
       </c>
       <c r="F221" t="n">
-        <v>98867200</v>
+        <v>75680900</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B222" t="n">
-        <v>226.5165415533859</v>
+        <v>225.7274161885591</v>
       </c>
       <c r="C222" t="n">
-        <v>227.2357380227387</v>
+        <v>227.6652502746616</v>
       </c>
       <c r="D222" t="n">
-        <v>224.2490744835724</v>
+        <v>224.6086728983284</v>
       </c>
       <c r="E222" t="n">
-        <v>224.9083404541016</v>
+        <v>224.7584991455078</v>
       </c>
       <c r="F222" t="n">
-        <v>75680900</v>
+        <v>93678700</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B223" t="n">
-        <v>225.7274161885591</v>
+        <v>220.203597915372</v>
       </c>
       <c r="C223" t="n">
-        <v>227.6652502746616</v>
+        <v>221.3922702798686</v>
       </c>
       <c r="D223" t="n">
-        <v>224.6086728983284</v>
+        <v>218.4455705709327</v>
       </c>
       <c r="E223" t="n">
-        <v>224.7584991455078</v>
+        <v>219.4944000244141</v>
       </c>
       <c r="F223" t="n">
-        <v>93678700</v>
+        <v>103128200</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B224" t="n">
-        <v>220.203597915372</v>
+        <v>221.4222404106533</v>
       </c>
       <c r="C224" t="n">
-        <v>221.3922702798686</v>
+        <v>222.6208961374568</v>
       </c>
       <c r="D224" t="n">
-        <v>218.4455705709327</v>
+        <v>216.5177245976465</v>
       </c>
       <c r="E224" t="n">
-        <v>219.4944000244141</v>
+        <v>217.3168334960938</v>
       </c>
       <c r="F224" t="n">
-        <v>103128200</v>
+        <v>96797300</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B225" t="n">
-        <v>221.4222404106533</v>
+        <v>218.1159423024499</v>
       </c>
       <c r="C225" t="n">
-        <v>222.6208961374568</v>
+        <v>219.6142657707553</v>
       </c>
       <c r="D225" t="n">
-        <v>216.5177245976465</v>
+        <v>215.418963107847</v>
       </c>
       <c r="E225" t="n">
-        <v>217.3168334960938</v>
+        <v>216.6076354980469</v>
       </c>
       <c r="F225" t="n">
-        <v>96797300</v>
+        <v>92457000</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B226" t="n">
-        <v>218.1159423024499</v>
+        <v>218.1758724878036</v>
       </c>
       <c r="C226" t="n">
-        <v>219.6142657707553</v>
+        <v>218.4955221432803</v>
       </c>
       <c r="D226" t="n">
-        <v>215.418963107847</v>
+        <v>214.2602556586216</v>
       </c>
       <c r="E226" t="n">
-        <v>216.6076354980469</v>
+        <v>214.4800109863281</v>
       </c>
       <c r="F226" t="n">
-        <v>92457000</v>
+        <v>98869300</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B227" t="n">
-        <v>218.1758724878036</v>
+        <v>215.2891020611033</v>
       </c>
       <c r="C227" t="n">
-        <v>218.4955221432803</v>
+        <v>215.3490325607492</v>
       </c>
       <c r="D227" t="n">
-        <v>214.2602556586216</v>
+        <v>207.0183577918231</v>
       </c>
       <c r="E227" t="n">
-        <v>214.4800109863281</v>
+        <v>208.2469787597656</v>
       </c>
       <c r="F227" t="n">
-        <v>98869300</v>
+        <v>135187300</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B228" t="n">
-        <v>215.2891020611033</v>
+        <v>210.7941279013131</v>
       </c>
       <c r="C228" t="n">
-        <v>215.3490325607492</v>
+        <v>214.4899893165327</v>
       </c>
       <c r="D228" t="n">
-        <v>207.0183577918231</v>
+        <v>209.8751580258669</v>
       </c>
       <c r="E228" t="n">
-        <v>208.2469787597656</v>
+        <v>212.8118743896484</v>
       </c>
       <c r="F228" t="n">
-        <v>135187300</v>
+        <v>122309000</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B229" t="n">
-        <v>210.7941279013131</v>
+        <v>212.4023240594531</v>
       </c>
       <c r="C229" t="n">
-        <v>214.4899893165327</v>
+        <v>213.3612577394914</v>
       </c>
       <c r="D229" t="n">
-        <v>209.8751580258669</v>
+        <v>208.9961318803605</v>
       </c>
       <c r="E229" t="n">
-        <v>212.8118743896484</v>
+        <v>209.4256591796875</v>
       </c>
       <c r="F229" t="n">
-        <v>122309000</v>
+        <v>179900000</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B230" t="n">
-        <v>212.4023240594531</v>
+        <v>222.6109016432552</v>
       </c>
       <c r="C230" t="n">
-        <v>213.3612577394914</v>
+        <v>230.2123962709879</v>
       </c>
       <c r="D230" t="n">
-        <v>208.9961318803605</v>
+        <v>220.6530857022795</v>
       </c>
       <c r="E230" t="n">
-        <v>209.4256591796875</v>
+        <v>227.7251739501953</v>
       </c>
       <c r="F230" t="n">
-        <v>179900000</v>
+        <v>298909800</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B231" t="n">
-        <v>222.6109016432552</v>
+        <v>227.1058715337123</v>
       </c>
       <c r="C231" t="n">
-        <v>230.2123962709879</v>
+        <v>229.003741733446</v>
       </c>
       <c r="D231" t="n">
-        <v>220.6530857022795</v>
+        <v>216.5676606288883</v>
       </c>
       <c r="E231" t="n">
-        <v>227.7251739501953</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="F231" t="n">
-        <v>298909800</v>
+        <v>195116400</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B232" t="n">
-        <v>227.1058715337123</v>
+        <v>218.6253647857836</v>
       </c>
       <c r="C232" t="n">
-        <v>229.003741733446</v>
+        <v>221.0526567078369</v>
       </c>
       <c r="D232" t="n">
-        <v>216.5676606288883</v>
+        <v>215.9683494434545</v>
       </c>
       <c r="E232" t="n">
-        <v>217.3068389892578</v>
+        <v>220.5332336425781</v>
       </c>
       <c r="F232" t="n">
-        <v>195116400</v>
+        <v>124702700</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B233" t="n">
-        <v>218.6253647857836</v>
+        <v>216.5077444634259</v>
       </c>
       <c r="C233" t="n">
-        <v>221.0526567078369</v>
+        <v>220.1636574397174</v>
       </c>
       <c r="D233" t="n">
-        <v>215.9683494434545</v>
+        <v>214.8595947199138</v>
       </c>
       <c r="E233" t="n">
-        <v>220.5332336425781</v>
+        <v>217.1969757080078</v>
       </c>
       <c r="F233" t="n">
-        <v>124702700</v>
+        <v>109756200</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B234" t="n">
-        <v>216.5077444634259</v>
+        <v>218.5454508199983</v>
       </c>
       <c r="C234" t="n">
-        <v>220.1636574397174</v>
+        <v>227.6952163087265</v>
       </c>
       <c r="D234" t="n">
-        <v>214.8595947199138</v>
+        <v>218.2357997469377</v>
       </c>
       <c r="E234" t="n">
-        <v>217.1969757080078</v>
+        <v>224.1591796875</v>
       </c>
       <c r="F234" t="n">
-        <v>109756200</v>
+        <v>157104700</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B235" t="n">
-        <v>218.5454508199983</v>
+        <v>225.7673797205316</v>
       </c>
       <c r="C235" t="n">
-        <v>227.6952163087265</v>
+        <v>230.1424737915274</v>
       </c>
       <c r="D235" t="n">
-        <v>218.2357997469377</v>
+        <v>224.4987949430455</v>
       </c>
       <c r="E235" t="n">
-        <v>224.1591796875</v>
+        <v>228.1946563720703</v>
       </c>
       <c r="F235" t="n">
-        <v>157104700</v>
+        <v>134681600</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B236" t="n">
-        <v>225.7673797205316</v>
+        <v>230.8317036041433</v>
       </c>
       <c r="C236" t="n">
-        <v>230.1424737915274</v>
+        <v>234.4975997614268</v>
       </c>
       <c r="D236" t="n">
-        <v>224.4987949430455</v>
+        <v>229.3733440032785</v>
       </c>
       <c r="E236" t="n">
-        <v>228.1946563720703</v>
+        <v>230.1025238037109</v>
       </c>
       <c r="F236" t="n">
-        <v>134681600</v>
+        <v>135352400</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B237" t="n">
-        <v>230.8317036041433</v>
+        <v>232.8494477166676</v>
       </c>
       <c r="C237" t="n">
-        <v>234.4975997614268</v>
+        <v>233.4487831783142</v>
       </c>
       <c r="D237" t="n">
-        <v>229.3733440032785</v>
+        <v>224.5986856128386</v>
       </c>
       <c r="E237" t="n">
-        <v>230.1025238037109</v>
+        <v>225.4776916503906</v>
       </c>
       <c r="F237" t="n">
-        <v>135352400</v>
+        <v>122965600</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B238" t="n">
-        <v>232.8494477166676</v>
+        <v>225.0281992525124</v>
       </c>
       <c r="C238" t="n">
-        <v>233.4487831783142</v>
+        <v>225.9271872095504</v>
       </c>
       <c r="D238" t="n">
-        <v>224.5986856128386</v>
+        <v>223.2102414251123</v>
       </c>
       <c r="E238" t="n">
-        <v>225.4776916503906</v>
+        <v>223.4199981689453</v>
       </c>
       <c r="F238" t="n">
-        <v>122965600</v>
+        <v>82955500</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,25 +6631,25 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B239" t="n">
-        <v>225.0281992525124</v>
+        <v>220.5299987792969</v>
       </c>
       <c r="C239" t="n">
-        <v>225.9271872095504</v>
+        <v>220.9900054931641</v>
       </c>
       <c r="D239" t="n">
-        <v>223.2102414251123</v>
+        <v>217.1999969482422</v>
       </c>
       <c r="E239" t="n">
-        <v>223.4199981689453</v>
+        <v>218.3600006103516</v>
       </c>
       <c r="F239" t="n">
-        <v>82955500</v>
+        <v>105768000</v>
       </c>
       <c r="G239" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -6657,25 +6657,25 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B240" t="n">
-        <v>220.5299987792969</v>
+        <v>221.2400054931641</v>
       </c>
       <c r="C240" t="n">
-        <v>220.9900054931641</v>
+        <v>222</v>
       </c>
       <c r="D240" t="n">
-        <v>217.1999969482422</v>
+        <v>218.1499938964844</v>
       </c>
       <c r="E240" t="n">
-        <v>218.3600006103516</v>
+        <v>218.2899932861328</v>
       </c>
       <c r="F240" t="n">
-        <v>105768000</v>
+        <v>89060100</v>
       </c>
       <c r="G240" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B241" t="n">
-        <v>221.2400054931641</v>
+        <v>211.2400054931641</v>
       </c>
       <c r="C241" t="n">
-        <v>222</v>
+        <v>212.7700042724609</v>
       </c>
       <c r="D241" t="n">
-        <v>218.1499938964844</v>
+        <v>208.9299926757812</v>
       </c>
       <c r="E241" t="n">
-        <v>218.2899932861328</v>
+        <v>210.9600067138672</v>
       </c>
       <c r="F241" t="n">
-        <v>89060100</v>
+        <v>132267200</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B242" t="n">
-        <v>211.2400054931641</v>
+        <v>213.3800048828125</v>
       </c>
       <c r="C242" t="n">
-        <v>212.7700042724609</v>
+        <v>213.9400024414062</v>
       </c>
       <c r="D242" t="n">
-        <v>208.9299926757812</v>
+        <v>211.1600036621094</v>
       </c>
       <c r="E242" t="n">
-        <v>210.9600067138672</v>
+        <v>212.1699981689453</v>
       </c>
       <c r="F242" t="n">
-        <v>132267200</v>
+        <v>88059700</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B243" t="n">
-        <v>213.3800048828125</v>
+        <v>214.1399993896484</v>
       </c>
       <c r="C243" t="n">
-        <v>213.9400024414062</v>
+        <v>216.7599945068359</v>
       </c>
       <c r="D243" t="n">
-        <v>211.1600036621094</v>
+        <v>212.5</v>
       </c>
       <c r="E243" t="n">
-        <v>212.1699981689453</v>
+        <v>213.8999938964844</v>
       </c>
       <c r="F243" t="n">
-        <v>88059700</v>
+        <v>96563600</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B244" t="n">
-        <v>214.1399993896484</v>
+        <v>218.3800048828125</v>
       </c>
       <c r="C244" t="n">
-        <v>216.7599945068359</v>
+        <v>219.9100036621094</v>
       </c>
       <c r="D244" t="n">
-        <v>212.5</v>
+        <v>217.1499938964844</v>
       </c>
       <c r="E244" t="n">
-        <v>213.8999938964844</v>
+        <v>219.3399963378906</v>
       </c>
       <c r="F244" t="n">
-        <v>96563600</v>
+        <v>94191300</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B245" t="n">
-        <v>218.3800048828125</v>
+        <v>219.3500061035156</v>
       </c>
       <c r="C245" t="n">
-        <v>219.9100036621094</v>
+        <v>222.7299957275391</v>
       </c>
       <c r="D245" t="n">
-        <v>217.1499938964844</v>
+        <v>218.0299987792969</v>
       </c>
       <c r="E245" t="n">
-        <v>219.3399963378906</v>
+        <v>222.2700042724609</v>
       </c>
       <c r="F245" t="n">
-        <v>94191300</v>
+        <v>190287400</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B246" t="n">
-        <v>219.3500061035156</v>
+        <v>222.9400024414062</v>
       </c>
       <c r="C246" t="n">
-        <v>222.7299957275391</v>
+        <v>228.5</v>
       </c>
       <c r="D246" t="n">
-        <v>218.0299987792969</v>
+        <v>221.5599975585938</v>
       </c>
       <c r="E246" t="n">
-        <v>222.2700042724609</v>
+        <v>227.3800048828125</v>
       </c>
       <c r="F246" t="n">
-        <v>190287400</v>
+        <v>109806100</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B247" t="n">
-        <v>222.9400024414062</v>
+        <v>226.8500061035156</v>
       </c>
       <c r="C247" t="n">
-        <v>228.5</v>
+        <v>229.9799957275391</v>
       </c>
       <c r="D247" t="n">
-        <v>221.5599975585938</v>
+        <v>226.5</v>
       </c>
       <c r="E247" t="n">
-        <v>227.3800048828125</v>
+        <v>228.8699951171875</v>
       </c>
       <c r="F247" t="n">
-        <v>109806100</v>
+        <v>95746700</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B248" t="n">
-        <v>226.8500061035156</v>
+        <v>228.0299987792969</v>
       </c>
       <c r="C248" t="n">
-        <v>229.9799957275391</v>
+        <v>228.9499969482422</v>
       </c>
       <c r="D248" t="n">
-        <v>226.5</v>
+        <v>224.0200042724609</v>
       </c>
       <c r="E248" t="n">
-        <v>228.8699951171875</v>
+        <v>225.5099945068359</v>
       </c>
       <c r="F248" t="n">
-        <v>95746700</v>
+        <v>89547300</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B249" t="n">
-        <v>228.0299987792969</v>
+        <v>222.0800018310547</v>
       </c>
       <c r="C249" t="n">
-        <v>228.9499969482422</v>
+        <v>224.9400024414062</v>
       </c>
       <c r="D249" t="n">
-        <v>224.0200042724609</v>
+        <v>221.0899963378906</v>
       </c>
       <c r="E249" t="n">
-        <v>225.5099945068359</v>
+        <v>224.5800018310547</v>
       </c>
       <c r="F249" t="n">
-        <v>89547300</v>
+        <v>77469900</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B250" t="n">
-        <v>222.0800018310547</v>
+        <v>225.1300048828125</v>
       </c>
       <c r="C250" t="n">
-        <v>224.9400024414062</v>
+        <v>226.9400024414062</v>
       </c>
       <c r="D250" t="n">
-        <v>221.0899963378906</v>
+        <v>223.1300048828125</v>
       </c>
       <c r="E250" t="n">
-        <v>224.5800018310547</v>
+        <v>225.0700073242188</v>
       </c>
       <c r="F250" t="n">
-        <v>77469900</v>
+        <v>89947700</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B251" t="n">
-        <v>225.1300048828125</v>
+        <v>229.75</v>
       </c>
       <c r="C251" t="n">
-        <v>226.9400024414062</v>
+        <v>233.2100067138672</v>
       </c>
       <c r="D251" t="n">
-        <v>223.1300048828125</v>
+        <v>228.0399932861328</v>
       </c>
       <c r="E251" t="n">
-        <v>225.0700073242188</v>
+        <v>228.8600006103516</v>
       </c>
       <c r="F251" t="n">
-        <v>89947700</v>
+        <v>142344300</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B252" t="n">
-        <v>229.75</v>
+        <v>230.9700012207031</v>
       </c>
       <c r="C252" t="n">
-        <v>233.2100067138672</v>
+        <v>232.8200073242188</v>
       </c>
       <c r="D252" t="n">
-        <v>228.0399932861328</v>
+        <v>227.0299987792969</v>
       </c>
       <c r="E252" t="n">
-        <v>228.8600006103516</v>
+        <v>227.2100067138672</v>
       </c>
       <c r="F252" t="n">
-        <v>141544300</v>
+        <v>101203000</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10884,37 +10884,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>227.21</v>
+      </c>
+      <c r="D2" t="n">
         <v>228.86</v>
       </c>
-      <c r="D2" t="n">
-        <v>225.07</v>
-      </c>
       <c r="E2" t="n">
-        <v>229.7</v>
+        <v>230.995</v>
       </c>
       <c r="F2" t="n">
-        <v>233.21</v>
+        <v>232.82</v>
       </c>
       <c r="G2" t="n">
-        <v>228.04</v>
+        <v>227.025</v>
       </c>
       <c r="H2" t="n">
-        <v>141276939</v>
+        <v>98224511</v>
       </c>
       <c r="I2" t="n">
-        <v>124520330</v>
+        <v>123496938</v>
       </c>
       <c r="J2" t="n">
-        <v>5526282305536</v>
+        <v>5486440087552</v>
       </c>
       <c r="K2" t="n">
-        <v>28.500624</v>
+        <v>28.907125</v>
       </c>
       <c r="L2" t="n">
-        <v>14.593216</v>
+        <v>14.488005</v>
       </c>
       <c r="M2" t="n">
-        <v>8.029999999999999</v>
+        <v>7.86</v>
       </c>
       <c r="N2" t="n">
         <v>236.54</v>
@@ -10950,7 +10950,7 @@
         <v>9.483000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>24.133713</v>
+        <v>23.959719</v>
       </c>
       <c r="Z2" t="n">
         <v>1.278</v>
@@ -10962,7 +10962,7 @@
         <v>302970011648</v>
       </c>
       <c r="AC2" t="n">
-        <v>5491916800000</v>
+        <v>5452152176640</v>
       </c>
       <c r="AD2" t="n">
         <v>201266003968</v>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:24:35</t>
+          <t>2026-09-30 16:07:01</t>
         </is>
       </c>
     </row>

--- a/data/NVDA_data.xlsx
+++ b/data/NVDA_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B2" t="n">
-        <v>181.6448190078555</v>
+        <v>184.7972757932568</v>
       </c>
       <c r="C2" t="n">
-        <v>186.9022276338177</v>
+        <v>187.690338609038</v>
       </c>
       <c r="D2" t="n">
-        <v>181.0462469572146</v>
+        <v>183.4604668683245</v>
       </c>
       <c r="E2" t="n">
-        <v>186.1340637207031</v>
+        <v>186.7924957275391</v>
       </c>
       <c r="F2" t="n">
-        <v>236981000</v>
+        <v>173844900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B3" t="n">
-        <v>184.7972606974542</v>
+        <v>189.146847340247</v>
       </c>
       <c r="C3" t="n">
-        <v>187.6903232769056</v>
+        <v>190.59337868299</v>
       </c>
       <c r="D3" t="n">
-        <v>183.4604518817237</v>
+        <v>187.6105195355423</v>
       </c>
       <c r="E3" t="n">
-        <v>186.79248046875</v>
+        <v>188.4385375976562</v>
       </c>
       <c r="F3" t="n">
-        <v>173844900</v>
+        <v>136805800</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B4" t="n">
-        <v>189.1468626563914</v>
+        <v>188.7378093314507</v>
       </c>
       <c r="C4" t="n">
-        <v>190.593394116267</v>
+        <v>189.9050110254035</v>
       </c>
       <c r="D4" t="n">
-        <v>187.6105347272827</v>
+        <v>184.9369182511207</v>
       </c>
       <c r="E4" t="n">
-        <v>188.4385528564453</v>
+        <v>187.1715545654297</v>
       </c>
       <c r="F4" t="n">
-        <v>136805800</v>
+        <v>137596900</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B5" t="n">
-        <v>188.7378247179256</v>
+        <v>185.0566446584491</v>
       </c>
       <c r="C5" t="n">
-        <v>189.9050265070322</v>
+        <v>186.7825055997528</v>
       </c>
       <c r="D5" t="n">
-        <v>184.9369333277354</v>
+        <v>182.8918329061041</v>
       </c>
       <c r="E5" t="n">
-        <v>187.1715698242188</v>
+        <v>185.0965423583984</v>
       </c>
       <c r="F5" t="n">
-        <v>137596900</v>
+        <v>157678100</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B6" t="n">
-        <v>185.0566446584491</v>
+        <v>185.7848907820332</v>
       </c>
       <c r="C6" t="n">
-        <v>186.7825055997528</v>
+        <v>188.6081286768816</v>
       </c>
       <c r="D6" t="n">
-        <v>182.8918329061041</v>
+        <v>183.5602249269612</v>
       </c>
       <c r="E6" t="n">
-        <v>185.0965423583984</v>
+        <v>184.5977325439453</v>
       </c>
       <c r="F6" t="n">
-        <v>157678100</v>
+        <v>140088000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B7" t="n">
-        <v>185.7848907820332</v>
+        <v>186.1240823667868</v>
       </c>
       <c r="C7" t="n">
-        <v>188.6081286768816</v>
+        <v>189.1468390813163</v>
       </c>
       <c r="D7" t="n">
-        <v>183.5602249269612</v>
+        <v>186.094140065894</v>
       </c>
       <c r="E7" t="n">
-        <v>184.5977325439453</v>
+        <v>188.6580047607422</v>
       </c>
       <c r="F7" t="n">
-        <v>140088000</v>
+        <v>130168900</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B8" t="n">
-        <v>186.1240974206304</v>
+        <v>191.7705422839889</v>
       </c>
       <c r="C8" t="n">
-        <v>189.1468543796426</v>
+        <v>194.8332119113436</v>
       </c>
       <c r="D8" t="n">
-        <v>186.0941551173159</v>
+        <v>190.6033405552435</v>
       </c>
       <c r="E8" t="n">
-        <v>188.6580200195312</v>
+        <v>192.1097412109375</v>
       </c>
       <c r="F8" t="n">
-        <v>130168900</v>
+        <v>182997200</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B9" t="n">
-        <v>191.7705422839889</v>
+        <v>193.0474982342752</v>
       </c>
       <c r="C9" t="n">
-        <v>194.8332119113436</v>
+        <v>195.1524558626357</v>
       </c>
       <c r="D9" t="n">
-        <v>190.6033405552435</v>
+        <v>181.6148965961679</v>
       </c>
       <c r="E9" t="n">
-        <v>192.1097412109375</v>
+        <v>182.7222442626953</v>
       </c>
       <c r="F9" t="n">
-        <v>182997200</v>
+        <v>268774400</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B10" t="n">
-        <v>193.0474982342752</v>
+        <v>187.5207340107304</v>
       </c>
       <c r="C10" t="n">
-        <v>195.1524558626357</v>
+        <v>189.6556185865847</v>
       </c>
       <c r="D10" t="n">
-        <v>181.6148965961679</v>
+        <v>185.5155435929421</v>
       </c>
       <c r="E10" t="n">
-        <v>182.7222442626953</v>
+        <v>187.8699035644531</v>
       </c>
       <c r="F10" t="n">
-        <v>268774400</v>
+        <v>153482800</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B11" t="n">
-        <v>187.52074924116</v>
+        <v>184.3283927796865</v>
       </c>
       <c r="C11" t="n">
-        <v>189.6556339904095</v>
+        <v>184.3583198600852</v>
       </c>
       <c r="D11" t="n">
-        <v>185.5155586605101</v>
+        <v>179.2705030798172</v>
       </c>
       <c r="E11" t="n">
-        <v>187.8699188232422</v>
+        <v>179.5997161865234</v>
       </c>
       <c r="F11" t="n">
-        <v>153482800</v>
+        <v>205641400</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B12" t="n">
-        <v>184.3283927796865</v>
+        <v>184.3583147400375</v>
       </c>
       <c r="C12" t="n">
-        <v>184.3583198600852</v>
+        <v>184.4281395182556</v>
       </c>
       <c r="D12" t="n">
-        <v>179.2705030798172</v>
+        <v>176.866254560341</v>
       </c>
       <c r="E12" t="n">
-        <v>179.5997161865234</v>
+        <v>179.4001922607422</v>
       </c>
       <c r="F12" t="n">
-        <v>205641400</v>
+        <v>214450500</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B13" t="n">
-        <v>184.358330420537</v>
+        <v>181.7944521048813</v>
       </c>
       <c r="C13" t="n">
-        <v>184.428155204694</v>
+        <v>182.8419455690647</v>
       </c>
       <c r="D13" t="n">
-        <v>176.8662696036074</v>
+        <v>179.3403402174659</v>
       </c>
       <c r="E13" t="n">
-        <v>179.4002075195312</v>
+        <v>181.3754577636719</v>
       </c>
       <c r="F13" t="n">
-        <v>214450500</v>
+        <v>179723300</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B14" t="n">
-        <v>181.7944521048813</v>
+        <v>179.7493465774322</v>
       </c>
       <c r="C14" t="n">
-        <v>182.8419455690647</v>
+        <v>183.6599908268075</v>
       </c>
       <c r="D14" t="n">
-        <v>179.3403402174659</v>
+        <v>179.3203816221287</v>
       </c>
       <c r="E14" t="n">
-        <v>181.3754577636719</v>
+        <v>182.7820892333984</v>
       </c>
       <c r="F14" t="n">
-        <v>179723300</v>
+        <v>173135200</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B15" t="n">
-        <v>179.7493615830456</v>
+        <v>182.6923255947822</v>
       </c>
       <c r="C15" t="n">
-        <v>183.6600061588844</v>
+        <v>184.7573703952674</v>
       </c>
       <c r="D15" t="n">
-        <v>179.3203965919317</v>
+        <v>181.2956624505063</v>
       </c>
       <c r="E15" t="n">
-        <v>182.7821044921875</v>
+        <v>182.2034912109375</v>
       </c>
       <c r="F15" t="n">
-        <v>173135200</v>
+        <v>128544700</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B16" t="n">
-        <v>182.6923102950553</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="C16" t="n">
-        <v>184.7573549226016</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="D16" t="n">
-        <v>181.2956472677441</v>
+        <v>179.3702701372806</v>
       </c>
       <c r="E16" t="n">
-        <v>182.2034759521484</v>
+        <v>180.7270202636719</v>
       </c>
       <c r="F16" t="n">
-        <v>128544700</v>
+        <v>124240200</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B17" t="n">
-        <v>182.3531141136141</v>
+        <v>180.7070509305708</v>
       </c>
       <c r="C17" t="n">
-        <v>182.3531141136141</v>
+        <v>183.0015566720687</v>
       </c>
       <c r="D17" t="n">
-        <v>179.3702701372806</v>
+        <v>176.3375148363812</v>
       </c>
       <c r="E17" t="n">
-        <v>180.7270202636719</v>
+        <v>179.8491058349609</v>
       </c>
       <c r="F17" t="n">
-        <v>124240200</v>
+        <v>162249600</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B18" t="n">
-        <v>180.7070662621498</v>
+        <v>179.988777912505</v>
       </c>
       <c r="C18" t="n">
-        <v>183.0015721983185</v>
+        <v>182.5925403832715</v>
       </c>
       <c r="D18" t="n">
-        <v>176.3375297972393</v>
+        <v>179.3602787988416</v>
       </c>
       <c r="E18" t="n">
-        <v>179.84912109375</v>
+        <v>181.7246246337891</v>
       </c>
       <c r="F18" t="n">
-        <v>162249600</v>
+        <v>111363700</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B19" t="n">
-        <v>179.988762799469</v>
+        <v>183.400590081168</v>
       </c>
       <c r="C19" t="n">
-        <v>182.5925250516066</v>
+        <v>187.0219186862977</v>
       </c>
       <c r="D19" t="n">
-        <v>179.3602637385785</v>
+        <v>183.0614063875393</v>
       </c>
       <c r="E19" t="n">
-        <v>181.724609375</v>
+        <v>185.8148040771484</v>
       </c>
       <c r="F19" t="n">
-        <v>111363700</v>
+        <v>131296700</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B20" t="n">
-        <v>183.4006051417061</v>
+        <v>189.5359033209746</v>
       </c>
       <c r="C20" t="n">
-        <v>187.0219340442129</v>
+        <v>191.541093665248</v>
       </c>
       <c r="D20" t="n">
-        <v>183.0614214202242</v>
+        <v>187.979619148197</v>
       </c>
       <c r="E20" t="n">
-        <v>185.8148193359375</v>
+        <v>191.0323181152344</v>
       </c>
       <c r="F20" t="n">
-        <v>131296700</v>
+        <v>153452700</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B21" t="n">
-        <v>189.5359033209746</v>
+        <v>192.5886067715161</v>
       </c>
       <c r="C21" t="n">
-        <v>191.541093665248</v>
+        <v>202.6644582837766</v>
       </c>
       <c r="D21" t="n">
-        <v>187.979619148197</v>
+        <v>191.4513320204045</v>
       </c>
       <c r="E21" t="n">
-        <v>191.0323181152344</v>
+        <v>200.5495300292969</v>
       </c>
       <c r="F21" t="n">
-        <v>153452700</v>
+        <v>297986200</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B22" t="n">
-        <v>192.5886067715161</v>
+        <v>207.482921843539</v>
       </c>
       <c r="C22" t="n">
-        <v>202.6644582837766</v>
+        <v>211.6828666070652</v>
       </c>
       <c r="D22" t="n">
-        <v>191.4513320204045</v>
+        <v>204.2905729140704</v>
       </c>
       <c r="E22" t="n">
-        <v>200.5495300292969</v>
+        <v>206.545166015625</v>
       </c>
       <c r="F22" t="n">
-        <v>297986200</v>
+        <v>308829600</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B23" t="n">
-        <v>207.482906515472</v>
+        <v>204.6596680014167</v>
       </c>
       <c r="C23" t="n">
-        <v>211.6828509687219</v>
+        <v>205.6672637579894</v>
       </c>
       <c r="D23" t="n">
-        <v>204.2905578218423</v>
+        <v>200.9286166610889</v>
       </c>
       <c r="E23" t="n">
-        <v>206.5451507568359</v>
+        <v>202.4050750732422</v>
       </c>
       <c r="F23" t="n">
-        <v>308829600</v>
+        <v>178864400</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B24" t="n">
-        <v>204.6596680014167</v>
+        <v>205.9565693232556</v>
       </c>
       <c r="C24" t="n">
-        <v>205.6672637579894</v>
+        <v>207.4729406961805</v>
       </c>
       <c r="D24" t="n">
-        <v>200.9286166610889</v>
+        <v>201.5870481318289</v>
       </c>
       <c r="E24" t="n">
-        <v>202.4050750732422</v>
+        <v>202.0060424804688</v>
       </c>
       <c r="F24" t="n">
-        <v>178864400</v>
+        <v>179802200</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B25" t="n">
-        <v>205.9565537660584</v>
+        <v>207.5826573279554</v>
       </c>
       <c r="C25" t="n">
-        <v>207.4729250244422</v>
+        <v>210.834859926228</v>
       </c>
       <c r="D25" t="n">
-        <v>201.5870329046891</v>
+        <v>205.068676268978</v>
       </c>
       <c r="E25" t="n">
-        <v>202.0060272216797</v>
+        <v>206.3855285644531</v>
       </c>
       <c r="F25" t="n">
-        <v>179802200</v>
+        <v>180267300</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B26" t="n">
-        <v>207.5826880225491</v>
+        <v>202.5147991590425</v>
       </c>
       <c r="C26" t="n">
-        <v>210.8348911017148</v>
+        <v>203.4824819294599</v>
       </c>
       <c r="D26" t="n">
-        <v>205.0687065918373</v>
+        <v>197.4569099225941</v>
       </c>
       <c r="E26" t="n">
-        <v>206.3855590820312</v>
+        <v>198.2151031494141</v>
       </c>
       <c r="F26" t="n">
-        <v>180267300</v>
+        <v>188919300</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B27" t="n">
-        <v>202.5148147488263</v>
+        <v>198.2949275919373</v>
       </c>
       <c r="C27" t="n">
-        <v>203.4824975937368</v>
+        <v>202.4350026612236</v>
       </c>
       <c r="D27" t="n">
-        <v>197.4569251230167</v>
+        <v>194.1847643800754</v>
       </c>
       <c r="E27" t="n">
-        <v>198.2151184082031</v>
+        <v>194.7434387207031</v>
       </c>
       <c r="F27" t="n">
-        <v>188919300</v>
+        <v>171350300</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B28" t="n">
-        <v>198.2949275919373</v>
+        <v>195.9505570232203</v>
       </c>
       <c r="C28" t="n">
-        <v>202.4350026612236</v>
+        <v>197.1476859949454</v>
       </c>
       <c r="D28" t="n">
-        <v>194.1847643800754</v>
+        <v>185.934559185592</v>
       </c>
       <c r="E28" t="n">
-        <v>194.7434387207031</v>
+        <v>187.6304931640625</v>
       </c>
       <c r="F28" t="n">
-        <v>171350300</v>
+        <v>223029800</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B29" t="n">
-        <v>195.9505410878136</v>
+        <v>184.4580698535366</v>
       </c>
       <c r="C29" t="n">
-        <v>197.1476699621838</v>
+        <v>187.8699092076593</v>
       </c>
       <c r="D29" t="n">
-        <v>185.9345440647224</v>
+        <v>178.4823961188316</v>
       </c>
       <c r="E29" t="n">
-        <v>187.6304779052734</v>
+        <v>187.7003021240234</v>
       </c>
       <c r="F29" t="n">
-        <v>223029800</v>
+        <v>264942300</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B30" t="n">
-        <v>184.4580548583195</v>
+        <v>194.6436788693004</v>
       </c>
       <c r="C30" t="n">
-        <v>187.8698939350823</v>
+        <v>199.4621367771523</v>
       </c>
       <c r="D30" t="n">
-        <v>178.4823816093971</v>
+        <v>193.3268264223904</v>
       </c>
       <c r="E30" t="n">
-        <v>187.7002868652344</v>
+        <v>198.5742645263672</v>
       </c>
       <c r="F30" t="n">
-        <v>264942300</v>
+        <v>198897100</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B31" t="n">
-        <v>194.6436788693004</v>
+        <v>194.6935535589016</v>
       </c>
       <c r="C31" t="n">
-        <v>199.4621367771523</v>
+        <v>194.9529266552934</v>
       </c>
       <c r="D31" t="n">
-        <v>193.3268264223904</v>
+        <v>190.8427786999811</v>
       </c>
       <c r="E31" t="n">
-        <v>198.5742645263672</v>
+        <v>192.6983337402344</v>
       </c>
       <c r="F31" t="n">
-        <v>198897100</v>
+        <v>176483300</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B32" t="n">
-        <v>194.6935381421213</v>
+        <v>195.2522010776849</v>
       </c>
       <c r="C32" t="n">
-        <v>194.9529112179747</v>
+        <v>195.4217929255223</v>
       </c>
       <c r="D32" t="n">
-        <v>190.8427635881239</v>
+        <v>190.6731755191215</v>
       </c>
       <c r="E32" t="n">
-        <v>192.6983184814453</v>
+        <v>193.3367919921875</v>
       </c>
       <c r="F32" t="n">
-        <v>176483300</v>
+        <v>154935300</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B33" t="n">
-        <v>195.2522010776849</v>
+        <v>190.5933791327836</v>
       </c>
       <c r="C33" t="n">
-        <v>195.4217929255223</v>
+        <v>190.9824463944715</v>
       </c>
       <c r="D33" t="n">
-        <v>190.6731755191215</v>
+        <v>183.4105907203728</v>
       </c>
       <c r="E33" t="n">
-        <v>193.3367919921875</v>
+        <v>186.4133911132812</v>
       </c>
       <c r="F33" t="n">
-        <v>154935300</v>
+        <v>207423100</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B34" t="n">
-        <v>190.5933791327836</v>
+        <v>182.4229435613052</v>
       </c>
       <c r="C34" t="n">
-        <v>190.9824463944715</v>
+        <v>190.553458007553</v>
       </c>
       <c r="D34" t="n">
-        <v>183.4105907203728</v>
+        <v>180.1483942490048</v>
       </c>
       <c r="E34" t="n">
-        <v>186.4133911132812</v>
+        <v>189.7154693603516</v>
       </c>
       <c r="F34" t="n">
-        <v>207423100</v>
+        <v>186591900</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B35" t="n">
-        <v>182.4229435613052</v>
+        <v>185.5255230789849</v>
       </c>
       <c r="C35" t="n">
-        <v>190.553458007553</v>
+        <v>188.5482800008962</v>
       </c>
       <c r="D35" t="n">
-        <v>180.1483942490048</v>
+        <v>183.8794727552066</v>
       </c>
       <c r="E35" t="n">
-        <v>189.7154693603516</v>
+        <v>186.1540222167969</v>
       </c>
       <c r="F35" t="n">
-        <v>186591900</v>
+        <v>173628900</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B36" t="n">
-        <v>185.5255230789849</v>
+        <v>182.941705155915</v>
       </c>
       <c r="C36" t="n">
-        <v>188.5482800008962</v>
+        <v>184.3583093626339</v>
       </c>
       <c r="D36" t="n">
-        <v>183.8794727552066</v>
+        <v>179.2206093334711</v>
       </c>
       <c r="E36" t="n">
-        <v>186.1540222167969</v>
+        <v>180.9265289306641</v>
       </c>
       <c r="F36" t="n">
-        <v>173628900</v>
+        <v>213598900</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B37" t="n">
-        <v>182.9417205846578</v>
+        <v>184.3483273978252</v>
       </c>
       <c r="C37" t="n">
-        <v>184.3583249108488</v>
+        <v>187.4109971087465</v>
       </c>
       <c r="D37" t="n">
-        <v>179.2206244483882</v>
+        <v>182.3930205111681</v>
       </c>
       <c r="E37" t="n">
-        <v>180.9265441894531</v>
+        <v>186.0742034912109</v>
       </c>
       <c r="F37" t="n">
-        <v>213598900</v>
+        <v>247246400</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B38" t="n">
-        <v>184.3483273978252</v>
+        <v>195.4816571057099</v>
       </c>
       <c r="C38" t="n">
-        <v>187.4109971087465</v>
+        <v>195.5315406452363</v>
       </c>
       <c r="D38" t="n">
-        <v>182.3930205111681</v>
+        <v>179.4201468289569</v>
       </c>
       <c r="E38" t="n">
-        <v>186.0742034912109</v>
+        <v>180.208251953125</v>
       </c>
       <c r="F38" t="n">
-        <v>247246400</v>
+        <v>343504800</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B39" t="n">
-        <v>195.4816571057099</v>
+        <v>180.806813452001</v>
       </c>
       <c r="C39" t="n">
-        <v>195.5315406452363</v>
+        <v>184.1188702156436</v>
       </c>
       <c r="D39" t="n">
-        <v>179.4201468289569</v>
+        <v>172.5166628687019</v>
       </c>
       <c r="E39" t="n">
-        <v>180.208251953125</v>
+        <v>178.4524536132812</v>
       </c>
       <c r="F39" t="n">
-        <v>343504800</v>
+        <v>346926200</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B40" t="n">
-        <v>180.8068289121023</v>
+        <v>179.0609943264491</v>
       </c>
       <c r="C40" t="n">
-        <v>184.1188859589464</v>
+        <v>183.0614042749852</v>
       </c>
       <c r="D40" t="n">
-        <v>172.5166776199441</v>
+        <v>176.0581789881563</v>
       </c>
       <c r="E40" t="n">
-        <v>178.4524688720703</v>
+        <v>182.1136779785156</v>
       </c>
       <c r="F40" t="n">
-        <v>346926200</v>
+        <v>256618300</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B41" t="n">
-        <v>179.0610243324759</v>
+        <v>174.4919407266003</v>
       </c>
       <c r="C41" t="n">
-        <v>183.0614349513779</v>
+        <v>177.7341727058355</v>
       </c>
       <c r="D41" t="n">
-        <v>176.0582084909882</v>
+        <v>169.1447513765687</v>
       </c>
       <c r="E41" t="n">
-        <v>182.1137084960938</v>
+        <v>177.3949890136719</v>
       </c>
       <c r="F41" t="n">
-        <v>256618300</v>
+        <v>320600300</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B42" t="n">
-        <v>174.4919707447618</v>
+        <v>181.1958831941039</v>
       </c>
       <c r="C42" t="n">
-        <v>177.734203281764</v>
+        <v>182.4728225932506</v>
       </c>
       <c r="D42" t="n">
-        <v>169.1447804748437</v>
+        <v>177.8139863878403</v>
       </c>
       <c r="E42" t="n">
-        <v>177.39501953125</v>
+        <v>179.8291473388672</v>
       </c>
       <c r="F42" t="n">
-        <v>320600300</v>
+        <v>183852000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B43" t="n">
-        <v>181.1958831941039</v>
+        <v>178.5821404669205</v>
       </c>
       <c r="C43" t="n">
-        <v>182.4728225932506</v>
+        <v>178.8614700176124</v>
       </c>
       <c r="D43" t="n">
-        <v>177.8139863878403</v>
+        <v>176.0781451295325</v>
       </c>
       <c r="E43" t="n">
-        <v>179.8291473388672</v>
+        <v>176.5769500732422</v>
       </c>
       <c r="F43" t="n">
-        <v>183852000</v>
+        <v>121332800</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B44" t="n">
-        <v>178.5821558989869</v>
+        <v>174.3423189563235</v>
       </c>
       <c r="C44" t="n">
-        <v>178.8614854738169</v>
+        <v>179.8690869073362</v>
       </c>
       <c r="D44" t="n">
-        <v>176.0781603452176</v>
+        <v>173.2648983244765</v>
       </c>
       <c r="E44" t="n">
-        <v>176.5769653320312</v>
+        <v>179.489990234375</v>
       </c>
       <c r="F44" t="n">
-        <v>121332800</v>
+        <v>188131000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B45" t="n">
-        <v>174.3422893139723</v>
+        <v>181.3255769560617</v>
       </c>
       <c r="C45" t="n">
-        <v>179.8690563253026</v>
+        <v>185.2162648499111</v>
       </c>
       <c r="D45" t="n">
-        <v>173.2648688653124</v>
+        <v>179.569788944198</v>
       </c>
       <c r="E45" t="n">
-        <v>179.4899597167969</v>
+        <v>181.0263061523438</v>
       </c>
       <c r="F45" t="n">
-        <v>188131000</v>
+        <v>182632200</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B46" t="n">
-        <v>181.3255769560617</v>
+        <v>180.6472109015755</v>
       </c>
       <c r="C46" t="n">
-        <v>185.2162648499111</v>
+        <v>182.0139316568558</v>
       </c>
       <c r="D46" t="n">
-        <v>179.569788944198</v>
+        <v>178.681918089591</v>
       </c>
       <c r="E46" t="n">
-        <v>181.0263061523438</v>
+        <v>179.1607666015625</v>
       </c>
       <c r="F46" t="n">
-        <v>182632200</v>
+        <v>165138000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,25 +1639,25 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B47" t="n">
-        <v>180.6472262869623</v>
+        <v>181.1959881613664</v>
       </c>
       <c r="C47" t="n">
-        <v>182.0139471586436</v>
+        <v>184.089227004522</v>
       </c>
       <c r="D47" t="n">
-        <v>178.6819333075974</v>
+        <v>179.5398751387779</v>
       </c>
       <c r="E47" t="n">
-        <v>179.1607818603516</v>
+        <v>182.9518890380859</v>
       </c>
       <c r="F47" t="n">
-        <v>165138000</v>
+        <v>167364900</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -1665,25 +1665,25 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B48" t="n">
-        <v>181.1959881613664</v>
+        <v>183.4607020047171</v>
       </c>
       <c r="C48" t="n">
-        <v>184.089227004522</v>
+        <v>184.2289086763207</v>
       </c>
       <c r="D48" t="n">
-        <v>179.5398751387779</v>
+        <v>180.4876631773748</v>
       </c>
       <c r="E48" t="n">
-        <v>182.9518890380859</v>
+        <v>181.9841613769531</v>
       </c>
       <c r="F48" t="n">
-        <v>167364900</v>
+        <v>143971100</v>
       </c>
       <c r="G48" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B49" t="n">
-        <v>183.4606866221248</v>
+        <v>182.213626289633</v>
       </c>
       <c r="C49" t="n">
-        <v>184.2288932293168</v>
+        <v>187.5611139779305</v>
       </c>
       <c r="D49" t="n">
-        <v>180.4876480440623</v>
+        <v>181.9741810893209</v>
       </c>
       <c r="E49" t="n">
-        <v>181.9841461181641</v>
+        <v>185.1168365478516</v>
       </c>
       <c r="F49" t="n">
-        <v>143971100</v>
+        <v>204378100</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B50" t="n">
-        <v>182.2136112701494</v>
+        <v>185.12679644575</v>
       </c>
       <c r="C50" t="n">
-        <v>187.5610985176648</v>
+        <v>185.2864265695677</v>
       </c>
       <c r="D50" t="n">
-        <v>181.9741660895743</v>
+        <v>182.8920356049676</v>
       </c>
       <c r="E50" t="n">
-        <v>185.1168212890625</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="F50" t="n">
-        <v>204378100</v>
+        <v>144719700</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B51" t="n">
-        <v>185.12679644575</v>
+        <v>184.5381918075859</v>
       </c>
       <c r="C51" t="n">
-        <v>185.2864265695677</v>
+        <v>185.0469957406681</v>
       </c>
       <c r="D51" t="n">
-        <v>182.8920356049676</v>
+        <v>181.6150239281505</v>
       </c>
       <c r="E51" t="n">
-        <v>184.5381774902344</v>
+        <v>183.3509674072266</v>
       </c>
       <c r="F51" t="n">
-        <v>144719700</v>
+        <v>162785400</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B52" t="n">
-        <v>184.5381918075859</v>
+        <v>179.8591224369562</v>
       </c>
       <c r="C52" t="n">
-        <v>185.0469957406681</v>
+        <v>180.8967030087509</v>
       </c>
       <c r="D52" t="n">
-        <v>181.6150239281505</v>
+        <v>176.2076633109278</v>
       </c>
       <c r="E52" t="n">
-        <v>183.3509674072266</v>
+        <v>180.5075988769531</v>
       </c>
       <c r="F52" t="n">
-        <v>162785400</v>
+        <v>182136600</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B53" t="n">
-        <v>179.8591224369562</v>
+        <v>180.6871831157045</v>
       </c>
       <c r="C53" t="n">
-        <v>180.8967030087509</v>
+        <v>182.3931976659576</v>
       </c>
       <c r="D53" t="n">
-        <v>176.2076633109278</v>
+        <v>174.2123291208211</v>
       </c>
       <c r="E53" t="n">
-        <v>180.5075988769531</v>
+        <v>174.6114044189453</v>
       </c>
       <c r="F53" t="n">
-        <v>182136600</v>
+        <v>204274900</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B54" t="n">
-        <v>180.6871989054384</v>
+        <v>177.5245749312296</v>
       </c>
       <c r="C54" t="n">
-        <v>182.3932136047752</v>
+        <v>178.0034500370577</v>
       </c>
       <c r="D54" t="n">
-        <v>174.2123443447362</v>
+        <v>174.6213651072644</v>
       </c>
       <c r="E54" t="n">
-        <v>174.6114196777344</v>
+        <v>175.87841796875</v>
       </c>
       <c r="F54" t="n">
-        <v>204274900</v>
+        <v>164775600</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B55" t="n">
-        <v>177.5245903328353</v>
+        <v>175.8485012773324</v>
       </c>
       <c r="C55" t="n">
-        <v>178.0034654802094</v>
+        <v>178.0733061224419</v>
       </c>
       <c r="D55" t="n">
-        <v>174.6213802569945</v>
+        <v>174.4916756985292</v>
       </c>
       <c r="E55" t="n">
-        <v>175.8784332275391</v>
+        <v>177.3050994873047</v>
       </c>
       <c r="F55" t="n">
-        <v>164775600</v>
+        <v>148588100</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B56" t="n">
-        <v>175.8485012773324</v>
+        <v>175.6888811343</v>
       </c>
       <c r="C56" t="n">
-        <v>178.0733061224419</v>
+        <v>175.7188098781239</v>
       </c>
       <c r="D56" t="n">
-        <v>174.4916756985292</v>
+        <v>169.9123900056319</v>
       </c>
       <c r="E56" t="n">
-        <v>177.3050994873047</v>
+        <v>170.5409240722656</v>
       </c>
       <c r="F56" t="n">
-        <v>148588100</v>
+        <v>222775500</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B57" t="n">
-        <v>175.6888811343</v>
+        <v>174.1225483861358</v>
       </c>
       <c r="C57" t="n">
-        <v>175.7188098781239</v>
+        <v>175.7387615308714</v>
       </c>
       <c r="D57" t="n">
-        <v>169.9123900056319</v>
+        <v>171.4188835631069</v>
       </c>
       <c r="E57" t="n">
-        <v>170.5409240722656</v>
+        <v>173.7334594726562</v>
       </c>
       <c r="F57" t="n">
-        <v>222775500</v>
+        <v>176096000</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B58" t="n">
-        <v>174.1225483861358</v>
+        <v>176.2575672304301</v>
       </c>
       <c r="C58" t="n">
-        <v>175.7387615308714</v>
+        <v>181.0264072425164</v>
       </c>
       <c r="D58" t="n">
-        <v>171.4188835631069</v>
+        <v>175.9283357789888</v>
       </c>
       <c r="E58" t="n">
-        <v>173.7334594726562</v>
+        <v>180.5674896240234</v>
       </c>
       <c r="F58" t="n">
-        <v>176096000</v>
+        <v>324925900</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B59" t="n">
-        <v>176.2575672304301</v>
+        <v>183.4906282252173</v>
       </c>
       <c r="C59" t="n">
-        <v>181.0264072425164</v>
+        <v>183.7300734141942</v>
       </c>
       <c r="D59" t="n">
-        <v>175.9283357789888</v>
+        <v>181.9243013805983</v>
       </c>
       <c r="E59" t="n">
-        <v>180.5674896240234</v>
+        <v>183.2611694335938</v>
       </c>
       <c r="F59" t="n">
-        <v>324925900</v>
+        <v>129064400</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B60" t="n">
-        <v>183.4906282252173</v>
+        <v>182.5428571096804</v>
       </c>
       <c r="C60" t="n">
-        <v>183.7300734141942</v>
+        <v>188.8880102762506</v>
       </c>
       <c r="D60" t="n">
-        <v>181.9243013805983</v>
+        <v>182.4730132178061</v>
       </c>
       <c r="E60" t="n">
-        <v>183.2611694335938</v>
+        <v>188.7682952880859</v>
       </c>
       <c r="F60" t="n">
-        <v>129064400</v>
+        <v>174873600</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B61" t="n">
-        <v>182.5428571096804</v>
+        <v>187.5012437217294</v>
       </c>
       <c r="C61" t="n">
-        <v>188.8880102762506</v>
+        <v>188.4689804086018</v>
       </c>
       <c r="D61" t="n">
-        <v>182.4730132178061</v>
+        <v>186.154389299292</v>
       </c>
       <c r="E61" t="n">
-        <v>188.7682952880859</v>
+        <v>188.169677734375</v>
       </c>
       <c r="F61" t="n">
-        <v>174873600</v>
+        <v>65528500</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B62" t="n">
-        <v>187.5012437217294</v>
+        <v>189.4766285187414</v>
       </c>
       <c r="C62" t="n">
-        <v>188.4689804086018</v>
+        <v>192.240166195598</v>
       </c>
       <c r="D62" t="n">
-        <v>186.154389299292</v>
+        <v>187.5611125998212</v>
       </c>
       <c r="E62" t="n">
-        <v>188.169677734375</v>
+        <v>190.085205078125</v>
       </c>
       <c r="F62" t="n">
-        <v>65528500</v>
+        <v>139740300</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B63" t="n">
-        <v>189.4766285187414</v>
+        <v>187.2717899684254</v>
       </c>
       <c r="C63" t="n">
-        <v>192.240166195598</v>
+        <v>188.3193265216257</v>
       </c>
       <c r="D63" t="n">
-        <v>187.5611125998212</v>
+        <v>185.4759890979627</v>
       </c>
       <c r="E63" t="n">
-        <v>190.085205078125</v>
+        <v>187.7805938720703</v>
       </c>
       <c r="F63" t="n">
-        <v>139740300</v>
+        <v>120006100</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B64" t="n">
-        <v>187.2717899684254</v>
+        <v>187.8005508490403</v>
       </c>
       <c r="C64" t="n">
-        <v>188.3193265216257</v>
+        <v>188.5487999407664</v>
       </c>
       <c r="D64" t="n">
-        <v>185.4759890979627</v>
+        <v>186.4935963146986</v>
       </c>
       <c r="E64" t="n">
-        <v>187.7805938720703</v>
+        <v>187.1021728515625</v>
       </c>
       <c r="F64" t="n">
-        <v>120006100</v>
+        <v>97687300</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B65" t="n">
-        <v>187.8005508490403</v>
+        <v>189.1274459397885</v>
       </c>
       <c r="C65" t="n">
-        <v>188.5487999407664</v>
+        <v>190.1151249886817</v>
       </c>
       <c r="D65" t="n">
-        <v>186.4935963146986</v>
+        <v>186.0546345387688</v>
       </c>
       <c r="E65" t="n">
-        <v>187.1021728515625</v>
+        <v>186.0646057128906</v>
       </c>
       <c r="F65" t="n">
-        <v>97687300</v>
+        <v>120100500</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B66" t="n">
-        <v>189.1274459397885</v>
+        <v>189.3968130035911</v>
       </c>
       <c r="C66" t="n">
-        <v>190.1151249886817</v>
+        <v>192.4795957147097</v>
       </c>
       <c r="D66" t="n">
-        <v>186.0546345387688</v>
+        <v>187.8204997023152</v>
       </c>
       <c r="E66" t="n">
-        <v>186.0646057128906</v>
+        <v>188.4091339111328</v>
       </c>
       <c r="F66" t="n">
-        <v>120100500</v>
+        <v>148240500</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B67" t="n">
-        <v>189.3968130035911</v>
+        <v>191.3123337767646</v>
       </c>
       <c r="C67" t="n">
-        <v>192.4795957147097</v>
+        <v>193.1779786425506</v>
       </c>
       <c r="D67" t="n">
-        <v>187.8204997023152</v>
+        <v>185.7154296257417</v>
       </c>
       <c r="E67" t="n">
-        <v>188.4091339111328</v>
+        <v>187.6808319091797</v>
       </c>
       <c r="F67" t="n">
-        <v>148240500</v>
+        <v>183529700</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B68" t="n">
-        <v>191.3123182227279</v>
+        <v>190.0752284670132</v>
       </c>
       <c r="C68" t="n">
-        <v>193.1779629368336</v>
+        <v>191.7213703933745</v>
       </c>
       <c r="D68" t="n">
-        <v>185.7154145267434</v>
+        <v>186.3838692947835</v>
       </c>
       <c r="E68" t="n">
-        <v>187.6808166503906</v>
+        <v>186.8028869628906</v>
       </c>
       <c r="F68" t="n">
-        <v>183529700</v>
+        <v>176862600</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B69" t="n">
-        <v>190.0752284670132</v>
+        <v>188.1297854095839</v>
       </c>
       <c r="C69" t="n">
-        <v>191.7213703933745</v>
+        <v>190.9232365533545</v>
       </c>
       <c r="D69" t="n">
-        <v>186.3838692947835</v>
+        <v>186.1244680675316</v>
       </c>
       <c r="E69" t="n">
-        <v>186.8028869628906</v>
+        <v>188.6685180664062</v>
       </c>
       <c r="F69" t="n">
-        <v>176862600</v>
+        <v>153543200</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B70" t="n">
-        <v>188.1297854095839</v>
+        <v>188.6685072554968</v>
       </c>
       <c r="C70" t="n">
-        <v>190.9232365533545</v>
+        <v>189.1074824738404</v>
       </c>
       <c r="D70" t="n">
-        <v>186.1244680675316</v>
+        <v>183.2811201033086</v>
       </c>
       <c r="E70" t="n">
-        <v>188.6685180664062</v>
+        <v>184.6080017089844</v>
       </c>
       <c r="F70" t="n">
-        <v>153543200</v>
+        <v>172457000</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B71" t="n">
-        <v>188.6685228499072</v>
+        <v>184.6479238968445</v>
       </c>
       <c r="C71" t="n">
-        <v>189.1074981045344</v>
+        <v>185.9049768874807</v>
       </c>
       <c r="D71" t="n">
-        <v>183.2811352524241</v>
+        <v>183.2412119543349</v>
       </c>
       <c r="E71" t="n">
-        <v>184.6080169677734</v>
+        <v>184.4284362792969</v>
       </c>
       <c r="F71" t="n">
-        <v>172457000</v>
+        <v>131327500</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B72" t="n">
-        <v>184.6479238968445</v>
+        <v>182.7922691735387</v>
       </c>
       <c r="C72" t="n">
-        <v>185.9049768874807</v>
+        <v>186.6831584288149</v>
       </c>
       <c r="D72" t="n">
-        <v>183.2412119543349</v>
+        <v>182.5927391235801</v>
       </c>
       <c r="E72" t="n">
-        <v>184.4284362792969</v>
+        <v>184.5082550048828</v>
       </c>
       <c r="F72" t="n">
-        <v>131327500</v>
+        <v>137968500</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B73" t="n">
-        <v>182.7922691735387</v>
+        <v>184.5681140987238</v>
       </c>
       <c r="C73" t="n">
-        <v>186.6831584288149</v>
+        <v>187.6708543554723</v>
       </c>
       <c r="D73" t="n">
-        <v>182.5927391235801</v>
+        <v>182.9718432388734</v>
       </c>
       <c r="E73" t="n">
-        <v>184.5082550048828</v>
+        <v>185.376220703125</v>
       </c>
       <c r="F73" t="n">
-        <v>137968500</v>
+        <v>160128900</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B74" t="n">
-        <v>184.5680989064521</v>
+        <v>183.8897012556695</v>
       </c>
       <c r="C74" t="n">
-        <v>187.6708389078061</v>
+        <v>184.0293738083791</v>
       </c>
       <c r="D74" t="n">
-        <v>182.9718281779948</v>
+        <v>180.3779146434709</v>
       </c>
       <c r="E74" t="n">
-        <v>185.3762054443359</v>
+        <v>182.7124481201172</v>
       </c>
       <c r="F74" t="n">
-        <v>160128900</v>
+        <v>159586100</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B75" t="n">
-        <v>183.889716612774</v>
+        <v>186.0645927657271</v>
       </c>
       <c r="C75" t="n">
-        <v>184.029389177148</v>
+        <v>189.2571189267257</v>
       </c>
       <c r="D75" t="n">
-        <v>180.3779297072971</v>
+        <v>185.8949914784577</v>
       </c>
       <c r="E75" t="n">
-        <v>182.7124633789062</v>
+        <v>186.6133117675781</v>
       </c>
       <c r="F75" t="n">
-        <v>159586100</v>
+        <v>206188600</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B76" t="n">
-        <v>186.0646079796491</v>
+        <v>188.6385795892923</v>
       </c>
       <c r="C76" t="n">
-        <v>189.2571344016907</v>
+        <v>189.99540517049</v>
       </c>
       <c r="D76" t="n">
-        <v>185.895006678512</v>
+        <v>185.6455833269296</v>
       </c>
       <c r="E76" t="n">
-        <v>186.6133270263672</v>
+        <v>185.7952270507812</v>
       </c>
       <c r="F76" t="n">
-        <v>206188600</v>
+        <v>187967200</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B77" t="n">
-        <v>188.6385950815971</v>
+        <v>181.4753422141945</v>
       </c>
       <c r="C77" t="n">
-        <v>189.9954207742267</v>
+        <v>181.9542325986551</v>
       </c>
       <c r="D77" t="n">
-        <v>185.6455985734289</v>
+        <v>177.1953640623503</v>
       </c>
       <c r="E77" t="n">
-        <v>185.7952423095703</v>
+        <v>177.654296875</v>
       </c>
       <c r="F77" t="n">
-        <v>187967200</v>
+        <v>223345300</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B78" t="n">
-        <v>181.4753578011745</v>
+        <v>178.6320081827799</v>
       </c>
       <c r="C78" t="n">
-        <v>181.9542482267672</v>
+        <v>184.9472325313386</v>
       </c>
       <c r="D78" t="n">
-        <v>177.1953792817215</v>
+        <v>177.9835164834521</v>
       </c>
       <c r="E78" t="n">
-        <v>177.6543121337891</v>
+        <v>182.8920440673828</v>
       </c>
       <c r="F78" t="n">
-        <v>223345300</v>
+        <v>200381000</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B79" t="n">
-        <v>178.6319932794081</v>
+        <v>184.3186915464293</v>
       </c>
       <c r="C79" t="n">
-        <v>184.947217101084</v>
+        <v>185.7353746560278</v>
       </c>
       <c r="D79" t="n">
-        <v>177.9835016341843</v>
+        <v>183.5005985718231</v>
       </c>
       <c r="E79" t="n">
-        <v>182.8920288085938</v>
+        <v>184.4084777832031</v>
       </c>
       <c r="F79" t="n">
-        <v>200381000</v>
+        <v>139636600</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B80" t="n">
-        <v>184.3186915464293</v>
+        <v>187.0622712594319</v>
       </c>
       <c r="C80" t="n">
-        <v>185.7353746560278</v>
+        <v>189.1573747868041</v>
       </c>
       <c r="D80" t="n">
-        <v>183.5005985718231</v>
+        <v>186.3838660627843</v>
       </c>
       <c r="E80" t="n">
-        <v>184.4084777832031</v>
+        <v>187.2318725585938</v>
       </c>
       <c r="F80" t="n">
-        <v>139636600</v>
+        <v>142748100</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B81" t="n">
-        <v>187.0622712594319</v>
+        <v>186.7230748442759</v>
       </c>
       <c r="C81" t="n">
-        <v>189.1573747868041</v>
+        <v>188.6784906596197</v>
       </c>
       <c r="D81" t="n">
-        <v>186.3838660627843</v>
+        <v>185.555808059744</v>
       </c>
       <c r="E81" t="n">
-        <v>187.2318725585938</v>
+        <v>186.0346832275391</v>
       </c>
       <c r="F81" t="n">
-        <v>142748100</v>
+        <v>124799600</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B82" t="n">
-        <v>186.7230748442759</v>
+        <v>186.8028844605491</v>
       </c>
       <c r="C82" t="n">
-        <v>188.6784906596197</v>
+        <v>189.5564356240106</v>
       </c>
       <c r="D82" t="n">
-        <v>185.555808059744</v>
+        <v>185.2664711415707</v>
       </c>
       <c r="E82" t="n">
-        <v>186.0346832275391</v>
+        <v>188.0798950195312</v>
       </c>
       <c r="F82" t="n">
-        <v>124799600</v>
+        <v>143711600</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B83" t="n">
-        <v>186.8028844605491</v>
+        <v>190.823459633995</v>
       </c>
       <c r="C83" t="n">
-        <v>189.5564356240106</v>
+        <v>191.9009400606663</v>
       </c>
       <c r="D83" t="n">
-        <v>185.2664711415707</v>
+        <v>189.3967902384632</v>
       </c>
       <c r="E83" t="n">
-        <v>188.0798950195312</v>
+        <v>191.0728759765625</v>
       </c>
       <c r="F83" t="n">
-        <v>143711600</v>
+        <v>148552700</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B84" t="n">
-        <v>190.823459633995</v>
+        <v>190.8933105997472</v>
       </c>
       <c r="C84" t="n">
-        <v>191.9009400606663</v>
+        <v>193.0283141326731</v>
       </c>
       <c r="D84" t="n">
-        <v>189.3967902384632</v>
+        <v>185.6256380470483</v>
       </c>
       <c r="E84" t="n">
-        <v>191.0728759765625</v>
+        <v>192.0605773925781</v>
       </c>
       <c r="F84" t="n">
-        <v>148552700</v>
+        <v>171764400</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B85" t="n">
-        <v>190.8933105997472</v>
+        <v>190.7636224379378</v>
       </c>
       <c r="C85" t="n">
-        <v>193.0283141326731</v>
+        <v>194.0359639826301</v>
       </c>
       <c r="D85" t="n">
-        <v>185.6256380470483</v>
+        <v>189.0276790286862</v>
       </c>
       <c r="E85" t="n">
-        <v>192.0605773925781</v>
+        <v>190.6838073730469</v>
       </c>
       <c r="F85" t="n">
-        <v>171764400</v>
+        <v>179489500</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B86" t="n">
-        <v>190.7636224379378</v>
+        <v>186.7629659025267</v>
       </c>
       <c r="C86" t="n">
-        <v>194.0359639826301</v>
+        <v>189.8557348322644</v>
       </c>
       <c r="D86" t="n">
-        <v>189.0276790286862</v>
+        <v>184.4483900153819</v>
       </c>
       <c r="E86" t="n">
-        <v>190.6838073730469</v>
+        <v>185.1766815185547</v>
       </c>
       <c r="F86" t="n">
-        <v>179489500</v>
+        <v>165794100</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B87" t="n">
-        <v>186.7629659025267</v>
+        <v>185.8052108647954</v>
       </c>
       <c r="C87" t="n">
-        <v>189.8557348322644</v>
+        <v>185.8351396091497</v>
       </c>
       <c r="D87" t="n">
-        <v>184.4483900153819</v>
+        <v>175.8185703987175</v>
       </c>
       <c r="E87" t="n">
-        <v>185.1766815185547</v>
+        <v>179.9189758300781</v>
       </c>
       <c r="F87" t="n">
-        <v>165794100</v>
+        <v>204019600</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B88" t="n">
-        <v>185.8052108647954</v>
+        <v>179.0410571553003</v>
       </c>
       <c r="C88" t="n">
-        <v>185.8351396091497</v>
+        <v>179.1607721437711</v>
       </c>
       <c r="D88" t="n">
-        <v>175.8185703987175</v>
+        <v>171.5086795929406</v>
       </c>
       <c r="E88" t="n">
-        <v>179.9189758300781</v>
+        <v>173.7833557128906</v>
       </c>
       <c r="F88" t="n">
-        <v>204019600</v>
+        <v>207014100</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B89" t="n">
-        <v>179.0410571553003</v>
+        <v>174.5216119878791</v>
       </c>
       <c r="C89" t="n">
-        <v>179.1607721437711</v>
+        <v>176.4072143255947</v>
       </c>
       <c r="D89" t="n">
-        <v>171.5086795929406</v>
+        <v>170.6307227747363</v>
       </c>
       <c r="E89" t="n">
-        <v>173.7833557128906</v>
+        <v>171.4787445068359</v>
       </c>
       <c r="F89" t="n">
-        <v>207014100</v>
+        <v>206312900</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B90" t="n">
-        <v>174.5216119878791</v>
+        <v>176.2775135166603</v>
       </c>
       <c r="C90" t="n">
-        <v>176.4072143255947</v>
+        <v>186.5634420291942</v>
       </c>
       <c r="D90" t="n">
-        <v>170.6307227747363</v>
+        <v>174.1923963475411</v>
       </c>
       <c r="E90" t="n">
-        <v>171.4787445068359</v>
+        <v>184.9771575927734</v>
       </c>
       <c r="F90" t="n">
-        <v>206312900</v>
+        <v>231346200</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B91" t="n">
-        <v>176.2775280578147</v>
+        <v>183.8298386502086</v>
       </c>
       <c r="C91" t="n">
-        <v>186.5634574188361</v>
+        <v>193.2079034382237</v>
       </c>
       <c r="D91" t="n">
-        <v>174.1924107166939</v>
+        <v>183.5205647824287</v>
       </c>
       <c r="E91" t="n">
-        <v>184.9771728515625</v>
+        <v>189.5963439941406</v>
       </c>
       <c r="F91" t="n">
-        <v>231346200</v>
+        <v>196387400</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B92" t="n">
-        <v>183.8298238555102</v>
+        <v>190.933219719687</v>
       </c>
       <c r="C92" t="n">
-        <v>193.2078878887748</v>
+        <v>192.0306425866914</v>
       </c>
       <c r="D92" t="n">
-        <v>183.5205500126207</v>
+        <v>187.6808205923615</v>
       </c>
       <c r="E92" t="n">
-        <v>189.5963287353516</v>
+        <v>188.0998382568359</v>
       </c>
       <c r="F92" t="n">
-        <v>196387400</v>
+        <v>136764800</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B93" t="n">
-        <v>190.9332352083219</v>
+        <v>192.0007297023972</v>
       </c>
       <c r="C93" t="n">
-        <v>192.0306581643501</v>
+        <v>192.8088363522974</v>
       </c>
       <c r="D93" t="n">
-        <v>187.6808358171596</v>
+        <v>188.3293278304631</v>
       </c>
       <c r="E93" t="n">
-        <v>188.099853515625</v>
+        <v>189.6063385009766</v>
       </c>
       <c r="F93" t="n">
-        <v>136764800</v>
+        <v>144192700</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B94" t="n">
-        <v>192.0007142509167</v>
+        <v>192.5793648877844</v>
       </c>
       <c r="C94" t="n">
-        <v>192.8088208357837</v>
+        <v>193.1580126884611</v>
       </c>
       <c r="D94" t="n">
-        <v>188.329312674443</v>
+        <v>186.0745817463215</v>
       </c>
       <c r="E94" t="n">
-        <v>189.6063232421875</v>
+        <v>186.5035858154297</v>
       </c>
       <c r="F94" t="n">
-        <v>144192700</v>
+        <v>189932500</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B95" t="n">
-        <v>192.5793648877844</v>
+        <v>187.0423048169314</v>
       </c>
       <c r="C95" t="n">
-        <v>193.1580126884611</v>
+        <v>187.0622623874058</v>
       </c>
       <c r="D95" t="n">
-        <v>186.0745817463215</v>
+        <v>181.1660562233949</v>
       </c>
       <c r="E95" t="n">
-        <v>186.5035858154297</v>
+        <v>182.3832092285156</v>
       </c>
       <c r="F95" t="n">
-        <v>189932500</v>
+        <v>161888000</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B96" t="n">
-        <v>187.042320465516</v>
+        <v>181.3256935584433</v>
       </c>
       <c r="C96" t="n">
-        <v>187.0622780376601</v>
+        <v>186.7130808403767</v>
       </c>
       <c r="D96" t="n">
-        <v>181.1660713803529</v>
+        <v>178.7616860728079</v>
       </c>
       <c r="E96" t="n">
-        <v>182.3832244873047</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="F96" t="n">
-        <v>161888000</v>
+        <v>162276900</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B97" t="n">
-        <v>181.3256935584433</v>
+        <v>188.3093443160685</v>
       </c>
       <c r="C97" t="n">
-        <v>186.7130808403767</v>
+        <v>189.9255573932224</v>
       </c>
       <c r="D97" t="n">
-        <v>178.7616860728079</v>
+        <v>186.3239846890322</v>
       </c>
       <c r="E97" t="n">
-        <v>184.5381774902344</v>
+        <v>187.5411376953125</v>
       </c>
       <c r="F97" t="n">
-        <v>162276900</v>
+        <v>164749100</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B98" t="n">
-        <v>188.3093443160685</v>
+        <v>186.62329889396</v>
       </c>
       <c r="C98" t="n">
-        <v>189.9255573932224</v>
+        <v>187.9900957055448</v>
       </c>
       <c r="D98" t="n">
-        <v>186.3239846890322</v>
+        <v>185.2265733363672</v>
       </c>
       <c r="E98" t="n">
-        <v>187.5411376953125</v>
+        <v>187.4613342285156</v>
       </c>
       <c r="F98" t="n">
-        <v>164749100</v>
+        <v>126554500</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B99" t="n">
-        <v>186.62329889396</v>
+        <v>186.1344638821937</v>
       </c>
       <c r="C99" t="n">
-        <v>187.9900957055448</v>
+        <v>189.8856807673048</v>
       </c>
       <c r="D99" t="n">
-        <v>185.2265733363672</v>
+        <v>185.5059297314624</v>
       </c>
       <c r="E99" t="n">
-        <v>187.4613342285156</v>
+        <v>189.3768768310547</v>
       </c>
       <c r="F99" t="n">
-        <v>126554500</v>
+        <v>178422300</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B100" t="n">
-        <v>186.1344488846578</v>
+        <v>190.9531547742145</v>
       </c>
       <c r="C100" t="n">
-        <v>189.8856654675195</v>
+        <v>193.4972046328596</v>
       </c>
       <c r="D100" t="n">
-        <v>185.5059147845697</v>
+        <v>189.1374116308485</v>
       </c>
       <c r="E100" t="n">
-        <v>189.3768615722656</v>
+        <v>191.1028137207031</v>
       </c>
       <c r="F100" t="n">
-        <v>178422300</v>
+        <v>171584800</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B101" t="n">
-        <v>190.9531547742145</v>
+        <v>191.0429698590405</v>
       </c>
       <c r="C101" t="n">
-        <v>193.4972046328596</v>
+        <v>193.3176459547985</v>
       </c>
       <c r="D101" t="n">
-        <v>189.1374116308485</v>
+        <v>186.9625064417709</v>
       </c>
       <c r="E101" t="n">
-        <v>191.1028137207031</v>
+        <v>192.3997955322266</v>
       </c>
       <c r="F101" t="n">
-        <v>171584800</v>
+        <v>175123600</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B102" t="n">
-        <v>191.0429698590405</v>
+        <v>193.9960453222018</v>
       </c>
       <c r="C102" t="n">
-        <v>193.3176459547985</v>
+        <v>197.1686293956491</v>
       </c>
       <c r="D102" t="n">
-        <v>186.9625064417709</v>
+        <v>193.3375824661624</v>
       </c>
       <c r="E102" t="n">
-        <v>192.3997955322266</v>
+        <v>195.1034545898438</v>
       </c>
       <c r="F102" t="n">
-        <v>175123600</v>
+        <v>250637100</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B103" t="n">
-        <v>193.9960453222018</v>
+        <v>193.8164652690549</v>
       </c>
       <c r="C103" t="n">
-        <v>197.1686293956491</v>
+        <v>193.8364076167612</v>
       </c>
       <c r="D103" t="n">
-        <v>193.3375824661624</v>
+        <v>183.8896973916963</v>
       </c>
       <c r="E103" t="n">
-        <v>195.1034545898438</v>
+        <v>184.4583587646484</v>
       </c>
       <c r="F103" t="n">
-        <v>250637100</v>
+        <v>360807900</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B104" t="n">
-        <v>193.8164813019665</v>
+        <v>180.8268714126474</v>
       </c>
       <c r="C104" t="n">
-        <v>193.8364236513225</v>
+        <v>182.1637395256691</v>
       </c>
       <c r="D104" t="n">
-        <v>183.8897126034445</v>
+        <v>175.9682453114839</v>
       </c>
       <c r="E104" t="n">
-        <v>184.4583740234375</v>
+        <v>176.7763519287109</v>
       </c>
       <c r="F104" t="n">
-        <v>360807900</v>
+        <v>311636500</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B105" t="n">
-        <v>180.8268714126474</v>
+        <v>174.601438160182</v>
       </c>
       <c r="C105" t="n">
-        <v>182.1637395256691</v>
+        <v>183.0317240302905</v>
       </c>
       <c r="D105" t="n">
-        <v>175.9682453114839</v>
+        <v>174.2323067871125</v>
       </c>
       <c r="E105" t="n">
-        <v>176.7763519287109</v>
+        <v>182.0540008544922</v>
       </c>
       <c r="F105" t="n">
-        <v>311636500</v>
+        <v>209095300</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B106" t="n">
-        <v>174.6014235260267</v>
+        <v>178.0732983803544</v>
       </c>
       <c r="C106" t="n">
-        <v>183.0317086895539</v>
+        <v>180.4776603660684</v>
       </c>
       <c r="D106" t="n">
-        <v>174.2322921838959</v>
+        <v>176.5069564334623</v>
       </c>
       <c r="E106" t="n">
-        <v>182.0539855957031</v>
+        <v>179.6296539306641</v>
       </c>
       <c r="F106" t="n">
-        <v>209095300</v>
+        <v>178099400</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B107" t="n">
-        <v>178.0733135069376</v>
+        <v>180.0187649948852</v>
       </c>
       <c r="C107" t="n">
-        <v>180.4776756968921</v>
+        <v>184.2688145383873</v>
       </c>
       <c r="D107" t="n">
-        <v>176.5069714269912</v>
+        <v>179.6396472340209</v>
       </c>
       <c r="E107" t="n">
-        <v>179.6296691894531</v>
+        <v>182.6126861572266</v>
       </c>
       <c r="F107" t="n">
-        <v>178099400</v>
+        <v>177731200</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B108" t="n">
-        <v>180.0187499528396</v>
+        <v>180.7470399397241</v>
       </c>
       <c r="C108" t="n">
-        <v>184.2687991412151</v>
+        <v>183.6302923567135</v>
       </c>
       <c r="D108" t="n">
-        <v>179.6396322236537</v>
+        <v>177.4647274492447</v>
       </c>
       <c r="E108" t="n">
-        <v>182.6126708984375</v>
+        <v>182.9119720458984</v>
       </c>
       <c r="F108" t="n">
-        <v>177731200</v>
+        <v>198779700</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B109" t="n">
-        <v>180.7470399397241</v>
+        <v>179.4201653790109</v>
       </c>
       <c r="C109" t="n">
-        <v>183.6302923567135</v>
+        <v>182.3333469017365</v>
       </c>
       <c r="D109" t="n">
-        <v>177.4647274492447</v>
+        <v>176.4072264371208</v>
       </c>
       <c r="E109" t="n">
-        <v>182.9119720458984</v>
+        <v>177.4048919677734</v>
       </c>
       <c r="F109" t="n">
-        <v>198779700</v>
+        <v>189021900</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B110" t="n">
-        <v>179.4201653790109</v>
+        <v>176.4171820751478</v>
       </c>
       <c r="C110" t="n">
-        <v>182.3333469017365</v>
+        <v>182.4829897940845</v>
       </c>
       <c r="D110" t="n">
-        <v>176.4072264371208</v>
+        <v>175.1501427003192</v>
       </c>
       <c r="E110" t="n">
-        <v>177.4048919677734</v>
+        <v>182.2235870361328</v>
       </c>
       <c r="F110" t="n">
-        <v>189021900</v>
+        <v>177213600</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B111" t="n">
-        <v>176.4171820751478</v>
+        <v>181.9741609804723</v>
       </c>
       <c r="C111" t="n">
-        <v>182.4829897940845</v>
+        <v>186.0047376795775</v>
       </c>
       <c r="D111" t="n">
-        <v>175.1501427003192</v>
+        <v>181.5850720874406</v>
       </c>
       <c r="E111" t="n">
-        <v>182.2235870361328</v>
+        <v>184.3386383056641</v>
       </c>
       <c r="F111" t="n">
-        <v>177213600</v>
+        <v>179118500</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,25 +3329,25 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B112" t="n">
-        <v>181.9741609804723</v>
+        <v>185.4860219488843</v>
       </c>
       <c r="C112" t="n">
-        <v>186.0047376795775</v>
+        <v>187.1921136401388</v>
       </c>
       <c r="D112" t="n">
-        <v>181.5850720874406</v>
+        <v>184.0293448898806</v>
       </c>
       <c r="E112" t="n">
-        <v>184.3386383056641</v>
+        <v>185.6057434082031</v>
       </c>
       <c r="F112" t="n">
-        <v>179118500</v>
+        <v>145280400</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3355,25 +3355,25 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B113" t="n">
-        <v>185.4860219488843</v>
+        <v>183.6302794851663</v>
       </c>
       <c r="C113" t="n">
-        <v>187.1921136401388</v>
+        <v>184.5182492431283</v>
       </c>
       <c r="D113" t="n">
-        <v>184.0293448898806</v>
+        <v>181.3355215595592</v>
       </c>
       <c r="E113" t="n">
-        <v>185.6057434082031</v>
+        <v>182.7223510742188</v>
       </c>
       <c r="F113" t="n">
-        <v>145280400</v>
+        <v>155762700</v>
       </c>
       <c r="G113" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B114" t="n">
-        <v>183.6302794851663</v>
+        <v>184.4982761588831</v>
       </c>
       <c r="C114" t="n">
-        <v>184.5182492431283</v>
+        <v>185.6656060713691</v>
       </c>
       <c r="D114" t="n">
-        <v>181.3355215595592</v>
+        <v>179.5296376335348</v>
       </c>
       <c r="E114" t="n">
-        <v>182.7223510742188</v>
+        <v>179.8389282226562</v>
       </c>
       <c r="F114" t="n">
-        <v>155762700</v>
+        <v>160988400</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B115" t="n">
-        <v>184.4982761588831</v>
+        <v>182.5527399223597</v>
       </c>
       <c r="C115" t="n">
-        <v>185.6656060713691</v>
+        <v>188.4492658789173</v>
       </c>
       <c r="D115" t="n">
-        <v>179.5296376335348</v>
+        <v>180.9962999229416</v>
       </c>
       <c r="E115" t="n">
-        <v>179.8389282226562</v>
+        <v>182.8021697998047</v>
       </c>
       <c r="F115" t="n">
-        <v>160988400</v>
+        <v>217307400</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B116" t="n">
-        <v>182.5527399223597</v>
+        <v>184.6379576703901</v>
       </c>
       <c r="C116" t="n">
-        <v>188.4492658789173</v>
+        <v>184.9771786272242</v>
       </c>
       <c r="D116" t="n">
-        <v>180.9962999229416</v>
+        <v>181.2656610816535</v>
       </c>
       <c r="E116" t="n">
-        <v>182.8021697998047</v>
+        <v>181.5150909423828</v>
       </c>
       <c r="F116" t="n">
-        <v>217307400</v>
+        <v>182497800</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B117" t="n">
-        <v>184.6379576703901</v>
+        <v>182.0638447517288</v>
       </c>
       <c r="C117" t="n">
-        <v>184.9771786272242</v>
+        <v>182.9618014097589</v>
       </c>
       <c r="D117" t="n">
-        <v>181.2656610816535</v>
+        <v>179.9187539793071</v>
       </c>
       <c r="E117" t="n">
-        <v>181.5150909423828</v>
+        <v>179.9885864257812</v>
       </c>
       <c r="F117" t="n">
-        <v>182497800</v>
+        <v>156683100</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B118" t="n">
-        <v>182.0638447517288</v>
+        <v>177.6040375011918</v>
       </c>
       <c r="C118" t="n">
-        <v>182.9618014097589</v>
+        <v>179.569546076418</v>
       </c>
       <c r="D118" t="n">
-        <v>179.9187539793071</v>
+        <v>175.3890990582871</v>
       </c>
       <c r="E118" t="n">
-        <v>179.9885864257812</v>
+        <v>178.1527862548828</v>
       </c>
       <c r="F118" t="n">
-        <v>156683100</v>
+        <v>170968500</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B119" t="n">
-        <v>177.6040375011918</v>
+        <v>177.5940529420793</v>
       </c>
       <c r="C119" t="n">
-        <v>179.569546076418</v>
+        <v>177.8534545050662</v>
       </c>
       <c r="D119" t="n">
-        <v>175.3890990582871</v>
+        <v>171.3283763370981</v>
       </c>
       <c r="E119" t="n">
-        <v>178.1527862548828</v>
+        <v>172.3061370849609</v>
       </c>
       <c r="F119" t="n">
-        <v>170968500</v>
+        <v>241323500</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B120" t="n">
-        <v>177.5940529420793</v>
+        <v>176.8557415306554</v>
       </c>
       <c r="C120" t="n">
-        <v>177.8534545050662</v>
+        <v>177.9632107122345</v>
       </c>
       <c r="D120" t="n">
-        <v>171.3283763370981</v>
+        <v>174.3614429436745</v>
       </c>
       <c r="E120" t="n">
-        <v>172.3061370849609</v>
+        <v>175.2394409179688</v>
       </c>
       <c r="F120" t="n">
-        <v>241323500</v>
+        <v>182836300</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B121" t="n">
-        <v>176.8557415306554</v>
+        <v>174.4312942297872</v>
       </c>
       <c r="C121" t="n">
-        <v>177.9632107122345</v>
+        <v>175.8181236639554</v>
       </c>
       <c r="D121" t="n">
-        <v>174.3614429436745</v>
+        <v>173.5832266030264</v>
       </c>
       <c r="E121" t="n">
-        <v>175.2394409179688</v>
+        <v>174.8004455566406</v>
       </c>
       <c r="F121" t="n">
-        <v>182836300</v>
+        <v>147667800</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B122" t="n">
-        <v>174.4312942297872</v>
+        <v>176.6961233561449</v>
       </c>
       <c r="C122" t="n">
-        <v>175.8181236639554</v>
+        <v>180.8067226806179</v>
       </c>
       <c r="D122" t="n">
-        <v>173.5832266030264</v>
+        <v>176.4466934898736</v>
       </c>
       <c r="E122" t="n">
-        <v>174.8004455566406</v>
+        <v>178.2725067138672</v>
       </c>
       <c r="F122" t="n">
-        <v>147667800</v>
+        <v>162602100</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B123" t="n">
-        <v>176.6961233561449</v>
+        <v>175.6684741654964</v>
       </c>
       <c r="C123" t="n">
-        <v>180.8067226806179</v>
+        <v>176.1074579435819</v>
       </c>
       <c r="D123" t="n">
-        <v>176.4466934898736</v>
+        <v>170.7497092682189</v>
       </c>
       <c r="E123" t="n">
-        <v>178.2725067138672</v>
+        <v>170.8494873046875</v>
       </c>
       <c r="F123" t="n">
-        <v>162602100</v>
+        <v>186152200</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B124" t="n">
-        <v>175.6684741654964</v>
+        <v>169.6122945102883</v>
       </c>
       <c r="C124" t="n">
-        <v>176.1074579435819</v>
+        <v>170.5800835262955</v>
       </c>
       <c r="D124" t="n">
-        <v>170.7497092682189</v>
+        <v>166.6291080850299</v>
       </c>
       <c r="E124" t="n">
-        <v>170.8494873046875</v>
+        <v>167.1379547119141</v>
       </c>
       <c r="F124" t="n">
-        <v>186152200</v>
+        <v>196212700</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B125" t="n">
-        <v>169.6122945102883</v>
+        <v>168.3950875250076</v>
       </c>
       <c r="C125" t="n">
-        <v>170.5800835262955</v>
+        <v>169.0635577295173</v>
       </c>
       <c r="D125" t="n">
-        <v>166.6291080850299</v>
+        <v>163.8953782868944</v>
       </c>
       <c r="E125" t="n">
-        <v>167.1379547119141</v>
+        <v>164.7933197021484</v>
       </c>
       <c r="F125" t="n">
-        <v>196212700</v>
+        <v>185627000</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B126" t="n">
-        <v>168.3950875250076</v>
+        <v>166.5892250311153</v>
       </c>
       <c r="C126" t="n">
-        <v>169.0635577295173</v>
+        <v>174.2217730660379</v>
       </c>
       <c r="D126" t="n">
-        <v>163.8953782868944</v>
+        <v>166.5792533168182</v>
       </c>
       <c r="E126" t="n">
-        <v>164.7933197021484</v>
+        <v>174.0022735595703</v>
       </c>
       <c r="F126" t="n">
-        <v>185627000</v>
+        <v>226181300</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B127" t="n">
-        <v>166.5892250311153</v>
+        <v>175.5986272559566</v>
       </c>
       <c r="C127" t="n">
-        <v>174.2217730660379</v>
+        <v>176.9654980623514</v>
       </c>
       <c r="D127" t="n">
-        <v>166.5792533168182</v>
+        <v>174.3514779146501</v>
       </c>
       <c r="E127" t="n">
-        <v>174.0022735595703</v>
+        <v>175.3491973876953</v>
       </c>
       <c r="F127" t="n">
-        <v>226181300</v>
+        <v>168132000</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B128" t="n">
-        <v>175.5986272559566</v>
+        <v>171.7873183615289</v>
       </c>
       <c r="C128" t="n">
-        <v>176.9654980623514</v>
+        <v>177.0852211444685</v>
       </c>
       <c r="D128" t="n">
-        <v>174.3514779146501</v>
+        <v>170.9791680862979</v>
       </c>
       <c r="E128" t="n">
-        <v>175.3491973876953</v>
+        <v>176.9854431152344</v>
       </c>
       <c r="F128" t="n">
-        <v>168132000</v>
+        <v>143143200</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B129" t="n">
-        <v>171.7873183615289</v>
+        <v>176.7559774774269</v>
       </c>
       <c r="C129" t="n">
-        <v>177.0852211444685</v>
+        <v>177.3845303646084</v>
       </c>
       <c r="D129" t="n">
-        <v>170.9791680862979</v>
+        <v>175.3591611441553</v>
       </c>
       <c r="E129" t="n">
-        <v>176.9854431152344</v>
+        <v>177.2348785400391</v>
       </c>
       <c r="F129" t="n">
-        <v>143143200</v>
+        <v>107564300</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B130" t="n">
-        <v>176.7559774774269</v>
+        <v>175.3292270516068</v>
       </c>
       <c r="C130" t="n">
-        <v>177.3845303646084</v>
+        <v>177.8235255680002</v>
       </c>
       <c r="D130" t="n">
-        <v>175.3591611441553</v>
+        <v>173.2639557965079</v>
       </c>
       <c r="E130" t="n">
-        <v>177.2348785400391</v>
+        <v>177.6938323974609</v>
       </c>
       <c r="F130" t="n">
-        <v>107564300</v>
+        <v>132534900</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B131" t="n">
-        <v>175.3292270516068</v>
+        <v>184.079243714486</v>
       </c>
       <c r="C131" t="n">
-        <v>177.8235255680002</v>
+        <v>184.837505037226</v>
       </c>
       <c r="D131" t="n">
-        <v>173.2639557965079</v>
+        <v>179.8888249511496</v>
       </c>
       <c r="E131" t="n">
-        <v>177.6938323974609</v>
+        <v>181.6647644042969</v>
       </c>
       <c r="F131" t="n">
-        <v>132534900</v>
+        <v>147732700</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B132" t="n">
-        <v>184.079243714486</v>
+        <v>181.4252987848774</v>
       </c>
       <c r="C132" t="n">
-        <v>184.837505037226</v>
+        <v>183.6601958045732</v>
       </c>
       <c r="D132" t="n">
-        <v>179.8888249511496</v>
+        <v>180.2080798537204</v>
       </c>
       <c r="E132" t="n">
-        <v>181.6647644042969</v>
+        <v>183.4905853271484</v>
       </c>
       <c r="F132" t="n">
-        <v>147732700</v>
+        <v>116428500</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B133" t="n">
-        <v>181.4252987848774</v>
+        <v>183.8896736698189</v>
       </c>
       <c r="C133" t="n">
-        <v>183.6601958045732</v>
+        <v>189.5666999081706</v>
       </c>
       <c r="D133" t="n">
-        <v>180.2080798537204</v>
+        <v>183.8797019557237</v>
       </c>
       <c r="E133" t="n">
-        <v>183.4905853271484</v>
+        <v>188.1998291015625</v>
       </c>
       <c r="F133" t="n">
-        <v>116428500</v>
+        <v>160459500</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B134" t="n">
-        <v>183.8896736698189</v>
+        <v>185.605746824658</v>
       </c>
       <c r="C134" t="n">
-        <v>189.5666999081706</v>
+        <v>189.2274732756209</v>
       </c>
       <c r="D134" t="n">
-        <v>183.8797019557237</v>
+        <v>185.3164148846483</v>
       </c>
       <c r="E134" t="n">
-        <v>188.1998291015625</v>
+        <v>188.8782653808594</v>
       </c>
       <c r="F134" t="n">
-        <v>160459500</v>
+        <v>133648200</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B135" t="n">
-        <v>185.605746824658</v>
+        <v>190.4047764107204</v>
       </c>
       <c r="C135" t="n">
-        <v>189.2274732756209</v>
+        <v>196.0618438720703</v>
       </c>
       <c r="D135" t="n">
-        <v>185.3164148846483</v>
+        <v>190.3349439656124</v>
       </c>
       <c r="E135" t="n">
-        <v>188.8782653808594</v>
+        <v>196.0618438720703</v>
       </c>
       <c r="F135" t="n">
-        <v>133648200</v>
+        <v>161307000</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B136" t="n">
-        <v>190.4047764107204</v>
+        <v>196.0917851116163</v>
       </c>
       <c r="C136" t="n">
-        <v>196.0618438720703</v>
+        <v>199.9429830157183</v>
       </c>
       <c r="D136" t="n">
-        <v>190.3349439656124</v>
+        <v>195.2936216855987</v>
       </c>
       <c r="E136" t="n">
-        <v>196.0618438720703</v>
+        <v>198.4164733886719</v>
       </c>
       <c r="F136" t="n">
-        <v>161307000</v>
+        <v>185338400</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B137" t="n">
-        <v>196.0917851116163</v>
+        <v>196.9797440092329</v>
       </c>
       <c r="C137" t="n">
-        <v>199.9429830157183</v>
+        <v>199.3942384790618</v>
       </c>
       <c r="D137" t="n">
-        <v>195.2936216855987</v>
+        <v>195.3634433694217</v>
       </c>
       <c r="E137" t="n">
-        <v>198.4164733886719</v>
+        <v>197.8976593017578</v>
       </c>
       <c r="F137" t="n">
-        <v>185338400</v>
+        <v>134012900</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B138" t="n">
-        <v>196.9797440092329</v>
+        <v>199.444107632571</v>
       </c>
       <c r="C138" t="n">
-        <v>199.3942384790618</v>
+        <v>201.2400056483541</v>
       </c>
       <c r="D138" t="n">
-        <v>195.3634433694217</v>
+        <v>198.8155547450397</v>
       </c>
       <c r="E138" t="n">
-        <v>197.8976593017578</v>
+        <v>201.2200469970703</v>
       </c>
       <c r="F138" t="n">
-        <v>134012900</v>
+        <v>160324400</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B139" t="n">
-        <v>199.444107632571</v>
+        <v>199.5239239232554</v>
       </c>
       <c r="C139" t="n">
-        <v>201.2400056483541</v>
+        <v>201.7089318732817</v>
       </c>
       <c r="D139" t="n">
-        <v>198.8155547450397</v>
+        <v>197.3888049886708</v>
       </c>
       <c r="E139" t="n">
-        <v>201.2200469970703</v>
+        <v>201.5991821289062</v>
       </c>
       <c r="F139" t="n">
-        <v>160324400</v>
+        <v>119381400</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B140" t="n">
-        <v>199.5239239232554</v>
+        <v>201.6690479582887</v>
       </c>
       <c r="C140" t="n">
-        <v>201.7089318732817</v>
+        <v>202.2876291783034</v>
       </c>
       <c r="D140" t="n">
-        <v>197.3888049886708</v>
+        <v>198.5461810430697</v>
       </c>
       <c r="E140" t="n">
-        <v>201.5991821289062</v>
+        <v>199.4241790771484</v>
       </c>
       <c r="F140" t="n">
-        <v>119381400</v>
+        <v>107945300</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B141" t="n">
-        <v>201.6690479582887</v>
+        <v>200.5316418294082</v>
       </c>
       <c r="C141" t="n">
-        <v>202.2876291783034</v>
+        <v>202.0381927490234</v>
       </c>
       <c r="D141" t="n">
-        <v>198.5461810430697</v>
+        <v>198.546174602744</v>
       </c>
       <c r="E141" t="n">
-        <v>199.4241790771484</v>
+        <v>202.0381927490234</v>
       </c>
       <c r="F141" t="n">
-        <v>107945300</v>
+        <v>107501000</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B142" t="n">
-        <v>200.5316418294082</v>
+        <v>201.9982837593082</v>
       </c>
       <c r="C142" t="n">
-        <v>202.0381927490234</v>
+        <v>203.3651545152774</v>
       </c>
       <c r="D142" t="n">
-        <v>198.546174602744</v>
+        <v>196.7702284327844</v>
       </c>
       <c r="E142" t="n">
-        <v>202.0381927490234</v>
+        <v>199.1847076416016</v>
       </c>
       <c r="F142" t="n">
-        <v>107501000</v>
+        <v>113561800</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B143" t="n">
-        <v>201.9982837593082</v>
+        <v>199.5039827094276</v>
       </c>
       <c r="C143" t="n">
-        <v>203.3651545152774</v>
+        <v>210.468909435165</v>
       </c>
       <c r="D143" t="n">
-        <v>196.7702284327844</v>
+        <v>199.3543156614425</v>
       </c>
       <c r="E143" t="n">
-        <v>199.1847076416016</v>
+        <v>207.7950286865234</v>
       </c>
       <c r="F143" t="n">
-        <v>113561800</v>
+        <v>214134400</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B144" t="n">
-        <v>199.5039827094276</v>
+        <v>209.1718784416434</v>
       </c>
       <c r="C144" t="n">
-        <v>210.468909435165</v>
+        <v>216.335512072091</v>
       </c>
       <c r="D144" t="n">
-        <v>199.3543156614425</v>
+        <v>206.9070662315077</v>
       </c>
       <c r="E144" t="n">
-        <v>207.7950286865234</v>
+        <v>216.1160125732422</v>
       </c>
       <c r="F144" t="n">
-        <v>214134400</v>
+        <v>187172400</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B145" t="n">
-        <v>209.1718784416434</v>
+        <v>209.0122528840405</v>
       </c>
       <c r="C145" t="n">
-        <v>216.335512072091</v>
+        <v>214.2402930542568</v>
       </c>
       <c r="D145" t="n">
-        <v>206.9070662315077</v>
+        <v>207.7251862691963</v>
       </c>
       <c r="E145" t="n">
-        <v>216.1160125732422</v>
+        <v>212.6838531494141</v>
       </c>
       <c r="F145" t="n">
-        <v>187172400</v>
+        <v>180275400</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B146" t="n">
-        <v>209.0122528840405</v>
+        <v>212.2149257168926</v>
       </c>
       <c r="C146" t="n">
-        <v>214.2402930542568</v>
+        <v>212.2348843687743</v>
       </c>
       <c r="D146" t="n">
-        <v>207.7251862691963</v>
+        <v>207.1066069625242</v>
       </c>
       <c r="E146" t="n">
-        <v>212.6838531494141</v>
+        <v>208.7727966308594</v>
       </c>
       <c r="F146" t="n">
-        <v>180275400</v>
+        <v>123711800</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B147" t="n">
-        <v>212.2149257168926</v>
+        <v>209.4512425942353</v>
       </c>
       <c r="C147" t="n">
-        <v>212.2348843687743</v>
+        <v>209.820409153207</v>
       </c>
       <c r="D147" t="n">
-        <v>207.1066069625242</v>
+        <v>198.2468571251534</v>
       </c>
       <c r="E147" t="n">
-        <v>208.7727966308594</v>
+        <v>199.1148834228516</v>
       </c>
       <c r="F147" t="n">
-        <v>123711800</v>
+        <v>225239200</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B148" t="n">
-        <v>209.4512425942353</v>
+        <v>200.8209691272831</v>
       </c>
       <c r="C148" t="n">
-        <v>209.820409153207</v>
+        <v>202.5370477944956</v>
       </c>
       <c r="D148" t="n">
-        <v>198.2468571251534</v>
+        <v>196.6704525729091</v>
       </c>
       <c r="E148" t="n">
-        <v>199.1148834228516</v>
+        <v>197.9974212646484</v>
       </c>
       <c r="F148" t="n">
-        <v>225239200</v>
+        <v>128647000</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B149" t="n">
-        <v>200.8209691272831</v>
+        <v>199.0450218084295</v>
       </c>
       <c r="C149" t="n">
-        <v>202.5370477944956</v>
+        <v>201.2699318245734</v>
       </c>
       <c r="D149" t="n">
-        <v>196.6704525729091</v>
+        <v>194.2958829090753</v>
       </c>
       <c r="E149" t="n">
-        <v>197.9974212646484</v>
+        <v>198.02734375</v>
       </c>
       <c r="F149" t="n">
-        <v>128647000</v>
+        <v>125368100</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B150" t="n">
-        <v>199.0450218084295</v>
+        <v>198.8454820247872</v>
       </c>
       <c r="C150" t="n">
-        <v>201.2699318245734</v>
+        <v>199.7833407086998</v>
       </c>
       <c r="D150" t="n">
-        <v>194.2958829090753</v>
+        <v>195.5829352820671</v>
       </c>
       <c r="E150" t="n">
-        <v>198.02734375</v>
+        <v>196.0518646240234</v>
       </c>
       <c r="F150" t="n">
-        <v>125368100</v>
+        <v>113406600</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B151" t="n">
-        <v>198.8454820247872</v>
+        <v>199.4341385249406</v>
       </c>
       <c r="C151" t="n">
-        <v>199.7833407086998</v>
+        <v>207.7950323152332</v>
       </c>
       <c r="D151" t="n">
-        <v>195.5829352820671</v>
+        <v>198.1570588579161</v>
       </c>
       <c r="E151" t="n">
-        <v>196.0518646240234</v>
+        <v>207.3560333251953</v>
       </c>
       <c r="F151" t="n">
-        <v>113406600</v>
+        <v>188362800</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B152" t="n">
-        <v>199.4341385249406</v>
+        <v>207.8648724722903</v>
       </c>
       <c r="C152" t="n">
-        <v>207.7950323152332</v>
+        <v>213.7115092245668</v>
       </c>
       <c r="D152" t="n">
-        <v>198.1570588579161</v>
+        <v>206.0290722858257</v>
       </c>
       <c r="E152" t="n">
-        <v>207.3560333251953</v>
+        <v>211.0176696777344</v>
       </c>
       <c r="F152" t="n">
-        <v>188362800</v>
+        <v>168307900</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B153" t="n">
-        <v>207.8648724722903</v>
+        <v>212.5441790763045</v>
       </c>
       <c r="C153" t="n">
-        <v>213.7115092245668</v>
+        <v>217.3033052467507</v>
       </c>
       <c r="D153" t="n">
-        <v>206.0290722858257</v>
+        <v>212.4044989584125</v>
       </c>
       <c r="E153" t="n">
-        <v>211.0176696777344</v>
+        <v>214.709228515625</v>
       </c>
       <c r="F153" t="n">
-        <v>168307900</v>
+        <v>136421400</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B154" t="n">
-        <v>212.5441790763045</v>
+        <v>213.5518657378577</v>
       </c>
       <c r="C154" t="n">
-        <v>217.3033052467507</v>
+        <v>221.7930381906342</v>
       </c>
       <c r="D154" t="n">
-        <v>212.4044989584125</v>
+        <v>213.402213909002</v>
       </c>
       <c r="E154" t="n">
-        <v>214.709228515625</v>
+        <v>218.9395599365234</v>
       </c>
       <c r="F154" t="n">
-        <v>136421400</v>
+        <v>160685800</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B155" t="n">
-        <v>213.5518657378577</v>
+        <v>218.0515943496244</v>
       </c>
       <c r="C155" t="n">
-        <v>221.7930381906342</v>
+        <v>223.239732575863</v>
       </c>
       <c r="D155" t="n">
-        <v>213.402213909002</v>
+        <v>214.4298677829735</v>
       </c>
       <c r="E155" t="n">
-        <v>218.9395599365234</v>
+        <v>220.2765045166016</v>
       </c>
       <c r="F155" t="n">
-        <v>160685800</v>
+        <v>159176600</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B156" t="n">
-        <v>218.0515943496244</v>
+        <v>224.4170305354026</v>
       </c>
       <c r="C156" t="n">
-        <v>223.239732575863</v>
+        <v>227.3203978139454</v>
       </c>
       <c r="D156" t="n">
-        <v>214.4298677829735</v>
+        <v>221.0647077692387</v>
       </c>
       <c r="E156" t="n">
-        <v>220.2765045166016</v>
+        <v>225.3149871826172</v>
       </c>
       <c r="F156" t="n">
-        <v>159176600</v>
+        <v>150405400</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B157" t="n">
-        <v>224.4170305354026</v>
+        <v>229.3258255277811</v>
       </c>
       <c r="C157" t="n">
-        <v>227.3203978139454</v>
+        <v>236.0005559723521</v>
       </c>
       <c r="D157" t="n">
-        <v>221.0647077692387</v>
+        <v>228.7770767762568</v>
       </c>
       <c r="E157" t="n">
-        <v>225.3149871826172</v>
+        <v>235.202392578125</v>
       </c>
       <c r="F157" t="n">
-        <v>150405400</v>
+        <v>180782900</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B158" t="n">
-        <v>229.3258255277811</v>
+        <v>229.2360294447337</v>
       </c>
       <c r="C158" t="n">
-        <v>236.0005559723521</v>
+        <v>230.9720668751014</v>
       </c>
       <c r="D158" t="n">
-        <v>228.7770767762568</v>
+        <v>223.7286287034134</v>
       </c>
       <c r="E158" t="n">
-        <v>235.202392578125</v>
+        <v>224.8061676025391</v>
       </c>
       <c r="F158" t="n">
-        <v>180782900</v>
+        <v>180977600</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B159" t="n">
-        <v>229.2360294447337</v>
+        <v>229.345773483712</v>
       </c>
       <c r="C159" t="n">
-        <v>230.9720668751014</v>
+        <v>229.4754818886306</v>
       </c>
       <c r="D159" t="n">
-        <v>223.7286287034134</v>
+        <v>217.8719993892805</v>
       </c>
       <c r="E159" t="n">
-        <v>224.8061676025391</v>
+        <v>221.8130035400391</v>
       </c>
       <c r="F159" t="n">
-        <v>180977600</v>
+        <v>146280900</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B160" t="n">
-        <v>229.345773483712</v>
+        <v>219.1191400841904</v>
       </c>
       <c r="C160" t="n">
-        <v>229.4754818886306</v>
+        <v>223.9680572056967</v>
       </c>
       <c r="D160" t="n">
-        <v>217.8719993892805</v>
+        <v>217.4130483552105</v>
       </c>
       <c r="E160" t="n">
-        <v>221.8130035400391</v>
+        <v>220.1068878173828</v>
       </c>
       <c r="F160" t="n">
-        <v>146280900</v>
+        <v>140948200</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B161" t="n">
-        <v>219.1191400841904</v>
+        <v>222.6710257508039</v>
       </c>
       <c r="C161" t="n">
-        <v>223.9680572056967</v>
+        <v>225.6143103895453</v>
       </c>
       <c r="D161" t="n">
-        <v>217.4130483552105</v>
+        <v>219.9971448577806</v>
       </c>
       <c r="E161" t="n">
-        <v>220.1068878173828</v>
+        <v>222.9603729248047</v>
       </c>
       <c r="F161" t="n">
-        <v>140948200</v>
+        <v>184201600</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B162" t="n">
-        <v>222.6710257508039</v>
+        <v>221.7830583738447</v>
       </c>
       <c r="C162" t="n">
-        <v>225.6143103895453</v>
+        <v>226.8814055684356</v>
       </c>
       <c r="D162" t="n">
-        <v>219.9971448577806</v>
+        <v>217.4330007955402</v>
       </c>
       <c r="E162" t="n">
-        <v>222.9603729248047</v>
+        <v>219.0093994140625</v>
       </c>
       <c r="F162" t="n">
-        <v>184201600</v>
+        <v>203381800</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B163" t="n">
-        <v>221.7830583738447</v>
+        <v>220.3962175709585</v>
       </c>
       <c r="C163" t="n">
-        <v>226.8814055684356</v>
+        <v>220.5059673180016</v>
       </c>
       <c r="D163" t="n">
-        <v>217.4330007955402</v>
+        <v>214.3101381389001</v>
       </c>
       <c r="E163" t="n">
-        <v>219.0093994140625</v>
+        <v>214.8389282226562</v>
       </c>
       <c r="F163" t="n">
-        <v>203381800</v>
+        <v>169275700</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B164" t="n">
-        <v>220.3962175709585</v>
+        <v>216.0461718127993</v>
       </c>
       <c r="C164" t="n">
-        <v>220.5059673180016</v>
+        <v>217.6824311685512</v>
       </c>
       <c r="D164" t="n">
-        <v>214.3101381389001</v>
+        <v>211.5165320236786</v>
       </c>
       <c r="E164" t="n">
-        <v>214.8389282226562</v>
+        <v>214.3700103759766</v>
       </c>
       <c r="F164" t="n">
-        <v>169275700</v>
+        <v>187202600</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B165" t="n">
-        <v>216.0461718127993</v>
+        <v>213.6316806617713</v>
       </c>
       <c r="C165" t="n">
-        <v>217.6824311685512</v>
+        <v>213.6616110269177</v>
       </c>
       <c r="D165" t="n">
-        <v>211.5165320236786</v>
+        <v>208.3038625298546</v>
       </c>
       <c r="E165" t="n">
-        <v>214.3700103759766</v>
+        <v>212.1151580810547</v>
       </c>
       <c r="F165" t="n">
-        <v>187202600</v>
+        <v>167601200</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B166" t="n">
-        <v>213.6316806617713</v>
+        <v>210.7981551984497</v>
       </c>
       <c r="C166" t="n">
-        <v>213.6616110269177</v>
+        <v>215.0284909668814</v>
       </c>
       <c r="D166" t="n">
-        <v>208.3038625298546</v>
+        <v>210.7382944698381</v>
       </c>
       <c r="E166" t="n">
-        <v>212.1151580810547</v>
+        <v>213.7613830566406</v>
       </c>
       <c r="F166" t="n">
-        <v>167601200</v>
+        <v>143996000</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B167" t="n">
-        <v>210.7981551984497</v>
+        <v>214.0906505321041</v>
       </c>
       <c r="C167" t="n">
-        <v>215.0284909668814</v>
+        <v>217.3631692496548</v>
       </c>
       <c r="D167" t="n">
-        <v>210.7382944698381</v>
+        <v>210.6485213277038</v>
       </c>
       <c r="E167" t="n">
-        <v>213.7613830566406</v>
+        <v>210.6584930419922</v>
       </c>
       <c r="F167" t="n">
-        <v>143996000</v>
+        <v>289410600</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B168" t="n">
-        <v>214.0906505321041</v>
+        <v>215.2380189209027</v>
       </c>
       <c r="C168" t="n">
-        <v>217.3631692496548</v>
+        <v>224.3571743491113</v>
       </c>
       <c r="D168" t="n">
-        <v>210.6485213277038</v>
+        <v>215.2080885544549</v>
       </c>
       <c r="E168" t="n">
-        <v>210.6584930419922</v>
+        <v>223.8483428955078</v>
       </c>
       <c r="F168" t="n">
-        <v>289410600</v>
+        <v>212850700</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B169" t="n">
-        <v>215.2380189209027</v>
+        <v>226.6618858382332</v>
       </c>
       <c r="C169" t="n">
-        <v>224.3571743491113</v>
+        <v>231.7502608645459</v>
       </c>
       <c r="D169" t="n">
-        <v>215.2080885544549</v>
+        <v>220.8451951370975</v>
       </c>
       <c r="E169" t="n">
-        <v>223.8483428955078</v>
+        <v>222.3118438720703</v>
       </c>
       <c r="F169" t="n">
-        <v>212850700</v>
+        <v>193362900</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B170" t="n">
-        <v>226.6618858382332</v>
+        <v>221.2143597561905</v>
       </c>
       <c r="C170" t="n">
-        <v>231.7502608645459</v>
+        <v>222.3118572511273</v>
       </c>
       <c r="D170" t="n">
-        <v>220.8451951370975</v>
+        <v>214.0207957553572</v>
       </c>
       <c r="E170" t="n">
-        <v>222.3118438720703</v>
+        <v>214.26025390625</v>
       </c>
       <c r="F170" t="n">
-        <v>193362900</v>
+        <v>160907000</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,25 +4863,25 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B171" t="n">
-        <v>221.2143597561905</v>
+        <v>213.6709127939037</v>
       </c>
       <c r="C171" t="n">
-        <v>222.3118572511273</v>
+        <v>221.3523199881091</v>
       </c>
       <c r="D171" t="n">
-        <v>214.0207957553572</v>
+        <v>210.73419644349</v>
       </c>
       <c r="E171" t="n">
-        <v>214.26025390625</v>
+        <v>218.4156036376953</v>
       </c>
       <c r="F171" t="n">
-        <v>160907000</v>
+        <v>169022200</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -4889,25 +4889,25 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B172" t="n">
-        <v>213.6709127939037</v>
+        <v>214.2902104723603</v>
       </c>
       <c r="C172" t="n">
-        <v>221.3523199881091</v>
+        <v>214.6298267834636</v>
       </c>
       <c r="D172" t="n">
-        <v>210.73419644349</v>
+        <v>204.101614447126</v>
       </c>
       <c r="E172" t="n">
-        <v>218.4156036376953</v>
+        <v>204.8707580566406</v>
       </c>
       <c r="F172" t="n">
-        <v>169022200</v>
+        <v>219655500</v>
       </c>
       <c r="G172" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B173" t="n">
-        <v>214.2902104723603</v>
+        <v>209.9450713288228</v>
       </c>
       <c r="C173" t="n">
-        <v>214.6298267834636</v>
+        <v>210.2347557268212</v>
       </c>
       <c r="D173" t="n">
-        <v>204.101614447126</v>
+        <v>205.7697506938822</v>
       </c>
       <c r="E173" t="n">
-        <v>204.8707580566406</v>
+        <v>208.4067993164062</v>
       </c>
       <c r="F173" t="n">
-        <v>219655500</v>
+        <v>138372800</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B174" t="n">
-        <v>209.9450713288228</v>
+        <v>210.3845825512031</v>
       </c>
       <c r="C174" t="n">
-        <v>210.2347557268212</v>
+        <v>211.1637095162451</v>
       </c>
       <c r="D174" t="n">
-        <v>205.7697506938822</v>
+        <v>199.1171915656509</v>
       </c>
       <c r="E174" t="n">
-        <v>208.4067993164062</v>
+        <v>207.9573059082031</v>
       </c>
       <c r="F174" t="n">
-        <v>138372800</v>
+        <v>180962500</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B175" t="n">
-        <v>210.3845825512031</v>
+        <v>204.2014963256503</v>
       </c>
       <c r="C175" t="n">
-        <v>211.1637095162451</v>
+        <v>206.9883864105018</v>
       </c>
       <c r="D175" t="n">
-        <v>199.1171915656509</v>
+        <v>199.696542748819</v>
       </c>
       <c r="E175" t="n">
-        <v>207.9573059082031</v>
+        <v>200.1959838867188</v>
       </c>
       <c r="F175" t="n">
-        <v>180962500</v>
+        <v>161746600</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B176" t="n">
-        <v>204.2014963256503</v>
+        <v>201.2647947500858</v>
       </c>
       <c r="C176" t="n">
-        <v>206.9883864105018</v>
+        <v>205.4301320010667</v>
       </c>
       <c r="D176" t="n">
-        <v>199.696542748819</v>
+        <v>199.3169621236104</v>
       </c>
       <c r="E176" t="n">
-        <v>200.1959838867188</v>
+        <v>204.6410064697266</v>
       </c>
       <c r="F176" t="n">
-        <v>161746600</v>
+        <v>158643200</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B177" t="n">
-        <v>201.2647947500858</v>
+        <v>204.6310298517525</v>
       </c>
       <c r="C177" t="n">
-        <v>205.4301320010667</v>
+        <v>206.8385664547524</v>
       </c>
       <c r="D177" t="n">
-        <v>199.3169621236104</v>
+        <v>203.2126188059985</v>
       </c>
       <c r="E177" t="n">
-        <v>204.6410064697266</v>
+        <v>204.9606628417969</v>
       </c>
       <c r="F177" t="n">
-        <v>158643200</v>
+        <v>112001800</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B178" t="n">
-        <v>204.6310298517525</v>
+        <v>208.6864864049894</v>
       </c>
       <c r="C178" t="n">
-        <v>206.8385664547524</v>
+        <v>212.4722588232193</v>
       </c>
       <c r="D178" t="n">
-        <v>203.2126188059985</v>
+        <v>208.1071328472061</v>
       </c>
       <c r="E178" t="n">
-        <v>204.9606628417969</v>
+        <v>212.2125396728516</v>
       </c>
       <c r="F178" t="n">
-        <v>112001800</v>
+        <v>149936700</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B179" t="n">
-        <v>208.6864864049894</v>
+        <v>210.9439520928381</v>
       </c>
       <c r="C179" t="n">
-        <v>212.4722588232193</v>
+        <v>211.2536184019877</v>
       </c>
       <c r="D179" t="n">
-        <v>208.1071328472061</v>
+        <v>207.0583006421773</v>
       </c>
       <c r="E179" t="n">
-        <v>212.2125396728516</v>
+        <v>207.1781768798828</v>
       </c>
       <c r="F179" t="n">
-        <v>149936700</v>
+        <v>125694100</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B180" t="n">
-        <v>210.9439520928381</v>
+        <v>208.2969174543329</v>
       </c>
       <c r="C180" t="n">
-        <v>211.2536184019877</v>
+        <v>208.9761653200819</v>
       </c>
       <c r="D180" t="n">
-        <v>207.0583006421773</v>
+        <v>202.8530121596522</v>
       </c>
       <c r="E180" t="n">
-        <v>207.1781768798828</v>
+        <v>204.4212493896484</v>
       </c>
       <c r="F180" t="n">
-        <v>125694100</v>
+        <v>128363500</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B181" t="n">
-        <v>208.2969174543329</v>
+        <v>207.0982684229139</v>
       </c>
       <c r="C181" t="n">
-        <v>208.9761653200819</v>
+        <v>211.1537281092123</v>
       </c>
       <c r="D181" t="n">
-        <v>202.8530121596522</v>
+        <v>206.2691942875683</v>
       </c>
       <c r="E181" t="n">
-        <v>204.4212493896484</v>
+        <v>210.4545135498047</v>
       </c>
       <c r="F181" t="n">
-        <v>128363500</v>
+        <v>241272000</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B182" t="n">
-        <v>207.0982684229139</v>
+        <v>211.2036686200953</v>
       </c>
       <c r="C182" t="n">
-        <v>211.1537281092123</v>
+        <v>213.7508214450341</v>
       </c>
       <c r="D182" t="n">
-        <v>206.2691942875683</v>
+        <v>207.4878253737282</v>
       </c>
       <c r="E182" t="n">
-        <v>210.4545135498047</v>
+        <v>208.4167785644531</v>
       </c>
       <c r="F182" t="n">
-        <v>241272000</v>
+        <v>122041400</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B183" t="n">
-        <v>211.2036686200953</v>
+        <v>201.9440304014853</v>
       </c>
       <c r="C183" t="n">
-        <v>213.7508214450341</v>
+        <v>203.5422481594977</v>
       </c>
       <c r="D183" t="n">
-        <v>207.4878253737282</v>
+        <v>199.77645766483</v>
       </c>
       <c r="E183" t="n">
-        <v>208.4167785644531</v>
+        <v>199.81640625</v>
       </c>
       <c r="F183" t="n">
-        <v>122041400</v>
+        <v>153496200</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B184" t="n">
-        <v>201.9440304014853</v>
+        <v>199.8963159019567</v>
       </c>
       <c r="C184" t="n">
-        <v>203.5422481594977</v>
+        <v>201.4445864758279</v>
       </c>
       <c r="D184" t="n">
-        <v>199.77645766483</v>
+        <v>196.360279356477</v>
       </c>
       <c r="E184" t="n">
-        <v>199.81640625</v>
+        <v>198.7775726318359</v>
       </c>
       <c r="F184" t="n">
-        <v>153496200</v>
+        <v>151810700</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B185" t="n">
-        <v>199.8963159019567</v>
+        <v>199.8563704571445</v>
       </c>
       <c r="C185" t="n">
-        <v>201.4445864758279</v>
+        <v>200.5755669254449</v>
       </c>
       <c r="D185" t="n">
-        <v>196.360279356477</v>
+        <v>191.9152592982058</v>
       </c>
       <c r="E185" t="n">
-        <v>198.7775726318359</v>
+        <v>195.5212249755859</v>
       </c>
       <c r="F185" t="n">
-        <v>151810700</v>
+        <v>149550000</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B186" t="n">
-        <v>199.8563704571445</v>
+        <v>192.9041409641119</v>
       </c>
       <c r="C186" t="n">
-        <v>200.5755669254449</v>
+        <v>195.331432829306</v>
       </c>
       <c r="D186" t="n">
-        <v>191.9152592982058</v>
+        <v>191.0062707295152</v>
       </c>
       <c r="E186" t="n">
-        <v>195.5212249755859</v>
+        <v>192.3148040771484</v>
       </c>
       <c r="F186" t="n">
-        <v>149550000</v>
+        <v>179304100</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B187" t="n">
-        <v>192.9041409641119</v>
+        <v>193.6333319429392</v>
       </c>
       <c r="C187" t="n">
-        <v>195.331432829306</v>
+        <v>195.9607141929515</v>
       </c>
       <c r="D187" t="n">
-        <v>191.0062707295152</v>
+        <v>189.5878557469149</v>
       </c>
       <c r="E187" t="n">
-        <v>192.3148040771484</v>
+        <v>194.7520751953125</v>
       </c>
       <c r="F187" t="n">
-        <v>179304100</v>
+        <v>148835700</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B188" t="n">
-        <v>193.6333319429392</v>
+        <v>197.0195429632178</v>
       </c>
       <c r="C188" t="n">
-        <v>195.9607141929515</v>
+        <v>200.4057532237791</v>
       </c>
       <c r="D188" t="n">
-        <v>189.5878557469149</v>
+        <v>194.8919188665145</v>
       </c>
       <c r="E188" t="n">
-        <v>194.7520751953125</v>
+        <v>199.8663482666016</v>
       </c>
       <c r="F188" t="n">
-        <v>148835700</v>
+        <v>166476700</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B189" t="n">
-        <v>197.0195429632178</v>
+        <v>195.9806989625188</v>
       </c>
       <c r="C189" t="n">
-        <v>200.4057532237791</v>
+        <v>199.626628404907</v>
       </c>
       <c r="D189" t="n">
-        <v>194.8919188665145</v>
+        <v>193.2337727110923</v>
       </c>
       <c r="E189" t="n">
-        <v>199.8663482666016</v>
+        <v>197.3591613769531</v>
       </c>
       <c r="F189" t="n">
-        <v>166476700</v>
+        <v>146147600</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B190" t="n">
-        <v>195.9806989625188</v>
+        <v>196.9196593659626</v>
       </c>
       <c r="C190" t="n">
-        <v>199.626628404907</v>
+        <v>199.8363939026278</v>
       </c>
       <c r="D190" t="n">
-        <v>193.2337727110923</v>
+        <v>192.1350197738411</v>
       </c>
       <c r="E190" t="n">
-        <v>197.3591613769531</v>
+        <v>194.6122436523438</v>
       </c>
       <c r="F190" t="n">
-        <v>146147600</v>
+        <v>142068700</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B191" t="n">
-        <v>196.9196593659626</v>
+        <v>194.202694284663</v>
       </c>
       <c r="C191" t="n">
-        <v>199.8363939026278</v>
+        <v>197.3292007505161</v>
       </c>
       <c r="D191" t="n">
-        <v>192.1350197738411</v>
+        <v>193.7731822131383</v>
       </c>
       <c r="E191" t="n">
-        <v>194.6122436523438</v>
+        <v>195.3314361572266</v>
       </c>
       <c r="F191" t="n">
-        <v>142068700</v>
+        <v>108999000</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B192" t="n">
-        <v>194.202694284663</v>
+        <v>192.1549837798622</v>
       </c>
       <c r="C192" t="n">
-        <v>197.3292007505161</v>
+        <v>198.1882414262674</v>
       </c>
       <c r="D192" t="n">
-        <v>193.7731822131383</v>
+        <v>190.9263628146717</v>
       </c>
       <c r="E192" t="n">
-        <v>195.3314361572266</v>
+        <v>196.7098846435547</v>
       </c>
       <c r="F192" t="n">
-        <v>108999000</v>
+        <v>124154600</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B193" t="n">
-        <v>192.1549837798622</v>
+        <v>194.9618356993413</v>
       </c>
       <c r="C193" t="n">
-        <v>198.1882414262674</v>
+        <v>204.9306918075912</v>
       </c>
       <c r="D193" t="n">
-        <v>190.9263628146717</v>
+        <v>194.841974703339</v>
       </c>
       <c r="E193" t="n">
-        <v>196.7098846435547</v>
+        <v>203.891845703125</v>
       </c>
       <c r="F193" t="n">
-        <v>124154600</v>
+        <v>147419100</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B194" t="n">
-        <v>194.9618356993413</v>
+        <v>204.2314748595287</v>
       </c>
       <c r="C194" t="n">
-        <v>204.9306918075912</v>
+        <v>204.3613191897594</v>
       </c>
       <c r="D194" t="n">
-        <v>194.841974703339</v>
+        <v>198.7376223952696</v>
       </c>
       <c r="E194" t="n">
-        <v>203.891845703125</v>
+        <v>202.5533447265625</v>
       </c>
       <c r="F194" t="n">
-        <v>147419100</v>
+        <v>132037400</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B195" t="n">
-        <v>204.2314748595287</v>
+        <v>201.7742207048944</v>
       </c>
       <c r="C195" t="n">
-        <v>204.3613191897594</v>
+        <v>210.7641612313501</v>
       </c>
       <c r="D195" t="n">
-        <v>198.7376223952696</v>
+        <v>201.6943082934289</v>
       </c>
       <c r="E195" t="n">
-        <v>202.5533447265625</v>
+        <v>210.7242126464844</v>
       </c>
       <c r="F195" t="n">
-        <v>132037400</v>
+        <v>148421000</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B196" t="n">
-        <v>201.7742207048944</v>
+        <v>208.3069001369788</v>
       </c>
       <c r="C196" t="n">
-        <v>210.7641612313501</v>
+        <v>210.3346451505122</v>
       </c>
       <c r="D196" t="n">
-        <v>201.6943082934289</v>
+        <v>202.7730991138312</v>
       </c>
       <c r="E196" t="n">
-        <v>210.7242126464844</v>
+        <v>203.3025054931641</v>
       </c>
       <c r="F196" t="n">
-        <v>148421000</v>
+        <v>121411000</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B197" t="n">
-        <v>208.3069001369788</v>
+        <v>207.9672957533915</v>
       </c>
       <c r="C197" t="n">
-        <v>210.3346451505122</v>
+        <v>212.3124399374416</v>
       </c>
       <c r="D197" t="n">
-        <v>202.7730991138312</v>
+        <v>203.5722196467825</v>
       </c>
       <c r="E197" t="n">
-        <v>203.3025054931641</v>
+        <v>211.5632781982422</v>
       </c>
       <c r="F197" t="n">
-        <v>121411000</v>
+        <v>124379600</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B198" t="n">
-        <v>207.9672957533915</v>
+        <v>211.7230919717581</v>
       </c>
       <c r="C198" t="n">
-        <v>212.3124399374416</v>
+        <v>213.5710150202495</v>
       </c>
       <c r="D198" t="n">
-        <v>203.5722196467825</v>
+        <v>205.8096955397309</v>
       </c>
       <c r="E198" t="n">
-        <v>211.5632781982422</v>
+        <v>212.2624816894531</v>
       </c>
       <c r="F198" t="n">
-        <v>124379600</v>
+        <v>124797200</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B199" t="n">
-        <v>211.7230919717581</v>
+        <v>209.9350906043833</v>
       </c>
       <c r="C199" t="n">
-        <v>213.5710150202495</v>
+        <v>210.8440771529852</v>
       </c>
       <c r="D199" t="n">
-        <v>205.8096955397309</v>
+        <v>205.6199270055466</v>
       </c>
       <c r="E199" t="n">
-        <v>212.2624816894531</v>
+        <v>207.1681823730469</v>
       </c>
       <c r="F199" t="n">
-        <v>124797200</v>
+        <v>122986100</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B200" t="n">
-        <v>209.9350906043833</v>
+        <v>202.4135048295048</v>
       </c>
       <c r="C200" t="n">
-        <v>210.8440771529852</v>
+        <v>206.4190172896336</v>
       </c>
       <c r="D200" t="n">
-        <v>205.6199270055466</v>
+        <v>197.7487264058434</v>
       </c>
       <c r="E200" t="n">
-        <v>207.1681823730469</v>
+        <v>202.5833129882812</v>
       </c>
       <c r="F200" t="n">
-        <v>122986100</v>
+        <v>144281900</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B201" t="n">
-        <v>202.4135048295048</v>
+        <v>205.639896943356</v>
       </c>
       <c r="C201" t="n">
-        <v>206.4190172896336</v>
+        <v>207.5078172334397</v>
       </c>
       <c r="D201" t="n">
-        <v>197.7487264058434</v>
+        <v>202.0539130969454</v>
       </c>
       <c r="E201" t="n">
-        <v>202.5833129882812</v>
+        <v>203.0527954101562</v>
       </c>
       <c r="F201" t="n">
-        <v>144281900</v>
+        <v>88701500</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B202" t="n">
-        <v>205.639896943356</v>
+        <v>207.308024406286</v>
       </c>
       <c r="C202" t="n">
-        <v>207.5078172334397</v>
+        <v>208.4167843613107</v>
       </c>
       <c r="D202" t="n">
-        <v>202.0539130969454</v>
+        <v>203.7819711309363</v>
       </c>
       <c r="E202" t="n">
-        <v>203.0527954101562</v>
+        <v>207.0583038330078</v>
       </c>
       <c r="F202" t="n">
-        <v>88701500</v>
+        <v>108685600</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B203" t="n">
-        <v>207.308024406286</v>
+        <v>205.579968274895</v>
       </c>
       <c r="C203" t="n">
-        <v>208.4167843613107</v>
+        <v>214.1503804276117</v>
       </c>
       <c r="D203" t="n">
-        <v>203.7819711309363</v>
+        <v>204.7209288682105</v>
       </c>
       <c r="E203" t="n">
-        <v>207.0583038330078</v>
+        <v>211.8229827880859</v>
       </c>
       <c r="F203" t="n">
-        <v>108685600</v>
+        <v>137645600</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B204" t="n">
-        <v>205.579968274895</v>
+        <v>209.2258868865651</v>
       </c>
       <c r="C204" t="n">
-        <v>214.1503804276117</v>
+        <v>210.6342993029147</v>
       </c>
       <c r="D204" t="n">
-        <v>204.7209288682105</v>
+        <v>205.7297989431358</v>
       </c>
       <c r="E204" t="n">
-        <v>211.8229827880859</v>
+        <v>208.5266571044922</v>
       </c>
       <c r="F204" t="n">
-        <v>137645600</v>
+        <v>110505300</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B205" t="n">
-        <v>209.2258868865651</v>
+        <v>207.2181292349697</v>
       </c>
       <c r="C205" t="n">
-        <v>210.6342993029147</v>
+        <v>211.6731509810223</v>
       </c>
       <c r="D205" t="n">
-        <v>205.7297989431358</v>
+        <v>204.5810805834776</v>
       </c>
       <c r="E205" t="n">
-        <v>208.5266571044922</v>
+        <v>206.6088104248047</v>
       </c>
       <c r="F205" t="n">
-        <v>110505300</v>
+        <v>114836800</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B206" t="n">
-        <v>207.2181292349697</v>
+        <v>207.9672962732577</v>
       </c>
       <c r="C206" t="n">
-        <v>211.6731509810223</v>
+        <v>208.5166845983908</v>
       </c>
       <c r="D206" t="n">
-        <v>204.5810805834776</v>
+        <v>195.2215633388429</v>
       </c>
       <c r="E206" t="n">
-        <v>206.6088104248047</v>
+        <v>196.2903594970703</v>
       </c>
       <c r="F206" t="n">
-        <v>114836800</v>
+        <v>154353700</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B207" t="n">
-        <v>207.9672962732577</v>
+        <v>194.782047001347</v>
       </c>
       <c r="C207" t="n">
-        <v>208.5166845983908</v>
+        <v>198.4779084345641</v>
       </c>
       <c r="D207" t="n">
-        <v>195.2215633388429</v>
+        <v>192.5245785077403</v>
       </c>
       <c r="E207" t="n">
-        <v>196.2903594970703</v>
+        <v>196.789794921875</v>
       </c>
       <c r="F207" t="n">
-        <v>154353700</v>
+        <v>134111500</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B208" t="n">
-        <v>194.782047001347</v>
+        <v>195.6311069684468</v>
       </c>
       <c r="C208" t="n">
-        <v>198.4779084345641</v>
+        <v>196.8497446088402</v>
       </c>
       <c r="D208" t="n">
-        <v>192.5245785077403</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="E208" t="n">
-        <v>196.789794921875</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="F208" t="n">
-        <v>134111500</v>
+        <v>147680800</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B209" t="n">
-        <v>195.6311069684468</v>
+        <v>193.2337718176948</v>
       </c>
       <c r="C209" t="n">
-        <v>196.8497446088402</v>
+        <v>197.0295274868271</v>
       </c>
       <c r="D209" t="n">
-        <v>189.7976226806641</v>
+        <v>191.3059363552755</v>
       </c>
       <c r="E209" t="n">
-        <v>189.7976226806641</v>
+        <v>194.8219909667969</v>
       </c>
       <c r="F209" t="n">
-        <v>147680800</v>
+        <v>129010200</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B210" t="n">
-        <v>193.2337718176948</v>
+        <v>198.2182038580375</v>
       </c>
       <c r="C210" t="n">
-        <v>197.0295274868271</v>
+        <v>201.7742223680242</v>
       </c>
       <c r="D210" t="n">
-        <v>191.3059363552755</v>
+        <v>194.7320991825756</v>
       </c>
       <c r="E210" t="n">
-        <v>194.8219909667969</v>
+        <v>200.5256195068359</v>
       </c>
       <c r="F210" t="n">
-        <v>129010200</v>
+        <v>139961200</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B211" t="n">
-        <v>198.2182038580375</v>
+        <v>197.4690486270115</v>
       </c>
       <c r="C211" t="n">
-        <v>201.7742223680242</v>
+        <v>208.506701330784</v>
       </c>
       <c r="D211" t="n">
-        <v>194.7320991825756</v>
+        <v>196.6299911347511</v>
       </c>
       <c r="E211" t="n">
-        <v>200.5256195068359</v>
+        <v>206.4090423583984</v>
       </c>
       <c r="F211" t="n">
-        <v>139961200</v>
+        <v>128406900</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B212" t="n">
-        <v>197.4690486270115</v>
+        <v>211.0638257011038</v>
       </c>
       <c r="C212" t="n">
-        <v>208.506701330784</v>
+        <v>212.8218530009649</v>
       </c>
       <c r="D212" t="n">
-        <v>196.6299911347511</v>
+        <v>208.8163406042335</v>
       </c>
       <c r="E212" t="n">
-        <v>206.4090423583984</v>
+        <v>211.7031097412109</v>
       </c>
       <c r="F212" t="n">
-        <v>128406900</v>
+        <v>134922000</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B213" t="n">
-        <v>211.0638257011038</v>
+        <v>216.6176127852948</v>
       </c>
       <c r="C213" t="n">
-        <v>212.8218530009649</v>
+        <v>221.9716224388697</v>
       </c>
       <c r="D213" t="n">
-        <v>208.8163406042335</v>
+        <v>216.1581202281489</v>
       </c>
       <c r="E213" t="n">
-        <v>211.7031097412109</v>
+        <v>218.9749755859375</v>
       </c>
       <c r="F213" t="n">
-        <v>134922000</v>
+        <v>158187400</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B214" t="n">
-        <v>216.6176127852948</v>
+        <v>221.2823935806188</v>
       </c>
       <c r="C214" t="n">
-        <v>221.9716224388697</v>
+        <v>223.3800524967045</v>
       </c>
       <c r="D214" t="n">
-        <v>216.1581202281489</v>
+        <v>216.7574580038405</v>
       </c>
       <c r="E214" t="n">
-        <v>218.9749755859375</v>
+        <v>218.7452392578125</v>
       </c>
       <c r="F214" t="n">
-        <v>158187400</v>
+        <v>113940600</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B215" t="n">
-        <v>221.2823935806188</v>
+        <v>221.2923777041913</v>
       </c>
       <c r="C215" t="n">
-        <v>223.3800524967045</v>
+        <v>224.5087799247126</v>
       </c>
       <c r="D215" t="n">
-        <v>216.7574580038405</v>
+        <v>220.4133716458871</v>
       </c>
       <c r="E215" t="n">
-        <v>218.7452392578125</v>
+        <v>223.7096862792969</v>
       </c>
       <c r="F215" t="n">
-        <v>113940600</v>
+        <v>105669400</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B216" t="n">
-        <v>221.2923777041913</v>
+        <v>223.1502910726907</v>
       </c>
       <c r="C216" t="n">
-        <v>224.5087799247126</v>
+        <v>223.8894694330602</v>
       </c>
       <c r="D216" t="n">
-        <v>220.4133716458871</v>
+        <v>216.5277120448001</v>
       </c>
       <c r="E216" t="n">
-        <v>223.7096862792969</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="F216" t="n">
-        <v>105669400</v>
+        <v>115846600</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B217" t="n">
-        <v>223.1502910726907</v>
+        <v>221.9216754142795</v>
       </c>
       <c r="C217" t="n">
-        <v>223.8894694330602</v>
+        <v>221.9516406634887</v>
       </c>
       <c r="D217" t="n">
-        <v>216.5277120448001</v>
+        <v>215.9583469538982</v>
       </c>
       <c r="E217" t="n">
-        <v>217.3068389892578</v>
+        <v>217.2568969726562</v>
       </c>
       <c r="F217" t="n">
-        <v>115846600</v>
+        <v>101273100</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B218" t="n">
-        <v>221.9216754142795</v>
+        <v>220.7929293559802</v>
       </c>
       <c r="C218" t="n">
-        <v>221.9516406634887</v>
+        <v>224.848404158734</v>
       </c>
       <c r="D218" t="n">
-        <v>215.9583469538982</v>
+        <v>219.9538719106106</v>
       </c>
       <c r="E218" t="n">
-        <v>217.2568969726562</v>
+        <v>223.8395233154297</v>
       </c>
       <c r="F218" t="n">
-        <v>101273100</v>
+        <v>108783600</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B219" t="n">
-        <v>220.7929293559802</v>
+        <v>224.8084500146858</v>
       </c>
       <c r="C219" t="n">
-        <v>224.848404158734</v>
+        <v>226.9760227961096</v>
       </c>
       <c r="D219" t="n">
-        <v>219.9538719106106</v>
+        <v>223.4599680426375</v>
       </c>
       <c r="E219" t="n">
-        <v>223.8395233154297</v>
+        <v>225.0481872558594</v>
       </c>
       <c r="F219" t="n">
-        <v>108783600</v>
+        <v>98867200</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B220" t="n">
-        <v>224.8084500146858</v>
+        <v>226.5165415533859</v>
       </c>
       <c r="C220" t="n">
-        <v>226.9760227961096</v>
+        <v>227.2357380227387</v>
       </c>
       <c r="D220" t="n">
-        <v>223.4599680426375</v>
+        <v>224.2490744835724</v>
       </c>
       <c r="E220" t="n">
-        <v>225.0481872558594</v>
+        <v>224.9083404541016</v>
       </c>
       <c r="F220" t="n">
-        <v>98867200</v>
+        <v>75680900</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B221" t="n">
-        <v>226.5165415533859</v>
+        <v>225.7274161885591</v>
       </c>
       <c r="C221" t="n">
-        <v>227.2357380227387</v>
+        <v>227.6652502746616</v>
       </c>
       <c r="D221" t="n">
-        <v>224.2490744835724</v>
+        <v>224.6086728983284</v>
       </c>
       <c r="E221" t="n">
-        <v>224.9083404541016</v>
+        <v>224.7584991455078</v>
       </c>
       <c r="F221" t="n">
-        <v>75680900</v>
+        <v>93678700</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B222" t="n">
-        <v>225.7274161885591</v>
+        <v>220.203597915372</v>
       </c>
       <c r="C222" t="n">
-        <v>227.6652502746616</v>
+        <v>221.3922702798686</v>
       </c>
       <c r="D222" t="n">
-        <v>224.6086728983284</v>
+        <v>218.4455705709327</v>
       </c>
       <c r="E222" t="n">
-        <v>224.7584991455078</v>
+        <v>219.4944000244141</v>
       </c>
       <c r="F222" t="n">
-        <v>93678700</v>
+        <v>103128200</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B223" t="n">
-        <v>220.203597915372</v>
+        <v>221.4222404106533</v>
       </c>
       <c r="C223" t="n">
-        <v>221.3922702798686</v>
+        <v>222.6208961374568</v>
       </c>
       <c r="D223" t="n">
-        <v>218.4455705709327</v>
+        <v>216.5177245976465</v>
       </c>
       <c r="E223" t="n">
-        <v>219.4944000244141</v>
+        <v>217.3168334960938</v>
       </c>
       <c r="F223" t="n">
-        <v>103128200</v>
+        <v>96797300</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B224" t="n">
-        <v>221.4222404106533</v>
+        <v>218.1159423024499</v>
       </c>
       <c r="C224" t="n">
-        <v>222.6208961374568</v>
+        <v>219.6142657707553</v>
       </c>
       <c r="D224" t="n">
-        <v>216.5177245976465</v>
+        <v>215.418963107847</v>
       </c>
       <c r="E224" t="n">
-        <v>217.3168334960938</v>
+        <v>216.6076354980469</v>
       </c>
       <c r="F224" t="n">
-        <v>96797300</v>
+        <v>92457000</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B225" t="n">
-        <v>218.1159423024499</v>
+        <v>218.1758724878036</v>
       </c>
       <c r="C225" t="n">
-        <v>219.6142657707553</v>
+        <v>218.4955221432803</v>
       </c>
       <c r="D225" t="n">
-        <v>215.418963107847</v>
+        <v>214.2602556586216</v>
       </c>
       <c r="E225" t="n">
-        <v>216.6076354980469</v>
+        <v>214.4800109863281</v>
       </c>
       <c r="F225" t="n">
-        <v>92457000</v>
+        <v>98869300</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B226" t="n">
-        <v>218.1758724878036</v>
+        <v>215.2891020611033</v>
       </c>
       <c r="C226" t="n">
-        <v>218.4955221432803</v>
+        <v>215.3490325607492</v>
       </c>
       <c r="D226" t="n">
-        <v>214.2602556586216</v>
+        <v>207.0183577918231</v>
       </c>
       <c r="E226" t="n">
-        <v>214.4800109863281</v>
+        <v>208.2469787597656</v>
       </c>
       <c r="F226" t="n">
-        <v>98869300</v>
+        <v>135187300</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B227" t="n">
-        <v>215.2891020611033</v>
+        <v>210.7941279013131</v>
       </c>
       <c r="C227" t="n">
-        <v>215.3490325607492</v>
+        <v>214.4899893165327</v>
       </c>
       <c r="D227" t="n">
-        <v>207.0183577918231</v>
+        <v>209.8751580258669</v>
       </c>
       <c r="E227" t="n">
-        <v>208.2469787597656</v>
+        <v>212.8118743896484</v>
       </c>
       <c r="F227" t="n">
-        <v>135187300</v>
+        <v>122309000</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B228" t="n">
-        <v>210.7941279013131</v>
+        <v>212.4023240594531</v>
       </c>
       <c r="C228" t="n">
-        <v>214.4899893165327</v>
+        <v>213.3612577394914</v>
       </c>
       <c r="D228" t="n">
-        <v>209.8751580258669</v>
+        <v>208.9961318803605</v>
       </c>
       <c r="E228" t="n">
-        <v>212.8118743896484</v>
+        <v>209.4256591796875</v>
       </c>
       <c r="F228" t="n">
-        <v>122309000</v>
+        <v>179900000</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B229" t="n">
-        <v>212.4023240594531</v>
+        <v>222.6109016432552</v>
       </c>
       <c r="C229" t="n">
-        <v>213.3612577394914</v>
+        <v>230.2123962709879</v>
       </c>
       <c r="D229" t="n">
-        <v>208.9961318803605</v>
+        <v>220.6530857022795</v>
       </c>
       <c r="E229" t="n">
-        <v>209.4256591796875</v>
+        <v>227.7251739501953</v>
       </c>
       <c r="F229" t="n">
-        <v>179900000</v>
+        <v>298909800</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B230" t="n">
-        <v>222.6109016432552</v>
+        <v>227.1058715337123</v>
       </c>
       <c r="C230" t="n">
-        <v>230.2123962709879</v>
+        <v>229.003741733446</v>
       </c>
       <c r="D230" t="n">
-        <v>220.6530857022795</v>
+        <v>216.5676606288883</v>
       </c>
       <c r="E230" t="n">
-        <v>227.7251739501953</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="F230" t="n">
-        <v>298909800</v>
+        <v>195116400</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B231" t="n">
-        <v>227.1058715337123</v>
+        <v>218.6253647857836</v>
       </c>
       <c r="C231" t="n">
-        <v>229.003741733446</v>
+        <v>221.0526567078369</v>
       </c>
       <c r="D231" t="n">
-        <v>216.5676606288883</v>
+        <v>215.9683494434545</v>
       </c>
       <c r="E231" t="n">
-        <v>217.3068389892578</v>
+        <v>220.5332336425781</v>
       </c>
       <c r="F231" t="n">
-        <v>195116400</v>
+        <v>124702700</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B232" t="n">
-        <v>218.6253647857836</v>
+        <v>216.5077444634259</v>
       </c>
       <c r="C232" t="n">
-        <v>221.0526567078369</v>
+        <v>220.1636574397174</v>
       </c>
       <c r="D232" t="n">
-        <v>215.9683494434545</v>
+        <v>214.8595947199138</v>
       </c>
       <c r="E232" t="n">
-        <v>220.5332336425781</v>
+        <v>217.1969757080078</v>
       </c>
       <c r="F232" t="n">
-        <v>124702700</v>
+        <v>109756200</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B233" t="n">
-        <v>216.5077444634259</v>
+        <v>218.5454508199983</v>
       </c>
       <c r="C233" t="n">
-        <v>220.1636574397174</v>
+        <v>227.6952163087265</v>
       </c>
       <c r="D233" t="n">
-        <v>214.8595947199138</v>
+        <v>218.2357997469377</v>
       </c>
       <c r="E233" t="n">
-        <v>217.1969757080078</v>
+        <v>224.1591796875</v>
       </c>
       <c r="F233" t="n">
-        <v>109756200</v>
+        <v>157104700</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B234" t="n">
-        <v>218.5454508199983</v>
+        <v>225.7673797205316</v>
       </c>
       <c r="C234" t="n">
-        <v>227.6952163087265</v>
+        <v>230.1424737915274</v>
       </c>
       <c r="D234" t="n">
-        <v>218.2357997469377</v>
+        <v>224.4987949430455</v>
       </c>
       <c r="E234" t="n">
-        <v>224.1591796875</v>
+        <v>228.1946563720703</v>
       </c>
       <c r="F234" t="n">
-        <v>157104700</v>
+        <v>134681600</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B235" t="n">
-        <v>225.7673797205316</v>
+        <v>230.8317036041433</v>
       </c>
       <c r="C235" t="n">
-        <v>230.1424737915274</v>
+        <v>234.4975997614268</v>
       </c>
       <c r="D235" t="n">
-        <v>224.4987949430455</v>
+        <v>229.3733440032785</v>
       </c>
       <c r="E235" t="n">
-        <v>228.1946563720703</v>
+        <v>230.1025238037109</v>
       </c>
       <c r="F235" t="n">
-        <v>134681600</v>
+        <v>135352400</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B236" t="n">
-        <v>230.8317036041433</v>
+        <v>232.8494477166676</v>
       </c>
       <c r="C236" t="n">
-        <v>234.4975997614268</v>
+        <v>233.4487831783142</v>
       </c>
       <c r="D236" t="n">
-        <v>229.3733440032785</v>
+        <v>224.5986856128386</v>
       </c>
       <c r="E236" t="n">
-        <v>230.1025238037109</v>
+        <v>225.4776916503906</v>
       </c>
       <c r="F236" t="n">
-        <v>135352400</v>
+        <v>122965600</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B237" t="n">
-        <v>232.8494477166676</v>
+        <v>225.0281992525124</v>
       </c>
       <c r="C237" t="n">
-        <v>233.4487831783142</v>
+        <v>225.9271872095504</v>
       </c>
       <c r="D237" t="n">
-        <v>224.5986856128386</v>
+        <v>223.2102414251123</v>
       </c>
       <c r="E237" t="n">
-        <v>225.4776916503906</v>
+        <v>223.4199981689453</v>
       </c>
       <c r="F237" t="n">
-        <v>122965600</v>
+        <v>82955500</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,25 +6605,25 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B238" t="n">
-        <v>225.0281992525124</v>
+        <v>220.5299987792969</v>
       </c>
       <c r="C238" t="n">
-        <v>225.9271872095504</v>
+        <v>220.9900054931641</v>
       </c>
       <c r="D238" t="n">
-        <v>223.2102414251123</v>
+        <v>217.1999969482422</v>
       </c>
       <c r="E238" t="n">
-        <v>223.4199981689453</v>
+        <v>218.3600006103516</v>
       </c>
       <c r="F238" t="n">
-        <v>82955500</v>
+        <v>105768000</v>
       </c>
       <c r="G238" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -6631,25 +6631,25 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B239" t="n">
-        <v>220.5299987792969</v>
+        <v>221.2400054931641</v>
       </c>
       <c r="C239" t="n">
-        <v>220.9900054931641</v>
+        <v>222</v>
       </c>
       <c r="D239" t="n">
-        <v>217.1999969482422</v>
+        <v>218.1499938964844</v>
       </c>
       <c r="E239" t="n">
-        <v>218.3600006103516</v>
+        <v>218.2899932861328</v>
       </c>
       <c r="F239" t="n">
-        <v>105768000</v>
+        <v>89060100</v>
       </c>
       <c r="G239" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B240" t="n">
-        <v>221.2400054931641</v>
+        <v>211.2400054931641</v>
       </c>
       <c r="C240" t="n">
-        <v>222</v>
+        <v>212.7700042724609</v>
       </c>
       <c r="D240" t="n">
-        <v>218.1499938964844</v>
+        <v>208.9299926757812</v>
       </c>
       <c r="E240" t="n">
-        <v>218.2899932861328</v>
+        <v>210.9600067138672</v>
       </c>
       <c r="F240" t="n">
-        <v>89060100</v>
+        <v>132267200</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B241" t="n">
-        <v>211.2400054931641</v>
+        <v>213.3800048828125</v>
       </c>
       <c r="C241" t="n">
-        <v>212.7700042724609</v>
+        <v>213.9400024414062</v>
       </c>
       <c r="D241" t="n">
-        <v>208.9299926757812</v>
+        <v>211.1600036621094</v>
       </c>
       <c r="E241" t="n">
-        <v>210.9600067138672</v>
+        <v>212.1699981689453</v>
       </c>
       <c r="F241" t="n">
-        <v>132267200</v>
+        <v>88059700</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B242" t="n">
-        <v>213.3800048828125</v>
+        <v>214.1399993896484</v>
       </c>
       <c r="C242" t="n">
-        <v>213.9400024414062</v>
+        <v>216.7599945068359</v>
       </c>
       <c r="D242" t="n">
-        <v>211.1600036621094</v>
+        <v>212.5</v>
       </c>
       <c r="E242" t="n">
-        <v>212.1699981689453</v>
+        <v>213.8999938964844</v>
       </c>
       <c r="F242" t="n">
-        <v>88059700</v>
+        <v>96563600</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B243" t="n">
-        <v>214.1399993896484</v>
+        <v>218.3800048828125</v>
       </c>
       <c r="C243" t="n">
-        <v>216.7599945068359</v>
+        <v>219.9100036621094</v>
       </c>
       <c r="D243" t="n">
-        <v>212.5</v>
+        <v>217.1499938964844</v>
       </c>
       <c r="E243" t="n">
-        <v>213.8999938964844</v>
+        <v>219.3399963378906</v>
       </c>
       <c r="F243" t="n">
-        <v>96563600</v>
+        <v>94191300</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B244" t="n">
-        <v>218.3800048828125</v>
+        <v>219.3500061035156</v>
       </c>
       <c r="C244" t="n">
-        <v>219.9100036621094</v>
+        <v>222.7299957275391</v>
       </c>
       <c r="D244" t="n">
-        <v>217.1499938964844</v>
+        <v>218.0299987792969</v>
       </c>
       <c r="E244" t="n">
-        <v>219.3399963378906</v>
+        <v>222.2700042724609</v>
       </c>
       <c r="F244" t="n">
-        <v>94191300</v>
+        <v>190287400</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B245" t="n">
-        <v>219.3500061035156</v>
+        <v>222.9400024414062</v>
       </c>
       <c r="C245" t="n">
-        <v>222.7299957275391</v>
+        <v>228.5</v>
       </c>
       <c r="D245" t="n">
-        <v>218.0299987792969</v>
+        <v>221.5599975585938</v>
       </c>
       <c r="E245" t="n">
-        <v>222.2700042724609</v>
+        <v>227.3800048828125</v>
       </c>
       <c r="F245" t="n">
-        <v>190287400</v>
+        <v>109806100</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B246" t="n">
-        <v>222.9400024414062</v>
+        <v>226.8500061035156</v>
       </c>
       <c r="C246" t="n">
-        <v>228.5</v>
+        <v>229.9799957275391</v>
       </c>
       <c r="D246" t="n">
-        <v>221.5599975585938</v>
+        <v>226.5</v>
       </c>
       <c r="E246" t="n">
-        <v>227.3800048828125</v>
+        <v>228.8699951171875</v>
       </c>
       <c r="F246" t="n">
-        <v>109806100</v>
+        <v>95746700</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B247" t="n">
-        <v>226.8500061035156</v>
+        <v>228.0299987792969</v>
       </c>
       <c r="C247" t="n">
-        <v>229.9799957275391</v>
+        <v>228.9499969482422</v>
       </c>
       <c r="D247" t="n">
-        <v>226.5</v>
+        <v>224.0200042724609</v>
       </c>
       <c r="E247" t="n">
-        <v>228.8699951171875</v>
+        <v>225.5099945068359</v>
       </c>
       <c r="F247" t="n">
-        <v>95746700</v>
+        <v>89547300</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B248" t="n">
-        <v>228.0299987792969</v>
+        <v>222.0800018310547</v>
       </c>
       <c r="C248" t="n">
-        <v>228.9499969482422</v>
+        <v>224.9400024414062</v>
       </c>
       <c r="D248" t="n">
-        <v>224.0200042724609</v>
+        <v>221.0899963378906</v>
       </c>
       <c r="E248" t="n">
-        <v>225.5099945068359</v>
+        <v>224.5800018310547</v>
       </c>
       <c r="F248" t="n">
-        <v>89547300</v>
+        <v>77469900</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B249" t="n">
-        <v>222.0800018310547</v>
+        <v>225.1300048828125</v>
       </c>
       <c r="C249" t="n">
-        <v>224.9400024414062</v>
+        <v>226.9400024414062</v>
       </c>
       <c r="D249" t="n">
-        <v>221.0899963378906</v>
+        <v>223.1300048828125</v>
       </c>
       <c r="E249" t="n">
-        <v>224.5800018310547</v>
+        <v>225.0700073242188</v>
       </c>
       <c r="F249" t="n">
-        <v>77469900</v>
+        <v>89947700</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B250" t="n">
-        <v>225.1300048828125</v>
+        <v>229.75</v>
       </c>
       <c r="C250" t="n">
-        <v>226.9400024414062</v>
+        <v>233.2100067138672</v>
       </c>
       <c r="D250" t="n">
-        <v>223.1300048828125</v>
+        <v>228.0399932861328</v>
       </c>
       <c r="E250" t="n">
-        <v>225.0700073242188</v>
+        <v>228.8600006103516</v>
       </c>
       <c r="F250" t="n">
-        <v>89947700</v>
+        <v>142344300</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B251" t="n">
-        <v>229.75</v>
+        <v>230.9700012207031</v>
       </c>
       <c r="C251" t="n">
-        <v>233.2100067138672</v>
+        <v>232.8200073242188</v>
       </c>
       <c r="D251" t="n">
-        <v>228.0399932861328</v>
+        <v>227.0299987792969</v>
       </c>
       <c r="E251" t="n">
-        <v>228.8600006103516</v>
+        <v>227.2100067138672</v>
       </c>
       <c r="F251" t="n">
-        <v>142344300</v>
+        <v>101494900</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B252" t="n">
-        <v>230.9700012207031</v>
+        <v>229.2700042724609</v>
       </c>
       <c r="C252" t="n">
-        <v>232.8200073242188</v>
+        <v>232.3699951171875</v>
       </c>
       <c r="D252" t="n">
-        <v>227.0299987792969</v>
+        <v>228.1699981689453</v>
       </c>
       <c r="E252" t="n">
-        <v>227.2100067138672</v>
+        <v>228.3800048828125</v>
       </c>
       <c r="F252" t="n">
-        <v>101203000</v>
+        <v>121269300</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10884,37 +10884,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>228.38</v>
+      </c>
+      <c r="D2" t="n">
         <v>227.21</v>
       </c>
-      <c r="D2" t="n">
-        <v>228.86</v>
-      </c>
       <c r="E2" t="n">
-        <v>230.995</v>
+        <v>229</v>
       </c>
       <c r="F2" t="n">
-        <v>232.82</v>
+        <v>232.37</v>
       </c>
       <c r="G2" t="n">
-        <v>227.025</v>
+        <v>228.17</v>
       </c>
       <c r="H2" t="n">
-        <v>98224511</v>
+        <v>118683065</v>
       </c>
       <c r="I2" t="n">
-        <v>123496938</v>
+        <v>123136312</v>
       </c>
       <c r="J2" t="n">
-        <v>5486440087552</v>
+        <v>5514691870720</v>
       </c>
       <c r="K2" t="n">
-        <v>28.907125</v>
+        <v>28.908861</v>
       </c>
       <c r="L2" t="n">
-        <v>14.488005</v>
+        <v>14.562609</v>
       </c>
       <c r="M2" t="n">
-        <v>7.86</v>
+        <v>7.9</v>
       </c>
       <c r="N2" t="n">
         <v>236.54</v>
@@ -10950,7 +10950,7 @@
         <v>9.483000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>23.959719</v>
+        <v>24.083097</v>
       </c>
       <c r="Z2" t="n">
         <v>1.278</v>
@@ -10962,7 +10962,7 @@
         <v>302970011648</v>
       </c>
       <c r="AC2" t="n">
-        <v>5452152176640</v>
+        <v>5480348909568</v>
       </c>
       <c r="AD2" t="n">
         <v>201266003968</v>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:07:01</t>
+          <t>2026-10-01 17:02:42</t>
         </is>
       </c>
     </row>

--- a/data/NVDA_data.xlsx
+++ b/data/NVDA_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B2" t="n">
-        <v>184.7972757932568</v>
+        <v>189.1468626563914</v>
       </c>
       <c r="C2" t="n">
-        <v>187.690338609038</v>
+        <v>190.593394116267</v>
       </c>
       <c r="D2" t="n">
-        <v>183.4604668683245</v>
+        <v>187.6105347272827</v>
       </c>
       <c r="E2" t="n">
-        <v>186.7924957275391</v>
+        <v>188.4385528564453</v>
       </c>
       <c r="F2" t="n">
-        <v>173844900</v>
+        <v>136805800</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B3" t="n">
-        <v>189.146847340247</v>
+        <v>188.7378247179256</v>
       </c>
       <c r="C3" t="n">
-        <v>190.59337868299</v>
+        <v>189.9050265070322</v>
       </c>
       <c r="D3" t="n">
-        <v>187.6105195355423</v>
+        <v>184.9369333277354</v>
       </c>
       <c r="E3" t="n">
-        <v>188.4385375976562</v>
+        <v>187.1715698242188</v>
       </c>
       <c r="F3" t="n">
-        <v>136805800</v>
+        <v>137596900</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B4" t="n">
-        <v>188.7378093314507</v>
+        <v>185.0566294029491</v>
       </c>
       <c r="C4" t="n">
-        <v>189.9050110254035</v>
+        <v>186.7824902019781</v>
       </c>
       <c r="D4" t="n">
-        <v>184.9369182511207</v>
+        <v>182.8918178290645</v>
       </c>
       <c r="E4" t="n">
-        <v>187.1715545654297</v>
+        <v>185.0965270996094</v>
       </c>
       <c r="F4" t="n">
-        <v>137596900</v>
+        <v>157678100</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B5" t="n">
-        <v>185.0566446584491</v>
+        <v>185.7848907820332</v>
       </c>
       <c r="C5" t="n">
-        <v>186.7825055997528</v>
+        <v>188.6081286768816</v>
       </c>
       <c r="D5" t="n">
-        <v>182.8918329061041</v>
+        <v>183.5602249269612</v>
       </c>
       <c r="E5" t="n">
-        <v>185.0965423583984</v>
+        <v>184.5977325439453</v>
       </c>
       <c r="F5" t="n">
-        <v>157678100</v>
+        <v>140088000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B6" t="n">
-        <v>185.7848907820332</v>
+        <v>186.1240974206304</v>
       </c>
       <c r="C6" t="n">
-        <v>188.6081286768816</v>
+        <v>189.1468543796426</v>
       </c>
       <c r="D6" t="n">
-        <v>183.5602249269612</v>
+        <v>186.0941551173159</v>
       </c>
       <c r="E6" t="n">
-        <v>184.5977325439453</v>
+        <v>188.6580200195312</v>
       </c>
       <c r="F6" t="n">
-        <v>140088000</v>
+        <v>130168900</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B7" t="n">
-        <v>186.1240823667868</v>
+        <v>191.7705422839889</v>
       </c>
       <c r="C7" t="n">
-        <v>189.1468390813163</v>
+        <v>194.8332119113436</v>
       </c>
       <c r="D7" t="n">
-        <v>186.094140065894</v>
+        <v>190.6033405552435</v>
       </c>
       <c r="E7" t="n">
-        <v>188.6580047607422</v>
+        <v>192.1097412109375</v>
       </c>
       <c r="F7" t="n">
-        <v>130168900</v>
+        <v>182997200</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B8" t="n">
-        <v>191.7705422839889</v>
+        <v>193.0474982342752</v>
       </c>
       <c r="C8" t="n">
-        <v>194.8332119113436</v>
+        <v>195.1524558626357</v>
       </c>
       <c r="D8" t="n">
-        <v>190.6033405552435</v>
+        <v>181.6148965961679</v>
       </c>
       <c r="E8" t="n">
-        <v>192.1097412109375</v>
+        <v>182.7222442626953</v>
       </c>
       <c r="F8" t="n">
-        <v>182997200</v>
+        <v>268774400</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B9" t="n">
-        <v>193.0474982342752</v>
+        <v>187.5207340107304</v>
       </c>
       <c r="C9" t="n">
-        <v>195.1524558626357</v>
+        <v>189.6556185865847</v>
       </c>
       <c r="D9" t="n">
-        <v>181.6148965961679</v>
+        <v>185.5155435929421</v>
       </c>
       <c r="E9" t="n">
-        <v>182.7222442626953</v>
+        <v>187.8699035644531</v>
       </c>
       <c r="F9" t="n">
-        <v>268774400</v>
+        <v>153482800</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B10" t="n">
-        <v>187.5207340107304</v>
+        <v>184.3283927796865</v>
       </c>
       <c r="C10" t="n">
-        <v>189.6556185865847</v>
+        <v>184.3583198600852</v>
       </c>
       <c r="D10" t="n">
-        <v>185.5155435929421</v>
+        <v>179.2705030798172</v>
       </c>
       <c r="E10" t="n">
-        <v>187.8699035644531</v>
+        <v>179.5997161865234</v>
       </c>
       <c r="F10" t="n">
-        <v>153482800</v>
+        <v>205641400</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B11" t="n">
-        <v>184.3283927796865</v>
+        <v>184.358330420537</v>
       </c>
       <c r="C11" t="n">
-        <v>184.3583198600852</v>
+        <v>184.428155204694</v>
       </c>
       <c r="D11" t="n">
-        <v>179.2705030798172</v>
+        <v>176.8662696036074</v>
       </c>
       <c r="E11" t="n">
-        <v>179.5997161865234</v>
+        <v>179.4002075195312</v>
       </c>
       <c r="F11" t="n">
-        <v>205641400</v>
+        <v>214450500</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B12" t="n">
-        <v>184.3583147400375</v>
+        <v>181.7944673989196</v>
       </c>
       <c r="C12" t="n">
-        <v>184.4281395182556</v>
+        <v>182.8419609512268</v>
       </c>
       <c r="D12" t="n">
-        <v>176.866254560341</v>
+        <v>179.3403553050442</v>
       </c>
       <c r="E12" t="n">
-        <v>179.4001922607422</v>
+        <v>181.3754730224609</v>
       </c>
       <c r="F12" t="n">
-        <v>214450500</v>
+        <v>179723300</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B13" t="n">
-        <v>181.7944521048813</v>
+        <v>179.7493615830456</v>
       </c>
       <c r="C13" t="n">
-        <v>182.8419455690647</v>
+        <v>183.6600061588844</v>
       </c>
       <c r="D13" t="n">
-        <v>179.3403402174659</v>
+        <v>179.3203965919317</v>
       </c>
       <c r="E13" t="n">
-        <v>181.3754577636719</v>
+        <v>182.7821044921875</v>
       </c>
       <c r="F13" t="n">
-        <v>179723300</v>
+        <v>173135200</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B14" t="n">
-        <v>179.7493465774322</v>
+        <v>182.6923255947822</v>
       </c>
       <c r="C14" t="n">
-        <v>183.6599908268075</v>
+        <v>184.7573703952674</v>
       </c>
       <c r="D14" t="n">
-        <v>179.3203816221287</v>
+        <v>181.2956624505063</v>
       </c>
       <c r="E14" t="n">
-        <v>182.7820892333984</v>
+        <v>182.2034912109375</v>
       </c>
       <c r="F14" t="n">
-        <v>173135200</v>
+        <v>128544700</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B15" t="n">
-        <v>182.6923255947822</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="C15" t="n">
-        <v>184.7573703952674</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="D15" t="n">
-        <v>181.2956624505063</v>
+        <v>179.3702701372806</v>
       </c>
       <c r="E15" t="n">
-        <v>182.2034912109375</v>
+        <v>180.7270202636719</v>
       </c>
       <c r="F15" t="n">
-        <v>128544700</v>
+        <v>124240200</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B16" t="n">
-        <v>182.3531141136141</v>
+        <v>180.7070662621498</v>
       </c>
       <c r="C16" t="n">
-        <v>182.3531141136141</v>
+        <v>183.0015721983185</v>
       </c>
       <c r="D16" t="n">
-        <v>179.3702701372806</v>
+        <v>176.3375297972393</v>
       </c>
       <c r="E16" t="n">
-        <v>180.7270202636719</v>
+        <v>179.84912109375</v>
       </c>
       <c r="F16" t="n">
-        <v>124240200</v>
+        <v>162249600</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B17" t="n">
-        <v>180.7070509305708</v>
+        <v>179.988762799469</v>
       </c>
       <c r="C17" t="n">
-        <v>183.0015566720687</v>
+        <v>182.5925250516066</v>
       </c>
       <c r="D17" t="n">
-        <v>176.3375148363812</v>
+        <v>179.3602637385785</v>
       </c>
       <c r="E17" t="n">
-        <v>179.8491058349609</v>
+        <v>181.724609375</v>
       </c>
       <c r="F17" t="n">
-        <v>162249600</v>
+        <v>111363700</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B18" t="n">
-        <v>179.988777912505</v>
+        <v>183.400590081168</v>
       </c>
       <c r="C18" t="n">
-        <v>182.5925403832715</v>
+        <v>187.0219186862977</v>
       </c>
       <c r="D18" t="n">
-        <v>179.3602787988416</v>
+        <v>183.0614063875393</v>
       </c>
       <c r="E18" t="n">
-        <v>181.7246246337891</v>
+        <v>185.8148040771484</v>
       </c>
       <c r="F18" t="n">
-        <v>111363700</v>
+        <v>131296700</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B19" t="n">
-        <v>183.400590081168</v>
+        <v>189.5358881817124</v>
       </c>
       <c r="C19" t="n">
-        <v>187.0219186862977</v>
+        <v>191.5410783658203</v>
       </c>
       <c r="D19" t="n">
-        <v>183.0614063875393</v>
+        <v>187.9796041332436</v>
       </c>
       <c r="E19" t="n">
-        <v>185.8148040771484</v>
+        <v>191.0323028564453</v>
       </c>
       <c r="F19" t="n">
-        <v>131296700</v>
+        <v>153452700</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B20" t="n">
-        <v>189.5359033209746</v>
+        <v>192.5886214245991</v>
       </c>
       <c r="C20" t="n">
-        <v>191.541093665248</v>
+        <v>202.6644737034797</v>
       </c>
       <c r="D20" t="n">
-        <v>187.979619148197</v>
+        <v>191.4513465869582</v>
       </c>
       <c r="E20" t="n">
-        <v>191.0323181152344</v>
+        <v>200.5495452880859</v>
       </c>
       <c r="F20" t="n">
-        <v>153452700</v>
+        <v>297986200</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B21" t="n">
-        <v>192.5886067715161</v>
+        <v>207.482906515472</v>
       </c>
       <c r="C21" t="n">
-        <v>202.6644582837766</v>
+        <v>211.6828509687219</v>
       </c>
       <c r="D21" t="n">
-        <v>191.4513320204045</v>
+        <v>204.2905578218423</v>
       </c>
       <c r="E21" t="n">
-        <v>200.5495300292969</v>
+        <v>206.5451507568359</v>
       </c>
       <c r="F21" t="n">
-        <v>297986200</v>
+        <v>308829600</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B22" t="n">
-        <v>207.482921843539</v>
+        <v>204.6596680014167</v>
       </c>
       <c r="C22" t="n">
-        <v>211.6828666070652</v>
+        <v>205.6672637579894</v>
       </c>
       <c r="D22" t="n">
-        <v>204.2905729140704</v>
+        <v>200.9286166610889</v>
       </c>
       <c r="E22" t="n">
-        <v>206.545166015625</v>
+        <v>202.4050750732422</v>
       </c>
       <c r="F22" t="n">
-        <v>308829600</v>
+        <v>178864400</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B23" t="n">
-        <v>204.6596680014167</v>
+        <v>205.9565537660584</v>
       </c>
       <c r="C23" t="n">
-        <v>205.6672637579894</v>
+        <v>207.4729250244422</v>
       </c>
       <c r="D23" t="n">
-        <v>200.9286166610889</v>
+        <v>201.5870329046891</v>
       </c>
       <c r="E23" t="n">
-        <v>202.4050750732422</v>
+        <v>202.0060272216797</v>
       </c>
       <c r="F23" t="n">
-        <v>178864400</v>
+        <v>179802200</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B24" t="n">
-        <v>205.9565693232556</v>
+        <v>207.5826726752522</v>
       </c>
       <c r="C24" t="n">
-        <v>207.4729406961805</v>
+        <v>210.8348755139714</v>
       </c>
       <c r="D24" t="n">
-        <v>201.5870481318289</v>
+        <v>205.0686914304077</v>
       </c>
       <c r="E24" t="n">
-        <v>202.0060424804688</v>
+        <v>206.3855438232422</v>
       </c>
       <c r="F24" t="n">
-        <v>179802200</v>
+        <v>180267300</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B25" t="n">
-        <v>207.5826573279554</v>
+        <v>202.5148147488263</v>
       </c>
       <c r="C25" t="n">
-        <v>210.834859926228</v>
+        <v>203.4824975937368</v>
       </c>
       <c r="D25" t="n">
-        <v>205.068676268978</v>
+        <v>197.4569251230167</v>
       </c>
       <c r="E25" t="n">
-        <v>206.3855285644531</v>
+        <v>198.2151184082031</v>
       </c>
       <c r="F25" t="n">
-        <v>180267300</v>
+        <v>188919300</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B26" t="n">
-        <v>202.5147991590425</v>
+        <v>198.2949275919373</v>
       </c>
       <c r="C26" t="n">
-        <v>203.4824819294599</v>
+        <v>202.4350026612236</v>
       </c>
       <c r="D26" t="n">
-        <v>197.4569099225941</v>
+        <v>194.1847643800754</v>
       </c>
       <c r="E26" t="n">
-        <v>198.2151031494141</v>
+        <v>194.7434387207031</v>
       </c>
       <c r="F26" t="n">
-        <v>188919300</v>
+        <v>171350300</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B27" t="n">
-        <v>198.2949275919373</v>
+        <v>195.9505410878136</v>
       </c>
       <c r="C27" t="n">
-        <v>202.4350026612236</v>
+        <v>197.1476699621838</v>
       </c>
       <c r="D27" t="n">
-        <v>194.1847643800754</v>
+        <v>185.9345440647224</v>
       </c>
       <c r="E27" t="n">
-        <v>194.7434387207031</v>
+        <v>187.6304779052734</v>
       </c>
       <c r="F27" t="n">
-        <v>171350300</v>
+        <v>223029800</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B28" t="n">
-        <v>195.9505570232203</v>
+        <v>184.4580698535366</v>
       </c>
       <c r="C28" t="n">
-        <v>197.1476859949454</v>
+        <v>187.8699092076593</v>
       </c>
       <c r="D28" t="n">
-        <v>185.934559185592</v>
+        <v>178.4823961188316</v>
       </c>
       <c r="E28" t="n">
-        <v>187.6304931640625</v>
+        <v>187.7003021240234</v>
       </c>
       <c r="F28" t="n">
-        <v>223029800</v>
+        <v>264942300</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B29" t="n">
-        <v>184.4580698535366</v>
+        <v>194.6436788693004</v>
       </c>
       <c r="C29" t="n">
-        <v>187.8699092076593</v>
+        <v>199.4621367771523</v>
       </c>
       <c r="D29" t="n">
-        <v>178.4823961188316</v>
+        <v>193.3268264223904</v>
       </c>
       <c r="E29" t="n">
-        <v>187.7003021240234</v>
+        <v>198.5742645263672</v>
       </c>
       <c r="F29" t="n">
-        <v>264942300</v>
+        <v>198897100</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B30" t="n">
-        <v>194.6436788693004</v>
+        <v>194.6935381421213</v>
       </c>
       <c r="C30" t="n">
-        <v>199.4621367771523</v>
+        <v>194.9529112179747</v>
       </c>
       <c r="D30" t="n">
-        <v>193.3268264223904</v>
+        <v>190.8427635881239</v>
       </c>
       <c r="E30" t="n">
-        <v>198.5742645263672</v>
+        <v>192.6983184814453</v>
       </c>
       <c r="F30" t="n">
-        <v>198897100</v>
+        <v>176483300</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B31" t="n">
-        <v>194.6935535589016</v>
+        <v>195.2522010776849</v>
       </c>
       <c r="C31" t="n">
-        <v>194.9529266552934</v>
+        <v>195.4217929255223</v>
       </c>
       <c r="D31" t="n">
-        <v>190.8427786999811</v>
+        <v>190.6731755191215</v>
       </c>
       <c r="E31" t="n">
-        <v>192.6983337402344</v>
+        <v>193.3367919921875</v>
       </c>
       <c r="F31" t="n">
-        <v>176483300</v>
+        <v>154935300</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B32" t="n">
-        <v>195.2522010776849</v>
+        <v>190.5933791327836</v>
       </c>
       <c r="C32" t="n">
-        <v>195.4217929255223</v>
+        <v>190.9824463944715</v>
       </c>
       <c r="D32" t="n">
-        <v>190.6731755191215</v>
+        <v>183.4105907203728</v>
       </c>
       <c r="E32" t="n">
-        <v>193.3367919921875</v>
+        <v>186.4133911132812</v>
       </c>
       <c r="F32" t="n">
-        <v>154935300</v>
+        <v>207423100</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B33" t="n">
-        <v>190.5933791327836</v>
+        <v>182.4229435613052</v>
       </c>
       <c r="C33" t="n">
-        <v>190.9824463944715</v>
+        <v>190.553458007553</v>
       </c>
       <c r="D33" t="n">
-        <v>183.4105907203728</v>
+        <v>180.1483942490048</v>
       </c>
       <c r="E33" t="n">
-        <v>186.4133911132812</v>
+        <v>189.7154693603516</v>
       </c>
       <c r="F33" t="n">
-        <v>207423100</v>
+        <v>186591900</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B34" t="n">
-        <v>182.4229435613052</v>
+        <v>185.5255230789849</v>
       </c>
       <c r="C34" t="n">
-        <v>190.553458007553</v>
+        <v>188.5482800008962</v>
       </c>
       <c r="D34" t="n">
-        <v>180.1483942490048</v>
+        <v>183.8794727552066</v>
       </c>
       <c r="E34" t="n">
-        <v>189.7154693603516</v>
+        <v>186.1540222167969</v>
       </c>
       <c r="F34" t="n">
-        <v>186591900</v>
+        <v>173628900</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B35" t="n">
-        <v>185.5255230789849</v>
+        <v>182.941705155915</v>
       </c>
       <c r="C35" t="n">
-        <v>188.5482800008962</v>
+        <v>184.3583093626339</v>
       </c>
       <c r="D35" t="n">
-        <v>183.8794727552066</v>
+        <v>179.2206093334711</v>
       </c>
       <c r="E35" t="n">
-        <v>186.1540222167969</v>
+        <v>180.9265289306641</v>
       </c>
       <c r="F35" t="n">
-        <v>173628900</v>
+        <v>213598900</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B36" t="n">
-        <v>182.941705155915</v>
+        <v>184.3483273978252</v>
       </c>
       <c r="C36" t="n">
-        <v>184.3583093626339</v>
+        <v>187.4109971087465</v>
       </c>
       <c r="D36" t="n">
-        <v>179.2206093334711</v>
+        <v>182.3930205111681</v>
       </c>
       <c r="E36" t="n">
-        <v>180.9265289306641</v>
+        <v>186.0742034912109</v>
       </c>
       <c r="F36" t="n">
-        <v>213598900</v>
+        <v>247246400</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B37" t="n">
-        <v>184.3483273978252</v>
+        <v>195.4816571057099</v>
       </c>
       <c r="C37" t="n">
-        <v>187.4109971087465</v>
+        <v>195.5315406452363</v>
       </c>
       <c r="D37" t="n">
-        <v>182.3930205111681</v>
+        <v>179.4201468289569</v>
       </c>
       <c r="E37" t="n">
-        <v>186.0742034912109</v>
+        <v>180.208251953125</v>
       </c>
       <c r="F37" t="n">
-        <v>247246400</v>
+        <v>343504800</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B38" t="n">
-        <v>195.4816571057099</v>
+        <v>180.806813452001</v>
       </c>
       <c r="C38" t="n">
-        <v>195.5315406452363</v>
+        <v>184.1188702156436</v>
       </c>
       <c r="D38" t="n">
-        <v>179.4201468289569</v>
+        <v>172.5166628687019</v>
       </c>
       <c r="E38" t="n">
-        <v>180.208251953125</v>
+        <v>178.4524536132812</v>
       </c>
       <c r="F38" t="n">
-        <v>343504800</v>
+        <v>346926200</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B39" t="n">
-        <v>180.806813452001</v>
+        <v>179.0610093294625</v>
       </c>
       <c r="C39" t="n">
-        <v>184.1188702156436</v>
+        <v>183.0614196131816</v>
       </c>
       <c r="D39" t="n">
-        <v>172.5166628687019</v>
+        <v>176.0581937395723</v>
       </c>
       <c r="E39" t="n">
-        <v>178.4524536132812</v>
+        <v>182.1136932373047</v>
       </c>
       <c r="F39" t="n">
-        <v>346926200</v>
+        <v>256618300</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B40" t="n">
-        <v>179.0609943264491</v>
+        <v>174.491955735681</v>
       </c>
       <c r="C40" t="n">
-        <v>183.0614042749852</v>
+        <v>177.7341879937998</v>
       </c>
       <c r="D40" t="n">
-        <v>176.0581789881563</v>
+        <v>169.1447659257062</v>
       </c>
       <c r="E40" t="n">
-        <v>182.1136779785156</v>
+        <v>177.3950042724609</v>
       </c>
       <c r="F40" t="n">
-        <v>256618300</v>
+        <v>320600300</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B41" t="n">
-        <v>174.4919407266003</v>
+        <v>181.1958831941039</v>
       </c>
       <c r="C41" t="n">
-        <v>177.7341727058355</v>
+        <v>182.4728225932506</v>
       </c>
       <c r="D41" t="n">
-        <v>169.1447513765687</v>
+        <v>177.8139863878403</v>
       </c>
       <c r="E41" t="n">
-        <v>177.3949890136719</v>
+        <v>179.8291473388672</v>
       </c>
       <c r="F41" t="n">
-        <v>320600300</v>
+        <v>183852000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B42" t="n">
-        <v>181.1958831941039</v>
+        <v>178.5821558989869</v>
       </c>
       <c r="C42" t="n">
-        <v>182.4728225932506</v>
+        <v>178.8614854738169</v>
       </c>
       <c r="D42" t="n">
-        <v>177.8139863878403</v>
+        <v>176.0781603452176</v>
       </c>
       <c r="E42" t="n">
-        <v>179.8291473388672</v>
+        <v>176.5769653320312</v>
       </c>
       <c r="F42" t="n">
-        <v>183852000</v>
+        <v>121332800</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B43" t="n">
-        <v>178.5821404669205</v>
+        <v>174.3423041351479</v>
       </c>
       <c r="C43" t="n">
-        <v>178.8614700176124</v>
+        <v>179.8690716163194</v>
       </c>
       <c r="D43" t="n">
-        <v>176.0781451295325</v>
+        <v>173.2648835948944</v>
       </c>
       <c r="E43" t="n">
-        <v>176.5769500732422</v>
+        <v>179.4899749755859</v>
       </c>
       <c r="F43" t="n">
-        <v>121332800</v>
+        <v>188131000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B44" t="n">
-        <v>174.3423189563235</v>
+        <v>181.3255769560617</v>
       </c>
       <c r="C44" t="n">
-        <v>179.8690869073362</v>
+        <v>185.2162648499111</v>
       </c>
       <c r="D44" t="n">
-        <v>173.2648983244765</v>
+        <v>179.569788944198</v>
       </c>
       <c r="E44" t="n">
-        <v>179.489990234375</v>
+        <v>181.0263061523438</v>
       </c>
       <c r="F44" t="n">
-        <v>188131000</v>
+        <v>182632200</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B45" t="n">
-        <v>181.3255769560617</v>
+        <v>180.6472109015755</v>
       </c>
       <c r="C45" t="n">
-        <v>185.2162648499111</v>
+        <v>182.0139316568558</v>
       </c>
       <c r="D45" t="n">
-        <v>179.569788944198</v>
+        <v>178.681918089591</v>
       </c>
       <c r="E45" t="n">
-        <v>181.0263061523438</v>
+        <v>179.1607666015625</v>
       </c>
       <c r="F45" t="n">
-        <v>182632200</v>
+        <v>165138000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,25 +1613,25 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B46" t="n">
-        <v>180.6472109015755</v>
+        <v>181.1959881613664</v>
       </c>
       <c r="C46" t="n">
-        <v>182.0139316568558</v>
+        <v>184.089227004522</v>
       </c>
       <c r="D46" t="n">
-        <v>178.681918089591</v>
+        <v>179.5398751387779</v>
       </c>
       <c r="E46" t="n">
-        <v>179.1607666015625</v>
+        <v>182.9518890380859</v>
       </c>
       <c r="F46" t="n">
-        <v>165138000</v>
+        <v>167364900</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1639,25 +1639,25 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B47" t="n">
-        <v>181.1959881613664</v>
+        <v>183.4606866221248</v>
       </c>
       <c r="C47" t="n">
-        <v>184.089227004522</v>
+        <v>184.2288932293168</v>
       </c>
       <c r="D47" t="n">
-        <v>179.5398751387779</v>
+        <v>180.4876480440623</v>
       </c>
       <c r="E47" t="n">
-        <v>182.9518890380859</v>
+        <v>181.9841461181641</v>
       </c>
       <c r="F47" t="n">
-        <v>167364900</v>
+        <v>143971100</v>
       </c>
       <c r="G47" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B48" t="n">
-        <v>183.4607020047171</v>
+        <v>182.2136112701494</v>
       </c>
       <c r="C48" t="n">
-        <v>184.2289086763207</v>
+        <v>187.5610985176648</v>
       </c>
       <c r="D48" t="n">
-        <v>180.4876631773748</v>
+        <v>181.9741660895743</v>
       </c>
       <c r="E48" t="n">
-        <v>181.9841613769531</v>
+        <v>185.1168212890625</v>
       </c>
       <c r="F48" t="n">
-        <v>143971100</v>
+        <v>204378100</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B49" t="n">
-        <v>182.213626289633</v>
+        <v>185.12679644575</v>
       </c>
       <c r="C49" t="n">
-        <v>187.5611139779305</v>
+        <v>185.2864265695677</v>
       </c>
       <c r="D49" t="n">
-        <v>181.9741810893209</v>
+        <v>182.8920356049676</v>
       </c>
       <c r="E49" t="n">
-        <v>185.1168365478516</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="F49" t="n">
-        <v>204378100</v>
+        <v>144719700</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B50" t="n">
-        <v>185.12679644575</v>
+        <v>184.5381918075859</v>
       </c>
       <c r="C50" t="n">
-        <v>185.2864265695677</v>
+        <v>185.0469957406681</v>
       </c>
       <c r="D50" t="n">
-        <v>182.8920356049676</v>
+        <v>181.6150239281505</v>
       </c>
       <c r="E50" t="n">
-        <v>184.5381774902344</v>
+        <v>183.3509674072266</v>
       </c>
       <c r="F50" t="n">
-        <v>144719700</v>
+        <v>162785400</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B51" t="n">
-        <v>184.5381918075859</v>
+        <v>179.8591224369562</v>
       </c>
       <c r="C51" t="n">
-        <v>185.0469957406681</v>
+        <v>180.8967030087509</v>
       </c>
       <c r="D51" t="n">
-        <v>181.6150239281505</v>
+        <v>176.2076633109278</v>
       </c>
       <c r="E51" t="n">
-        <v>183.3509674072266</v>
+        <v>180.5075988769531</v>
       </c>
       <c r="F51" t="n">
-        <v>162785400</v>
+        <v>182136600</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B52" t="n">
-        <v>179.8591224369562</v>
+        <v>180.6871989054384</v>
       </c>
       <c r="C52" t="n">
-        <v>180.8967030087509</v>
+        <v>182.3932136047752</v>
       </c>
       <c r="D52" t="n">
-        <v>176.2076633109278</v>
+        <v>174.2123443447362</v>
       </c>
       <c r="E52" t="n">
-        <v>180.5075988769531</v>
+        <v>174.6114196777344</v>
       </c>
       <c r="F52" t="n">
-        <v>182136600</v>
+        <v>204274900</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B53" t="n">
-        <v>180.6871831157045</v>
+        <v>177.5245903328353</v>
       </c>
       <c r="C53" t="n">
-        <v>182.3931976659576</v>
+        <v>178.0034654802094</v>
       </c>
       <c r="D53" t="n">
-        <v>174.2123291208211</v>
+        <v>174.6213802569945</v>
       </c>
       <c r="E53" t="n">
-        <v>174.6114044189453</v>
+        <v>175.8784332275391</v>
       </c>
       <c r="F53" t="n">
-        <v>204274900</v>
+        <v>164775600</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B54" t="n">
-        <v>177.5245749312296</v>
+        <v>175.8485012773324</v>
       </c>
       <c r="C54" t="n">
-        <v>178.0034500370577</v>
+        <v>178.0733061224419</v>
       </c>
       <c r="D54" t="n">
-        <v>174.6213651072644</v>
+        <v>174.4916756985292</v>
       </c>
       <c r="E54" t="n">
-        <v>175.87841796875</v>
+        <v>177.3050994873047</v>
       </c>
       <c r="F54" t="n">
-        <v>164775600</v>
+        <v>148588100</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B55" t="n">
-        <v>175.8485012773324</v>
+        <v>175.6888811343</v>
       </c>
       <c r="C55" t="n">
-        <v>178.0733061224419</v>
+        <v>175.7188098781239</v>
       </c>
       <c r="D55" t="n">
-        <v>174.4916756985292</v>
+        <v>169.9123900056319</v>
       </c>
       <c r="E55" t="n">
-        <v>177.3050994873047</v>
+        <v>170.5409240722656</v>
       </c>
       <c r="F55" t="n">
-        <v>148588100</v>
+        <v>222775500</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B56" t="n">
-        <v>175.6888811343</v>
+        <v>174.1225483861358</v>
       </c>
       <c r="C56" t="n">
-        <v>175.7188098781239</v>
+        <v>175.7387615308714</v>
       </c>
       <c r="D56" t="n">
-        <v>169.9123900056319</v>
+        <v>171.4188835631069</v>
       </c>
       <c r="E56" t="n">
-        <v>170.5409240722656</v>
+        <v>173.7334594726562</v>
       </c>
       <c r="F56" t="n">
-        <v>222775500</v>
+        <v>176096000</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B57" t="n">
-        <v>174.1225483861358</v>
+        <v>176.2575672304301</v>
       </c>
       <c r="C57" t="n">
-        <v>175.7387615308714</v>
+        <v>181.0264072425164</v>
       </c>
       <c r="D57" t="n">
-        <v>171.4188835631069</v>
+        <v>175.9283357789888</v>
       </c>
       <c r="E57" t="n">
-        <v>173.7334594726562</v>
+        <v>180.5674896240234</v>
       </c>
       <c r="F57" t="n">
-        <v>176096000</v>
+        <v>324925900</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B58" t="n">
-        <v>176.2575672304301</v>
+        <v>183.4906282252173</v>
       </c>
       <c r="C58" t="n">
-        <v>181.0264072425164</v>
+        <v>183.7300734141942</v>
       </c>
       <c r="D58" t="n">
-        <v>175.9283357789888</v>
+        <v>181.9243013805983</v>
       </c>
       <c r="E58" t="n">
-        <v>180.5674896240234</v>
+        <v>183.2611694335938</v>
       </c>
       <c r="F58" t="n">
-        <v>324925900</v>
+        <v>129064400</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B59" t="n">
-        <v>183.4906282252173</v>
+        <v>182.5428571096804</v>
       </c>
       <c r="C59" t="n">
-        <v>183.7300734141942</v>
+        <v>188.8880102762506</v>
       </c>
       <c r="D59" t="n">
-        <v>181.9243013805983</v>
+        <v>182.4730132178061</v>
       </c>
       <c r="E59" t="n">
-        <v>183.2611694335938</v>
+        <v>188.7682952880859</v>
       </c>
       <c r="F59" t="n">
-        <v>129064400</v>
+        <v>174873600</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B60" t="n">
-        <v>182.5428571096804</v>
+        <v>187.5012437217294</v>
       </c>
       <c r="C60" t="n">
-        <v>188.8880102762506</v>
+        <v>188.4689804086018</v>
       </c>
       <c r="D60" t="n">
-        <v>182.4730132178061</v>
+        <v>186.154389299292</v>
       </c>
       <c r="E60" t="n">
-        <v>188.7682952880859</v>
+        <v>188.169677734375</v>
       </c>
       <c r="F60" t="n">
-        <v>174873600</v>
+        <v>65528500</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B61" t="n">
-        <v>187.5012437217294</v>
+        <v>189.4766285187414</v>
       </c>
       <c r="C61" t="n">
-        <v>188.4689804086018</v>
+        <v>192.240166195598</v>
       </c>
       <c r="D61" t="n">
-        <v>186.154389299292</v>
+        <v>187.5611125998212</v>
       </c>
       <c r="E61" t="n">
-        <v>188.169677734375</v>
+        <v>190.085205078125</v>
       </c>
       <c r="F61" t="n">
-        <v>65528500</v>
+        <v>139740300</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B62" t="n">
-        <v>189.4766285187414</v>
+        <v>187.2717899684254</v>
       </c>
       <c r="C62" t="n">
-        <v>192.240166195598</v>
+        <v>188.3193265216257</v>
       </c>
       <c r="D62" t="n">
-        <v>187.5611125998212</v>
+        <v>185.4759890979627</v>
       </c>
       <c r="E62" t="n">
-        <v>190.085205078125</v>
+        <v>187.7805938720703</v>
       </c>
       <c r="F62" t="n">
-        <v>139740300</v>
+        <v>120006100</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B63" t="n">
-        <v>187.2717899684254</v>
+        <v>187.8005508490403</v>
       </c>
       <c r="C63" t="n">
-        <v>188.3193265216257</v>
+        <v>188.5487999407664</v>
       </c>
       <c r="D63" t="n">
-        <v>185.4759890979627</v>
+        <v>186.4935963146986</v>
       </c>
       <c r="E63" t="n">
-        <v>187.7805938720703</v>
+        <v>187.1021728515625</v>
       </c>
       <c r="F63" t="n">
-        <v>120006100</v>
+        <v>97687300</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B64" t="n">
-        <v>187.8005508490403</v>
+        <v>189.1274459397885</v>
       </c>
       <c r="C64" t="n">
-        <v>188.5487999407664</v>
+        <v>190.1151249886817</v>
       </c>
       <c r="D64" t="n">
-        <v>186.4935963146986</v>
+        <v>186.0546345387688</v>
       </c>
       <c r="E64" t="n">
-        <v>187.1021728515625</v>
+        <v>186.0646057128906</v>
       </c>
       <c r="F64" t="n">
-        <v>97687300</v>
+        <v>120100500</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B65" t="n">
-        <v>189.1274459397885</v>
+        <v>189.3968130035911</v>
       </c>
       <c r="C65" t="n">
-        <v>190.1151249886817</v>
+        <v>192.4795957147097</v>
       </c>
       <c r="D65" t="n">
-        <v>186.0546345387688</v>
+        <v>187.8204997023152</v>
       </c>
       <c r="E65" t="n">
-        <v>186.0646057128906</v>
+        <v>188.4091339111328</v>
       </c>
       <c r="F65" t="n">
-        <v>120100500</v>
+        <v>148240500</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B66" t="n">
-        <v>189.3968130035911</v>
+        <v>191.3123182227279</v>
       </c>
       <c r="C66" t="n">
-        <v>192.4795957147097</v>
+        <v>193.1779629368336</v>
       </c>
       <c r="D66" t="n">
-        <v>187.8204997023152</v>
+        <v>185.7154145267434</v>
       </c>
       <c r="E66" t="n">
-        <v>188.4091339111328</v>
+        <v>187.6808166503906</v>
       </c>
       <c r="F66" t="n">
-        <v>148240500</v>
+        <v>183529700</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B67" t="n">
-        <v>191.3123337767646</v>
+        <v>190.0752284670132</v>
       </c>
       <c r="C67" t="n">
-        <v>193.1779786425506</v>
+        <v>191.7213703933745</v>
       </c>
       <c r="D67" t="n">
-        <v>185.7154296257417</v>
+        <v>186.3838692947835</v>
       </c>
       <c r="E67" t="n">
-        <v>187.6808319091797</v>
+        <v>186.8028869628906</v>
       </c>
       <c r="F67" t="n">
-        <v>183529700</v>
+        <v>176862600</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B68" t="n">
-        <v>190.0752284670132</v>
+        <v>188.1297854095839</v>
       </c>
       <c r="C68" t="n">
-        <v>191.7213703933745</v>
+        <v>190.9232365533545</v>
       </c>
       <c r="D68" t="n">
-        <v>186.3838692947835</v>
+        <v>186.1244680675316</v>
       </c>
       <c r="E68" t="n">
-        <v>186.8028869628906</v>
+        <v>188.6685180664062</v>
       </c>
       <c r="F68" t="n">
-        <v>176862600</v>
+        <v>153543200</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B69" t="n">
-        <v>188.1297854095839</v>
+        <v>188.6685228499072</v>
       </c>
       <c r="C69" t="n">
-        <v>190.9232365533545</v>
+        <v>189.1074981045344</v>
       </c>
       <c r="D69" t="n">
-        <v>186.1244680675316</v>
+        <v>183.2811352524241</v>
       </c>
       <c r="E69" t="n">
-        <v>188.6685180664062</v>
+        <v>184.6080169677734</v>
       </c>
       <c r="F69" t="n">
-        <v>153543200</v>
+        <v>172457000</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B70" t="n">
-        <v>188.6685072554968</v>
+        <v>184.6479238968445</v>
       </c>
       <c r="C70" t="n">
-        <v>189.1074824738404</v>
+        <v>185.9049768874807</v>
       </c>
       <c r="D70" t="n">
-        <v>183.2811201033086</v>
+        <v>183.2412119543349</v>
       </c>
       <c r="E70" t="n">
-        <v>184.6080017089844</v>
+        <v>184.4284362792969</v>
       </c>
       <c r="F70" t="n">
-        <v>172457000</v>
+        <v>131327500</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B71" t="n">
-        <v>184.6479238968445</v>
+        <v>182.7922691735387</v>
       </c>
       <c r="C71" t="n">
-        <v>185.9049768874807</v>
+        <v>186.6831584288149</v>
       </c>
       <c r="D71" t="n">
-        <v>183.2412119543349</v>
+        <v>182.5927391235801</v>
       </c>
       <c r="E71" t="n">
-        <v>184.4284362792969</v>
+        <v>184.5082550048828</v>
       </c>
       <c r="F71" t="n">
-        <v>131327500</v>
+        <v>137968500</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B72" t="n">
-        <v>182.7922691735387</v>
+        <v>184.5680989064521</v>
       </c>
       <c r="C72" t="n">
-        <v>186.6831584288149</v>
+        <v>187.6708389078061</v>
       </c>
       <c r="D72" t="n">
-        <v>182.5927391235801</v>
+        <v>182.9718281779948</v>
       </c>
       <c r="E72" t="n">
-        <v>184.5082550048828</v>
+        <v>185.3762054443359</v>
       </c>
       <c r="F72" t="n">
-        <v>137968500</v>
+        <v>160128900</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B73" t="n">
-        <v>184.5681140987238</v>
+        <v>183.889716612774</v>
       </c>
       <c r="C73" t="n">
-        <v>187.6708543554723</v>
+        <v>184.029389177148</v>
       </c>
       <c r="D73" t="n">
-        <v>182.9718432388734</v>
+        <v>180.3779297072971</v>
       </c>
       <c r="E73" t="n">
-        <v>185.376220703125</v>
+        <v>182.7124633789062</v>
       </c>
       <c r="F73" t="n">
-        <v>160128900</v>
+        <v>159586100</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B74" t="n">
-        <v>183.8897012556695</v>
+        <v>186.0646079796491</v>
       </c>
       <c r="C74" t="n">
-        <v>184.0293738083791</v>
+        <v>189.2571344016907</v>
       </c>
       <c r="D74" t="n">
-        <v>180.3779146434709</v>
+        <v>185.895006678512</v>
       </c>
       <c r="E74" t="n">
-        <v>182.7124481201172</v>
+        <v>186.6133270263672</v>
       </c>
       <c r="F74" t="n">
-        <v>159586100</v>
+        <v>206188600</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B75" t="n">
-        <v>186.0645927657271</v>
+        <v>188.6385950815971</v>
       </c>
       <c r="C75" t="n">
-        <v>189.2571189267257</v>
+        <v>189.9954207742267</v>
       </c>
       <c r="D75" t="n">
-        <v>185.8949914784577</v>
+        <v>185.6455985734289</v>
       </c>
       <c r="E75" t="n">
-        <v>186.6133117675781</v>
+        <v>185.7952423095703</v>
       </c>
       <c r="F75" t="n">
-        <v>206188600</v>
+        <v>187967200</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B76" t="n">
-        <v>188.6385795892923</v>
+        <v>181.4753578011745</v>
       </c>
       <c r="C76" t="n">
-        <v>189.99540517049</v>
+        <v>181.9542482267672</v>
       </c>
       <c r="D76" t="n">
-        <v>185.6455833269296</v>
+        <v>177.1953792817215</v>
       </c>
       <c r="E76" t="n">
-        <v>185.7952270507812</v>
+        <v>177.6543121337891</v>
       </c>
       <c r="F76" t="n">
-        <v>187967200</v>
+        <v>223345300</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B77" t="n">
-        <v>181.4753422141945</v>
+        <v>178.6319932794081</v>
       </c>
       <c r="C77" t="n">
-        <v>181.9542325986551</v>
+        <v>184.947217101084</v>
       </c>
       <c r="D77" t="n">
-        <v>177.1953640623503</v>
+        <v>177.9835016341843</v>
       </c>
       <c r="E77" t="n">
-        <v>177.654296875</v>
+        <v>182.8920288085938</v>
       </c>
       <c r="F77" t="n">
-        <v>223345300</v>
+        <v>200381000</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B78" t="n">
-        <v>178.6320081827799</v>
+        <v>184.3186915464293</v>
       </c>
       <c r="C78" t="n">
-        <v>184.9472325313386</v>
+        <v>185.7353746560278</v>
       </c>
       <c r="D78" t="n">
-        <v>177.9835164834521</v>
+        <v>183.5005985718231</v>
       </c>
       <c r="E78" t="n">
-        <v>182.8920440673828</v>
+        <v>184.4084777832031</v>
       </c>
       <c r="F78" t="n">
-        <v>200381000</v>
+        <v>139636600</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B79" t="n">
-        <v>184.3186915464293</v>
+        <v>187.0622712594319</v>
       </c>
       <c r="C79" t="n">
-        <v>185.7353746560278</v>
+        <v>189.1573747868041</v>
       </c>
       <c r="D79" t="n">
-        <v>183.5005985718231</v>
+        <v>186.3838660627843</v>
       </c>
       <c r="E79" t="n">
-        <v>184.4084777832031</v>
+        <v>187.2318725585938</v>
       </c>
       <c r="F79" t="n">
-        <v>139636600</v>
+        <v>142748100</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B80" t="n">
-        <v>187.0622712594319</v>
+        <v>186.7230748442759</v>
       </c>
       <c r="C80" t="n">
-        <v>189.1573747868041</v>
+        <v>188.6784906596197</v>
       </c>
       <c r="D80" t="n">
-        <v>186.3838660627843</v>
+        <v>185.555808059744</v>
       </c>
       <c r="E80" t="n">
-        <v>187.2318725585938</v>
+        <v>186.0346832275391</v>
       </c>
       <c r="F80" t="n">
-        <v>142748100</v>
+        <v>124799600</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B81" t="n">
-        <v>186.7230748442759</v>
+        <v>186.8028844605491</v>
       </c>
       <c r="C81" t="n">
-        <v>188.6784906596197</v>
+        <v>189.5564356240106</v>
       </c>
       <c r="D81" t="n">
-        <v>185.555808059744</v>
+        <v>185.2664711415707</v>
       </c>
       <c r="E81" t="n">
-        <v>186.0346832275391</v>
+        <v>188.0798950195312</v>
       </c>
       <c r="F81" t="n">
-        <v>124799600</v>
+        <v>143711600</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B82" t="n">
-        <v>186.8028844605491</v>
+        <v>190.823459633995</v>
       </c>
       <c r="C82" t="n">
-        <v>189.5564356240106</v>
+        <v>191.9009400606663</v>
       </c>
       <c r="D82" t="n">
-        <v>185.2664711415707</v>
+        <v>189.3967902384632</v>
       </c>
       <c r="E82" t="n">
-        <v>188.0798950195312</v>
+        <v>191.0728759765625</v>
       </c>
       <c r="F82" t="n">
-        <v>143711600</v>
+        <v>148552700</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B83" t="n">
-        <v>190.823459633995</v>
+        <v>190.8933105997472</v>
       </c>
       <c r="C83" t="n">
-        <v>191.9009400606663</v>
+        <v>193.0283141326731</v>
       </c>
       <c r="D83" t="n">
-        <v>189.3967902384632</v>
+        <v>185.6256380470483</v>
       </c>
       <c r="E83" t="n">
-        <v>191.0728759765625</v>
+        <v>192.0605773925781</v>
       </c>
       <c r="F83" t="n">
-        <v>148552700</v>
+        <v>171764400</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B84" t="n">
-        <v>190.8933105997472</v>
+        <v>190.7636224379378</v>
       </c>
       <c r="C84" t="n">
-        <v>193.0283141326731</v>
+        <v>194.0359639826301</v>
       </c>
       <c r="D84" t="n">
-        <v>185.6256380470483</v>
+        <v>189.0276790286862</v>
       </c>
       <c r="E84" t="n">
-        <v>192.0605773925781</v>
+        <v>190.6838073730469</v>
       </c>
       <c r="F84" t="n">
-        <v>171764400</v>
+        <v>179489500</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B85" t="n">
-        <v>190.7636224379378</v>
+        <v>186.7629659025267</v>
       </c>
       <c r="C85" t="n">
-        <v>194.0359639826301</v>
+        <v>189.8557348322644</v>
       </c>
       <c r="D85" t="n">
-        <v>189.0276790286862</v>
+        <v>184.4483900153819</v>
       </c>
       <c r="E85" t="n">
-        <v>190.6838073730469</v>
+        <v>185.1766815185547</v>
       </c>
       <c r="F85" t="n">
-        <v>179489500</v>
+        <v>165794100</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B86" t="n">
-        <v>186.7629659025267</v>
+        <v>185.8052108647954</v>
       </c>
       <c r="C86" t="n">
-        <v>189.8557348322644</v>
+        <v>185.8351396091497</v>
       </c>
       <c r="D86" t="n">
-        <v>184.4483900153819</v>
+        <v>175.8185703987175</v>
       </c>
       <c r="E86" t="n">
-        <v>185.1766815185547</v>
+        <v>179.9189758300781</v>
       </c>
       <c r="F86" t="n">
-        <v>165794100</v>
+        <v>204019600</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B87" t="n">
-        <v>185.8052108647954</v>
+        <v>179.0410571553003</v>
       </c>
       <c r="C87" t="n">
-        <v>185.8351396091497</v>
+        <v>179.1607721437711</v>
       </c>
       <c r="D87" t="n">
-        <v>175.8185703987175</v>
+        <v>171.5086795929406</v>
       </c>
       <c r="E87" t="n">
-        <v>179.9189758300781</v>
+        <v>173.7833557128906</v>
       </c>
       <c r="F87" t="n">
-        <v>204019600</v>
+        <v>207014100</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B88" t="n">
-        <v>179.0410571553003</v>
+        <v>174.5216119878791</v>
       </c>
       <c r="C88" t="n">
-        <v>179.1607721437711</v>
+        <v>176.4072143255947</v>
       </c>
       <c r="D88" t="n">
-        <v>171.5086795929406</v>
+        <v>170.6307227747363</v>
       </c>
       <c r="E88" t="n">
-        <v>173.7833557128906</v>
+        <v>171.4787445068359</v>
       </c>
       <c r="F88" t="n">
-        <v>207014100</v>
+        <v>206312900</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B89" t="n">
-        <v>174.5216119878791</v>
+        <v>176.2775280578147</v>
       </c>
       <c r="C89" t="n">
-        <v>176.4072143255947</v>
+        <v>186.5634574188361</v>
       </c>
       <c r="D89" t="n">
-        <v>170.6307227747363</v>
+        <v>174.1924107166939</v>
       </c>
       <c r="E89" t="n">
-        <v>171.4787445068359</v>
+        <v>184.9771728515625</v>
       </c>
       <c r="F89" t="n">
-        <v>206312900</v>
+        <v>231346200</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B90" t="n">
-        <v>176.2775135166603</v>
+        <v>183.8298238555102</v>
       </c>
       <c r="C90" t="n">
-        <v>186.5634420291942</v>
+        <v>193.2078878887748</v>
       </c>
       <c r="D90" t="n">
-        <v>174.1923963475411</v>
+        <v>183.5205500126207</v>
       </c>
       <c r="E90" t="n">
-        <v>184.9771575927734</v>
+        <v>189.5963287353516</v>
       </c>
       <c r="F90" t="n">
-        <v>231346200</v>
+        <v>196387400</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B91" t="n">
-        <v>183.8298386502086</v>
+        <v>190.9332352083219</v>
       </c>
       <c r="C91" t="n">
-        <v>193.2079034382237</v>
+        <v>192.0306581643501</v>
       </c>
       <c r="D91" t="n">
-        <v>183.5205647824287</v>
+        <v>187.6808358171596</v>
       </c>
       <c r="E91" t="n">
-        <v>189.5963439941406</v>
+        <v>188.099853515625</v>
       </c>
       <c r="F91" t="n">
-        <v>196387400</v>
+        <v>136764800</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B92" t="n">
-        <v>190.933219719687</v>
+        <v>192.0007142509167</v>
       </c>
       <c r="C92" t="n">
-        <v>192.0306425866914</v>
+        <v>192.8088208357837</v>
       </c>
       <c r="D92" t="n">
-        <v>187.6808205923615</v>
+        <v>188.329312674443</v>
       </c>
       <c r="E92" t="n">
-        <v>188.0998382568359</v>
+        <v>189.6063232421875</v>
       </c>
       <c r="F92" t="n">
-        <v>136764800</v>
+        <v>144192700</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B93" t="n">
-        <v>192.0007297023972</v>
+        <v>192.5793648877844</v>
       </c>
       <c r="C93" t="n">
-        <v>192.8088363522974</v>
+        <v>193.1580126884611</v>
       </c>
       <c r="D93" t="n">
-        <v>188.3293278304631</v>
+        <v>186.0745817463215</v>
       </c>
       <c r="E93" t="n">
-        <v>189.6063385009766</v>
+        <v>186.5035858154297</v>
       </c>
       <c r="F93" t="n">
-        <v>144192700</v>
+        <v>189932500</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B94" t="n">
-        <v>192.5793648877844</v>
+        <v>187.042320465516</v>
       </c>
       <c r="C94" t="n">
-        <v>193.1580126884611</v>
+        <v>187.0622780376601</v>
       </c>
       <c r="D94" t="n">
-        <v>186.0745817463215</v>
+        <v>181.1660713803529</v>
       </c>
       <c r="E94" t="n">
-        <v>186.5035858154297</v>
+        <v>182.3832244873047</v>
       </c>
       <c r="F94" t="n">
-        <v>189932500</v>
+        <v>161888000</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B95" t="n">
-        <v>187.0423048169314</v>
+        <v>181.3256935584433</v>
       </c>
       <c r="C95" t="n">
-        <v>187.0622623874058</v>
+        <v>186.7130808403767</v>
       </c>
       <c r="D95" t="n">
-        <v>181.1660562233949</v>
+        <v>178.7616860728079</v>
       </c>
       <c r="E95" t="n">
-        <v>182.3832092285156</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="F95" t="n">
-        <v>161888000</v>
+        <v>162276900</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B96" t="n">
-        <v>181.3256935584433</v>
+        <v>188.3093443160685</v>
       </c>
       <c r="C96" t="n">
-        <v>186.7130808403767</v>
+        <v>189.9255573932224</v>
       </c>
       <c r="D96" t="n">
-        <v>178.7616860728079</v>
+        <v>186.3239846890322</v>
       </c>
       <c r="E96" t="n">
-        <v>184.5381774902344</v>
+        <v>187.5411376953125</v>
       </c>
       <c r="F96" t="n">
-        <v>162276900</v>
+        <v>164749100</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B97" t="n">
-        <v>188.3093443160685</v>
+        <v>186.62329889396</v>
       </c>
       <c r="C97" t="n">
-        <v>189.9255573932224</v>
+        <v>187.9900957055448</v>
       </c>
       <c r="D97" t="n">
-        <v>186.3239846890322</v>
+        <v>185.2265733363672</v>
       </c>
       <c r="E97" t="n">
-        <v>187.5411376953125</v>
+        <v>187.4613342285156</v>
       </c>
       <c r="F97" t="n">
-        <v>164749100</v>
+        <v>126554500</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B98" t="n">
-        <v>186.62329889396</v>
+        <v>186.1344488846578</v>
       </c>
       <c r="C98" t="n">
-        <v>187.9900957055448</v>
+        <v>189.8856654675195</v>
       </c>
       <c r="D98" t="n">
-        <v>185.2265733363672</v>
+        <v>185.5059147845697</v>
       </c>
       <c r="E98" t="n">
-        <v>187.4613342285156</v>
+        <v>189.3768615722656</v>
       </c>
       <c r="F98" t="n">
-        <v>126554500</v>
+        <v>178422300</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B99" t="n">
-        <v>186.1344638821937</v>
+        <v>190.9531547742145</v>
       </c>
       <c r="C99" t="n">
-        <v>189.8856807673048</v>
+        <v>193.4972046328596</v>
       </c>
       <c r="D99" t="n">
-        <v>185.5059297314624</v>
+        <v>189.1374116308485</v>
       </c>
       <c r="E99" t="n">
-        <v>189.3768768310547</v>
+        <v>191.1028137207031</v>
       </c>
       <c r="F99" t="n">
-        <v>178422300</v>
+        <v>171584800</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B100" t="n">
-        <v>190.9531547742145</v>
+        <v>191.0429698590405</v>
       </c>
       <c r="C100" t="n">
-        <v>193.4972046328596</v>
+        <v>193.3176459547985</v>
       </c>
       <c r="D100" t="n">
-        <v>189.1374116308485</v>
+        <v>186.9625064417709</v>
       </c>
       <c r="E100" t="n">
-        <v>191.1028137207031</v>
+        <v>192.3997955322266</v>
       </c>
       <c r="F100" t="n">
-        <v>171584800</v>
+        <v>175123600</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B101" t="n">
-        <v>191.0429698590405</v>
+        <v>193.9960453222018</v>
       </c>
       <c r="C101" t="n">
-        <v>193.3176459547985</v>
+        <v>197.1686293956491</v>
       </c>
       <c r="D101" t="n">
-        <v>186.9625064417709</v>
+        <v>193.3375824661624</v>
       </c>
       <c r="E101" t="n">
-        <v>192.3997955322266</v>
+        <v>195.1034545898438</v>
       </c>
       <c r="F101" t="n">
-        <v>175123600</v>
+        <v>250637100</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B102" t="n">
-        <v>193.9960453222018</v>
+        <v>193.8164813019665</v>
       </c>
       <c r="C102" t="n">
-        <v>197.1686293956491</v>
+        <v>193.8364236513225</v>
       </c>
       <c r="D102" t="n">
-        <v>193.3375824661624</v>
+        <v>183.8897126034445</v>
       </c>
       <c r="E102" t="n">
-        <v>195.1034545898438</v>
+        <v>184.4583740234375</v>
       </c>
       <c r="F102" t="n">
-        <v>250637100</v>
+        <v>360807900</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B103" t="n">
-        <v>193.8164652690549</v>
+        <v>180.8268714126474</v>
       </c>
       <c r="C103" t="n">
-        <v>193.8364076167612</v>
+        <v>182.1637395256691</v>
       </c>
       <c r="D103" t="n">
-        <v>183.8896973916963</v>
+        <v>175.9682453114839</v>
       </c>
       <c r="E103" t="n">
-        <v>184.4583587646484</v>
+        <v>176.7763519287109</v>
       </c>
       <c r="F103" t="n">
-        <v>360807900</v>
+        <v>311636500</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B104" t="n">
-        <v>180.8268714126474</v>
+        <v>174.6014235260267</v>
       </c>
       <c r="C104" t="n">
-        <v>182.1637395256691</v>
+        <v>183.0317086895539</v>
       </c>
       <c r="D104" t="n">
-        <v>175.9682453114839</v>
+        <v>174.2322921838959</v>
       </c>
       <c r="E104" t="n">
-        <v>176.7763519287109</v>
+        <v>182.0539855957031</v>
       </c>
       <c r="F104" t="n">
-        <v>311636500</v>
+        <v>209095300</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B105" t="n">
-        <v>174.601438160182</v>
+        <v>178.0733135069376</v>
       </c>
       <c r="C105" t="n">
-        <v>183.0317240302905</v>
+        <v>180.4776756968921</v>
       </c>
       <c r="D105" t="n">
-        <v>174.2323067871125</v>
+        <v>176.5069714269912</v>
       </c>
       <c r="E105" t="n">
-        <v>182.0540008544922</v>
+        <v>179.6296691894531</v>
       </c>
       <c r="F105" t="n">
-        <v>209095300</v>
+        <v>178099400</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B106" t="n">
-        <v>178.0732983803544</v>
+        <v>180.0187499528396</v>
       </c>
       <c r="C106" t="n">
-        <v>180.4776603660684</v>
+        <v>184.2687991412151</v>
       </c>
       <c r="D106" t="n">
-        <v>176.5069564334623</v>
+        <v>179.6396322236537</v>
       </c>
       <c r="E106" t="n">
-        <v>179.6296539306641</v>
+        <v>182.6126708984375</v>
       </c>
       <c r="F106" t="n">
-        <v>178099400</v>
+        <v>177731200</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B107" t="n">
-        <v>180.0187649948852</v>
+        <v>180.7470399397241</v>
       </c>
       <c r="C107" t="n">
-        <v>184.2688145383873</v>
+        <v>183.6302923567135</v>
       </c>
       <c r="D107" t="n">
-        <v>179.6396472340209</v>
+        <v>177.4647274492447</v>
       </c>
       <c r="E107" t="n">
-        <v>182.6126861572266</v>
+        <v>182.9119720458984</v>
       </c>
       <c r="F107" t="n">
-        <v>177731200</v>
+        <v>198779700</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B108" t="n">
-        <v>180.7470399397241</v>
+        <v>179.4201653790109</v>
       </c>
       <c r="C108" t="n">
-        <v>183.6302923567135</v>
+        <v>182.3333469017365</v>
       </c>
       <c r="D108" t="n">
-        <v>177.4647274492447</v>
+        <v>176.4072264371208</v>
       </c>
       <c r="E108" t="n">
-        <v>182.9119720458984</v>
+        <v>177.4048919677734</v>
       </c>
       <c r="F108" t="n">
-        <v>198779700</v>
+        <v>189021900</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B109" t="n">
-        <v>179.4201653790109</v>
+        <v>176.4171820751478</v>
       </c>
       <c r="C109" t="n">
-        <v>182.3333469017365</v>
+        <v>182.4829897940845</v>
       </c>
       <c r="D109" t="n">
-        <v>176.4072264371208</v>
+        <v>175.1501427003192</v>
       </c>
       <c r="E109" t="n">
-        <v>177.4048919677734</v>
+        <v>182.2235870361328</v>
       </c>
       <c r="F109" t="n">
-        <v>189021900</v>
+        <v>177213600</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B110" t="n">
-        <v>176.4171820751478</v>
+        <v>181.9741609804723</v>
       </c>
       <c r="C110" t="n">
-        <v>182.4829897940845</v>
+        <v>186.0047376795775</v>
       </c>
       <c r="D110" t="n">
-        <v>175.1501427003192</v>
+        <v>181.5850720874406</v>
       </c>
       <c r="E110" t="n">
-        <v>182.2235870361328</v>
+        <v>184.3386383056641</v>
       </c>
       <c r="F110" t="n">
-        <v>177213600</v>
+        <v>179118500</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,25 +3303,25 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B111" t="n">
-        <v>181.9741609804723</v>
+        <v>185.4860219488843</v>
       </c>
       <c r="C111" t="n">
-        <v>186.0047376795775</v>
+        <v>187.1921136401388</v>
       </c>
       <c r="D111" t="n">
-        <v>181.5850720874406</v>
+        <v>184.0293448898806</v>
       </c>
       <c r="E111" t="n">
-        <v>184.3386383056641</v>
+        <v>185.6057434082031</v>
       </c>
       <c r="F111" t="n">
-        <v>179118500</v>
+        <v>145280400</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3329,25 +3329,25 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B112" t="n">
-        <v>185.4860219488843</v>
+        <v>183.6302794851663</v>
       </c>
       <c r="C112" t="n">
-        <v>187.1921136401388</v>
+        <v>184.5182492431283</v>
       </c>
       <c r="D112" t="n">
-        <v>184.0293448898806</v>
+        <v>181.3355215595592</v>
       </c>
       <c r="E112" t="n">
-        <v>185.6057434082031</v>
+        <v>182.7223510742188</v>
       </c>
       <c r="F112" t="n">
-        <v>145280400</v>
+        <v>155762700</v>
       </c>
       <c r="G112" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B113" t="n">
-        <v>183.6302794851663</v>
+        <v>184.4982761588831</v>
       </c>
       <c r="C113" t="n">
-        <v>184.5182492431283</v>
+        <v>185.6656060713691</v>
       </c>
       <c r="D113" t="n">
-        <v>181.3355215595592</v>
+        <v>179.5296376335348</v>
       </c>
       <c r="E113" t="n">
-        <v>182.7223510742188</v>
+        <v>179.8389282226562</v>
       </c>
       <c r="F113" t="n">
-        <v>155762700</v>
+        <v>160988400</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B114" t="n">
-        <v>184.4982761588831</v>
+        <v>182.5527399223597</v>
       </c>
       <c r="C114" t="n">
-        <v>185.6656060713691</v>
+        <v>188.4492658789173</v>
       </c>
       <c r="D114" t="n">
-        <v>179.5296376335348</v>
+        <v>180.9962999229416</v>
       </c>
       <c r="E114" t="n">
-        <v>179.8389282226562</v>
+        <v>182.8021697998047</v>
       </c>
       <c r="F114" t="n">
-        <v>160988400</v>
+        <v>217307400</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B115" t="n">
-        <v>182.5527399223597</v>
+        <v>184.6379576703901</v>
       </c>
       <c r="C115" t="n">
-        <v>188.4492658789173</v>
+        <v>184.9771786272242</v>
       </c>
       <c r="D115" t="n">
-        <v>180.9962999229416</v>
+        <v>181.2656610816535</v>
       </c>
       <c r="E115" t="n">
-        <v>182.8021697998047</v>
+        <v>181.5150909423828</v>
       </c>
       <c r="F115" t="n">
-        <v>217307400</v>
+        <v>182497800</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B116" t="n">
-        <v>184.6379576703901</v>
+        <v>182.0638447517288</v>
       </c>
       <c r="C116" t="n">
-        <v>184.9771786272242</v>
+        <v>182.9618014097589</v>
       </c>
       <c r="D116" t="n">
-        <v>181.2656610816535</v>
+        <v>179.9187539793071</v>
       </c>
       <c r="E116" t="n">
-        <v>181.5150909423828</v>
+        <v>179.9885864257812</v>
       </c>
       <c r="F116" t="n">
-        <v>182497800</v>
+        <v>156683100</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B117" t="n">
-        <v>182.0638447517288</v>
+        <v>177.6040375011918</v>
       </c>
       <c r="C117" t="n">
-        <v>182.9618014097589</v>
+        <v>179.569546076418</v>
       </c>
       <c r="D117" t="n">
-        <v>179.9187539793071</v>
+        <v>175.3890990582871</v>
       </c>
       <c r="E117" t="n">
-        <v>179.9885864257812</v>
+        <v>178.1527862548828</v>
       </c>
       <c r="F117" t="n">
-        <v>156683100</v>
+        <v>170968500</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B118" t="n">
-        <v>177.6040375011918</v>
+        <v>177.5940529420793</v>
       </c>
       <c r="C118" t="n">
-        <v>179.569546076418</v>
+        <v>177.8534545050662</v>
       </c>
       <c r="D118" t="n">
-        <v>175.3890990582871</v>
+        <v>171.3283763370981</v>
       </c>
       <c r="E118" t="n">
-        <v>178.1527862548828</v>
+        <v>172.3061370849609</v>
       </c>
       <c r="F118" t="n">
-        <v>170968500</v>
+        <v>241323500</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B119" t="n">
-        <v>177.5940529420793</v>
+        <v>176.8557415306554</v>
       </c>
       <c r="C119" t="n">
-        <v>177.8534545050662</v>
+        <v>177.9632107122345</v>
       </c>
       <c r="D119" t="n">
-        <v>171.3283763370981</v>
+        <v>174.3614429436745</v>
       </c>
       <c r="E119" t="n">
-        <v>172.3061370849609</v>
+        <v>175.2394409179688</v>
       </c>
       <c r="F119" t="n">
-        <v>241323500</v>
+        <v>182836300</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B120" t="n">
-        <v>176.8557415306554</v>
+        <v>174.4312942297872</v>
       </c>
       <c r="C120" t="n">
-        <v>177.9632107122345</v>
+        <v>175.8181236639554</v>
       </c>
       <c r="D120" t="n">
-        <v>174.3614429436745</v>
+        <v>173.5832266030264</v>
       </c>
       <c r="E120" t="n">
-        <v>175.2394409179688</v>
+        <v>174.8004455566406</v>
       </c>
       <c r="F120" t="n">
-        <v>182836300</v>
+        <v>147667800</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B121" t="n">
-        <v>174.4312942297872</v>
+        <v>176.6961233561449</v>
       </c>
       <c r="C121" t="n">
-        <v>175.8181236639554</v>
+        <v>180.8067226806179</v>
       </c>
       <c r="D121" t="n">
-        <v>173.5832266030264</v>
+        <v>176.4466934898736</v>
       </c>
       <c r="E121" t="n">
-        <v>174.8004455566406</v>
+        <v>178.2725067138672</v>
       </c>
       <c r="F121" t="n">
-        <v>147667800</v>
+        <v>162602100</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B122" t="n">
-        <v>176.6961233561449</v>
+        <v>175.6684741654964</v>
       </c>
       <c r="C122" t="n">
-        <v>180.8067226806179</v>
+        <v>176.1074579435819</v>
       </c>
       <c r="D122" t="n">
-        <v>176.4466934898736</v>
+        <v>170.7497092682189</v>
       </c>
       <c r="E122" t="n">
-        <v>178.2725067138672</v>
+        <v>170.8494873046875</v>
       </c>
       <c r="F122" t="n">
-        <v>162602100</v>
+        <v>186152200</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B123" t="n">
-        <v>175.6684741654964</v>
+        <v>169.6122945102883</v>
       </c>
       <c r="C123" t="n">
-        <v>176.1074579435819</v>
+        <v>170.5800835262955</v>
       </c>
       <c r="D123" t="n">
-        <v>170.7497092682189</v>
+        <v>166.6291080850299</v>
       </c>
       <c r="E123" t="n">
-        <v>170.8494873046875</v>
+        <v>167.1379547119141</v>
       </c>
       <c r="F123" t="n">
-        <v>186152200</v>
+        <v>196212700</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B124" t="n">
-        <v>169.6122945102883</v>
+        <v>168.3950875250076</v>
       </c>
       <c r="C124" t="n">
-        <v>170.5800835262955</v>
+        <v>169.0635577295173</v>
       </c>
       <c r="D124" t="n">
-        <v>166.6291080850299</v>
+        <v>163.8953782868944</v>
       </c>
       <c r="E124" t="n">
-        <v>167.1379547119141</v>
+        <v>164.7933197021484</v>
       </c>
       <c r="F124" t="n">
-        <v>196212700</v>
+        <v>185627000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B125" t="n">
-        <v>168.3950875250076</v>
+        <v>166.5892250311153</v>
       </c>
       <c r="C125" t="n">
-        <v>169.0635577295173</v>
+        <v>174.2217730660379</v>
       </c>
       <c r="D125" t="n">
-        <v>163.8953782868944</v>
+        <v>166.5792533168182</v>
       </c>
       <c r="E125" t="n">
-        <v>164.7933197021484</v>
+        <v>174.0022735595703</v>
       </c>
       <c r="F125" t="n">
-        <v>185627000</v>
+        <v>226181300</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B126" t="n">
-        <v>166.5892250311153</v>
+        <v>175.5986272559566</v>
       </c>
       <c r="C126" t="n">
-        <v>174.2217730660379</v>
+        <v>176.9654980623514</v>
       </c>
       <c r="D126" t="n">
-        <v>166.5792533168182</v>
+        <v>174.3514779146501</v>
       </c>
       <c r="E126" t="n">
-        <v>174.0022735595703</v>
+        <v>175.3491973876953</v>
       </c>
       <c r="F126" t="n">
-        <v>226181300</v>
+        <v>168132000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B127" t="n">
-        <v>175.5986272559566</v>
+        <v>171.7873183615289</v>
       </c>
       <c r="C127" t="n">
-        <v>176.9654980623514</v>
+        <v>177.0852211444685</v>
       </c>
       <c r="D127" t="n">
-        <v>174.3514779146501</v>
+        <v>170.9791680862979</v>
       </c>
       <c r="E127" t="n">
-        <v>175.3491973876953</v>
+        <v>176.9854431152344</v>
       </c>
       <c r="F127" t="n">
-        <v>168132000</v>
+        <v>143143200</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B128" t="n">
-        <v>171.7873183615289</v>
+        <v>176.7559774774269</v>
       </c>
       <c r="C128" t="n">
-        <v>177.0852211444685</v>
+        <v>177.3845303646084</v>
       </c>
       <c r="D128" t="n">
-        <v>170.9791680862979</v>
+        <v>175.3591611441553</v>
       </c>
       <c r="E128" t="n">
-        <v>176.9854431152344</v>
+        <v>177.2348785400391</v>
       </c>
       <c r="F128" t="n">
-        <v>143143200</v>
+        <v>107564300</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B129" t="n">
-        <v>176.7559774774269</v>
+        <v>175.3292270516068</v>
       </c>
       <c r="C129" t="n">
-        <v>177.3845303646084</v>
+        <v>177.8235255680002</v>
       </c>
       <c r="D129" t="n">
-        <v>175.3591611441553</v>
+        <v>173.2639557965079</v>
       </c>
       <c r="E129" t="n">
-        <v>177.2348785400391</v>
+        <v>177.6938323974609</v>
       </c>
       <c r="F129" t="n">
-        <v>107564300</v>
+        <v>132534900</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B130" t="n">
-        <v>175.3292270516068</v>
+        <v>184.079243714486</v>
       </c>
       <c r="C130" t="n">
-        <v>177.8235255680002</v>
+        <v>184.837505037226</v>
       </c>
       <c r="D130" t="n">
-        <v>173.2639557965079</v>
+        <v>179.8888249511496</v>
       </c>
       <c r="E130" t="n">
-        <v>177.6938323974609</v>
+        <v>181.6647644042969</v>
       </c>
       <c r="F130" t="n">
-        <v>132534900</v>
+        <v>147732700</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B131" t="n">
-        <v>184.079243714486</v>
+        <v>181.4252987848774</v>
       </c>
       <c r="C131" t="n">
-        <v>184.837505037226</v>
+        <v>183.6601958045732</v>
       </c>
       <c r="D131" t="n">
-        <v>179.8888249511496</v>
+        <v>180.2080798537204</v>
       </c>
       <c r="E131" t="n">
-        <v>181.6647644042969</v>
+        <v>183.4905853271484</v>
       </c>
       <c r="F131" t="n">
-        <v>147732700</v>
+        <v>116428500</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B132" t="n">
-        <v>181.4252987848774</v>
+        <v>183.8896736698189</v>
       </c>
       <c r="C132" t="n">
-        <v>183.6601958045732</v>
+        <v>189.5666999081706</v>
       </c>
       <c r="D132" t="n">
-        <v>180.2080798537204</v>
+        <v>183.8797019557237</v>
       </c>
       <c r="E132" t="n">
-        <v>183.4905853271484</v>
+        <v>188.1998291015625</v>
       </c>
       <c r="F132" t="n">
-        <v>116428500</v>
+        <v>160459500</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B133" t="n">
-        <v>183.8896736698189</v>
+        <v>185.605746824658</v>
       </c>
       <c r="C133" t="n">
-        <v>189.5666999081706</v>
+        <v>189.2274732756209</v>
       </c>
       <c r="D133" t="n">
-        <v>183.8797019557237</v>
+        <v>185.3164148846483</v>
       </c>
       <c r="E133" t="n">
-        <v>188.1998291015625</v>
+        <v>188.8782653808594</v>
       </c>
       <c r="F133" t="n">
-        <v>160459500</v>
+        <v>133648200</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B134" t="n">
-        <v>185.605746824658</v>
+        <v>190.4047764107204</v>
       </c>
       <c r="C134" t="n">
-        <v>189.2274732756209</v>
+        <v>196.0618438720703</v>
       </c>
       <c r="D134" t="n">
-        <v>185.3164148846483</v>
+        <v>190.3349439656124</v>
       </c>
       <c r="E134" t="n">
-        <v>188.8782653808594</v>
+        <v>196.0618438720703</v>
       </c>
       <c r="F134" t="n">
-        <v>133648200</v>
+        <v>161307000</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B135" t="n">
-        <v>190.4047764107204</v>
+        <v>196.0917851116163</v>
       </c>
       <c r="C135" t="n">
-        <v>196.0618438720703</v>
+        <v>199.9429830157183</v>
       </c>
       <c r="D135" t="n">
-        <v>190.3349439656124</v>
+        <v>195.2936216855987</v>
       </c>
       <c r="E135" t="n">
-        <v>196.0618438720703</v>
+        <v>198.4164733886719</v>
       </c>
       <c r="F135" t="n">
-        <v>161307000</v>
+        <v>185338400</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B136" t="n">
-        <v>196.0917851116163</v>
+        <v>196.9797440092329</v>
       </c>
       <c r="C136" t="n">
-        <v>199.9429830157183</v>
+        <v>199.3942384790618</v>
       </c>
       <c r="D136" t="n">
-        <v>195.2936216855987</v>
+        <v>195.3634433694217</v>
       </c>
       <c r="E136" t="n">
-        <v>198.4164733886719</v>
+        <v>197.8976593017578</v>
       </c>
       <c r="F136" t="n">
-        <v>185338400</v>
+        <v>134012900</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B137" t="n">
-        <v>196.9797440092329</v>
+        <v>199.444107632571</v>
       </c>
       <c r="C137" t="n">
-        <v>199.3942384790618</v>
+        <v>201.2400056483541</v>
       </c>
       <c r="D137" t="n">
-        <v>195.3634433694217</v>
+        <v>198.8155547450397</v>
       </c>
       <c r="E137" t="n">
-        <v>197.8976593017578</v>
+        <v>201.2200469970703</v>
       </c>
       <c r="F137" t="n">
-        <v>134012900</v>
+        <v>160324400</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B138" t="n">
-        <v>199.444107632571</v>
+        <v>199.5239239232554</v>
       </c>
       <c r="C138" t="n">
-        <v>201.2400056483541</v>
+        <v>201.7089318732817</v>
       </c>
       <c r="D138" t="n">
-        <v>198.8155547450397</v>
+        <v>197.3888049886708</v>
       </c>
       <c r="E138" t="n">
-        <v>201.2200469970703</v>
+        <v>201.5991821289062</v>
       </c>
       <c r="F138" t="n">
-        <v>160324400</v>
+        <v>119381400</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B139" t="n">
-        <v>199.5239239232554</v>
+        <v>201.6690479582887</v>
       </c>
       <c r="C139" t="n">
-        <v>201.7089318732817</v>
+        <v>202.2876291783034</v>
       </c>
       <c r="D139" t="n">
-        <v>197.3888049886708</v>
+        <v>198.5461810430697</v>
       </c>
       <c r="E139" t="n">
-        <v>201.5991821289062</v>
+        <v>199.4241790771484</v>
       </c>
       <c r="F139" t="n">
-        <v>119381400</v>
+        <v>107945300</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B140" t="n">
-        <v>201.6690479582887</v>
+        <v>200.5316418294082</v>
       </c>
       <c r="C140" t="n">
-        <v>202.2876291783034</v>
+        <v>202.0381927490234</v>
       </c>
       <c r="D140" t="n">
-        <v>198.5461810430697</v>
+        <v>198.546174602744</v>
       </c>
       <c r="E140" t="n">
-        <v>199.4241790771484</v>
+        <v>202.0381927490234</v>
       </c>
       <c r="F140" t="n">
-        <v>107945300</v>
+        <v>107501000</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B141" t="n">
-        <v>200.5316418294082</v>
+        <v>201.9982837593082</v>
       </c>
       <c r="C141" t="n">
-        <v>202.0381927490234</v>
+        <v>203.3651545152774</v>
       </c>
       <c r="D141" t="n">
-        <v>198.546174602744</v>
+        <v>196.7702284327844</v>
       </c>
       <c r="E141" t="n">
-        <v>202.0381927490234</v>
+        <v>199.1847076416016</v>
       </c>
       <c r="F141" t="n">
-        <v>107501000</v>
+        <v>113561800</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B142" t="n">
-        <v>201.9982837593082</v>
+        <v>199.5039827094276</v>
       </c>
       <c r="C142" t="n">
-        <v>203.3651545152774</v>
+        <v>210.468909435165</v>
       </c>
       <c r="D142" t="n">
-        <v>196.7702284327844</v>
+        <v>199.3543156614425</v>
       </c>
       <c r="E142" t="n">
-        <v>199.1847076416016</v>
+        <v>207.7950286865234</v>
       </c>
       <c r="F142" t="n">
-        <v>113561800</v>
+        <v>214134400</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B143" t="n">
-        <v>199.5039827094276</v>
+        <v>209.1718784416434</v>
       </c>
       <c r="C143" t="n">
-        <v>210.468909435165</v>
+        <v>216.335512072091</v>
       </c>
       <c r="D143" t="n">
-        <v>199.3543156614425</v>
+        <v>206.9070662315077</v>
       </c>
       <c r="E143" t="n">
-        <v>207.7950286865234</v>
+        <v>216.1160125732422</v>
       </c>
       <c r="F143" t="n">
-        <v>214134400</v>
+        <v>187172400</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B144" t="n">
-        <v>209.1718784416434</v>
+        <v>209.0122528840405</v>
       </c>
       <c r="C144" t="n">
-        <v>216.335512072091</v>
+        <v>214.2402930542568</v>
       </c>
       <c r="D144" t="n">
-        <v>206.9070662315077</v>
+        <v>207.7251862691963</v>
       </c>
       <c r="E144" t="n">
-        <v>216.1160125732422</v>
+        <v>212.6838531494141</v>
       </c>
       <c r="F144" t="n">
-        <v>187172400</v>
+        <v>180275400</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B145" t="n">
-        <v>209.0122528840405</v>
+        <v>212.2149257168926</v>
       </c>
       <c r="C145" t="n">
-        <v>214.2402930542568</v>
+        <v>212.2348843687743</v>
       </c>
       <c r="D145" t="n">
-        <v>207.7251862691963</v>
+        <v>207.1066069625242</v>
       </c>
       <c r="E145" t="n">
-        <v>212.6838531494141</v>
+        <v>208.7727966308594</v>
       </c>
       <c r="F145" t="n">
-        <v>180275400</v>
+        <v>123711800</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B146" t="n">
-        <v>212.2149257168926</v>
+        <v>209.4512425942353</v>
       </c>
       <c r="C146" t="n">
-        <v>212.2348843687743</v>
+        <v>209.820409153207</v>
       </c>
       <c r="D146" t="n">
-        <v>207.1066069625242</v>
+        <v>198.2468571251534</v>
       </c>
       <c r="E146" t="n">
-        <v>208.7727966308594</v>
+        <v>199.1148834228516</v>
       </c>
       <c r="F146" t="n">
-        <v>123711800</v>
+        <v>225239200</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B147" t="n">
-        <v>209.4512425942353</v>
+        <v>200.8209691272831</v>
       </c>
       <c r="C147" t="n">
-        <v>209.820409153207</v>
+        <v>202.5370477944956</v>
       </c>
       <c r="D147" t="n">
-        <v>198.2468571251534</v>
+        <v>196.6704525729091</v>
       </c>
       <c r="E147" t="n">
-        <v>199.1148834228516</v>
+        <v>197.9974212646484</v>
       </c>
       <c r="F147" t="n">
-        <v>225239200</v>
+        <v>128647000</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B148" t="n">
-        <v>200.8209691272831</v>
+        <v>199.0450218084295</v>
       </c>
       <c r="C148" t="n">
-        <v>202.5370477944956</v>
+        <v>201.2699318245734</v>
       </c>
       <c r="D148" t="n">
-        <v>196.6704525729091</v>
+        <v>194.2958829090753</v>
       </c>
       <c r="E148" t="n">
-        <v>197.9974212646484</v>
+        <v>198.02734375</v>
       </c>
       <c r="F148" t="n">
-        <v>128647000</v>
+        <v>125368100</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B149" t="n">
-        <v>199.0450218084295</v>
+        <v>198.8454820247872</v>
       </c>
       <c r="C149" t="n">
-        <v>201.2699318245734</v>
+        <v>199.7833407086998</v>
       </c>
       <c r="D149" t="n">
-        <v>194.2958829090753</v>
+        <v>195.5829352820671</v>
       </c>
       <c r="E149" t="n">
-        <v>198.02734375</v>
+        <v>196.0518646240234</v>
       </c>
       <c r="F149" t="n">
-        <v>125368100</v>
+        <v>113406600</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B150" t="n">
-        <v>198.8454820247872</v>
+        <v>199.4341385249406</v>
       </c>
       <c r="C150" t="n">
-        <v>199.7833407086998</v>
+        <v>207.7950323152332</v>
       </c>
       <c r="D150" t="n">
-        <v>195.5829352820671</v>
+        <v>198.1570588579161</v>
       </c>
       <c r="E150" t="n">
-        <v>196.0518646240234</v>
+        <v>207.3560333251953</v>
       </c>
       <c r="F150" t="n">
-        <v>113406600</v>
+        <v>188362800</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B151" t="n">
-        <v>199.4341385249406</v>
+        <v>207.8648724722903</v>
       </c>
       <c r="C151" t="n">
-        <v>207.7950323152332</v>
+        <v>213.7115092245668</v>
       </c>
       <c r="D151" t="n">
-        <v>198.1570588579161</v>
+        <v>206.0290722858257</v>
       </c>
       <c r="E151" t="n">
-        <v>207.3560333251953</v>
+        <v>211.0176696777344</v>
       </c>
       <c r="F151" t="n">
-        <v>188362800</v>
+        <v>168307900</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B152" t="n">
-        <v>207.8648724722903</v>
+        <v>212.5441790763045</v>
       </c>
       <c r="C152" t="n">
-        <v>213.7115092245668</v>
+        <v>217.3033052467507</v>
       </c>
       <c r="D152" t="n">
-        <v>206.0290722858257</v>
+        <v>212.4044989584125</v>
       </c>
       <c r="E152" t="n">
-        <v>211.0176696777344</v>
+        <v>214.709228515625</v>
       </c>
       <c r="F152" t="n">
-        <v>168307900</v>
+        <v>136421400</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B153" t="n">
-        <v>212.5441790763045</v>
+        <v>213.5518657378577</v>
       </c>
       <c r="C153" t="n">
-        <v>217.3033052467507</v>
+        <v>221.7930381906342</v>
       </c>
       <c r="D153" t="n">
-        <v>212.4044989584125</v>
+        <v>213.402213909002</v>
       </c>
       <c r="E153" t="n">
-        <v>214.709228515625</v>
+        <v>218.9395599365234</v>
       </c>
       <c r="F153" t="n">
-        <v>136421400</v>
+        <v>160685800</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B154" t="n">
-        <v>213.5518657378577</v>
+        <v>218.0515943496244</v>
       </c>
       <c r="C154" t="n">
-        <v>221.7930381906342</v>
+        <v>223.239732575863</v>
       </c>
       <c r="D154" t="n">
-        <v>213.402213909002</v>
+        <v>214.4298677829735</v>
       </c>
       <c r="E154" t="n">
-        <v>218.9395599365234</v>
+        <v>220.2765045166016</v>
       </c>
       <c r="F154" t="n">
-        <v>160685800</v>
+        <v>159176600</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B155" t="n">
-        <v>218.0515943496244</v>
+        <v>224.4170305354026</v>
       </c>
       <c r="C155" t="n">
-        <v>223.239732575863</v>
+        <v>227.3203978139454</v>
       </c>
       <c r="D155" t="n">
-        <v>214.4298677829735</v>
+        <v>221.0647077692387</v>
       </c>
       <c r="E155" t="n">
-        <v>220.2765045166016</v>
+        <v>225.3149871826172</v>
       </c>
       <c r="F155" t="n">
-        <v>159176600</v>
+        <v>150405400</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B156" t="n">
-        <v>224.4170305354026</v>
+        <v>229.3258255277811</v>
       </c>
       <c r="C156" t="n">
-        <v>227.3203978139454</v>
+        <v>236.0005559723521</v>
       </c>
       <c r="D156" t="n">
-        <v>221.0647077692387</v>
+        <v>228.7770767762568</v>
       </c>
       <c r="E156" t="n">
-        <v>225.3149871826172</v>
+        <v>235.202392578125</v>
       </c>
       <c r="F156" t="n">
-        <v>150405400</v>
+        <v>180782900</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B157" t="n">
-        <v>229.3258255277811</v>
+        <v>229.2360294447337</v>
       </c>
       <c r="C157" t="n">
-        <v>236.0005559723521</v>
+        <v>230.9720668751014</v>
       </c>
       <c r="D157" t="n">
-        <v>228.7770767762568</v>
+        <v>223.7286287034134</v>
       </c>
       <c r="E157" t="n">
-        <v>235.202392578125</v>
+        <v>224.8061676025391</v>
       </c>
       <c r="F157" t="n">
-        <v>180782900</v>
+        <v>180977600</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B158" t="n">
-        <v>229.2360294447337</v>
+        <v>229.345773483712</v>
       </c>
       <c r="C158" t="n">
-        <v>230.9720668751014</v>
+        <v>229.4754818886306</v>
       </c>
       <c r="D158" t="n">
-        <v>223.7286287034134</v>
+        <v>217.8719993892805</v>
       </c>
       <c r="E158" t="n">
-        <v>224.8061676025391</v>
+        <v>221.8130035400391</v>
       </c>
       <c r="F158" t="n">
-        <v>180977600</v>
+        <v>146280900</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B159" t="n">
-        <v>229.345773483712</v>
+        <v>219.1191400841904</v>
       </c>
       <c r="C159" t="n">
-        <v>229.4754818886306</v>
+        <v>223.9680572056967</v>
       </c>
       <c r="D159" t="n">
-        <v>217.8719993892805</v>
+        <v>217.4130483552105</v>
       </c>
       <c r="E159" t="n">
-        <v>221.8130035400391</v>
+        <v>220.1068878173828</v>
       </c>
       <c r="F159" t="n">
-        <v>146280900</v>
+        <v>140948200</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B160" t="n">
-        <v>219.1191400841904</v>
+        <v>222.6710257508039</v>
       </c>
       <c r="C160" t="n">
-        <v>223.9680572056967</v>
+        <v>225.6143103895453</v>
       </c>
       <c r="D160" t="n">
-        <v>217.4130483552105</v>
+        <v>219.9971448577806</v>
       </c>
       <c r="E160" t="n">
-        <v>220.1068878173828</v>
+        <v>222.9603729248047</v>
       </c>
       <c r="F160" t="n">
-        <v>140948200</v>
+        <v>184201600</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B161" t="n">
-        <v>222.6710257508039</v>
+        <v>221.7830583738447</v>
       </c>
       <c r="C161" t="n">
-        <v>225.6143103895453</v>
+        <v>226.8814055684356</v>
       </c>
       <c r="D161" t="n">
-        <v>219.9971448577806</v>
+        <v>217.4330007955402</v>
       </c>
       <c r="E161" t="n">
-        <v>222.9603729248047</v>
+        <v>219.0093994140625</v>
       </c>
       <c r="F161" t="n">
-        <v>184201600</v>
+        <v>203381800</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B162" t="n">
-        <v>221.7830583738447</v>
+        <v>220.3962175709585</v>
       </c>
       <c r="C162" t="n">
-        <v>226.8814055684356</v>
+        <v>220.5059673180016</v>
       </c>
       <c r="D162" t="n">
-        <v>217.4330007955402</v>
+        <v>214.3101381389001</v>
       </c>
       <c r="E162" t="n">
-        <v>219.0093994140625</v>
+        <v>214.8389282226562</v>
       </c>
       <c r="F162" t="n">
-        <v>203381800</v>
+        <v>169275700</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B163" t="n">
-        <v>220.3962175709585</v>
+        <v>216.0461718127993</v>
       </c>
       <c r="C163" t="n">
-        <v>220.5059673180016</v>
+        <v>217.6824311685512</v>
       </c>
       <c r="D163" t="n">
-        <v>214.3101381389001</v>
+        <v>211.5165320236786</v>
       </c>
       <c r="E163" t="n">
-        <v>214.8389282226562</v>
+        <v>214.3700103759766</v>
       </c>
       <c r="F163" t="n">
-        <v>169275700</v>
+        <v>187202600</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B164" t="n">
-        <v>216.0461718127993</v>
+        <v>213.6316806617713</v>
       </c>
       <c r="C164" t="n">
-        <v>217.6824311685512</v>
+        <v>213.6616110269177</v>
       </c>
       <c r="D164" t="n">
-        <v>211.5165320236786</v>
+        <v>208.3038625298546</v>
       </c>
       <c r="E164" t="n">
-        <v>214.3700103759766</v>
+        <v>212.1151580810547</v>
       </c>
       <c r="F164" t="n">
-        <v>187202600</v>
+        <v>167601200</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B165" t="n">
-        <v>213.6316806617713</v>
+        <v>210.7981551984497</v>
       </c>
       <c r="C165" t="n">
-        <v>213.6616110269177</v>
+        <v>215.0284909668814</v>
       </c>
       <c r="D165" t="n">
-        <v>208.3038625298546</v>
+        <v>210.7382944698381</v>
       </c>
       <c r="E165" t="n">
-        <v>212.1151580810547</v>
+        <v>213.7613830566406</v>
       </c>
       <c r="F165" t="n">
-        <v>167601200</v>
+        <v>143996000</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B166" t="n">
-        <v>210.7981551984497</v>
+        <v>214.0906505321041</v>
       </c>
       <c r="C166" t="n">
-        <v>215.0284909668814</v>
+        <v>217.3631692496548</v>
       </c>
       <c r="D166" t="n">
-        <v>210.7382944698381</v>
+        <v>210.6485213277038</v>
       </c>
       <c r="E166" t="n">
-        <v>213.7613830566406</v>
+        <v>210.6584930419922</v>
       </c>
       <c r="F166" t="n">
-        <v>143996000</v>
+        <v>289410600</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B167" t="n">
-        <v>214.0906505321041</v>
+        <v>215.2380189209027</v>
       </c>
       <c r="C167" t="n">
-        <v>217.3631692496548</v>
+        <v>224.3571743491113</v>
       </c>
       <c r="D167" t="n">
-        <v>210.6485213277038</v>
+        <v>215.2080885544549</v>
       </c>
       <c r="E167" t="n">
-        <v>210.6584930419922</v>
+        <v>223.8483428955078</v>
       </c>
       <c r="F167" t="n">
-        <v>289410600</v>
+        <v>212850700</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B168" t="n">
-        <v>215.2380189209027</v>
+        <v>226.6618858382332</v>
       </c>
       <c r="C168" t="n">
-        <v>224.3571743491113</v>
+        <v>231.7502608645459</v>
       </c>
       <c r="D168" t="n">
-        <v>215.2080885544549</v>
+        <v>220.8451951370975</v>
       </c>
       <c r="E168" t="n">
-        <v>223.8483428955078</v>
+        <v>222.3118438720703</v>
       </c>
       <c r="F168" t="n">
-        <v>212850700</v>
+        <v>193362900</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B169" t="n">
-        <v>226.6618858382332</v>
+        <v>221.2143597561905</v>
       </c>
       <c r="C169" t="n">
-        <v>231.7502608645459</v>
+        <v>222.3118572511273</v>
       </c>
       <c r="D169" t="n">
-        <v>220.8451951370975</v>
+        <v>214.0207957553572</v>
       </c>
       <c r="E169" t="n">
-        <v>222.3118438720703</v>
+        <v>214.26025390625</v>
       </c>
       <c r="F169" t="n">
-        <v>193362900</v>
+        <v>160907000</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,25 +4837,25 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B170" t="n">
-        <v>221.2143597561905</v>
+        <v>213.6709127939037</v>
       </c>
       <c r="C170" t="n">
-        <v>222.3118572511273</v>
+        <v>221.3523199881091</v>
       </c>
       <c r="D170" t="n">
-        <v>214.0207957553572</v>
+        <v>210.73419644349</v>
       </c>
       <c r="E170" t="n">
-        <v>214.26025390625</v>
+        <v>218.4156036376953</v>
       </c>
       <c r="F170" t="n">
-        <v>160907000</v>
+        <v>169022200</v>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -4863,25 +4863,25 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B171" t="n">
-        <v>213.6709127939037</v>
+        <v>214.2902104723603</v>
       </c>
       <c r="C171" t="n">
-        <v>221.3523199881091</v>
+        <v>214.6298267834636</v>
       </c>
       <c r="D171" t="n">
-        <v>210.73419644349</v>
+        <v>204.101614447126</v>
       </c>
       <c r="E171" t="n">
-        <v>218.4156036376953</v>
+        <v>204.8707580566406</v>
       </c>
       <c r="F171" t="n">
-        <v>169022200</v>
+        <v>219655500</v>
       </c>
       <c r="G171" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B172" t="n">
-        <v>214.2902104723603</v>
+        <v>209.9450713288228</v>
       </c>
       <c r="C172" t="n">
-        <v>214.6298267834636</v>
+        <v>210.2347557268212</v>
       </c>
       <c r="D172" t="n">
-        <v>204.101614447126</v>
+        <v>205.7697506938822</v>
       </c>
       <c r="E172" t="n">
-        <v>204.8707580566406</v>
+        <v>208.4067993164062</v>
       </c>
       <c r="F172" t="n">
-        <v>219655500</v>
+        <v>138372800</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B173" t="n">
-        <v>209.9450713288228</v>
+        <v>210.3845825512031</v>
       </c>
       <c r="C173" t="n">
-        <v>210.2347557268212</v>
+        <v>211.1637095162451</v>
       </c>
       <c r="D173" t="n">
-        <v>205.7697506938822</v>
+        <v>199.1171915656509</v>
       </c>
       <c r="E173" t="n">
-        <v>208.4067993164062</v>
+        <v>207.9573059082031</v>
       </c>
       <c r="F173" t="n">
-        <v>138372800</v>
+        <v>180962500</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B174" t="n">
-        <v>210.3845825512031</v>
+        <v>204.2014963256503</v>
       </c>
       <c r="C174" t="n">
-        <v>211.1637095162451</v>
+        <v>206.9883864105018</v>
       </c>
       <c r="D174" t="n">
-        <v>199.1171915656509</v>
+        <v>199.696542748819</v>
       </c>
       <c r="E174" t="n">
-        <v>207.9573059082031</v>
+        <v>200.1959838867188</v>
       </c>
       <c r="F174" t="n">
-        <v>180962500</v>
+        <v>161746600</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B175" t="n">
-        <v>204.2014963256503</v>
+        <v>201.2647947500858</v>
       </c>
       <c r="C175" t="n">
-        <v>206.9883864105018</v>
+        <v>205.4301320010667</v>
       </c>
       <c r="D175" t="n">
-        <v>199.696542748819</v>
+        <v>199.3169621236104</v>
       </c>
       <c r="E175" t="n">
-        <v>200.1959838867188</v>
+        <v>204.6410064697266</v>
       </c>
       <c r="F175" t="n">
-        <v>161746600</v>
+        <v>158643200</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B176" t="n">
-        <v>201.2647947500858</v>
+        <v>204.6310298517525</v>
       </c>
       <c r="C176" t="n">
-        <v>205.4301320010667</v>
+        <v>206.8385664547524</v>
       </c>
       <c r="D176" t="n">
-        <v>199.3169621236104</v>
+        <v>203.2126188059985</v>
       </c>
       <c r="E176" t="n">
-        <v>204.6410064697266</v>
+        <v>204.9606628417969</v>
       </c>
       <c r="F176" t="n">
-        <v>158643200</v>
+        <v>112001800</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B177" t="n">
-        <v>204.6310298517525</v>
+        <v>208.6864864049894</v>
       </c>
       <c r="C177" t="n">
-        <v>206.8385664547524</v>
+        <v>212.4722588232193</v>
       </c>
       <c r="D177" t="n">
-        <v>203.2126188059985</v>
+        <v>208.1071328472061</v>
       </c>
       <c r="E177" t="n">
-        <v>204.9606628417969</v>
+        <v>212.2125396728516</v>
       </c>
       <c r="F177" t="n">
-        <v>112001800</v>
+        <v>149936700</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B178" t="n">
-        <v>208.6864864049894</v>
+        <v>210.9439520928381</v>
       </c>
       <c r="C178" t="n">
-        <v>212.4722588232193</v>
+        <v>211.2536184019877</v>
       </c>
       <c r="D178" t="n">
-        <v>208.1071328472061</v>
+        <v>207.0583006421773</v>
       </c>
       <c r="E178" t="n">
-        <v>212.2125396728516</v>
+        <v>207.1781768798828</v>
       </c>
       <c r="F178" t="n">
-        <v>149936700</v>
+        <v>125694100</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B179" t="n">
-        <v>210.9439520928381</v>
+        <v>208.2969174543329</v>
       </c>
       <c r="C179" t="n">
-        <v>211.2536184019877</v>
+        <v>208.9761653200819</v>
       </c>
       <c r="D179" t="n">
-        <v>207.0583006421773</v>
+        <v>202.8530121596522</v>
       </c>
       <c r="E179" t="n">
-        <v>207.1781768798828</v>
+        <v>204.4212493896484</v>
       </c>
       <c r="F179" t="n">
-        <v>125694100</v>
+        <v>128363500</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B180" t="n">
-        <v>208.2969174543329</v>
+        <v>207.0982684229139</v>
       </c>
       <c r="C180" t="n">
-        <v>208.9761653200819</v>
+        <v>211.1537281092123</v>
       </c>
       <c r="D180" t="n">
-        <v>202.8530121596522</v>
+        <v>206.2691942875683</v>
       </c>
       <c r="E180" t="n">
-        <v>204.4212493896484</v>
+        <v>210.4545135498047</v>
       </c>
       <c r="F180" t="n">
-        <v>128363500</v>
+        <v>241272000</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B181" t="n">
-        <v>207.0982684229139</v>
+        <v>211.2036686200953</v>
       </c>
       <c r="C181" t="n">
-        <v>211.1537281092123</v>
+        <v>213.7508214450341</v>
       </c>
       <c r="D181" t="n">
-        <v>206.2691942875683</v>
+        <v>207.4878253737282</v>
       </c>
       <c r="E181" t="n">
-        <v>210.4545135498047</v>
+        <v>208.4167785644531</v>
       </c>
       <c r="F181" t="n">
-        <v>241272000</v>
+        <v>122041400</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B182" t="n">
-        <v>211.2036686200953</v>
+        <v>201.9440304014853</v>
       </c>
       <c r="C182" t="n">
-        <v>213.7508214450341</v>
+        <v>203.5422481594977</v>
       </c>
       <c r="D182" t="n">
-        <v>207.4878253737282</v>
+        <v>199.77645766483</v>
       </c>
       <c r="E182" t="n">
-        <v>208.4167785644531</v>
+        <v>199.81640625</v>
       </c>
       <c r="F182" t="n">
-        <v>122041400</v>
+        <v>153496200</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B183" t="n">
-        <v>201.9440304014853</v>
+        <v>199.8963159019567</v>
       </c>
       <c r="C183" t="n">
-        <v>203.5422481594977</v>
+        <v>201.4445864758279</v>
       </c>
       <c r="D183" t="n">
-        <v>199.77645766483</v>
+        <v>196.360279356477</v>
       </c>
       <c r="E183" t="n">
-        <v>199.81640625</v>
+        <v>198.7775726318359</v>
       </c>
       <c r="F183" t="n">
-        <v>153496200</v>
+        <v>151810700</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B184" t="n">
-        <v>199.8963159019567</v>
+        <v>199.8563704571445</v>
       </c>
       <c r="C184" t="n">
-        <v>201.4445864758279</v>
+        <v>200.5755669254449</v>
       </c>
       <c r="D184" t="n">
-        <v>196.360279356477</v>
+        <v>191.9152592982058</v>
       </c>
       <c r="E184" t="n">
-        <v>198.7775726318359</v>
+        <v>195.5212249755859</v>
       </c>
       <c r="F184" t="n">
-        <v>151810700</v>
+        <v>149550000</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B185" t="n">
-        <v>199.8563704571445</v>
+        <v>192.9041409641119</v>
       </c>
       <c r="C185" t="n">
-        <v>200.5755669254449</v>
+        <v>195.331432829306</v>
       </c>
       <c r="D185" t="n">
-        <v>191.9152592982058</v>
+        <v>191.0062707295152</v>
       </c>
       <c r="E185" t="n">
-        <v>195.5212249755859</v>
+        <v>192.3148040771484</v>
       </c>
       <c r="F185" t="n">
-        <v>149550000</v>
+        <v>179304100</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B186" t="n">
-        <v>192.9041409641119</v>
+        <v>193.6333319429392</v>
       </c>
       <c r="C186" t="n">
-        <v>195.331432829306</v>
+        <v>195.9607141929515</v>
       </c>
       <c r="D186" t="n">
-        <v>191.0062707295152</v>
+        <v>189.5878557469149</v>
       </c>
       <c r="E186" t="n">
-        <v>192.3148040771484</v>
+        <v>194.7520751953125</v>
       </c>
       <c r="F186" t="n">
-        <v>179304100</v>
+        <v>148835700</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B187" t="n">
-        <v>193.6333319429392</v>
+        <v>197.0195429632178</v>
       </c>
       <c r="C187" t="n">
-        <v>195.9607141929515</v>
+        <v>200.4057532237791</v>
       </c>
       <c r="D187" t="n">
-        <v>189.5878557469149</v>
+        <v>194.8919188665145</v>
       </c>
       <c r="E187" t="n">
-        <v>194.7520751953125</v>
+        <v>199.8663482666016</v>
       </c>
       <c r="F187" t="n">
-        <v>148835700</v>
+        <v>166476700</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B188" t="n">
-        <v>197.0195429632178</v>
+        <v>195.9806989625188</v>
       </c>
       <c r="C188" t="n">
-        <v>200.4057532237791</v>
+        <v>199.626628404907</v>
       </c>
       <c r="D188" t="n">
-        <v>194.8919188665145</v>
+        <v>193.2337727110923</v>
       </c>
       <c r="E188" t="n">
-        <v>199.8663482666016</v>
+        <v>197.3591613769531</v>
       </c>
       <c r="F188" t="n">
-        <v>166476700</v>
+        <v>146147600</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B189" t="n">
-        <v>195.9806989625188</v>
+        <v>196.9196593659626</v>
       </c>
       <c r="C189" t="n">
-        <v>199.626628404907</v>
+        <v>199.8363939026278</v>
       </c>
       <c r="D189" t="n">
-        <v>193.2337727110923</v>
+        <v>192.1350197738411</v>
       </c>
       <c r="E189" t="n">
-        <v>197.3591613769531</v>
+        <v>194.6122436523438</v>
       </c>
       <c r="F189" t="n">
-        <v>146147600</v>
+        <v>142068700</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B190" t="n">
-        <v>196.9196593659626</v>
+        <v>194.202694284663</v>
       </c>
       <c r="C190" t="n">
-        <v>199.8363939026278</v>
+        <v>197.3292007505161</v>
       </c>
       <c r="D190" t="n">
-        <v>192.1350197738411</v>
+        <v>193.7731822131383</v>
       </c>
       <c r="E190" t="n">
-        <v>194.6122436523438</v>
+        <v>195.3314361572266</v>
       </c>
       <c r="F190" t="n">
-        <v>142068700</v>
+        <v>108999000</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B191" t="n">
-        <v>194.202694284663</v>
+        <v>192.1549837798622</v>
       </c>
       <c r="C191" t="n">
-        <v>197.3292007505161</v>
+        <v>198.1882414262674</v>
       </c>
       <c r="D191" t="n">
-        <v>193.7731822131383</v>
+        <v>190.9263628146717</v>
       </c>
       <c r="E191" t="n">
-        <v>195.3314361572266</v>
+        <v>196.7098846435547</v>
       </c>
       <c r="F191" t="n">
-        <v>108999000</v>
+        <v>124154600</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B192" t="n">
-        <v>192.1549837798622</v>
+        <v>194.9618356993413</v>
       </c>
       <c r="C192" t="n">
-        <v>198.1882414262674</v>
+        <v>204.9306918075912</v>
       </c>
       <c r="D192" t="n">
-        <v>190.9263628146717</v>
+        <v>194.841974703339</v>
       </c>
       <c r="E192" t="n">
-        <v>196.7098846435547</v>
+        <v>203.891845703125</v>
       </c>
       <c r="F192" t="n">
-        <v>124154600</v>
+        <v>147419100</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B193" t="n">
-        <v>194.9618356993413</v>
+        <v>204.2314748595287</v>
       </c>
       <c r="C193" t="n">
-        <v>204.9306918075912</v>
+        <v>204.3613191897594</v>
       </c>
       <c r="D193" t="n">
-        <v>194.841974703339</v>
+        <v>198.7376223952696</v>
       </c>
       <c r="E193" t="n">
-        <v>203.891845703125</v>
+        <v>202.5533447265625</v>
       </c>
       <c r="F193" t="n">
-        <v>147419100</v>
+        <v>132037400</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B194" t="n">
-        <v>204.2314748595287</v>
+        <v>201.7742207048944</v>
       </c>
       <c r="C194" t="n">
-        <v>204.3613191897594</v>
+        <v>210.7641612313501</v>
       </c>
       <c r="D194" t="n">
-        <v>198.7376223952696</v>
+        <v>201.6943082934289</v>
       </c>
       <c r="E194" t="n">
-        <v>202.5533447265625</v>
+        <v>210.7242126464844</v>
       </c>
       <c r="F194" t="n">
-        <v>132037400</v>
+        <v>148421000</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B195" t="n">
-        <v>201.7742207048944</v>
+        <v>208.3069001369788</v>
       </c>
       <c r="C195" t="n">
-        <v>210.7641612313501</v>
+        <v>210.3346451505122</v>
       </c>
       <c r="D195" t="n">
-        <v>201.6943082934289</v>
+        <v>202.7730991138312</v>
       </c>
       <c r="E195" t="n">
-        <v>210.7242126464844</v>
+        <v>203.3025054931641</v>
       </c>
       <c r="F195" t="n">
-        <v>148421000</v>
+        <v>121411000</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B196" t="n">
-        <v>208.3069001369788</v>
+        <v>207.9672957533915</v>
       </c>
       <c r="C196" t="n">
-        <v>210.3346451505122</v>
+        <v>212.3124399374416</v>
       </c>
       <c r="D196" t="n">
-        <v>202.7730991138312</v>
+        <v>203.5722196467825</v>
       </c>
       <c r="E196" t="n">
-        <v>203.3025054931641</v>
+        <v>211.5632781982422</v>
       </c>
       <c r="F196" t="n">
-        <v>121411000</v>
+        <v>124379600</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B197" t="n">
-        <v>207.9672957533915</v>
+        <v>211.7230919717581</v>
       </c>
       <c r="C197" t="n">
-        <v>212.3124399374416</v>
+        <v>213.5710150202495</v>
       </c>
       <c r="D197" t="n">
-        <v>203.5722196467825</v>
+        <v>205.8096955397309</v>
       </c>
       <c r="E197" t="n">
-        <v>211.5632781982422</v>
+        <v>212.2624816894531</v>
       </c>
       <c r="F197" t="n">
-        <v>124379600</v>
+        <v>124797200</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B198" t="n">
-        <v>211.7230919717581</v>
+        <v>209.9350906043833</v>
       </c>
       <c r="C198" t="n">
-        <v>213.5710150202495</v>
+        <v>210.8440771529852</v>
       </c>
       <c r="D198" t="n">
-        <v>205.8096955397309</v>
+        <v>205.6199270055466</v>
       </c>
       <c r="E198" t="n">
-        <v>212.2624816894531</v>
+        <v>207.1681823730469</v>
       </c>
       <c r="F198" t="n">
-        <v>124797200</v>
+        <v>122986100</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B199" t="n">
-        <v>209.9350906043833</v>
+        <v>202.4135048295048</v>
       </c>
       <c r="C199" t="n">
-        <v>210.8440771529852</v>
+        <v>206.4190172896336</v>
       </c>
       <c r="D199" t="n">
-        <v>205.6199270055466</v>
+        <v>197.7487264058434</v>
       </c>
       <c r="E199" t="n">
-        <v>207.1681823730469</v>
+        <v>202.5833129882812</v>
       </c>
       <c r="F199" t="n">
-        <v>122986100</v>
+        <v>144281900</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B200" t="n">
-        <v>202.4135048295048</v>
+        <v>205.639896943356</v>
       </c>
       <c r="C200" t="n">
-        <v>206.4190172896336</v>
+        <v>207.5078172334397</v>
       </c>
       <c r="D200" t="n">
-        <v>197.7487264058434</v>
+        <v>202.0539130969454</v>
       </c>
       <c r="E200" t="n">
-        <v>202.5833129882812</v>
+        <v>203.0527954101562</v>
       </c>
       <c r="F200" t="n">
-        <v>144281900</v>
+        <v>88701500</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B201" t="n">
-        <v>205.639896943356</v>
+        <v>207.308024406286</v>
       </c>
       <c r="C201" t="n">
-        <v>207.5078172334397</v>
+        <v>208.4167843613107</v>
       </c>
       <c r="D201" t="n">
-        <v>202.0539130969454</v>
+        <v>203.7819711309363</v>
       </c>
       <c r="E201" t="n">
-        <v>203.0527954101562</v>
+        <v>207.0583038330078</v>
       </c>
       <c r="F201" t="n">
-        <v>88701500</v>
+        <v>108685600</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B202" t="n">
-        <v>207.308024406286</v>
+        <v>205.579968274895</v>
       </c>
       <c r="C202" t="n">
-        <v>208.4167843613107</v>
+        <v>214.1503804276117</v>
       </c>
       <c r="D202" t="n">
-        <v>203.7819711309363</v>
+        <v>204.7209288682105</v>
       </c>
       <c r="E202" t="n">
-        <v>207.0583038330078</v>
+        <v>211.8229827880859</v>
       </c>
       <c r="F202" t="n">
-        <v>108685600</v>
+        <v>137645600</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B203" t="n">
-        <v>205.579968274895</v>
+        <v>209.2258868865651</v>
       </c>
       <c r="C203" t="n">
-        <v>214.1503804276117</v>
+        <v>210.6342993029147</v>
       </c>
       <c r="D203" t="n">
-        <v>204.7209288682105</v>
+        <v>205.7297989431358</v>
       </c>
       <c r="E203" t="n">
-        <v>211.8229827880859</v>
+        <v>208.5266571044922</v>
       </c>
       <c r="F203" t="n">
-        <v>137645600</v>
+        <v>110505300</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B204" t="n">
-        <v>209.2258868865651</v>
+        <v>207.2181292349697</v>
       </c>
       <c r="C204" t="n">
-        <v>210.6342993029147</v>
+        <v>211.6731509810223</v>
       </c>
       <c r="D204" t="n">
-        <v>205.7297989431358</v>
+        <v>204.5810805834776</v>
       </c>
       <c r="E204" t="n">
-        <v>208.5266571044922</v>
+        <v>206.6088104248047</v>
       </c>
       <c r="F204" t="n">
-        <v>110505300</v>
+        <v>114836800</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B205" t="n">
-        <v>207.2181292349697</v>
+        <v>207.9672962732577</v>
       </c>
       <c r="C205" t="n">
-        <v>211.6731509810223</v>
+        <v>208.5166845983908</v>
       </c>
       <c r="D205" t="n">
-        <v>204.5810805834776</v>
+        <v>195.2215633388429</v>
       </c>
       <c r="E205" t="n">
-        <v>206.6088104248047</v>
+        <v>196.2903594970703</v>
       </c>
       <c r="F205" t="n">
-        <v>114836800</v>
+        <v>154353700</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B206" t="n">
-        <v>207.9672962732577</v>
+        <v>194.782047001347</v>
       </c>
       <c r="C206" t="n">
-        <v>208.5166845983908</v>
+        <v>198.4779084345641</v>
       </c>
       <c r="D206" t="n">
-        <v>195.2215633388429</v>
+        <v>192.5245785077403</v>
       </c>
       <c r="E206" t="n">
-        <v>196.2903594970703</v>
+        <v>196.789794921875</v>
       </c>
       <c r="F206" t="n">
-        <v>154353700</v>
+        <v>134111500</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B207" t="n">
-        <v>194.782047001347</v>
+        <v>195.6311069684468</v>
       </c>
       <c r="C207" t="n">
-        <v>198.4779084345641</v>
+        <v>196.8497446088402</v>
       </c>
       <c r="D207" t="n">
-        <v>192.5245785077403</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="E207" t="n">
-        <v>196.789794921875</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="F207" t="n">
-        <v>134111500</v>
+        <v>147680800</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B208" t="n">
-        <v>195.6311069684468</v>
+        <v>193.2337718176948</v>
       </c>
       <c r="C208" t="n">
-        <v>196.8497446088402</v>
+        <v>197.0295274868271</v>
       </c>
       <c r="D208" t="n">
-        <v>189.7976226806641</v>
+        <v>191.3059363552755</v>
       </c>
       <c r="E208" t="n">
-        <v>189.7976226806641</v>
+        <v>194.8219909667969</v>
       </c>
       <c r="F208" t="n">
-        <v>147680800</v>
+        <v>129010200</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B209" t="n">
-        <v>193.2337718176948</v>
+        <v>198.2182038580375</v>
       </c>
       <c r="C209" t="n">
-        <v>197.0295274868271</v>
+        <v>201.7742223680242</v>
       </c>
       <c r="D209" t="n">
-        <v>191.3059363552755</v>
+        <v>194.7320991825756</v>
       </c>
       <c r="E209" t="n">
-        <v>194.8219909667969</v>
+        <v>200.5256195068359</v>
       </c>
       <c r="F209" t="n">
-        <v>129010200</v>
+        <v>139961200</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B210" t="n">
-        <v>198.2182038580375</v>
+        <v>197.4690486270115</v>
       </c>
       <c r="C210" t="n">
-        <v>201.7742223680242</v>
+        <v>208.506701330784</v>
       </c>
       <c r="D210" t="n">
-        <v>194.7320991825756</v>
+        <v>196.6299911347511</v>
       </c>
       <c r="E210" t="n">
-        <v>200.5256195068359</v>
+        <v>206.4090423583984</v>
       </c>
       <c r="F210" t="n">
-        <v>139961200</v>
+        <v>128406900</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B211" t="n">
-        <v>197.4690486270115</v>
+        <v>211.0638257011038</v>
       </c>
       <c r="C211" t="n">
-        <v>208.506701330784</v>
+        <v>212.8218530009649</v>
       </c>
       <c r="D211" t="n">
-        <v>196.6299911347511</v>
+        <v>208.8163406042335</v>
       </c>
       <c r="E211" t="n">
-        <v>206.4090423583984</v>
+        <v>211.7031097412109</v>
       </c>
       <c r="F211" t="n">
-        <v>128406900</v>
+        <v>134922000</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B212" t="n">
-        <v>211.0638257011038</v>
+        <v>216.6176127852948</v>
       </c>
       <c r="C212" t="n">
-        <v>212.8218530009649</v>
+        <v>221.9716224388697</v>
       </c>
       <c r="D212" t="n">
-        <v>208.8163406042335</v>
+        <v>216.1581202281489</v>
       </c>
       <c r="E212" t="n">
-        <v>211.7031097412109</v>
+        <v>218.9749755859375</v>
       </c>
       <c r="F212" t="n">
-        <v>134922000</v>
+        <v>158187400</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B213" t="n">
-        <v>216.6176127852948</v>
+        <v>221.2823935806188</v>
       </c>
       <c r="C213" t="n">
-        <v>221.9716224388697</v>
+        <v>223.3800524967045</v>
       </c>
       <c r="D213" t="n">
-        <v>216.1581202281489</v>
+        <v>216.7574580038405</v>
       </c>
       <c r="E213" t="n">
-        <v>218.9749755859375</v>
+        <v>218.7452392578125</v>
       </c>
       <c r="F213" t="n">
-        <v>158187400</v>
+        <v>113940600</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B214" t="n">
-        <v>221.2823935806188</v>
+        <v>221.2923777041913</v>
       </c>
       <c r="C214" t="n">
-        <v>223.3800524967045</v>
+        <v>224.5087799247126</v>
       </c>
       <c r="D214" t="n">
-        <v>216.7574580038405</v>
+        <v>220.4133716458871</v>
       </c>
       <c r="E214" t="n">
-        <v>218.7452392578125</v>
+        <v>223.7096862792969</v>
       </c>
       <c r="F214" t="n">
-        <v>113940600</v>
+        <v>105669400</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B215" t="n">
-        <v>221.2923777041913</v>
+        <v>223.1502910726907</v>
       </c>
       <c r="C215" t="n">
-        <v>224.5087799247126</v>
+        <v>223.8894694330602</v>
       </c>
       <c r="D215" t="n">
-        <v>220.4133716458871</v>
+        <v>216.5277120448001</v>
       </c>
       <c r="E215" t="n">
-        <v>223.7096862792969</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="F215" t="n">
-        <v>105669400</v>
+        <v>115846600</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B216" t="n">
-        <v>223.1502910726907</v>
+        <v>221.9216754142795</v>
       </c>
       <c r="C216" t="n">
-        <v>223.8894694330602</v>
+        <v>221.9516406634887</v>
       </c>
       <c r="D216" t="n">
-        <v>216.5277120448001</v>
+        <v>215.9583469538982</v>
       </c>
       <c r="E216" t="n">
-        <v>217.3068389892578</v>
+        <v>217.2568969726562</v>
       </c>
       <c r="F216" t="n">
-        <v>115846600</v>
+        <v>101273100</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B217" t="n">
-        <v>221.9216754142795</v>
+        <v>220.7929293559802</v>
       </c>
       <c r="C217" t="n">
-        <v>221.9516406634887</v>
+        <v>224.848404158734</v>
       </c>
       <c r="D217" t="n">
-        <v>215.9583469538982</v>
+        <v>219.9538719106106</v>
       </c>
       <c r="E217" t="n">
-        <v>217.2568969726562</v>
+        <v>223.8395233154297</v>
       </c>
       <c r="F217" t="n">
-        <v>101273100</v>
+        <v>108783600</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B218" t="n">
-        <v>220.7929293559802</v>
+        <v>224.8084500146858</v>
       </c>
       <c r="C218" t="n">
-        <v>224.848404158734</v>
+        <v>226.9760227961096</v>
       </c>
       <c r="D218" t="n">
-        <v>219.9538719106106</v>
+        <v>223.4599680426375</v>
       </c>
       <c r="E218" t="n">
-        <v>223.8395233154297</v>
+        <v>225.0481872558594</v>
       </c>
       <c r="F218" t="n">
-        <v>108783600</v>
+        <v>98867200</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B219" t="n">
-        <v>224.8084500146858</v>
+        <v>226.5165415533859</v>
       </c>
       <c r="C219" t="n">
-        <v>226.9760227961096</v>
+        <v>227.2357380227387</v>
       </c>
       <c r="D219" t="n">
-        <v>223.4599680426375</v>
+        <v>224.2490744835724</v>
       </c>
       <c r="E219" t="n">
-        <v>225.0481872558594</v>
+        <v>224.9083404541016</v>
       </c>
       <c r="F219" t="n">
-        <v>98867200</v>
+        <v>75680900</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B220" t="n">
-        <v>226.5165415533859</v>
+        <v>225.7274161885591</v>
       </c>
       <c r="C220" t="n">
-        <v>227.2357380227387</v>
+        <v>227.6652502746616</v>
       </c>
       <c r="D220" t="n">
-        <v>224.2490744835724</v>
+        <v>224.6086728983284</v>
       </c>
       <c r="E220" t="n">
-        <v>224.9083404541016</v>
+        <v>224.7584991455078</v>
       </c>
       <c r="F220" t="n">
-        <v>75680900</v>
+        <v>93678700</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B221" t="n">
-        <v>225.7274161885591</v>
+        <v>220.203597915372</v>
       </c>
       <c r="C221" t="n">
-        <v>227.6652502746616</v>
+        <v>221.3922702798686</v>
       </c>
       <c r="D221" t="n">
-        <v>224.6086728983284</v>
+        <v>218.4455705709327</v>
       </c>
       <c r="E221" t="n">
-        <v>224.7584991455078</v>
+        <v>219.4944000244141</v>
       </c>
       <c r="F221" t="n">
-        <v>93678700</v>
+        <v>103128200</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B222" t="n">
-        <v>220.203597915372</v>
+        <v>221.4222404106533</v>
       </c>
       <c r="C222" t="n">
-        <v>221.3922702798686</v>
+        <v>222.6208961374568</v>
       </c>
       <c r="D222" t="n">
-        <v>218.4455705709327</v>
+        <v>216.5177245976465</v>
       </c>
       <c r="E222" t="n">
-        <v>219.4944000244141</v>
+        <v>217.3168334960938</v>
       </c>
       <c r="F222" t="n">
-        <v>103128200</v>
+        <v>96797300</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B223" t="n">
-        <v>221.4222404106533</v>
+        <v>218.1159423024499</v>
       </c>
       <c r="C223" t="n">
-        <v>222.6208961374568</v>
+        <v>219.6142657707553</v>
       </c>
       <c r="D223" t="n">
-        <v>216.5177245976465</v>
+        <v>215.418963107847</v>
       </c>
       <c r="E223" t="n">
-        <v>217.3168334960938</v>
+        <v>216.6076354980469</v>
       </c>
       <c r="F223" t="n">
-        <v>96797300</v>
+        <v>92457000</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B224" t="n">
-        <v>218.1159423024499</v>
+        <v>218.1758724878036</v>
       </c>
       <c r="C224" t="n">
-        <v>219.6142657707553</v>
+        <v>218.4955221432803</v>
       </c>
       <c r="D224" t="n">
-        <v>215.418963107847</v>
+        <v>214.2602556586216</v>
       </c>
       <c r="E224" t="n">
-        <v>216.6076354980469</v>
+        <v>214.4800109863281</v>
       </c>
       <c r="F224" t="n">
-        <v>92457000</v>
+        <v>98869300</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B225" t="n">
-        <v>218.1758724878036</v>
+        <v>215.2891020611033</v>
       </c>
       <c r="C225" t="n">
-        <v>218.4955221432803</v>
+        <v>215.3490325607492</v>
       </c>
       <c r="D225" t="n">
-        <v>214.2602556586216</v>
+        <v>207.0183577918231</v>
       </c>
       <c r="E225" t="n">
-        <v>214.4800109863281</v>
+        <v>208.2469787597656</v>
       </c>
       <c r="F225" t="n">
-        <v>98869300</v>
+        <v>135187300</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B226" t="n">
-        <v>215.2891020611033</v>
+        <v>210.7941279013131</v>
       </c>
       <c r="C226" t="n">
-        <v>215.3490325607492</v>
+        <v>214.4899893165327</v>
       </c>
       <c r="D226" t="n">
-        <v>207.0183577918231</v>
+        <v>209.8751580258669</v>
       </c>
       <c r="E226" t="n">
-        <v>208.2469787597656</v>
+        <v>212.8118743896484</v>
       </c>
       <c r="F226" t="n">
-        <v>135187300</v>
+        <v>122309000</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B227" t="n">
-        <v>210.7941279013131</v>
+        <v>212.4023240594531</v>
       </c>
       <c r="C227" t="n">
-        <v>214.4899893165327</v>
+        <v>213.3612577394914</v>
       </c>
       <c r="D227" t="n">
-        <v>209.8751580258669</v>
+        <v>208.9961318803605</v>
       </c>
       <c r="E227" t="n">
-        <v>212.8118743896484</v>
+        <v>209.4256591796875</v>
       </c>
       <c r="F227" t="n">
-        <v>122309000</v>
+        <v>179900000</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B228" t="n">
-        <v>212.4023240594531</v>
+        <v>222.6109016432552</v>
       </c>
       <c r="C228" t="n">
-        <v>213.3612577394914</v>
+        <v>230.2123962709879</v>
       </c>
       <c r="D228" t="n">
-        <v>208.9961318803605</v>
+        <v>220.6530857022795</v>
       </c>
       <c r="E228" t="n">
-        <v>209.4256591796875</v>
+        <v>227.7251739501953</v>
       </c>
       <c r="F228" t="n">
-        <v>179900000</v>
+        <v>298909800</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B229" t="n">
-        <v>222.6109016432552</v>
+        <v>227.1058715337123</v>
       </c>
       <c r="C229" t="n">
-        <v>230.2123962709879</v>
+        <v>229.003741733446</v>
       </c>
       <c r="D229" t="n">
-        <v>220.6530857022795</v>
+        <v>216.5676606288883</v>
       </c>
       <c r="E229" t="n">
-        <v>227.7251739501953</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="F229" t="n">
-        <v>298909800</v>
+        <v>195116400</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B230" t="n">
-        <v>227.1058715337123</v>
+        <v>218.6253647857836</v>
       </c>
       <c r="C230" t="n">
-        <v>229.003741733446</v>
+        <v>221.0526567078369</v>
       </c>
       <c r="D230" t="n">
-        <v>216.5676606288883</v>
+        <v>215.9683494434545</v>
       </c>
       <c r="E230" t="n">
-        <v>217.3068389892578</v>
+        <v>220.5332336425781</v>
       </c>
       <c r="F230" t="n">
-        <v>195116400</v>
+        <v>124702700</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B231" t="n">
-        <v>218.6253647857836</v>
+        <v>216.5077444634259</v>
       </c>
       <c r="C231" t="n">
-        <v>221.0526567078369</v>
+        <v>220.1636574397174</v>
       </c>
       <c r="D231" t="n">
-        <v>215.9683494434545</v>
+        <v>214.8595947199138</v>
       </c>
       <c r="E231" t="n">
-        <v>220.5332336425781</v>
+        <v>217.1969757080078</v>
       </c>
       <c r="F231" t="n">
-        <v>124702700</v>
+        <v>109756200</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B232" t="n">
-        <v>216.5077444634259</v>
+        <v>218.5454508199983</v>
       </c>
       <c r="C232" t="n">
-        <v>220.1636574397174</v>
+        <v>227.6952163087265</v>
       </c>
       <c r="D232" t="n">
-        <v>214.8595947199138</v>
+        <v>218.2357997469377</v>
       </c>
       <c r="E232" t="n">
-        <v>217.1969757080078</v>
+        <v>224.1591796875</v>
       </c>
       <c r="F232" t="n">
-        <v>109756200</v>
+        <v>157104700</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B233" t="n">
-        <v>218.5454508199983</v>
+        <v>225.7673797205316</v>
       </c>
       <c r="C233" t="n">
-        <v>227.6952163087265</v>
+        <v>230.1424737915274</v>
       </c>
       <c r="D233" t="n">
-        <v>218.2357997469377</v>
+        <v>224.4987949430455</v>
       </c>
       <c r="E233" t="n">
-        <v>224.1591796875</v>
+        <v>228.1946563720703</v>
       </c>
       <c r="F233" t="n">
-        <v>157104700</v>
+        <v>134681600</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B234" t="n">
-        <v>225.7673797205316</v>
+        <v>230.8317036041433</v>
       </c>
       <c r="C234" t="n">
-        <v>230.1424737915274</v>
+        <v>234.4975997614268</v>
       </c>
       <c r="D234" t="n">
-        <v>224.4987949430455</v>
+        <v>229.3733440032785</v>
       </c>
       <c r="E234" t="n">
-        <v>228.1946563720703</v>
+        <v>230.1025238037109</v>
       </c>
       <c r="F234" t="n">
-        <v>134681600</v>
+        <v>135352400</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B235" t="n">
-        <v>230.8317036041433</v>
+        <v>232.8494477166676</v>
       </c>
       <c r="C235" t="n">
-        <v>234.4975997614268</v>
+        <v>233.4487831783142</v>
       </c>
       <c r="D235" t="n">
-        <v>229.3733440032785</v>
+        <v>224.5986856128386</v>
       </c>
       <c r="E235" t="n">
-        <v>230.1025238037109</v>
+        <v>225.4776916503906</v>
       </c>
       <c r="F235" t="n">
-        <v>135352400</v>
+        <v>122965600</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B236" t="n">
-        <v>232.8494477166676</v>
+        <v>225.0281992525124</v>
       </c>
       <c r="C236" t="n">
-        <v>233.4487831783142</v>
+        <v>225.9271872095504</v>
       </c>
       <c r="D236" t="n">
-        <v>224.5986856128386</v>
+        <v>223.2102414251123</v>
       </c>
       <c r="E236" t="n">
-        <v>225.4776916503906</v>
+        <v>223.4199981689453</v>
       </c>
       <c r="F236" t="n">
-        <v>122965600</v>
+        <v>82955500</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,25 +6579,25 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B237" t="n">
-        <v>225.0281992525124</v>
+        <v>220.5299987792969</v>
       </c>
       <c r="C237" t="n">
-        <v>225.9271872095504</v>
+        <v>220.9900054931641</v>
       </c>
       <c r="D237" t="n">
-        <v>223.2102414251123</v>
+        <v>217.1999969482422</v>
       </c>
       <c r="E237" t="n">
-        <v>223.4199981689453</v>
+        <v>218.3600006103516</v>
       </c>
       <c r="F237" t="n">
-        <v>82955500</v>
+        <v>105768000</v>
       </c>
       <c r="G237" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -6605,25 +6605,25 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B238" t="n">
-        <v>220.5299987792969</v>
+        <v>221.2400054931641</v>
       </c>
       <c r="C238" t="n">
-        <v>220.9900054931641</v>
+        <v>222</v>
       </c>
       <c r="D238" t="n">
-        <v>217.1999969482422</v>
+        <v>218.1499938964844</v>
       </c>
       <c r="E238" t="n">
-        <v>218.3600006103516</v>
+        <v>218.2899932861328</v>
       </c>
       <c r="F238" t="n">
-        <v>105768000</v>
+        <v>89060100</v>
       </c>
       <c r="G238" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B239" t="n">
-        <v>221.2400054931641</v>
+        <v>211.2400054931641</v>
       </c>
       <c r="C239" t="n">
-        <v>222</v>
+        <v>212.7700042724609</v>
       </c>
       <c r="D239" t="n">
-        <v>218.1499938964844</v>
+        <v>208.9299926757812</v>
       </c>
       <c r="E239" t="n">
-        <v>218.2899932861328</v>
+        <v>210.9600067138672</v>
       </c>
       <c r="F239" t="n">
-        <v>89060100</v>
+        <v>132267200</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B240" t="n">
-        <v>211.2400054931641</v>
+        <v>213.3800048828125</v>
       </c>
       <c r="C240" t="n">
-        <v>212.7700042724609</v>
+        <v>213.9400024414062</v>
       </c>
       <c r="D240" t="n">
-        <v>208.9299926757812</v>
+        <v>211.1600036621094</v>
       </c>
       <c r="E240" t="n">
-        <v>210.9600067138672</v>
+        <v>212.1699981689453</v>
       </c>
       <c r="F240" t="n">
-        <v>132267200</v>
+        <v>88059700</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B241" t="n">
-        <v>213.3800048828125</v>
+        <v>214.1399993896484</v>
       </c>
       <c r="C241" t="n">
-        <v>213.9400024414062</v>
+        <v>216.7599945068359</v>
       </c>
       <c r="D241" t="n">
-        <v>211.1600036621094</v>
+        <v>212.5</v>
       </c>
       <c r="E241" t="n">
-        <v>212.1699981689453</v>
+        <v>213.8999938964844</v>
       </c>
       <c r="F241" t="n">
-        <v>88059700</v>
+        <v>96563600</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B242" t="n">
-        <v>214.1399993896484</v>
+        <v>218.3800048828125</v>
       </c>
       <c r="C242" t="n">
-        <v>216.7599945068359</v>
+        <v>219.9100036621094</v>
       </c>
       <c r="D242" t="n">
-        <v>212.5</v>
+        <v>217.1499938964844</v>
       </c>
       <c r="E242" t="n">
-        <v>213.8999938964844</v>
+        <v>219.3399963378906</v>
       </c>
       <c r="F242" t="n">
-        <v>96563600</v>
+        <v>94191300</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B243" t="n">
-        <v>218.3800048828125</v>
+        <v>219.3500061035156</v>
       </c>
       <c r="C243" t="n">
-        <v>219.9100036621094</v>
+        <v>222.7299957275391</v>
       </c>
       <c r="D243" t="n">
-        <v>217.1499938964844</v>
+        <v>218.0299987792969</v>
       </c>
       <c r="E243" t="n">
-        <v>219.3399963378906</v>
+        <v>222.2700042724609</v>
       </c>
       <c r="F243" t="n">
-        <v>94191300</v>
+        <v>190287400</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B244" t="n">
-        <v>219.3500061035156</v>
+        <v>222.9400024414062</v>
       </c>
       <c r="C244" t="n">
-        <v>222.7299957275391</v>
+        <v>228.5</v>
       </c>
       <c r="D244" t="n">
-        <v>218.0299987792969</v>
+        <v>221.5599975585938</v>
       </c>
       <c r="E244" t="n">
-        <v>222.2700042724609</v>
+        <v>227.3800048828125</v>
       </c>
       <c r="F244" t="n">
-        <v>190287400</v>
+        <v>109806100</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B245" t="n">
-        <v>222.9400024414062</v>
+        <v>226.8500061035156</v>
       </c>
       <c r="C245" t="n">
-        <v>228.5</v>
+        <v>229.9799957275391</v>
       </c>
       <c r="D245" t="n">
-        <v>221.5599975585938</v>
+        <v>226.5</v>
       </c>
       <c r="E245" t="n">
-        <v>227.3800048828125</v>
+        <v>228.8699951171875</v>
       </c>
       <c r="F245" t="n">
-        <v>109806100</v>
+        <v>95746700</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B246" t="n">
-        <v>226.8500061035156</v>
+        <v>228.0299987792969</v>
       </c>
       <c r="C246" t="n">
-        <v>229.9799957275391</v>
+        <v>228.9499969482422</v>
       </c>
       <c r="D246" t="n">
-        <v>226.5</v>
+        <v>224.0200042724609</v>
       </c>
       <c r="E246" t="n">
-        <v>228.8699951171875</v>
+        <v>225.5099945068359</v>
       </c>
       <c r="F246" t="n">
-        <v>95746700</v>
+        <v>89547300</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B247" t="n">
-        <v>228.0299987792969</v>
+        <v>222.0800018310547</v>
       </c>
       <c r="C247" t="n">
-        <v>228.9499969482422</v>
+        <v>224.9400024414062</v>
       </c>
       <c r="D247" t="n">
-        <v>224.0200042724609</v>
+        <v>221.0899963378906</v>
       </c>
       <c r="E247" t="n">
-        <v>225.5099945068359</v>
+        <v>224.5800018310547</v>
       </c>
       <c r="F247" t="n">
-        <v>89547300</v>
+        <v>77469900</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B248" t="n">
-        <v>222.0800018310547</v>
+        <v>225.1300048828125</v>
       </c>
       <c r="C248" t="n">
-        <v>224.9400024414062</v>
+        <v>226.9400024414062</v>
       </c>
       <c r="D248" t="n">
-        <v>221.0899963378906</v>
+        <v>223.1300048828125</v>
       </c>
       <c r="E248" t="n">
-        <v>224.5800018310547</v>
+        <v>225.0700073242188</v>
       </c>
       <c r="F248" t="n">
-        <v>77469900</v>
+        <v>89947700</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B249" t="n">
-        <v>225.1300048828125</v>
+        <v>229.75</v>
       </c>
       <c r="C249" t="n">
-        <v>226.9400024414062</v>
+        <v>233.2100067138672</v>
       </c>
       <c r="D249" t="n">
-        <v>223.1300048828125</v>
+        <v>228.0399932861328</v>
       </c>
       <c r="E249" t="n">
-        <v>225.0700073242188</v>
+        <v>228.8600006103516</v>
       </c>
       <c r="F249" t="n">
-        <v>89947700</v>
+        <v>142344300</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B250" t="n">
-        <v>229.75</v>
+        <v>230.9700012207031</v>
       </c>
       <c r="C250" t="n">
-        <v>233.2100067138672</v>
+        <v>232.8200073242188</v>
       </c>
       <c r="D250" t="n">
-        <v>228.0399932861328</v>
+        <v>227.0299987792969</v>
       </c>
       <c r="E250" t="n">
-        <v>228.8600006103516</v>
+        <v>227.2100067138672</v>
       </c>
       <c r="F250" t="n">
-        <v>142344300</v>
+        <v>101494900</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B251" t="n">
-        <v>230.9700012207031</v>
+        <v>229.2700042724609</v>
       </c>
       <c r="C251" t="n">
-        <v>232.8200073242188</v>
+        <v>232.3699951171875</v>
       </c>
       <c r="D251" t="n">
-        <v>227.0299987792969</v>
+        <v>228.1699981689453</v>
       </c>
       <c r="E251" t="n">
-        <v>227.2100067138672</v>
+        <v>228.3800048828125</v>
       </c>
       <c r="F251" t="n">
-        <v>101494900</v>
+        <v>121732200</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B252" t="n">
-        <v>229.2700042724609</v>
+        <v>229.9799957275391</v>
       </c>
       <c r="C252" t="n">
-        <v>232.3699951171875</v>
+        <v>232.2899932861328</v>
       </c>
       <c r="D252" t="n">
-        <v>228.1699981689453</v>
+        <v>228.1600036621094</v>
       </c>
       <c r="E252" t="n">
-        <v>228.3800048828125</v>
+        <v>230.8600006103516</v>
       </c>
       <c r="F252" t="n">
-        <v>121269300</v>
+        <v>98369800</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10884,37 +10884,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>230.86</v>
+      </c>
+      <c r="D2" t="n">
         <v>228.38</v>
       </c>
-      <c r="D2" t="n">
-        <v>227.21</v>
-      </c>
       <c r="E2" t="n">
-        <v>229</v>
+        <v>229.95</v>
       </c>
       <c r="F2" t="n">
-        <v>232.37</v>
+        <v>232.285</v>
       </c>
       <c r="G2" t="n">
-        <v>228.17</v>
+        <v>228.16</v>
       </c>
       <c r="H2" t="n">
-        <v>118683065</v>
+        <v>97538145</v>
       </c>
       <c r="I2" t="n">
-        <v>123136312</v>
+        <v>122420392</v>
       </c>
       <c r="J2" t="n">
-        <v>5514691870720</v>
+        <v>5574576046080</v>
       </c>
       <c r="K2" t="n">
-        <v>28.908861</v>
+        <v>29.14899</v>
       </c>
       <c r="L2" t="n">
-        <v>14.562609</v>
+        <v>14.709068</v>
       </c>
       <c r="M2" t="n">
-        <v>7.9</v>
+        <v>7.92</v>
       </c>
       <c r="N2" t="n">
         <v>236.54</v>
@@ -10926,7 +10926,7 @@
         <v>2.217</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="R2" t="n">
         <v>0.63663</v>
@@ -10950,7 +10950,7 @@
         <v>9.483000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>24.083097</v>
+        <v>24.344618</v>
       </c>
       <c r="Z2" t="n">
         <v>1.278</v>
@@ -10962,7 +10962,7 @@
         <v>302970011648</v>
       </c>
       <c r="AC2" t="n">
-        <v>5480348909568</v>
+        <v>5540117217280</v>
       </c>
       <c r="AD2" t="n">
         <v>201266003968</v>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-10-01 17:02:42</t>
+          <t>2026-10-02 19:38:24</t>
         </is>
       </c>
     </row>

--- a/data/NVDA_data.xlsx
+++ b/data/NVDA_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B2" t="n">
-        <v>189.1468626563914</v>
+        <v>188.7378247179256</v>
       </c>
       <c r="C2" t="n">
-        <v>190.593394116267</v>
+        <v>189.9050265070322</v>
       </c>
       <c r="D2" t="n">
-        <v>187.6105347272827</v>
+        <v>184.9369333277354</v>
       </c>
       <c r="E2" t="n">
-        <v>188.4385528564453</v>
+        <v>187.1715698242188</v>
       </c>
       <c r="F2" t="n">
-        <v>136805800</v>
+        <v>137596900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B3" t="n">
-        <v>188.7378247179256</v>
+        <v>185.0566446584491</v>
       </c>
       <c r="C3" t="n">
-        <v>189.9050265070322</v>
+        <v>186.7825055997528</v>
       </c>
       <c r="D3" t="n">
-        <v>184.9369333277354</v>
+        <v>182.8918329061041</v>
       </c>
       <c r="E3" t="n">
-        <v>187.1715698242188</v>
+        <v>185.0965423583984</v>
       </c>
       <c r="F3" t="n">
-        <v>137596900</v>
+        <v>157678100</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B4" t="n">
-        <v>185.0566294029491</v>
+        <v>185.7849061389523</v>
       </c>
       <c r="C4" t="n">
-        <v>186.7824902019781</v>
+        <v>188.6081442671687</v>
       </c>
       <c r="D4" t="n">
-        <v>182.8918178290645</v>
+        <v>183.5602400999903</v>
       </c>
       <c r="E4" t="n">
-        <v>185.0965270996094</v>
+        <v>184.5977478027344</v>
       </c>
       <c r="F4" t="n">
-        <v>157678100</v>
+        <v>140088000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B5" t="n">
-        <v>185.7848907820332</v>
+        <v>186.1240823667868</v>
       </c>
       <c r="C5" t="n">
-        <v>188.6081286768816</v>
+        <v>189.1468390813163</v>
       </c>
       <c r="D5" t="n">
-        <v>183.5602249269612</v>
+        <v>186.094140065894</v>
       </c>
       <c r="E5" t="n">
-        <v>184.5977325439453</v>
+        <v>188.6580047607422</v>
       </c>
       <c r="F5" t="n">
-        <v>140088000</v>
+        <v>130168900</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B6" t="n">
-        <v>186.1240974206304</v>
+        <v>191.7705422839889</v>
       </c>
       <c r="C6" t="n">
-        <v>189.1468543796426</v>
+        <v>194.8332119113436</v>
       </c>
       <c r="D6" t="n">
-        <v>186.0941551173159</v>
+        <v>190.6033405552435</v>
       </c>
       <c r="E6" t="n">
-        <v>188.6580200195312</v>
+        <v>192.1097412109375</v>
       </c>
       <c r="F6" t="n">
-        <v>130168900</v>
+        <v>182997200</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B7" t="n">
-        <v>191.7705422839889</v>
+        <v>193.0474821132437</v>
       </c>
       <c r="C7" t="n">
-        <v>194.8332119113436</v>
+        <v>195.1524395658232</v>
       </c>
       <c r="D7" t="n">
-        <v>190.6033405552435</v>
+        <v>181.6148814298513</v>
       </c>
       <c r="E7" t="n">
-        <v>192.1097412109375</v>
+        <v>182.7222290039062</v>
       </c>
       <c r="F7" t="n">
-        <v>182997200</v>
+        <v>268774400</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B8" t="n">
-        <v>193.0474982342752</v>
+        <v>187.5207340107304</v>
       </c>
       <c r="C8" t="n">
-        <v>195.1524558626357</v>
+        <v>189.6556185865847</v>
       </c>
       <c r="D8" t="n">
-        <v>181.6148965961679</v>
+        <v>185.5155435929421</v>
       </c>
       <c r="E8" t="n">
-        <v>182.7222442626953</v>
+        <v>187.8699035644531</v>
       </c>
       <c r="F8" t="n">
-        <v>268774400</v>
+        <v>153482800</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B9" t="n">
-        <v>187.5207340107304</v>
+        <v>184.3283927796865</v>
       </c>
       <c r="C9" t="n">
-        <v>189.6556185865847</v>
+        <v>184.3583198600852</v>
       </c>
       <c r="D9" t="n">
-        <v>185.5155435929421</v>
+        <v>179.2705030798172</v>
       </c>
       <c r="E9" t="n">
-        <v>187.8699035644531</v>
+        <v>179.5997161865234</v>
       </c>
       <c r="F9" t="n">
-        <v>153482800</v>
+        <v>205641400</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B10" t="n">
-        <v>184.3283927796865</v>
+        <v>184.3583147400375</v>
       </c>
       <c r="C10" t="n">
-        <v>184.3583198600852</v>
+        <v>184.4281395182556</v>
       </c>
       <c r="D10" t="n">
-        <v>179.2705030798172</v>
+        <v>176.866254560341</v>
       </c>
       <c r="E10" t="n">
-        <v>179.5997161865234</v>
+        <v>179.4001922607422</v>
       </c>
       <c r="F10" t="n">
-        <v>205641400</v>
+        <v>214450500</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B11" t="n">
-        <v>184.358330420537</v>
+        <v>181.7944368108431</v>
       </c>
       <c r="C11" t="n">
-        <v>184.428155204694</v>
+        <v>182.8419301869027</v>
       </c>
       <c r="D11" t="n">
-        <v>176.8662696036074</v>
+        <v>179.3403251298876</v>
       </c>
       <c r="E11" t="n">
-        <v>179.4002075195312</v>
+        <v>181.3754425048828</v>
       </c>
       <c r="F11" t="n">
-        <v>214450500</v>
+        <v>179723300</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B12" t="n">
-        <v>181.7944673989196</v>
+        <v>179.7493465774322</v>
       </c>
       <c r="C12" t="n">
-        <v>182.8419609512268</v>
+        <v>183.6599908268075</v>
       </c>
       <c r="D12" t="n">
-        <v>179.3403553050442</v>
+        <v>179.3203816221287</v>
       </c>
       <c r="E12" t="n">
-        <v>181.3754730224609</v>
+        <v>182.7820892333984</v>
       </c>
       <c r="F12" t="n">
-        <v>179723300</v>
+        <v>173135200</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B13" t="n">
-        <v>179.7493615830456</v>
+        <v>182.6922949953283</v>
       </c>
       <c r="C13" t="n">
-        <v>183.6600061588844</v>
+        <v>184.7573394499357</v>
       </c>
       <c r="D13" t="n">
-        <v>179.3203965919317</v>
+        <v>181.2956320849819</v>
       </c>
       <c r="E13" t="n">
-        <v>182.7821044921875</v>
+        <v>182.2034606933594</v>
       </c>
       <c r="F13" t="n">
-        <v>173135200</v>
+        <v>128544700</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B14" t="n">
-        <v>182.6923255947822</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="C14" t="n">
-        <v>184.7573703952674</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="D14" t="n">
-        <v>181.2956624505063</v>
+        <v>179.3702701372806</v>
       </c>
       <c r="E14" t="n">
-        <v>182.2034912109375</v>
+        <v>180.7270202636719</v>
       </c>
       <c r="F14" t="n">
-        <v>128544700</v>
+        <v>124240200</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B15" t="n">
-        <v>182.3531141136141</v>
+        <v>180.7070662621498</v>
       </c>
       <c r="C15" t="n">
-        <v>182.3531141136141</v>
+        <v>183.0015721983185</v>
       </c>
       <c r="D15" t="n">
-        <v>179.3702701372806</v>
+        <v>176.3375297972393</v>
       </c>
       <c r="E15" t="n">
-        <v>180.7270202636719</v>
+        <v>179.84912109375</v>
       </c>
       <c r="F15" t="n">
-        <v>124240200</v>
+        <v>162249600</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B16" t="n">
-        <v>180.7070662621498</v>
+        <v>179.988793025541</v>
       </c>
       <c r="C16" t="n">
-        <v>183.0015721983185</v>
+        <v>182.5925557149365</v>
       </c>
       <c r="D16" t="n">
-        <v>176.3375297972393</v>
+        <v>179.3602938591047</v>
       </c>
       <c r="E16" t="n">
-        <v>179.84912109375</v>
+        <v>181.7246398925781</v>
       </c>
       <c r="F16" t="n">
-        <v>162249600</v>
+        <v>111363700</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B17" t="n">
-        <v>179.988762799469</v>
+        <v>183.400590081168</v>
       </c>
       <c r="C17" t="n">
-        <v>182.5925250516066</v>
+        <v>187.0219186862977</v>
       </c>
       <c r="D17" t="n">
-        <v>179.3602637385785</v>
+        <v>183.0614063875393</v>
       </c>
       <c r="E17" t="n">
-        <v>181.724609375</v>
+        <v>185.8148040771484</v>
       </c>
       <c r="F17" t="n">
-        <v>111363700</v>
+        <v>131296700</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B18" t="n">
-        <v>183.400590081168</v>
+        <v>189.5359184602369</v>
       </c>
       <c r="C18" t="n">
-        <v>187.0219186862977</v>
+        <v>191.5411089646758</v>
       </c>
       <c r="D18" t="n">
-        <v>183.0614063875393</v>
+        <v>187.9796341631504</v>
       </c>
       <c r="E18" t="n">
-        <v>185.8148040771484</v>
+        <v>191.0323333740234</v>
       </c>
       <c r="F18" t="n">
-        <v>131296700</v>
+        <v>153452700</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B19" t="n">
-        <v>189.5358881817124</v>
+        <v>192.588592118433</v>
       </c>
       <c r="C19" t="n">
-        <v>191.5410783658203</v>
+        <v>202.6644428640734</v>
       </c>
       <c r="D19" t="n">
-        <v>187.9796041332436</v>
+        <v>191.4513174538508</v>
       </c>
       <c r="E19" t="n">
-        <v>191.0323028564453</v>
+        <v>200.5495147705078</v>
       </c>
       <c r="F19" t="n">
-        <v>153452700</v>
+        <v>297986200</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B20" t="n">
-        <v>192.5886214245991</v>
+        <v>207.482921843539</v>
       </c>
       <c r="C20" t="n">
-        <v>202.6644737034797</v>
+        <v>211.6828666070652</v>
       </c>
       <c r="D20" t="n">
-        <v>191.4513465869582</v>
+        <v>204.2905729140704</v>
       </c>
       <c r="E20" t="n">
-        <v>200.5495452880859</v>
+        <v>206.545166015625</v>
       </c>
       <c r="F20" t="n">
-        <v>297986200</v>
+        <v>308829600</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B21" t="n">
-        <v>207.482906515472</v>
+        <v>204.6596680014167</v>
       </c>
       <c r="C21" t="n">
-        <v>211.6828509687219</v>
+        <v>205.6672637579894</v>
       </c>
       <c r="D21" t="n">
-        <v>204.2905578218423</v>
+        <v>200.9286166610889</v>
       </c>
       <c r="E21" t="n">
-        <v>206.5451507568359</v>
+        <v>202.4050750732422</v>
       </c>
       <c r="F21" t="n">
-        <v>308829600</v>
+        <v>178864400</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B22" t="n">
-        <v>204.6596680014167</v>
+        <v>205.9565537660584</v>
       </c>
       <c r="C22" t="n">
-        <v>205.6672637579894</v>
+        <v>207.4729250244422</v>
       </c>
       <c r="D22" t="n">
-        <v>200.9286166610889</v>
+        <v>201.5870329046891</v>
       </c>
       <c r="E22" t="n">
-        <v>202.4050750732422</v>
+        <v>202.0060272216797</v>
       </c>
       <c r="F22" t="n">
-        <v>178864400</v>
+        <v>179802200</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B23" t="n">
-        <v>205.9565537660584</v>
+        <v>207.5826726752522</v>
       </c>
       <c r="C23" t="n">
-        <v>207.4729250244422</v>
+        <v>210.8348755139714</v>
       </c>
       <c r="D23" t="n">
-        <v>201.5870329046891</v>
+        <v>205.0686914304077</v>
       </c>
       <c r="E23" t="n">
-        <v>202.0060272216797</v>
+        <v>206.3855438232422</v>
       </c>
       <c r="F23" t="n">
-        <v>179802200</v>
+        <v>180267300</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B24" t="n">
-        <v>207.5826726752522</v>
+        <v>202.5148147488263</v>
       </c>
       <c r="C24" t="n">
-        <v>210.8348755139714</v>
+        <v>203.4824975937368</v>
       </c>
       <c r="D24" t="n">
-        <v>205.0686914304077</v>
+        <v>197.4569251230167</v>
       </c>
       <c r="E24" t="n">
-        <v>206.3855438232422</v>
+        <v>198.2151184082031</v>
       </c>
       <c r="F24" t="n">
-        <v>180267300</v>
+        <v>188919300</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B25" t="n">
-        <v>202.5148147488263</v>
+        <v>198.2949431289972</v>
       </c>
       <c r="C25" t="n">
-        <v>203.4824975937368</v>
+        <v>202.4350185226721</v>
       </c>
       <c r="D25" t="n">
-        <v>197.4569251230167</v>
+        <v>194.1847795950905</v>
       </c>
       <c r="E25" t="n">
-        <v>198.2151184082031</v>
+        <v>194.7434539794922</v>
       </c>
       <c r="F25" t="n">
-        <v>188919300</v>
+        <v>171350300</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B26" t="n">
-        <v>198.2949275919373</v>
+        <v>195.9505410878136</v>
       </c>
       <c r="C26" t="n">
-        <v>202.4350026612236</v>
+        <v>197.1476699621838</v>
       </c>
       <c r="D26" t="n">
-        <v>194.1847643800754</v>
+        <v>185.9345440647224</v>
       </c>
       <c r="E26" t="n">
-        <v>194.7434387207031</v>
+        <v>187.6304779052734</v>
       </c>
       <c r="F26" t="n">
-        <v>171350300</v>
+        <v>223029800</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B27" t="n">
-        <v>195.9505410878136</v>
+        <v>184.4580698535366</v>
       </c>
       <c r="C27" t="n">
-        <v>197.1476699621838</v>
+        <v>187.8699092076593</v>
       </c>
       <c r="D27" t="n">
-        <v>185.9345440647224</v>
+        <v>178.4823961188316</v>
       </c>
       <c r="E27" t="n">
-        <v>187.6304779052734</v>
+        <v>187.7003021240234</v>
       </c>
       <c r="F27" t="n">
-        <v>223029800</v>
+        <v>264942300</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B28" t="n">
-        <v>184.4580698535366</v>
+        <v>194.6436788693004</v>
       </c>
       <c r="C28" t="n">
-        <v>187.8699092076593</v>
+        <v>199.4621367771523</v>
       </c>
       <c r="D28" t="n">
-        <v>178.4823961188316</v>
+        <v>193.3268264223904</v>
       </c>
       <c r="E28" t="n">
-        <v>187.7003021240234</v>
+        <v>198.5742645263672</v>
       </c>
       <c r="F28" t="n">
-        <v>264942300</v>
+        <v>198897100</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B29" t="n">
-        <v>194.6436788693004</v>
+        <v>194.6935535589016</v>
       </c>
       <c r="C29" t="n">
-        <v>199.4621367771523</v>
+        <v>194.9529266552934</v>
       </c>
       <c r="D29" t="n">
-        <v>193.3268264223904</v>
+        <v>190.8427786999811</v>
       </c>
       <c r="E29" t="n">
-        <v>198.5742645263672</v>
+        <v>192.6983337402344</v>
       </c>
       <c r="F29" t="n">
-        <v>198897100</v>
+        <v>176483300</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B30" t="n">
-        <v>194.6935381421213</v>
+        <v>195.2522318976041</v>
       </c>
       <c r="C30" t="n">
-        <v>194.9529112179747</v>
+        <v>195.4218237722109</v>
       </c>
       <c r="D30" t="n">
-        <v>190.8427635881239</v>
+        <v>190.6732056162565</v>
       </c>
       <c r="E30" t="n">
-        <v>192.6983184814453</v>
+        <v>193.3368225097656</v>
       </c>
       <c r="F30" t="n">
-        <v>176483300</v>
+        <v>154935300</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B31" t="n">
-        <v>195.2522010776849</v>
+        <v>190.5933635318434</v>
       </c>
       <c r="C31" t="n">
-        <v>195.4217929255223</v>
+        <v>190.9824307616844</v>
       </c>
       <c r="D31" t="n">
-        <v>190.6731755191215</v>
+        <v>183.4105757073767</v>
       </c>
       <c r="E31" t="n">
-        <v>193.3367919921875</v>
+        <v>186.4133758544922</v>
       </c>
       <c r="F31" t="n">
-        <v>154935300</v>
+        <v>207423100</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B32" t="n">
-        <v>190.5933791327836</v>
+        <v>182.4229435613052</v>
       </c>
       <c r="C32" t="n">
-        <v>190.9824463944715</v>
+        <v>190.553458007553</v>
       </c>
       <c r="D32" t="n">
-        <v>183.4105907203728</v>
+        <v>180.1483942490048</v>
       </c>
       <c r="E32" t="n">
-        <v>186.4133911132812</v>
+        <v>189.7154693603516</v>
       </c>
       <c r="F32" t="n">
-        <v>207423100</v>
+        <v>186591900</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B33" t="n">
-        <v>182.4229435613052</v>
+        <v>185.525507871713</v>
       </c>
       <c r="C33" t="n">
-        <v>190.553458007553</v>
+        <v>188.5482645458532</v>
       </c>
       <c r="D33" t="n">
-        <v>180.1483942490048</v>
+        <v>183.8794576828592</v>
       </c>
       <c r="E33" t="n">
-        <v>189.7154693603516</v>
+        <v>186.1540069580078</v>
       </c>
       <c r="F33" t="n">
-        <v>186591900</v>
+        <v>173628900</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B34" t="n">
-        <v>185.5255230789849</v>
+        <v>182.941705155915</v>
       </c>
       <c r="C34" t="n">
-        <v>188.5482800008962</v>
+        <v>184.3583093626339</v>
       </c>
       <c r="D34" t="n">
-        <v>183.8794727552066</v>
+        <v>179.2206093334711</v>
       </c>
       <c r="E34" t="n">
-        <v>186.1540222167969</v>
+        <v>180.9265289306641</v>
       </c>
       <c r="F34" t="n">
-        <v>173628900</v>
+        <v>213598900</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B35" t="n">
-        <v>182.941705155915</v>
+        <v>184.3483122805645</v>
       </c>
       <c r="C35" t="n">
-        <v>184.3583093626339</v>
+        <v>187.4109817403353</v>
       </c>
       <c r="D35" t="n">
-        <v>179.2206093334711</v>
+        <v>182.39300555425</v>
       </c>
       <c r="E35" t="n">
-        <v>180.9265289306641</v>
+        <v>186.0741882324219</v>
       </c>
       <c r="F35" t="n">
-        <v>213598900</v>
+        <v>247246400</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B36" t="n">
-        <v>184.3483273978252</v>
+        <v>195.4816571057099</v>
       </c>
       <c r="C36" t="n">
-        <v>187.4109971087465</v>
+        <v>195.5315406452363</v>
       </c>
       <c r="D36" t="n">
-        <v>182.3930205111681</v>
+        <v>179.4201468289569</v>
       </c>
       <c r="E36" t="n">
-        <v>186.0742034912109</v>
+        <v>180.208251953125</v>
       </c>
       <c r="F36" t="n">
-        <v>247246400</v>
+        <v>343504800</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B37" t="n">
-        <v>195.4816571057099</v>
+        <v>180.8068289121023</v>
       </c>
       <c r="C37" t="n">
-        <v>195.5315406452363</v>
+        <v>184.1188859589464</v>
       </c>
       <c r="D37" t="n">
-        <v>179.4201468289569</v>
+        <v>172.5166776199441</v>
       </c>
       <c r="E37" t="n">
-        <v>180.208251953125</v>
+        <v>178.4524688720703</v>
       </c>
       <c r="F37" t="n">
-        <v>343504800</v>
+        <v>346926200</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B38" t="n">
-        <v>180.806813452001</v>
+        <v>179.0610243324759</v>
       </c>
       <c r="C38" t="n">
-        <v>184.1188702156436</v>
+        <v>183.0614349513779</v>
       </c>
       <c r="D38" t="n">
-        <v>172.5166628687019</v>
+        <v>176.0582084909882</v>
       </c>
       <c r="E38" t="n">
-        <v>178.4524536132812</v>
+        <v>182.1137084960938</v>
       </c>
       <c r="F38" t="n">
-        <v>346926200</v>
+        <v>256618300</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B39" t="n">
-        <v>179.0610093294625</v>
+        <v>174.4919407266003</v>
       </c>
       <c r="C39" t="n">
-        <v>183.0614196131816</v>
+        <v>177.7341727058355</v>
       </c>
       <c r="D39" t="n">
-        <v>176.0581937395723</v>
+        <v>169.1447513765687</v>
       </c>
       <c r="E39" t="n">
-        <v>182.1136932373047</v>
+        <v>177.3949890136719</v>
       </c>
       <c r="F39" t="n">
-        <v>256618300</v>
+        <v>320600300</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B40" t="n">
-        <v>174.491955735681</v>
+        <v>181.1958985688627</v>
       </c>
       <c r="C40" t="n">
-        <v>177.7341879937998</v>
+        <v>182.4728380763597</v>
       </c>
       <c r="D40" t="n">
-        <v>169.1447659257062</v>
+        <v>177.8140014756398</v>
       </c>
       <c r="E40" t="n">
-        <v>177.3950042724609</v>
+        <v>179.8291625976562</v>
       </c>
       <c r="F40" t="n">
-        <v>320600300</v>
+        <v>183852000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B41" t="n">
-        <v>181.1958831941039</v>
+        <v>178.5821404669205</v>
       </c>
       <c r="C41" t="n">
-        <v>182.4728225932506</v>
+        <v>178.8614700176124</v>
       </c>
       <c r="D41" t="n">
-        <v>177.8139863878403</v>
+        <v>176.0781451295325</v>
       </c>
       <c r="E41" t="n">
-        <v>179.8291473388672</v>
+        <v>176.5769500732422</v>
       </c>
       <c r="F41" t="n">
-        <v>183852000</v>
+        <v>121332800</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B42" t="n">
-        <v>178.5821558989869</v>
+        <v>174.3423041351479</v>
       </c>
       <c r="C42" t="n">
-        <v>178.8614854738169</v>
+        <v>179.8690716163194</v>
       </c>
       <c r="D42" t="n">
-        <v>176.0781603452176</v>
+        <v>173.2648835948944</v>
       </c>
       <c r="E42" t="n">
-        <v>176.5769653320312</v>
+        <v>179.4899749755859</v>
       </c>
       <c r="F42" t="n">
-        <v>121332800</v>
+        <v>188131000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B43" t="n">
-        <v>174.3423041351479</v>
+        <v>181.3255769560617</v>
       </c>
       <c r="C43" t="n">
-        <v>179.8690716163194</v>
+        <v>185.2162648499111</v>
       </c>
       <c r="D43" t="n">
-        <v>173.2648835948944</v>
+        <v>179.569788944198</v>
       </c>
       <c r="E43" t="n">
-        <v>179.4899749755859</v>
+        <v>181.0263061523438</v>
       </c>
       <c r="F43" t="n">
-        <v>188131000</v>
+        <v>182632200</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B44" t="n">
-        <v>181.3255769560617</v>
+        <v>180.6472109015755</v>
       </c>
       <c r="C44" t="n">
-        <v>185.2162648499111</v>
+        <v>182.0139316568558</v>
       </c>
       <c r="D44" t="n">
-        <v>179.569788944198</v>
+        <v>178.681918089591</v>
       </c>
       <c r="E44" t="n">
-        <v>181.0263061523438</v>
+        <v>179.1607666015625</v>
       </c>
       <c r="F44" t="n">
-        <v>182632200</v>
+        <v>165138000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,25 +1587,25 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B45" t="n">
-        <v>180.6472109015755</v>
+        <v>181.1960032737075</v>
       </c>
       <c r="C45" t="n">
-        <v>182.0139316568558</v>
+        <v>184.0892423581687</v>
       </c>
       <c r="D45" t="n">
-        <v>178.681918089591</v>
+        <v>179.5398901129937</v>
       </c>
       <c r="E45" t="n">
-        <v>179.1607666015625</v>
+        <v>182.951904296875</v>
       </c>
       <c r="F45" t="n">
-        <v>165138000</v>
+        <v>167364900</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1613,25 +1613,25 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B46" t="n">
-        <v>181.1959881613664</v>
+        <v>183.4607020047171</v>
       </c>
       <c r="C46" t="n">
-        <v>184.089227004522</v>
+        <v>184.2289086763207</v>
       </c>
       <c r="D46" t="n">
-        <v>179.5398751387779</v>
+        <v>180.4876631773748</v>
       </c>
       <c r="E46" t="n">
-        <v>182.9518890380859</v>
+        <v>181.9841613769531</v>
       </c>
       <c r="F46" t="n">
-        <v>167364900</v>
+        <v>143971100</v>
       </c>
       <c r="G46" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B47" t="n">
-        <v>183.4606866221248</v>
+        <v>182.2136112701494</v>
       </c>
       <c r="C47" t="n">
-        <v>184.2288932293168</v>
+        <v>187.5610985176648</v>
       </c>
       <c r="D47" t="n">
-        <v>180.4876480440623</v>
+        <v>181.9741660895743</v>
       </c>
       <c r="E47" t="n">
-        <v>181.9841461181641</v>
+        <v>185.1168212890625</v>
       </c>
       <c r="F47" t="n">
-        <v>143971100</v>
+        <v>204378100</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B48" t="n">
-        <v>182.2136112701494</v>
+        <v>185.1268117532098</v>
       </c>
       <c r="C48" t="n">
-        <v>187.5610985176648</v>
+        <v>185.2864418902268</v>
       </c>
       <c r="D48" t="n">
-        <v>181.9741660895743</v>
+        <v>182.8920507276432</v>
       </c>
       <c r="E48" t="n">
-        <v>185.1168212890625</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="F48" t="n">
-        <v>204378100</v>
+        <v>144719700</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B49" t="n">
-        <v>185.12679644575</v>
+        <v>184.538176449994</v>
       </c>
       <c r="C49" t="n">
-        <v>185.2864265695677</v>
+        <v>185.0469803407326</v>
       </c>
       <c r="D49" t="n">
-        <v>182.8920356049676</v>
+        <v>181.6150088138297</v>
       </c>
       <c r="E49" t="n">
-        <v>184.5381774902344</v>
+        <v>183.3509521484375</v>
       </c>
       <c r="F49" t="n">
-        <v>144719700</v>
+        <v>162785400</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B50" t="n">
-        <v>184.5381918075859</v>
+        <v>179.8591224369562</v>
       </c>
       <c r="C50" t="n">
-        <v>185.0469957406681</v>
+        <v>180.8967030087509</v>
       </c>
       <c r="D50" t="n">
-        <v>181.6150239281505</v>
+        <v>176.2076633109278</v>
       </c>
       <c r="E50" t="n">
-        <v>183.3509674072266</v>
+        <v>180.5075988769531</v>
       </c>
       <c r="F50" t="n">
-        <v>162785400</v>
+        <v>182136600</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B51" t="n">
-        <v>179.8591224369562</v>
+        <v>180.6871831157045</v>
       </c>
       <c r="C51" t="n">
-        <v>180.8967030087509</v>
+        <v>182.3931976659576</v>
       </c>
       <c r="D51" t="n">
-        <v>176.2076633109278</v>
+        <v>174.2123291208211</v>
       </c>
       <c r="E51" t="n">
-        <v>180.5075988769531</v>
+        <v>174.6114044189453</v>
       </c>
       <c r="F51" t="n">
-        <v>182136600</v>
+        <v>204274900</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B52" t="n">
-        <v>180.6871989054384</v>
+        <v>177.5245903328353</v>
       </c>
       <c r="C52" t="n">
-        <v>182.3932136047752</v>
+        <v>178.0034654802094</v>
       </c>
       <c r="D52" t="n">
-        <v>174.2123443447362</v>
+        <v>174.6213802569945</v>
       </c>
       <c r="E52" t="n">
-        <v>174.6114196777344</v>
+        <v>175.8784332275391</v>
       </c>
       <c r="F52" t="n">
-        <v>204274900</v>
+        <v>164775600</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B53" t="n">
-        <v>177.5245903328353</v>
+        <v>175.8485164107673</v>
       </c>
       <c r="C53" t="n">
-        <v>178.0034654802094</v>
+        <v>178.0733214473424</v>
       </c>
       <c r="D53" t="n">
-        <v>174.6213802569945</v>
+        <v>174.4916907151964</v>
       </c>
       <c r="E53" t="n">
-        <v>175.8784332275391</v>
+        <v>177.3051147460938</v>
       </c>
       <c r="F53" t="n">
-        <v>164775600</v>
+        <v>148588100</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B54" t="n">
-        <v>175.8485012773324</v>
+        <v>175.6888968536916</v>
       </c>
       <c r="C54" t="n">
-        <v>178.0733061224419</v>
+        <v>175.7188256001934</v>
       </c>
       <c r="D54" t="n">
-        <v>174.4916756985292</v>
+        <v>169.9124052081842</v>
       </c>
       <c r="E54" t="n">
-        <v>177.3050994873047</v>
+        <v>170.5409393310547</v>
       </c>
       <c r="F54" t="n">
-        <v>148588100</v>
+        <v>222775500</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B55" t="n">
-        <v>175.6888811343</v>
+        <v>174.1225483861358</v>
       </c>
       <c r="C55" t="n">
-        <v>175.7188098781239</v>
+        <v>175.7387615308714</v>
       </c>
       <c r="D55" t="n">
-        <v>169.9123900056319</v>
+        <v>171.4188835631069</v>
       </c>
       <c r="E55" t="n">
-        <v>170.5409240722656</v>
+        <v>173.7334594726562</v>
       </c>
       <c r="F55" t="n">
-        <v>222775500</v>
+        <v>176096000</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B56" t="n">
-        <v>174.1225483861358</v>
+        <v>176.2575523358494</v>
       </c>
       <c r="C56" t="n">
-        <v>175.7387615308714</v>
+        <v>181.0263919449467</v>
       </c>
       <c r="D56" t="n">
-        <v>171.4188835631069</v>
+        <v>175.9283209122297</v>
       </c>
       <c r="E56" t="n">
-        <v>173.7334594726562</v>
+        <v>180.5674743652344</v>
       </c>
       <c r="F56" t="n">
-        <v>176096000</v>
+        <v>324925900</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B57" t="n">
-        <v>176.2575672304301</v>
+        <v>183.4906129473229</v>
       </c>
       <c r="C57" t="n">
-        <v>181.0264072425164</v>
+        <v>183.730058116363</v>
       </c>
       <c r="D57" t="n">
-        <v>175.9283357789888</v>
+        <v>181.9242862331203</v>
       </c>
       <c r="E57" t="n">
-        <v>180.5674896240234</v>
+        <v>183.2611541748047</v>
       </c>
       <c r="F57" t="n">
-        <v>324925900</v>
+        <v>129064400</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B58" t="n">
-        <v>183.4906282252173</v>
+        <v>182.5428571096804</v>
       </c>
       <c r="C58" t="n">
-        <v>183.7300734141942</v>
+        <v>188.8880102762506</v>
       </c>
       <c r="D58" t="n">
-        <v>181.9243013805983</v>
+        <v>182.4730132178061</v>
       </c>
       <c r="E58" t="n">
-        <v>183.2611694335938</v>
+        <v>188.7682952880859</v>
       </c>
       <c r="F58" t="n">
-        <v>129064400</v>
+        <v>174873600</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B59" t="n">
-        <v>182.5428571096804</v>
+        <v>187.5012437217294</v>
       </c>
       <c r="C59" t="n">
-        <v>188.8880102762506</v>
+        <v>188.4689804086018</v>
       </c>
       <c r="D59" t="n">
-        <v>182.4730132178061</v>
+        <v>186.154389299292</v>
       </c>
       <c r="E59" t="n">
-        <v>188.7682952880859</v>
+        <v>188.169677734375</v>
       </c>
       <c r="F59" t="n">
-        <v>174873600</v>
+        <v>65528500</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B60" t="n">
-        <v>187.5012437217294</v>
+        <v>189.4766133088049</v>
       </c>
       <c r="C60" t="n">
-        <v>188.4689804086018</v>
+        <v>192.2401507638228</v>
       </c>
       <c r="D60" t="n">
-        <v>186.154389299292</v>
+        <v>187.5610975436497</v>
       </c>
       <c r="E60" t="n">
-        <v>188.169677734375</v>
+        <v>190.0851898193359</v>
       </c>
       <c r="F60" t="n">
-        <v>65528500</v>
+        <v>139740300</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B61" t="n">
-        <v>189.4766285187414</v>
+        <v>187.2717899684254</v>
       </c>
       <c r="C61" t="n">
-        <v>192.240166195598</v>
+        <v>188.3193265216257</v>
       </c>
       <c r="D61" t="n">
-        <v>187.5611125998212</v>
+        <v>185.4759890979627</v>
       </c>
       <c r="E61" t="n">
-        <v>190.085205078125</v>
+        <v>187.7805938720703</v>
       </c>
       <c r="F61" t="n">
-        <v>139740300</v>
+        <v>120006100</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B62" t="n">
-        <v>187.2717899684254</v>
+        <v>187.8005508490403</v>
       </c>
       <c r="C62" t="n">
-        <v>188.3193265216257</v>
+        <v>188.5487999407664</v>
       </c>
       <c r="D62" t="n">
-        <v>185.4759890979627</v>
+        <v>186.4935963146986</v>
       </c>
       <c r="E62" t="n">
-        <v>187.7805938720703</v>
+        <v>187.1021728515625</v>
       </c>
       <c r="F62" t="n">
-        <v>120006100</v>
+        <v>97687300</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B63" t="n">
-        <v>187.8005508490403</v>
+        <v>189.127461449755</v>
       </c>
       <c r="C63" t="n">
-        <v>188.5487999407664</v>
+        <v>190.1151405796458</v>
       </c>
       <c r="D63" t="n">
-        <v>186.4935963146986</v>
+        <v>186.0546497967401</v>
       </c>
       <c r="E63" t="n">
-        <v>187.1021728515625</v>
+        <v>186.0646209716797</v>
       </c>
       <c r="F63" t="n">
-        <v>97687300</v>
+        <v>120100500</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B64" t="n">
-        <v>189.1274459397885</v>
+        <v>189.3967976648124</v>
       </c>
       <c r="C64" t="n">
-        <v>190.1151249886817</v>
+        <v>192.479580126264</v>
       </c>
       <c r="D64" t="n">
-        <v>186.0546345387688</v>
+        <v>187.8204844911982</v>
       </c>
       <c r="E64" t="n">
-        <v>186.0646057128906</v>
+        <v>188.4091186523438</v>
       </c>
       <c r="F64" t="n">
-        <v>120100500</v>
+        <v>148240500</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B65" t="n">
-        <v>189.3968130035911</v>
+        <v>191.3123337767646</v>
       </c>
       <c r="C65" t="n">
-        <v>192.4795957147097</v>
+        <v>193.1779786425506</v>
       </c>
       <c r="D65" t="n">
-        <v>187.8204997023152</v>
+        <v>185.7154296257417</v>
       </c>
       <c r="E65" t="n">
-        <v>188.4091339111328</v>
+        <v>187.6808319091797</v>
       </c>
       <c r="F65" t="n">
-        <v>148240500</v>
+        <v>183529700</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B66" t="n">
-        <v>191.3123182227279</v>
+        <v>190.0752284670132</v>
       </c>
       <c r="C66" t="n">
-        <v>193.1779629368336</v>
+        <v>191.7213703933745</v>
       </c>
       <c r="D66" t="n">
-        <v>185.7154145267434</v>
+        <v>186.3838692947835</v>
       </c>
       <c r="E66" t="n">
-        <v>187.6808166503906</v>
+        <v>186.8028869628906</v>
       </c>
       <c r="F66" t="n">
-        <v>183529700</v>
+        <v>176862600</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B67" t="n">
-        <v>190.0752284670132</v>
+        <v>188.1297701943655</v>
       </c>
       <c r="C67" t="n">
-        <v>191.7213703933745</v>
+        <v>190.9232211122124</v>
       </c>
       <c r="D67" t="n">
-        <v>186.3838692947835</v>
+        <v>186.1244530144955</v>
       </c>
       <c r="E67" t="n">
-        <v>186.8028869628906</v>
+        <v>188.6685028076172</v>
       </c>
       <c r="F67" t="n">
-        <v>176862600</v>
+        <v>153543200</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B68" t="n">
-        <v>188.1297854095839</v>
+        <v>188.6685228499072</v>
       </c>
       <c r="C68" t="n">
-        <v>190.9232365533545</v>
+        <v>189.1074981045344</v>
       </c>
       <c r="D68" t="n">
-        <v>186.1244680675316</v>
+        <v>183.2811352524241</v>
       </c>
       <c r="E68" t="n">
-        <v>188.6685180664062</v>
+        <v>184.6080169677734</v>
       </c>
       <c r="F68" t="n">
-        <v>153543200</v>
+        <v>172457000</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B69" t="n">
-        <v>188.6685228499072</v>
+        <v>184.6479238968445</v>
       </c>
       <c r="C69" t="n">
-        <v>189.1074981045344</v>
+        <v>185.9049768874807</v>
       </c>
       <c r="D69" t="n">
-        <v>183.2811352524241</v>
+        <v>183.2412119543349</v>
       </c>
       <c r="E69" t="n">
-        <v>184.6080169677734</v>
+        <v>184.4284362792969</v>
       </c>
       <c r="F69" t="n">
-        <v>172457000</v>
+        <v>131327500</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B70" t="n">
-        <v>184.6479238968445</v>
+        <v>182.7922691735387</v>
       </c>
       <c r="C70" t="n">
-        <v>185.9049768874807</v>
+        <v>186.6831584288149</v>
       </c>
       <c r="D70" t="n">
-        <v>183.2412119543349</v>
+        <v>182.5927391235801</v>
       </c>
       <c r="E70" t="n">
-        <v>184.4284362792969</v>
+        <v>184.5082550048828</v>
       </c>
       <c r="F70" t="n">
-        <v>131327500</v>
+        <v>137968500</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B71" t="n">
-        <v>182.7922691735387</v>
+        <v>184.5681140987238</v>
       </c>
       <c r="C71" t="n">
-        <v>186.6831584288149</v>
+        <v>187.6708543554723</v>
       </c>
       <c r="D71" t="n">
-        <v>182.5927391235801</v>
+        <v>182.9718432388734</v>
       </c>
       <c r="E71" t="n">
-        <v>184.5082550048828</v>
+        <v>185.376220703125</v>
       </c>
       <c r="F71" t="n">
-        <v>137968500</v>
+        <v>160128900</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B72" t="n">
-        <v>184.5680989064521</v>
+        <v>183.8897012556695</v>
       </c>
       <c r="C72" t="n">
-        <v>187.6708389078061</v>
+        <v>184.0293738083791</v>
       </c>
       <c r="D72" t="n">
-        <v>182.9718281779948</v>
+        <v>180.3779146434709</v>
       </c>
       <c r="E72" t="n">
-        <v>185.3762054443359</v>
+        <v>182.7124481201172</v>
       </c>
       <c r="F72" t="n">
-        <v>160128900</v>
+        <v>159586100</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B73" t="n">
-        <v>183.889716612774</v>
+        <v>186.0646079796491</v>
       </c>
       <c r="C73" t="n">
-        <v>184.029389177148</v>
+        <v>189.2571344016907</v>
       </c>
       <c r="D73" t="n">
-        <v>180.3779297072971</v>
+        <v>185.895006678512</v>
       </c>
       <c r="E73" t="n">
-        <v>182.7124633789062</v>
+        <v>186.6133270263672</v>
       </c>
       <c r="F73" t="n">
-        <v>159586100</v>
+        <v>206188600</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B74" t="n">
-        <v>186.0646079796491</v>
+        <v>188.6385795892923</v>
       </c>
       <c r="C74" t="n">
-        <v>189.2571344016907</v>
+        <v>189.99540517049</v>
       </c>
       <c r="D74" t="n">
-        <v>185.895006678512</v>
+        <v>185.6455833269296</v>
       </c>
       <c r="E74" t="n">
-        <v>186.6133270263672</v>
+        <v>185.7952270507812</v>
       </c>
       <c r="F74" t="n">
-        <v>206188600</v>
+        <v>187967200</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B75" t="n">
-        <v>188.6385950815971</v>
+        <v>181.4753266272146</v>
       </c>
       <c r="C75" t="n">
-        <v>189.9954207742267</v>
+        <v>181.9542169705431</v>
       </c>
       <c r="D75" t="n">
-        <v>185.6455985734289</v>
+        <v>177.1953488429791</v>
       </c>
       <c r="E75" t="n">
-        <v>185.7952423095703</v>
+        <v>177.6542816162109</v>
       </c>
       <c r="F75" t="n">
-        <v>187967200</v>
+        <v>223345300</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B76" t="n">
-        <v>181.4753578011745</v>
+        <v>178.6320081827799</v>
       </c>
       <c r="C76" t="n">
-        <v>181.9542482267672</v>
+        <v>184.9472325313386</v>
       </c>
       <c r="D76" t="n">
-        <v>177.1953792817215</v>
+        <v>177.9835164834521</v>
       </c>
       <c r="E76" t="n">
-        <v>177.6543121337891</v>
+        <v>182.8920440673828</v>
       </c>
       <c r="F76" t="n">
-        <v>223345300</v>
+        <v>200381000</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B77" t="n">
-        <v>178.6319932794081</v>
+        <v>184.3186915464293</v>
       </c>
       <c r="C77" t="n">
-        <v>184.947217101084</v>
+        <v>185.7353746560278</v>
       </c>
       <c r="D77" t="n">
-        <v>177.9835016341843</v>
+        <v>183.5005985718231</v>
       </c>
       <c r="E77" t="n">
-        <v>182.8920288085938</v>
+        <v>184.4084777832031</v>
       </c>
       <c r="F77" t="n">
-        <v>200381000</v>
+        <v>139636600</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B78" t="n">
-        <v>184.3186915464293</v>
+        <v>187.0622712594319</v>
       </c>
       <c r="C78" t="n">
-        <v>185.7353746560278</v>
+        <v>189.1573747868041</v>
       </c>
       <c r="D78" t="n">
-        <v>183.5005985718231</v>
+        <v>186.3838660627843</v>
       </c>
       <c r="E78" t="n">
-        <v>184.4084777832031</v>
+        <v>187.2318725585938</v>
       </c>
       <c r="F78" t="n">
-        <v>139636600</v>
+        <v>142748100</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B79" t="n">
-        <v>187.0622712594319</v>
+        <v>186.7230748442759</v>
       </c>
       <c r="C79" t="n">
-        <v>189.1573747868041</v>
+        <v>188.6784906596197</v>
       </c>
       <c r="D79" t="n">
-        <v>186.3838660627843</v>
+        <v>185.555808059744</v>
       </c>
       <c r="E79" t="n">
-        <v>187.2318725585938</v>
+        <v>186.0346832275391</v>
       </c>
       <c r="F79" t="n">
-        <v>142748100</v>
+        <v>124799600</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B80" t="n">
-        <v>186.7230748442759</v>
+        <v>186.8028844605491</v>
       </c>
       <c r="C80" t="n">
-        <v>188.6784906596197</v>
+        <v>189.5564356240106</v>
       </c>
       <c r="D80" t="n">
-        <v>185.555808059744</v>
+        <v>185.2664711415707</v>
       </c>
       <c r="E80" t="n">
-        <v>186.0346832275391</v>
+        <v>188.0798950195312</v>
       </c>
       <c r="F80" t="n">
-        <v>124799600</v>
+        <v>143711600</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B81" t="n">
-        <v>186.8028844605491</v>
+        <v>190.8234748728661</v>
       </c>
       <c r="C81" t="n">
-        <v>189.5564356240106</v>
+        <v>191.9009553855833</v>
       </c>
       <c r="D81" t="n">
-        <v>185.2664711415707</v>
+        <v>189.3968053634026</v>
       </c>
       <c r="E81" t="n">
-        <v>188.0798950195312</v>
+        <v>191.0728912353516</v>
       </c>
       <c r="F81" t="n">
-        <v>143711600</v>
+        <v>148552700</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B82" t="n">
-        <v>190.823459633995</v>
+        <v>190.8932954336949</v>
       </c>
       <c r="C82" t="n">
-        <v>191.9009400606663</v>
+        <v>193.0282987969995</v>
       </c>
       <c r="D82" t="n">
-        <v>189.3967902384632</v>
+        <v>185.625623299501</v>
       </c>
       <c r="E82" t="n">
-        <v>191.0728759765625</v>
+        <v>192.0605621337891</v>
       </c>
       <c r="F82" t="n">
-        <v>148552700</v>
+        <v>171764400</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B83" t="n">
-        <v>190.8933105997472</v>
+        <v>190.7636071727618</v>
       </c>
       <c r="C83" t="n">
-        <v>193.0283141326731</v>
+        <v>194.0359484555967</v>
       </c>
       <c r="D83" t="n">
-        <v>185.6256380470483</v>
+        <v>189.0276639024229</v>
       </c>
       <c r="E83" t="n">
-        <v>192.0605773925781</v>
+        <v>190.6837921142578</v>
       </c>
       <c r="F83" t="n">
-        <v>171764400</v>
+        <v>179489500</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B84" t="n">
-        <v>190.7636224379378</v>
+        <v>186.7629812920276</v>
       </c>
       <c r="C84" t="n">
-        <v>194.0359639826301</v>
+        <v>189.8557504766133</v>
       </c>
       <c r="D84" t="n">
-        <v>189.0276790286862</v>
+        <v>184.4484052141589</v>
       </c>
       <c r="E84" t="n">
-        <v>190.6838073730469</v>
+        <v>185.1766967773438</v>
       </c>
       <c r="F84" t="n">
-        <v>179489500</v>
+        <v>165794100</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B85" t="n">
-        <v>186.7629659025267</v>
+        <v>185.8052108647954</v>
       </c>
       <c r="C85" t="n">
-        <v>189.8557348322644</v>
+        <v>185.8351396091497</v>
       </c>
       <c r="D85" t="n">
-        <v>184.4483900153819</v>
+        <v>175.8185703987175</v>
       </c>
       <c r="E85" t="n">
-        <v>185.1766815185547</v>
+        <v>179.9189758300781</v>
       </c>
       <c r="F85" t="n">
-        <v>165794100</v>
+        <v>204019600</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B86" t="n">
-        <v>185.8052108647954</v>
+        <v>179.0410414348666</v>
       </c>
       <c r="C86" t="n">
-        <v>185.8351396091497</v>
+        <v>179.160756412826</v>
       </c>
       <c r="D86" t="n">
-        <v>175.8185703987175</v>
+        <v>171.5086645338761</v>
       </c>
       <c r="E86" t="n">
-        <v>179.9189758300781</v>
+        <v>173.7833404541016</v>
       </c>
       <c r="F86" t="n">
-        <v>204019600</v>
+        <v>207014100</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B87" t="n">
-        <v>179.0410571553003</v>
+        <v>174.5215964583249</v>
       </c>
       <c r="C87" t="n">
-        <v>179.1607721437711</v>
+        <v>176.4071986282528</v>
       </c>
       <c r="D87" t="n">
-        <v>171.5086795929406</v>
+        <v>170.6307075914073</v>
       </c>
       <c r="E87" t="n">
-        <v>173.7833557128906</v>
+        <v>171.4787292480469</v>
       </c>
       <c r="F87" t="n">
-        <v>207014100</v>
+        <v>206312900</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B88" t="n">
-        <v>174.5216119878791</v>
+        <v>176.277498975506</v>
       </c>
       <c r="C88" t="n">
-        <v>176.4072143255947</v>
+        <v>186.5634266395524</v>
       </c>
       <c r="D88" t="n">
-        <v>170.6307227747363</v>
+        <v>174.1923819783884</v>
       </c>
       <c r="E88" t="n">
-        <v>171.4787445068359</v>
+        <v>184.9771423339844</v>
       </c>
       <c r="F88" t="n">
-        <v>206312900</v>
+        <v>231346200</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B89" t="n">
-        <v>176.2775280578147</v>
+        <v>183.8298238555102</v>
       </c>
       <c r="C89" t="n">
-        <v>186.5634574188361</v>
+        <v>193.2078878887748</v>
       </c>
       <c r="D89" t="n">
-        <v>174.1924107166939</v>
+        <v>183.5205500126207</v>
       </c>
       <c r="E89" t="n">
-        <v>184.9771728515625</v>
+        <v>189.5963287353516</v>
       </c>
       <c r="F89" t="n">
-        <v>231346200</v>
+        <v>196387400</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B90" t="n">
-        <v>183.8298238555102</v>
+        <v>190.933219719687</v>
       </c>
       <c r="C90" t="n">
-        <v>193.2078878887748</v>
+        <v>192.0306425866914</v>
       </c>
       <c r="D90" t="n">
-        <v>183.5205500126207</v>
+        <v>187.6808205923615</v>
       </c>
       <c r="E90" t="n">
-        <v>189.5963287353516</v>
+        <v>188.0998382568359</v>
       </c>
       <c r="F90" t="n">
-        <v>196387400</v>
+        <v>136764800</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B91" t="n">
-        <v>190.9332352083219</v>
+        <v>192.0007297023972</v>
       </c>
       <c r="C91" t="n">
-        <v>192.0306581643501</v>
+        <v>192.8088363522974</v>
       </c>
       <c r="D91" t="n">
-        <v>187.6808358171596</v>
+        <v>188.3293278304631</v>
       </c>
       <c r="E91" t="n">
-        <v>188.099853515625</v>
+        <v>189.6063385009766</v>
       </c>
       <c r="F91" t="n">
-        <v>136764800</v>
+        <v>144192700</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B92" t="n">
-        <v>192.0007142509167</v>
+        <v>192.5793648877844</v>
       </c>
       <c r="C92" t="n">
-        <v>192.8088208357837</v>
+        <v>193.1580126884611</v>
       </c>
       <c r="D92" t="n">
-        <v>188.329312674443</v>
+        <v>186.0745817463215</v>
       </c>
       <c r="E92" t="n">
-        <v>189.6063232421875</v>
+        <v>186.5035858154297</v>
       </c>
       <c r="F92" t="n">
-        <v>144192700</v>
+        <v>189932500</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B93" t="n">
-        <v>192.5793648877844</v>
+        <v>187.042320465516</v>
       </c>
       <c r="C93" t="n">
-        <v>193.1580126884611</v>
+        <v>187.0622780376601</v>
       </c>
       <c r="D93" t="n">
-        <v>186.0745817463215</v>
+        <v>181.1660713803529</v>
       </c>
       <c r="E93" t="n">
-        <v>186.5035858154297</v>
+        <v>182.3832244873047</v>
       </c>
       <c r="F93" t="n">
-        <v>189932500</v>
+        <v>161888000</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B94" t="n">
-        <v>187.042320465516</v>
+        <v>181.3257085516038</v>
       </c>
       <c r="C94" t="n">
-        <v>187.0622780376601</v>
+        <v>186.7130962790006</v>
       </c>
       <c r="D94" t="n">
-        <v>181.1660713803529</v>
+        <v>178.7617008539599</v>
       </c>
       <c r="E94" t="n">
-        <v>182.3832244873047</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="F94" t="n">
-        <v>161888000</v>
+        <v>162276900</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B95" t="n">
-        <v>181.3256935584433</v>
+        <v>188.3093443160685</v>
       </c>
       <c r="C95" t="n">
-        <v>186.7130808403767</v>
+        <v>189.9255573932224</v>
       </c>
       <c r="D95" t="n">
-        <v>178.7616860728079</v>
+        <v>186.3239846890322</v>
       </c>
       <c r="E95" t="n">
-        <v>184.5381774902344</v>
+        <v>187.5411376953125</v>
       </c>
       <c r="F95" t="n">
-        <v>162276900</v>
+        <v>164749100</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B96" t="n">
-        <v>188.3093443160685</v>
+        <v>186.62329889396</v>
       </c>
       <c r="C96" t="n">
-        <v>189.9255573932224</v>
+        <v>187.9900957055448</v>
       </c>
       <c r="D96" t="n">
-        <v>186.3239846890322</v>
+        <v>185.2265733363672</v>
       </c>
       <c r="E96" t="n">
-        <v>187.5411376953125</v>
+        <v>187.4613342285156</v>
       </c>
       <c r="F96" t="n">
-        <v>164749100</v>
+        <v>126554500</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B97" t="n">
-        <v>186.62329889396</v>
+        <v>186.1344488846578</v>
       </c>
       <c r="C97" t="n">
-        <v>187.9900957055448</v>
+        <v>189.8856654675195</v>
       </c>
       <c r="D97" t="n">
-        <v>185.2265733363672</v>
+        <v>185.5059147845697</v>
       </c>
       <c r="E97" t="n">
-        <v>187.4613342285156</v>
+        <v>189.3768615722656</v>
       </c>
       <c r="F97" t="n">
-        <v>126554500</v>
+        <v>178422300</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B98" t="n">
-        <v>186.1344488846578</v>
+        <v>190.9531700210539</v>
       </c>
       <c r="C98" t="n">
-        <v>189.8856654675195</v>
+        <v>193.4972200828311</v>
       </c>
       <c r="D98" t="n">
-        <v>185.5059147845697</v>
+        <v>189.1374267327081</v>
       </c>
       <c r="E98" t="n">
-        <v>189.3768615722656</v>
+        <v>191.1028289794922</v>
       </c>
       <c r="F98" t="n">
-        <v>178422300</v>
+        <v>171584800</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B99" t="n">
-        <v>190.9531547742145</v>
+        <v>191.0429698590405</v>
       </c>
       <c r="C99" t="n">
-        <v>193.4972046328596</v>
+        <v>193.3176459547985</v>
       </c>
       <c r="D99" t="n">
-        <v>189.1374116308485</v>
+        <v>186.9625064417709</v>
       </c>
       <c r="E99" t="n">
-        <v>191.1028137207031</v>
+        <v>192.3997955322266</v>
       </c>
       <c r="F99" t="n">
-        <v>171584800</v>
+        <v>175123600</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B100" t="n">
-        <v>191.0429698590405</v>
+        <v>193.9960453222018</v>
       </c>
       <c r="C100" t="n">
-        <v>193.3176459547985</v>
+        <v>197.1686293956491</v>
       </c>
       <c r="D100" t="n">
-        <v>186.9625064417709</v>
+        <v>193.3375824661624</v>
       </c>
       <c r="E100" t="n">
-        <v>192.3997955322266</v>
+        <v>195.1034545898438</v>
       </c>
       <c r="F100" t="n">
-        <v>175123600</v>
+        <v>250637100</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B101" t="n">
-        <v>193.9960453222018</v>
+        <v>193.8164813019665</v>
       </c>
       <c r="C101" t="n">
-        <v>197.1686293956491</v>
+        <v>193.8364236513225</v>
       </c>
       <c r="D101" t="n">
-        <v>193.3375824661624</v>
+        <v>183.8897126034445</v>
       </c>
       <c r="E101" t="n">
-        <v>195.1034545898438</v>
+        <v>184.4583740234375</v>
       </c>
       <c r="F101" t="n">
-        <v>250637100</v>
+        <v>360807900</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B102" t="n">
-        <v>193.8164813019665</v>
+        <v>180.8268714126474</v>
       </c>
       <c r="C102" t="n">
-        <v>193.8364236513225</v>
+        <v>182.1637395256691</v>
       </c>
       <c r="D102" t="n">
-        <v>183.8897126034445</v>
+        <v>175.9682453114839</v>
       </c>
       <c r="E102" t="n">
-        <v>184.4583740234375</v>
+        <v>176.7763519287109</v>
       </c>
       <c r="F102" t="n">
-        <v>360807900</v>
+        <v>311636500</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B103" t="n">
-        <v>180.8268714126474</v>
+        <v>174.6014235260267</v>
       </c>
       <c r="C103" t="n">
-        <v>182.1637395256691</v>
+        <v>183.0317086895539</v>
       </c>
       <c r="D103" t="n">
-        <v>175.9682453114839</v>
+        <v>174.2322921838959</v>
       </c>
       <c r="E103" t="n">
-        <v>176.7763519287109</v>
+        <v>182.0539855957031</v>
       </c>
       <c r="F103" t="n">
-        <v>311636500</v>
+        <v>209095300</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B104" t="n">
-        <v>174.6014235260267</v>
+        <v>178.0733135069376</v>
       </c>
       <c r="C104" t="n">
-        <v>183.0317086895539</v>
+        <v>180.4776756968921</v>
       </c>
       <c r="D104" t="n">
-        <v>174.2322921838959</v>
+        <v>176.5069714269912</v>
       </c>
       <c r="E104" t="n">
-        <v>182.0539855957031</v>
+        <v>179.6296691894531</v>
       </c>
       <c r="F104" t="n">
-        <v>209095300</v>
+        <v>178099400</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B105" t="n">
-        <v>178.0733135069376</v>
+        <v>180.0187649948852</v>
       </c>
       <c r="C105" t="n">
-        <v>180.4776756968921</v>
+        <v>184.2688145383873</v>
       </c>
       <c r="D105" t="n">
-        <v>176.5069714269912</v>
+        <v>179.6396472340209</v>
       </c>
       <c r="E105" t="n">
-        <v>179.6296691894531</v>
+        <v>182.6126861572266</v>
       </c>
       <c r="F105" t="n">
-        <v>178099400</v>
+        <v>177731200</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B106" t="n">
-        <v>180.0187499528396</v>
+        <v>180.7470550179114</v>
       </c>
       <c r="C106" t="n">
-        <v>184.2687991412151</v>
+        <v>183.6303076754259</v>
       </c>
       <c r="D106" t="n">
-        <v>179.6396322236537</v>
+        <v>177.4647422536165</v>
       </c>
       <c r="E106" t="n">
-        <v>182.6126708984375</v>
+        <v>182.9119873046875</v>
       </c>
       <c r="F106" t="n">
-        <v>177731200</v>
+        <v>198779700</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B107" t="n">
-        <v>180.7470399397241</v>
+        <v>179.420134514761</v>
       </c>
       <c r="C107" t="n">
-        <v>183.6302923567135</v>
+        <v>182.3333155363547</v>
       </c>
       <c r="D107" t="n">
-        <v>177.4647274492447</v>
+        <v>176.4071960911633</v>
       </c>
       <c r="E107" t="n">
-        <v>182.9119720458984</v>
+        <v>177.4048614501953</v>
       </c>
       <c r="F107" t="n">
-        <v>198779700</v>
+        <v>189021900</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B108" t="n">
-        <v>179.4201653790109</v>
+        <v>176.4171820751478</v>
       </c>
       <c r="C108" t="n">
-        <v>182.3333469017365</v>
+        <v>182.4829897940845</v>
       </c>
       <c r="D108" t="n">
-        <v>176.4072264371208</v>
+        <v>175.1501427003192</v>
       </c>
       <c r="E108" t="n">
-        <v>177.4048919677734</v>
+        <v>182.2235870361328</v>
       </c>
       <c r="F108" t="n">
-        <v>189021900</v>
+        <v>177213600</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B109" t="n">
-        <v>176.4171820751478</v>
+        <v>181.9741760435397</v>
       </c>
       <c r="C109" t="n">
-        <v>182.4829897940845</v>
+        <v>186.0047530762794</v>
       </c>
       <c r="D109" t="n">
-        <v>175.1501427003192</v>
+        <v>181.5850871183009</v>
       </c>
       <c r="E109" t="n">
-        <v>182.2235870361328</v>
+        <v>184.3386535644531</v>
       </c>
       <c r="F109" t="n">
-        <v>177213600</v>
+        <v>179118500</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,25 +3277,25 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B110" t="n">
-        <v>181.9741609804723</v>
+        <v>185.4860219488843</v>
       </c>
       <c r="C110" t="n">
-        <v>186.0047376795775</v>
+        <v>187.1921136401388</v>
       </c>
       <c r="D110" t="n">
-        <v>181.5850720874406</v>
+        <v>184.0293448898806</v>
       </c>
       <c r="E110" t="n">
-        <v>184.3386383056641</v>
+        <v>185.6057434082031</v>
       </c>
       <c r="F110" t="n">
-        <v>179118500</v>
+        <v>145280400</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3303,25 +3303,25 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B111" t="n">
-        <v>185.4860219488843</v>
+        <v>183.6302641505579</v>
       </c>
       <c r="C111" t="n">
-        <v>187.1921136401388</v>
+        <v>184.5182338343672</v>
       </c>
       <c r="D111" t="n">
-        <v>184.0293448898806</v>
+        <v>181.3355064165816</v>
       </c>
       <c r="E111" t="n">
-        <v>185.6057434082031</v>
+        <v>182.7223358154297</v>
       </c>
       <c r="F111" t="n">
-        <v>145280400</v>
+        <v>155762700</v>
       </c>
       <c r="G111" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B112" t="n">
-        <v>183.6302794851663</v>
+        <v>184.4982918130038</v>
       </c>
       <c r="C112" t="n">
-        <v>184.5182492431283</v>
+        <v>185.6656218245341</v>
       </c>
       <c r="D112" t="n">
-        <v>181.3355215595592</v>
+        <v>179.5296528660815</v>
       </c>
       <c r="E112" t="n">
-        <v>182.7223510742188</v>
+        <v>179.8389434814453</v>
       </c>
       <c r="F112" t="n">
-        <v>155762700</v>
+        <v>160988400</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B113" t="n">
-        <v>184.4982761588831</v>
+        <v>182.5527246843909</v>
       </c>
       <c r="C113" t="n">
-        <v>185.6656060713691</v>
+        <v>188.4492501487561</v>
       </c>
       <c r="D113" t="n">
-        <v>179.5296376335348</v>
+        <v>180.9962848148914</v>
       </c>
       <c r="E113" t="n">
-        <v>179.8389282226562</v>
+        <v>182.8021545410156</v>
       </c>
       <c r="F113" t="n">
-        <v>160988400</v>
+        <v>217307400</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B114" t="n">
-        <v>182.5527399223597</v>
+        <v>184.6379731916982</v>
       </c>
       <c r="C114" t="n">
-        <v>188.4492658789173</v>
+        <v>184.9771941770484</v>
       </c>
       <c r="D114" t="n">
-        <v>180.9962999229416</v>
+        <v>181.2656763194747</v>
       </c>
       <c r="E114" t="n">
-        <v>182.8021697998047</v>
+        <v>181.5151062011719</v>
       </c>
       <c r="F114" t="n">
-        <v>217307400</v>
+        <v>182497800</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B115" t="n">
-        <v>184.6379576703901</v>
+        <v>182.0638447517288</v>
       </c>
       <c r="C115" t="n">
-        <v>184.9771786272242</v>
+        <v>182.9618014097589</v>
       </c>
       <c r="D115" t="n">
-        <v>181.2656610816535</v>
+        <v>179.9187539793071</v>
       </c>
       <c r="E115" t="n">
-        <v>181.5150909423828</v>
+        <v>179.9885864257812</v>
       </c>
       <c r="F115" t="n">
-        <v>182497800</v>
+        <v>156683100</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B116" t="n">
-        <v>182.0638447517288</v>
+        <v>177.6040222894031</v>
       </c>
       <c r="C116" t="n">
-        <v>182.9618014097589</v>
+        <v>179.5695306962835</v>
       </c>
       <c r="D116" t="n">
-        <v>179.9187539793071</v>
+        <v>175.3890840362079</v>
       </c>
       <c r="E116" t="n">
-        <v>179.9885864257812</v>
+        <v>178.1527709960938</v>
       </c>
       <c r="F116" t="n">
-        <v>156683100</v>
+        <v>170968500</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B117" t="n">
-        <v>177.6040375011918</v>
+        <v>177.5940686691464</v>
       </c>
       <c r="C117" t="n">
-        <v>179.569546076418</v>
+        <v>177.853470255105</v>
       </c>
       <c r="D117" t="n">
-        <v>175.3890990582871</v>
+        <v>171.3283915093003</v>
       </c>
       <c r="E117" t="n">
-        <v>178.1527862548828</v>
+        <v>172.30615234375</v>
       </c>
       <c r="F117" t="n">
-        <v>170968500</v>
+        <v>241323500</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B118" t="n">
-        <v>177.5940529420793</v>
+        <v>176.8557415306554</v>
       </c>
       <c r="C118" t="n">
-        <v>177.8534545050662</v>
+        <v>177.9632107122345</v>
       </c>
       <c r="D118" t="n">
-        <v>171.3283763370981</v>
+        <v>174.3614429436745</v>
       </c>
       <c r="E118" t="n">
-        <v>172.3061370849609</v>
+        <v>175.2394409179688</v>
       </c>
       <c r="F118" t="n">
-        <v>241323500</v>
+        <v>182836300</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B119" t="n">
-        <v>176.8557415306554</v>
+        <v>174.4312942297872</v>
       </c>
       <c r="C119" t="n">
-        <v>177.9632107122345</v>
+        <v>175.8181236639554</v>
       </c>
       <c r="D119" t="n">
-        <v>174.3614429436745</v>
+        <v>173.5832266030264</v>
       </c>
       <c r="E119" t="n">
-        <v>175.2394409179688</v>
+        <v>174.8004455566406</v>
       </c>
       <c r="F119" t="n">
-        <v>182836300</v>
+        <v>147667800</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B120" t="n">
-        <v>174.4312942297872</v>
+        <v>176.6961233561449</v>
       </c>
       <c r="C120" t="n">
-        <v>175.8181236639554</v>
+        <v>180.8067226806179</v>
       </c>
       <c r="D120" t="n">
-        <v>173.5832266030264</v>
+        <v>176.4466934898736</v>
       </c>
       <c r="E120" t="n">
-        <v>174.8004455566406</v>
+        <v>178.2725067138672</v>
       </c>
       <c r="F120" t="n">
-        <v>147667800</v>
+        <v>162602100</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B121" t="n">
-        <v>176.6961233561449</v>
+        <v>175.6684741654964</v>
       </c>
       <c r="C121" t="n">
-        <v>180.8067226806179</v>
+        <v>176.1074579435819</v>
       </c>
       <c r="D121" t="n">
-        <v>176.4466934898736</v>
+        <v>170.7497092682189</v>
       </c>
       <c r="E121" t="n">
-        <v>178.2725067138672</v>
+        <v>170.8494873046875</v>
       </c>
       <c r="F121" t="n">
-        <v>162602100</v>
+        <v>186152200</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B122" t="n">
-        <v>175.6684741654964</v>
+        <v>169.6123099949711</v>
       </c>
       <c r="C122" t="n">
-        <v>176.1074579435819</v>
+        <v>170.5800990993323</v>
       </c>
       <c r="D122" t="n">
-        <v>170.7497092682189</v>
+        <v>166.629123297364</v>
       </c>
       <c r="E122" t="n">
-        <v>170.8494873046875</v>
+        <v>167.1379699707031</v>
       </c>
       <c r="F122" t="n">
-        <v>186152200</v>
+        <v>196212700</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B123" t="n">
-        <v>169.6122945102883</v>
+        <v>168.3950875250076</v>
       </c>
       <c r="C123" t="n">
-        <v>170.5800835262955</v>
+        <v>169.0635577295173</v>
       </c>
       <c r="D123" t="n">
-        <v>166.6291080850299</v>
+        <v>163.8953782868944</v>
       </c>
       <c r="E123" t="n">
-        <v>167.1379547119141</v>
+        <v>164.7933197021484</v>
       </c>
       <c r="F123" t="n">
-        <v>196212700</v>
+        <v>185627000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B124" t="n">
-        <v>168.3950875250076</v>
+        <v>166.589210422399</v>
       </c>
       <c r="C124" t="n">
-        <v>169.0635577295173</v>
+        <v>174.2217577880002</v>
       </c>
       <c r="D124" t="n">
-        <v>163.8953782868944</v>
+        <v>166.5792387089764</v>
       </c>
       <c r="E124" t="n">
-        <v>164.7933197021484</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="F124" t="n">
-        <v>185627000</v>
+        <v>226181300</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B125" t="n">
-        <v>166.5892250311153</v>
+        <v>175.5986119754623</v>
       </c>
       <c r="C125" t="n">
-        <v>174.2217730660379</v>
+        <v>176.9654826629128</v>
       </c>
       <c r="D125" t="n">
-        <v>166.5792533168182</v>
+        <v>174.351462742682</v>
       </c>
       <c r="E125" t="n">
-        <v>174.0022735595703</v>
+        <v>175.3491821289062</v>
       </c>
       <c r="F125" t="n">
-        <v>226181300</v>
+        <v>168132000</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B126" t="n">
-        <v>175.5986272559566</v>
+        <v>171.787333172162</v>
       </c>
       <c r="C126" t="n">
-        <v>176.9654980623514</v>
+        <v>177.0852364118599</v>
       </c>
       <c r="D126" t="n">
-        <v>174.3514779146501</v>
+        <v>170.9791828272563</v>
       </c>
       <c r="E126" t="n">
-        <v>175.3491973876953</v>
+        <v>176.9854583740234</v>
       </c>
       <c r="F126" t="n">
-        <v>168132000</v>
+        <v>143143200</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B127" t="n">
-        <v>171.7873183615289</v>
+        <v>176.7559774774269</v>
       </c>
       <c r="C127" t="n">
-        <v>177.0852211444685</v>
+        <v>177.3845303646084</v>
       </c>
       <c r="D127" t="n">
-        <v>170.9791680862979</v>
+        <v>175.3591611441553</v>
       </c>
       <c r="E127" t="n">
-        <v>176.9854431152344</v>
+        <v>177.2348785400391</v>
       </c>
       <c r="F127" t="n">
-        <v>143143200</v>
+        <v>107564300</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B128" t="n">
-        <v>176.7559774774269</v>
+        <v>175.3292270516068</v>
       </c>
       <c r="C128" t="n">
-        <v>177.3845303646084</v>
+        <v>177.8235255680002</v>
       </c>
       <c r="D128" t="n">
-        <v>175.3591611441553</v>
+        <v>173.2639557965079</v>
       </c>
       <c r="E128" t="n">
-        <v>177.2348785400391</v>
+        <v>177.6938323974609</v>
       </c>
       <c r="F128" t="n">
-        <v>107564300</v>
+        <v>132534900</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B129" t="n">
-        <v>175.3292270516068</v>
+        <v>184.079243714486</v>
       </c>
       <c r="C129" t="n">
-        <v>177.8235255680002</v>
+        <v>184.837505037226</v>
       </c>
       <c r="D129" t="n">
-        <v>173.2639557965079</v>
+        <v>179.8888249511496</v>
       </c>
       <c r="E129" t="n">
-        <v>177.6938323974609</v>
+        <v>181.6647644042969</v>
       </c>
       <c r="F129" t="n">
-        <v>132534900</v>
+        <v>147732700</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B130" t="n">
-        <v>184.079243714486</v>
+        <v>181.4253138719204</v>
       </c>
       <c r="C130" t="n">
-        <v>184.837505037226</v>
+        <v>183.6602110774668</v>
       </c>
       <c r="D130" t="n">
-        <v>179.8888249511496</v>
+        <v>180.2080948395415</v>
       </c>
       <c r="E130" t="n">
-        <v>181.6647644042969</v>
+        <v>183.4906005859375</v>
       </c>
       <c r="F130" t="n">
-        <v>147732700</v>
+        <v>116428500</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B131" t="n">
-        <v>181.4252987848774</v>
+        <v>183.8896736698189</v>
       </c>
       <c r="C131" t="n">
-        <v>183.6601958045732</v>
+        <v>189.5666999081706</v>
       </c>
       <c r="D131" t="n">
-        <v>180.2080798537204</v>
+        <v>183.8797019557237</v>
       </c>
       <c r="E131" t="n">
-        <v>183.4905853271484</v>
+        <v>188.1998291015625</v>
       </c>
       <c r="F131" t="n">
-        <v>116428500</v>
+        <v>160459500</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B132" t="n">
-        <v>183.8896736698189</v>
+        <v>185.605746824658</v>
       </c>
       <c r="C132" t="n">
-        <v>189.5666999081706</v>
+        <v>189.2274732756209</v>
       </c>
       <c r="D132" t="n">
-        <v>183.8797019557237</v>
+        <v>185.3164148846483</v>
       </c>
       <c r="E132" t="n">
-        <v>188.1998291015625</v>
+        <v>188.8782653808594</v>
       </c>
       <c r="F132" t="n">
-        <v>160459500</v>
+        <v>133648200</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B133" t="n">
-        <v>185.605746824658</v>
+        <v>190.4047764107204</v>
       </c>
       <c r="C133" t="n">
-        <v>189.2274732756209</v>
+        <v>196.0618438720703</v>
       </c>
       <c r="D133" t="n">
-        <v>185.3164148846483</v>
+        <v>190.3349439656124</v>
       </c>
       <c r="E133" t="n">
-        <v>188.8782653808594</v>
+        <v>196.0618438720703</v>
       </c>
       <c r="F133" t="n">
-        <v>133648200</v>
+        <v>161307000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B134" t="n">
-        <v>190.4047764107204</v>
+        <v>196.0917851116163</v>
       </c>
       <c r="C134" t="n">
-        <v>196.0618438720703</v>
+        <v>199.9429830157183</v>
       </c>
       <c r="D134" t="n">
-        <v>190.3349439656124</v>
+        <v>195.2936216855987</v>
       </c>
       <c r="E134" t="n">
-        <v>196.0618438720703</v>
+        <v>198.4164733886719</v>
       </c>
       <c r="F134" t="n">
-        <v>161307000</v>
+        <v>185338400</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B135" t="n">
-        <v>196.0917851116163</v>
+        <v>196.9797440092329</v>
       </c>
       <c r="C135" t="n">
-        <v>199.9429830157183</v>
+        <v>199.3942384790618</v>
       </c>
       <c r="D135" t="n">
-        <v>195.2936216855987</v>
+        <v>195.3634433694217</v>
       </c>
       <c r="E135" t="n">
-        <v>198.4164733886719</v>
+        <v>197.8976593017578</v>
       </c>
       <c r="F135" t="n">
-        <v>185338400</v>
+        <v>134012900</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B136" t="n">
-        <v>196.9797440092329</v>
+        <v>199.444107632571</v>
       </c>
       <c r="C136" t="n">
-        <v>199.3942384790618</v>
+        <v>201.2400056483541</v>
       </c>
       <c r="D136" t="n">
-        <v>195.3634433694217</v>
+        <v>198.8155547450397</v>
       </c>
       <c r="E136" t="n">
-        <v>197.8976593017578</v>
+        <v>201.2200469970703</v>
       </c>
       <c r="F136" t="n">
-        <v>134012900</v>
+        <v>160324400</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B137" t="n">
-        <v>199.444107632571</v>
+        <v>199.5239239232554</v>
       </c>
       <c r="C137" t="n">
-        <v>201.2400056483541</v>
+        <v>201.7089318732817</v>
       </c>
       <c r="D137" t="n">
-        <v>198.8155547450397</v>
+        <v>197.3888049886708</v>
       </c>
       <c r="E137" t="n">
-        <v>201.2200469970703</v>
+        <v>201.5991821289062</v>
       </c>
       <c r="F137" t="n">
-        <v>160324400</v>
+        <v>119381400</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B138" t="n">
-        <v>199.5239239232554</v>
+        <v>201.6690479582887</v>
       </c>
       <c r="C138" t="n">
-        <v>201.7089318732817</v>
+        <v>202.2876291783034</v>
       </c>
       <c r="D138" t="n">
-        <v>197.3888049886708</v>
+        <v>198.5461810430697</v>
       </c>
       <c r="E138" t="n">
-        <v>201.5991821289062</v>
+        <v>199.4241790771484</v>
       </c>
       <c r="F138" t="n">
-        <v>119381400</v>
+        <v>107945300</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B139" t="n">
-        <v>201.6690479582887</v>
+        <v>200.5316418294082</v>
       </c>
       <c r="C139" t="n">
-        <v>202.2876291783034</v>
+        <v>202.0381927490234</v>
       </c>
       <c r="D139" t="n">
-        <v>198.5461810430697</v>
+        <v>198.546174602744</v>
       </c>
       <c r="E139" t="n">
-        <v>199.4241790771484</v>
+        <v>202.0381927490234</v>
       </c>
       <c r="F139" t="n">
-        <v>107945300</v>
+        <v>107501000</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B140" t="n">
-        <v>200.5316418294082</v>
+        <v>201.9982837593082</v>
       </c>
       <c r="C140" t="n">
-        <v>202.0381927490234</v>
+        <v>203.3651545152774</v>
       </c>
       <c r="D140" t="n">
-        <v>198.546174602744</v>
+        <v>196.7702284327844</v>
       </c>
       <c r="E140" t="n">
-        <v>202.0381927490234</v>
+        <v>199.1847076416016</v>
       </c>
       <c r="F140" t="n">
-        <v>107501000</v>
+        <v>113561800</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B141" t="n">
-        <v>201.9982837593082</v>
+        <v>199.5039827094276</v>
       </c>
       <c r="C141" t="n">
-        <v>203.3651545152774</v>
+        <v>210.468909435165</v>
       </c>
       <c r="D141" t="n">
-        <v>196.7702284327844</v>
+        <v>199.3543156614425</v>
       </c>
       <c r="E141" t="n">
-        <v>199.1847076416016</v>
+        <v>207.7950286865234</v>
       </c>
       <c r="F141" t="n">
-        <v>113561800</v>
+        <v>214134400</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B142" t="n">
-        <v>199.5039827094276</v>
+        <v>209.1718784416434</v>
       </c>
       <c r="C142" t="n">
-        <v>210.468909435165</v>
+        <v>216.335512072091</v>
       </c>
       <c r="D142" t="n">
-        <v>199.3543156614425</v>
+        <v>206.9070662315077</v>
       </c>
       <c r="E142" t="n">
-        <v>207.7950286865234</v>
+        <v>216.1160125732422</v>
       </c>
       <c r="F142" t="n">
-        <v>214134400</v>
+        <v>187172400</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B143" t="n">
-        <v>209.1718784416434</v>
+        <v>209.0122528840405</v>
       </c>
       <c r="C143" t="n">
-        <v>216.335512072091</v>
+        <v>214.2402930542568</v>
       </c>
       <c r="D143" t="n">
-        <v>206.9070662315077</v>
+        <v>207.7251862691963</v>
       </c>
       <c r="E143" t="n">
-        <v>216.1160125732422</v>
+        <v>212.6838531494141</v>
       </c>
       <c r="F143" t="n">
-        <v>187172400</v>
+        <v>180275400</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B144" t="n">
-        <v>209.0122528840405</v>
+        <v>212.2149257168926</v>
       </c>
       <c r="C144" t="n">
-        <v>214.2402930542568</v>
+        <v>212.2348843687743</v>
       </c>
       <c r="D144" t="n">
-        <v>207.7251862691963</v>
+        <v>207.1066069625242</v>
       </c>
       <c r="E144" t="n">
-        <v>212.6838531494141</v>
+        <v>208.7727966308594</v>
       </c>
       <c r="F144" t="n">
-        <v>180275400</v>
+        <v>123711800</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B145" t="n">
-        <v>212.2149257168926</v>
+        <v>209.4512265433391</v>
       </c>
       <c r="C145" t="n">
-        <v>212.2348843687743</v>
+        <v>209.8203930740204</v>
       </c>
       <c r="D145" t="n">
-        <v>207.1066069625242</v>
+        <v>198.2468419328838</v>
       </c>
       <c r="E145" t="n">
-        <v>208.7727966308594</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="F145" t="n">
-        <v>123711800</v>
+        <v>225239200</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B146" t="n">
-        <v>209.4512425942353</v>
+        <v>200.8209846036705</v>
       </c>
       <c r="C146" t="n">
-        <v>209.820409153207</v>
+        <v>202.5370634031337</v>
       </c>
       <c r="D146" t="n">
-        <v>198.2468571251534</v>
+        <v>196.6704677294345</v>
       </c>
       <c r="E146" t="n">
-        <v>199.1148834228516</v>
+        <v>197.9974365234375</v>
       </c>
       <c r="F146" t="n">
-        <v>225239200</v>
+        <v>128647000</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B147" t="n">
-        <v>200.8209691272831</v>
+        <v>199.0450218084295</v>
       </c>
       <c r="C147" t="n">
-        <v>202.5370477944956</v>
+        <v>201.2699318245734</v>
       </c>
       <c r="D147" t="n">
-        <v>196.6704525729091</v>
+        <v>194.2958829090753</v>
       </c>
       <c r="E147" t="n">
-        <v>197.9974212646484</v>
+        <v>198.02734375</v>
       </c>
       <c r="F147" t="n">
-        <v>128647000</v>
+        <v>125368100</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B148" t="n">
-        <v>199.0450218084295</v>
+        <v>198.8454820247872</v>
       </c>
       <c r="C148" t="n">
-        <v>201.2699318245734</v>
+        <v>199.7833407086998</v>
       </c>
       <c r="D148" t="n">
-        <v>194.2958829090753</v>
+        <v>195.5829352820671</v>
       </c>
       <c r="E148" t="n">
-        <v>198.02734375</v>
+        <v>196.0518646240234</v>
       </c>
       <c r="F148" t="n">
-        <v>125368100</v>
+        <v>113406600</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B149" t="n">
-        <v>198.8454820247872</v>
+        <v>199.4341385249406</v>
       </c>
       <c r="C149" t="n">
-        <v>199.7833407086998</v>
+        <v>207.7950323152332</v>
       </c>
       <c r="D149" t="n">
-        <v>195.5829352820671</v>
+        <v>198.1570588579161</v>
       </c>
       <c r="E149" t="n">
-        <v>196.0518646240234</v>
+        <v>207.3560333251953</v>
       </c>
       <c r="F149" t="n">
-        <v>113406600</v>
+        <v>188362800</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B150" t="n">
-        <v>199.4341385249406</v>
+        <v>207.8648724722903</v>
       </c>
       <c r="C150" t="n">
-        <v>207.7950323152332</v>
+        <v>213.7115092245668</v>
       </c>
       <c r="D150" t="n">
-        <v>198.1570588579161</v>
+        <v>206.0290722858257</v>
       </c>
       <c r="E150" t="n">
-        <v>207.3560333251953</v>
+        <v>211.0176696777344</v>
       </c>
       <c r="F150" t="n">
-        <v>188362800</v>
+        <v>168307900</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B151" t="n">
-        <v>207.8648724722903</v>
+        <v>212.5441790763045</v>
       </c>
       <c r="C151" t="n">
-        <v>213.7115092245668</v>
+        <v>217.3033052467507</v>
       </c>
       <c r="D151" t="n">
-        <v>206.0290722858257</v>
+        <v>212.4044989584125</v>
       </c>
       <c r="E151" t="n">
-        <v>211.0176696777344</v>
+        <v>214.709228515625</v>
       </c>
       <c r="F151" t="n">
-        <v>168307900</v>
+        <v>136421400</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B152" t="n">
-        <v>212.5441790763045</v>
+        <v>213.5518657378577</v>
       </c>
       <c r="C152" t="n">
-        <v>217.3033052467507</v>
+        <v>221.7930381906342</v>
       </c>
       <c r="D152" t="n">
-        <v>212.4044989584125</v>
+        <v>213.402213909002</v>
       </c>
       <c r="E152" t="n">
-        <v>214.709228515625</v>
+        <v>218.9395599365234</v>
       </c>
       <c r="F152" t="n">
-        <v>136421400</v>
+        <v>160685800</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B153" t="n">
-        <v>213.5518657378577</v>
+        <v>218.0515943496244</v>
       </c>
       <c r="C153" t="n">
-        <v>221.7930381906342</v>
+        <v>223.239732575863</v>
       </c>
       <c r="D153" t="n">
-        <v>213.402213909002</v>
+        <v>214.4298677829735</v>
       </c>
       <c r="E153" t="n">
-        <v>218.9395599365234</v>
+        <v>220.2765045166016</v>
       </c>
       <c r="F153" t="n">
-        <v>160685800</v>
+        <v>159176600</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B154" t="n">
-        <v>218.0515943496244</v>
+        <v>224.4170305354026</v>
       </c>
       <c r="C154" t="n">
-        <v>223.239732575863</v>
+        <v>227.3203978139454</v>
       </c>
       <c r="D154" t="n">
-        <v>214.4298677829735</v>
+        <v>221.0647077692387</v>
       </c>
       <c r="E154" t="n">
-        <v>220.2765045166016</v>
+        <v>225.3149871826172</v>
       </c>
       <c r="F154" t="n">
-        <v>159176600</v>
+        <v>150405400</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B155" t="n">
-        <v>224.4170305354026</v>
+        <v>229.3258255277811</v>
       </c>
       <c r="C155" t="n">
-        <v>227.3203978139454</v>
+        <v>236.0005559723521</v>
       </c>
       <c r="D155" t="n">
-        <v>221.0647077692387</v>
+        <v>228.7770767762568</v>
       </c>
       <c r="E155" t="n">
-        <v>225.3149871826172</v>
+        <v>235.202392578125</v>
       </c>
       <c r="F155" t="n">
-        <v>150405400</v>
+        <v>180782900</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B156" t="n">
-        <v>229.3258255277811</v>
+        <v>229.2360138852663</v>
       </c>
       <c r="C156" t="n">
-        <v>236.0005559723521</v>
+        <v>230.9720511978</v>
       </c>
       <c r="D156" t="n">
-        <v>228.7770767762568</v>
+        <v>223.7286135177626</v>
       </c>
       <c r="E156" t="n">
-        <v>235.202392578125</v>
+        <v>224.80615234375</v>
       </c>
       <c r="F156" t="n">
-        <v>180782900</v>
+        <v>180977600</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B157" t="n">
-        <v>229.2360294447337</v>
+        <v>229.345773483712</v>
       </c>
       <c r="C157" t="n">
-        <v>230.9720668751014</v>
+        <v>229.4754818886306</v>
       </c>
       <c r="D157" t="n">
-        <v>223.7286287034134</v>
+        <v>217.8719993892805</v>
       </c>
       <c r="E157" t="n">
-        <v>224.8061676025391</v>
+        <v>221.8130035400391</v>
       </c>
       <c r="F157" t="n">
-        <v>180977600</v>
+        <v>146280900</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B158" t="n">
-        <v>229.345773483712</v>
+        <v>219.1191400841904</v>
       </c>
       <c r="C158" t="n">
-        <v>229.4754818886306</v>
+        <v>223.9680572056967</v>
       </c>
       <c r="D158" t="n">
-        <v>217.8719993892805</v>
+        <v>217.4130483552105</v>
       </c>
       <c r="E158" t="n">
-        <v>221.8130035400391</v>
+        <v>220.1068878173828</v>
       </c>
       <c r="F158" t="n">
-        <v>146280900</v>
+        <v>140948200</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B159" t="n">
-        <v>219.1191400841904</v>
+        <v>222.6710257508039</v>
       </c>
       <c r="C159" t="n">
-        <v>223.9680572056967</v>
+        <v>225.6143103895453</v>
       </c>
       <c r="D159" t="n">
-        <v>217.4130483552105</v>
+        <v>219.9971448577806</v>
       </c>
       <c r="E159" t="n">
-        <v>220.1068878173828</v>
+        <v>222.9603729248047</v>
       </c>
       <c r="F159" t="n">
-        <v>140948200</v>
+        <v>184201600</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B160" t="n">
-        <v>222.6710257508039</v>
+        <v>221.7830583738447</v>
       </c>
       <c r="C160" t="n">
-        <v>225.6143103895453</v>
+        <v>226.8814055684356</v>
       </c>
       <c r="D160" t="n">
-        <v>219.9971448577806</v>
+        <v>217.4330007955402</v>
       </c>
       <c r="E160" t="n">
-        <v>222.9603729248047</v>
+        <v>219.0093994140625</v>
       </c>
       <c r="F160" t="n">
-        <v>184201600</v>
+        <v>203381800</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B161" t="n">
-        <v>221.7830583738447</v>
+        <v>220.3962175709585</v>
       </c>
       <c r="C161" t="n">
-        <v>226.8814055684356</v>
+        <v>220.5059673180016</v>
       </c>
       <c r="D161" t="n">
-        <v>217.4330007955402</v>
+        <v>214.3101381389001</v>
       </c>
       <c r="E161" t="n">
-        <v>219.0093994140625</v>
+        <v>214.8389282226562</v>
       </c>
       <c r="F161" t="n">
-        <v>203381800</v>
+        <v>169275700</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B162" t="n">
-        <v>220.3962175709585</v>
+        <v>216.0461718127993</v>
       </c>
       <c r="C162" t="n">
-        <v>220.5059673180016</v>
+        <v>217.6824311685512</v>
       </c>
       <c r="D162" t="n">
-        <v>214.3101381389001</v>
+        <v>211.5165320236786</v>
       </c>
       <c r="E162" t="n">
-        <v>214.8389282226562</v>
+        <v>214.3700103759766</v>
       </c>
       <c r="F162" t="n">
-        <v>169275700</v>
+        <v>187202600</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B163" t="n">
-        <v>216.0461718127993</v>
+        <v>213.6316806617713</v>
       </c>
       <c r="C163" t="n">
-        <v>217.6824311685512</v>
+        <v>213.6616110269177</v>
       </c>
       <c r="D163" t="n">
-        <v>211.5165320236786</v>
+        <v>208.3038625298546</v>
       </c>
       <c r="E163" t="n">
-        <v>214.3700103759766</v>
+        <v>212.1151580810547</v>
       </c>
       <c r="F163" t="n">
-        <v>187202600</v>
+        <v>167601200</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B164" t="n">
-        <v>213.6316806617713</v>
+        <v>210.7981702457166</v>
       </c>
       <c r="C164" t="n">
-        <v>213.6616110269177</v>
+        <v>215.0285063161196</v>
       </c>
       <c r="D164" t="n">
-        <v>208.3038625298546</v>
+        <v>210.738309512832</v>
       </c>
       <c r="E164" t="n">
-        <v>212.1151580810547</v>
+        <v>213.7613983154297</v>
       </c>
       <c r="F164" t="n">
-        <v>167601200</v>
+        <v>143996000</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B165" t="n">
-        <v>210.7981551984497</v>
+        <v>214.0906505321041</v>
       </c>
       <c r="C165" t="n">
-        <v>215.0284909668814</v>
+        <v>217.3631692496548</v>
       </c>
       <c r="D165" t="n">
-        <v>210.7382944698381</v>
+        <v>210.6485213277038</v>
       </c>
       <c r="E165" t="n">
-        <v>213.7613830566406</v>
+        <v>210.6584930419922</v>
       </c>
       <c r="F165" t="n">
-        <v>143996000</v>
+        <v>289410600</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B166" t="n">
-        <v>214.0906505321041</v>
+        <v>215.2380189209027</v>
       </c>
       <c r="C166" t="n">
-        <v>217.3631692496548</v>
+        <v>224.3571743491113</v>
       </c>
       <c r="D166" t="n">
-        <v>210.6485213277038</v>
+        <v>215.2080885544549</v>
       </c>
       <c r="E166" t="n">
-        <v>210.6584930419922</v>
+        <v>223.8483428955078</v>
       </c>
       <c r="F166" t="n">
-        <v>289410600</v>
+        <v>212850700</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B167" t="n">
-        <v>215.2380189209027</v>
+        <v>226.6618858382332</v>
       </c>
       <c r="C167" t="n">
-        <v>224.3571743491113</v>
+        <v>231.7502608645459</v>
       </c>
       <c r="D167" t="n">
-        <v>215.2080885544549</v>
+        <v>220.8451951370975</v>
       </c>
       <c r="E167" t="n">
-        <v>223.8483428955078</v>
+        <v>222.3118438720703</v>
       </c>
       <c r="F167" t="n">
-        <v>212850700</v>
+        <v>193362900</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B168" t="n">
-        <v>226.6618858382332</v>
+        <v>221.2143597561905</v>
       </c>
       <c r="C168" t="n">
-        <v>231.7502608645459</v>
+        <v>222.3118572511273</v>
       </c>
       <c r="D168" t="n">
-        <v>220.8451951370975</v>
+        <v>214.0207957553572</v>
       </c>
       <c r="E168" t="n">
-        <v>222.3118438720703</v>
+        <v>214.26025390625</v>
       </c>
       <c r="F168" t="n">
-        <v>193362900</v>
+        <v>160907000</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,25 +4811,25 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B169" t="n">
-        <v>221.2143597561905</v>
+        <v>213.6709127939037</v>
       </c>
       <c r="C169" t="n">
-        <v>222.3118572511273</v>
+        <v>221.3523199881091</v>
       </c>
       <c r="D169" t="n">
-        <v>214.0207957553572</v>
+        <v>210.73419644349</v>
       </c>
       <c r="E169" t="n">
-        <v>214.26025390625</v>
+        <v>218.4156036376953</v>
       </c>
       <c r="F169" t="n">
-        <v>160907000</v>
+        <v>169022200</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -4837,25 +4837,25 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B170" t="n">
-        <v>213.6709127939037</v>
+        <v>214.2902104723603</v>
       </c>
       <c r="C170" t="n">
-        <v>221.3523199881091</v>
+        <v>214.6298267834636</v>
       </c>
       <c r="D170" t="n">
-        <v>210.73419644349</v>
+        <v>204.101614447126</v>
       </c>
       <c r="E170" t="n">
-        <v>218.4156036376953</v>
+        <v>204.8707580566406</v>
       </c>
       <c r="F170" t="n">
-        <v>169022200</v>
+        <v>219655500</v>
       </c>
       <c r="G170" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B171" t="n">
-        <v>214.2902104723603</v>
+        <v>209.9450713288228</v>
       </c>
       <c r="C171" t="n">
-        <v>214.6298267834636</v>
+        <v>210.2347557268212</v>
       </c>
       <c r="D171" t="n">
-        <v>204.101614447126</v>
+        <v>205.7697506938822</v>
       </c>
       <c r="E171" t="n">
-        <v>204.8707580566406</v>
+        <v>208.4067993164062</v>
       </c>
       <c r="F171" t="n">
-        <v>219655500</v>
+        <v>138372800</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B172" t="n">
-        <v>209.9450713288228</v>
+        <v>210.3845825512031</v>
       </c>
       <c r="C172" t="n">
-        <v>210.2347557268212</v>
+        <v>211.1637095162451</v>
       </c>
       <c r="D172" t="n">
-        <v>205.7697506938822</v>
+        <v>199.1171915656509</v>
       </c>
       <c r="E172" t="n">
-        <v>208.4067993164062</v>
+        <v>207.9573059082031</v>
       </c>
       <c r="F172" t="n">
-        <v>138372800</v>
+        <v>180962500</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B173" t="n">
-        <v>210.3845825512031</v>
+        <v>204.2014963256503</v>
       </c>
       <c r="C173" t="n">
-        <v>211.1637095162451</v>
+        <v>206.9883864105018</v>
       </c>
       <c r="D173" t="n">
-        <v>199.1171915656509</v>
+        <v>199.696542748819</v>
       </c>
       <c r="E173" t="n">
-        <v>207.9573059082031</v>
+        <v>200.1959838867188</v>
       </c>
       <c r="F173" t="n">
-        <v>180962500</v>
+        <v>161746600</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B174" t="n">
-        <v>204.2014963256503</v>
+        <v>201.2647947500858</v>
       </c>
       <c r="C174" t="n">
-        <v>206.9883864105018</v>
+        <v>205.4301320010667</v>
       </c>
       <c r="D174" t="n">
-        <v>199.696542748819</v>
+        <v>199.3169621236104</v>
       </c>
       <c r="E174" t="n">
-        <v>200.1959838867188</v>
+        <v>204.6410064697266</v>
       </c>
       <c r="F174" t="n">
-        <v>161746600</v>
+        <v>158643200</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B175" t="n">
-        <v>201.2647947500858</v>
+        <v>204.6310298517525</v>
       </c>
       <c r="C175" t="n">
-        <v>205.4301320010667</v>
+        <v>206.8385664547524</v>
       </c>
       <c r="D175" t="n">
-        <v>199.3169621236104</v>
+        <v>203.2126188059985</v>
       </c>
       <c r="E175" t="n">
-        <v>204.6410064697266</v>
+        <v>204.9606628417969</v>
       </c>
       <c r="F175" t="n">
-        <v>158643200</v>
+        <v>112001800</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B176" t="n">
-        <v>204.6310298517525</v>
+        <v>208.6864864049894</v>
       </c>
       <c r="C176" t="n">
-        <v>206.8385664547524</v>
+        <v>212.4722588232193</v>
       </c>
       <c r="D176" t="n">
-        <v>203.2126188059985</v>
+        <v>208.1071328472061</v>
       </c>
       <c r="E176" t="n">
-        <v>204.9606628417969</v>
+        <v>212.2125396728516</v>
       </c>
       <c r="F176" t="n">
-        <v>112001800</v>
+        <v>149936700</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B177" t="n">
-        <v>208.6864864049894</v>
+        <v>210.9439520928381</v>
       </c>
       <c r="C177" t="n">
-        <v>212.4722588232193</v>
+        <v>211.2536184019877</v>
       </c>
       <c r="D177" t="n">
-        <v>208.1071328472061</v>
+        <v>207.0583006421773</v>
       </c>
       <c r="E177" t="n">
-        <v>212.2125396728516</v>
+        <v>207.1781768798828</v>
       </c>
       <c r="F177" t="n">
-        <v>149936700</v>
+        <v>125694100</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B178" t="n">
-        <v>210.9439520928381</v>
+        <v>208.2969174543329</v>
       </c>
       <c r="C178" t="n">
-        <v>211.2536184019877</v>
+        <v>208.9761653200819</v>
       </c>
       <c r="D178" t="n">
-        <v>207.0583006421773</v>
+        <v>202.8530121596522</v>
       </c>
       <c r="E178" t="n">
-        <v>207.1781768798828</v>
+        <v>204.4212493896484</v>
       </c>
       <c r="F178" t="n">
-        <v>125694100</v>
+        <v>128363500</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B179" t="n">
-        <v>208.2969174543329</v>
+        <v>207.0982684229139</v>
       </c>
       <c r="C179" t="n">
-        <v>208.9761653200819</v>
+        <v>211.1537281092123</v>
       </c>
       <c r="D179" t="n">
-        <v>202.8530121596522</v>
+        <v>206.2691942875683</v>
       </c>
       <c r="E179" t="n">
-        <v>204.4212493896484</v>
+        <v>210.4545135498047</v>
       </c>
       <c r="F179" t="n">
-        <v>128363500</v>
+        <v>241272000</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B180" t="n">
-        <v>207.0982684229139</v>
+        <v>211.2036686200953</v>
       </c>
       <c r="C180" t="n">
-        <v>211.1537281092123</v>
+        <v>213.7508214450341</v>
       </c>
       <c r="D180" t="n">
-        <v>206.2691942875683</v>
+        <v>207.4878253737282</v>
       </c>
       <c r="E180" t="n">
-        <v>210.4545135498047</v>
+        <v>208.4167785644531</v>
       </c>
       <c r="F180" t="n">
-        <v>241272000</v>
+        <v>122041400</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B181" t="n">
-        <v>211.2036686200953</v>
+        <v>201.9440304014853</v>
       </c>
       <c r="C181" t="n">
-        <v>213.7508214450341</v>
+        <v>203.5422481594977</v>
       </c>
       <c r="D181" t="n">
-        <v>207.4878253737282</v>
+        <v>199.77645766483</v>
       </c>
       <c r="E181" t="n">
-        <v>208.4167785644531</v>
+        <v>199.81640625</v>
       </c>
       <c r="F181" t="n">
-        <v>122041400</v>
+        <v>153496200</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B182" t="n">
-        <v>201.9440304014853</v>
+        <v>199.8963159019567</v>
       </c>
       <c r="C182" t="n">
-        <v>203.5422481594977</v>
+        <v>201.4445864758279</v>
       </c>
       <c r="D182" t="n">
-        <v>199.77645766483</v>
+        <v>196.360279356477</v>
       </c>
       <c r="E182" t="n">
-        <v>199.81640625</v>
+        <v>198.7775726318359</v>
       </c>
       <c r="F182" t="n">
-        <v>153496200</v>
+        <v>151810700</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B183" t="n">
-        <v>199.8963159019567</v>
+        <v>199.8563704571445</v>
       </c>
       <c r="C183" t="n">
-        <v>201.4445864758279</v>
+        <v>200.5755669254449</v>
       </c>
       <c r="D183" t="n">
-        <v>196.360279356477</v>
+        <v>191.9152592982058</v>
       </c>
       <c r="E183" t="n">
-        <v>198.7775726318359</v>
+        <v>195.5212249755859</v>
       </c>
       <c r="F183" t="n">
-        <v>151810700</v>
+        <v>149550000</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B184" t="n">
-        <v>199.8563704571445</v>
+        <v>192.9041409641119</v>
       </c>
       <c r="C184" t="n">
-        <v>200.5755669254449</v>
+        <v>195.331432829306</v>
       </c>
       <c r="D184" t="n">
-        <v>191.9152592982058</v>
+        <v>191.0062707295152</v>
       </c>
       <c r="E184" t="n">
-        <v>195.5212249755859</v>
+        <v>192.3148040771484</v>
       </c>
       <c r="F184" t="n">
-        <v>149550000</v>
+        <v>179304100</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B185" t="n">
-        <v>192.9041409641119</v>
+        <v>193.6333319429392</v>
       </c>
       <c r="C185" t="n">
-        <v>195.331432829306</v>
+        <v>195.9607141929515</v>
       </c>
       <c r="D185" t="n">
-        <v>191.0062707295152</v>
+        <v>189.5878557469149</v>
       </c>
       <c r="E185" t="n">
-        <v>192.3148040771484</v>
+        <v>194.7520751953125</v>
       </c>
       <c r="F185" t="n">
-        <v>179304100</v>
+        <v>148835700</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B186" t="n">
-        <v>193.6333319429392</v>
+        <v>197.0195429632178</v>
       </c>
       <c r="C186" t="n">
-        <v>195.9607141929515</v>
+        <v>200.4057532237791</v>
       </c>
       <c r="D186" t="n">
-        <v>189.5878557469149</v>
+        <v>194.8919188665145</v>
       </c>
       <c r="E186" t="n">
-        <v>194.7520751953125</v>
+        <v>199.8663482666016</v>
       </c>
       <c r="F186" t="n">
-        <v>148835700</v>
+        <v>166476700</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B187" t="n">
-        <v>197.0195429632178</v>
+        <v>195.9806989625188</v>
       </c>
       <c r="C187" t="n">
-        <v>200.4057532237791</v>
+        <v>199.626628404907</v>
       </c>
       <c r="D187" t="n">
-        <v>194.8919188665145</v>
+        <v>193.2337727110923</v>
       </c>
       <c r="E187" t="n">
-        <v>199.8663482666016</v>
+        <v>197.3591613769531</v>
       </c>
       <c r="F187" t="n">
-        <v>166476700</v>
+        <v>146147600</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B188" t="n">
-        <v>195.9806989625188</v>
+        <v>196.9196593659626</v>
       </c>
       <c r="C188" t="n">
-        <v>199.626628404907</v>
+        <v>199.8363939026278</v>
       </c>
       <c r="D188" t="n">
-        <v>193.2337727110923</v>
+        <v>192.1350197738411</v>
       </c>
       <c r="E188" t="n">
-        <v>197.3591613769531</v>
+        <v>194.6122436523438</v>
       </c>
       <c r="F188" t="n">
-        <v>146147600</v>
+        <v>142068700</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B189" t="n">
-        <v>196.9196593659626</v>
+        <v>194.202694284663</v>
       </c>
       <c r="C189" t="n">
-        <v>199.8363939026278</v>
+        <v>197.3292007505161</v>
       </c>
       <c r="D189" t="n">
-        <v>192.1350197738411</v>
+        <v>193.7731822131383</v>
       </c>
       <c r="E189" t="n">
-        <v>194.6122436523438</v>
+        <v>195.3314361572266</v>
       </c>
       <c r="F189" t="n">
-        <v>142068700</v>
+        <v>108999000</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B190" t="n">
-        <v>194.202694284663</v>
+        <v>192.1549837798622</v>
       </c>
       <c r="C190" t="n">
-        <v>197.3292007505161</v>
+        <v>198.1882414262674</v>
       </c>
       <c r="D190" t="n">
-        <v>193.7731822131383</v>
+        <v>190.9263628146717</v>
       </c>
       <c r="E190" t="n">
-        <v>195.3314361572266</v>
+        <v>196.7098846435547</v>
       </c>
       <c r="F190" t="n">
-        <v>108999000</v>
+        <v>124154600</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B191" t="n">
-        <v>192.1549837798622</v>
+        <v>194.9618356993413</v>
       </c>
       <c r="C191" t="n">
-        <v>198.1882414262674</v>
+        <v>204.9306918075912</v>
       </c>
       <c r="D191" t="n">
-        <v>190.9263628146717</v>
+        <v>194.841974703339</v>
       </c>
       <c r="E191" t="n">
-        <v>196.7098846435547</v>
+        <v>203.891845703125</v>
       </c>
       <c r="F191" t="n">
-        <v>124154600</v>
+        <v>147419100</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B192" t="n">
-        <v>194.9618356993413</v>
+        <v>204.2314748595287</v>
       </c>
       <c r="C192" t="n">
-        <v>204.9306918075912</v>
+        <v>204.3613191897594</v>
       </c>
       <c r="D192" t="n">
-        <v>194.841974703339</v>
+        <v>198.7376223952696</v>
       </c>
       <c r="E192" t="n">
-        <v>203.891845703125</v>
+        <v>202.5533447265625</v>
       </c>
       <c r="F192" t="n">
-        <v>147419100</v>
+        <v>132037400</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B193" t="n">
-        <v>204.2314748595287</v>
+        <v>201.7742207048944</v>
       </c>
       <c r="C193" t="n">
-        <v>204.3613191897594</v>
+        <v>210.7641612313501</v>
       </c>
       <c r="D193" t="n">
-        <v>198.7376223952696</v>
+        <v>201.6943082934289</v>
       </c>
       <c r="E193" t="n">
-        <v>202.5533447265625</v>
+        <v>210.7242126464844</v>
       </c>
       <c r="F193" t="n">
-        <v>132037400</v>
+        <v>148421000</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B194" t="n">
-        <v>201.7742207048944</v>
+        <v>208.3069001369788</v>
       </c>
       <c r="C194" t="n">
-        <v>210.7641612313501</v>
+        <v>210.3346451505122</v>
       </c>
       <c r="D194" t="n">
-        <v>201.6943082934289</v>
+        <v>202.7730991138312</v>
       </c>
       <c r="E194" t="n">
-        <v>210.7242126464844</v>
+        <v>203.3025054931641</v>
       </c>
       <c r="F194" t="n">
-        <v>148421000</v>
+        <v>121411000</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B195" t="n">
-        <v>208.3069001369788</v>
+        <v>207.9672957533915</v>
       </c>
       <c r="C195" t="n">
-        <v>210.3346451505122</v>
+        <v>212.3124399374416</v>
       </c>
       <c r="D195" t="n">
-        <v>202.7730991138312</v>
+        <v>203.5722196467825</v>
       </c>
       <c r="E195" t="n">
-        <v>203.3025054931641</v>
+        <v>211.5632781982422</v>
       </c>
       <c r="F195" t="n">
-        <v>121411000</v>
+        <v>124379600</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B196" t="n">
-        <v>207.9672957533915</v>
+        <v>211.7230919717581</v>
       </c>
       <c r="C196" t="n">
-        <v>212.3124399374416</v>
+        <v>213.5710150202495</v>
       </c>
       <c r="D196" t="n">
-        <v>203.5722196467825</v>
+        <v>205.8096955397309</v>
       </c>
       <c r="E196" t="n">
-        <v>211.5632781982422</v>
+        <v>212.2624816894531</v>
       </c>
       <c r="F196" t="n">
-        <v>124379600</v>
+        <v>124797200</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B197" t="n">
-        <v>211.7230919717581</v>
+        <v>209.9350906043833</v>
       </c>
       <c r="C197" t="n">
-        <v>213.5710150202495</v>
+        <v>210.8440771529852</v>
       </c>
       <c r="D197" t="n">
-        <v>205.8096955397309</v>
+        <v>205.6199270055466</v>
       </c>
       <c r="E197" t="n">
-        <v>212.2624816894531</v>
+        <v>207.1681823730469</v>
       </c>
       <c r="F197" t="n">
-        <v>124797200</v>
+        <v>122986100</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B198" t="n">
-        <v>209.9350906043833</v>
+        <v>202.4135048295048</v>
       </c>
       <c r="C198" t="n">
-        <v>210.8440771529852</v>
+        <v>206.4190172896336</v>
       </c>
       <c r="D198" t="n">
-        <v>205.6199270055466</v>
+        <v>197.7487264058434</v>
       </c>
       <c r="E198" t="n">
-        <v>207.1681823730469</v>
+        <v>202.5833129882812</v>
       </c>
       <c r="F198" t="n">
-        <v>122986100</v>
+        <v>144281900</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B199" t="n">
-        <v>202.4135048295048</v>
+        <v>205.639896943356</v>
       </c>
       <c r="C199" t="n">
-        <v>206.4190172896336</v>
+        <v>207.5078172334397</v>
       </c>
       <c r="D199" t="n">
-        <v>197.7487264058434</v>
+        <v>202.0539130969454</v>
       </c>
       <c r="E199" t="n">
-        <v>202.5833129882812</v>
+        <v>203.0527954101562</v>
       </c>
       <c r="F199" t="n">
-        <v>144281900</v>
+        <v>88701500</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B200" t="n">
-        <v>205.639896943356</v>
+        <v>207.308024406286</v>
       </c>
       <c r="C200" t="n">
-        <v>207.5078172334397</v>
+        <v>208.4167843613107</v>
       </c>
       <c r="D200" t="n">
-        <v>202.0539130969454</v>
+        <v>203.7819711309363</v>
       </c>
       <c r="E200" t="n">
-        <v>203.0527954101562</v>
+        <v>207.0583038330078</v>
       </c>
       <c r="F200" t="n">
-        <v>88701500</v>
+        <v>108685600</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B201" t="n">
-        <v>207.308024406286</v>
+        <v>205.579968274895</v>
       </c>
       <c r="C201" t="n">
-        <v>208.4167843613107</v>
+        <v>214.1503804276117</v>
       </c>
       <c r="D201" t="n">
-        <v>203.7819711309363</v>
+        <v>204.7209288682105</v>
       </c>
       <c r="E201" t="n">
-        <v>207.0583038330078</v>
+        <v>211.8229827880859</v>
       </c>
       <c r="F201" t="n">
-        <v>108685600</v>
+        <v>137645600</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B202" t="n">
-        <v>205.579968274895</v>
+        <v>209.2258868865651</v>
       </c>
       <c r="C202" t="n">
-        <v>214.1503804276117</v>
+        <v>210.6342993029147</v>
       </c>
       <c r="D202" t="n">
-        <v>204.7209288682105</v>
+        <v>205.7297989431358</v>
       </c>
       <c r="E202" t="n">
-        <v>211.8229827880859</v>
+        <v>208.5266571044922</v>
       </c>
       <c r="F202" t="n">
-        <v>137645600</v>
+        <v>110505300</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B203" t="n">
-        <v>209.2258868865651</v>
+        <v>207.2181292349697</v>
       </c>
       <c r="C203" t="n">
-        <v>210.6342993029147</v>
+        <v>211.6731509810223</v>
       </c>
       <c r="D203" t="n">
-        <v>205.7297989431358</v>
+        <v>204.5810805834776</v>
       </c>
       <c r="E203" t="n">
-        <v>208.5266571044922</v>
+        <v>206.6088104248047</v>
       </c>
       <c r="F203" t="n">
-        <v>110505300</v>
+        <v>114836800</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B204" t="n">
-        <v>207.2181292349697</v>
+        <v>207.9672962732577</v>
       </c>
       <c r="C204" t="n">
-        <v>211.6731509810223</v>
+        <v>208.5166845983908</v>
       </c>
       <c r="D204" t="n">
-        <v>204.5810805834776</v>
+        <v>195.2215633388429</v>
       </c>
       <c r="E204" t="n">
-        <v>206.6088104248047</v>
+        <v>196.2903594970703</v>
       </c>
       <c r="F204" t="n">
-        <v>114836800</v>
+        <v>154353700</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B205" t="n">
-        <v>207.9672962732577</v>
+        <v>194.782047001347</v>
       </c>
       <c r="C205" t="n">
-        <v>208.5166845983908</v>
+        <v>198.4779084345641</v>
       </c>
       <c r="D205" t="n">
-        <v>195.2215633388429</v>
+        <v>192.5245785077403</v>
       </c>
       <c r="E205" t="n">
-        <v>196.2903594970703</v>
+        <v>196.789794921875</v>
       </c>
       <c r="F205" t="n">
-        <v>154353700</v>
+        <v>134111500</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B206" t="n">
-        <v>194.782047001347</v>
+        <v>195.6311069684468</v>
       </c>
       <c r="C206" t="n">
-        <v>198.4779084345641</v>
+        <v>196.8497446088402</v>
       </c>
       <c r="D206" t="n">
-        <v>192.5245785077403</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="E206" t="n">
-        <v>196.789794921875</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="F206" t="n">
-        <v>134111500</v>
+        <v>147680800</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B207" t="n">
-        <v>195.6311069684468</v>
+        <v>193.2337718176948</v>
       </c>
       <c r="C207" t="n">
-        <v>196.8497446088402</v>
+        <v>197.0295274868271</v>
       </c>
       <c r="D207" t="n">
-        <v>189.7976226806641</v>
+        <v>191.3059363552755</v>
       </c>
       <c r="E207" t="n">
-        <v>189.7976226806641</v>
+        <v>194.8219909667969</v>
       </c>
       <c r="F207" t="n">
-        <v>147680800</v>
+        <v>129010200</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B208" t="n">
-        <v>193.2337718176948</v>
+        <v>198.2182038580375</v>
       </c>
       <c r="C208" t="n">
-        <v>197.0295274868271</v>
+        <v>201.7742223680242</v>
       </c>
       <c r="D208" t="n">
-        <v>191.3059363552755</v>
+        <v>194.7320991825756</v>
       </c>
       <c r="E208" t="n">
-        <v>194.8219909667969</v>
+        <v>200.5256195068359</v>
       </c>
       <c r="F208" t="n">
-        <v>129010200</v>
+        <v>139961200</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B209" t="n">
-        <v>198.2182038580375</v>
+        <v>197.4690486270115</v>
       </c>
       <c r="C209" t="n">
-        <v>201.7742223680242</v>
+        <v>208.506701330784</v>
       </c>
       <c r="D209" t="n">
-        <v>194.7320991825756</v>
+        <v>196.6299911347511</v>
       </c>
       <c r="E209" t="n">
-        <v>200.5256195068359</v>
+        <v>206.4090423583984</v>
       </c>
       <c r="F209" t="n">
-        <v>139961200</v>
+        <v>128406900</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B210" t="n">
-        <v>197.4690486270115</v>
+        <v>211.0638257011038</v>
       </c>
       <c r="C210" t="n">
-        <v>208.506701330784</v>
+        <v>212.8218530009649</v>
       </c>
       <c r="D210" t="n">
-        <v>196.6299911347511</v>
+        <v>208.8163406042335</v>
       </c>
       <c r="E210" t="n">
-        <v>206.4090423583984</v>
+        <v>211.7031097412109</v>
       </c>
       <c r="F210" t="n">
-        <v>128406900</v>
+        <v>134922000</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B211" t="n">
-        <v>211.0638257011038</v>
+        <v>216.6176127852948</v>
       </c>
       <c r="C211" t="n">
-        <v>212.8218530009649</v>
+        <v>221.9716224388697</v>
       </c>
       <c r="D211" t="n">
-        <v>208.8163406042335</v>
+        <v>216.1581202281489</v>
       </c>
       <c r="E211" t="n">
-        <v>211.7031097412109</v>
+        <v>218.9749755859375</v>
       </c>
       <c r="F211" t="n">
-        <v>134922000</v>
+        <v>158187400</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B212" t="n">
-        <v>216.6176127852948</v>
+        <v>221.2823935806188</v>
       </c>
       <c r="C212" t="n">
-        <v>221.9716224388697</v>
+        <v>223.3800524967045</v>
       </c>
       <c r="D212" t="n">
-        <v>216.1581202281489</v>
+        <v>216.7574580038405</v>
       </c>
       <c r="E212" t="n">
-        <v>218.9749755859375</v>
+        <v>218.7452392578125</v>
       </c>
       <c r="F212" t="n">
-        <v>158187400</v>
+        <v>113940600</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B213" t="n">
-        <v>221.2823935806188</v>
+        <v>221.2923777041913</v>
       </c>
       <c r="C213" t="n">
-        <v>223.3800524967045</v>
+        <v>224.5087799247126</v>
       </c>
       <c r="D213" t="n">
-        <v>216.7574580038405</v>
+        <v>220.4133716458871</v>
       </c>
       <c r="E213" t="n">
-        <v>218.7452392578125</v>
+        <v>223.7096862792969</v>
       </c>
       <c r="F213" t="n">
-        <v>113940600</v>
+        <v>105669400</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B214" t="n">
-        <v>221.2923777041913</v>
+        <v>223.1502910726907</v>
       </c>
       <c r="C214" t="n">
-        <v>224.5087799247126</v>
+        <v>223.8894694330602</v>
       </c>
       <c r="D214" t="n">
-        <v>220.4133716458871</v>
+        <v>216.5277120448001</v>
       </c>
       <c r="E214" t="n">
-        <v>223.7096862792969</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="F214" t="n">
-        <v>105669400</v>
+        <v>115846600</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B215" t="n">
-        <v>223.1502910726907</v>
+        <v>221.9216754142795</v>
       </c>
       <c r="C215" t="n">
-        <v>223.8894694330602</v>
+        <v>221.9516406634887</v>
       </c>
       <c r="D215" t="n">
-        <v>216.5277120448001</v>
+        <v>215.9583469538982</v>
       </c>
       <c r="E215" t="n">
-        <v>217.3068389892578</v>
+        <v>217.2568969726562</v>
       </c>
       <c r="F215" t="n">
-        <v>115846600</v>
+        <v>101273100</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B216" t="n">
-        <v>221.9216754142795</v>
+        <v>220.7929293559802</v>
       </c>
       <c r="C216" t="n">
-        <v>221.9516406634887</v>
+        <v>224.848404158734</v>
       </c>
       <c r="D216" t="n">
-        <v>215.9583469538982</v>
+        <v>219.9538719106106</v>
       </c>
       <c r="E216" t="n">
-        <v>217.2568969726562</v>
+        <v>223.8395233154297</v>
       </c>
       <c r="F216" t="n">
-        <v>101273100</v>
+        <v>108783600</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B217" t="n">
-        <v>220.7929293559802</v>
+        <v>224.8084500146858</v>
       </c>
       <c r="C217" t="n">
-        <v>224.848404158734</v>
+        <v>226.9760227961096</v>
       </c>
       <c r="D217" t="n">
-        <v>219.9538719106106</v>
+        <v>223.4599680426375</v>
       </c>
       <c r="E217" t="n">
-        <v>223.8395233154297</v>
+        <v>225.0481872558594</v>
       </c>
       <c r="F217" t="n">
-        <v>108783600</v>
+        <v>98867200</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B218" t="n">
-        <v>224.8084500146858</v>
+        <v>226.5165415533859</v>
       </c>
       <c r="C218" t="n">
-        <v>226.9760227961096</v>
+        <v>227.2357380227387</v>
       </c>
       <c r="D218" t="n">
-        <v>223.4599680426375</v>
+        <v>224.2490744835724</v>
       </c>
       <c r="E218" t="n">
-        <v>225.0481872558594</v>
+        <v>224.9083404541016</v>
       </c>
       <c r="F218" t="n">
-        <v>98867200</v>
+        <v>75680900</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B219" t="n">
-        <v>226.5165415533859</v>
+        <v>225.7274161885591</v>
       </c>
       <c r="C219" t="n">
-        <v>227.2357380227387</v>
+        <v>227.6652502746616</v>
       </c>
       <c r="D219" t="n">
-        <v>224.2490744835724</v>
+        <v>224.6086728983284</v>
       </c>
       <c r="E219" t="n">
-        <v>224.9083404541016</v>
+        <v>224.7584991455078</v>
       </c>
       <c r="F219" t="n">
-        <v>75680900</v>
+        <v>93678700</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B220" t="n">
-        <v>225.7274161885591</v>
+        <v>220.203597915372</v>
       </c>
       <c r="C220" t="n">
-        <v>227.6652502746616</v>
+        <v>221.3922702798686</v>
       </c>
       <c r="D220" t="n">
-        <v>224.6086728983284</v>
+        <v>218.4455705709327</v>
       </c>
       <c r="E220" t="n">
-        <v>224.7584991455078</v>
+        <v>219.4944000244141</v>
       </c>
       <c r="F220" t="n">
-        <v>93678700</v>
+        <v>103128200</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B221" t="n">
-        <v>220.203597915372</v>
+        <v>221.4222404106533</v>
       </c>
       <c r="C221" t="n">
-        <v>221.3922702798686</v>
+        <v>222.6208961374568</v>
       </c>
       <c r="D221" t="n">
-        <v>218.4455705709327</v>
+        <v>216.5177245976465</v>
       </c>
       <c r="E221" t="n">
-        <v>219.4944000244141</v>
+        <v>217.3168334960938</v>
       </c>
       <c r="F221" t="n">
-        <v>103128200</v>
+        <v>96797300</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B222" t="n">
-        <v>221.4222404106533</v>
+        <v>218.1159423024499</v>
       </c>
       <c r="C222" t="n">
-        <v>222.6208961374568</v>
+        <v>219.6142657707553</v>
       </c>
       <c r="D222" t="n">
-        <v>216.5177245976465</v>
+        <v>215.418963107847</v>
       </c>
       <c r="E222" t="n">
-        <v>217.3168334960938</v>
+        <v>216.6076354980469</v>
       </c>
       <c r="F222" t="n">
-        <v>96797300</v>
+        <v>92457000</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B223" t="n">
-        <v>218.1159423024499</v>
+        <v>218.1758724878036</v>
       </c>
       <c r="C223" t="n">
-        <v>219.6142657707553</v>
+        <v>218.4955221432803</v>
       </c>
       <c r="D223" t="n">
-        <v>215.418963107847</v>
+        <v>214.2602556586216</v>
       </c>
       <c r="E223" t="n">
-        <v>216.6076354980469</v>
+        <v>214.4800109863281</v>
       </c>
       <c r="F223" t="n">
-        <v>92457000</v>
+        <v>98869300</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B224" t="n">
-        <v>218.1758724878036</v>
+        <v>215.2891020611033</v>
       </c>
       <c r="C224" t="n">
-        <v>218.4955221432803</v>
+        <v>215.3490325607492</v>
       </c>
       <c r="D224" t="n">
-        <v>214.2602556586216</v>
+        <v>207.0183577918231</v>
       </c>
       <c r="E224" t="n">
-        <v>214.4800109863281</v>
+        <v>208.2469787597656</v>
       </c>
       <c r="F224" t="n">
-        <v>98869300</v>
+        <v>135187300</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B225" t="n">
-        <v>215.2891020611033</v>
+        <v>210.7941279013131</v>
       </c>
       <c r="C225" t="n">
-        <v>215.3490325607492</v>
+        <v>214.4899893165327</v>
       </c>
       <c r="D225" t="n">
-        <v>207.0183577918231</v>
+        <v>209.8751580258669</v>
       </c>
       <c r="E225" t="n">
-        <v>208.2469787597656</v>
+        <v>212.8118743896484</v>
       </c>
       <c r="F225" t="n">
-        <v>135187300</v>
+        <v>122309000</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B226" t="n">
-        <v>210.7941279013131</v>
+        <v>212.4023240594531</v>
       </c>
       <c r="C226" t="n">
-        <v>214.4899893165327</v>
+        <v>213.3612577394914</v>
       </c>
       <c r="D226" t="n">
-        <v>209.8751580258669</v>
+        <v>208.9961318803605</v>
       </c>
       <c r="E226" t="n">
-        <v>212.8118743896484</v>
+        <v>209.4256591796875</v>
       </c>
       <c r="F226" t="n">
-        <v>122309000</v>
+        <v>179900000</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B227" t="n">
-        <v>212.4023240594531</v>
+        <v>222.6109016432552</v>
       </c>
       <c r="C227" t="n">
-        <v>213.3612577394914</v>
+        <v>230.2123962709879</v>
       </c>
       <c r="D227" t="n">
-        <v>208.9961318803605</v>
+        <v>220.6530857022795</v>
       </c>
       <c r="E227" t="n">
-        <v>209.4256591796875</v>
+        <v>227.7251739501953</v>
       </c>
       <c r="F227" t="n">
-        <v>179900000</v>
+        <v>298909800</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B228" t="n">
-        <v>222.6109016432552</v>
+        <v>227.1058715337123</v>
       </c>
       <c r="C228" t="n">
-        <v>230.2123962709879</v>
+        <v>229.003741733446</v>
       </c>
       <c r="D228" t="n">
-        <v>220.6530857022795</v>
+        <v>216.5676606288883</v>
       </c>
       <c r="E228" t="n">
-        <v>227.7251739501953</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="F228" t="n">
-        <v>298909800</v>
+        <v>195116400</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B229" t="n">
-        <v>227.1058715337123</v>
+        <v>218.6253647857836</v>
       </c>
       <c r="C229" t="n">
-        <v>229.003741733446</v>
+        <v>221.0526567078369</v>
       </c>
       <c r="D229" t="n">
-        <v>216.5676606288883</v>
+        <v>215.9683494434545</v>
       </c>
       <c r="E229" t="n">
-        <v>217.3068389892578</v>
+        <v>220.5332336425781</v>
       </c>
       <c r="F229" t="n">
-        <v>195116400</v>
+        <v>124702700</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B230" t="n">
-        <v>218.6253647857836</v>
+        <v>216.5077444634259</v>
       </c>
       <c r="C230" t="n">
-        <v>221.0526567078369</v>
+        <v>220.1636574397174</v>
       </c>
       <c r="D230" t="n">
-        <v>215.9683494434545</v>
+        <v>214.8595947199138</v>
       </c>
       <c r="E230" t="n">
-        <v>220.5332336425781</v>
+        <v>217.1969757080078</v>
       </c>
       <c r="F230" t="n">
-        <v>124702700</v>
+        <v>109756200</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B231" t="n">
-        <v>216.5077444634259</v>
+        <v>218.5454508199983</v>
       </c>
       <c r="C231" t="n">
-        <v>220.1636574397174</v>
+        <v>227.6952163087265</v>
       </c>
       <c r="D231" t="n">
-        <v>214.8595947199138</v>
+        <v>218.2357997469377</v>
       </c>
       <c r="E231" t="n">
-        <v>217.1969757080078</v>
+        <v>224.1591796875</v>
       </c>
       <c r="F231" t="n">
-        <v>109756200</v>
+        <v>157104700</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B232" t="n">
-        <v>218.5454508199983</v>
+        <v>225.7673797205316</v>
       </c>
       <c r="C232" t="n">
-        <v>227.6952163087265</v>
+        <v>230.1424737915274</v>
       </c>
       <c r="D232" t="n">
-        <v>218.2357997469377</v>
+        <v>224.4987949430455</v>
       </c>
       <c r="E232" t="n">
-        <v>224.1591796875</v>
+        <v>228.1946563720703</v>
       </c>
       <c r="F232" t="n">
-        <v>157104700</v>
+        <v>134681600</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B233" t="n">
-        <v>225.7673797205316</v>
+        <v>230.8317036041433</v>
       </c>
       <c r="C233" t="n">
-        <v>230.1424737915274</v>
+        <v>234.4975997614268</v>
       </c>
       <c r="D233" t="n">
-        <v>224.4987949430455</v>
+        <v>229.3733440032785</v>
       </c>
       <c r="E233" t="n">
-        <v>228.1946563720703</v>
+        <v>230.1025238037109</v>
       </c>
       <c r="F233" t="n">
-        <v>134681600</v>
+        <v>135352400</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B234" t="n">
-        <v>230.8317036041433</v>
+        <v>232.8494477166676</v>
       </c>
       <c r="C234" t="n">
-        <v>234.4975997614268</v>
+        <v>233.4487831783142</v>
       </c>
       <c r="D234" t="n">
-        <v>229.3733440032785</v>
+        <v>224.5986856128386</v>
       </c>
       <c r="E234" t="n">
-        <v>230.1025238037109</v>
+        <v>225.4776916503906</v>
       </c>
       <c r="F234" t="n">
-        <v>135352400</v>
+        <v>122965600</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B235" t="n">
-        <v>232.8494477166676</v>
+        <v>225.0281992525124</v>
       </c>
       <c r="C235" t="n">
-        <v>233.4487831783142</v>
+        <v>225.9271872095504</v>
       </c>
       <c r="D235" t="n">
-        <v>224.5986856128386</v>
+        <v>223.2102414251123</v>
       </c>
       <c r="E235" t="n">
-        <v>225.4776916503906</v>
+        <v>223.4199981689453</v>
       </c>
       <c r="F235" t="n">
-        <v>122965600</v>
+        <v>82955500</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,25 +6553,25 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B236" t="n">
-        <v>225.0281992525124</v>
+        <v>220.5299987792969</v>
       </c>
       <c r="C236" t="n">
-        <v>225.9271872095504</v>
+        <v>220.9900054931641</v>
       </c>
       <c r="D236" t="n">
-        <v>223.2102414251123</v>
+        <v>217.1999969482422</v>
       </c>
       <c r="E236" t="n">
-        <v>223.4199981689453</v>
+        <v>218.3600006103516</v>
       </c>
       <c r="F236" t="n">
-        <v>82955500</v>
+        <v>105768000</v>
       </c>
       <c r="G236" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -6579,25 +6579,25 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B237" t="n">
-        <v>220.5299987792969</v>
+        <v>221.2400054931641</v>
       </c>
       <c r="C237" t="n">
-        <v>220.9900054931641</v>
+        <v>222</v>
       </c>
       <c r="D237" t="n">
-        <v>217.1999969482422</v>
+        <v>218.1499938964844</v>
       </c>
       <c r="E237" t="n">
-        <v>218.3600006103516</v>
+        <v>218.2899932861328</v>
       </c>
       <c r="F237" t="n">
-        <v>105768000</v>
+        <v>89060100</v>
       </c>
       <c r="G237" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B238" t="n">
-        <v>221.2400054931641</v>
+        <v>211.2400054931641</v>
       </c>
       <c r="C238" t="n">
-        <v>222</v>
+        <v>212.7700042724609</v>
       </c>
       <c r="D238" t="n">
-        <v>218.1499938964844</v>
+        <v>208.9299926757812</v>
       </c>
       <c r="E238" t="n">
-        <v>218.2899932861328</v>
+        <v>210.9600067138672</v>
       </c>
       <c r="F238" t="n">
-        <v>89060100</v>
+        <v>132267200</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B239" t="n">
-        <v>211.2400054931641</v>
+        <v>213.3800048828125</v>
       </c>
       <c r="C239" t="n">
-        <v>212.7700042724609</v>
+        <v>213.9400024414062</v>
       </c>
       <c r="D239" t="n">
-        <v>208.9299926757812</v>
+        <v>211.1600036621094</v>
       </c>
       <c r="E239" t="n">
-        <v>210.9600067138672</v>
+        <v>212.1699981689453</v>
       </c>
       <c r="F239" t="n">
-        <v>132267200</v>
+        <v>88059700</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B240" t="n">
-        <v>213.3800048828125</v>
+        <v>214.1399993896484</v>
       </c>
       <c r="C240" t="n">
-        <v>213.9400024414062</v>
+        <v>216.7599945068359</v>
       </c>
       <c r="D240" t="n">
-        <v>211.1600036621094</v>
+        <v>212.5</v>
       </c>
       <c r="E240" t="n">
-        <v>212.1699981689453</v>
+        <v>213.8999938964844</v>
       </c>
       <c r="F240" t="n">
-        <v>88059700</v>
+        <v>96563600</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B241" t="n">
-        <v>214.1399993896484</v>
+        <v>218.3800048828125</v>
       </c>
       <c r="C241" t="n">
-        <v>216.7599945068359</v>
+        <v>219.9100036621094</v>
       </c>
       <c r="D241" t="n">
-        <v>212.5</v>
+        <v>217.1499938964844</v>
       </c>
       <c r="E241" t="n">
-        <v>213.8999938964844</v>
+        <v>219.3399963378906</v>
       </c>
       <c r="F241" t="n">
-        <v>96563600</v>
+        <v>94191300</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B242" t="n">
-        <v>218.3800048828125</v>
+        <v>219.3500061035156</v>
       </c>
       <c r="C242" t="n">
-        <v>219.9100036621094</v>
+        <v>222.7299957275391</v>
       </c>
       <c r="D242" t="n">
-        <v>217.1499938964844</v>
+        <v>218.0299987792969</v>
       </c>
       <c r="E242" t="n">
-        <v>219.3399963378906</v>
+        <v>222.2700042724609</v>
       </c>
       <c r="F242" t="n">
-        <v>94191300</v>
+        <v>190287400</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B243" t="n">
-        <v>219.3500061035156</v>
+        <v>222.9400024414062</v>
       </c>
       <c r="C243" t="n">
-        <v>222.7299957275391</v>
+        <v>228.5</v>
       </c>
       <c r="D243" t="n">
-        <v>218.0299987792969</v>
+        <v>221.5599975585938</v>
       </c>
       <c r="E243" t="n">
-        <v>222.2700042724609</v>
+        <v>227.3800048828125</v>
       </c>
       <c r="F243" t="n">
-        <v>190287400</v>
+        <v>109806100</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B244" t="n">
-        <v>222.9400024414062</v>
+        <v>226.8500061035156</v>
       </c>
       <c r="C244" t="n">
-        <v>228.5</v>
+        <v>229.9799957275391</v>
       </c>
       <c r="D244" t="n">
-        <v>221.5599975585938</v>
+        <v>226.5</v>
       </c>
       <c r="E244" t="n">
-        <v>227.3800048828125</v>
+        <v>228.8699951171875</v>
       </c>
       <c r="F244" t="n">
-        <v>109806100</v>
+        <v>95746700</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B245" t="n">
-        <v>226.8500061035156</v>
+        <v>228.0299987792969</v>
       </c>
       <c r="C245" t="n">
-        <v>229.9799957275391</v>
+        <v>228.9499969482422</v>
       </c>
       <c r="D245" t="n">
-        <v>226.5</v>
+        <v>224.0200042724609</v>
       </c>
       <c r="E245" t="n">
-        <v>228.8699951171875</v>
+        <v>225.5099945068359</v>
       </c>
       <c r="F245" t="n">
-        <v>95746700</v>
+        <v>89547300</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B246" t="n">
-        <v>228.0299987792969</v>
+        <v>222.0800018310547</v>
       </c>
       <c r="C246" t="n">
-        <v>228.9499969482422</v>
+        <v>224.9400024414062</v>
       </c>
       <c r="D246" t="n">
-        <v>224.0200042724609</v>
+        <v>221.0899963378906</v>
       </c>
       <c r="E246" t="n">
-        <v>225.5099945068359</v>
+        <v>224.5800018310547</v>
       </c>
       <c r="F246" t="n">
-        <v>89547300</v>
+        <v>77469900</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B247" t="n">
-        <v>222.0800018310547</v>
+        <v>225.1300048828125</v>
       </c>
       <c r="C247" t="n">
-        <v>224.9400024414062</v>
+        <v>226.9400024414062</v>
       </c>
       <c r="D247" t="n">
-        <v>221.0899963378906</v>
+        <v>223.1300048828125</v>
       </c>
       <c r="E247" t="n">
-        <v>224.5800018310547</v>
+        <v>225.0700073242188</v>
       </c>
       <c r="F247" t="n">
-        <v>77469900</v>
+        <v>89947700</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B248" t="n">
-        <v>225.1300048828125</v>
+        <v>229.75</v>
       </c>
       <c r="C248" t="n">
-        <v>226.9400024414062</v>
+        <v>233.2100067138672</v>
       </c>
       <c r="D248" t="n">
-        <v>223.1300048828125</v>
+        <v>228.0399932861328</v>
       </c>
       <c r="E248" t="n">
-        <v>225.0700073242188</v>
+        <v>228.8600006103516</v>
       </c>
       <c r="F248" t="n">
-        <v>89947700</v>
+        <v>142344300</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B249" t="n">
-        <v>229.75</v>
+        <v>230.9700012207031</v>
       </c>
       <c r="C249" t="n">
-        <v>233.2100067138672</v>
+        <v>232.8200073242188</v>
       </c>
       <c r="D249" t="n">
-        <v>228.0399932861328</v>
+        <v>227.0299987792969</v>
       </c>
       <c r="E249" t="n">
-        <v>228.8600006103516</v>
+        <v>227.2100067138672</v>
       </c>
       <c r="F249" t="n">
-        <v>142344300</v>
+        <v>101494900</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>230.9700012207031</v>
+        <v>229.2700042724609</v>
       </c>
       <c r="C250" t="n">
-        <v>232.8200073242188</v>
+        <v>232.3699951171875</v>
       </c>
       <c r="D250" t="n">
-        <v>227.0299987792969</v>
+        <v>228.1699981689453</v>
       </c>
       <c r="E250" t="n">
-        <v>227.2100067138672</v>
+        <v>228.3800048828125</v>
       </c>
       <c r="F250" t="n">
-        <v>101494900</v>
+        <v>121732200</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B251" t="n">
-        <v>229.2700042724609</v>
+        <v>229.9799957275391</v>
       </c>
       <c r="C251" t="n">
-        <v>232.3699951171875</v>
+        <v>232.2899932861328</v>
       </c>
       <c r="D251" t="n">
-        <v>228.1699981689453</v>
+        <v>228.1600036621094</v>
       </c>
       <c r="E251" t="n">
-        <v>228.3800048828125</v>
+        <v>230.8600006103516</v>
       </c>
       <c r="F251" t="n">
-        <v>121732200</v>
+        <v>98591400</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B252" t="n">
-        <v>229.9799957275391</v>
+        <v>236.0549926757812</v>
       </c>
       <c r="C252" t="n">
-        <v>232.2899932861328</v>
+        <v>237.8699951171875</v>
       </c>
       <c r="D252" t="n">
-        <v>228.1600036621094</v>
+        <v>233.6000061035156</v>
       </c>
       <c r="E252" t="n">
-        <v>230.8600006103516</v>
+        <v>233.9499969482422</v>
       </c>
       <c r="F252" t="n">
-        <v>98369800</v>
+        <v>134470648</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10884,40 +10884,40 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>233.95</v>
+      </c>
+      <c r="D2" t="n">
         <v>230.86</v>
       </c>
-      <c r="D2" t="n">
-        <v>228.38</v>
-      </c>
       <c r="E2" t="n">
-        <v>229.95</v>
+        <v>236.055</v>
       </c>
       <c r="F2" t="n">
-        <v>232.285</v>
+        <v>237.87</v>
       </c>
       <c r="G2" t="n">
-        <v>228.16</v>
+        <v>233.6</v>
       </c>
       <c r="H2" t="n">
-        <v>97538145</v>
+        <v>134470648</v>
       </c>
       <c r="I2" t="n">
         <v>122420392</v>
       </c>
       <c r="J2" t="n">
-        <v>5574576046080</v>
+        <v>5649190617088</v>
       </c>
       <c r="K2" t="n">
-        <v>29.14899</v>
+        <v>29.53914</v>
       </c>
       <c r="L2" t="n">
-        <v>14.709068</v>
+        <v>14.905945</v>
       </c>
       <c r="M2" t="n">
         <v>7.92</v>
       </c>
       <c r="N2" t="n">
-        <v>236.54</v>
+        <v>237.87</v>
       </c>
       <c r="O2" t="n">
         <v>164.27</v>
@@ -10950,7 +10950,7 @@
         <v>9.483000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>24.344618</v>
+        <v>24.670464</v>
       </c>
       <c r="Z2" t="n">
         <v>1.278</v>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-10-02 19:38:24</t>
+          <t>2026-10-03 05:34:27</t>
         </is>
       </c>
     </row>

--- a/data/NVDA_data.xlsx
+++ b/data/NVDA_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B2" t="n">
-        <v>188.7378247179256</v>
+        <v>185.0566294029491</v>
       </c>
       <c r="C2" t="n">
-        <v>189.9050265070322</v>
+        <v>186.7824902019781</v>
       </c>
       <c r="D2" t="n">
-        <v>184.9369333277354</v>
+        <v>182.8918178290645</v>
       </c>
       <c r="E2" t="n">
-        <v>187.1715698242188</v>
+        <v>185.0965270996094</v>
       </c>
       <c r="F2" t="n">
-        <v>137596900</v>
+        <v>157678100</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B3" t="n">
-        <v>185.0566446584491</v>
+        <v>185.7848907820332</v>
       </c>
       <c r="C3" t="n">
-        <v>186.7825055997528</v>
+        <v>188.6081286768816</v>
       </c>
       <c r="D3" t="n">
-        <v>182.8918329061041</v>
+        <v>183.5602249269612</v>
       </c>
       <c r="E3" t="n">
-        <v>185.0965423583984</v>
+        <v>184.5977325439453</v>
       </c>
       <c r="F3" t="n">
-        <v>157678100</v>
+        <v>140088000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B4" t="n">
-        <v>185.7849061389523</v>
+        <v>186.1240974206304</v>
       </c>
       <c r="C4" t="n">
-        <v>188.6081442671687</v>
+        <v>189.1468543796426</v>
       </c>
       <c r="D4" t="n">
-        <v>183.5602400999903</v>
+        <v>186.0941551173159</v>
       </c>
       <c r="E4" t="n">
-        <v>184.5977478027344</v>
+        <v>188.6580200195312</v>
       </c>
       <c r="F4" t="n">
-        <v>140088000</v>
+        <v>130168900</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B5" t="n">
-        <v>186.1240823667868</v>
+        <v>191.7705575158363</v>
       </c>
       <c r="C5" t="n">
-        <v>189.1468390813163</v>
+        <v>194.833227386451</v>
       </c>
       <c r="D5" t="n">
-        <v>186.094140065894</v>
+        <v>190.6033556943829</v>
       </c>
       <c r="E5" t="n">
-        <v>188.6580047607422</v>
+        <v>192.1097564697266</v>
       </c>
       <c r="F5" t="n">
-        <v>130168900</v>
+        <v>182997200</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B6" t="n">
-        <v>191.7705422839889</v>
+        <v>193.0474982342752</v>
       </c>
       <c r="C6" t="n">
-        <v>194.8332119113436</v>
+        <v>195.1524558626357</v>
       </c>
       <c r="D6" t="n">
-        <v>190.6033405552435</v>
+        <v>181.6148965961679</v>
       </c>
       <c r="E6" t="n">
-        <v>192.1097412109375</v>
+        <v>182.7222442626953</v>
       </c>
       <c r="F6" t="n">
-        <v>182997200</v>
+        <v>268774400</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B7" t="n">
-        <v>193.0474821132437</v>
+        <v>187.52074924116</v>
       </c>
       <c r="C7" t="n">
-        <v>195.1524395658232</v>
+        <v>189.6556339904095</v>
       </c>
       <c r="D7" t="n">
-        <v>181.6148814298513</v>
+        <v>185.5155586605101</v>
       </c>
       <c r="E7" t="n">
-        <v>182.7222290039062</v>
+        <v>187.8699188232422</v>
       </c>
       <c r="F7" t="n">
-        <v>268774400</v>
+        <v>153482800</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B8" t="n">
-        <v>187.5207340107304</v>
+        <v>184.3283927796865</v>
       </c>
       <c r="C8" t="n">
-        <v>189.6556185865847</v>
+        <v>184.3583198600852</v>
       </c>
       <c r="D8" t="n">
-        <v>185.5155435929421</v>
+        <v>179.2705030798172</v>
       </c>
       <c r="E8" t="n">
-        <v>187.8699035644531</v>
+        <v>179.5997161865234</v>
       </c>
       <c r="F8" t="n">
-        <v>153482800</v>
+        <v>205641400</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B9" t="n">
-        <v>184.3283927796865</v>
+        <v>184.3583147400375</v>
       </c>
       <c r="C9" t="n">
-        <v>184.3583198600852</v>
+        <v>184.4281395182556</v>
       </c>
       <c r="D9" t="n">
-        <v>179.2705030798172</v>
+        <v>176.866254560341</v>
       </c>
       <c r="E9" t="n">
-        <v>179.5997161865234</v>
+        <v>179.4001922607422</v>
       </c>
       <c r="F9" t="n">
-        <v>205641400</v>
+        <v>214450500</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B10" t="n">
-        <v>184.3583147400375</v>
+        <v>181.7944521048813</v>
       </c>
       <c r="C10" t="n">
-        <v>184.4281395182556</v>
+        <v>182.8419455690647</v>
       </c>
       <c r="D10" t="n">
-        <v>176.866254560341</v>
+        <v>179.3403402174659</v>
       </c>
       <c r="E10" t="n">
-        <v>179.4001922607422</v>
+        <v>181.3754577636719</v>
       </c>
       <c r="F10" t="n">
-        <v>214450500</v>
+        <v>179723300</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B11" t="n">
-        <v>181.7944368108431</v>
+        <v>179.7493465774322</v>
       </c>
       <c r="C11" t="n">
-        <v>182.8419301869027</v>
+        <v>183.6599908268075</v>
       </c>
       <c r="D11" t="n">
-        <v>179.3403251298876</v>
+        <v>179.3203816221287</v>
       </c>
       <c r="E11" t="n">
-        <v>181.3754425048828</v>
+        <v>182.7820892333984</v>
       </c>
       <c r="F11" t="n">
-        <v>179723300</v>
+        <v>173135200</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B12" t="n">
-        <v>179.7493465774322</v>
+        <v>182.6923102950553</v>
       </c>
       <c r="C12" t="n">
-        <v>183.6599908268075</v>
+        <v>184.7573549226016</v>
       </c>
       <c r="D12" t="n">
-        <v>179.3203816221287</v>
+        <v>181.2956472677441</v>
       </c>
       <c r="E12" t="n">
-        <v>182.7820892333984</v>
+        <v>182.2034759521484</v>
       </c>
       <c r="F12" t="n">
-        <v>173135200</v>
+        <v>128544700</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B13" t="n">
-        <v>182.6922949953283</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="C13" t="n">
-        <v>184.7573394499357</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="D13" t="n">
-        <v>181.2956320849819</v>
+        <v>179.3702701372806</v>
       </c>
       <c r="E13" t="n">
-        <v>182.2034606933594</v>
+        <v>180.7270202636719</v>
       </c>
       <c r="F13" t="n">
-        <v>128544700</v>
+        <v>124240200</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B14" t="n">
-        <v>182.3531141136141</v>
+        <v>180.7070509305708</v>
       </c>
       <c r="C14" t="n">
-        <v>182.3531141136141</v>
+        <v>183.0015566720687</v>
       </c>
       <c r="D14" t="n">
-        <v>179.3702701372806</v>
+        <v>176.3375148363812</v>
       </c>
       <c r="E14" t="n">
-        <v>180.7270202636719</v>
+        <v>179.8491058349609</v>
       </c>
       <c r="F14" t="n">
-        <v>124240200</v>
+        <v>162249600</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B15" t="n">
-        <v>180.7070662621498</v>
+        <v>179.988777912505</v>
       </c>
       <c r="C15" t="n">
-        <v>183.0015721983185</v>
+        <v>182.5925403832715</v>
       </c>
       <c r="D15" t="n">
-        <v>176.3375297972393</v>
+        <v>179.3602787988416</v>
       </c>
       <c r="E15" t="n">
-        <v>179.84912109375</v>
+        <v>181.7246246337891</v>
       </c>
       <c r="F15" t="n">
-        <v>162249600</v>
+        <v>111363700</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B16" t="n">
-        <v>179.988793025541</v>
+        <v>183.4006051417061</v>
       </c>
       <c r="C16" t="n">
-        <v>182.5925557149365</v>
+        <v>187.0219340442129</v>
       </c>
       <c r="D16" t="n">
-        <v>179.3602938591047</v>
+        <v>183.0614214202242</v>
       </c>
       <c r="E16" t="n">
-        <v>181.7246398925781</v>
+        <v>185.8148193359375</v>
       </c>
       <c r="F16" t="n">
-        <v>111363700</v>
+        <v>131296700</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B17" t="n">
-        <v>183.400590081168</v>
+        <v>189.5359033209746</v>
       </c>
       <c r="C17" t="n">
-        <v>187.0219186862977</v>
+        <v>191.541093665248</v>
       </c>
       <c r="D17" t="n">
-        <v>183.0614063875393</v>
+        <v>187.979619148197</v>
       </c>
       <c r="E17" t="n">
-        <v>185.8148040771484</v>
+        <v>191.0323181152344</v>
       </c>
       <c r="F17" t="n">
-        <v>131296700</v>
+        <v>153452700</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B18" t="n">
-        <v>189.5359184602369</v>
+        <v>192.5886067715161</v>
       </c>
       <c r="C18" t="n">
-        <v>191.5411089646758</v>
+        <v>202.6644582837766</v>
       </c>
       <c r="D18" t="n">
-        <v>187.9796341631504</v>
+        <v>191.4513320204045</v>
       </c>
       <c r="E18" t="n">
-        <v>191.0323333740234</v>
+        <v>200.5495300292969</v>
       </c>
       <c r="F18" t="n">
-        <v>153452700</v>
+        <v>297986200</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B19" t="n">
-        <v>192.588592118433</v>
+        <v>207.482891187405</v>
       </c>
       <c r="C19" t="n">
-        <v>202.6644428640734</v>
+        <v>211.6828353303786</v>
       </c>
       <c r="D19" t="n">
-        <v>191.4513174538508</v>
+        <v>204.2905427296142</v>
       </c>
       <c r="E19" t="n">
-        <v>200.5495147705078</v>
+        <v>206.5451354980469</v>
       </c>
       <c r="F19" t="n">
-        <v>297986200</v>
+        <v>308829600</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B20" t="n">
-        <v>207.482921843539</v>
+        <v>204.6596525726598</v>
       </c>
       <c r="C20" t="n">
-        <v>211.6828666070652</v>
+        <v>205.6672482532724</v>
       </c>
       <c r="D20" t="n">
-        <v>204.2905729140704</v>
+        <v>200.9286015136062</v>
       </c>
       <c r="E20" t="n">
-        <v>206.545166015625</v>
+        <v>202.4050598144531</v>
       </c>
       <c r="F20" t="n">
-        <v>308829600</v>
+        <v>178864400</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B21" t="n">
-        <v>204.6596680014167</v>
+        <v>205.9565693232556</v>
       </c>
       <c r="C21" t="n">
-        <v>205.6672637579894</v>
+        <v>207.4729406961805</v>
       </c>
       <c r="D21" t="n">
-        <v>200.9286166610889</v>
+        <v>201.5870481318289</v>
       </c>
       <c r="E21" t="n">
-        <v>202.4050750732422</v>
+        <v>202.0060424804688</v>
       </c>
       <c r="F21" t="n">
-        <v>178864400</v>
+        <v>179802200</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B22" t="n">
-        <v>205.9565537660584</v>
+        <v>207.5826726752522</v>
       </c>
       <c r="C22" t="n">
-        <v>207.4729250244422</v>
+        <v>210.8348755139714</v>
       </c>
       <c r="D22" t="n">
-        <v>201.5870329046891</v>
+        <v>205.0686914304077</v>
       </c>
       <c r="E22" t="n">
-        <v>202.0060272216797</v>
+        <v>206.3855438232422</v>
       </c>
       <c r="F22" t="n">
-        <v>179802200</v>
+        <v>180267300</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B23" t="n">
-        <v>207.5826726752522</v>
+        <v>202.5148147488263</v>
       </c>
       <c r="C23" t="n">
-        <v>210.8348755139714</v>
+        <v>203.4824975937368</v>
       </c>
       <c r="D23" t="n">
-        <v>205.0686914304077</v>
+        <v>197.4569251230167</v>
       </c>
       <c r="E23" t="n">
-        <v>206.3855438232422</v>
+        <v>198.2151184082031</v>
       </c>
       <c r="F23" t="n">
-        <v>180267300</v>
+        <v>188919300</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B24" t="n">
-        <v>202.5148147488263</v>
+        <v>198.2949120548774</v>
       </c>
       <c r="C24" t="n">
-        <v>203.4824975937368</v>
+        <v>202.4349867997753</v>
       </c>
       <c r="D24" t="n">
-        <v>197.4569251230167</v>
+        <v>194.1847491650603</v>
       </c>
       <c r="E24" t="n">
-        <v>198.2151184082031</v>
+        <v>194.7434234619141</v>
       </c>
       <c r="F24" t="n">
-        <v>188919300</v>
+        <v>171350300</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B25" t="n">
-        <v>198.2949431289972</v>
+        <v>195.9505251524069</v>
       </c>
       <c r="C25" t="n">
-        <v>202.4350185226721</v>
+        <v>197.1476539294223</v>
       </c>
       <c r="D25" t="n">
-        <v>194.1847795950905</v>
+        <v>185.9345289438528</v>
       </c>
       <c r="E25" t="n">
-        <v>194.7434539794922</v>
+        <v>187.6304626464844</v>
       </c>
       <c r="F25" t="n">
-        <v>171350300</v>
+        <v>223029800</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B26" t="n">
-        <v>195.9505410878136</v>
+        <v>184.4580698535366</v>
       </c>
       <c r="C26" t="n">
-        <v>197.1476699621838</v>
+        <v>187.8699092076593</v>
       </c>
       <c r="D26" t="n">
-        <v>185.9345440647224</v>
+        <v>178.4823961188316</v>
       </c>
       <c r="E26" t="n">
-        <v>187.6304779052734</v>
+        <v>187.7003021240234</v>
       </c>
       <c r="F26" t="n">
-        <v>223029800</v>
+        <v>264942300</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B27" t="n">
-        <v>184.4580698535366</v>
+        <v>194.6436788693004</v>
       </c>
       <c r="C27" t="n">
-        <v>187.8699092076593</v>
+        <v>199.4621367771523</v>
       </c>
       <c r="D27" t="n">
-        <v>178.4823961188316</v>
+        <v>193.3268264223904</v>
       </c>
       <c r="E27" t="n">
-        <v>187.7003021240234</v>
+        <v>198.5742645263672</v>
       </c>
       <c r="F27" t="n">
-        <v>264942300</v>
+        <v>198897100</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B28" t="n">
-        <v>194.6436788693004</v>
+        <v>194.6935535589016</v>
       </c>
       <c r="C28" t="n">
-        <v>199.4621367771523</v>
+        <v>194.9529266552934</v>
       </c>
       <c r="D28" t="n">
-        <v>193.3268264223904</v>
+        <v>190.8427786999811</v>
       </c>
       <c r="E28" t="n">
-        <v>198.5742645263672</v>
+        <v>192.6983337402344</v>
       </c>
       <c r="F28" t="n">
-        <v>198897100</v>
+        <v>176483300</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B29" t="n">
-        <v>194.6935535589016</v>
+        <v>195.2522164876445</v>
       </c>
       <c r="C29" t="n">
-        <v>194.9529266552934</v>
+        <v>195.4218083488666</v>
       </c>
       <c r="D29" t="n">
-        <v>190.8427786999811</v>
+        <v>190.673190567689</v>
       </c>
       <c r="E29" t="n">
-        <v>192.6983337402344</v>
+        <v>193.3368072509766</v>
       </c>
       <c r="F29" t="n">
-        <v>176483300</v>
+        <v>154935300</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B30" t="n">
-        <v>195.2522318976041</v>
+        <v>190.5933947337238</v>
       </c>
       <c r="C30" t="n">
-        <v>195.4218237722109</v>
+        <v>190.9824620272586</v>
       </c>
       <c r="D30" t="n">
-        <v>190.6732056162565</v>
+        <v>183.4106057333689</v>
       </c>
       <c r="E30" t="n">
-        <v>193.3368225097656</v>
+        <v>186.4134063720703</v>
       </c>
       <c r="F30" t="n">
-        <v>154935300</v>
+        <v>207423100</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B31" t="n">
-        <v>190.5933635318434</v>
+        <v>182.4229582335574</v>
       </c>
       <c r="C31" t="n">
-        <v>190.9824307616844</v>
+        <v>190.5534733337414</v>
       </c>
       <c r="D31" t="n">
-        <v>183.4105757073767</v>
+        <v>180.1484087383153</v>
       </c>
       <c r="E31" t="n">
-        <v>186.4133758544922</v>
+        <v>189.7154846191406</v>
       </c>
       <c r="F31" t="n">
-        <v>207423100</v>
+        <v>186591900</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B32" t="n">
-        <v>182.4229435613052</v>
+        <v>185.5255382862568</v>
       </c>
       <c r="C32" t="n">
-        <v>190.553458007553</v>
+        <v>188.5482954559393</v>
       </c>
       <c r="D32" t="n">
-        <v>180.1483942490048</v>
+        <v>183.879487827554</v>
       </c>
       <c r="E32" t="n">
-        <v>189.7154693603516</v>
+        <v>186.1540374755859</v>
       </c>
       <c r="F32" t="n">
-        <v>186591900</v>
+        <v>173628900</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B33" t="n">
-        <v>185.525507871713</v>
+        <v>182.941705155915</v>
       </c>
       <c r="C33" t="n">
-        <v>188.5482645458532</v>
+        <v>184.3583093626339</v>
       </c>
       <c r="D33" t="n">
-        <v>183.8794576828592</v>
+        <v>179.2206093334711</v>
       </c>
       <c r="E33" t="n">
-        <v>186.1540069580078</v>
+        <v>180.9265289306641</v>
       </c>
       <c r="F33" t="n">
-        <v>173628900</v>
+        <v>213598900</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B34" t="n">
-        <v>182.941705155915</v>
+        <v>184.3483273978252</v>
       </c>
       <c r="C34" t="n">
-        <v>184.3583093626339</v>
+        <v>187.4109971087465</v>
       </c>
       <c r="D34" t="n">
-        <v>179.2206093334711</v>
+        <v>182.3930205111681</v>
       </c>
       <c r="E34" t="n">
-        <v>180.9265289306641</v>
+        <v>186.0742034912109</v>
       </c>
       <c r="F34" t="n">
-        <v>213598900</v>
+        <v>247246400</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B35" t="n">
-        <v>184.3483122805645</v>
+        <v>195.4816571057099</v>
       </c>
       <c r="C35" t="n">
-        <v>187.4109817403353</v>
+        <v>195.5315406452363</v>
       </c>
       <c r="D35" t="n">
-        <v>182.39300555425</v>
+        <v>179.4201468289569</v>
       </c>
       <c r="E35" t="n">
-        <v>186.0741882324219</v>
+        <v>180.208251953125</v>
       </c>
       <c r="F35" t="n">
-        <v>247246400</v>
+        <v>343504800</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B36" t="n">
-        <v>195.4816571057099</v>
+        <v>180.8068289121023</v>
       </c>
       <c r="C36" t="n">
-        <v>195.5315406452363</v>
+        <v>184.1188859589464</v>
       </c>
       <c r="D36" t="n">
-        <v>179.4201468289569</v>
+        <v>172.5166776199441</v>
       </c>
       <c r="E36" t="n">
-        <v>180.208251953125</v>
+        <v>178.4524688720703</v>
       </c>
       <c r="F36" t="n">
-        <v>343504800</v>
+        <v>346926200</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B37" t="n">
-        <v>180.8068289121023</v>
+        <v>179.0609943264491</v>
       </c>
       <c r="C37" t="n">
-        <v>184.1188859589464</v>
+        <v>183.0614042749852</v>
       </c>
       <c r="D37" t="n">
-        <v>172.5166776199441</v>
+        <v>176.0581789881563</v>
       </c>
       <c r="E37" t="n">
-        <v>178.4524688720703</v>
+        <v>182.1136779785156</v>
       </c>
       <c r="F37" t="n">
-        <v>346926200</v>
+        <v>256618300</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B38" t="n">
-        <v>179.0610243324759</v>
+        <v>174.4919707447618</v>
       </c>
       <c r="C38" t="n">
-        <v>183.0614349513779</v>
+        <v>177.734203281764</v>
       </c>
       <c r="D38" t="n">
-        <v>176.0582084909882</v>
+        <v>169.1447804748437</v>
       </c>
       <c r="E38" t="n">
-        <v>182.1137084960938</v>
+        <v>177.39501953125</v>
       </c>
       <c r="F38" t="n">
-        <v>256618300</v>
+        <v>320600300</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B39" t="n">
-        <v>174.4919407266003</v>
+        <v>181.1958985688627</v>
       </c>
       <c r="C39" t="n">
-        <v>177.7341727058355</v>
+        <v>182.4728380763597</v>
       </c>
       <c r="D39" t="n">
-        <v>169.1447513765687</v>
+        <v>177.8140014756398</v>
       </c>
       <c r="E39" t="n">
-        <v>177.3949890136719</v>
+        <v>179.8291625976562</v>
       </c>
       <c r="F39" t="n">
-        <v>320600300</v>
+        <v>183852000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B40" t="n">
-        <v>181.1958985688627</v>
+        <v>178.5821558989869</v>
       </c>
       <c r="C40" t="n">
-        <v>182.4728380763597</v>
+        <v>178.8614854738169</v>
       </c>
       <c r="D40" t="n">
-        <v>177.8140014756398</v>
+        <v>176.0781603452176</v>
       </c>
       <c r="E40" t="n">
-        <v>179.8291625976562</v>
+        <v>176.5769653320312</v>
       </c>
       <c r="F40" t="n">
-        <v>183852000</v>
+        <v>121332800</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B41" t="n">
-        <v>178.5821404669205</v>
+        <v>174.3423041351479</v>
       </c>
       <c r="C41" t="n">
-        <v>178.8614700176124</v>
+        <v>179.8690716163194</v>
       </c>
       <c r="D41" t="n">
-        <v>176.0781451295325</v>
+        <v>173.2648835948944</v>
       </c>
       <c r="E41" t="n">
-        <v>176.5769500732422</v>
+        <v>179.4899749755859</v>
       </c>
       <c r="F41" t="n">
-        <v>121332800</v>
+        <v>188131000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B42" t="n">
-        <v>174.3423041351479</v>
+        <v>181.325561672047</v>
       </c>
       <c r="C42" t="n">
-        <v>179.8690716163194</v>
+        <v>185.2162492379485</v>
       </c>
       <c r="D42" t="n">
-        <v>173.2648835948944</v>
+        <v>179.5697738081794</v>
       </c>
       <c r="E42" t="n">
-        <v>179.4899749755859</v>
+        <v>181.0262908935547</v>
       </c>
       <c r="F42" t="n">
-        <v>188131000</v>
+        <v>182632200</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B43" t="n">
-        <v>181.3255769560617</v>
+        <v>180.6472109015755</v>
       </c>
       <c r="C43" t="n">
-        <v>185.2162648499111</v>
+        <v>182.0139316568558</v>
       </c>
       <c r="D43" t="n">
-        <v>179.569788944198</v>
+        <v>178.681918089591</v>
       </c>
       <c r="E43" t="n">
-        <v>181.0263061523438</v>
+        <v>179.1607666015625</v>
       </c>
       <c r="F43" t="n">
-        <v>182632200</v>
+        <v>165138000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,25 +1561,25 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B44" t="n">
-        <v>180.6472109015755</v>
+        <v>181.1959881613664</v>
       </c>
       <c r="C44" t="n">
-        <v>182.0139316568558</v>
+        <v>184.089227004522</v>
       </c>
       <c r="D44" t="n">
-        <v>178.681918089591</v>
+        <v>179.5398751387779</v>
       </c>
       <c r="E44" t="n">
-        <v>179.1607666015625</v>
+        <v>182.9518890380859</v>
       </c>
       <c r="F44" t="n">
-        <v>165138000</v>
+        <v>167364900</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1587,25 +1587,25 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B45" t="n">
-        <v>181.1960032737075</v>
+        <v>183.4606866221248</v>
       </c>
       <c r="C45" t="n">
-        <v>184.0892423581687</v>
+        <v>184.2288932293168</v>
       </c>
       <c r="D45" t="n">
-        <v>179.5398901129937</v>
+        <v>180.4876480440623</v>
       </c>
       <c r="E45" t="n">
-        <v>182.951904296875</v>
+        <v>181.9841461181641</v>
       </c>
       <c r="F45" t="n">
-        <v>167364900</v>
+        <v>143971100</v>
       </c>
       <c r="G45" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B46" t="n">
-        <v>183.4607020047171</v>
+        <v>182.2136112701494</v>
       </c>
       <c r="C46" t="n">
-        <v>184.2289086763207</v>
+        <v>187.5610985176648</v>
       </c>
       <c r="D46" t="n">
-        <v>180.4876631773748</v>
+        <v>181.9741660895743</v>
       </c>
       <c r="E46" t="n">
-        <v>181.9841613769531</v>
+        <v>185.1168212890625</v>
       </c>
       <c r="F46" t="n">
-        <v>143971100</v>
+        <v>204378100</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B47" t="n">
-        <v>182.2136112701494</v>
+        <v>185.12679644575</v>
       </c>
       <c r="C47" t="n">
-        <v>187.5610985176648</v>
+        <v>185.2864265695677</v>
       </c>
       <c r="D47" t="n">
-        <v>181.9741660895743</v>
+        <v>182.8920356049676</v>
       </c>
       <c r="E47" t="n">
-        <v>185.1168212890625</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="F47" t="n">
-        <v>204378100</v>
+        <v>144719700</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B48" t="n">
-        <v>185.1268117532098</v>
+        <v>184.5381918075859</v>
       </c>
       <c r="C48" t="n">
-        <v>185.2864418902268</v>
+        <v>185.0469957406681</v>
       </c>
       <c r="D48" t="n">
-        <v>182.8920507276432</v>
+        <v>181.6150239281505</v>
       </c>
       <c r="E48" t="n">
-        <v>184.5381927490234</v>
+        <v>183.3509674072266</v>
       </c>
       <c r="F48" t="n">
-        <v>144719700</v>
+        <v>162785400</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B49" t="n">
-        <v>184.538176449994</v>
+        <v>179.8591376409278</v>
       </c>
       <c r="C49" t="n">
-        <v>185.0469803407326</v>
+        <v>180.896718300432</v>
       </c>
       <c r="D49" t="n">
-        <v>181.6150088138297</v>
+        <v>176.2076782062319</v>
       </c>
       <c r="E49" t="n">
-        <v>183.3509521484375</v>
+        <v>180.5076141357422</v>
       </c>
       <c r="F49" t="n">
-        <v>162785400</v>
+        <v>182136600</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B50" t="n">
-        <v>179.8591224369562</v>
+        <v>180.6871989054384</v>
       </c>
       <c r="C50" t="n">
-        <v>180.8967030087509</v>
+        <v>182.3932136047752</v>
       </c>
       <c r="D50" t="n">
-        <v>176.2076633109278</v>
+        <v>174.2123443447362</v>
       </c>
       <c r="E50" t="n">
-        <v>180.5075988769531</v>
+        <v>174.6114196777344</v>
       </c>
       <c r="F50" t="n">
-        <v>182136600</v>
+        <v>204274900</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B51" t="n">
-        <v>180.6871831157045</v>
+        <v>177.5245903328353</v>
       </c>
       <c r="C51" t="n">
-        <v>182.3931976659576</v>
+        <v>178.0034654802094</v>
       </c>
       <c r="D51" t="n">
-        <v>174.2123291208211</v>
+        <v>174.6213802569945</v>
       </c>
       <c r="E51" t="n">
-        <v>174.6114044189453</v>
+        <v>175.8784332275391</v>
       </c>
       <c r="F51" t="n">
-        <v>204274900</v>
+        <v>164775600</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B52" t="n">
-        <v>177.5245903328353</v>
+        <v>175.8485012773324</v>
       </c>
       <c r="C52" t="n">
-        <v>178.0034654802094</v>
+        <v>178.0733061224419</v>
       </c>
       <c r="D52" t="n">
-        <v>174.6213802569945</v>
+        <v>174.4916756985292</v>
       </c>
       <c r="E52" t="n">
-        <v>175.8784332275391</v>
+        <v>177.3050994873047</v>
       </c>
       <c r="F52" t="n">
-        <v>164775600</v>
+        <v>148588100</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B53" t="n">
-        <v>175.8485164107673</v>
+        <v>175.6888968536916</v>
       </c>
       <c r="C53" t="n">
-        <v>178.0733214473424</v>
+        <v>175.7188256001934</v>
       </c>
       <c r="D53" t="n">
-        <v>174.4916907151964</v>
+        <v>169.9124052081842</v>
       </c>
       <c r="E53" t="n">
-        <v>177.3051147460938</v>
+        <v>170.5409393310547</v>
       </c>
       <c r="F53" t="n">
-        <v>148588100</v>
+        <v>222775500</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B54" t="n">
-        <v>175.6888968536916</v>
+        <v>174.1225483861358</v>
       </c>
       <c r="C54" t="n">
-        <v>175.7188256001934</v>
+        <v>175.7387615308714</v>
       </c>
       <c r="D54" t="n">
-        <v>169.9124052081842</v>
+        <v>171.4188835631069</v>
       </c>
       <c r="E54" t="n">
-        <v>170.5409393310547</v>
+        <v>173.7334594726562</v>
       </c>
       <c r="F54" t="n">
-        <v>222775500</v>
+        <v>176096000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B55" t="n">
-        <v>174.1225483861358</v>
+        <v>176.2575523358494</v>
       </c>
       <c r="C55" t="n">
-        <v>175.7387615308714</v>
+        <v>181.0263919449467</v>
       </c>
       <c r="D55" t="n">
-        <v>171.4188835631069</v>
+        <v>175.9283209122297</v>
       </c>
       <c r="E55" t="n">
-        <v>173.7334594726562</v>
+        <v>180.5674743652344</v>
       </c>
       <c r="F55" t="n">
-        <v>176096000</v>
+        <v>324925900</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B56" t="n">
-        <v>176.2575523358494</v>
+        <v>183.4906282252173</v>
       </c>
       <c r="C56" t="n">
-        <v>181.0263919449467</v>
+        <v>183.7300734141942</v>
       </c>
       <c r="D56" t="n">
-        <v>175.9283209122297</v>
+        <v>181.9243013805983</v>
       </c>
       <c r="E56" t="n">
-        <v>180.5674743652344</v>
+        <v>183.2611694335938</v>
       </c>
       <c r="F56" t="n">
-        <v>324925900</v>
+        <v>129064400</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B57" t="n">
-        <v>183.4906129473229</v>
+        <v>182.5428423541149</v>
       </c>
       <c r="C57" t="n">
-        <v>183.730058116363</v>
+        <v>188.8879950077845</v>
       </c>
       <c r="D57" t="n">
-        <v>181.9242862331203</v>
+        <v>182.4729984678863</v>
       </c>
       <c r="E57" t="n">
-        <v>183.2611541748047</v>
+        <v>188.7682800292969</v>
       </c>
       <c r="F57" t="n">
-        <v>129064400</v>
+        <v>174873600</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B58" t="n">
-        <v>182.5428571096804</v>
+        <v>187.5012437217294</v>
       </c>
       <c r="C58" t="n">
-        <v>188.8880102762506</v>
+        <v>188.4689804086018</v>
       </c>
       <c r="D58" t="n">
-        <v>182.4730132178061</v>
+        <v>186.154389299292</v>
       </c>
       <c r="E58" t="n">
-        <v>188.7682952880859</v>
+        <v>188.169677734375</v>
       </c>
       <c r="F58" t="n">
-        <v>174873600</v>
+        <v>65528500</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B59" t="n">
-        <v>187.5012437217294</v>
+        <v>189.4766285187414</v>
       </c>
       <c r="C59" t="n">
-        <v>188.4689804086018</v>
+        <v>192.240166195598</v>
       </c>
       <c r="D59" t="n">
-        <v>186.154389299292</v>
+        <v>187.5611125998212</v>
       </c>
       <c r="E59" t="n">
-        <v>188.169677734375</v>
+        <v>190.085205078125</v>
       </c>
       <c r="F59" t="n">
-        <v>65528500</v>
+        <v>139740300</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B60" t="n">
-        <v>189.4766133088049</v>
+        <v>187.2717899684254</v>
       </c>
       <c r="C60" t="n">
-        <v>192.2401507638228</v>
+        <v>188.3193265216257</v>
       </c>
       <c r="D60" t="n">
-        <v>187.5610975436497</v>
+        <v>185.4759890979627</v>
       </c>
       <c r="E60" t="n">
-        <v>190.0851898193359</v>
+        <v>187.7805938720703</v>
       </c>
       <c r="F60" t="n">
-        <v>139740300</v>
+        <v>120006100</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B61" t="n">
-        <v>187.2717899684254</v>
+        <v>187.8005508490403</v>
       </c>
       <c r="C61" t="n">
-        <v>188.3193265216257</v>
+        <v>188.5487999407664</v>
       </c>
       <c r="D61" t="n">
-        <v>185.4759890979627</v>
+        <v>186.4935963146986</v>
       </c>
       <c r="E61" t="n">
-        <v>187.7805938720703</v>
+        <v>187.1021728515625</v>
       </c>
       <c r="F61" t="n">
-        <v>120006100</v>
+        <v>97687300</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B62" t="n">
-        <v>187.8005508490403</v>
+        <v>189.1274459397885</v>
       </c>
       <c r="C62" t="n">
-        <v>188.5487999407664</v>
+        <v>190.1151249886817</v>
       </c>
       <c r="D62" t="n">
-        <v>186.4935963146986</v>
+        <v>186.0546345387688</v>
       </c>
       <c r="E62" t="n">
-        <v>187.1021728515625</v>
+        <v>186.0646057128906</v>
       </c>
       <c r="F62" t="n">
-        <v>97687300</v>
+        <v>120100500</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B63" t="n">
-        <v>189.127461449755</v>
+        <v>189.3968130035911</v>
       </c>
       <c r="C63" t="n">
-        <v>190.1151405796458</v>
+        <v>192.4795957147097</v>
       </c>
       <c r="D63" t="n">
-        <v>186.0546497967401</v>
+        <v>187.8204997023152</v>
       </c>
       <c r="E63" t="n">
-        <v>186.0646209716797</v>
+        <v>188.4091339111328</v>
       </c>
       <c r="F63" t="n">
-        <v>120100500</v>
+        <v>148240500</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B64" t="n">
-        <v>189.3967976648124</v>
+        <v>191.3123182227279</v>
       </c>
       <c r="C64" t="n">
-        <v>192.479580126264</v>
+        <v>193.1779629368336</v>
       </c>
       <c r="D64" t="n">
-        <v>187.8204844911982</v>
+        <v>185.7154145267434</v>
       </c>
       <c r="E64" t="n">
-        <v>188.4091186523438</v>
+        <v>187.6808166503906</v>
       </c>
       <c r="F64" t="n">
-        <v>148240500</v>
+        <v>183529700</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B65" t="n">
-        <v>191.3123337767646</v>
+        <v>190.0752284670132</v>
       </c>
       <c r="C65" t="n">
-        <v>193.1779786425506</v>
+        <v>191.7213703933745</v>
       </c>
       <c r="D65" t="n">
-        <v>185.7154296257417</v>
+        <v>186.3838692947835</v>
       </c>
       <c r="E65" t="n">
-        <v>187.6808319091797</v>
+        <v>186.8028869628906</v>
       </c>
       <c r="F65" t="n">
-        <v>183529700</v>
+        <v>176862600</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B66" t="n">
-        <v>190.0752284670132</v>
+        <v>188.1297854095839</v>
       </c>
       <c r="C66" t="n">
-        <v>191.7213703933745</v>
+        <v>190.9232365533545</v>
       </c>
       <c r="D66" t="n">
-        <v>186.3838692947835</v>
+        <v>186.1244680675316</v>
       </c>
       <c r="E66" t="n">
-        <v>186.8028869628906</v>
+        <v>188.6685180664062</v>
       </c>
       <c r="F66" t="n">
-        <v>176862600</v>
+        <v>153543200</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B67" t="n">
-        <v>188.1297701943655</v>
+        <v>188.6685228499072</v>
       </c>
       <c r="C67" t="n">
-        <v>190.9232211122124</v>
+        <v>189.1074981045344</v>
       </c>
       <c r="D67" t="n">
-        <v>186.1244530144955</v>
+        <v>183.2811352524241</v>
       </c>
       <c r="E67" t="n">
-        <v>188.6685028076172</v>
+        <v>184.6080169677734</v>
       </c>
       <c r="F67" t="n">
-        <v>153543200</v>
+        <v>172457000</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B68" t="n">
-        <v>188.6685228499072</v>
+        <v>184.6479238968445</v>
       </c>
       <c r="C68" t="n">
-        <v>189.1074981045344</v>
+        <v>185.9049768874807</v>
       </c>
       <c r="D68" t="n">
-        <v>183.2811352524241</v>
+        <v>183.2412119543349</v>
       </c>
       <c r="E68" t="n">
-        <v>184.6080169677734</v>
+        <v>184.4284362792969</v>
       </c>
       <c r="F68" t="n">
-        <v>172457000</v>
+        <v>131327500</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B69" t="n">
-        <v>184.6479238968445</v>
+        <v>182.7922691735387</v>
       </c>
       <c r="C69" t="n">
-        <v>185.9049768874807</v>
+        <v>186.6831584288149</v>
       </c>
       <c r="D69" t="n">
-        <v>183.2412119543349</v>
+        <v>182.5927391235801</v>
       </c>
       <c r="E69" t="n">
-        <v>184.4284362792969</v>
+        <v>184.5082550048828</v>
       </c>
       <c r="F69" t="n">
-        <v>131327500</v>
+        <v>137968500</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B70" t="n">
-        <v>182.7922691735387</v>
+        <v>184.5680989064521</v>
       </c>
       <c r="C70" t="n">
-        <v>186.6831584288149</v>
+        <v>187.6708389078061</v>
       </c>
       <c r="D70" t="n">
-        <v>182.5927391235801</v>
+        <v>182.9718281779948</v>
       </c>
       <c r="E70" t="n">
-        <v>184.5082550048828</v>
+        <v>185.3762054443359</v>
       </c>
       <c r="F70" t="n">
-        <v>137968500</v>
+        <v>160128900</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B71" t="n">
-        <v>184.5681140987238</v>
+        <v>183.8897012556695</v>
       </c>
       <c r="C71" t="n">
-        <v>187.6708543554723</v>
+        <v>184.0293738083791</v>
       </c>
       <c r="D71" t="n">
-        <v>182.9718432388734</v>
+        <v>180.3779146434709</v>
       </c>
       <c r="E71" t="n">
-        <v>185.376220703125</v>
+        <v>182.7124481201172</v>
       </c>
       <c r="F71" t="n">
-        <v>160128900</v>
+        <v>159586100</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B72" t="n">
-        <v>183.8897012556695</v>
+        <v>186.0646079796491</v>
       </c>
       <c r="C72" t="n">
-        <v>184.0293738083791</v>
+        <v>189.2571344016907</v>
       </c>
       <c r="D72" t="n">
-        <v>180.3779146434709</v>
+        <v>185.895006678512</v>
       </c>
       <c r="E72" t="n">
-        <v>182.7124481201172</v>
+        <v>186.6133270263672</v>
       </c>
       <c r="F72" t="n">
-        <v>159586100</v>
+        <v>206188600</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B73" t="n">
-        <v>186.0646079796491</v>
+        <v>188.6385950815971</v>
       </c>
       <c r="C73" t="n">
-        <v>189.2571344016907</v>
+        <v>189.99542